--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Elements_hybrides" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Noeuds_stockage" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Resume_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Template_est_2p5m" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -108,6 +109,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -577,6 +579,20 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mise a jour: bande est 2.5 m avec arbres modelisee en mode tranchee drainante + underdrain (E01/E02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Le gabarit de section est dans Template_est_2p5m; micro-noue de surface + underdrain en emprise contrainte.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -591,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1050,6 +1066,206 @@
       <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Volume tampon noeud = Qin*temps</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>East_strip_total_width_m</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Largeur bande verte est disponible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>East_surface_depression_width_m</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Largeur depression superficielle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>East_surface_depression_depth_m</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Profondeur depression de surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>East_tree_soil_zone_width_m</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Zone sol vegetal / arbres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>East_underdrain_trench_width_m</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Largeur tranchee drainante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>East_underdrain_trench_depth_m</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Profondeur tranchee drainante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>East_underdrain_pipe_diameter_mm</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Diametre perforé recommandé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>East_root_barrier_offset_m</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Distance cible entre conduite et tronc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>East_cleanout_spacing_m</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Espacement regards/cleanouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>East_underdrain_slope_m_per_m</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>m/m</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Pente longitudinale de l underdrain.</t>
         </is>
       </c>
     </row>
@@ -5989,7 +6205,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>TRENCH</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -6010,26 +6226,33 @@
       <c r="F4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>0.01</v>
+      <c r="G4" s="7">
+        <f>Inputs!$B$33</f>
+        <v/>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
       <c r="I4" s="8">
         <f>IF(A4="","",IF(H4&lt;&gt;"",H4,IF(UPPER(TRIM(B4))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B4))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J4" s="7" t="inlineStr"/>
-      <c r="K4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>0.3</v>
+      <c r="J4" s="7">
+        <f>Inputs!$B$30</f>
+        <v/>
+      </c>
+      <c r="K4" s="7">
+        <f>Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="L4" s="7">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="M4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N4" s="7">
+        <f>Inputs!$B$22</f>
+        <v/>
       </c>
       <c r="O4" s="8">
         <f>IF(A4="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A4))</f>
@@ -6085,7 +6308,7 @@
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Noue est amont (zone arbres)</t>
+          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6320,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>TRENCH</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6118,26 +6341,33 @@
       <c r="F5" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>0.01</v>
+      <c r="G5" s="7">
+        <f>Inputs!$B$33</f>
+        <v/>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="8">
         <f>IF(A5="","",IF(H5&lt;&gt;"",H5,IF(UPPER(TRIM(B5))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B5))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>0.3</v>
+      <c r="J5" s="7">
+        <f>Inputs!$B$30</f>
+        <v/>
+      </c>
+      <c r="K5" s="7">
+        <f>Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="L5" s="7">
+        <f>Inputs!$B$29</f>
+        <v/>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <f>Inputs!$B$22</f>
+        <v/>
       </c>
       <c r="O5" s="8">
         <f>IF(A5="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A5))</f>
@@ -6193,7 +6423,7 @@
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Noue est aval</t>
+          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.</t>
         </is>
       </c>
     </row>
@@ -6339,14 +6569,17 @@
         <v/>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>3</v>
+      <c r="K7" s="7">
+        <f>Inputs!$B$25</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>Inputs!$B$26</f>
+        <v/>
+      </c>
+      <c r="M7" s="7">
+        <f>Inputs!$B$20</f>
+        <v/>
       </c>
       <c r="N7" s="7" t="n">
         <v>0</v>
@@ -6405,7 +6638,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue sud recevant toiture</t>
+          <t>Noue sud peu profonde (collecte toiture/tresfond sud).</t>
         </is>
       </c>
     </row>
@@ -27472,4 +27705,321 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GABARIT BANDE EST 2.5 m (ARBRES) - SOLUTION HYBRIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Composante</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Largeur m</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Profondeur m</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Parametre</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Unite</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Volume utile m3/m</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Depression de surface (micro-noue)</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>Inputs!$B$25</f>
+        <v/>
+      </c>
+      <c r="C4" s="5">
+        <f>Inputs!$B$26</f>
+        <v/>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Storage_surface_m3_per_m</t>
+        </is>
+      </c>
+      <c r="E4" s="5">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>m3/m</t>
+        </is>
+      </c>
+      <c r="G4" s="9">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Captation initiale / pretaitement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Tranchee drainante (sous-sol)</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>Inputs!$B$29</f>
+        <v/>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Porosite</t>
+        </is>
+      </c>
+      <c r="E5" s="5">
+        <f>Inputs!$B$22</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>B5*C5*E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Conveyance + stockage utile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sous-total stockage</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Storage_total_m3_per_m</t>
+        </is>
+      </c>
+      <c r="E6" s="5">
+        <f>G4+G5</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>m3/m</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>G4+G5</f>
+        <v/>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Base dimensionnement lineaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Underdrain perforé</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Diametre_pipe_mm</t>
+        </is>
+      </c>
+      <c r="E7" s="5">
+        <f>Inputs!$B$30</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PVC/PEHD perforé, pente Inputs!B33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Espacement cleanout</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Spacing_m</t>
+        </is>
+      </c>
+      <c r="E8" s="5">
+        <f>Inputs!$B$32</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Aux changements de direction et max 25-30 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Offset barriere racinaire</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Offset_m</t>
+        </is>
+      </c>
+      <c r="E9" s="5">
+        <f>Inputs!$B$31</f>
+        <v/>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Eloigner la conduite de la zone tronc/racines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Controle rapide capacite lineaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Longueur active bande est (m)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>(input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Stockage lineaire m3/m</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="C13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Stockage total disponible m3</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <f>B12*B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Noeuds_stockage" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Resume_checks" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Template_est_2p5m" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Convention_labels" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -590,6 +591,13 @@
       <c r="A18" t="inlineStr">
         <is>
           <t>Le gabarit de section est dans Template_est_2p5m; micro-noue de surface + underdrain en emprise contrainte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Labels harmonises: placeholders remplaces par P-01/P-02/P-03 et jonctions explicites (voir Convention_labels).</t>
         </is>
       </c>
     </row>
@@ -1303,6 +1311,13 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ZONES TRIBUTAIRES - TOIT / TRESFOND / VERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Routing des zones se fait via Element_ID (colonne J), independamment du renommage des noeuds.</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6225,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -6308,7 +6323,7 @@
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.</t>
+          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6340,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -6423,7 +6438,7 @@
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.</t>
+          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6455,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>BASIN_IN</t>
+          <t>J-BASSIN-IN</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -6527,7 +6542,7 @@
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Collecteur vers bassin</t>
+          <t>Collecteur vers bassin; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6544,12 +6559,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>S_EAST</t>
+          <t>J-SUD-EST</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>S_MID</t>
+          <t>J-SUD-OUEST</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6638,7 +6653,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue sud peu profonde (collecte toiture/tresfond sud).</t>
+          <t>Noue sud peu profonde (collecte toiture/tresfond sud).; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6670,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>W_UP</t>
+          <t>J-OUEST-AMONT</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>W_LOW</t>
+          <t>J-OUEST-AVAL</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -6746,7 +6761,7 @@
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Tranchee drainante ouest</t>
+          <t>Tranchee drainante ouest; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6778,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>W_LOW</t>
+          <t>J-OUEST-AVAL</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>BASIN_IN</t>
+          <t>J-BASSIN-IN</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -6850,7 +6865,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Branche ouest vers bassin</t>
+          <t>Branche ouest vers bassin; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6882,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>BASIN_IN</t>
+          <t>J-BASSIN-IN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BASIN_RET</t>
+          <t>BASSIN-RET</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -6950,7 +6965,7 @@
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Troncon final au bassin</t>
+          <t>Troncon final au bassin; Labels projet harmonises (2026-07-02).</t>
         </is>
       </c>
     </row>
@@ -21419,7 +21434,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -21466,7 +21481,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -21513,7 +21528,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -21560,7 +21575,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>S_EAST</t>
+          <t>J-SUD-EST</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -21609,7 +21624,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>S_MID</t>
+          <t>J-SUD-OUEST</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -21658,7 +21673,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>W_UP</t>
+          <t>J-OUEST-AMONT</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -21705,7 +21720,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>W_LOW</t>
+          <t>J-OUEST-AVAL</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -21752,7 +21767,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>BASIN_IN</t>
+          <t>J-BASSIN-IN</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -21799,7 +21814,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BASIN_RET</t>
+          <t>BASSIN-RET</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -28022,4 +28037,305 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CONVENTION DE NOMMAGE - MODELE HYBRIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Label projet</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Role hydraulique</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Noeud amont est</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Puisard/CB existant amont</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>P-02</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Noeud intermediaire est</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Puisard/CB milieu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>P-03</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Noeud aval est</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Puisard/CB aval</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>S_EAST</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>J-SUD-EST</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SWALE_NODE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Jonction sud est</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Point de collecte sud est</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>S_MID</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>J-SUD-OUEST</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SWALE_NODE</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Jonction sud ouest</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Point de rassemblement sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>W_UP</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AMONT</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Noeud ouest amont</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Collecte bande ouest</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>W_LOW</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Noeud ouest aval</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Transition vers pipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BASIN_IN</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Regard amont bassin</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Noeud avant bassin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>BASIN_RET</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>RETENTION</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Bassin de retention</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Exutoire final</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Resume_checks" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Template_est_2p5m" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Convention_labels" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Contraintes_ouest_utilites" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dimensionnement_est" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +44,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -111,6 +118,8 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -601,9 +610,342 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Implantation mise a jour: bassin lineaire dans bande sud 2m + guidance conflits utilites ouest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Voir Dimensionnement_est et Contraintes_ouest_utilites pour dimensionnement et implantation recommandee.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DIMENSIONNEMENT BANDE EST (2.5m) - ESTIMATION A PARTIR DES AIRES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Formule/Source</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Unite</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Critere</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Resultat</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Q_design est aval (E02)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Elements_hybrides Q(E02)</t>
+        </is>
+      </c>
+      <c r="C4" s="8">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH("E02",Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Capacite pipe 200mm (s=Inputs!B33)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Manning plein</t>
+        </is>
+      </c>
+      <c r="C5" s="8">
+        <f>(1/Inputs!$B$9)*(PI()*(Inputs!$B$30/1000)^2/4)*(((Inputs!$B$30/1000)/4)^(2/3))*SQRT(Inputs!$B$33)</f>
+        <v/>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Capacite pipe 250mm</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Manning plein</t>
+        </is>
+      </c>
+      <c r="C6" s="8">
+        <f>(1/Inputs!$B$9)*(PI()*(0.25)^2/4)*((0.25/4)^(2/3))*SQRT(Inputs!$B$33)</f>
+        <v/>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Capacite pipe 300mm</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Manning plein</t>
+        </is>
+      </c>
+      <c r="C7" s="8">
+        <f>(1/Inputs!$B$9)*(PI()*(0.30)^2/4)*((0.30/4)^(2/3))*SQRT(Inputs!$B$33)</f>
+        <v/>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Diametre recommande est</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Q_design / fill_limit</t>
+        </is>
+      </c>
+      <c r="C8" s="11">
+        <f>IF(C4="","",IF(C4/Inputs!$B$19&lt;=C5,200,IF(C4/Inputs!$B$19&lt;=C6,250,IF(C4/Inputs!$B$19&lt;=C7,300,375))))</f>
+        <v/>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Stockage lineaire surface+tranchee (m3/m)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Template_est_2p5m</t>
+        </is>
+      </c>
+      <c r="C10" s="8">
+        <f>IFERROR(Template_est_2p5m!$G$6,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>m3/m</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Longueur active bande est</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>E01+E02</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
+        <f>IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH("E01",Elements_hybrides!$A$4:$A$204,0)),0)+IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH("E02",Elements_hybrides!$A$4:$A$204,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Stockage dispo bande est</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>C10*C11</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>IF(OR(C10="",C11=""),"",C10*C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Volume tampon requis est</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Q_design*buffer</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>IF(C4="","",C4*Inputs!$B$23*60)</f>
+        <v/>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Check stockage est</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>C12 vs C13</t>
+        </is>
+      </c>
+      <c r="C14" s="11">
+        <f>IF(OR(C12="",C13=""),"",IF(C12&gt;=C13,"OK","AUGMENTER VOLUME"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -615,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1274,6 +1616,127 @@
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Pente longitudinale de l underdrain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Basin_corridor_width_m</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Largeur disponible entre batiment et cheminement pieton sud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Basin_corridor_length_m</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Longueur exploitable du bassin lineaire sud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Basin_target_depth_m</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Profondeur cible bassin de retention lineaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Basin_ret_top_level_m</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Niveau de reference du bassin (a ajuster avec topographie).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Basin_ret_invert_m</t>
+        </is>
+      </c>
+      <c r="B38" s="5">
+        <f>B37-B36</f>
+        <v/>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Radier bassin lineaire (derive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Max_cover_near_utilities_m</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Profondeur max recommandee dans zone lateraux ouest (approche conservatrice).</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Toiture principale</t>
+          <t>Toiture principale (bloc jaune)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1420,7 +1883,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Toiture vers noue sud</t>
+          <t>Toiture vers collecte sud</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1895,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Tresfond est</t>
+          <t>Tresfond est (gris)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1466,7 +1929,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Pente vers noue est</t>
+          <t>Pente vers bande est</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1975,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Noue est peu profonde</t>
+          <t>Vers underdrain est</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1987,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bande verte ouest haute</t>
+          <t>Ouest vert 1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1533,7 +1996,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>51.3</v>
+        <v>12.5</v>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="8">
@@ -1558,7 +2021,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Vers tranchee ouest</t>
+          <t>Vers collecte ouest</t>
         </is>
       </c>
     </row>
@@ -1570,7 +2033,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Bande verte ouest milieu</t>
+          <t>Ouest vert 2</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1579,7 +2042,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>27.2</v>
+        <v>6.7</v>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="8">
@@ -1604,7 +2067,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Vers tranchee ouest</t>
+          <t>Vers collecte ouest</t>
         </is>
       </c>
     </row>
@@ -1616,7 +2079,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bande verte sud gauche</t>
+          <t>Ouest vert 3</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1625,7 +2088,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>21.9</v>
+        <v>27.2</v>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="8">
@@ -1650,7 +2113,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Vers collecteur ouest</t>
+          <t>Vers collecte ouest</t>
         </is>
       </c>
     </row>
@@ -1662,16 +2125,16 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Bande verte sud droite</t>
+          <t>Ouest pave-uni</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>GRASS</t>
+          <t>TRESFOND</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>20.5</v>
+        <v>37.5</v>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="8">
@@ -1679,7 +2142,7 @@
         <v/>
       </c>
       <c r="G10" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" s="8">
         <f>IF(A10="","",Inputs!$B$3/((IF(G10="",Inputs!$B$14,G10)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -1691,12 +2154,12 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Vers noue sud</t>
+          <t>Surface mineralisee ouest</t>
         </is>
       </c>
     </row>
@@ -1708,16 +2171,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Surface mineralisee sud</t>
+          <t>Ouest vert 4</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>GRASS</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>44.3</v>
+        <v>21.9</v>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="8">
@@ -1725,7 +2188,7 @@
         <v/>
       </c>
       <c r="G11" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11" s="8">
         <f>IF(A11="","",Inputs!$B$3/((IF(G11="",Inputs!$B$14,G11)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -1737,12 +2200,12 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Vers noue sud</t>
+          <t>Vers collecte ouest</t>
         </is>
       </c>
     </row>
@@ -1754,16 +2217,16 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Petite surface minerale</t>
+          <t>Bande sud verte centrale</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>GRASS</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>5.8</v>
+        <v>109.7</v>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="8">
@@ -1771,7 +2234,7 @@
         <v/>
       </c>
       <c r="G12" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H12" s="8">
         <f>IF(A12="","",Inputs!$B$3/((IF(G12="",Inputs!$B$14,G12)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -1793,16 +2256,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Z10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Sud gris local</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>TRESFOND</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="8">
         <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n"/>
+      <c r="G13" s="7" t="n">
+        <v>8</v>
+      </c>
       <c r="H13" s="8">
         <f>IF(A13="","",Inputs!$B$3/((IF(G13="",Inputs!$B$14,G13)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -1811,20 +2290,44 @@
         <f>IF(A13="","",2.78E-7*F13*D13*H13)</f>
         <v/>
       </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Vers noue sud</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Z11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Sud est vert</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GRASS</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="8">
         <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
         <v/>
       </c>
-      <c r="G14" s="7" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="H14" s="8">
         <f>IF(A14="","",Inputs!$B$3/((IF(G14="",Inputs!$B$14,G14)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -1833,20 +2336,44 @@
         <f>IF(A14="","",2.78E-7*F14*D14*H14)</f>
         <v/>
       </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Vers noue sud</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Z12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sud est gris petit</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>TRESFOND</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="8">
         <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
         <v/>
       </c>
-      <c r="G15" s="7" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>8</v>
+      </c>
       <c r="H15" s="8">
         <f>IF(A15="","",Inputs!$B$3/((IF(G15="",Inputs!$B$14,G15)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -1855,8 +2382,16 @@
         <f>IF(A15="","",2.78E-7*F15*D15*H15)</f>
         <v/>
       </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Vers noue sud</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -6239,7 +6774,7 @@
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>12</v>
+        <v>21.6</v>
       </c>
       <c r="G4" s="7">
         <f>Inputs!$B$33</f>
@@ -6323,7 +6858,7 @@
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.; Labels projet harmonises (2026-07-02).</t>
+          <t>Bande est amont: tranchee drainante sous arbres (segment 1).</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6889,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14</v>
+        <v>21.6</v>
       </c>
       <c r="G5" s="7">
         <f>Inputs!$B$33</f>
@@ -6438,7 +6973,7 @@
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Bande est 2.5m: tranchee drainante + underdrain; micro-noue de surface 0.6x0.10 m en complement.; Labels projet harmonises (2026-07-02).</t>
+          <t>Bande est aval: tranchee drainante sous arbres (segment 2).</t>
         </is>
       </c>
     </row>
@@ -6469,7 +7004,7 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0.006</v>
@@ -6542,7 +7077,7 @@
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Collecteur vers bassin; Labels projet harmonises (2026-07-02).</t>
+          <t>Collecteur est vers J-BASSIN-IN (hors zone racinaire dense).</t>
         </is>
       </c>
     </row>
@@ -6572,8 +7107,9 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>29.4</v>
+      <c r="F7" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.008</v>
@@ -6653,7 +7189,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue sud peu profonde (collecte toiture/tresfond sud).; Labels projet harmonises (2026-07-02).</t>
+          <t>Noue/tranchee sud dans bande 2.0m vers bassin lineaire.</t>
         </is>
       </c>
     </row>
@@ -6665,7 +7201,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TRENCH</t>
+          <t>SWALE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -6684,7 +7220,7 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0.008</v>
@@ -6694,18 +7230,18 @@
         <f>IF(A8="","",IF(H8&lt;&gt;"",H8,IF(UPPER(TRIM(B8))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B8))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>3</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O8" s="8">
         <f>IF(A8="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A8))</f>
@@ -6761,7 +7297,7 @@
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Tranchee drainante ouest; Labels projet harmonises (2026-07-02).</t>
+          <t>Collecte ouest avec conduite peu profonde/element lineaire compatible utilites.</t>
         </is>
       </c>
     </row>
@@ -6792,7 +7328,7 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.008</v>
@@ -6865,7 +7401,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Branche ouest vers bassin; Labels projet harmonises (2026-07-02).</t>
+          <t>Branche ouest vers J-BASSIN-IN (traverse utilites avec precautions).</t>
         </is>
       </c>
     </row>
@@ -6892,7 +7428,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0.006</v>
@@ -6965,7 +7501,7 @@
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Troncon final au bassin; Labels projet harmonises (2026-07-02).</t>
+          <t>Injection finale vers BASSIN-RET lineaire sud.</t>
         </is>
       </c>
     </row>
@@ -21787,7 +22323,7 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
@@ -21822,8 +22358,14 @@
           <t>RETENTION</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
+      <c r="C12" s="7">
+        <f>Inputs!$B$37</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>Inputs!$B$38</f>
+        <v/>
+      </c>
       <c r="E12" s="8">
         <f>IF(OR(C12="",D12=""),"",MAX(0,C12-D12))</f>
         <v/>
@@ -21833,19 +22375,20 @@
           <t>RECT</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>15</v>
+      <c r="G12" s="7">
+        <f>Inputs!$B$34</f>
+        <v/>
+      </c>
+      <c r="H12" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
       </c>
       <c r="I12" s="8">
         <f>IF(A12="","",IF(UPPER(TRIM(F12))="CIRC",PI()*(G12/2)^2*E12,IF(UPPER(TRIM(F12))="RECT",G12*H12*E12,"")))</f>
         <v/>
       </c>
-      <c r="J12" s="7">
-        <f>Inputs!$B$23</f>
-        <v/>
+      <c r="J12" s="7" t="n">
+        <v>30</v>
       </c>
       <c r="K12" s="8">
         <f>IF(A12="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A12))</f>
@@ -28338,4 +28881,204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IMPLANTATION OUEST - CONFLITS UTILITES (AEP / PLUVIAL / SANITAIRE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Contrainte</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Strategie recommandee</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Element modele</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Parametre cible</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ouest haut</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Lateraux multiples</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Privilegier ecoulement de surface (noue peu profonde)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>E05 (SWALE)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>profondeur ~0.20 m</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Limiter fouille profonde dans emprise chargee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Traverse vers bassin</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Croisement inevitable</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Croiser perpendiculaire + gaine + pente mini</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>E06 (PIPE)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>slope 0.8%</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Verifier degagement vertical avec as-built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Bande sud 2m</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Emprise contrainte</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Bassin lineaire + noue/tranchee compacte</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>E04 + BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>width 2.0 m</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Stockage distribue + transfert au bassin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Bande est arbres</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Zone racinaire</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Tranchee drainante + underdrain + barriere racinaire</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>E01/E02 (TRENCH)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>offset &gt;=1.0 m</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Eviter conduite profonde continue en pied d arbres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Note: Les degagements finaux avec lateraux existants doivent etre confirmes par releves terrain/TQC avant IFC.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Convention_labels" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Contraintes_ouest_utilites" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Dimensionnement_est" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Decision_Summary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -120,10 +121,46 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDEBF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -485,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -621,6 +658,13 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>Voir Dimensionnement_est et Contraintes_ouest_utilites pour dimensionnement et implantation recommandee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Presentation pass added: row color coding in Elements_hybrides and one-page Decision_Summary tab.</t>
         </is>
       </c>
     </row>
@@ -947,6 +991,478 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DECISION SUMMARY - DRAINAGE HYBRIDE TRESFOND (PRET POUR PARTAGE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Project strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1) Bande est (arbres): tranchee drainante + underdrain (E01/E02) au lieu d une noue profonde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2) Bande sud (2.0 m): noue lineaire + volume de retention dans le corridor contraint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3) Ouest (utilities): collecte de surface peu profonde priorisee, traverses ponctuelles controlees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4) Exutoire final au bassin de retention via J-BASSIN-IN -&gt; BASSIN-RET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Key dimensions and constraints</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Qdesign (m3/s)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>East strip total width (m)</t>
+        </is>
+      </c>
+      <c r="B11" s="9">
+        <f>Inputs!B24</f>
+        <v/>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>&lt;= site 2.5 m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="F11" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E11,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E11,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E11,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Underdrain trench width x depth (m)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>Inputs!B28&amp;" x "&amp;Inputs!B29</f>
+        <v/>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Tree-compatible trench</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E12,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E12,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E12,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Underdrain diameter (mm)</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>Inputs!B30</f>
+        <v/>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Initial recommendation</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="F13" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E13,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E13,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E13,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>South basin corridor width x length (m)</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>Inputs!B34&amp;" x "&amp;Inputs!B35</f>
+        <v/>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Between building and pedestrian road</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E14,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E14,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E14,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Basin target depth (m)</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>Inputs!B36</f>
+        <v/>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Adjust with topo survey</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Max cover near west utilities (m)</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Inputs!B39</f>
+        <v/>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Conservative limit</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="F16" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E16,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E16,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E16,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="F17" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E17,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="13">
+        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E17,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E17,Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>KPI checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Elements CHECK count</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Resume_checks!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Nodes CHECK count</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Resume_checks!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Global status</t>
+        </is>
+      </c>
+      <c r="B23" s="8">
+        <f>Resume_checks!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Total peak runoff (m3/s)</t>
+        </is>
+      </c>
+      <c r="B24" s="8">
+        <f>Resume_checks!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Total element storage (m3)</t>
+        </is>
+      </c>
+      <c r="B25" s="8">
+        <f>Resume_checks!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Retention storage node (m3)</t>
+        </is>
+      </c>
+      <c r="B26" s="8">
+        <f>Resume_checks!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Actions before IFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Confirmer positions/degagements exacts des lateraux ouest (AEP/pluvial/sanitaire) avec releves TQC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>- Valider niveau radier/top bassin avec topographie terrain et profil final du cheminement pieton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>- Ajuster diametre underdrain est (Inputs!B30) selon Qdesign final de E02 et critere de remplissage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>- Verifier protection racinaire et details constructifs (barriere racinaire + cleanouts + acces entretien).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H11:H17">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>=$H11="CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:B26">
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>=OR(AND($A21="Elements CHECK count",$B21&gt;0),AND($A22="Nodes CHECK count",$B22&gt;0),AND($A23="Global status",$B23="CHECK"))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6605,6 +7121,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Legend: PIPE=blue, SWALE=green, TRENCH=orange, CHECK=red.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -21862,9 +22385,31 @@
       <c r="AB204" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A4:AB204">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>=$B4="PIPE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>=$B4="SWALE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>=$B4="TRENCH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA204">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>=$AA4="CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4:U204">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>=$U4&gt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -45,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,6 +128,7 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -665,6 +671,20 @@
       <c r="A22" t="inlineStr">
         <is>
           <t>Presentation pass added: row color coding in Elements_hybrides and one-page Decision_Summary tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mise a jour ouest: sequence grass/pave-uni/grass/pave-uni/grass modelee en E05A..E05E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Connexion entre types d elements implementee via AC:AH (controle continuité d invert).</t>
         </is>
       </c>
     </row>
@@ -1439,9 +1459,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
@@ -2532,7 +2552,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05A</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -2578,7 +2598,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05B</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -2624,7 +2644,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05C</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -2670,7 +2690,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05D</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -2716,7 +2736,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05E</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -7081,7 +7101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB204"/>
+  <dimension ref="A1:AH204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7112,6 +7132,12 @@
     <col width="11" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
     <col width="34" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7269,6 +7295,36 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="AC3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_down_override_m</t>
+        </is>
+      </c>
+      <c r="AD3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_down_used_m</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_up_m</t>
+        </is>
+      </c>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>Downstream_invert_up_m</t>
+        </is>
+      </c>
+      <c r="AG3" s="6" t="inlineStr">
+        <is>
+          <t>Connection_delta_m</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="inlineStr">
+        <is>
+          <t>Connection_status</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7376,13 +7432,34 @@
         <v/>
       </c>
       <c r="AA4" s="4">
-        <f>IF(A4="","",IF(OR(U4&gt;1,AND(X4&lt;&gt;"",X4&lt;Inputs!$B$16),AND(X4&lt;&gt;"",X4&gt;Inputs!$B$17),G4&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A4="","",IF(OR(U4&gt;1,AND(X4&lt;&gt;"",X4&lt;Inputs!$B$16),AND(X4&lt;&gt;"",X4&gt;Inputs!$B$17),G4&lt;Inputs!$B$18,AH4="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Bande est amont: tranchee drainante sous arbres (segment 1).</t>
-        </is>
+          <t>Bande est amont (arbres) - underdrain segment 1.</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="n"/>
+      <c r="AD4" s="8">
+        <f>IF(A4="","",IF(AC4&lt;&gt;"",AC4,IF(E4="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="8">
+        <f>IF(OR(AD4="",F4="",G4=""),"",AD4+F4*G4)</f>
+        <v/>
+      </c>
+      <c r="AF4" s="8">
+        <f>IF(OR(E4="",A4=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="8">
+        <f>IF(OR(AD4="",AF4=""),"",AD4-AF4)</f>
+        <v/>
+      </c>
+      <c r="AH4" s="4">
+        <f>IF(A4="","",IF(E4="","TERMINAL",IF(AG4="","INFO",IF(ABS(AG4)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -7491,13 +7568,34 @@
         <v/>
       </c>
       <c r="AA5" s="4">
-        <f>IF(A5="","",IF(OR(U5&gt;1,AND(X5&lt;&gt;"",X5&lt;Inputs!$B$16),AND(X5&lt;&gt;"",X5&gt;Inputs!$B$17),G5&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A5="","",IF(OR(U5&gt;1,AND(X5&lt;&gt;"",X5&lt;Inputs!$B$16),AND(X5&lt;&gt;"",X5&gt;Inputs!$B$17),G5&lt;Inputs!$B$18,AH5="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Bande est aval: tranchee drainante sous arbres (segment 2).</t>
-        </is>
+          <t>Bande est aval (arbres) - underdrain segment 2.</t>
+        </is>
+      </c>
+      <c r="AC5" s="7" t="n"/>
+      <c r="AD5" s="8">
+        <f>IF(A5="","",IF(AC5&lt;&gt;"",AC5,IF(E5="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="8">
+        <f>IF(OR(AD5="",F5="",G5=""),"",AD5+F5*G5)</f>
+        <v/>
+      </c>
+      <c r="AF5" s="8">
+        <f>IF(OR(E5="",A5=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="8">
+        <f>IF(OR(AD5="",AF5=""),"",AD5-AF5)</f>
+        <v/>
+      </c>
+      <c r="AH5" s="4">
+        <f>IF(A5="","",IF(E5="","TERMINAL",IF(AG5="","INFO",IF(ABS(AG5)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -7542,7 +7640,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
-      <c r="M6" s="7" t="n"/>
+      <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="n">
         <v>0</v>
       </c>
@@ -7595,13 +7693,34 @@
         <v/>
       </c>
       <c r="AA6" s="4">
-        <f>IF(A6="","",IF(OR(U6&gt;1,AND(X6&lt;&gt;"",X6&lt;Inputs!$B$16),AND(X6&lt;&gt;"",X6&gt;Inputs!$B$17),G6&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A6="","",IF(OR(U6&gt;1,AND(X6&lt;&gt;"",X6&lt;Inputs!$B$16),AND(X6&lt;&gt;"",X6&gt;Inputs!$B$17),G6&lt;Inputs!$B$18,AH6="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Collecteur est vers J-BASSIN-IN (hors zone racinaire dense).</t>
-        </is>
+          <t>Collecteur est vers entree bassin.</t>
+        </is>
+      </c>
+      <c r="AC6" s="7" t="n"/>
+      <c r="AD6" s="8">
+        <f>IF(A6="","",IF(AC6&lt;&gt;"",AC6,IF(E6="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="8">
+        <f>IF(OR(AD6="",F6="",G6=""),"",AD6+F6*G6)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="8">
+        <f>IF(OR(E6="",A6=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="8">
+        <f>IF(OR(AD6="",AF6=""),"",AD6-AF6)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="4">
+        <f>IF(A6="","",IF(E6="","TERMINAL",IF(AG6="","INFO",IF(ABS(AG6)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -7630,9 +7749,8 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="F7" s="7">
-        <f>Inputs!$B$35</f>
-        <v/>
+      <c r="F7" s="7" t="n">
+        <v>16.1</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.008</v>
@@ -7707,19 +7825,40 @@
         <v/>
       </c>
       <c r="AA7" s="4">
-        <f>IF(A7="","",IF(OR(U7&gt;1,AND(X7&lt;&gt;"",X7&lt;Inputs!$B$16),AND(X7&lt;&gt;"",X7&gt;Inputs!$B$17),G7&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A7="","",IF(OR(U7&gt;1,AND(X7&lt;&gt;"",X7&lt;Inputs!$B$16),AND(X7&lt;&gt;"",X7&gt;Inputs!$B$17),G7&lt;Inputs!$B$18,AH7="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue/tranchee sud dans bande 2.0m vers bassin lineaire.</t>
-        </is>
+          <t>Noue sud principale (corridor 2 m).</t>
+        </is>
+      </c>
+      <c r="AC7" s="7" t="n"/>
+      <c r="AD7" s="8">
+        <f>IF(A7="","",IF(AC7&lt;&gt;"",AC7,IF(E7="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="8">
+        <f>IF(OR(AD7="",F7="",G7=""),"",AD7+F7*G7)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="8">
+        <f>IF(OR(E7="",A7=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="8">
+        <f>IF(OR(AD7="",AF7=""),"",AD7-AF7)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="4">
+        <f>IF(A7="","",IF(E7="","TERMINAL",IF(AG7="","INFO",IF(ABS(AG7)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05A</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -7734,31 +7873,31 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05B</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8">
         <f>IF(A8="","",IF(H8&lt;&gt;"",H8,IF(UPPER(TRIM(B8))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B8))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="n"/>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>3</v>
@@ -7815,19 +7954,40 @@
         <v/>
       </c>
       <c r="AA8" s="4">
-        <f>IF(A8="","",IF(OR(U8&gt;1,AND(X8&lt;&gt;"",X8&lt;Inputs!$B$16),AND(X8&lt;&gt;"",X8&gt;Inputs!$B$17),G8&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A8="","",IF(OR(U8&gt;1,AND(X8&lt;&gt;"",X8&lt;Inputs!$B$16),AND(X8&lt;&gt;"",X8&gt;Inputs!$B$17),G8&lt;Inputs!$B$18,AH8="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Collecte ouest avec conduite peu profonde/element lineaire compatible utilites.</t>
-        </is>
+          <t>Ouest grass 12.5 m2 (surface).</t>
+        </is>
+      </c>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="8">
+        <f>IF(A8="","",IF(AC8&lt;&gt;"",AC8,IF(E8="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="8">
+        <f>IF(OR(AD8="",F8="",G8=""),"",AD8+F8*G8)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="8">
+        <f>IF(OR(E8="",A8=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="8">
+        <f>IF(OR(AD8="",AF8=""),"",AD8-AF8)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>IF(A8="","",IF(E8="","TERMINAL",IF(AG8="","INFO",IF(ABS(AG8)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05B</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -7837,24 +7997,24 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05C</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8">
@@ -7862,11 +8022,11 @@
         <v/>
       </c>
       <c r="J9" s="7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="n"/>
+      <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
@@ -7919,54 +8079,83 @@
         <v/>
       </c>
       <c r="AA9" s="4">
-        <f>IF(A9="","",IF(OR(U9&gt;1,AND(X9&lt;&gt;"",X9&lt;Inputs!$B$16),AND(X9&lt;&gt;"",X9&gt;Inputs!$B$17),G9&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A9="","",IF(OR(U9&gt;1,AND(X9&lt;&gt;"",X9&lt;Inputs!$B$16),AND(X9&lt;&gt;"",X9&gt;Inputs!$B$17),G9&lt;Inputs!$B$18,AH9="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Branche ouest vers J-BASSIN-IN (traverse utilites avec precautions).</t>
-        </is>
+          <t>Traverse pave-uni 6.7 m2 (caniveau/pipe).</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="n"/>
+      <c r="AD9" s="8">
+        <f>IF(A9="","",IF(AC9&lt;&gt;"",AC9,IF(E9="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="8">
+        <f>IF(OR(AD9="",F9="",G9=""),"",AD9+F9*G9)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="8">
+        <f>IF(OR(E9="",A9=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="8">
+        <f>IF(OR(AD9="",AF9=""),"",AD9-AF9)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>IF(A9="","",IF(E9="","TERMINAL",IF(AG9="","INFO",IF(ABS(AG9)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05C</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>SWALE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BASSIN-RET</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
+          <t>J-OUEST-PU3</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>E05D</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8">
         <f>IF(A10="","",IF(H10&lt;&gt;"",H10,IF(UPPER(TRIM(B10))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B10))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>525</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="n"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
@@ -8019,32 +8208,79 @@
         <v/>
       </c>
       <c r="AA10" s="4">
-        <f>IF(A10="","",IF(OR(U10&gt;1,AND(X10&lt;&gt;"",X10&lt;Inputs!$B$16),AND(X10&lt;&gt;"",X10&gt;Inputs!$B$17),G10&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A10="","",IF(OR(U10&gt;1,AND(X10&lt;&gt;"",X10&lt;Inputs!$B$16),AND(X10&lt;&gt;"",X10&gt;Inputs!$B$17),G10&lt;Inputs!$B$18,AH10="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Injection finale vers BASSIN-RET lineaire sud.</t>
-        </is>
+          <t>Ouest grass 27.2 m2 (surface).</t>
+        </is>
+      </c>
+      <c r="AC10" s="7" t="n"/>
+      <c r="AD10" s="8">
+        <f>IF(A10="","",IF(AC10&lt;&gt;"",AC10,IF(E10="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="8">
+        <f>IF(OR(AD10="",F10="",G10=""),"",AD10+F10*G10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="8">
+        <f>IF(OR(E10="",A10=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="8">
+        <f>IF(OR(AD10="",AF10=""),"",AD10-AF10)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>IF(A10="","",IF(E10="","TERMINAL",IF(AG10="","INFO",IF(ABS(AG10)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E05D</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>E05E</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
         <f>IF(A11="","",IF(H11&lt;&gt;"",H11,IF(UPPER(TRIM(B11))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B11))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
+      <c r="J11" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
@@ -8097,28 +8333,83 @@
         <v/>
       </c>
       <c r="AA11" s="4">
-        <f>IF(A11="","",IF(OR(U11&gt;1,AND(X11&lt;&gt;"",X11&lt;Inputs!$B$16),AND(X11&lt;&gt;"",X11&gt;Inputs!$B$17),G11&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB11" s="4" t="n"/>
+        <f>IF(A11="","",IF(OR(U11&gt;1,AND(X11&lt;&gt;"",X11&lt;Inputs!$B$16),AND(X11&lt;&gt;"",X11&gt;Inputs!$B$17),G11&lt;Inputs!$B$18,AH11="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>Traverse pave-uni 37.5 m2 (caniveau/pipe).</t>
+        </is>
+      </c>
+      <c r="AC11" s="7" t="n"/>
+      <c r="AD11" s="8">
+        <f>IF(A11="","",IF(AC11&lt;&gt;"",AC11,IF(E11="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="8">
+        <f>IF(OR(AD11="",F11="",G11=""),"",AD11+F11*G11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="8">
+        <f>IF(OR(E11="",A11=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="8">
+        <f>IF(OR(AD11="",AF11=""),"",AD11-AF11)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>IF(A11="","",IF(E11="","TERMINAL",IF(AG11="","INFO",IF(ABS(AG11)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E05E</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SWALE</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="8">
         <f>IF(A12="","",IF(H12&lt;&gt;"",H12,IF(UPPER(TRIM(B12))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B12))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
@@ -8171,28 +8462,79 @@
         <v/>
       </c>
       <c r="AA12" s="4">
-        <f>IF(A12="","",IF(OR(U12&gt;1,AND(X12&lt;&gt;"",X12&lt;Inputs!$B$16),AND(X12&lt;&gt;"",X12&gt;Inputs!$B$17),G12&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB12" s="4" t="n"/>
+        <f>IF(A12="","",IF(OR(U12&gt;1,AND(X12&lt;&gt;"",X12&lt;Inputs!$B$16),AND(X12&lt;&gt;"",X12&gt;Inputs!$B$17),G12&lt;Inputs!$B$18,AH12="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>Ouest grass 21.9 m2 (surface vers aval).</t>
+        </is>
+      </c>
+      <c r="AC12" s="7" t="n"/>
+      <c r="AD12" s="8">
+        <f>IF(A12="","",IF(AC12&lt;&gt;"",AC12,IF(E12="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="8">
+        <f>IF(OR(AD12="",F12="",G12=""),"",AD12+F12*G12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="8">
+        <f>IF(OR(E12="",A12=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="8">
+        <f>IF(OR(AD12="",AF12=""),"",AD12-AF12)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>IF(A12="","",IF(E12="","TERMINAL",IF(AG12="","INFO",IF(ABS(AG12)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="8">
         <f>IF(A13="","",IF(H13&lt;&gt;"",H13,IF(UPPER(TRIM(B13))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B13))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
+      <c r="J13" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
@@ -8245,28 +8587,75 @@
         <v/>
       </c>
       <c r="AA13" s="4">
-        <f>IF(A13="","",IF(OR(U13&gt;1,AND(X13&lt;&gt;"",X13&lt;Inputs!$B$16),AND(X13&lt;&gt;"",X13&gt;Inputs!$B$17),G13&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB13" s="4" t="n"/>
+        <f>IF(A13="","",IF(OR(U13&gt;1,AND(X13&lt;&gt;"",X13&lt;Inputs!$B$16),AND(X13&lt;&gt;"",X13&gt;Inputs!$B$17),G13&lt;Inputs!$B$18,AH13="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>Branche ouest vers entree bassin.</t>
+        </is>
+      </c>
+      <c r="AC13" s="7" t="n"/>
+      <c r="AD13" s="8">
+        <f>IF(A13="","",IF(AC13&lt;&gt;"",AC13,IF(E13="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="8">
+        <f>IF(OR(AD13="",F13="",G13=""),"",AD13+F13*G13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="8">
+        <f>IF(OR(E13="",A13=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="8">
+        <f>IF(OR(AD13="",AF13=""),"",AD13-AF13)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>IF(A13="","",IF(E13="","TERMINAL",IF(AG13="","INFO",IF(ABS(AG13)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
         <f>IF(A14="","",IF(H14&lt;&gt;"",H14,IF(UPPER(TRIM(B14))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B14))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
+      <c r="J14" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="n">
         <v>0</v>
       </c>
@@ -8319,10 +8708,35 @@
         <v/>
       </c>
       <c r="AA14" s="4">
-        <f>IF(A14="","",IF(OR(U14&gt;1,AND(X14&lt;&gt;"",X14&lt;Inputs!$B$16),AND(X14&lt;&gt;"",X14&gt;Inputs!$B$17),G14&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB14" s="4" t="n"/>
+        <f>IF(A14="","",IF(OR(U14&gt;1,AND(X14&lt;&gt;"",X14&lt;Inputs!$B$16),AND(X14&lt;&gt;"",X14&gt;Inputs!$B$17),G14&lt;Inputs!$B$18,AH14="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>Injection finale vers bassin retention.</t>
+        </is>
+      </c>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="8">
+        <f>IF(A14="","",IF(AC14&lt;&gt;"",AC14,IF(E14="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="8">
+        <f>IF(OR(AD14="",F14="",G14=""),"",AD14+F14*G14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="8">
+        <f>IF(OR(E14="",A14=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="8">
+        <f>IF(OR(AD14="",AF14=""),"",AD14-AF14)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>IF(A14="","",IF(E14="","TERMINAL",IF(AG14="","INFO",IF(ABS(AG14)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -8341,9 +8755,7 @@
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" s="7" t="n"/>
       <c r="O15" s="8">
         <f>IF(A15="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A15))</f>
         <v/>
@@ -8393,10 +8805,31 @@
         <v/>
       </c>
       <c r="AA15" s="4">
-        <f>IF(A15="","",IF(OR(U15&gt;1,AND(X15&lt;&gt;"",X15&lt;Inputs!$B$16),AND(X15&lt;&gt;"",X15&gt;Inputs!$B$17),G15&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A15="","",IF(OR(U15&gt;1,AND(X15&lt;&gt;"",X15&lt;Inputs!$B$16),AND(X15&lt;&gt;"",X15&gt;Inputs!$B$17),G15&lt;Inputs!$B$18,AH15="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="8">
+        <f>IF(A15="","",IF(AC15&lt;&gt;"",AC15,IF(E15="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="8">
+        <f>IF(OR(AD15="",F15="",G15=""),"",AD15+F15*G15)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="8">
+        <f>IF(OR(E15="",A15=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="8">
+        <f>IF(OR(AD15="",AF15=""),"",AD15-AF15)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>IF(A15="","",IF(E15="","TERMINAL",IF(AG15="","INFO",IF(ABS(AG15)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -8415,9 +8848,7 @@
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" s="7" t="n"/>
       <c r="O16" s="8">
         <f>IF(A16="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A16))</f>
         <v/>
@@ -8467,10 +8898,31 @@
         <v/>
       </c>
       <c r="AA16" s="4">
-        <f>IF(A16="","",IF(OR(U16&gt;1,AND(X16&lt;&gt;"",X16&lt;Inputs!$B$16),AND(X16&lt;&gt;"",X16&gt;Inputs!$B$17),G16&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A16="","",IF(OR(U16&gt;1,AND(X16&lt;&gt;"",X16&lt;Inputs!$B$16),AND(X16&lt;&gt;"",X16&gt;Inputs!$B$17),G16&lt;Inputs!$B$18,AH16="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="7" t="n"/>
+      <c r="AD16" s="8">
+        <f>IF(A16="","",IF(AC16&lt;&gt;"",AC16,IF(E16="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="8">
+        <f>IF(OR(AD16="",F16="",G16=""),"",AD16+F16*G16)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="8">
+        <f>IF(OR(E16="",A16=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="8">
+        <f>IF(OR(AD16="",AF16=""),"",AD16-AF16)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>IF(A16="","",IF(E16="","TERMINAL",IF(AG16="","INFO",IF(ABS(AG16)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -8489,9 +8941,7 @@
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" s="7" t="n"/>
       <c r="O17" s="8">
         <f>IF(A17="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A17))</f>
         <v/>
@@ -8541,10 +8991,31 @@
         <v/>
       </c>
       <c r="AA17" s="4">
-        <f>IF(A17="","",IF(OR(U17&gt;1,AND(X17&lt;&gt;"",X17&lt;Inputs!$B$16),AND(X17&lt;&gt;"",X17&gt;Inputs!$B$17),G17&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A17="","",IF(OR(U17&gt;1,AND(X17&lt;&gt;"",X17&lt;Inputs!$B$16),AND(X17&lt;&gt;"",X17&gt;Inputs!$B$17),G17&lt;Inputs!$B$18,AH17="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="7" t="n"/>
+      <c r="AD17" s="8">
+        <f>IF(A17="","",IF(AC17&lt;&gt;"",AC17,IF(E17="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="8">
+        <f>IF(OR(AD17="",F17="",G17=""),"",AD17+F17*G17)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="8">
+        <f>IF(OR(E17="",A17=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="8">
+        <f>IF(OR(AD17="",AF17=""),"",AD17-AF17)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>IF(A17="","",IF(E17="","TERMINAL",IF(AG17="","INFO",IF(ABS(AG17)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -8563,9 +9034,7 @@
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" s="7" t="n"/>
       <c r="O18" s="8">
         <f>IF(A18="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A18))</f>
         <v/>
@@ -8615,10 +9084,31 @@
         <v/>
       </c>
       <c r="AA18" s="4">
-        <f>IF(A18="","",IF(OR(U18&gt;1,AND(X18&lt;&gt;"",X18&lt;Inputs!$B$16),AND(X18&lt;&gt;"",X18&gt;Inputs!$B$17),G18&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A18="","",IF(OR(U18&gt;1,AND(X18&lt;&gt;"",X18&lt;Inputs!$B$16),AND(X18&lt;&gt;"",X18&gt;Inputs!$B$17),G18&lt;Inputs!$B$18,AH18="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="8">
+        <f>IF(A18="","",IF(AC18&lt;&gt;"",AC18,IF(E18="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="8">
+        <f>IF(OR(AD18="",F18="",G18=""),"",AD18+F18*G18)</f>
+        <v/>
+      </c>
+      <c r="AF18" s="8">
+        <f>IF(OR(E18="",A18=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="8">
+        <f>IF(OR(AD18="",AF18=""),"",AD18-AF18)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>IF(A18="","",IF(E18="","TERMINAL",IF(AG18="","INFO",IF(ABS(AG18)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -8637,9 +9127,7 @@
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" s="7" t="n"/>
       <c r="O19" s="8">
         <f>IF(A19="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A19))</f>
         <v/>
@@ -8689,10 +9177,31 @@
         <v/>
       </c>
       <c r="AA19" s="4">
-        <f>IF(A19="","",IF(OR(U19&gt;1,AND(X19&lt;&gt;"",X19&lt;Inputs!$B$16),AND(X19&lt;&gt;"",X19&gt;Inputs!$B$17),G19&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A19="","",IF(OR(U19&gt;1,AND(X19&lt;&gt;"",X19&lt;Inputs!$B$16),AND(X19&lt;&gt;"",X19&gt;Inputs!$B$17),G19&lt;Inputs!$B$18,AH19="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB19" s="4" t="n"/>
+      <c r="AC19" s="7" t="n"/>
+      <c r="AD19" s="8">
+        <f>IF(A19="","",IF(AC19&lt;&gt;"",AC19,IF(E19="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="8">
+        <f>IF(OR(AD19="",F19="",G19=""),"",AD19+F19*G19)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="8">
+        <f>IF(OR(E19="",A19=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="8">
+        <f>IF(OR(AD19="",AF19=""),"",AD19-AF19)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>IF(A19="","",IF(E19="","TERMINAL",IF(AG19="","INFO",IF(ABS(AG19)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -8711,9 +9220,7 @@
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" s="7" t="n"/>
       <c r="O20" s="8">
         <f>IF(A20="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A20))</f>
         <v/>
@@ -8763,10 +9270,31 @@
         <v/>
       </c>
       <c r="AA20" s="4">
-        <f>IF(A20="","",IF(OR(U20&gt;1,AND(X20&lt;&gt;"",X20&lt;Inputs!$B$16),AND(X20&lt;&gt;"",X20&gt;Inputs!$B$17),G20&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A20="","",IF(OR(U20&gt;1,AND(X20&lt;&gt;"",X20&lt;Inputs!$B$16),AND(X20&lt;&gt;"",X20&gt;Inputs!$B$17),G20&lt;Inputs!$B$18,AH20="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="7" t="n"/>
+      <c r="AD20" s="8">
+        <f>IF(A20="","",IF(AC20&lt;&gt;"",AC20,IF(E20="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="8">
+        <f>IF(OR(AD20="",F20="",G20=""),"",AD20+F20*G20)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="8">
+        <f>IF(OR(E20="",A20=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="8">
+        <f>IF(OR(AD20="",AF20=""),"",AD20-AF20)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>IF(A20="","",IF(E20="","TERMINAL",IF(AG20="","INFO",IF(ABS(AG20)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -8837,10 +9365,31 @@
         <v/>
       </c>
       <c r="AA21" s="4">
-        <f>IF(A21="","",IF(OR(U21&gt;1,AND(X21&lt;&gt;"",X21&lt;Inputs!$B$16),AND(X21&lt;&gt;"",X21&gt;Inputs!$B$17),G21&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A21="","",IF(OR(U21&gt;1,AND(X21&lt;&gt;"",X21&lt;Inputs!$B$16),AND(X21&lt;&gt;"",X21&gt;Inputs!$B$17),G21&lt;Inputs!$B$18,AH21="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB21" s="4" t="n"/>
+      <c r="AC21" s="7" t="n"/>
+      <c r="AD21" s="8">
+        <f>IF(A21="","",IF(AC21&lt;&gt;"",AC21,IF(E21="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="8">
+        <f>IF(OR(AD21="",F21="",G21=""),"",AD21+F21*G21)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="8">
+        <f>IF(OR(E21="",A21=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="8">
+        <f>IF(OR(AD21="",AF21=""),"",AD21-AF21)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>IF(A21="","",IF(E21="","TERMINAL",IF(AG21="","INFO",IF(ABS(AG21)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -8911,10 +9460,31 @@
         <v/>
       </c>
       <c r="AA22" s="4">
-        <f>IF(A22="","",IF(OR(U22&gt;1,AND(X22&lt;&gt;"",X22&lt;Inputs!$B$16),AND(X22&lt;&gt;"",X22&gt;Inputs!$B$17),G22&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A22="","",IF(OR(U22&gt;1,AND(X22&lt;&gt;"",X22&lt;Inputs!$B$16),AND(X22&lt;&gt;"",X22&gt;Inputs!$B$17),G22&lt;Inputs!$B$18,AH22="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="7" t="n"/>
+      <c r="AD22" s="8">
+        <f>IF(A22="","",IF(AC22&lt;&gt;"",AC22,IF(E22="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="8">
+        <f>IF(OR(AD22="",F22="",G22=""),"",AD22+F22*G22)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="8">
+        <f>IF(OR(E22="",A22=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="8">
+        <f>IF(OR(AD22="",AF22=""),"",AD22-AF22)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>IF(A22="","",IF(E22="","TERMINAL",IF(AG22="","INFO",IF(ABS(AG22)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -8985,10 +9555,31 @@
         <v/>
       </c>
       <c r="AA23" s="4">
-        <f>IF(A23="","",IF(OR(U23&gt;1,AND(X23&lt;&gt;"",X23&lt;Inputs!$B$16),AND(X23&lt;&gt;"",X23&gt;Inputs!$B$17),G23&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A23="","",IF(OR(U23&gt;1,AND(X23&lt;&gt;"",X23&lt;Inputs!$B$16),AND(X23&lt;&gt;"",X23&gt;Inputs!$B$17),G23&lt;Inputs!$B$18,AH23="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB23" s="4" t="n"/>
+      <c r="AC23" s="7" t="n"/>
+      <c r="AD23" s="8">
+        <f>IF(A23="","",IF(AC23&lt;&gt;"",AC23,IF(E23="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="8">
+        <f>IF(OR(AD23="",F23="",G23=""),"",AD23+F23*G23)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="8">
+        <f>IF(OR(E23="",A23=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="8">
+        <f>IF(OR(AD23="",AF23=""),"",AD23-AF23)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>IF(A23="","",IF(E23="","TERMINAL",IF(AG23="","INFO",IF(ABS(AG23)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -9059,10 +9650,31 @@
         <v/>
       </c>
       <c r="AA24" s="4">
-        <f>IF(A24="","",IF(OR(U24&gt;1,AND(X24&lt;&gt;"",X24&lt;Inputs!$B$16),AND(X24&lt;&gt;"",X24&gt;Inputs!$B$17),G24&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A24="","",IF(OR(U24&gt;1,AND(X24&lt;&gt;"",X24&lt;Inputs!$B$16),AND(X24&lt;&gt;"",X24&gt;Inputs!$B$17),G24&lt;Inputs!$B$18,AH24="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB24" s="4" t="n"/>
+      <c r="AC24" s="7" t="n"/>
+      <c r="AD24" s="8">
+        <f>IF(A24="","",IF(AC24&lt;&gt;"",AC24,IF(E24="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="8">
+        <f>IF(OR(AD24="",F24="",G24=""),"",AD24+F24*G24)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="8">
+        <f>IF(OR(E24="",A24=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="8">
+        <f>IF(OR(AD24="",AF24=""),"",AD24-AF24)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>IF(A24="","",IF(E24="","TERMINAL",IF(AG24="","INFO",IF(ABS(AG24)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -9133,10 +9745,31 @@
         <v/>
       </c>
       <c r="AA25" s="4">
-        <f>IF(A25="","",IF(OR(U25&gt;1,AND(X25&lt;&gt;"",X25&lt;Inputs!$B$16),AND(X25&lt;&gt;"",X25&gt;Inputs!$B$17),G25&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A25="","",IF(OR(U25&gt;1,AND(X25&lt;&gt;"",X25&lt;Inputs!$B$16),AND(X25&lt;&gt;"",X25&gt;Inputs!$B$17),G25&lt;Inputs!$B$18,AH25="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB25" s="4" t="n"/>
+      <c r="AC25" s="7" t="n"/>
+      <c r="AD25" s="8">
+        <f>IF(A25="","",IF(AC25&lt;&gt;"",AC25,IF(E25="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="8">
+        <f>IF(OR(AD25="",F25="",G25=""),"",AD25+F25*G25)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="8">
+        <f>IF(OR(E25="",A25=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="8">
+        <f>IF(OR(AD25="",AF25=""),"",AD25-AF25)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>IF(A25="","",IF(E25="","TERMINAL",IF(AG25="","INFO",IF(ABS(AG25)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -9207,10 +9840,31 @@
         <v/>
       </c>
       <c r="AA26" s="4">
-        <f>IF(A26="","",IF(OR(U26&gt;1,AND(X26&lt;&gt;"",X26&lt;Inputs!$B$16),AND(X26&lt;&gt;"",X26&gt;Inputs!$B$17),G26&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A26="","",IF(OR(U26&gt;1,AND(X26&lt;&gt;"",X26&lt;Inputs!$B$16),AND(X26&lt;&gt;"",X26&gt;Inputs!$B$17),G26&lt;Inputs!$B$18,AH26="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB26" s="4" t="n"/>
+      <c r="AC26" s="7" t="n"/>
+      <c r="AD26" s="8">
+        <f>IF(A26="","",IF(AC26&lt;&gt;"",AC26,IF(E26="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="8">
+        <f>IF(OR(AD26="",F26="",G26=""),"",AD26+F26*G26)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="8">
+        <f>IF(OR(E26="",A26=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="8">
+        <f>IF(OR(AD26="",AF26=""),"",AD26-AF26)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>IF(A26="","",IF(E26="","TERMINAL",IF(AG26="","INFO",IF(ABS(AG26)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -9281,10 +9935,31 @@
         <v/>
       </c>
       <c r="AA27" s="4">
-        <f>IF(A27="","",IF(OR(U27&gt;1,AND(X27&lt;&gt;"",X27&lt;Inputs!$B$16),AND(X27&lt;&gt;"",X27&gt;Inputs!$B$17),G27&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A27="","",IF(OR(U27&gt;1,AND(X27&lt;&gt;"",X27&lt;Inputs!$B$16),AND(X27&lt;&gt;"",X27&gt;Inputs!$B$17),G27&lt;Inputs!$B$18,AH27="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB27" s="4" t="n"/>
+      <c r="AC27" s="7" t="n"/>
+      <c r="AD27" s="8">
+        <f>IF(A27="","",IF(AC27&lt;&gt;"",AC27,IF(E27="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="8">
+        <f>IF(OR(AD27="",F27="",G27=""),"",AD27+F27*G27)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="8">
+        <f>IF(OR(E27="",A27=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="8">
+        <f>IF(OR(AD27="",AF27=""),"",AD27-AF27)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>IF(A27="","",IF(E27="","TERMINAL",IF(AG27="","INFO",IF(ABS(AG27)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -9355,10 +10030,31 @@
         <v/>
       </c>
       <c r="AA28" s="4">
-        <f>IF(A28="","",IF(OR(U28&gt;1,AND(X28&lt;&gt;"",X28&lt;Inputs!$B$16),AND(X28&lt;&gt;"",X28&gt;Inputs!$B$17),G28&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A28="","",IF(OR(U28&gt;1,AND(X28&lt;&gt;"",X28&lt;Inputs!$B$16),AND(X28&lt;&gt;"",X28&gt;Inputs!$B$17),G28&lt;Inputs!$B$18,AH28="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB28" s="4" t="n"/>
+      <c r="AC28" s="7" t="n"/>
+      <c r="AD28" s="8">
+        <f>IF(A28="","",IF(AC28&lt;&gt;"",AC28,IF(E28="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="8">
+        <f>IF(OR(AD28="",F28="",G28=""),"",AD28+F28*G28)</f>
+        <v/>
+      </c>
+      <c r="AF28" s="8">
+        <f>IF(OR(E28="",A28=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="8">
+        <f>IF(OR(AD28="",AF28=""),"",AD28-AF28)</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>IF(A28="","",IF(E28="","TERMINAL",IF(AG28="","INFO",IF(ABS(AG28)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -9429,10 +10125,31 @@
         <v/>
       </c>
       <c r="AA29" s="4">
-        <f>IF(A29="","",IF(OR(U29&gt;1,AND(X29&lt;&gt;"",X29&lt;Inputs!$B$16),AND(X29&lt;&gt;"",X29&gt;Inputs!$B$17),G29&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A29="","",IF(OR(U29&gt;1,AND(X29&lt;&gt;"",X29&lt;Inputs!$B$16),AND(X29&lt;&gt;"",X29&gt;Inputs!$B$17),G29&lt;Inputs!$B$18,AH29="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB29" s="4" t="n"/>
+      <c r="AC29" s="7" t="n"/>
+      <c r="AD29" s="8">
+        <f>IF(A29="","",IF(AC29&lt;&gt;"",AC29,IF(E29="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="8">
+        <f>IF(OR(AD29="",F29="",G29=""),"",AD29+F29*G29)</f>
+        <v/>
+      </c>
+      <c r="AF29" s="8">
+        <f>IF(OR(E29="",A29=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="8">
+        <f>IF(OR(AD29="",AF29=""),"",AD29-AF29)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="4">
+        <f>IF(A29="","",IF(E29="","TERMINAL",IF(AG29="","INFO",IF(ABS(AG29)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -9503,10 +10220,31 @@
         <v/>
       </c>
       <c r="AA30" s="4">
-        <f>IF(A30="","",IF(OR(U30&gt;1,AND(X30&lt;&gt;"",X30&lt;Inputs!$B$16),AND(X30&lt;&gt;"",X30&gt;Inputs!$B$17),G30&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A30="","",IF(OR(U30&gt;1,AND(X30&lt;&gt;"",X30&lt;Inputs!$B$16),AND(X30&lt;&gt;"",X30&gt;Inputs!$B$17),G30&lt;Inputs!$B$18,AH30="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB30" s="4" t="n"/>
+      <c r="AC30" s="7" t="n"/>
+      <c r="AD30" s="8">
+        <f>IF(A30="","",IF(AC30&lt;&gt;"",AC30,IF(E30="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="8">
+        <f>IF(OR(AD30="",F30="",G30=""),"",AD30+F30*G30)</f>
+        <v/>
+      </c>
+      <c r="AF30" s="8">
+        <f>IF(OR(E30="",A30=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="8">
+        <f>IF(OR(AD30="",AF30=""),"",AD30-AF30)</f>
+        <v/>
+      </c>
+      <c r="AH30" s="4">
+        <f>IF(A30="","",IF(E30="","TERMINAL",IF(AG30="","INFO",IF(ABS(AG30)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -9577,10 +10315,31 @@
         <v/>
       </c>
       <c r="AA31" s="4">
-        <f>IF(A31="","",IF(OR(U31&gt;1,AND(X31&lt;&gt;"",X31&lt;Inputs!$B$16),AND(X31&lt;&gt;"",X31&gt;Inputs!$B$17),G31&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A31="","",IF(OR(U31&gt;1,AND(X31&lt;&gt;"",X31&lt;Inputs!$B$16),AND(X31&lt;&gt;"",X31&gt;Inputs!$B$17),G31&lt;Inputs!$B$18,AH31="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB31" s="4" t="n"/>
+      <c r="AC31" s="7" t="n"/>
+      <c r="AD31" s="8">
+        <f>IF(A31="","",IF(AC31&lt;&gt;"",AC31,IF(E31="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="8">
+        <f>IF(OR(AD31="",F31="",G31=""),"",AD31+F31*G31)</f>
+        <v/>
+      </c>
+      <c r="AF31" s="8">
+        <f>IF(OR(E31="",A31=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="8">
+        <f>IF(OR(AD31="",AF31=""),"",AD31-AF31)</f>
+        <v/>
+      </c>
+      <c r="AH31" s="4">
+        <f>IF(A31="","",IF(E31="","TERMINAL",IF(AG31="","INFO",IF(ABS(AG31)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -9651,10 +10410,31 @@
         <v/>
       </c>
       <c r="AA32" s="4">
-        <f>IF(A32="","",IF(OR(U32&gt;1,AND(X32&lt;&gt;"",X32&lt;Inputs!$B$16),AND(X32&lt;&gt;"",X32&gt;Inputs!$B$17),G32&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A32="","",IF(OR(U32&gt;1,AND(X32&lt;&gt;"",X32&lt;Inputs!$B$16),AND(X32&lt;&gt;"",X32&gt;Inputs!$B$17),G32&lt;Inputs!$B$18,AH32="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB32" s="4" t="n"/>
+      <c r="AC32" s="7" t="n"/>
+      <c r="AD32" s="8">
+        <f>IF(A32="","",IF(AC32&lt;&gt;"",AC32,IF(E32="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="8">
+        <f>IF(OR(AD32="",F32="",G32=""),"",AD32+F32*G32)</f>
+        <v/>
+      </c>
+      <c r="AF32" s="8">
+        <f>IF(OR(E32="",A32=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="8">
+        <f>IF(OR(AD32="",AF32=""),"",AD32-AF32)</f>
+        <v/>
+      </c>
+      <c r="AH32" s="4">
+        <f>IF(A32="","",IF(E32="","TERMINAL",IF(AG32="","INFO",IF(ABS(AG32)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -9725,10 +10505,31 @@
         <v/>
       </c>
       <c r="AA33" s="4">
-        <f>IF(A33="","",IF(OR(U33&gt;1,AND(X33&lt;&gt;"",X33&lt;Inputs!$B$16),AND(X33&lt;&gt;"",X33&gt;Inputs!$B$17),G33&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A33="","",IF(OR(U33&gt;1,AND(X33&lt;&gt;"",X33&lt;Inputs!$B$16),AND(X33&lt;&gt;"",X33&gt;Inputs!$B$17),G33&lt;Inputs!$B$18,AH33="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB33" s="4" t="n"/>
+      <c r="AC33" s="7" t="n"/>
+      <c r="AD33" s="8">
+        <f>IF(A33="","",IF(AC33&lt;&gt;"",AC33,IF(E33="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="8">
+        <f>IF(OR(AD33="",F33="",G33=""),"",AD33+F33*G33)</f>
+        <v/>
+      </c>
+      <c r="AF33" s="8">
+        <f>IF(OR(E33="",A33=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="8">
+        <f>IF(OR(AD33="",AF33=""),"",AD33-AF33)</f>
+        <v/>
+      </c>
+      <c r="AH33" s="4">
+        <f>IF(A33="","",IF(E33="","TERMINAL",IF(AG33="","INFO",IF(ABS(AG33)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -9799,10 +10600,31 @@
         <v/>
       </c>
       <c r="AA34" s="4">
-        <f>IF(A34="","",IF(OR(U34&gt;1,AND(X34&lt;&gt;"",X34&lt;Inputs!$B$16),AND(X34&lt;&gt;"",X34&gt;Inputs!$B$17),G34&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A34="","",IF(OR(U34&gt;1,AND(X34&lt;&gt;"",X34&lt;Inputs!$B$16),AND(X34&lt;&gt;"",X34&gt;Inputs!$B$17),G34&lt;Inputs!$B$18,AH34="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB34" s="4" t="n"/>
+      <c r="AC34" s="7" t="n"/>
+      <c r="AD34" s="8">
+        <f>IF(A34="","",IF(AC34&lt;&gt;"",AC34,IF(E34="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="8">
+        <f>IF(OR(AD34="",F34="",G34=""),"",AD34+F34*G34)</f>
+        <v/>
+      </c>
+      <c r="AF34" s="8">
+        <f>IF(OR(E34="",A34=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="8">
+        <f>IF(OR(AD34="",AF34=""),"",AD34-AF34)</f>
+        <v/>
+      </c>
+      <c r="AH34" s="4">
+        <f>IF(A34="","",IF(E34="","TERMINAL",IF(AG34="","INFO",IF(ABS(AG34)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -9873,10 +10695,31 @@
         <v/>
       </c>
       <c r="AA35" s="4">
-        <f>IF(A35="","",IF(OR(U35&gt;1,AND(X35&lt;&gt;"",X35&lt;Inputs!$B$16),AND(X35&lt;&gt;"",X35&gt;Inputs!$B$17),G35&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A35="","",IF(OR(U35&gt;1,AND(X35&lt;&gt;"",X35&lt;Inputs!$B$16),AND(X35&lt;&gt;"",X35&gt;Inputs!$B$17),G35&lt;Inputs!$B$18,AH35="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB35" s="4" t="n"/>
+      <c r="AC35" s="7" t="n"/>
+      <c r="AD35" s="8">
+        <f>IF(A35="","",IF(AC35&lt;&gt;"",AC35,IF(E35="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="8">
+        <f>IF(OR(AD35="",F35="",G35=""),"",AD35+F35*G35)</f>
+        <v/>
+      </c>
+      <c r="AF35" s="8">
+        <f>IF(OR(E35="",A35=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="8">
+        <f>IF(OR(AD35="",AF35=""),"",AD35-AF35)</f>
+        <v/>
+      </c>
+      <c r="AH35" s="4">
+        <f>IF(A35="","",IF(E35="","TERMINAL",IF(AG35="","INFO",IF(ABS(AG35)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -9947,10 +10790,31 @@
         <v/>
       </c>
       <c r="AA36" s="4">
-        <f>IF(A36="","",IF(OR(U36&gt;1,AND(X36&lt;&gt;"",X36&lt;Inputs!$B$16),AND(X36&lt;&gt;"",X36&gt;Inputs!$B$17),G36&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A36="","",IF(OR(U36&gt;1,AND(X36&lt;&gt;"",X36&lt;Inputs!$B$16),AND(X36&lt;&gt;"",X36&gt;Inputs!$B$17),G36&lt;Inputs!$B$18,AH36="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB36" s="4" t="n"/>
+      <c r="AC36" s="7" t="n"/>
+      <c r="AD36" s="8">
+        <f>IF(A36="","",IF(AC36&lt;&gt;"",AC36,IF(E36="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="8">
+        <f>IF(OR(AD36="",F36="",G36=""),"",AD36+F36*G36)</f>
+        <v/>
+      </c>
+      <c r="AF36" s="8">
+        <f>IF(OR(E36="",A36=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="8">
+        <f>IF(OR(AD36="",AF36=""),"",AD36-AF36)</f>
+        <v/>
+      </c>
+      <c r="AH36" s="4">
+        <f>IF(A36="","",IF(E36="","TERMINAL",IF(AG36="","INFO",IF(ABS(AG36)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -10021,10 +10885,31 @@
         <v/>
       </c>
       <c r="AA37" s="4">
-        <f>IF(A37="","",IF(OR(U37&gt;1,AND(X37&lt;&gt;"",X37&lt;Inputs!$B$16),AND(X37&lt;&gt;"",X37&gt;Inputs!$B$17),G37&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A37="","",IF(OR(U37&gt;1,AND(X37&lt;&gt;"",X37&lt;Inputs!$B$16),AND(X37&lt;&gt;"",X37&gt;Inputs!$B$17),G37&lt;Inputs!$B$18,AH37="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB37" s="4" t="n"/>
+      <c r="AC37" s="7" t="n"/>
+      <c r="AD37" s="8">
+        <f>IF(A37="","",IF(AC37&lt;&gt;"",AC37,IF(E37="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="8">
+        <f>IF(OR(AD37="",F37="",G37=""),"",AD37+F37*G37)</f>
+        <v/>
+      </c>
+      <c r="AF37" s="8">
+        <f>IF(OR(E37="",A37=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="8">
+        <f>IF(OR(AD37="",AF37=""),"",AD37-AF37)</f>
+        <v/>
+      </c>
+      <c r="AH37" s="4">
+        <f>IF(A37="","",IF(E37="","TERMINAL",IF(AG37="","INFO",IF(ABS(AG37)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -10095,10 +10980,31 @@
         <v/>
       </c>
       <c r="AA38" s="4">
-        <f>IF(A38="","",IF(OR(U38&gt;1,AND(X38&lt;&gt;"",X38&lt;Inputs!$B$16),AND(X38&lt;&gt;"",X38&gt;Inputs!$B$17),G38&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A38="","",IF(OR(U38&gt;1,AND(X38&lt;&gt;"",X38&lt;Inputs!$B$16),AND(X38&lt;&gt;"",X38&gt;Inputs!$B$17),G38&lt;Inputs!$B$18,AH38="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB38" s="4" t="n"/>
+      <c r="AC38" s="7" t="n"/>
+      <c r="AD38" s="8">
+        <f>IF(A38="","",IF(AC38&lt;&gt;"",AC38,IF(E38="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE38" s="8">
+        <f>IF(OR(AD38="",F38="",G38=""),"",AD38+F38*G38)</f>
+        <v/>
+      </c>
+      <c r="AF38" s="8">
+        <f>IF(OR(E38="",A38=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG38" s="8">
+        <f>IF(OR(AD38="",AF38=""),"",AD38-AF38)</f>
+        <v/>
+      </c>
+      <c r="AH38" s="4">
+        <f>IF(A38="","",IF(E38="","TERMINAL",IF(AG38="","INFO",IF(ABS(AG38)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -10169,10 +11075,31 @@
         <v/>
       </c>
       <c r="AA39" s="4">
-        <f>IF(A39="","",IF(OR(U39&gt;1,AND(X39&lt;&gt;"",X39&lt;Inputs!$B$16),AND(X39&lt;&gt;"",X39&gt;Inputs!$B$17),G39&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A39="","",IF(OR(U39&gt;1,AND(X39&lt;&gt;"",X39&lt;Inputs!$B$16),AND(X39&lt;&gt;"",X39&gt;Inputs!$B$17),G39&lt;Inputs!$B$18,AH39="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB39" s="4" t="n"/>
+      <c r="AC39" s="7" t="n"/>
+      <c r="AD39" s="8">
+        <f>IF(A39="","",IF(AC39&lt;&gt;"",AC39,IF(E39="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE39" s="8">
+        <f>IF(OR(AD39="",F39="",G39=""),"",AD39+F39*G39)</f>
+        <v/>
+      </c>
+      <c r="AF39" s="8">
+        <f>IF(OR(E39="",A39=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG39" s="8">
+        <f>IF(OR(AD39="",AF39=""),"",AD39-AF39)</f>
+        <v/>
+      </c>
+      <c r="AH39" s="4">
+        <f>IF(A39="","",IF(E39="","TERMINAL",IF(AG39="","INFO",IF(ABS(AG39)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -10243,10 +11170,31 @@
         <v/>
       </c>
       <c r="AA40" s="4">
-        <f>IF(A40="","",IF(OR(U40&gt;1,AND(X40&lt;&gt;"",X40&lt;Inputs!$B$16),AND(X40&lt;&gt;"",X40&gt;Inputs!$B$17),G40&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A40="","",IF(OR(U40&gt;1,AND(X40&lt;&gt;"",X40&lt;Inputs!$B$16),AND(X40&lt;&gt;"",X40&gt;Inputs!$B$17),G40&lt;Inputs!$B$18,AH40="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB40" s="4" t="n"/>
+      <c r="AC40" s="7" t="n"/>
+      <c r="AD40" s="8">
+        <f>IF(A40="","",IF(AC40&lt;&gt;"",AC40,IF(E40="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE40" s="8">
+        <f>IF(OR(AD40="",F40="",G40=""),"",AD40+F40*G40)</f>
+        <v/>
+      </c>
+      <c r="AF40" s="8">
+        <f>IF(OR(E40="",A40=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG40" s="8">
+        <f>IF(OR(AD40="",AF40=""),"",AD40-AF40)</f>
+        <v/>
+      </c>
+      <c r="AH40" s="4">
+        <f>IF(A40="","",IF(E40="","TERMINAL",IF(AG40="","INFO",IF(ABS(AG40)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -10317,10 +11265,31 @@
         <v/>
       </c>
       <c r="AA41" s="4">
-        <f>IF(A41="","",IF(OR(U41&gt;1,AND(X41&lt;&gt;"",X41&lt;Inputs!$B$16),AND(X41&lt;&gt;"",X41&gt;Inputs!$B$17),G41&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A41="","",IF(OR(U41&gt;1,AND(X41&lt;&gt;"",X41&lt;Inputs!$B$16),AND(X41&lt;&gt;"",X41&gt;Inputs!$B$17),G41&lt;Inputs!$B$18,AH41="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB41" s="4" t="n"/>
+      <c r="AC41" s="7" t="n"/>
+      <c r="AD41" s="8">
+        <f>IF(A41="","",IF(AC41&lt;&gt;"",AC41,IF(E41="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE41" s="8">
+        <f>IF(OR(AD41="",F41="",G41=""),"",AD41+F41*G41)</f>
+        <v/>
+      </c>
+      <c r="AF41" s="8">
+        <f>IF(OR(E41="",A41=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG41" s="8">
+        <f>IF(OR(AD41="",AF41=""),"",AD41-AF41)</f>
+        <v/>
+      </c>
+      <c r="AH41" s="4">
+        <f>IF(A41="","",IF(E41="","TERMINAL",IF(AG41="","INFO",IF(ABS(AG41)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -10391,10 +11360,31 @@
         <v/>
       </c>
       <c r="AA42" s="4">
-        <f>IF(A42="","",IF(OR(U42&gt;1,AND(X42&lt;&gt;"",X42&lt;Inputs!$B$16),AND(X42&lt;&gt;"",X42&gt;Inputs!$B$17),G42&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A42="","",IF(OR(U42&gt;1,AND(X42&lt;&gt;"",X42&lt;Inputs!$B$16),AND(X42&lt;&gt;"",X42&gt;Inputs!$B$17),G42&lt;Inputs!$B$18,AH42="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB42" s="4" t="n"/>
+      <c r="AC42" s="7" t="n"/>
+      <c r="AD42" s="8">
+        <f>IF(A42="","",IF(AC42&lt;&gt;"",AC42,IF(E42="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE42" s="8">
+        <f>IF(OR(AD42="",F42="",G42=""),"",AD42+F42*G42)</f>
+        <v/>
+      </c>
+      <c r="AF42" s="8">
+        <f>IF(OR(E42="",A42=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG42" s="8">
+        <f>IF(OR(AD42="",AF42=""),"",AD42-AF42)</f>
+        <v/>
+      </c>
+      <c r="AH42" s="4">
+        <f>IF(A42="","",IF(E42="","TERMINAL",IF(AG42="","INFO",IF(ABS(AG42)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -10465,10 +11455,31 @@
         <v/>
       </c>
       <c r="AA43" s="4">
-        <f>IF(A43="","",IF(OR(U43&gt;1,AND(X43&lt;&gt;"",X43&lt;Inputs!$B$16),AND(X43&lt;&gt;"",X43&gt;Inputs!$B$17),G43&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A43="","",IF(OR(U43&gt;1,AND(X43&lt;&gt;"",X43&lt;Inputs!$B$16),AND(X43&lt;&gt;"",X43&gt;Inputs!$B$17),G43&lt;Inputs!$B$18,AH43="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB43" s="4" t="n"/>
+      <c r="AC43" s="7" t="n"/>
+      <c r="AD43" s="8">
+        <f>IF(A43="","",IF(AC43&lt;&gt;"",AC43,IF(E43="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE43" s="8">
+        <f>IF(OR(AD43="",F43="",G43=""),"",AD43+F43*G43)</f>
+        <v/>
+      </c>
+      <c r="AF43" s="8">
+        <f>IF(OR(E43="",A43=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG43" s="8">
+        <f>IF(OR(AD43="",AF43=""),"",AD43-AF43)</f>
+        <v/>
+      </c>
+      <c r="AH43" s="4">
+        <f>IF(A43="","",IF(E43="","TERMINAL",IF(AG43="","INFO",IF(ABS(AG43)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -10539,10 +11550,31 @@
         <v/>
       </c>
       <c r="AA44" s="4">
-        <f>IF(A44="","",IF(OR(U44&gt;1,AND(X44&lt;&gt;"",X44&lt;Inputs!$B$16),AND(X44&lt;&gt;"",X44&gt;Inputs!$B$17),G44&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A44="","",IF(OR(U44&gt;1,AND(X44&lt;&gt;"",X44&lt;Inputs!$B$16),AND(X44&lt;&gt;"",X44&gt;Inputs!$B$17),G44&lt;Inputs!$B$18,AH44="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB44" s="4" t="n"/>
+      <c r="AC44" s="7" t="n"/>
+      <c r="AD44" s="8">
+        <f>IF(A44="","",IF(AC44&lt;&gt;"",AC44,IF(E44="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE44" s="8">
+        <f>IF(OR(AD44="",F44="",G44=""),"",AD44+F44*G44)</f>
+        <v/>
+      </c>
+      <c r="AF44" s="8">
+        <f>IF(OR(E44="",A44=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG44" s="8">
+        <f>IF(OR(AD44="",AF44=""),"",AD44-AF44)</f>
+        <v/>
+      </c>
+      <c r="AH44" s="4">
+        <f>IF(A44="","",IF(E44="","TERMINAL",IF(AG44="","INFO",IF(ABS(AG44)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -10613,10 +11645,31 @@
         <v/>
       </c>
       <c r="AA45" s="4">
-        <f>IF(A45="","",IF(OR(U45&gt;1,AND(X45&lt;&gt;"",X45&lt;Inputs!$B$16),AND(X45&lt;&gt;"",X45&gt;Inputs!$B$17),G45&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A45="","",IF(OR(U45&gt;1,AND(X45&lt;&gt;"",X45&lt;Inputs!$B$16),AND(X45&lt;&gt;"",X45&gt;Inputs!$B$17),G45&lt;Inputs!$B$18,AH45="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB45" s="4" t="n"/>
+      <c r="AC45" s="7" t="n"/>
+      <c r="AD45" s="8">
+        <f>IF(A45="","",IF(AC45&lt;&gt;"",AC45,IF(E45="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE45" s="8">
+        <f>IF(OR(AD45="",F45="",G45=""),"",AD45+F45*G45)</f>
+        <v/>
+      </c>
+      <c r="AF45" s="8">
+        <f>IF(OR(E45="",A45=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG45" s="8">
+        <f>IF(OR(AD45="",AF45=""),"",AD45-AF45)</f>
+        <v/>
+      </c>
+      <c r="AH45" s="4">
+        <f>IF(A45="","",IF(E45="","TERMINAL",IF(AG45="","INFO",IF(ABS(AG45)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -10687,10 +11740,31 @@
         <v/>
       </c>
       <c r="AA46" s="4">
-        <f>IF(A46="","",IF(OR(U46&gt;1,AND(X46&lt;&gt;"",X46&lt;Inputs!$B$16),AND(X46&lt;&gt;"",X46&gt;Inputs!$B$17),G46&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A46="","",IF(OR(U46&gt;1,AND(X46&lt;&gt;"",X46&lt;Inputs!$B$16),AND(X46&lt;&gt;"",X46&gt;Inputs!$B$17),G46&lt;Inputs!$B$18,AH46="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB46" s="4" t="n"/>
+      <c r="AC46" s="7" t="n"/>
+      <c r="AD46" s="8">
+        <f>IF(A46="","",IF(AC46&lt;&gt;"",AC46,IF(E46="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE46" s="8">
+        <f>IF(OR(AD46="",F46="",G46=""),"",AD46+F46*G46)</f>
+        <v/>
+      </c>
+      <c r="AF46" s="8">
+        <f>IF(OR(E46="",A46=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG46" s="8">
+        <f>IF(OR(AD46="",AF46=""),"",AD46-AF46)</f>
+        <v/>
+      </c>
+      <c r="AH46" s="4">
+        <f>IF(A46="","",IF(E46="","TERMINAL",IF(AG46="","INFO",IF(ABS(AG46)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -10761,10 +11835,31 @@
         <v/>
       </c>
       <c r="AA47" s="4">
-        <f>IF(A47="","",IF(OR(U47&gt;1,AND(X47&lt;&gt;"",X47&lt;Inputs!$B$16),AND(X47&lt;&gt;"",X47&gt;Inputs!$B$17),G47&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A47="","",IF(OR(U47&gt;1,AND(X47&lt;&gt;"",X47&lt;Inputs!$B$16),AND(X47&lt;&gt;"",X47&gt;Inputs!$B$17),G47&lt;Inputs!$B$18,AH47="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB47" s="4" t="n"/>
+      <c r="AC47" s="7" t="n"/>
+      <c r="AD47" s="8">
+        <f>IF(A47="","",IF(AC47&lt;&gt;"",AC47,IF(E47="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE47" s="8">
+        <f>IF(OR(AD47="",F47="",G47=""),"",AD47+F47*G47)</f>
+        <v/>
+      </c>
+      <c r="AF47" s="8">
+        <f>IF(OR(E47="",A47=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG47" s="8">
+        <f>IF(OR(AD47="",AF47=""),"",AD47-AF47)</f>
+        <v/>
+      </c>
+      <c r="AH47" s="4">
+        <f>IF(A47="","",IF(E47="","TERMINAL",IF(AG47="","INFO",IF(ABS(AG47)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -10835,10 +11930,31 @@
         <v/>
       </c>
       <c r="AA48" s="4">
-        <f>IF(A48="","",IF(OR(U48&gt;1,AND(X48&lt;&gt;"",X48&lt;Inputs!$B$16),AND(X48&lt;&gt;"",X48&gt;Inputs!$B$17),G48&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A48="","",IF(OR(U48&gt;1,AND(X48&lt;&gt;"",X48&lt;Inputs!$B$16),AND(X48&lt;&gt;"",X48&gt;Inputs!$B$17),G48&lt;Inputs!$B$18,AH48="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB48" s="4" t="n"/>
+      <c r="AC48" s="7" t="n"/>
+      <c r="AD48" s="8">
+        <f>IF(A48="","",IF(AC48&lt;&gt;"",AC48,IF(E48="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE48" s="8">
+        <f>IF(OR(AD48="",F48="",G48=""),"",AD48+F48*G48)</f>
+        <v/>
+      </c>
+      <c r="AF48" s="8">
+        <f>IF(OR(E48="",A48=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG48" s="8">
+        <f>IF(OR(AD48="",AF48=""),"",AD48-AF48)</f>
+        <v/>
+      </c>
+      <c r="AH48" s="4">
+        <f>IF(A48="","",IF(E48="","TERMINAL",IF(AG48="","INFO",IF(ABS(AG48)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -10909,10 +12025,31 @@
         <v/>
       </c>
       <c r="AA49" s="4">
-        <f>IF(A49="","",IF(OR(U49&gt;1,AND(X49&lt;&gt;"",X49&lt;Inputs!$B$16),AND(X49&lt;&gt;"",X49&gt;Inputs!$B$17),G49&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A49="","",IF(OR(U49&gt;1,AND(X49&lt;&gt;"",X49&lt;Inputs!$B$16),AND(X49&lt;&gt;"",X49&gt;Inputs!$B$17),G49&lt;Inputs!$B$18,AH49="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB49" s="4" t="n"/>
+      <c r="AC49" s="7" t="n"/>
+      <c r="AD49" s="8">
+        <f>IF(A49="","",IF(AC49&lt;&gt;"",AC49,IF(E49="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE49" s="8">
+        <f>IF(OR(AD49="",F49="",G49=""),"",AD49+F49*G49)</f>
+        <v/>
+      </c>
+      <c r="AF49" s="8">
+        <f>IF(OR(E49="",A49=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG49" s="8">
+        <f>IF(OR(AD49="",AF49=""),"",AD49-AF49)</f>
+        <v/>
+      </c>
+      <c r="AH49" s="4">
+        <f>IF(A49="","",IF(E49="","TERMINAL",IF(AG49="","INFO",IF(ABS(AG49)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -10983,10 +12120,31 @@
         <v/>
       </c>
       <c r="AA50" s="4">
-        <f>IF(A50="","",IF(OR(U50&gt;1,AND(X50&lt;&gt;"",X50&lt;Inputs!$B$16),AND(X50&lt;&gt;"",X50&gt;Inputs!$B$17),G50&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A50="","",IF(OR(U50&gt;1,AND(X50&lt;&gt;"",X50&lt;Inputs!$B$16),AND(X50&lt;&gt;"",X50&gt;Inputs!$B$17),G50&lt;Inputs!$B$18,AH50="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB50" s="4" t="n"/>
+      <c r="AC50" s="7" t="n"/>
+      <c r="AD50" s="8">
+        <f>IF(A50="","",IF(AC50&lt;&gt;"",AC50,IF(E50="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE50" s="8">
+        <f>IF(OR(AD50="",F50="",G50=""),"",AD50+F50*G50)</f>
+        <v/>
+      </c>
+      <c r="AF50" s="8">
+        <f>IF(OR(E50="",A50=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG50" s="8">
+        <f>IF(OR(AD50="",AF50=""),"",AD50-AF50)</f>
+        <v/>
+      </c>
+      <c r="AH50" s="4">
+        <f>IF(A50="","",IF(E50="","TERMINAL",IF(AG50="","INFO",IF(ABS(AG50)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -11057,10 +12215,31 @@
         <v/>
       </c>
       <c r="AA51" s="4">
-        <f>IF(A51="","",IF(OR(U51&gt;1,AND(X51&lt;&gt;"",X51&lt;Inputs!$B$16),AND(X51&lt;&gt;"",X51&gt;Inputs!$B$17),G51&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A51="","",IF(OR(U51&gt;1,AND(X51&lt;&gt;"",X51&lt;Inputs!$B$16),AND(X51&lt;&gt;"",X51&gt;Inputs!$B$17),G51&lt;Inputs!$B$18,AH51="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB51" s="4" t="n"/>
+      <c r="AC51" s="7" t="n"/>
+      <c r="AD51" s="8">
+        <f>IF(A51="","",IF(AC51&lt;&gt;"",AC51,IF(E51="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE51" s="8">
+        <f>IF(OR(AD51="",F51="",G51=""),"",AD51+F51*G51)</f>
+        <v/>
+      </c>
+      <c r="AF51" s="8">
+        <f>IF(OR(E51="",A51=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG51" s="8">
+        <f>IF(OR(AD51="",AF51=""),"",AD51-AF51)</f>
+        <v/>
+      </c>
+      <c r="AH51" s="4">
+        <f>IF(A51="","",IF(E51="","TERMINAL",IF(AG51="","INFO",IF(ABS(AG51)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -11131,10 +12310,31 @@
         <v/>
       </c>
       <c r="AA52" s="4">
-        <f>IF(A52="","",IF(OR(U52&gt;1,AND(X52&lt;&gt;"",X52&lt;Inputs!$B$16),AND(X52&lt;&gt;"",X52&gt;Inputs!$B$17),G52&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A52="","",IF(OR(U52&gt;1,AND(X52&lt;&gt;"",X52&lt;Inputs!$B$16),AND(X52&lt;&gt;"",X52&gt;Inputs!$B$17),G52&lt;Inputs!$B$18,AH52="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB52" s="4" t="n"/>
+      <c r="AC52" s="7" t="n"/>
+      <c r="AD52" s="8">
+        <f>IF(A52="","",IF(AC52&lt;&gt;"",AC52,IF(E52="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE52" s="8">
+        <f>IF(OR(AD52="",F52="",G52=""),"",AD52+F52*G52)</f>
+        <v/>
+      </c>
+      <c r="AF52" s="8">
+        <f>IF(OR(E52="",A52=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG52" s="8">
+        <f>IF(OR(AD52="",AF52=""),"",AD52-AF52)</f>
+        <v/>
+      </c>
+      <c r="AH52" s="4">
+        <f>IF(A52="","",IF(E52="","TERMINAL",IF(AG52="","INFO",IF(ABS(AG52)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -11205,10 +12405,31 @@
         <v/>
       </c>
       <c r="AA53" s="4">
-        <f>IF(A53="","",IF(OR(U53&gt;1,AND(X53&lt;&gt;"",X53&lt;Inputs!$B$16),AND(X53&lt;&gt;"",X53&gt;Inputs!$B$17),G53&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A53="","",IF(OR(U53&gt;1,AND(X53&lt;&gt;"",X53&lt;Inputs!$B$16),AND(X53&lt;&gt;"",X53&gt;Inputs!$B$17),G53&lt;Inputs!$B$18,AH53="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB53" s="4" t="n"/>
+      <c r="AC53" s="7" t="n"/>
+      <c r="AD53" s="8">
+        <f>IF(A53="","",IF(AC53&lt;&gt;"",AC53,IF(E53="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE53" s="8">
+        <f>IF(OR(AD53="",F53="",G53=""),"",AD53+F53*G53)</f>
+        <v/>
+      </c>
+      <c r="AF53" s="8">
+        <f>IF(OR(E53="",A53=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG53" s="8">
+        <f>IF(OR(AD53="",AF53=""),"",AD53-AF53)</f>
+        <v/>
+      </c>
+      <c r="AH53" s="4">
+        <f>IF(A53="","",IF(E53="","TERMINAL",IF(AG53="","INFO",IF(ABS(AG53)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -11279,10 +12500,31 @@
         <v/>
       </c>
       <c r="AA54" s="4">
-        <f>IF(A54="","",IF(OR(U54&gt;1,AND(X54&lt;&gt;"",X54&lt;Inputs!$B$16),AND(X54&lt;&gt;"",X54&gt;Inputs!$B$17),G54&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A54="","",IF(OR(U54&gt;1,AND(X54&lt;&gt;"",X54&lt;Inputs!$B$16),AND(X54&lt;&gt;"",X54&gt;Inputs!$B$17),G54&lt;Inputs!$B$18,AH54="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB54" s="4" t="n"/>
+      <c r="AC54" s="7" t="n"/>
+      <c r="AD54" s="8">
+        <f>IF(A54="","",IF(AC54&lt;&gt;"",AC54,IF(E54="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE54" s="8">
+        <f>IF(OR(AD54="",F54="",G54=""),"",AD54+F54*G54)</f>
+        <v/>
+      </c>
+      <c r="AF54" s="8">
+        <f>IF(OR(E54="",A54=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG54" s="8">
+        <f>IF(OR(AD54="",AF54=""),"",AD54-AF54)</f>
+        <v/>
+      </c>
+      <c r="AH54" s="4">
+        <f>IF(A54="","",IF(E54="","TERMINAL",IF(AG54="","INFO",IF(ABS(AG54)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -11353,10 +12595,31 @@
         <v/>
       </c>
       <c r="AA55" s="4">
-        <f>IF(A55="","",IF(OR(U55&gt;1,AND(X55&lt;&gt;"",X55&lt;Inputs!$B$16),AND(X55&lt;&gt;"",X55&gt;Inputs!$B$17),G55&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A55="","",IF(OR(U55&gt;1,AND(X55&lt;&gt;"",X55&lt;Inputs!$B$16),AND(X55&lt;&gt;"",X55&gt;Inputs!$B$17),G55&lt;Inputs!$B$18,AH55="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB55" s="4" t="n"/>
+      <c r="AC55" s="7" t="n"/>
+      <c r="AD55" s="8">
+        <f>IF(A55="","",IF(AC55&lt;&gt;"",AC55,IF(E55="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE55" s="8">
+        <f>IF(OR(AD55="",F55="",G55=""),"",AD55+F55*G55)</f>
+        <v/>
+      </c>
+      <c r="AF55" s="8">
+        <f>IF(OR(E55="",A55=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG55" s="8">
+        <f>IF(OR(AD55="",AF55=""),"",AD55-AF55)</f>
+        <v/>
+      </c>
+      <c r="AH55" s="4">
+        <f>IF(A55="","",IF(E55="","TERMINAL",IF(AG55="","INFO",IF(ABS(AG55)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -11427,10 +12690,31 @@
         <v/>
       </c>
       <c r="AA56" s="4">
-        <f>IF(A56="","",IF(OR(U56&gt;1,AND(X56&lt;&gt;"",X56&lt;Inputs!$B$16),AND(X56&lt;&gt;"",X56&gt;Inputs!$B$17),G56&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A56="","",IF(OR(U56&gt;1,AND(X56&lt;&gt;"",X56&lt;Inputs!$B$16),AND(X56&lt;&gt;"",X56&gt;Inputs!$B$17),G56&lt;Inputs!$B$18,AH56="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB56" s="4" t="n"/>
+      <c r="AC56" s="7" t="n"/>
+      <c r="AD56" s="8">
+        <f>IF(A56="","",IF(AC56&lt;&gt;"",AC56,IF(E56="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE56" s="8">
+        <f>IF(OR(AD56="",F56="",G56=""),"",AD56+F56*G56)</f>
+        <v/>
+      </c>
+      <c r="AF56" s="8">
+        <f>IF(OR(E56="",A56=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG56" s="8">
+        <f>IF(OR(AD56="",AF56=""),"",AD56-AF56)</f>
+        <v/>
+      </c>
+      <c r="AH56" s="4">
+        <f>IF(A56="","",IF(E56="","TERMINAL",IF(AG56="","INFO",IF(ABS(AG56)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -11501,10 +12785,31 @@
         <v/>
       </c>
       <c r="AA57" s="4">
-        <f>IF(A57="","",IF(OR(U57&gt;1,AND(X57&lt;&gt;"",X57&lt;Inputs!$B$16),AND(X57&lt;&gt;"",X57&gt;Inputs!$B$17),G57&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A57="","",IF(OR(U57&gt;1,AND(X57&lt;&gt;"",X57&lt;Inputs!$B$16),AND(X57&lt;&gt;"",X57&gt;Inputs!$B$17),G57&lt;Inputs!$B$18,AH57="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB57" s="4" t="n"/>
+      <c r="AC57" s="7" t="n"/>
+      <c r="AD57" s="8">
+        <f>IF(A57="","",IF(AC57&lt;&gt;"",AC57,IF(E57="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE57" s="8">
+        <f>IF(OR(AD57="",F57="",G57=""),"",AD57+F57*G57)</f>
+        <v/>
+      </c>
+      <c r="AF57" s="8">
+        <f>IF(OR(E57="",A57=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG57" s="8">
+        <f>IF(OR(AD57="",AF57=""),"",AD57-AF57)</f>
+        <v/>
+      </c>
+      <c r="AH57" s="4">
+        <f>IF(A57="","",IF(E57="","TERMINAL",IF(AG57="","INFO",IF(ABS(AG57)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -11575,10 +12880,31 @@
         <v/>
       </c>
       <c r="AA58" s="4">
-        <f>IF(A58="","",IF(OR(U58&gt;1,AND(X58&lt;&gt;"",X58&lt;Inputs!$B$16),AND(X58&lt;&gt;"",X58&gt;Inputs!$B$17),G58&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A58="","",IF(OR(U58&gt;1,AND(X58&lt;&gt;"",X58&lt;Inputs!$B$16),AND(X58&lt;&gt;"",X58&gt;Inputs!$B$17),G58&lt;Inputs!$B$18,AH58="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB58" s="4" t="n"/>
+      <c r="AC58" s="7" t="n"/>
+      <c r="AD58" s="8">
+        <f>IF(A58="","",IF(AC58&lt;&gt;"",AC58,IF(E58="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE58" s="8">
+        <f>IF(OR(AD58="",F58="",G58=""),"",AD58+F58*G58)</f>
+        <v/>
+      </c>
+      <c r="AF58" s="8">
+        <f>IF(OR(E58="",A58=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG58" s="8">
+        <f>IF(OR(AD58="",AF58=""),"",AD58-AF58)</f>
+        <v/>
+      </c>
+      <c r="AH58" s="4">
+        <f>IF(A58="","",IF(E58="","TERMINAL",IF(AG58="","INFO",IF(ABS(AG58)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -11649,10 +12975,31 @@
         <v/>
       </c>
       <c r="AA59" s="4">
-        <f>IF(A59="","",IF(OR(U59&gt;1,AND(X59&lt;&gt;"",X59&lt;Inputs!$B$16),AND(X59&lt;&gt;"",X59&gt;Inputs!$B$17),G59&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A59="","",IF(OR(U59&gt;1,AND(X59&lt;&gt;"",X59&lt;Inputs!$B$16),AND(X59&lt;&gt;"",X59&gt;Inputs!$B$17),G59&lt;Inputs!$B$18,AH59="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB59" s="4" t="n"/>
+      <c r="AC59" s="7" t="n"/>
+      <c r="AD59" s="8">
+        <f>IF(A59="","",IF(AC59&lt;&gt;"",AC59,IF(E59="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE59" s="8">
+        <f>IF(OR(AD59="",F59="",G59=""),"",AD59+F59*G59)</f>
+        <v/>
+      </c>
+      <c r="AF59" s="8">
+        <f>IF(OR(E59="",A59=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG59" s="8">
+        <f>IF(OR(AD59="",AF59=""),"",AD59-AF59)</f>
+        <v/>
+      </c>
+      <c r="AH59" s="4">
+        <f>IF(A59="","",IF(E59="","TERMINAL",IF(AG59="","INFO",IF(ABS(AG59)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -11723,10 +13070,31 @@
         <v/>
       </c>
       <c r="AA60" s="4">
-        <f>IF(A60="","",IF(OR(U60&gt;1,AND(X60&lt;&gt;"",X60&lt;Inputs!$B$16),AND(X60&lt;&gt;"",X60&gt;Inputs!$B$17),G60&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A60="","",IF(OR(U60&gt;1,AND(X60&lt;&gt;"",X60&lt;Inputs!$B$16),AND(X60&lt;&gt;"",X60&gt;Inputs!$B$17),G60&lt;Inputs!$B$18,AH60="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB60" s="4" t="n"/>
+      <c r="AC60" s="7" t="n"/>
+      <c r="AD60" s="8">
+        <f>IF(A60="","",IF(AC60&lt;&gt;"",AC60,IF(E60="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE60" s="8">
+        <f>IF(OR(AD60="",F60="",G60=""),"",AD60+F60*G60)</f>
+        <v/>
+      </c>
+      <c r="AF60" s="8">
+        <f>IF(OR(E60="",A60=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG60" s="8">
+        <f>IF(OR(AD60="",AF60=""),"",AD60-AF60)</f>
+        <v/>
+      </c>
+      <c r="AH60" s="4">
+        <f>IF(A60="","",IF(E60="","TERMINAL",IF(AG60="","INFO",IF(ABS(AG60)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -11797,10 +13165,31 @@
         <v/>
       </c>
       <c r="AA61" s="4">
-        <f>IF(A61="","",IF(OR(U61&gt;1,AND(X61&lt;&gt;"",X61&lt;Inputs!$B$16),AND(X61&lt;&gt;"",X61&gt;Inputs!$B$17),G61&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A61="","",IF(OR(U61&gt;1,AND(X61&lt;&gt;"",X61&lt;Inputs!$B$16),AND(X61&lt;&gt;"",X61&gt;Inputs!$B$17),G61&lt;Inputs!$B$18,AH61="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB61" s="4" t="n"/>
+      <c r="AC61" s="7" t="n"/>
+      <c r="AD61" s="8">
+        <f>IF(A61="","",IF(AC61&lt;&gt;"",AC61,IF(E61="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE61" s="8">
+        <f>IF(OR(AD61="",F61="",G61=""),"",AD61+F61*G61)</f>
+        <v/>
+      </c>
+      <c r="AF61" s="8">
+        <f>IF(OR(E61="",A61=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG61" s="8">
+        <f>IF(OR(AD61="",AF61=""),"",AD61-AF61)</f>
+        <v/>
+      </c>
+      <c r="AH61" s="4">
+        <f>IF(A61="","",IF(E61="","TERMINAL",IF(AG61="","INFO",IF(ABS(AG61)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -11871,10 +13260,31 @@
         <v/>
       </c>
       <c r="AA62" s="4">
-        <f>IF(A62="","",IF(OR(U62&gt;1,AND(X62&lt;&gt;"",X62&lt;Inputs!$B$16),AND(X62&lt;&gt;"",X62&gt;Inputs!$B$17),G62&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A62="","",IF(OR(U62&gt;1,AND(X62&lt;&gt;"",X62&lt;Inputs!$B$16),AND(X62&lt;&gt;"",X62&gt;Inputs!$B$17),G62&lt;Inputs!$B$18,AH62="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB62" s="4" t="n"/>
+      <c r="AC62" s="7" t="n"/>
+      <c r="AD62" s="8">
+        <f>IF(A62="","",IF(AC62&lt;&gt;"",AC62,IF(E62="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE62" s="8">
+        <f>IF(OR(AD62="",F62="",G62=""),"",AD62+F62*G62)</f>
+        <v/>
+      </c>
+      <c r="AF62" s="8">
+        <f>IF(OR(E62="",A62=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG62" s="8">
+        <f>IF(OR(AD62="",AF62=""),"",AD62-AF62)</f>
+        <v/>
+      </c>
+      <c r="AH62" s="4">
+        <f>IF(A62="","",IF(E62="","TERMINAL",IF(AG62="","INFO",IF(ABS(AG62)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -11945,10 +13355,31 @@
         <v/>
       </c>
       <c r="AA63" s="4">
-        <f>IF(A63="","",IF(OR(U63&gt;1,AND(X63&lt;&gt;"",X63&lt;Inputs!$B$16),AND(X63&lt;&gt;"",X63&gt;Inputs!$B$17),G63&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A63="","",IF(OR(U63&gt;1,AND(X63&lt;&gt;"",X63&lt;Inputs!$B$16),AND(X63&lt;&gt;"",X63&gt;Inputs!$B$17),G63&lt;Inputs!$B$18,AH63="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB63" s="4" t="n"/>
+      <c r="AC63" s="7" t="n"/>
+      <c r="AD63" s="8">
+        <f>IF(A63="","",IF(AC63&lt;&gt;"",AC63,IF(E63="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE63" s="8">
+        <f>IF(OR(AD63="",F63="",G63=""),"",AD63+F63*G63)</f>
+        <v/>
+      </c>
+      <c r="AF63" s="8">
+        <f>IF(OR(E63="",A63=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG63" s="8">
+        <f>IF(OR(AD63="",AF63=""),"",AD63-AF63)</f>
+        <v/>
+      </c>
+      <c r="AH63" s="4">
+        <f>IF(A63="","",IF(E63="","TERMINAL",IF(AG63="","INFO",IF(ABS(AG63)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -12019,10 +13450,31 @@
         <v/>
       </c>
       <c r="AA64" s="4">
-        <f>IF(A64="","",IF(OR(U64&gt;1,AND(X64&lt;&gt;"",X64&lt;Inputs!$B$16),AND(X64&lt;&gt;"",X64&gt;Inputs!$B$17),G64&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A64="","",IF(OR(U64&gt;1,AND(X64&lt;&gt;"",X64&lt;Inputs!$B$16),AND(X64&lt;&gt;"",X64&gt;Inputs!$B$17),G64&lt;Inputs!$B$18,AH64="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB64" s="4" t="n"/>
+      <c r="AC64" s="7" t="n"/>
+      <c r="AD64" s="8">
+        <f>IF(A64="","",IF(AC64&lt;&gt;"",AC64,IF(E64="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE64" s="8">
+        <f>IF(OR(AD64="",F64="",G64=""),"",AD64+F64*G64)</f>
+        <v/>
+      </c>
+      <c r="AF64" s="8">
+        <f>IF(OR(E64="",A64=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG64" s="8">
+        <f>IF(OR(AD64="",AF64=""),"",AD64-AF64)</f>
+        <v/>
+      </c>
+      <c r="AH64" s="4">
+        <f>IF(A64="","",IF(E64="","TERMINAL",IF(AG64="","INFO",IF(ABS(AG64)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -12093,10 +13545,31 @@
         <v/>
       </c>
       <c r="AA65" s="4">
-        <f>IF(A65="","",IF(OR(U65&gt;1,AND(X65&lt;&gt;"",X65&lt;Inputs!$B$16),AND(X65&lt;&gt;"",X65&gt;Inputs!$B$17),G65&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A65="","",IF(OR(U65&gt;1,AND(X65&lt;&gt;"",X65&lt;Inputs!$B$16),AND(X65&lt;&gt;"",X65&gt;Inputs!$B$17),G65&lt;Inputs!$B$18,AH65="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB65" s="4" t="n"/>
+      <c r="AC65" s="7" t="n"/>
+      <c r="AD65" s="8">
+        <f>IF(A65="","",IF(AC65&lt;&gt;"",AC65,IF(E65="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE65" s="8">
+        <f>IF(OR(AD65="",F65="",G65=""),"",AD65+F65*G65)</f>
+        <v/>
+      </c>
+      <c r="AF65" s="8">
+        <f>IF(OR(E65="",A65=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG65" s="8">
+        <f>IF(OR(AD65="",AF65=""),"",AD65-AF65)</f>
+        <v/>
+      </c>
+      <c r="AH65" s="4">
+        <f>IF(A65="","",IF(E65="","TERMINAL",IF(AG65="","INFO",IF(ABS(AG65)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n"/>
@@ -12167,10 +13640,31 @@
         <v/>
       </c>
       <c r="AA66" s="4">
-        <f>IF(A66="","",IF(OR(U66&gt;1,AND(X66&lt;&gt;"",X66&lt;Inputs!$B$16),AND(X66&lt;&gt;"",X66&gt;Inputs!$B$17),G66&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A66="","",IF(OR(U66&gt;1,AND(X66&lt;&gt;"",X66&lt;Inputs!$B$16),AND(X66&lt;&gt;"",X66&gt;Inputs!$B$17),G66&lt;Inputs!$B$18,AH66="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB66" s="4" t="n"/>
+      <c r="AC66" s="7" t="n"/>
+      <c r="AD66" s="8">
+        <f>IF(A66="","",IF(AC66&lt;&gt;"",AC66,IF(E66="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE66" s="8">
+        <f>IF(OR(AD66="",F66="",G66=""),"",AD66+F66*G66)</f>
+        <v/>
+      </c>
+      <c r="AF66" s="8">
+        <f>IF(OR(E66="",A66=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG66" s="8">
+        <f>IF(OR(AD66="",AF66=""),"",AD66-AF66)</f>
+        <v/>
+      </c>
+      <c r="AH66" s="4">
+        <f>IF(A66="","",IF(E66="","TERMINAL",IF(AG66="","INFO",IF(ABS(AG66)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -12241,10 +13735,31 @@
         <v/>
       </c>
       <c r="AA67" s="4">
-        <f>IF(A67="","",IF(OR(U67&gt;1,AND(X67&lt;&gt;"",X67&lt;Inputs!$B$16),AND(X67&lt;&gt;"",X67&gt;Inputs!$B$17),G67&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A67="","",IF(OR(U67&gt;1,AND(X67&lt;&gt;"",X67&lt;Inputs!$B$16),AND(X67&lt;&gt;"",X67&gt;Inputs!$B$17),G67&lt;Inputs!$B$18,AH67="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB67" s="4" t="n"/>
+      <c r="AC67" s="7" t="n"/>
+      <c r="AD67" s="8">
+        <f>IF(A67="","",IF(AC67&lt;&gt;"",AC67,IF(E67="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE67" s="8">
+        <f>IF(OR(AD67="",F67="",G67=""),"",AD67+F67*G67)</f>
+        <v/>
+      </c>
+      <c r="AF67" s="8">
+        <f>IF(OR(E67="",A67=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG67" s="8">
+        <f>IF(OR(AD67="",AF67=""),"",AD67-AF67)</f>
+        <v/>
+      </c>
+      <c r="AH67" s="4">
+        <f>IF(A67="","",IF(E67="","TERMINAL",IF(AG67="","INFO",IF(ABS(AG67)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n"/>
@@ -12315,10 +13830,31 @@
         <v/>
       </c>
       <c r="AA68" s="4">
-        <f>IF(A68="","",IF(OR(U68&gt;1,AND(X68&lt;&gt;"",X68&lt;Inputs!$B$16),AND(X68&lt;&gt;"",X68&gt;Inputs!$B$17),G68&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A68="","",IF(OR(U68&gt;1,AND(X68&lt;&gt;"",X68&lt;Inputs!$B$16),AND(X68&lt;&gt;"",X68&gt;Inputs!$B$17),G68&lt;Inputs!$B$18,AH68="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB68" s="4" t="n"/>
+      <c r="AC68" s="7" t="n"/>
+      <c r="AD68" s="8">
+        <f>IF(A68="","",IF(AC68&lt;&gt;"",AC68,IF(E68="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE68" s="8">
+        <f>IF(OR(AD68="",F68="",G68=""),"",AD68+F68*G68)</f>
+        <v/>
+      </c>
+      <c r="AF68" s="8">
+        <f>IF(OR(E68="",A68=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG68" s="8">
+        <f>IF(OR(AD68="",AF68=""),"",AD68-AF68)</f>
+        <v/>
+      </c>
+      <c r="AH68" s="4">
+        <f>IF(A68="","",IF(E68="","TERMINAL",IF(AG68="","INFO",IF(ABS(AG68)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -12389,10 +13925,31 @@
         <v/>
       </c>
       <c r="AA69" s="4">
-        <f>IF(A69="","",IF(OR(U69&gt;1,AND(X69&lt;&gt;"",X69&lt;Inputs!$B$16),AND(X69&lt;&gt;"",X69&gt;Inputs!$B$17),G69&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A69="","",IF(OR(U69&gt;1,AND(X69&lt;&gt;"",X69&lt;Inputs!$B$16),AND(X69&lt;&gt;"",X69&gt;Inputs!$B$17),G69&lt;Inputs!$B$18,AH69="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB69" s="4" t="n"/>
+      <c r="AC69" s="7" t="n"/>
+      <c r="AD69" s="8">
+        <f>IF(A69="","",IF(AC69&lt;&gt;"",AC69,IF(E69="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE69" s="8">
+        <f>IF(OR(AD69="",F69="",G69=""),"",AD69+F69*G69)</f>
+        <v/>
+      </c>
+      <c r="AF69" s="8">
+        <f>IF(OR(E69="",A69=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG69" s="8">
+        <f>IF(OR(AD69="",AF69=""),"",AD69-AF69)</f>
+        <v/>
+      </c>
+      <c r="AH69" s="4">
+        <f>IF(A69="","",IF(E69="","TERMINAL",IF(AG69="","INFO",IF(ABS(AG69)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n"/>
@@ -12463,10 +14020,31 @@
         <v/>
       </c>
       <c r="AA70" s="4">
-        <f>IF(A70="","",IF(OR(U70&gt;1,AND(X70&lt;&gt;"",X70&lt;Inputs!$B$16),AND(X70&lt;&gt;"",X70&gt;Inputs!$B$17),G70&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A70="","",IF(OR(U70&gt;1,AND(X70&lt;&gt;"",X70&lt;Inputs!$B$16),AND(X70&lt;&gt;"",X70&gt;Inputs!$B$17),G70&lt;Inputs!$B$18,AH70="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB70" s="4" t="n"/>
+      <c r="AC70" s="7" t="n"/>
+      <c r="AD70" s="8">
+        <f>IF(A70="","",IF(AC70&lt;&gt;"",AC70,IF(E70="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE70" s="8">
+        <f>IF(OR(AD70="",F70="",G70=""),"",AD70+F70*G70)</f>
+        <v/>
+      </c>
+      <c r="AF70" s="8">
+        <f>IF(OR(E70="",A70=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG70" s="8">
+        <f>IF(OR(AD70="",AF70=""),"",AD70-AF70)</f>
+        <v/>
+      </c>
+      <c r="AH70" s="4">
+        <f>IF(A70="","",IF(E70="","TERMINAL",IF(AG70="","INFO",IF(ABS(AG70)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -12537,10 +14115,31 @@
         <v/>
       </c>
       <c r="AA71" s="4">
-        <f>IF(A71="","",IF(OR(U71&gt;1,AND(X71&lt;&gt;"",X71&lt;Inputs!$B$16),AND(X71&lt;&gt;"",X71&gt;Inputs!$B$17),G71&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A71="","",IF(OR(U71&gt;1,AND(X71&lt;&gt;"",X71&lt;Inputs!$B$16),AND(X71&lt;&gt;"",X71&gt;Inputs!$B$17),G71&lt;Inputs!$B$18,AH71="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB71" s="4" t="n"/>
+      <c r="AC71" s="7" t="n"/>
+      <c r="AD71" s="8">
+        <f>IF(A71="","",IF(AC71&lt;&gt;"",AC71,IF(E71="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE71" s="8">
+        <f>IF(OR(AD71="",F71="",G71=""),"",AD71+F71*G71)</f>
+        <v/>
+      </c>
+      <c r="AF71" s="8">
+        <f>IF(OR(E71="",A71=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG71" s="8">
+        <f>IF(OR(AD71="",AF71=""),"",AD71-AF71)</f>
+        <v/>
+      </c>
+      <c r="AH71" s="4">
+        <f>IF(A71="","",IF(E71="","TERMINAL",IF(AG71="","INFO",IF(ABS(AG71)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n"/>
@@ -12611,10 +14210,31 @@
         <v/>
       </c>
       <c r="AA72" s="4">
-        <f>IF(A72="","",IF(OR(U72&gt;1,AND(X72&lt;&gt;"",X72&lt;Inputs!$B$16),AND(X72&lt;&gt;"",X72&gt;Inputs!$B$17),G72&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A72="","",IF(OR(U72&gt;1,AND(X72&lt;&gt;"",X72&lt;Inputs!$B$16),AND(X72&lt;&gt;"",X72&gt;Inputs!$B$17),G72&lt;Inputs!$B$18,AH72="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB72" s="4" t="n"/>
+      <c r="AC72" s="7" t="n"/>
+      <c r="AD72" s="8">
+        <f>IF(A72="","",IF(AC72&lt;&gt;"",AC72,IF(E72="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE72" s="8">
+        <f>IF(OR(AD72="",F72="",G72=""),"",AD72+F72*G72)</f>
+        <v/>
+      </c>
+      <c r="AF72" s="8">
+        <f>IF(OR(E72="",A72=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG72" s="8">
+        <f>IF(OR(AD72="",AF72=""),"",AD72-AF72)</f>
+        <v/>
+      </c>
+      <c r="AH72" s="4">
+        <f>IF(A72="","",IF(E72="","TERMINAL",IF(AG72="","INFO",IF(ABS(AG72)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -12685,10 +14305,31 @@
         <v/>
       </c>
       <c r="AA73" s="4">
-        <f>IF(A73="","",IF(OR(U73&gt;1,AND(X73&lt;&gt;"",X73&lt;Inputs!$B$16),AND(X73&lt;&gt;"",X73&gt;Inputs!$B$17),G73&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A73="","",IF(OR(U73&gt;1,AND(X73&lt;&gt;"",X73&lt;Inputs!$B$16),AND(X73&lt;&gt;"",X73&gt;Inputs!$B$17),G73&lt;Inputs!$B$18,AH73="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB73" s="4" t="n"/>
+      <c r="AC73" s="7" t="n"/>
+      <c r="AD73" s="8">
+        <f>IF(A73="","",IF(AC73&lt;&gt;"",AC73,IF(E73="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE73" s="8">
+        <f>IF(OR(AD73="",F73="",G73=""),"",AD73+F73*G73)</f>
+        <v/>
+      </c>
+      <c r="AF73" s="8">
+        <f>IF(OR(E73="",A73=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG73" s="8">
+        <f>IF(OR(AD73="",AF73=""),"",AD73-AF73)</f>
+        <v/>
+      </c>
+      <c r="AH73" s="4">
+        <f>IF(A73="","",IF(E73="","TERMINAL",IF(AG73="","INFO",IF(ABS(AG73)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
@@ -12759,10 +14400,31 @@
         <v/>
       </c>
       <c r="AA74" s="4">
-        <f>IF(A74="","",IF(OR(U74&gt;1,AND(X74&lt;&gt;"",X74&lt;Inputs!$B$16),AND(X74&lt;&gt;"",X74&gt;Inputs!$B$17),G74&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A74="","",IF(OR(U74&gt;1,AND(X74&lt;&gt;"",X74&lt;Inputs!$B$16),AND(X74&lt;&gt;"",X74&gt;Inputs!$B$17),G74&lt;Inputs!$B$18,AH74="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB74" s="4" t="n"/>
+      <c r="AC74" s="7" t="n"/>
+      <c r="AD74" s="8">
+        <f>IF(A74="","",IF(AC74&lt;&gt;"",AC74,IF(E74="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE74" s="8">
+        <f>IF(OR(AD74="",F74="",G74=""),"",AD74+F74*G74)</f>
+        <v/>
+      </c>
+      <c r="AF74" s="8">
+        <f>IF(OR(E74="",A74=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG74" s="8">
+        <f>IF(OR(AD74="",AF74=""),"",AD74-AF74)</f>
+        <v/>
+      </c>
+      <c r="AH74" s="4">
+        <f>IF(A74="","",IF(E74="","TERMINAL",IF(AG74="","INFO",IF(ABS(AG74)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -12833,10 +14495,31 @@
         <v/>
       </c>
       <c r="AA75" s="4">
-        <f>IF(A75="","",IF(OR(U75&gt;1,AND(X75&lt;&gt;"",X75&lt;Inputs!$B$16),AND(X75&lt;&gt;"",X75&gt;Inputs!$B$17),G75&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A75="","",IF(OR(U75&gt;1,AND(X75&lt;&gt;"",X75&lt;Inputs!$B$16),AND(X75&lt;&gt;"",X75&gt;Inputs!$B$17),G75&lt;Inputs!$B$18,AH75="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB75" s="4" t="n"/>
+      <c r="AC75" s="7" t="n"/>
+      <c r="AD75" s="8">
+        <f>IF(A75="","",IF(AC75&lt;&gt;"",AC75,IF(E75="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE75" s="8">
+        <f>IF(OR(AD75="",F75="",G75=""),"",AD75+F75*G75)</f>
+        <v/>
+      </c>
+      <c r="AF75" s="8">
+        <f>IF(OR(E75="",A75=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG75" s="8">
+        <f>IF(OR(AD75="",AF75=""),"",AD75-AF75)</f>
+        <v/>
+      </c>
+      <c r="AH75" s="4">
+        <f>IF(A75="","",IF(E75="","TERMINAL",IF(AG75="","INFO",IF(ABS(AG75)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
@@ -12907,10 +14590,31 @@
         <v/>
       </c>
       <c r="AA76" s="4">
-        <f>IF(A76="","",IF(OR(U76&gt;1,AND(X76&lt;&gt;"",X76&lt;Inputs!$B$16),AND(X76&lt;&gt;"",X76&gt;Inputs!$B$17),G76&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A76="","",IF(OR(U76&gt;1,AND(X76&lt;&gt;"",X76&lt;Inputs!$B$16),AND(X76&lt;&gt;"",X76&gt;Inputs!$B$17),G76&lt;Inputs!$B$18,AH76="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB76" s="4" t="n"/>
+      <c r="AC76" s="7" t="n"/>
+      <c r="AD76" s="8">
+        <f>IF(A76="","",IF(AC76&lt;&gt;"",AC76,IF(E76="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE76" s="8">
+        <f>IF(OR(AD76="",F76="",G76=""),"",AD76+F76*G76)</f>
+        <v/>
+      </c>
+      <c r="AF76" s="8">
+        <f>IF(OR(E76="",A76=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG76" s="8">
+        <f>IF(OR(AD76="",AF76=""),"",AD76-AF76)</f>
+        <v/>
+      </c>
+      <c r="AH76" s="4">
+        <f>IF(A76="","",IF(E76="","TERMINAL",IF(AG76="","INFO",IF(ABS(AG76)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -12981,10 +14685,31 @@
         <v/>
       </c>
       <c r="AA77" s="4">
-        <f>IF(A77="","",IF(OR(U77&gt;1,AND(X77&lt;&gt;"",X77&lt;Inputs!$B$16),AND(X77&lt;&gt;"",X77&gt;Inputs!$B$17),G77&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A77="","",IF(OR(U77&gt;1,AND(X77&lt;&gt;"",X77&lt;Inputs!$B$16),AND(X77&lt;&gt;"",X77&gt;Inputs!$B$17),G77&lt;Inputs!$B$18,AH77="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB77" s="4" t="n"/>
+      <c r="AC77" s="7" t="n"/>
+      <c r="AD77" s="8">
+        <f>IF(A77="","",IF(AC77&lt;&gt;"",AC77,IF(E77="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE77" s="8">
+        <f>IF(OR(AD77="",F77="",G77=""),"",AD77+F77*G77)</f>
+        <v/>
+      </c>
+      <c r="AF77" s="8">
+        <f>IF(OR(E77="",A77=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG77" s="8">
+        <f>IF(OR(AD77="",AF77=""),"",AD77-AF77)</f>
+        <v/>
+      </c>
+      <c r="AH77" s="4">
+        <f>IF(A77="","",IF(E77="","TERMINAL",IF(AG77="","INFO",IF(ABS(AG77)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n"/>
@@ -13055,10 +14780,31 @@
         <v/>
       </c>
       <c r="AA78" s="4">
-        <f>IF(A78="","",IF(OR(U78&gt;1,AND(X78&lt;&gt;"",X78&lt;Inputs!$B$16),AND(X78&lt;&gt;"",X78&gt;Inputs!$B$17),G78&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A78="","",IF(OR(U78&gt;1,AND(X78&lt;&gt;"",X78&lt;Inputs!$B$16),AND(X78&lt;&gt;"",X78&gt;Inputs!$B$17),G78&lt;Inputs!$B$18,AH78="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB78" s="4" t="n"/>
+      <c r="AC78" s="7" t="n"/>
+      <c r="AD78" s="8">
+        <f>IF(A78="","",IF(AC78&lt;&gt;"",AC78,IF(E78="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE78" s="8">
+        <f>IF(OR(AD78="",F78="",G78=""),"",AD78+F78*G78)</f>
+        <v/>
+      </c>
+      <c r="AF78" s="8">
+        <f>IF(OR(E78="",A78=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG78" s="8">
+        <f>IF(OR(AD78="",AF78=""),"",AD78-AF78)</f>
+        <v/>
+      </c>
+      <c r="AH78" s="4">
+        <f>IF(A78="","",IF(E78="","TERMINAL",IF(AG78="","INFO",IF(ABS(AG78)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -13129,10 +14875,31 @@
         <v/>
       </c>
       <c r="AA79" s="4">
-        <f>IF(A79="","",IF(OR(U79&gt;1,AND(X79&lt;&gt;"",X79&lt;Inputs!$B$16),AND(X79&lt;&gt;"",X79&gt;Inputs!$B$17),G79&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A79="","",IF(OR(U79&gt;1,AND(X79&lt;&gt;"",X79&lt;Inputs!$B$16),AND(X79&lt;&gt;"",X79&gt;Inputs!$B$17),G79&lt;Inputs!$B$18,AH79="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB79" s="4" t="n"/>
+      <c r="AC79" s="7" t="n"/>
+      <c r="AD79" s="8">
+        <f>IF(A79="","",IF(AC79&lt;&gt;"",AC79,IF(E79="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE79" s="8">
+        <f>IF(OR(AD79="",F79="",G79=""),"",AD79+F79*G79)</f>
+        <v/>
+      </c>
+      <c r="AF79" s="8">
+        <f>IF(OR(E79="",A79=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG79" s="8">
+        <f>IF(OR(AD79="",AF79=""),"",AD79-AF79)</f>
+        <v/>
+      </c>
+      <c r="AH79" s="4">
+        <f>IF(A79="","",IF(E79="","TERMINAL",IF(AG79="","INFO",IF(ABS(AG79)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n"/>
@@ -13203,10 +14970,31 @@
         <v/>
       </c>
       <c r="AA80" s="4">
-        <f>IF(A80="","",IF(OR(U80&gt;1,AND(X80&lt;&gt;"",X80&lt;Inputs!$B$16),AND(X80&lt;&gt;"",X80&gt;Inputs!$B$17),G80&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A80="","",IF(OR(U80&gt;1,AND(X80&lt;&gt;"",X80&lt;Inputs!$B$16),AND(X80&lt;&gt;"",X80&gt;Inputs!$B$17),G80&lt;Inputs!$B$18,AH80="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB80" s="4" t="n"/>
+      <c r="AC80" s="7" t="n"/>
+      <c r="AD80" s="8">
+        <f>IF(A80="","",IF(AC80&lt;&gt;"",AC80,IF(E80="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE80" s="8">
+        <f>IF(OR(AD80="",F80="",G80=""),"",AD80+F80*G80)</f>
+        <v/>
+      </c>
+      <c r="AF80" s="8">
+        <f>IF(OR(E80="",A80=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG80" s="8">
+        <f>IF(OR(AD80="",AF80=""),"",AD80-AF80)</f>
+        <v/>
+      </c>
+      <c r="AH80" s="4">
+        <f>IF(A80="","",IF(E80="","TERMINAL",IF(AG80="","INFO",IF(ABS(AG80)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -13277,10 +15065,31 @@
         <v/>
       </c>
       <c r="AA81" s="4">
-        <f>IF(A81="","",IF(OR(U81&gt;1,AND(X81&lt;&gt;"",X81&lt;Inputs!$B$16),AND(X81&lt;&gt;"",X81&gt;Inputs!$B$17),G81&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A81="","",IF(OR(U81&gt;1,AND(X81&lt;&gt;"",X81&lt;Inputs!$B$16),AND(X81&lt;&gt;"",X81&gt;Inputs!$B$17),G81&lt;Inputs!$B$18,AH81="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB81" s="4" t="n"/>
+      <c r="AC81" s="7" t="n"/>
+      <c r="AD81" s="8">
+        <f>IF(A81="","",IF(AC81&lt;&gt;"",AC81,IF(E81="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE81" s="8">
+        <f>IF(OR(AD81="",F81="",G81=""),"",AD81+F81*G81)</f>
+        <v/>
+      </c>
+      <c r="AF81" s="8">
+        <f>IF(OR(E81="",A81=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG81" s="8">
+        <f>IF(OR(AD81="",AF81=""),"",AD81-AF81)</f>
+        <v/>
+      </c>
+      <c r="AH81" s="4">
+        <f>IF(A81="","",IF(E81="","TERMINAL",IF(AG81="","INFO",IF(ABS(AG81)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
@@ -13351,10 +15160,31 @@
         <v/>
       </c>
       <c r="AA82" s="4">
-        <f>IF(A82="","",IF(OR(U82&gt;1,AND(X82&lt;&gt;"",X82&lt;Inputs!$B$16),AND(X82&lt;&gt;"",X82&gt;Inputs!$B$17),G82&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A82="","",IF(OR(U82&gt;1,AND(X82&lt;&gt;"",X82&lt;Inputs!$B$16),AND(X82&lt;&gt;"",X82&gt;Inputs!$B$17),G82&lt;Inputs!$B$18,AH82="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB82" s="4" t="n"/>
+      <c r="AC82" s="7" t="n"/>
+      <c r="AD82" s="8">
+        <f>IF(A82="","",IF(AC82&lt;&gt;"",AC82,IF(E82="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE82" s="8">
+        <f>IF(OR(AD82="",F82="",G82=""),"",AD82+F82*G82)</f>
+        <v/>
+      </c>
+      <c r="AF82" s="8">
+        <f>IF(OR(E82="",A82=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG82" s="8">
+        <f>IF(OR(AD82="",AF82=""),"",AD82-AF82)</f>
+        <v/>
+      </c>
+      <c r="AH82" s="4">
+        <f>IF(A82="","",IF(E82="","TERMINAL",IF(AG82="","INFO",IF(ABS(AG82)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -13425,10 +15255,31 @@
         <v/>
       </c>
       <c r="AA83" s="4">
-        <f>IF(A83="","",IF(OR(U83&gt;1,AND(X83&lt;&gt;"",X83&lt;Inputs!$B$16),AND(X83&lt;&gt;"",X83&gt;Inputs!$B$17),G83&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A83="","",IF(OR(U83&gt;1,AND(X83&lt;&gt;"",X83&lt;Inputs!$B$16),AND(X83&lt;&gt;"",X83&gt;Inputs!$B$17),G83&lt;Inputs!$B$18,AH83="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB83" s="4" t="n"/>
+      <c r="AC83" s="7" t="n"/>
+      <c r="AD83" s="8">
+        <f>IF(A83="","",IF(AC83&lt;&gt;"",AC83,IF(E83="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE83" s="8">
+        <f>IF(OR(AD83="",F83="",G83=""),"",AD83+F83*G83)</f>
+        <v/>
+      </c>
+      <c r="AF83" s="8">
+        <f>IF(OR(E83="",A83=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG83" s="8">
+        <f>IF(OR(AD83="",AF83=""),"",AD83-AF83)</f>
+        <v/>
+      </c>
+      <c r="AH83" s="4">
+        <f>IF(A83="","",IF(E83="","TERMINAL",IF(AG83="","INFO",IF(ABS(AG83)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
@@ -13499,10 +15350,31 @@
         <v/>
       </c>
       <c r="AA84" s="4">
-        <f>IF(A84="","",IF(OR(U84&gt;1,AND(X84&lt;&gt;"",X84&lt;Inputs!$B$16),AND(X84&lt;&gt;"",X84&gt;Inputs!$B$17),G84&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A84="","",IF(OR(U84&gt;1,AND(X84&lt;&gt;"",X84&lt;Inputs!$B$16),AND(X84&lt;&gt;"",X84&gt;Inputs!$B$17),G84&lt;Inputs!$B$18,AH84="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB84" s="4" t="n"/>
+      <c r="AC84" s="7" t="n"/>
+      <c r="AD84" s="8">
+        <f>IF(A84="","",IF(AC84&lt;&gt;"",AC84,IF(E84="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE84" s="8">
+        <f>IF(OR(AD84="",F84="",G84=""),"",AD84+F84*G84)</f>
+        <v/>
+      </c>
+      <c r="AF84" s="8">
+        <f>IF(OR(E84="",A84=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG84" s="8">
+        <f>IF(OR(AD84="",AF84=""),"",AD84-AF84)</f>
+        <v/>
+      </c>
+      <c r="AH84" s="4">
+        <f>IF(A84="","",IF(E84="","TERMINAL",IF(AG84="","INFO",IF(ABS(AG84)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -13573,10 +15445,31 @@
         <v/>
       </c>
       <c r="AA85" s="4">
-        <f>IF(A85="","",IF(OR(U85&gt;1,AND(X85&lt;&gt;"",X85&lt;Inputs!$B$16),AND(X85&lt;&gt;"",X85&gt;Inputs!$B$17),G85&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A85="","",IF(OR(U85&gt;1,AND(X85&lt;&gt;"",X85&lt;Inputs!$B$16),AND(X85&lt;&gt;"",X85&gt;Inputs!$B$17),G85&lt;Inputs!$B$18,AH85="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB85" s="4" t="n"/>
+      <c r="AC85" s="7" t="n"/>
+      <c r="AD85" s="8">
+        <f>IF(A85="","",IF(AC85&lt;&gt;"",AC85,IF(E85="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE85" s="8">
+        <f>IF(OR(AD85="",F85="",G85=""),"",AD85+F85*G85)</f>
+        <v/>
+      </c>
+      <c r="AF85" s="8">
+        <f>IF(OR(E85="",A85=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG85" s="8">
+        <f>IF(OR(AD85="",AF85=""),"",AD85-AF85)</f>
+        <v/>
+      </c>
+      <c r="AH85" s="4">
+        <f>IF(A85="","",IF(E85="","TERMINAL",IF(AG85="","INFO",IF(ABS(AG85)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -13647,10 +15540,31 @@
         <v/>
       </c>
       <c r="AA86" s="4">
-        <f>IF(A86="","",IF(OR(U86&gt;1,AND(X86&lt;&gt;"",X86&lt;Inputs!$B$16),AND(X86&lt;&gt;"",X86&gt;Inputs!$B$17),G86&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A86="","",IF(OR(U86&gt;1,AND(X86&lt;&gt;"",X86&lt;Inputs!$B$16),AND(X86&lt;&gt;"",X86&gt;Inputs!$B$17),G86&lt;Inputs!$B$18,AH86="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB86" s="4" t="n"/>
+      <c r="AC86" s="7" t="n"/>
+      <c r="AD86" s="8">
+        <f>IF(A86="","",IF(AC86&lt;&gt;"",AC86,IF(E86="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE86" s="8">
+        <f>IF(OR(AD86="",F86="",G86=""),"",AD86+F86*G86)</f>
+        <v/>
+      </c>
+      <c r="AF86" s="8">
+        <f>IF(OR(E86="",A86=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG86" s="8">
+        <f>IF(OR(AD86="",AF86=""),"",AD86-AF86)</f>
+        <v/>
+      </c>
+      <c r="AH86" s="4">
+        <f>IF(A86="","",IF(E86="","TERMINAL",IF(AG86="","INFO",IF(ABS(AG86)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -13721,10 +15635,31 @@
         <v/>
       </c>
       <c r="AA87" s="4">
-        <f>IF(A87="","",IF(OR(U87&gt;1,AND(X87&lt;&gt;"",X87&lt;Inputs!$B$16),AND(X87&lt;&gt;"",X87&gt;Inputs!$B$17),G87&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A87="","",IF(OR(U87&gt;1,AND(X87&lt;&gt;"",X87&lt;Inputs!$B$16),AND(X87&lt;&gt;"",X87&gt;Inputs!$B$17),G87&lt;Inputs!$B$18,AH87="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB87" s="4" t="n"/>
+      <c r="AC87" s="7" t="n"/>
+      <c r="AD87" s="8">
+        <f>IF(A87="","",IF(AC87&lt;&gt;"",AC87,IF(E87="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE87" s="8">
+        <f>IF(OR(AD87="",F87="",G87=""),"",AD87+F87*G87)</f>
+        <v/>
+      </c>
+      <c r="AF87" s="8">
+        <f>IF(OR(E87="",A87=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG87" s="8">
+        <f>IF(OR(AD87="",AF87=""),"",AD87-AF87)</f>
+        <v/>
+      </c>
+      <c r="AH87" s="4">
+        <f>IF(A87="","",IF(E87="","TERMINAL",IF(AG87="","INFO",IF(ABS(AG87)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
@@ -13795,10 +15730,31 @@
         <v/>
       </c>
       <c r="AA88" s="4">
-        <f>IF(A88="","",IF(OR(U88&gt;1,AND(X88&lt;&gt;"",X88&lt;Inputs!$B$16),AND(X88&lt;&gt;"",X88&gt;Inputs!$B$17),G88&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A88="","",IF(OR(U88&gt;1,AND(X88&lt;&gt;"",X88&lt;Inputs!$B$16),AND(X88&lt;&gt;"",X88&gt;Inputs!$B$17),G88&lt;Inputs!$B$18,AH88="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB88" s="4" t="n"/>
+      <c r="AC88" s="7" t="n"/>
+      <c r="AD88" s="8">
+        <f>IF(A88="","",IF(AC88&lt;&gt;"",AC88,IF(E88="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE88" s="8">
+        <f>IF(OR(AD88="",F88="",G88=""),"",AD88+F88*G88)</f>
+        <v/>
+      </c>
+      <c r="AF88" s="8">
+        <f>IF(OR(E88="",A88=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG88" s="8">
+        <f>IF(OR(AD88="",AF88=""),"",AD88-AF88)</f>
+        <v/>
+      </c>
+      <c r="AH88" s="4">
+        <f>IF(A88="","",IF(E88="","TERMINAL",IF(AG88="","INFO",IF(ABS(AG88)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -13869,10 +15825,31 @@
         <v/>
       </c>
       <c r="AA89" s="4">
-        <f>IF(A89="","",IF(OR(U89&gt;1,AND(X89&lt;&gt;"",X89&lt;Inputs!$B$16),AND(X89&lt;&gt;"",X89&gt;Inputs!$B$17),G89&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A89="","",IF(OR(U89&gt;1,AND(X89&lt;&gt;"",X89&lt;Inputs!$B$16),AND(X89&lt;&gt;"",X89&gt;Inputs!$B$17),G89&lt;Inputs!$B$18,AH89="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB89" s="4" t="n"/>
+      <c r="AC89" s="7" t="n"/>
+      <c r="AD89" s="8">
+        <f>IF(A89="","",IF(AC89&lt;&gt;"",AC89,IF(E89="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE89" s="8">
+        <f>IF(OR(AD89="",F89="",G89=""),"",AD89+F89*G89)</f>
+        <v/>
+      </c>
+      <c r="AF89" s="8">
+        <f>IF(OR(E89="",A89=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG89" s="8">
+        <f>IF(OR(AD89="",AF89=""),"",AD89-AF89)</f>
+        <v/>
+      </c>
+      <c r="AH89" s="4">
+        <f>IF(A89="","",IF(E89="","TERMINAL",IF(AG89="","INFO",IF(ABS(AG89)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
@@ -13943,10 +15920,31 @@
         <v/>
       </c>
       <c r="AA90" s="4">
-        <f>IF(A90="","",IF(OR(U90&gt;1,AND(X90&lt;&gt;"",X90&lt;Inputs!$B$16),AND(X90&lt;&gt;"",X90&gt;Inputs!$B$17),G90&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A90="","",IF(OR(U90&gt;1,AND(X90&lt;&gt;"",X90&lt;Inputs!$B$16),AND(X90&lt;&gt;"",X90&gt;Inputs!$B$17),G90&lt;Inputs!$B$18,AH90="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB90" s="4" t="n"/>
+      <c r="AC90" s="7" t="n"/>
+      <c r="AD90" s="8">
+        <f>IF(A90="","",IF(AC90&lt;&gt;"",AC90,IF(E90="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE90" s="8">
+        <f>IF(OR(AD90="",F90="",G90=""),"",AD90+F90*G90)</f>
+        <v/>
+      </c>
+      <c r="AF90" s="8">
+        <f>IF(OR(E90="",A90=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG90" s="8">
+        <f>IF(OR(AD90="",AF90=""),"",AD90-AF90)</f>
+        <v/>
+      </c>
+      <c r="AH90" s="4">
+        <f>IF(A90="","",IF(E90="","TERMINAL",IF(AG90="","INFO",IF(ABS(AG90)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -14017,10 +16015,31 @@
         <v/>
       </c>
       <c r="AA91" s="4">
-        <f>IF(A91="","",IF(OR(U91&gt;1,AND(X91&lt;&gt;"",X91&lt;Inputs!$B$16),AND(X91&lt;&gt;"",X91&gt;Inputs!$B$17),G91&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A91="","",IF(OR(U91&gt;1,AND(X91&lt;&gt;"",X91&lt;Inputs!$B$16),AND(X91&lt;&gt;"",X91&gt;Inputs!$B$17),G91&lt;Inputs!$B$18,AH91="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB91" s="4" t="n"/>
+      <c r="AC91" s="7" t="n"/>
+      <c r="AD91" s="8">
+        <f>IF(A91="","",IF(AC91&lt;&gt;"",AC91,IF(E91="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE91" s="8">
+        <f>IF(OR(AD91="",F91="",G91=""),"",AD91+F91*G91)</f>
+        <v/>
+      </c>
+      <c r="AF91" s="8">
+        <f>IF(OR(E91="",A91=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG91" s="8">
+        <f>IF(OR(AD91="",AF91=""),"",AD91-AF91)</f>
+        <v/>
+      </c>
+      <c r="AH91" s="4">
+        <f>IF(A91="","",IF(E91="","TERMINAL",IF(AG91="","INFO",IF(ABS(AG91)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -14091,10 +16110,31 @@
         <v/>
       </c>
       <c r="AA92" s="4">
-        <f>IF(A92="","",IF(OR(U92&gt;1,AND(X92&lt;&gt;"",X92&lt;Inputs!$B$16),AND(X92&lt;&gt;"",X92&gt;Inputs!$B$17),G92&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A92="","",IF(OR(U92&gt;1,AND(X92&lt;&gt;"",X92&lt;Inputs!$B$16),AND(X92&lt;&gt;"",X92&gt;Inputs!$B$17),G92&lt;Inputs!$B$18,AH92="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB92" s="4" t="n"/>
+      <c r="AC92" s="7" t="n"/>
+      <c r="AD92" s="8">
+        <f>IF(A92="","",IF(AC92&lt;&gt;"",AC92,IF(E92="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE92" s="8">
+        <f>IF(OR(AD92="",F92="",G92=""),"",AD92+F92*G92)</f>
+        <v/>
+      </c>
+      <c r="AF92" s="8">
+        <f>IF(OR(E92="",A92=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG92" s="8">
+        <f>IF(OR(AD92="",AF92=""),"",AD92-AF92)</f>
+        <v/>
+      </c>
+      <c r="AH92" s="4">
+        <f>IF(A92="","",IF(E92="","TERMINAL",IF(AG92="","INFO",IF(ABS(AG92)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -14165,10 +16205,31 @@
         <v/>
       </c>
       <c r="AA93" s="4">
-        <f>IF(A93="","",IF(OR(U93&gt;1,AND(X93&lt;&gt;"",X93&lt;Inputs!$B$16),AND(X93&lt;&gt;"",X93&gt;Inputs!$B$17),G93&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A93="","",IF(OR(U93&gt;1,AND(X93&lt;&gt;"",X93&lt;Inputs!$B$16),AND(X93&lt;&gt;"",X93&gt;Inputs!$B$17),G93&lt;Inputs!$B$18,AH93="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB93" s="4" t="n"/>
+      <c r="AC93" s="7" t="n"/>
+      <c r="AD93" s="8">
+        <f>IF(A93="","",IF(AC93&lt;&gt;"",AC93,IF(E93="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE93" s="8">
+        <f>IF(OR(AD93="",F93="",G93=""),"",AD93+F93*G93)</f>
+        <v/>
+      </c>
+      <c r="AF93" s="8">
+        <f>IF(OR(E93="",A93=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG93" s="8">
+        <f>IF(OR(AD93="",AF93=""),"",AD93-AF93)</f>
+        <v/>
+      </c>
+      <c r="AH93" s="4">
+        <f>IF(A93="","",IF(E93="","TERMINAL",IF(AG93="","INFO",IF(ABS(AG93)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
@@ -14239,10 +16300,31 @@
         <v/>
       </c>
       <c r="AA94" s="4">
-        <f>IF(A94="","",IF(OR(U94&gt;1,AND(X94&lt;&gt;"",X94&lt;Inputs!$B$16),AND(X94&lt;&gt;"",X94&gt;Inputs!$B$17),G94&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A94="","",IF(OR(U94&gt;1,AND(X94&lt;&gt;"",X94&lt;Inputs!$B$16),AND(X94&lt;&gt;"",X94&gt;Inputs!$B$17),G94&lt;Inputs!$B$18,AH94="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB94" s="4" t="n"/>
+      <c r="AC94" s="7" t="n"/>
+      <c r="AD94" s="8">
+        <f>IF(A94="","",IF(AC94&lt;&gt;"",AC94,IF(E94="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE94" s="8">
+        <f>IF(OR(AD94="",F94="",G94=""),"",AD94+F94*G94)</f>
+        <v/>
+      </c>
+      <c r="AF94" s="8">
+        <f>IF(OR(E94="",A94=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG94" s="8">
+        <f>IF(OR(AD94="",AF94=""),"",AD94-AF94)</f>
+        <v/>
+      </c>
+      <c r="AH94" s="4">
+        <f>IF(A94="","",IF(E94="","TERMINAL",IF(AG94="","INFO",IF(ABS(AG94)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -14313,10 +16395,31 @@
         <v/>
       </c>
       <c r="AA95" s="4">
-        <f>IF(A95="","",IF(OR(U95&gt;1,AND(X95&lt;&gt;"",X95&lt;Inputs!$B$16),AND(X95&lt;&gt;"",X95&gt;Inputs!$B$17),G95&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A95="","",IF(OR(U95&gt;1,AND(X95&lt;&gt;"",X95&lt;Inputs!$B$16),AND(X95&lt;&gt;"",X95&gt;Inputs!$B$17),G95&lt;Inputs!$B$18,AH95="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB95" s="4" t="n"/>
+      <c r="AC95" s="7" t="n"/>
+      <c r="AD95" s="8">
+        <f>IF(A95="","",IF(AC95&lt;&gt;"",AC95,IF(E95="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE95" s="8">
+        <f>IF(OR(AD95="",F95="",G95=""),"",AD95+F95*G95)</f>
+        <v/>
+      </c>
+      <c r="AF95" s="8">
+        <f>IF(OR(E95="",A95=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG95" s="8">
+        <f>IF(OR(AD95="",AF95=""),"",AD95-AF95)</f>
+        <v/>
+      </c>
+      <c r="AH95" s="4">
+        <f>IF(A95="","",IF(E95="","TERMINAL",IF(AG95="","INFO",IF(ABS(AG95)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
@@ -14387,10 +16490,31 @@
         <v/>
       </c>
       <c r="AA96" s="4">
-        <f>IF(A96="","",IF(OR(U96&gt;1,AND(X96&lt;&gt;"",X96&lt;Inputs!$B$16),AND(X96&lt;&gt;"",X96&gt;Inputs!$B$17),G96&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A96="","",IF(OR(U96&gt;1,AND(X96&lt;&gt;"",X96&lt;Inputs!$B$16),AND(X96&lt;&gt;"",X96&gt;Inputs!$B$17),G96&lt;Inputs!$B$18,AH96="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB96" s="4" t="n"/>
+      <c r="AC96" s="7" t="n"/>
+      <c r="AD96" s="8">
+        <f>IF(A96="","",IF(AC96&lt;&gt;"",AC96,IF(E96="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE96" s="8">
+        <f>IF(OR(AD96="",F96="",G96=""),"",AD96+F96*G96)</f>
+        <v/>
+      </c>
+      <c r="AF96" s="8">
+        <f>IF(OR(E96="",A96=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG96" s="8">
+        <f>IF(OR(AD96="",AF96=""),"",AD96-AF96)</f>
+        <v/>
+      </c>
+      <c r="AH96" s="4">
+        <f>IF(A96="","",IF(E96="","TERMINAL",IF(AG96="","INFO",IF(ABS(AG96)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -14461,10 +16585,31 @@
         <v/>
       </c>
       <c r="AA97" s="4">
-        <f>IF(A97="","",IF(OR(U97&gt;1,AND(X97&lt;&gt;"",X97&lt;Inputs!$B$16),AND(X97&lt;&gt;"",X97&gt;Inputs!$B$17),G97&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A97="","",IF(OR(U97&gt;1,AND(X97&lt;&gt;"",X97&lt;Inputs!$B$16),AND(X97&lt;&gt;"",X97&gt;Inputs!$B$17),G97&lt;Inputs!$B$18,AH97="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB97" s="4" t="n"/>
+      <c r="AC97" s="7" t="n"/>
+      <c r="AD97" s="8">
+        <f>IF(A97="","",IF(AC97&lt;&gt;"",AC97,IF(E97="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE97" s="8">
+        <f>IF(OR(AD97="",F97="",G97=""),"",AD97+F97*G97)</f>
+        <v/>
+      </c>
+      <c r="AF97" s="8">
+        <f>IF(OR(E97="",A97=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG97" s="8">
+        <f>IF(OR(AD97="",AF97=""),"",AD97-AF97)</f>
+        <v/>
+      </c>
+      <c r="AH97" s="4">
+        <f>IF(A97="","",IF(E97="","TERMINAL",IF(AG97="","INFO",IF(ABS(AG97)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -14535,10 +16680,31 @@
         <v/>
       </c>
       <c r="AA98" s="4">
-        <f>IF(A98="","",IF(OR(U98&gt;1,AND(X98&lt;&gt;"",X98&lt;Inputs!$B$16),AND(X98&lt;&gt;"",X98&gt;Inputs!$B$17),G98&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A98="","",IF(OR(U98&gt;1,AND(X98&lt;&gt;"",X98&lt;Inputs!$B$16),AND(X98&lt;&gt;"",X98&gt;Inputs!$B$17),G98&lt;Inputs!$B$18,AH98="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB98" s="4" t="n"/>
+      <c r="AC98" s="7" t="n"/>
+      <c r="AD98" s="8">
+        <f>IF(A98="","",IF(AC98&lt;&gt;"",AC98,IF(E98="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE98" s="8">
+        <f>IF(OR(AD98="",F98="",G98=""),"",AD98+F98*G98)</f>
+        <v/>
+      </c>
+      <c r="AF98" s="8">
+        <f>IF(OR(E98="",A98=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG98" s="8">
+        <f>IF(OR(AD98="",AF98=""),"",AD98-AF98)</f>
+        <v/>
+      </c>
+      <c r="AH98" s="4">
+        <f>IF(A98="","",IF(E98="","TERMINAL",IF(AG98="","INFO",IF(ABS(AG98)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -14609,10 +16775,31 @@
         <v/>
       </c>
       <c r="AA99" s="4">
-        <f>IF(A99="","",IF(OR(U99&gt;1,AND(X99&lt;&gt;"",X99&lt;Inputs!$B$16),AND(X99&lt;&gt;"",X99&gt;Inputs!$B$17),G99&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A99="","",IF(OR(U99&gt;1,AND(X99&lt;&gt;"",X99&lt;Inputs!$B$16),AND(X99&lt;&gt;"",X99&gt;Inputs!$B$17),G99&lt;Inputs!$B$18,AH99="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB99" s="4" t="n"/>
+      <c r="AC99" s="7" t="n"/>
+      <c r="AD99" s="8">
+        <f>IF(A99="","",IF(AC99&lt;&gt;"",AC99,IF(E99="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE99" s="8">
+        <f>IF(OR(AD99="",F99="",G99=""),"",AD99+F99*G99)</f>
+        <v/>
+      </c>
+      <c r="AF99" s="8">
+        <f>IF(OR(E99="",A99=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG99" s="8">
+        <f>IF(OR(AD99="",AF99=""),"",AD99-AF99)</f>
+        <v/>
+      </c>
+      <c r="AH99" s="4">
+        <f>IF(A99="","",IF(E99="","TERMINAL",IF(AG99="","INFO",IF(ABS(AG99)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
@@ -14683,10 +16870,31 @@
         <v/>
       </c>
       <c r="AA100" s="4">
-        <f>IF(A100="","",IF(OR(U100&gt;1,AND(X100&lt;&gt;"",X100&lt;Inputs!$B$16),AND(X100&lt;&gt;"",X100&gt;Inputs!$B$17),G100&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A100="","",IF(OR(U100&gt;1,AND(X100&lt;&gt;"",X100&lt;Inputs!$B$16),AND(X100&lt;&gt;"",X100&gt;Inputs!$B$17),G100&lt;Inputs!$B$18,AH100="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB100" s="4" t="n"/>
+      <c r="AC100" s="7" t="n"/>
+      <c r="AD100" s="8">
+        <f>IF(A100="","",IF(AC100&lt;&gt;"",AC100,IF(E100="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE100" s="8">
+        <f>IF(OR(AD100="",F100="",G100=""),"",AD100+F100*G100)</f>
+        <v/>
+      </c>
+      <c r="AF100" s="8">
+        <f>IF(OR(E100="",A100=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG100" s="8">
+        <f>IF(OR(AD100="",AF100=""),"",AD100-AF100)</f>
+        <v/>
+      </c>
+      <c r="AH100" s="4">
+        <f>IF(A100="","",IF(E100="","TERMINAL",IF(AG100="","INFO",IF(ABS(AG100)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -14757,10 +16965,31 @@
         <v/>
       </c>
       <c r="AA101" s="4">
-        <f>IF(A101="","",IF(OR(U101&gt;1,AND(X101&lt;&gt;"",X101&lt;Inputs!$B$16),AND(X101&lt;&gt;"",X101&gt;Inputs!$B$17),G101&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A101="","",IF(OR(U101&gt;1,AND(X101&lt;&gt;"",X101&lt;Inputs!$B$16),AND(X101&lt;&gt;"",X101&gt;Inputs!$B$17),G101&lt;Inputs!$B$18,AH101="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB101" s="4" t="n"/>
+      <c r="AC101" s="7" t="n"/>
+      <c r="AD101" s="8">
+        <f>IF(A101="","",IF(AC101&lt;&gt;"",AC101,IF(E101="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE101" s="8">
+        <f>IF(OR(AD101="",F101="",G101=""),"",AD101+F101*G101)</f>
+        <v/>
+      </c>
+      <c r="AF101" s="8">
+        <f>IF(OR(E101="",A101=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG101" s="8">
+        <f>IF(OR(AD101="",AF101=""),"",AD101-AF101)</f>
+        <v/>
+      </c>
+      <c r="AH101" s="4">
+        <f>IF(A101="","",IF(E101="","TERMINAL",IF(AG101="","INFO",IF(ABS(AG101)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
@@ -14831,10 +17060,31 @@
         <v/>
       </c>
       <c r="AA102" s="4">
-        <f>IF(A102="","",IF(OR(U102&gt;1,AND(X102&lt;&gt;"",X102&lt;Inputs!$B$16),AND(X102&lt;&gt;"",X102&gt;Inputs!$B$17),G102&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A102="","",IF(OR(U102&gt;1,AND(X102&lt;&gt;"",X102&lt;Inputs!$B$16),AND(X102&lt;&gt;"",X102&gt;Inputs!$B$17),G102&lt;Inputs!$B$18,AH102="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB102" s="4" t="n"/>
+      <c r="AC102" s="7" t="n"/>
+      <c r="AD102" s="8">
+        <f>IF(A102="","",IF(AC102&lt;&gt;"",AC102,IF(E102="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE102" s="8">
+        <f>IF(OR(AD102="",F102="",G102=""),"",AD102+F102*G102)</f>
+        <v/>
+      </c>
+      <c r="AF102" s="8">
+        <f>IF(OR(E102="",A102=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG102" s="8">
+        <f>IF(OR(AD102="",AF102=""),"",AD102-AF102)</f>
+        <v/>
+      </c>
+      <c r="AH102" s="4">
+        <f>IF(A102="","",IF(E102="","TERMINAL",IF(AG102="","INFO",IF(ABS(AG102)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -14905,10 +17155,31 @@
         <v/>
       </c>
       <c r="AA103" s="4">
-        <f>IF(A103="","",IF(OR(U103&gt;1,AND(X103&lt;&gt;"",X103&lt;Inputs!$B$16),AND(X103&lt;&gt;"",X103&gt;Inputs!$B$17),G103&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A103="","",IF(OR(U103&gt;1,AND(X103&lt;&gt;"",X103&lt;Inputs!$B$16),AND(X103&lt;&gt;"",X103&gt;Inputs!$B$17),G103&lt;Inputs!$B$18,AH103="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB103" s="4" t="n"/>
+      <c r="AC103" s="7" t="n"/>
+      <c r="AD103" s="8">
+        <f>IF(A103="","",IF(AC103&lt;&gt;"",AC103,IF(E103="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE103" s="8">
+        <f>IF(OR(AD103="",F103="",G103=""),"",AD103+F103*G103)</f>
+        <v/>
+      </c>
+      <c r="AF103" s="8">
+        <f>IF(OR(E103="",A103=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG103" s="8">
+        <f>IF(OR(AD103="",AF103=""),"",AD103-AF103)</f>
+        <v/>
+      </c>
+      <c r="AH103" s="4">
+        <f>IF(A103="","",IF(E103="","TERMINAL",IF(AG103="","INFO",IF(ABS(AG103)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -14979,10 +17250,31 @@
         <v/>
       </c>
       <c r="AA104" s="4">
-        <f>IF(A104="","",IF(OR(U104&gt;1,AND(X104&lt;&gt;"",X104&lt;Inputs!$B$16),AND(X104&lt;&gt;"",X104&gt;Inputs!$B$17),G104&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A104="","",IF(OR(U104&gt;1,AND(X104&lt;&gt;"",X104&lt;Inputs!$B$16),AND(X104&lt;&gt;"",X104&gt;Inputs!$B$17),G104&lt;Inputs!$B$18,AH104="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB104" s="4" t="n"/>
+      <c r="AC104" s="7" t="n"/>
+      <c r="AD104" s="8">
+        <f>IF(A104="","",IF(AC104&lt;&gt;"",AC104,IF(E104="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE104" s="8">
+        <f>IF(OR(AD104="",F104="",G104=""),"",AD104+F104*G104)</f>
+        <v/>
+      </c>
+      <c r="AF104" s="8">
+        <f>IF(OR(E104="",A104=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG104" s="8">
+        <f>IF(OR(AD104="",AF104=""),"",AD104-AF104)</f>
+        <v/>
+      </c>
+      <c r="AH104" s="4">
+        <f>IF(A104="","",IF(E104="","TERMINAL",IF(AG104="","INFO",IF(ABS(AG104)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -15053,10 +17345,31 @@
         <v/>
       </c>
       <c r="AA105" s="4">
-        <f>IF(A105="","",IF(OR(U105&gt;1,AND(X105&lt;&gt;"",X105&lt;Inputs!$B$16),AND(X105&lt;&gt;"",X105&gt;Inputs!$B$17),G105&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A105="","",IF(OR(U105&gt;1,AND(X105&lt;&gt;"",X105&lt;Inputs!$B$16),AND(X105&lt;&gt;"",X105&gt;Inputs!$B$17),G105&lt;Inputs!$B$18,AH105="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB105" s="4" t="n"/>
+      <c r="AC105" s="7" t="n"/>
+      <c r="AD105" s="8">
+        <f>IF(A105="","",IF(AC105&lt;&gt;"",AC105,IF(E105="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE105" s="8">
+        <f>IF(OR(AD105="",F105="",G105=""),"",AD105+F105*G105)</f>
+        <v/>
+      </c>
+      <c r="AF105" s="8">
+        <f>IF(OR(E105="",A105=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG105" s="8">
+        <f>IF(OR(AD105="",AF105=""),"",AD105-AF105)</f>
+        <v/>
+      </c>
+      <c r="AH105" s="4">
+        <f>IF(A105="","",IF(E105="","TERMINAL",IF(AG105="","INFO",IF(ABS(AG105)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
@@ -15127,10 +17440,31 @@
         <v/>
       </c>
       <c r="AA106" s="4">
-        <f>IF(A106="","",IF(OR(U106&gt;1,AND(X106&lt;&gt;"",X106&lt;Inputs!$B$16),AND(X106&lt;&gt;"",X106&gt;Inputs!$B$17),G106&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A106="","",IF(OR(U106&gt;1,AND(X106&lt;&gt;"",X106&lt;Inputs!$B$16),AND(X106&lt;&gt;"",X106&gt;Inputs!$B$17),G106&lt;Inputs!$B$18,AH106="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB106" s="4" t="n"/>
+      <c r="AC106" s="7" t="n"/>
+      <c r="AD106" s="8">
+        <f>IF(A106="","",IF(AC106&lt;&gt;"",AC106,IF(E106="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE106" s="8">
+        <f>IF(OR(AD106="",F106="",G106=""),"",AD106+F106*G106)</f>
+        <v/>
+      </c>
+      <c r="AF106" s="8">
+        <f>IF(OR(E106="",A106=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG106" s="8">
+        <f>IF(OR(AD106="",AF106=""),"",AD106-AF106)</f>
+        <v/>
+      </c>
+      <c r="AH106" s="4">
+        <f>IF(A106="","",IF(E106="","TERMINAL",IF(AG106="","INFO",IF(ABS(AG106)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -15201,10 +17535,31 @@
         <v/>
       </c>
       <c r="AA107" s="4">
-        <f>IF(A107="","",IF(OR(U107&gt;1,AND(X107&lt;&gt;"",X107&lt;Inputs!$B$16),AND(X107&lt;&gt;"",X107&gt;Inputs!$B$17),G107&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A107="","",IF(OR(U107&gt;1,AND(X107&lt;&gt;"",X107&lt;Inputs!$B$16),AND(X107&lt;&gt;"",X107&gt;Inputs!$B$17),G107&lt;Inputs!$B$18,AH107="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB107" s="4" t="n"/>
+      <c r="AC107" s="7" t="n"/>
+      <c r="AD107" s="8">
+        <f>IF(A107="","",IF(AC107&lt;&gt;"",AC107,IF(E107="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE107" s="8">
+        <f>IF(OR(AD107="",F107="",G107=""),"",AD107+F107*G107)</f>
+        <v/>
+      </c>
+      <c r="AF107" s="8">
+        <f>IF(OR(E107="",A107=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG107" s="8">
+        <f>IF(OR(AD107="",AF107=""),"",AD107-AF107)</f>
+        <v/>
+      </c>
+      <c r="AH107" s="4">
+        <f>IF(A107="","",IF(E107="","TERMINAL",IF(AG107="","INFO",IF(ABS(AG107)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
@@ -15275,10 +17630,31 @@
         <v/>
       </c>
       <c r="AA108" s="4">
-        <f>IF(A108="","",IF(OR(U108&gt;1,AND(X108&lt;&gt;"",X108&lt;Inputs!$B$16),AND(X108&lt;&gt;"",X108&gt;Inputs!$B$17),G108&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A108="","",IF(OR(U108&gt;1,AND(X108&lt;&gt;"",X108&lt;Inputs!$B$16),AND(X108&lt;&gt;"",X108&gt;Inputs!$B$17),G108&lt;Inputs!$B$18,AH108="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB108" s="4" t="n"/>
+      <c r="AC108" s="7" t="n"/>
+      <c r="AD108" s="8">
+        <f>IF(A108="","",IF(AC108&lt;&gt;"",AC108,IF(E108="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE108" s="8">
+        <f>IF(OR(AD108="",F108="",G108=""),"",AD108+F108*G108)</f>
+        <v/>
+      </c>
+      <c r="AF108" s="8">
+        <f>IF(OR(E108="",A108=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG108" s="8">
+        <f>IF(OR(AD108="",AF108=""),"",AD108-AF108)</f>
+        <v/>
+      </c>
+      <c r="AH108" s="4">
+        <f>IF(A108="","",IF(E108="","TERMINAL",IF(AG108="","INFO",IF(ABS(AG108)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -15349,10 +17725,31 @@
         <v/>
       </c>
       <c r="AA109" s="4">
-        <f>IF(A109="","",IF(OR(U109&gt;1,AND(X109&lt;&gt;"",X109&lt;Inputs!$B$16),AND(X109&lt;&gt;"",X109&gt;Inputs!$B$17),G109&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A109="","",IF(OR(U109&gt;1,AND(X109&lt;&gt;"",X109&lt;Inputs!$B$16),AND(X109&lt;&gt;"",X109&gt;Inputs!$B$17),G109&lt;Inputs!$B$18,AH109="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB109" s="4" t="n"/>
+      <c r="AC109" s="7" t="n"/>
+      <c r="AD109" s="8">
+        <f>IF(A109="","",IF(AC109&lt;&gt;"",AC109,IF(E109="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE109" s="8">
+        <f>IF(OR(AD109="",F109="",G109=""),"",AD109+F109*G109)</f>
+        <v/>
+      </c>
+      <c r="AF109" s="8">
+        <f>IF(OR(E109="",A109=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG109" s="8">
+        <f>IF(OR(AD109="",AF109=""),"",AD109-AF109)</f>
+        <v/>
+      </c>
+      <c r="AH109" s="4">
+        <f>IF(A109="","",IF(E109="","TERMINAL",IF(AG109="","INFO",IF(ABS(AG109)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n"/>
@@ -15423,10 +17820,31 @@
         <v/>
       </c>
       <c r="AA110" s="4">
-        <f>IF(A110="","",IF(OR(U110&gt;1,AND(X110&lt;&gt;"",X110&lt;Inputs!$B$16),AND(X110&lt;&gt;"",X110&gt;Inputs!$B$17),G110&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A110="","",IF(OR(U110&gt;1,AND(X110&lt;&gt;"",X110&lt;Inputs!$B$16),AND(X110&lt;&gt;"",X110&gt;Inputs!$B$17),G110&lt;Inputs!$B$18,AH110="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB110" s="4" t="n"/>
+      <c r="AC110" s="7" t="n"/>
+      <c r="AD110" s="8">
+        <f>IF(A110="","",IF(AC110&lt;&gt;"",AC110,IF(E110="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE110" s="8">
+        <f>IF(OR(AD110="",F110="",G110=""),"",AD110+F110*G110)</f>
+        <v/>
+      </c>
+      <c r="AF110" s="8">
+        <f>IF(OR(E110="",A110=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG110" s="8">
+        <f>IF(OR(AD110="",AF110=""),"",AD110-AF110)</f>
+        <v/>
+      </c>
+      <c r="AH110" s="4">
+        <f>IF(A110="","",IF(E110="","TERMINAL",IF(AG110="","INFO",IF(ABS(AG110)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -15497,10 +17915,31 @@
         <v/>
       </c>
       <c r="AA111" s="4">
-        <f>IF(A111="","",IF(OR(U111&gt;1,AND(X111&lt;&gt;"",X111&lt;Inputs!$B$16),AND(X111&lt;&gt;"",X111&gt;Inputs!$B$17),G111&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A111="","",IF(OR(U111&gt;1,AND(X111&lt;&gt;"",X111&lt;Inputs!$B$16),AND(X111&lt;&gt;"",X111&gt;Inputs!$B$17),G111&lt;Inputs!$B$18,AH111="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB111" s="4" t="n"/>
+      <c r="AC111" s="7" t="n"/>
+      <c r="AD111" s="8">
+        <f>IF(A111="","",IF(AC111&lt;&gt;"",AC111,IF(E111="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE111" s="8">
+        <f>IF(OR(AD111="",F111="",G111=""),"",AD111+F111*G111)</f>
+        <v/>
+      </c>
+      <c r="AF111" s="8">
+        <f>IF(OR(E111="",A111=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG111" s="8">
+        <f>IF(OR(AD111="",AF111=""),"",AD111-AF111)</f>
+        <v/>
+      </c>
+      <c r="AH111" s="4">
+        <f>IF(A111="","",IF(E111="","TERMINAL",IF(AG111="","INFO",IF(ABS(AG111)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -15571,10 +18010,31 @@
         <v/>
       </c>
       <c r="AA112" s="4">
-        <f>IF(A112="","",IF(OR(U112&gt;1,AND(X112&lt;&gt;"",X112&lt;Inputs!$B$16),AND(X112&lt;&gt;"",X112&gt;Inputs!$B$17),G112&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A112="","",IF(OR(U112&gt;1,AND(X112&lt;&gt;"",X112&lt;Inputs!$B$16),AND(X112&lt;&gt;"",X112&gt;Inputs!$B$17),G112&lt;Inputs!$B$18,AH112="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB112" s="4" t="n"/>
+      <c r="AC112" s="7" t="n"/>
+      <c r="AD112" s="8">
+        <f>IF(A112="","",IF(AC112&lt;&gt;"",AC112,IF(E112="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE112" s="8">
+        <f>IF(OR(AD112="",F112="",G112=""),"",AD112+F112*G112)</f>
+        <v/>
+      </c>
+      <c r="AF112" s="8">
+        <f>IF(OR(E112="",A112=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG112" s="8">
+        <f>IF(OR(AD112="",AF112=""),"",AD112-AF112)</f>
+        <v/>
+      </c>
+      <c r="AH112" s="4">
+        <f>IF(A112="","",IF(E112="","TERMINAL",IF(AG112="","INFO",IF(ABS(AG112)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -15645,10 +18105,31 @@
         <v/>
       </c>
       <c r="AA113" s="4">
-        <f>IF(A113="","",IF(OR(U113&gt;1,AND(X113&lt;&gt;"",X113&lt;Inputs!$B$16),AND(X113&lt;&gt;"",X113&gt;Inputs!$B$17),G113&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A113="","",IF(OR(U113&gt;1,AND(X113&lt;&gt;"",X113&lt;Inputs!$B$16),AND(X113&lt;&gt;"",X113&gt;Inputs!$B$17),G113&lt;Inputs!$B$18,AH113="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB113" s="4" t="n"/>
+      <c r="AC113" s="7" t="n"/>
+      <c r="AD113" s="8">
+        <f>IF(A113="","",IF(AC113&lt;&gt;"",AC113,IF(E113="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE113" s="8">
+        <f>IF(OR(AD113="",F113="",G113=""),"",AD113+F113*G113)</f>
+        <v/>
+      </c>
+      <c r="AF113" s="8">
+        <f>IF(OR(E113="",A113=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG113" s="8">
+        <f>IF(OR(AD113="",AF113=""),"",AD113-AF113)</f>
+        <v/>
+      </c>
+      <c r="AH113" s="4">
+        <f>IF(A113="","",IF(E113="","TERMINAL",IF(AG113="","INFO",IF(ABS(AG113)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
@@ -15719,10 +18200,31 @@
         <v/>
       </c>
       <c r="AA114" s="4">
-        <f>IF(A114="","",IF(OR(U114&gt;1,AND(X114&lt;&gt;"",X114&lt;Inputs!$B$16),AND(X114&lt;&gt;"",X114&gt;Inputs!$B$17),G114&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A114="","",IF(OR(U114&gt;1,AND(X114&lt;&gt;"",X114&lt;Inputs!$B$16),AND(X114&lt;&gt;"",X114&gt;Inputs!$B$17),G114&lt;Inputs!$B$18,AH114="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB114" s="4" t="n"/>
+      <c r="AC114" s="7" t="n"/>
+      <c r="AD114" s="8">
+        <f>IF(A114="","",IF(AC114&lt;&gt;"",AC114,IF(E114="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE114" s="8">
+        <f>IF(OR(AD114="",F114="",G114=""),"",AD114+F114*G114)</f>
+        <v/>
+      </c>
+      <c r="AF114" s="8">
+        <f>IF(OR(E114="",A114=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG114" s="8">
+        <f>IF(OR(AD114="",AF114=""),"",AD114-AF114)</f>
+        <v/>
+      </c>
+      <c r="AH114" s="4">
+        <f>IF(A114="","",IF(E114="","TERMINAL",IF(AG114="","INFO",IF(ABS(AG114)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -15793,10 +18295,31 @@
         <v/>
       </c>
       <c r="AA115" s="4">
-        <f>IF(A115="","",IF(OR(U115&gt;1,AND(X115&lt;&gt;"",X115&lt;Inputs!$B$16),AND(X115&lt;&gt;"",X115&gt;Inputs!$B$17),G115&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A115="","",IF(OR(U115&gt;1,AND(X115&lt;&gt;"",X115&lt;Inputs!$B$16),AND(X115&lt;&gt;"",X115&gt;Inputs!$B$17),G115&lt;Inputs!$B$18,AH115="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB115" s="4" t="n"/>
+      <c r="AC115" s="7" t="n"/>
+      <c r="AD115" s="8">
+        <f>IF(A115="","",IF(AC115&lt;&gt;"",AC115,IF(E115="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE115" s="8">
+        <f>IF(OR(AD115="",F115="",G115=""),"",AD115+F115*G115)</f>
+        <v/>
+      </c>
+      <c r="AF115" s="8">
+        <f>IF(OR(E115="",A115=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG115" s="8">
+        <f>IF(OR(AD115="",AF115=""),"",AD115-AF115)</f>
+        <v/>
+      </c>
+      <c r="AH115" s="4">
+        <f>IF(A115="","",IF(E115="","TERMINAL",IF(AG115="","INFO",IF(ABS(AG115)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -15867,10 +18390,31 @@
         <v/>
       </c>
       <c r="AA116" s="4">
-        <f>IF(A116="","",IF(OR(U116&gt;1,AND(X116&lt;&gt;"",X116&lt;Inputs!$B$16),AND(X116&lt;&gt;"",X116&gt;Inputs!$B$17),G116&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A116="","",IF(OR(U116&gt;1,AND(X116&lt;&gt;"",X116&lt;Inputs!$B$16),AND(X116&lt;&gt;"",X116&gt;Inputs!$B$17),G116&lt;Inputs!$B$18,AH116="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB116" s="4" t="n"/>
+      <c r="AC116" s="7" t="n"/>
+      <c r="AD116" s="8">
+        <f>IF(A116="","",IF(AC116&lt;&gt;"",AC116,IF(E116="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE116" s="8">
+        <f>IF(OR(AD116="",F116="",G116=""),"",AD116+F116*G116)</f>
+        <v/>
+      </c>
+      <c r="AF116" s="8">
+        <f>IF(OR(E116="",A116=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG116" s="8">
+        <f>IF(OR(AD116="",AF116=""),"",AD116-AF116)</f>
+        <v/>
+      </c>
+      <c r="AH116" s="4">
+        <f>IF(A116="","",IF(E116="","TERMINAL",IF(AG116="","INFO",IF(ABS(AG116)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -15941,10 +18485,31 @@
         <v/>
       </c>
       <c r="AA117" s="4">
-        <f>IF(A117="","",IF(OR(U117&gt;1,AND(X117&lt;&gt;"",X117&lt;Inputs!$B$16),AND(X117&lt;&gt;"",X117&gt;Inputs!$B$17),G117&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A117="","",IF(OR(U117&gt;1,AND(X117&lt;&gt;"",X117&lt;Inputs!$B$16),AND(X117&lt;&gt;"",X117&gt;Inputs!$B$17),G117&lt;Inputs!$B$18,AH117="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB117" s="4" t="n"/>
+      <c r="AC117" s="7" t="n"/>
+      <c r="AD117" s="8">
+        <f>IF(A117="","",IF(AC117&lt;&gt;"",AC117,IF(E117="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE117" s="8">
+        <f>IF(OR(AD117="",F117="",G117=""),"",AD117+F117*G117)</f>
+        <v/>
+      </c>
+      <c r="AF117" s="8">
+        <f>IF(OR(E117="",A117=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG117" s="8">
+        <f>IF(OR(AD117="",AF117=""),"",AD117-AF117)</f>
+        <v/>
+      </c>
+      <c r="AH117" s="4">
+        <f>IF(A117="","",IF(E117="","TERMINAL",IF(AG117="","INFO",IF(ABS(AG117)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n"/>
@@ -16015,10 +18580,31 @@
         <v/>
       </c>
       <c r="AA118" s="4">
-        <f>IF(A118="","",IF(OR(U118&gt;1,AND(X118&lt;&gt;"",X118&lt;Inputs!$B$16),AND(X118&lt;&gt;"",X118&gt;Inputs!$B$17),G118&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A118="","",IF(OR(U118&gt;1,AND(X118&lt;&gt;"",X118&lt;Inputs!$B$16),AND(X118&lt;&gt;"",X118&gt;Inputs!$B$17),G118&lt;Inputs!$B$18,AH118="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB118" s="4" t="n"/>
+      <c r="AC118" s="7" t="n"/>
+      <c r="AD118" s="8">
+        <f>IF(A118="","",IF(AC118&lt;&gt;"",AC118,IF(E118="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE118" s="8">
+        <f>IF(OR(AD118="",F118="",G118=""),"",AD118+F118*G118)</f>
+        <v/>
+      </c>
+      <c r="AF118" s="8">
+        <f>IF(OR(E118="",A118=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG118" s="8">
+        <f>IF(OR(AD118="",AF118=""),"",AD118-AF118)</f>
+        <v/>
+      </c>
+      <c r="AH118" s="4">
+        <f>IF(A118="","",IF(E118="","TERMINAL",IF(AG118="","INFO",IF(ABS(AG118)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -16089,10 +18675,31 @@
         <v/>
       </c>
       <c r="AA119" s="4">
-        <f>IF(A119="","",IF(OR(U119&gt;1,AND(X119&lt;&gt;"",X119&lt;Inputs!$B$16),AND(X119&lt;&gt;"",X119&gt;Inputs!$B$17),G119&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A119="","",IF(OR(U119&gt;1,AND(X119&lt;&gt;"",X119&lt;Inputs!$B$16),AND(X119&lt;&gt;"",X119&gt;Inputs!$B$17),G119&lt;Inputs!$B$18,AH119="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB119" s="4" t="n"/>
+      <c r="AC119" s="7" t="n"/>
+      <c r="AD119" s="8">
+        <f>IF(A119="","",IF(AC119&lt;&gt;"",AC119,IF(E119="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE119" s="8">
+        <f>IF(OR(AD119="",F119="",G119=""),"",AD119+F119*G119)</f>
+        <v/>
+      </c>
+      <c r="AF119" s="8">
+        <f>IF(OR(E119="",A119=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG119" s="8">
+        <f>IF(OR(AD119="",AF119=""),"",AD119-AF119)</f>
+        <v/>
+      </c>
+      <c r="AH119" s="4">
+        <f>IF(A119="","",IF(E119="","TERMINAL",IF(AG119="","INFO",IF(ABS(AG119)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n"/>
@@ -16163,10 +18770,31 @@
         <v/>
       </c>
       <c r="AA120" s="4">
-        <f>IF(A120="","",IF(OR(U120&gt;1,AND(X120&lt;&gt;"",X120&lt;Inputs!$B$16),AND(X120&lt;&gt;"",X120&gt;Inputs!$B$17),G120&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A120="","",IF(OR(U120&gt;1,AND(X120&lt;&gt;"",X120&lt;Inputs!$B$16),AND(X120&lt;&gt;"",X120&gt;Inputs!$B$17),G120&lt;Inputs!$B$18,AH120="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB120" s="4" t="n"/>
+      <c r="AC120" s="7" t="n"/>
+      <c r="AD120" s="8">
+        <f>IF(A120="","",IF(AC120&lt;&gt;"",AC120,IF(E120="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE120" s="8">
+        <f>IF(OR(AD120="",F120="",G120=""),"",AD120+F120*G120)</f>
+        <v/>
+      </c>
+      <c r="AF120" s="8">
+        <f>IF(OR(E120="",A120=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG120" s="8">
+        <f>IF(OR(AD120="",AF120=""),"",AD120-AF120)</f>
+        <v/>
+      </c>
+      <c r="AH120" s="4">
+        <f>IF(A120="","",IF(E120="","TERMINAL",IF(AG120="","INFO",IF(ABS(AG120)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -16237,10 +18865,31 @@
         <v/>
       </c>
       <c r="AA121" s="4">
-        <f>IF(A121="","",IF(OR(U121&gt;1,AND(X121&lt;&gt;"",X121&lt;Inputs!$B$16),AND(X121&lt;&gt;"",X121&gt;Inputs!$B$17),G121&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A121="","",IF(OR(U121&gt;1,AND(X121&lt;&gt;"",X121&lt;Inputs!$B$16),AND(X121&lt;&gt;"",X121&gt;Inputs!$B$17),G121&lt;Inputs!$B$18,AH121="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB121" s="4" t="n"/>
+      <c r="AC121" s="7" t="n"/>
+      <c r="AD121" s="8">
+        <f>IF(A121="","",IF(AC121&lt;&gt;"",AC121,IF(E121="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE121" s="8">
+        <f>IF(OR(AD121="",F121="",G121=""),"",AD121+F121*G121)</f>
+        <v/>
+      </c>
+      <c r="AF121" s="8">
+        <f>IF(OR(E121="",A121=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG121" s="8">
+        <f>IF(OR(AD121="",AF121=""),"",AD121-AF121)</f>
+        <v/>
+      </c>
+      <c r="AH121" s="4">
+        <f>IF(A121="","",IF(E121="","TERMINAL",IF(AG121="","INFO",IF(ABS(AG121)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -16311,10 +18960,31 @@
         <v/>
       </c>
       <c r="AA122" s="4">
-        <f>IF(A122="","",IF(OR(U122&gt;1,AND(X122&lt;&gt;"",X122&lt;Inputs!$B$16),AND(X122&lt;&gt;"",X122&gt;Inputs!$B$17),G122&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A122="","",IF(OR(U122&gt;1,AND(X122&lt;&gt;"",X122&lt;Inputs!$B$16),AND(X122&lt;&gt;"",X122&gt;Inputs!$B$17),G122&lt;Inputs!$B$18,AH122="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB122" s="4" t="n"/>
+      <c r="AC122" s="7" t="n"/>
+      <c r="AD122" s="8">
+        <f>IF(A122="","",IF(AC122&lt;&gt;"",AC122,IF(E122="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE122" s="8">
+        <f>IF(OR(AD122="",F122="",G122=""),"",AD122+F122*G122)</f>
+        <v/>
+      </c>
+      <c r="AF122" s="8">
+        <f>IF(OR(E122="",A122=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG122" s="8">
+        <f>IF(OR(AD122="",AF122=""),"",AD122-AF122)</f>
+        <v/>
+      </c>
+      <c r="AH122" s="4">
+        <f>IF(A122="","",IF(E122="","TERMINAL",IF(AG122="","INFO",IF(ABS(AG122)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -16385,10 +19055,31 @@
         <v/>
       </c>
       <c r="AA123" s="4">
-        <f>IF(A123="","",IF(OR(U123&gt;1,AND(X123&lt;&gt;"",X123&lt;Inputs!$B$16),AND(X123&lt;&gt;"",X123&gt;Inputs!$B$17),G123&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A123="","",IF(OR(U123&gt;1,AND(X123&lt;&gt;"",X123&lt;Inputs!$B$16),AND(X123&lt;&gt;"",X123&gt;Inputs!$B$17),G123&lt;Inputs!$B$18,AH123="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB123" s="4" t="n"/>
+      <c r="AC123" s="7" t="n"/>
+      <c r="AD123" s="8">
+        <f>IF(A123="","",IF(AC123&lt;&gt;"",AC123,IF(E123="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE123" s="8">
+        <f>IF(OR(AD123="",F123="",G123=""),"",AD123+F123*G123)</f>
+        <v/>
+      </c>
+      <c r="AF123" s="8">
+        <f>IF(OR(E123="",A123=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG123" s="8">
+        <f>IF(OR(AD123="",AF123=""),"",AD123-AF123)</f>
+        <v/>
+      </c>
+      <c r="AH123" s="4">
+        <f>IF(A123="","",IF(E123="","TERMINAL",IF(AG123="","INFO",IF(ABS(AG123)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n"/>
@@ -16459,10 +19150,31 @@
         <v/>
       </c>
       <c r="AA124" s="4">
-        <f>IF(A124="","",IF(OR(U124&gt;1,AND(X124&lt;&gt;"",X124&lt;Inputs!$B$16),AND(X124&lt;&gt;"",X124&gt;Inputs!$B$17),G124&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A124="","",IF(OR(U124&gt;1,AND(X124&lt;&gt;"",X124&lt;Inputs!$B$16),AND(X124&lt;&gt;"",X124&gt;Inputs!$B$17),G124&lt;Inputs!$B$18,AH124="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB124" s="4" t="n"/>
+      <c r="AC124" s="7" t="n"/>
+      <c r="AD124" s="8">
+        <f>IF(A124="","",IF(AC124&lt;&gt;"",AC124,IF(E124="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE124" s="8">
+        <f>IF(OR(AD124="",F124="",G124=""),"",AD124+F124*G124)</f>
+        <v/>
+      </c>
+      <c r="AF124" s="8">
+        <f>IF(OR(E124="",A124=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG124" s="8">
+        <f>IF(OR(AD124="",AF124=""),"",AD124-AF124)</f>
+        <v/>
+      </c>
+      <c r="AH124" s="4">
+        <f>IF(A124="","",IF(E124="","TERMINAL",IF(AG124="","INFO",IF(ABS(AG124)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -16533,10 +19245,31 @@
         <v/>
       </c>
       <c r="AA125" s="4">
-        <f>IF(A125="","",IF(OR(U125&gt;1,AND(X125&lt;&gt;"",X125&lt;Inputs!$B$16),AND(X125&lt;&gt;"",X125&gt;Inputs!$B$17),G125&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A125="","",IF(OR(U125&gt;1,AND(X125&lt;&gt;"",X125&lt;Inputs!$B$16),AND(X125&lt;&gt;"",X125&gt;Inputs!$B$17),G125&lt;Inputs!$B$18,AH125="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB125" s="4" t="n"/>
+      <c r="AC125" s="7" t="n"/>
+      <c r="AD125" s="8">
+        <f>IF(A125="","",IF(AC125&lt;&gt;"",AC125,IF(E125="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE125" s="8">
+        <f>IF(OR(AD125="",F125="",G125=""),"",AD125+F125*G125)</f>
+        <v/>
+      </c>
+      <c r="AF125" s="8">
+        <f>IF(OR(E125="",A125=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG125" s="8">
+        <f>IF(OR(AD125="",AF125=""),"",AD125-AF125)</f>
+        <v/>
+      </c>
+      <c r="AH125" s="4">
+        <f>IF(A125="","",IF(E125="","TERMINAL",IF(AG125="","INFO",IF(ABS(AG125)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -16607,10 +19340,31 @@
         <v/>
       </c>
       <c r="AA126" s="4">
-        <f>IF(A126="","",IF(OR(U126&gt;1,AND(X126&lt;&gt;"",X126&lt;Inputs!$B$16),AND(X126&lt;&gt;"",X126&gt;Inputs!$B$17),G126&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A126="","",IF(OR(U126&gt;1,AND(X126&lt;&gt;"",X126&lt;Inputs!$B$16),AND(X126&lt;&gt;"",X126&gt;Inputs!$B$17),G126&lt;Inputs!$B$18,AH126="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB126" s="4" t="n"/>
+      <c r="AC126" s="7" t="n"/>
+      <c r="AD126" s="8">
+        <f>IF(A126="","",IF(AC126&lt;&gt;"",AC126,IF(E126="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE126" s="8">
+        <f>IF(OR(AD126="",F126="",G126=""),"",AD126+F126*G126)</f>
+        <v/>
+      </c>
+      <c r="AF126" s="8">
+        <f>IF(OR(E126="",A126=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG126" s="8">
+        <f>IF(OR(AD126="",AF126=""),"",AD126-AF126)</f>
+        <v/>
+      </c>
+      <c r="AH126" s="4">
+        <f>IF(A126="","",IF(E126="","TERMINAL",IF(AG126="","INFO",IF(ABS(AG126)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -16681,10 +19435,31 @@
         <v/>
       </c>
       <c r="AA127" s="4">
-        <f>IF(A127="","",IF(OR(U127&gt;1,AND(X127&lt;&gt;"",X127&lt;Inputs!$B$16),AND(X127&lt;&gt;"",X127&gt;Inputs!$B$17),G127&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A127="","",IF(OR(U127&gt;1,AND(X127&lt;&gt;"",X127&lt;Inputs!$B$16),AND(X127&lt;&gt;"",X127&gt;Inputs!$B$17),G127&lt;Inputs!$B$18,AH127="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB127" s="4" t="n"/>
+      <c r="AC127" s="7" t="n"/>
+      <c r="AD127" s="8">
+        <f>IF(A127="","",IF(AC127&lt;&gt;"",AC127,IF(E127="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE127" s="8">
+        <f>IF(OR(AD127="",F127="",G127=""),"",AD127+F127*G127)</f>
+        <v/>
+      </c>
+      <c r="AF127" s="8">
+        <f>IF(OR(E127="",A127=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG127" s="8">
+        <f>IF(OR(AD127="",AF127=""),"",AD127-AF127)</f>
+        <v/>
+      </c>
+      <c r="AH127" s="4">
+        <f>IF(A127="","",IF(E127="","TERMINAL",IF(AG127="","INFO",IF(ABS(AG127)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n"/>
@@ -16755,10 +19530,31 @@
         <v/>
       </c>
       <c r="AA128" s="4">
-        <f>IF(A128="","",IF(OR(U128&gt;1,AND(X128&lt;&gt;"",X128&lt;Inputs!$B$16),AND(X128&lt;&gt;"",X128&gt;Inputs!$B$17),G128&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A128="","",IF(OR(U128&gt;1,AND(X128&lt;&gt;"",X128&lt;Inputs!$B$16),AND(X128&lt;&gt;"",X128&gt;Inputs!$B$17),G128&lt;Inputs!$B$18,AH128="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB128" s="4" t="n"/>
+      <c r="AC128" s="7" t="n"/>
+      <c r="AD128" s="8">
+        <f>IF(A128="","",IF(AC128&lt;&gt;"",AC128,IF(E128="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE128" s="8">
+        <f>IF(OR(AD128="",F128="",G128=""),"",AD128+F128*G128)</f>
+        <v/>
+      </c>
+      <c r="AF128" s="8">
+        <f>IF(OR(E128="",A128=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG128" s="8">
+        <f>IF(OR(AD128="",AF128=""),"",AD128-AF128)</f>
+        <v/>
+      </c>
+      <c r="AH128" s="4">
+        <f>IF(A128="","",IF(E128="","TERMINAL",IF(AG128="","INFO",IF(ABS(AG128)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -16829,10 +19625,31 @@
         <v/>
       </c>
       <c r="AA129" s="4">
-        <f>IF(A129="","",IF(OR(U129&gt;1,AND(X129&lt;&gt;"",X129&lt;Inputs!$B$16),AND(X129&lt;&gt;"",X129&gt;Inputs!$B$17),G129&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A129="","",IF(OR(U129&gt;1,AND(X129&lt;&gt;"",X129&lt;Inputs!$B$16),AND(X129&lt;&gt;"",X129&gt;Inputs!$B$17),G129&lt;Inputs!$B$18,AH129="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB129" s="4" t="n"/>
+      <c r="AC129" s="7" t="n"/>
+      <c r="AD129" s="8">
+        <f>IF(A129="","",IF(AC129&lt;&gt;"",AC129,IF(E129="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE129" s="8">
+        <f>IF(OR(AD129="",F129="",G129=""),"",AD129+F129*G129)</f>
+        <v/>
+      </c>
+      <c r="AF129" s="8">
+        <f>IF(OR(E129="",A129=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG129" s="8">
+        <f>IF(OR(AD129="",AF129=""),"",AD129-AF129)</f>
+        <v/>
+      </c>
+      <c r="AH129" s="4">
+        <f>IF(A129="","",IF(E129="","TERMINAL",IF(AG129="","INFO",IF(ABS(AG129)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n"/>
@@ -16903,10 +19720,31 @@
         <v/>
       </c>
       <c r="AA130" s="4">
-        <f>IF(A130="","",IF(OR(U130&gt;1,AND(X130&lt;&gt;"",X130&lt;Inputs!$B$16),AND(X130&lt;&gt;"",X130&gt;Inputs!$B$17),G130&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A130="","",IF(OR(U130&gt;1,AND(X130&lt;&gt;"",X130&lt;Inputs!$B$16),AND(X130&lt;&gt;"",X130&gt;Inputs!$B$17),G130&lt;Inputs!$B$18,AH130="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB130" s="4" t="n"/>
+      <c r="AC130" s="7" t="n"/>
+      <c r="AD130" s="8">
+        <f>IF(A130="","",IF(AC130&lt;&gt;"",AC130,IF(E130="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE130" s="8">
+        <f>IF(OR(AD130="",F130="",G130=""),"",AD130+F130*G130)</f>
+        <v/>
+      </c>
+      <c r="AF130" s="8">
+        <f>IF(OR(E130="",A130=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG130" s="8">
+        <f>IF(OR(AD130="",AF130=""),"",AD130-AF130)</f>
+        <v/>
+      </c>
+      <c r="AH130" s="4">
+        <f>IF(A130="","",IF(E130="","TERMINAL",IF(AG130="","INFO",IF(ABS(AG130)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -16977,10 +19815,31 @@
         <v/>
       </c>
       <c r="AA131" s="4">
-        <f>IF(A131="","",IF(OR(U131&gt;1,AND(X131&lt;&gt;"",X131&lt;Inputs!$B$16),AND(X131&lt;&gt;"",X131&gt;Inputs!$B$17),G131&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A131="","",IF(OR(U131&gt;1,AND(X131&lt;&gt;"",X131&lt;Inputs!$B$16),AND(X131&lt;&gt;"",X131&gt;Inputs!$B$17),G131&lt;Inputs!$B$18,AH131="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB131" s="4" t="n"/>
+      <c r="AC131" s="7" t="n"/>
+      <c r="AD131" s="8">
+        <f>IF(A131="","",IF(AC131&lt;&gt;"",AC131,IF(E131="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE131" s="8">
+        <f>IF(OR(AD131="",F131="",G131=""),"",AD131+F131*G131)</f>
+        <v/>
+      </c>
+      <c r="AF131" s="8">
+        <f>IF(OR(E131="",A131=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG131" s="8">
+        <f>IF(OR(AD131="",AF131=""),"",AD131-AF131)</f>
+        <v/>
+      </c>
+      <c r="AH131" s="4">
+        <f>IF(A131="","",IF(E131="","TERMINAL",IF(AG131="","INFO",IF(ABS(AG131)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n"/>
@@ -17051,10 +19910,31 @@
         <v/>
       </c>
       <c r="AA132" s="4">
-        <f>IF(A132="","",IF(OR(U132&gt;1,AND(X132&lt;&gt;"",X132&lt;Inputs!$B$16),AND(X132&lt;&gt;"",X132&gt;Inputs!$B$17),G132&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A132="","",IF(OR(U132&gt;1,AND(X132&lt;&gt;"",X132&lt;Inputs!$B$16),AND(X132&lt;&gt;"",X132&gt;Inputs!$B$17),G132&lt;Inputs!$B$18,AH132="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB132" s="4" t="n"/>
+      <c r="AC132" s="7" t="n"/>
+      <c r="AD132" s="8">
+        <f>IF(A132="","",IF(AC132&lt;&gt;"",AC132,IF(E132="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE132" s="8">
+        <f>IF(OR(AD132="",F132="",G132=""),"",AD132+F132*G132)</f>
+        <v/>
+      </c>
+      <c r="AF132" s="8">
+        <f>IF(OR(E132="",A132=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG132" s="8">
+        <f>IF(OR(AD132="",AF132=""),"",AD132-AF132)</f>
+        <v/>
+      </c>
+      <c r="AH132" s="4">
+        <f>IF(A132="","",IF(E132="","TERMINAL",IF(AG132="","INFO",IF(ABS(AG132)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -17125,10 +20005,31 @@
         <v/>
       </c>
       <c r="AA133" s="4">
-        <f>IF(A133="","",IF(OR(U133&gt;1,AND(X133&lt;&gt;"",X133&lt;Inputs!$B$16),AND(X133&lt;&gt;"",X133&gt;Inputs!$B$17),G133&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A133="","",IF(OR(U133&gt;1,AND(X133&lt;&gt;"",X133&lt;Inputs!$B$16),AND(X133&lt;&gt;"",X133&gt;Inputs!$B$17),G133&lt;Inputs!$B$18,AH133="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB133" s="4" t="n"/>
+      <c r="AC133" s="7" t="n"/>
+      <c r="AD133" s="8">
+        <f>IF(A133="","",IF(AC133&lt;&gt;"",AC133,IF(E133="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE133" s="8">
+        <f>IF(OR(AD133="",F133="",G133=""),"",AD133+F133*G133)</f>
+        <v/>
+      </c>
+      <c r="AF133" s="8">
+        <f>IF(OR(E133="",A133=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG133" s="8">
+        <f>IF(OR(AD133="",AF133=""),"",AD133-AF133)</f>
+        <v/>
+      </c>
+      <c r="AH133" s="4">
+        <f>IF(A133="","",IF(E133="","TERMINAL",IF(AG133="","INFO",IF(ABS(AG133)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n"/>
@@ -17199,10 +20100,31 @@
         <v/>
       </c>
       <c r="AA134" s="4">
-        <f>IF(A134="","",IF(OR(U134&gt;1,AND(X134&lt;&gt;"",X134&lt;Inputs!$B$16),AND(X134&lt;&gt;"",X134&gt;Inputs!$B$17),G134&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A134="","",IF(OR(U134&gt;1,AND(X134&lt;&gt;"",X134&lt;Inputs!$B$16),AND(X134&lt;&gt;"",X134&gt;Inputs!$B$17),G134&lt;Inputs!$B$18,AH134="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB134" s="4" t="n"/>
+      <c r="AC134" s="7" t="n"/>
+      <c r="AD134" s="8">
+        <f>IF(A134="","",IF(AC134&lt;&gt;"",AC134,IF(E134="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE134" s="8">
+        <f>IF(OR(AD134="",F134="",G134=""),"",AD134+F134*G134)</f>
+        <v/>
+      </c>
+      <c r="AF134" s="8">
+        <f>IF(OR(E134="",A134=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG134" s="8">
+        <f>IF(OR(AD134="",AF134=""),"",AD134-AF134)</f>
+        <v/>
+      </c>
+      <c r="AH134" s="4">
+        <f>IF(A134="","",IF(E134="","TERMINAL",IF(AG134="","INFO",IF(ABS(AG134)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -17273,10 +20195,31 @@
         <v/>
       </c>
       <c r="AA135" s="4">
-        <f>IF(A135="","",IF(OR(U135&gt;1,AND(X135&lt;&gt;"",X135&lt;Inputs!$B$16),AND(X135&lt;&gt;"",X135&gt;Inputs!$B$17),G135&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A135="","",IF(OR(U135&gt;1,AND(X135&lt;&gt;"",X135&lt;Inputs!$B$16),AND(X135&lt;&gt;"",X135&gt;Inputs!$B$17),G135&lt;Inputs!$B$18,AH135="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB135" s="4" t="n"/>
+      <c r="AC135" s="7" t="n"/>
+      <c r="AD135" s="8">
+        <f>IF(A135="","",IF(AC135&lt;&gt;"",AC135,IF(E135="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE135" s="8">
+        <f>IF(OR(AD135="",F135="",G135=""),"",AD135+F135*G135)</f>
+        <v/>
+      </c>
+      <c r="AF135" s="8">
+        <f>IF(OR(E135="",A135=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG135" s="8">
+        <f>IF(OR(AD135="",AF135=""),"",AD135-AF135)</f>
+        <v/>
+      </c>
+      <c r="AH135" s="4">
+        <f>IF(A135="","",IF(E135="","TERMINAL",IF(AG135="","INFO",IF(ABS(AG135)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n"/>
@@ -17347,10 +20290,31 @@
         <v/>
       </c>
       <c r="AA136" s="4">
-        <f>IF(A136="","",IF(OR(U136&gt;1,AND(X136&lt;&gt;"",X136&lt;Inputs!$B$16),AND(X136&lt;&gt;"",X136&gt;Inputs!$B$17),G136&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A136="","",IF(OR(U136&gt;1,AND(X136&lt;&gt;"",X136&lt;Inputs!$B$16),AND(X136&lt;&gt;"",X136&gt;Inputs!$B$17),G136&lt;Inputs!$B$18,AH136="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB136" s="4" t="n"/>
+      <c r="AC136" s="7" t="n"/>
+      <c r="AD136" s="8">
+        <f>IF(A136="","",IF(AC136&lt;&gt;"",AC136,IF(E136="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE136" s="8">
+        <f>IF(OR(AD136="",F136="",G136=""),"",AD136+F136*G136)</f>
+        <v/>
+      </c>
+      <c r="AF136" s="8">
+        <f>IF(OR(E136="",A136=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG136" s="8">
+        <f>IF(OR(AD136="",AF136=""),"",AD136-AF136)</f>
+        <v/>
+      </c>
+      <c r="AH136" s="4">
+        <f>IF(A136="","",IF(E136="","TERMINAL",IF(AG136="","INFO",IF(ABS(AG136)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -17421,10 +20385,31 @@
         <v/>
       </c>
       <c r="AA137" s="4">
-        <f>IF(A137="","",IF(OR(U137&gt;1,AND(X137&lt;&gt;"",X137&lt;Inputs!$B$16),AND(X137&lt;&gt;"",X137&gt;Inputs!$B$17),G137&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A137="","",IF(OR(U137&gt;1,AND(X137&lt;&gt;"",X137&lt;Inputs!$B$16),AND(X137&lt;&gt;"",X137&gt;Inputs!$B$17),G137&lt;Inputs!$B$18,AH137="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB137" s="4" t="n"/>
+      <c r="AC137" s="7" t="n"/>
+      <c r="AD137" s="8">
+        <f>IF(A137="","",IF(AC137&lt;&gt;"",AC137,IF(E137="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE137" s="8">
+        <f>IF(OR(AD137="",F137="",G137=""),"",AD137+F137*G137)</f>
+        <v/>
+      </c>
+      <c r="AF137" s="8">
+        <f>IF(OR(E137="",A137=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG137" s="8">
+        <f>IF(OR(AD137="",AF137=""),"",AD137-AF137)</f>
+        <v/>
+      </c>
+      <c r="AH137" s="4">
+        <f>IF(A137="","",IF(E137="","TERMINAL",IF(AG137="","INFO",IF(ABS(AG137)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -17495,10 +20480,31 @@
         <v/>
       </c>
       <c r="AA138" s="4">
-        <f>IF(A138="","",IF(OR(U138&gt;1,AND(X138&lt;&gt;"",X138&lt;Inputs!$B$16),AND(X138&lt;&gt;"",X138&gt;Inputs!$B$17),G138&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A138="","",IF(OR(U138&gt;1,AND(X138&lt;&gt;"",X138&lt;Inputs!$B$16),AND(X138&lt;&gt;"",X138&gt;Inputs!$B$17),G138&lt;Inputs!$B$18,AH138="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB138" s="4" t="n"/>
+      <c r="AC138" s="7" t="n"/>
+      <c r="AD138" s="8">
+        <f>IF(A138="","",IF(AC138&lt;&gt;"",AC138,IF(E138="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE138" s="8">
+        <f>IF(OR(AD138="",F138="",G138=""),"",AD138+F138*G138)</f>
+        <v/>
+      </c>
+      <c r="AF138" s="8">
+        <f>IF(OR(E138="",A138=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG138" s="8">
+        <f>IF(OR(AD138="",AF138=""),"",AD138-AF138)</f>
+        <v/>
+      </c>
+      <c r="AH138" s="4">
+        <f>IF(A138="","",IF(E138="","TERMINAL",IF(AG138="","INFO",IF(ABS(AG138)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -17569,10 +20575,31 @@
         <v/>
       </c>
       <c r="AA139" s="4">
-        <f>IF(A139="","",IF(OR(U139&gt;1,AND(X139&lt;&gt;"",X139&lt;Inputs!$B$16),AND(X139&lt;&gt;"",X139&gt;Inputs!$B$17),G139&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A139="","",IF(OR(U139&gt;1,AND(X139&lt;&gt;"",X139&lt;Inputs!$B$16),AND(X139&lt;&gt;"",X139&gt;Inputs!$B$17),G139&lt;Inputs!$B$18,AH139="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB139" s="4" t="n"/>
+      <c r="AC139" s="7" t="n"/>
+      <c r="AD139" s="8">
+        <f>IF(A139="","",IF(AC139&lt;&gt;"",AC139,IF(E139="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE139" s="8">
+        <f>IF(OR(AD139="",F139="",G139=""),"",AD139+F139*G139)</f>
+        <v/>
+      </c>
+      <c r="AF139" s="8">
+        <f>IF(OR(E139="",A139=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG139" s="8">
+        <f>IF(OR(AD139="",AF139=""),"",AD139-AF139)</f>
+        <v/>
+      </c>
+      <c r="AH139" s="4">
+        <f>IF(A139="","",IF(E139="","TERMINAL",IF(AG139="","INFO",IF(ABS(AG139)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n"/>
@@ -17643,10 +20670,31 @@
         <v/>
       </c>
       <c r="AA140" s="4">
-        <f>IF(A140="","",IF(OR(U140&gt;1,AND(X140&lt;&gt;"",X140&lt;Inputs!$B$16),AND(X140&lt;&gt;"",X140&gt;Inputs!$B$17),G140&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A140="","",IF(OR(U140&gt;1,AND(X140&lt;&gt;"",X140&lt;Inputs!$B$16),AND(X140&lt;&gt;"",X140&gt;Inputs!$B$17),G140&lt;Inputs!$B$18,AH140="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB140" s="4" t="n"/>
+      <c r="AC140" s="7" t="n"/>
+      <c r="AD140" s="8">
+        <f>IF(A140="","",IF(AC140&lt;&gt;"",AC140,IF(E140="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE140" s="8">
+        <f>IF(OR(AD140="",F140="",G140=""),"",AD140+F140*G140)</f>
+        <v/>
+      </c>
+      <c r="AF140" s="8">
+        <f>IF(OR(E140="",A140=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG140" s="8">
+        <f>IF(OR(AD140="",AF140=""),"",AD140-AF140)</f>
+        <v/>
+      </c>
+      <c r="AH140" s="4">
+        <f>IF(A140="","",IF(E140="","TERMINAL",IF(AG140="","INFO",IF(ABS(AG140)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -17717,10 +20765,31 @@
         <v/>
       </c>
       <c r="AA141" s="4">
-        <f>IF(A141="","",IF(OR(U141&gt;1,AND(X141&lt;&gt;"",X141&lt;Inputs!$B$16),AND(X141&lt;&gt;"",X141&gt;Inputs!$B$17),G141&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A141="","",IF(OR(U141&gt;1,AND(X141&lt;&gt;"",X141&lt;Inputs!$B$16),AND(X141&lt;&gt;"",X141&gt;Inputs!$B$17),G141&lt;Inputs!$B$18,AH141="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB141" s="4" t="n"/>
+      <c r="AC141" s="7" t="n"/>
+      <c r="AD141" s="8">
+        <f>IF(A141="","",IF(AC141&lt;&gt;"",AC141,IF(E141="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE141" s="8">
+        <f>IF(OR(AD141="",F141="",G141=""),"",AD141+F141*G141)</f>
+        <v/>
+      </c>
+      <c r="AF141" s="8">
+        <f>IF(OR(E141="",A141=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG141" s="8">
+        <f>IF(OR(AD141="",AF141=""),"",AD141-AF141)</f>
+        <v/>
+      </c>
+      <c r="AH141" s="4">
+        <f>IF(A141="","",IF(E141="","TERMINAL",IF(AG141="","INFO",IF(ABS(AG141)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
@@ -17791,10 +20860,31 @@
         <v/>
       </c>
       <c r="AA142" s="4">
-        <f>IF(A142="","",IF(OR(U142&gt;1,AND(X142&lt;&gt;"",X142&lt;Inputs!$B$16),AND(X142&lt;&gt;"",X142&gt;Inputs!$B$17),G142&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A142="","",IF(OR(U142&gt;1,AND(X142&lt;&gt;"",X142&lt;Inputs!$B$16),AND(X142&lt;&gt;"",X142&gt;Inputs!$B$17),G142&lt;Inputs!$B$18,AH142="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB142" s="4" t="n"/>
+      <c r="AC142" s="7" t="n"/>
+      <c r="AD142" s="8">
+        <f>IF(A142="","",IF(AC142&lt;&gt;"",AC142,IF(E142="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE142" s="8">
+        <f>IF(OR(AD142="",F142="",G142=""),"",AD142+F142*G142)</f>
+        <v/>
+      </c>
+      <c r="AF142" s="8">
+        <f>IF(OR(E142="",A142=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG142" s="8">
+        <f>IF(OR(AD142="",AF142=""),"",AD142-AF142)</f>
+        <v/>
+      </c>
+      <c r="AH142" s="4">
+        <f>IF(A142="","",IF(E142="","TERMINAL",IF(AG142="","INFO",IF(ABS(AG142)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -17865,10 +20955,31 @@
         <v/>
       </c>
       <c r="AA143" s="4">
-        <f>IF(A143="","",IF(OR(U143&gt;1,AND(X143&lt;&gt;"",X143&lt;Inputs!$B$16),AND(X143&lt;&gt;"",X143&gt;Inputs!$B$17),G143&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A143="","",IF(OR(U143&gt;1,AND(X143&lt;&gt;"",X143&lt;Inputs!$B$16),AND(X143&lt;&gt;"",X143&gt;Inputs!$B$17),G143&lt;Inputs!$B$18,AH143="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB143" s="4" t="n"/>
+      <c r="AC143" s="7" t="n"/>
+      <c r="AD143" s="8">
+        <f>IF(A143="","",IF(AC143&lt;&gt;"",AC143,IF(E143="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE143" s="8">
+        <f>IF(OR(AD143="",F143="",G143=""),"",AD143+F143*G143)</f>
+        <v/>
+      </c>
+      <c r="AF143" s="8">
+        <f>IF(OR(E143="",A143=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG143" s="8">
+        <f>IF(OR(AD143="",AF143=""),"",AD143-AF143)</f>
+        <v/>
+      </c>
+      <c r="AH143" s="4">
+        <f>IF(A143="","",IF(E143="","TERMINAL",IF(AG143="","INFO",IF(ABS(AG143)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
@@ -17939,10 +21050,31 @@
         <v/>
       </c>
       <c r="AA144" s="4">
-        <f>IF(A144="","",IF(OR(U144&gt;1,AND(X144&lt;&gt;"",X144&lt;Inputs!$B$16),AND(X144&lt;&gt;"",X144&gt;Inputs!$B$17),G144&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A144="","",IF(OR(U144&gt;1,AND(X144&lt;&gt;"",X144&lt;Inputs!$B$16),AND(X144&lt;&gt;"",X144&gt;Inputs!$B$17),G144&lt;Inputs!$B$18,AH144="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB144" s="4" t="n"/>
+      <c r="AC144" s="7" t="n"/>
+      <c r="AD144" s="8">
+        <f>IF(A144="","",IF(AC144&lt;&gt;"",AC144,IF(E144="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE144" s="8">
+        <f>IF(OR(AD144="",F144="",G144=""),"",AD144+F144*G144)</f>
+        <v/>
+      </c>
+      <c r="AF144" s="8">
+        <f>IF(OR(E144="",A144=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG144" s="8">
+        <f>IF(OR(AD144="",AF144=""),"",AD144-AF144)</f>
+        <v/>
+      </c>
+      <c r="AH144" s="4">
+        <f>IF(A144="","",IF(E144="","TERMINAL",IF(AG144="","INFO",IF(ABS(AG144)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -18013,10 +21145,31 @@
         <v/>
       </c>
       <c r="AA145" s="4">
-        <f>IF(A145="","",IF(OR(U145&gt;1,AND(X145&lt;&gt;"",X145&lt;Inputs!$B$16),AND(X145&lt;&gt;"",X145&gt;Inputs!$B$17),G145&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A145="","",IF(OR(U145&gt;1,AND(X145&lt;&gt;"",X145&lt;Inputs!$B$16),AND(X145&lt;&gt;"",X145&gt;Inputs!$B$17),G145&lt;Inputs!$B$18,AH145="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB145" s="4" t="n"/>
+      <c r="AC145" s="7" t="n"/>
+      <c r="AD145" s="8">
+        <f>IF(A145="","",IF(AC145&lt;&gt;"",AC145,IF(E145="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE145" s="8">
+        <f>IF(OR(AD145="",F145="",G145=""),"",AD145+F145*G145)</f>
+        <v/>
+      </c>
+      <c r="AF145" s="8">
+        <f>IF(OR(E145="",A145=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG145" s="8">
+        <f>IF(OR(AD145="",AF145=""),"",AD145-AF145)</f>
+        <v/>
+      </c>
+      <c r="AH145" s="4">
+        <f>IF(A145="","",IF(E145="","TERMINAL",IF(AG145="","INFO",IF(ABS(AG145)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -18087,10 +21240,31 @@
         <v/>
       </c>
       <c r="AA146" s="4">
-        <f>IF(A146="","",IF(OR(U146&gt;1,AND(X146&lt;&gt;"",X146&lt;Inputs!$B$16),AND(X146&lt;&gt;"",X146&gt;Inputs!$B$17),G146&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A146="","",IF(OR(U146&gt;1,AND(X146&lt;&gt;"",X146&lt;Inputs!$B$16),AND(X146&lt;&gt;"",X146&gt;Inputs!$B$17),G146&lt;Inputs!$B$18,AH146="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB146" s="4" t="n"/>
+      <c r="AC146" s="7" t="n"/>
+      <c r="AD146" s="8">
+        <f>IF(A146="","",IF(AC146&lt;&gt;"",AC146,IF(E146="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE146" s="8">
+        <f>IF(OR(AD146="",F146="",G146=""),"",AD146+F146*G146)</f>
+        <v/>
+      </c>
+      <c r="AF146" s="8">
+        <f>IF(OR(E146="",A146=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG146" s="8">
+        <f>IF(OR(AD146="",AF146=""),"",AD146-AF146)</f>
+        <v/>
+      </c>
+      <c r="AH146" s="4">
+        <f>IF(A146="","",IF(E146="","TERMINAL",IF(AG146="","INFO",IF(ABS(AG146)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -18161,10 +21335,31 @@
         <v/>
       </c>
       <c r="AA147" s="4">
-        <f>IF(A147="","",IF(OR(U147&gt;1,AND(X147&lt;&gt;"",X147&lt;Inputs!$B$16),AND(X147&lt;&gt;"",X147&gt;Inputs!$B$17),G147&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A147="","",IF(OR(U147&gt;1,AND(X147&lt;&gt;"",X147&lt;Inputs!$B$16),AND(X147&lt;&gt;"",X147&gt;Inputs!$B$17),G147&lt;Inputs!$B$18,AH147="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB147" s="4" t="n"/>
+      <c r="AC147" s="7" t="n"/>
+      <c r="AD147" s="8">
+        <f>IF(A147="","",IF(AC147&lt;&gt;"",AC147,IF(E147="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE147" s="8">
+        <f>IF(OR(AD147="",F147="",G147=""),"",AD147+F147*G147)</f>
+        <v/>
+      </c>
+      <c r="AF147" s="8">
+        <f>IF(OR(E147="",A147=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG147" s="8">
+        <f>IF(OR(AD147="",AF147=""),"",AD147-AF147)</f>
+        <v/>
+      </c>
+      <c r="AH147" s="4">
+        <f>IF(A147="","",IF(E147="","TERMINAL",IF(AG147="","INFO",IF(ABS(AG147)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n"/>
@@ -18235,10 +21430,31 @@
         <v/>
       </c>
       <c r="AA148" s="4">
-        <f>IF(A148="","",IF(OR(U148&gt;1,AND(X148&lt;&gt;"",X148&lt;Inputs!$B$16),AND(X148&lt;&gt;"",X148&gt;Inputs!$B$17),G148&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A148="","",IF(OR(U148&gt;1,AND(X148&lt;&gt;"",X148&lt;Inputs!$B$16),AND(X148&lt;&gt;"",X148&gt;Inputs!$B$17),G148&lt;Inputs!$B$18,AH148="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB148" s="4" t="n"/>
+      <c r="AC148" s="7" t="n"/>
+      <c r="AD148" s="8">
+        <f>IF(A148="","",IF(AC148&lt;&gt;"",AC148,IF(E148="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE148" s="8">
+        <f>IF(OR(AD148="",F148="",G148=""),"",AD148+F148*G148)</f>
+        <v/>
+      </c>
+      <c r="AF148" s="8">
+        <f>IF(OR(E148="",A148=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG148" s="8">
+        <f>IF(OR(AD148="",AF148=""),"",AD148-AF148)</f>
+        <v/>
+      </c>
+      <c r="AH148" s="4">
+        <f>IF(A148="","",IF(E148="","TERMINAL",IF(AG148="","INFO",IF(ABS(AG148)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -18309,10 +21525,31 @@
         <v/>
       </c>
       <c r="AA149" s="4">
-        <f>IF(A149="","",IF(OR(U149&gt;1,AND(X149&lt;&gt;"",X149&lt;Inputs!$B$16),AND(X149&lt;&gt;"",X149&gt;Inputs!$B$17),G149&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A149="","",IF(OR(U149&gt;1,AND(X149&lt;&gt;"",X149&lt;Inputs!$B$16),AND(X149&lt;&gt;"",X149&gt;Inputs!$B$17),G149&lt;Inputs!$B$18,AH149="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB149" s="4" t="n"/>
+      <c r="AC149" s="7" t="n"/>
+      <c r="AD149" s="8">
+        <f>IF(A149="","",IF(AC149&lt;&gt;"",AC149,IF(E149="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE149" s="8">
+        <f>IF(OR(AD149="",F149="",G149=""),"",AD149+F149*G149)</f>
+        <v/>
+      </c>
+      <c r="AF149" s="8">
+        <f>IF(OR(E149="",A149=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG149" s="8">
+        <f>IF(OR(AD149="",AF149=""),"",AD149-AF149)</f>
+        <v/>
+      </c>
+      <c r="AH149" s="4">
+        <f>IF(A149="","",IF(E149="","TERMINAL",IF(AG149="","INFO",IF(ABS(AG149)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n"/>
@@ -18383,10 +21620,31 @@
         <v/>
       </c>
       <c r="AA150" s="4">
-        <f>IF(A150="","",IF(OR(U150&gt;1,AND(X150&lt;&gt;"",X150&lt;Inputs!$B$16),AND(X150&lt;&gt;"",X150&gt;Inputs!$B$17),G150&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A150="","",IF(OR(U150&gt;1,AND(X150&lt;&gt;"",X150&lt;Inputs!$B$16),AND(X150&lt;&gt;"",X150&gt;Inputs!$B$17),G150&lt;Inputs!$B$18,AH150="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB150" s="4" t="n"/>
+      <c r="AC150" s="7" t="n"/>
+      <c r="AD150" s="8">
+        <f>IF(A150="","",IF(AC150&lt;&gt;"",AC150,IF(E150="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE150" s="8">
+        <f>IF(OR(AD150="",F150="",G150=""),"",AD150+F150*G150)</f>
+        <v/>
+      </c>
+      <c r="AF150" s="8">
+        <f>IF(OR(E150="",A150=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG150" s="8">
+        <f>IF(OR(AD150="",AF150=""),"",AD150-AF150)</f>
+        <v/>
+      </c>
+      <c r="AH150" s="4">
+        <f>IF(A150="","",IF(E150="","TERMINAL",IF(AG150="","INFO",IF(ABS(AG150)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -18457,10 +21715,31 @@
         <v/>
       </c>
       <c r="AA151" s="4">
-        <f>IF(A151="","",IF(OR(U151&gt;1,AND(X151&lt;&gt;"",X151&lt;Inputs!$B$16),AND(X151&lt;&gt;"",X151&gt;Inputs!$B$17),G151&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A151="","",IF(OR(U151&gt;1,AND(X151&lt;&gt;"",X151&lt;Inputs!$B$16),AND(X151&lt;&gt;"",X151&gt;Inputs!$B$17),G151&lt;Inputs!$B$18,AH151="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB151" s="4" t="n"/>
+      <c r="AC151" s="7" t="n"/>
+      <c r="AD151" s="8">
+        <f>IF(A151="","",IF(AC151&lt;&gt;"",AC151,IF(E151="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE151" s="8">
+        <f>IF(OR(AD151="",F151="",G151=""),"",AD151+F151*G151)</f>
+        <v/>
+      </c>
+      <c r="AF151" s="8">
+        <f>IF(OR(E151="",A151=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG151" s="8">
+        <f>IF(OR(AD151="",AF151=""),"",AD151-AF151)</f>
+        <v/>
+      </c>
+      <c r="AH151" s="4">
+        <f>IF(A151="","",IF(E151="","TERMINAL",IF(AG151="","INFO",IF(ABS(AG151)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -18531,10 +21810,31 @@
         <v/>
       </c>
       <c r="AA152" s="4">
-        <f>IF(A152="","",IF(OR(U152&gt;1,AND(X152&lt;&gt;"",X152&lt;Inputs!$B$16),AND(X152&lt;&gt;"",X152&gt;Inputs!$B$17),G152&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A152="","",IF(OR(U152&gt;1,AND(X152&lt;&gt;"",X152&lt;Inputs!$B$16),AND(X152&lt;&gt;"",X152&gt;Inputs!$B$17),G152&lt;Inputs!$B$18,AH152="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB152" s="4" t="n"/>
+      <c r="AC152" s="7" t="n"/>
+      <c r="AD152" s="8">
+        <f>IF(A152="","",IF(AC152&lt;&gt;"",AC152,IF(E152="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE152" s="8">
+        <f>IF(OR(AD152="",F152="",G152=""),"",AD152+F152*G152)</f>
+        <v/>
+      </c>
+      <c r="AF152" s="8">
+        <f>IF(OR(E152="",A152=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG152" s="8">
+        <f>IF(OR(AD152="",AF152=""),"",AD152-AF152)</f>
+        <v/>
+      </c>
+      <c r="AH152" s="4">
+        <f>IF(A152="","",IF(E152="","TERMINAL",IF(AG152="","INFO",IF(ABS(AG152)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -18605,10 +21905,31 @@
         <v/>
       </c>
       <c r="AA153" s="4">
-        <f>IF(A153="","",IF(OR(U153&gt;1,AND(X153&lt;&gt;"",X153&lt;Inputs!$B$16),AND(X153&lt;&gt;"",X153&gt;Inputs!$B$17),G153&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A153="","",IF(OR(U153&gt;1,AND(X153&lt;&gt;"",X153&lt;Inputs!$B$16),AND(X153&lt;&gt;"",X153&gt;Inputs!$B$17),G153&lt;Inputs!$B$18,AH153="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB153" s="4" t="n"/>
+      <c r="AC153" s="7" t="n"/>
+      <c r="AD153" s="8">
+        <f>IF(A153="","",IF(AC153&lt;&gt;"",AC153,IF(E153="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE153" s="8">
+        <f>IF(OR(AD153="",F153="",G153=""),"",AD153+F153*G153)</f>
+        <v/>
+      </c>
+      <c r="AF153" s="8">
+        <f>IF(OR(E153="",A153=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG153" s="8">
+        <f>IF(OR(AD153="",AF153=""),"",AD153-AF153)</f>
+        <v/>
+      </c>
+      <c r="AH153" s="4">
+        <f>IF(A153="","",IF(E153="","TERMINAL",IF(AG153="","INFO",IF(ABS(AG153)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
@@ -18679,10 +22000,31 @@
         <v/>
       </c>
       <c r="AA154" s="4">
-        <f>IF(A154="","",IF(OR(U154&gt;1,AND(X154&lt;&gt;"",X154&lt;Inputs!$B$16),AND(X154&lt;&gt;"",X154&gt;Inputs!$B$17),G154&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A154="","",IF(OR(U154&gt;1,AND(X154&lt;&gt;"",X154&lt;Inputs!$B$16),AND(X154&lt;&gt;"",X154&gt;Inputs!$B$17),G154&lt;Inputs!$B$18,AH154="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB154" s="4" t="n"/>
+      <c r="AC154" s="7" t="n"/>
+      <c r="AD154" s="8">
+        <f>IF(A154="","",IF(AC154&lt;&gt;"",AC154,IF(E154="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE154" s="8">
+        <f>IF(OR(AD154="",F154="",G154=""),"",AD154+F154*G154)</f>
+        <v/>
+      </c>
+      <c r="AF154" s="8">
+        <f>IF(OR(E154="",A154=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG154" s="8">
+        <f>IF(OR(AD154="",AF154=""),"",AD154-AF154)</f>
+        <v/>
+      </c>
+      <c r="AH154" s="4">
+        <f>IF(A154="","",IF(E154="","TERMINAL",IF(AG154="","INFO",IF(ABS(AG154)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -18753,10 +22095,31 @@
         <v/>
       </c>
       <c r="AA155" s="4">
-        <f>IF(A155="","",IF(OR(U155&gt;1,AND(X155&lt;&gt;"",X155&lt;Inputs!$B$16),AND(X155&lt;&gt;"",X155&gt;Inputs!$B$17),G155&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A155="","",IF(OR(U155&gt;1,AND(X155&lt;&gt;"",X155&lt;Inputs!$B$16),AND(X155&lt;&gt;"",X155&gt;Inputs!$B$17),G155&lt;Inputs!$B$18,AH155="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB155" s="4" t="n"/>
+      <c r="AC155" s="7" t="n"/>
+      <c r="AD155" s="8">
+        <f>IF(A155="","",IF(AC155&lt;&gt;"",AC155,IF(E155="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE155" s="8">
+        <f>IF(OR(AD155="",F155="",G155=""),"",AD155+F155*G155)</f>
+        <v/>
+      </c>
+      <c r="AF155" s="8">
+        <f>IF(OR(E155="",A155=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG155" s="8">
+        <f>IF(OR(AD155="",AF155=""),"",AD155-AF155)</f>
+        <v/>
+      </c>
+      <c r="AH155" s="4">
+        <f>IF(A155="","",IF(E155="","TERMINAL",IF(AG155="","INFO",IF(ABS(AG155)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -18827,10 +22190,31 @@
         <v/>
       </c>
       <c r="AA156" s="4">
-        <f>IF(A156="","",IF(OR(U156&gt;1,AND(X156&lt;&gt;"",X156&lt;Inputs!$B$16),AND(X156&lt;&gt;"",X156&gt;Inputs!$B$17),G156&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A156="","",IF(OR(U156&gt;1,AND(X156&lt;&gt;"",X156&lt;Inputs!$B$16),AND(X156&lt;&gt;"",X156&gt;Inputs!$B$17),G156&lt;Inputs!$B$18,AH156="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB156" s="4" t="n"/>
+      <c r="AC156" s="7" t="n"/>
+      <c r="AD156" s="8">
+        <f>IF(A156="","",IF(AC156&lt;&gt;"",AC156,IF(E156="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE156" s="8">
+        <f>IF(OR(AD156="",F156="",G156=""),"",AD156+F156*G156)</f>
+        <v/>
+      </c>
+      <c r="AF156" s="8">
+        <f>IF(OR(E156="",A156=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG156" s="8">
+        <f>IF(OR(AD156="",AF156=""),"",AD156-AF156)</f>
+        <v/>
+      </c>
+      <c r="AH156" s="4">
+        <f>IF(A156="","",IF(E156="","TERMINAL",IF(AG156="","INFO",IF(ABS(AG156)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -18901,10 +22285,31 @@
         <v/>
       </c>
       <c r="AA157" s="4">
-        <f>IF(A157="","",IF(OR(U157&gt;1,AND(X157&lt;&gt;"",X157&lt;Inputs!$B$16),AND(X157&lt;&gt;"",X157&gt;Inputs!$B$17),G157&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A157="","",IF(OR(U157&gt;1,AND(X157&lt;&gt;"",X157&lt;Inputs!$B$16),AND(X157&lt;&gt;"",X157&gt;Inputs!$B$17),G157&lt;Inputs!$B$18,AH157="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB157" s="4" t="n"/>
+      <c r="AC157" s="7" t="n"/>
+      <c r="AD157" s="8">
+        <f>IF(A157="","",IF(AC157&lt;&gt;"",AC157,IF(E157="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE157" s="8">
+        <f>IF(OR(AD157="",F157="",G157=""),"",AD157+F157*G157)</f>
+        <v/>
+      </c>
+      <c r="AF157" s="8">
+        <f>IF(OR(E157="",A157=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG157" s="8">
+        <f>IF(OR(AD157="",AF157=""),"",AD157-AF157)</f>
+        <v/>
+      </c>
+      <c r="AH157" s="4">
+        <f>IF(A157="","",IF(E157="","TERMINAL",IF(AG157="","INFO",IF(ABS(AG157)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -18975,10 +22380,31 @@
         <v/>
       </c>
       <c r="AA158" s="4">
-        <f>IF(A158="","",IF(OR(U158&gt;1,AND(X158&lt;&gt;"",X158&lt;Inputs!$B$16),AND(X158&lt;&gt;"",X158&gt;Inputs!$B$17),G158&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A158="","",IF(OR(U158&gt;1,AND(X158&lt;&gt;"",X158&lt;Inputs!$B$16),AND(X158&lt;&gt;"",X158&gt;Inputs!$B$17),G158&lt;Inputs!$B$18,AH158="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB158" s="4" t="n"/>
+      <c r="AC158" s="7" t="n"/>
+      <c r="AD158" s="8">
+        <f>IF(A158="","",IF(AC158&lt;&gt;"",AC158,IF(E158="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE158" s="8">
+        <f>IF(OR(AD158="",F158="",G158=""),"",AD158+F158*G158)</f>
+        <v/>
+      </c>
+      <c r="AF158" s="8">
+        <f>IF(OR(E158="",A158=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG158" s="8">
+        <f>IF(OR(AD158="",AF158=""),"",AD158-AF158)</f>
+        <v/>
+      </c>
+      <c r="AH158" s="4">
+        <f>IF(A158="","",IF(E158="","TERMINAL",IF(AG158="","INFO",IF(ABS(AG158)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -19049,10 +22475,31 @@
         <v/>
       </c>
       <c r="AA159" s="4">
-        <f>IF(A159="","",IF(OR(U159&gt;1,AND(X159&lt;&gt;"",X159&lt;Inputs!$B$16),AND(X159&lt;&gt;"",X159&gt;Inputs!$B$17),G159&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A159="","",IF(OR(U159&gt;1,AND(X159&lt;&gt;"",X159&lt;Inputs!$B$16),AND(X159&lt;&gt;"",X159&gt;Inputs!$B$17),G159&lt;Inputs!$B$18,AH159="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB159" s="4" t="n"/>
+      <c r="AC159" s="7" t="n"/>
+      <c r="AD159" s="8">
+        <f>IF(A159="","",IF(AC159&lt;&gt;"",AC159,IF(E159="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE159" s="8">
+        <f>IF(OR(AD159="",F159="",G159=""),"",AD159+F159*G159)</f>
+        <v/>
+      </c>
+      <c r="AF159" s="8">
+        <f>IF(OR(E159="",A159=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG159" s="8">
+        <f>IF(OR(AD159="",AF159=""),"",AD159-AF159)</f>
+        <v/>
+      </c>
+      <c r="AH159" s="4">
+        <f>IF(A159="","",IF(E159="","TERMINAL",IF(AG159="","INFO",IF(ABS(AG159)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
@@ -19123,10 +22570,31 @@
         <v/>
       </c>
       <c r="AA160" s="4">
-        <f>IF(A160="","",IF(OR(U160&gt;1,AND(X160&lt;&gt;"",X160&lt;Inputs!$B$16),AND(X160&lt;&gt;"",X160&gt;Inputs!$B$17),G160&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A160="","",IF(OR(U160&gt;1,AND(X160&lt;&gt;"",X160&lt;Inputs!$B$16),AND(X160&lt;&gt;"",X160&gt;Inputs!$B$17),G160&lt;Inputs!$B$18,AH160="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB160" s="4" t="n"/>
+      <c r="AC160" s="7" t="n"/>
+      <c r="AD160" s="8">
+        <f>IF(A160="","",IF(AC160&lt;&gt;"",AC160,IF(E160="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE160" s="8">
+        <f>IF(OR(AD160="",F160="",G160=""),"",AD160+F160*G160)</f>
+        <v/>
+      </c>
+      <c r="AF160" s="8">
+        <f>IF(OR(E160="",A160=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG160" s="8">
+        <f>IF(OR(AD160="",AF160=""),"",AD160-AF160)</f>
+        <v/>
+      </c>
+      <c r="AH160" s="4">
+        <f>IF(A160="","",IF(E160="","TERMINAL",IF(AG160="","INFO",IF(ABS(AG160)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -19197,10 +22665,31 @@
         <v/>
       </c>
       <c r="AA161" s="4">
-        <f>IF(A161="","",IF(OR(U161&gt;1,AND(X161&lt;&gt;"",X161&lt;Inputs!$B$16),AND(X161&lt;&gt;"",X161&gt;Inputs!$B$17),G161&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A161="","",IF(OR(U161&gt;1,AND(X161&lt;&gt;"",X161&lt;Inputs!$B$16),AND(X161&lt;&gt;"",X161&gt;Inputs!$B$17),G161&lt;Inputs!$B$18,AH161="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB161" s="4" t="n"/>
+      <c r="AC161" s="7" t="n"/>
+      <c r="AD161" s="8">
+        <f>IF(A161="","",IF(AC161&lt;&gt;"",AC161,IF(E161="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE161" s="8">
+        <f>IF(OR(AD161="",F161="",G161=""),"",AD161+F161*G161)</f>
+        <v/>
+      </c>
+      <c r="AF161" s="8">
+        <f>IF(OR(E161="",A161=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG161" s="8">
+        <f>IF(OR(AD161="",AF161=""),"",AD161-AF161)</f>
+        <v/>
+      </c>
+      <c r="AH161" s="4">
+        <f>IF(A161="","",IF(E161="","TERMINAL",IF(AG161="","INFO",IF(ABS(AG161)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -19271,10 +22760,31 @@
         <v/>
       </c>
       <c r="AA162" s="4">
-        <f>IF(A162="","",IF(OR(U162&gt;1,AND(X162&lt;&gt;"",X162&lt;Inputs!$B$16),AND(X162&lt;&gt;"",X162&gt;Inputs!$B$17),G162&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A162="","",IF(OR(U162&gt;1,AND(X162&lt;&gt;"",X162&lt;Inputs!$B$16),AND(X162&lt;&gt;"",X162&gt;Inputs!$B$17),G162&lt;Inputs!$B$18,AH162="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB162" s="4" t="n"/>
+      <c r="AC162" s="7" t="n"/>
+      <c r="AD162" s="8">
+        <f>IF(A162="","",IF(AC162&lt;&gt;"",AC162,IF(E162="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE162" s="8">
+        <f>IF(OR(AD162="",F162="",G162=""),"",AD162+F162*G162)</f>
+        <v/>
+      </c>
+      <c r="AF162" s="8">
+        <f>IF(OR(E162="",A162=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG162" s="8">
+        <f>IF(OR(AD162="",AF162=""),"",AD162-AF162)</f>
+        <v/>
+      </c>
+      <c r="AH162" s="4">
+        <f>IF(A162="","",IF(E162="","TERMINAL",IF(AG162="","INFO",IF(ABS(AG162)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -19345,10 +22855,31 @@
         <v/>
       </c>
       <c r="AA163" s="4">
-        <f>IF(A163="","",IF(OR(U163&gt;1,AND(X163&lt;&gt;"",X163&lt;Inputs!$B$16),AND(X163&lt;&gt;"",X163&gt;Inputs!$B$17),G163&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A163="","",IF(OR(U163&gt;1,AND(X163&lt;&gt;"",X163&lt;Inputs!$B$16),AND(X163&lt;&gt;"",X163&gt;Inputs!$B$17),G163&lt;Inputs!$B$18,AH163="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB163" s="4" t="n"/>
+      <c r="AC163" s="7" t="n"/>
+      <c r="AD163" s="8">
+        <f>IF(A163="","",IF(AC163&lt;&gt;"",AC163,IF(E163="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE163" s="8">
+        <f>IF(OR(AD163="",F163="",G163=""),"",AD163+F163*G163)</f>
+        <v/>
+      </c>
+      <c r="AF163" s="8">
+        <f>IF(OR(E163="",A163=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG163" s="8">
+        <f>IF(OR(AD163="",AF163=""),"",AD163-AF163)</f>
+        <v/>
+      </c>
+      <c r="AH163" s="4">
+        <f>IF(A163="","",IF(E163="","TERMINAL",IF(AG163="","INFO",IF(ABS(AG163)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -19419,10 +22950,31 @@
         <v/>
       </c>
       <c r="AA164" s="4">
-        <f>IF(A164="","",IF(OR(U164&gt;1,AND(X164&lt;&gt;"",X164&lt;Inputs!$B$16),AND(X164&lt;&gt;"",X164&gt;Inputs!$B$17),G164&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A164="","",IF(OR(U164&gt;1,AND(X164&lt;&gt;"",X164&lt;Inputs!$B$16),AND(X164&lt;&gt;"",X164&gt;Inputs!$B$17),G164&lt;Inputs!$B$18,AH164="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB164" s="4" t="n"/>
+      <c r="AC164" s="7" t="n"/>
+      <c r="AD164" s="8">
+        <f>IF(A164="","",IF(AC164&lt;&gt;"",AC164,IF(E164="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE164" s="8">
+        <f>IF(OR(AD164="",F164="",G164=""),"",AD164+F164*G164)</f>
+        <v/>
+      </c>
+      <c r="AF164" s="8">
+        <f>IF(OR(E164="",A164=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG164" s="8">
+        <f>IF(OR(AD164="",AF164=""),"",AD164-AF164)</f>
+        <v/>
+      </c>
+      <c r="AH164" s="4">
+        <f>IF(A164="","",IF(E164="","TERMINAL",IF(AG164="","INFO",IF(ABS(AG164)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -19493,10 +23045,31 @@
         <v/>
       </c>
       <c r="AA165" s="4">
-        <f>IF(A165="","",IF(OR(U165&gt;1,AND(X165&lt;&gt;"",X165&lt;Inputs!$B$16),AND(X165&lt;&gt;"",X165&gt;Inputs!$B$17),G165&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A165="","",IF(OR(U165&gt;1,AND(X165&lt;&gt;"",X165&lt;Inputs!$B$16),AND(X165&lt;&gt;"",X165&gt;Inputs!$B$17),G165&lt;Inputs!$B$18,AH165="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB165" s="4" t="n"/>
+      <c r="AC165" s="7" t="n"/>
+      <c r="AD165" s="8">
+        <f>IF(A165="","",IF(AC165&lt;&gt;"",AC165,IF(E165="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE165" s="8">
+        <f>IF(OR(AD165="",F165="",G165=""),"",AD165+F165*G165)</f>
+        <v/>
+      </c>
+      <c r="AF165" s="8">
+        <f>IF(OR(E165="",A165=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG165" s="8">
+        <f>IF(OR(AD165="",AF165=""),"",AD165-AF165)</f>
+        <v/>
+      </c>
+      <c r="AH165" s="4">
+        <f>IF(A165="","",IF(E165="","TERMINAL",IF(AG165="","INFO",IF(ABS(AG165)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -19567,10 +23140,31 @@
         <v/>
       </c>
       <c r="AA166" s="4">
-        <f>IF(A166="","",IF(OR(U166&gt;1,AND(X166&lt;&gt;"",X166&lt;Inputs!$B$16),AND(X166&lt;&gt;"",X166&gt;Inputs!$B$17),G166&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A166="","",IF(OR(U166&gt;1,AND(X166&lt;&gt;"",X166&lt;Inputs!$B$16),AND(X166&lt;&gt;"",X166&gt;Inputs!$B$17),G166&lt;Inputs!$B$18,AH166="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB166" s="4" t="n"/>
+      <c r="AC166" s="7" t="n"/>
+      <c r="AD166" s="8">
+        <f>IF(A166="","",IF(AC166&lt;&gt;"",AC166,IF(E166="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE166" s="8">
+        <f>IF(OR(AD166="",F166="",G166=""),"",AD166+F166*G166)</f>
+        <v/>
+      </c>
+      <c r="AF166" s="8">
+        <f>IF(OR(E166="",A166=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG166" s="8">
+        <f>IF(OR(AD166="",AF166=""),"",AD166-AF166)</f>
+        <v/>
+      </c>
+      <c r="AH166" s="4">
+        <f>IF(A166="","",IF(E166="","TERMINAL",IF(AG166="","INFO",IF(ABS(AG166)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -19641,10 +23235,31 @@
         <v/>
       </c>
       <c r="AA167" s="4">
-        <f>IF(A167="","",IF(OR(U167&gt;1,AND(X167&lt;&gt;"",X167&lt;Inputs!$B$16),AND(X167&lt;&gt;"",X167&gt;Inputs!$B$17),G167&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A167="","",IF(OR(U167&gt;1,AND(X167&lt;&gt;"",X167&lt;Inputs!$B$16),AND(X167&lt;&gt;"",X167&gt;Inputs!$B$17),G167&lt;Inputs!$B$18,AH167="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB167" s="4" t="n"/>
+      <c r="AC167" s="7" t="n"/>
+      <c r="AD167" s="8">
+        <f>IF(A167="","",IF(AC167&lt;&gt;"",AC167,IF(E167="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE167" s="8">
+        <f>IF(OR(AD167="",F167="",G167=""),"",AD167+F167*G167)</f>
+        <v/>
+      </c>
+      <c r="AF167" s="8">
+        <f>IF(OR(E167="",A167=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG167" s="8">
+        <f>IF(OR(AD167="",AF167=""),"",AD167-AF167)</f>
+        <v/>
+      </c>
+      <c r="AH167" s="4">
+        <f>IF(A167="","",IF(E167="","TERMINAL",IF(AG167="","INFO",IF(ABS(AG167)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
@@ -19715,10 +23330,31 @@
         <v/>
       </c>
       <c r="AA168" s="4">
-        <f>IF(A168="","",IF(OR(U168&gt;1,AND(X168&lt;&gt;"",X168&lt;Inputs!$B$16),AND(X168&lt;&gt;"",X168&gt;Inputs!$B$17),G168&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A168="","",IF(OR(U168&gt;1,AND(X168&lt;&gt;"",X168&lt;Inputs!$B$16),AND(X168&lt;&gt;"",X168&gt;Inputs!$B$17),G168&lt;Inputs!$B$18,AH168="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB168" s="4" t="n"/>
+      <c r="AC168" s="7" t="n"/>
+      <c r="AD168" s="8">
+        <f>IF(A168="","",IF(AC168&lt;&gt;"",AC168,IF(E168="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE168" s="8">
+        <f>IF(OR(AD168="",F168="",G168=""),"",AD168+F168*G168)</f>
+        <v/>
+      </c>
+      <c r="AF168" s="8">
+        <f>IF(OR(E168="",A168=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG168" s="8">
+        <f>IF(OR(AD168="",AF168=""),"",AD168-AF168)</f>
+        <v/>
+      </c>
+      <c r="AH168" s="4">
+        <f>IF(A168="","",IF(E168="","TERMINAL",IF(AG168="","INFO",IF(ABS(AG168)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -19789,10 +23425,31 @@
         <v/>
       </c>
       <c r="AA169" s="4">
-        <f>IF(A169="","",IF(OR(U169&gt;1,AND(X169&lt;&gt;"",X169&lt;Inputs!$B$16),AND(X169&lt;&gt;"",X169&gt;Inputs!$B$17),G169&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A169="","",IF(OR(U169&gt;1,AND(X169&lt;&gt;"",X169&lt;Inputs!$B$16),AND(X169&lt;&gt;"",X169&gt;Inputs!$B$17),G169&lt;Inputs!$B$18,AH169="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB169" s="4" t="n"/>
+      <c r="AC169" s="7" t="n"/>
+      <c r="AD169" s="8">
+        <f>IF(A169="","",IF(AC169&lt;&gt;"",AC169,IF(E169="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE169" s="8">
+        <f>IF(OR(AD169="",F169="",G169=""),"",AD169+F169*G169)</f>
+        <v/>
+      </c>
+      <c r="AF169" s="8">
+        <f>IF(OR(E169="",A169=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG169" s="8">
+        <f>IF(OR(AD169="",AF169=""),"",AD169-AF169)</f>
+        <v/>
+      </c>
+      <c r="AH169" s="4">
+        <f>IF(A169="","",IF(E169="","TERMINAL",IF(AG169="","INFO",IF(ABS(AG169)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -19863,10 +23520,31 @@
         <v/>
       </c>
       <c r="AA170" s="4">
-        <f>IF(A170="","",IF(OR(U170&gt;1,AND(X170&lt;&gt;"",X170&lt;Inputs!$B$16),AND(X170&lt;&gt;"",X170&gt;Inputs!$B$17),G170&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A170="","",IF(OR(U170&gt;1,AND(X170&lt;&gt;"",X170&lt;Inputs!$B$16),AND(X170&lt;&gt;"",X170&gt;Inputs!$B$17),G170&lt;Inputs!$B$18,AH170="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB170" s="4" t="n"/>
+      <c r="AC170" s="7" t="n"/>
+      <c r="AD170" s="8">
+        <f>IF(A170="","",IF(AC170&lt;&gt;"",AC170,IF(E170="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE170" s="8">
+        <f>IF(OR(AD170="",F170="",G170=""),"",AD170+F170*G170)</f>
+        <v/>
+      </c>
+      <c r="AF170" s="8">
+        <f>IF(OR(E170="",A170=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG170" s="8">
+        <f>IF(OR(AD170="",AF170=""),"",AD170-AF170)</f>
+        <v/>
+      </c>
+      <c r="AH170" s="4">
+        <f>IF(A170="","",IF(E170="","TERMINAL",IF(AG170="","INFO",IF(ABS(AG170)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -19937,10 +23615,31 @@
         <v/>
       </c>
       <c r="AA171" s="4">
-        <f>IF(A171="","",IF(OR(U171&gt;1,AND(X171&lt;&gt;"",X171&lt;Inputs!$B$16),AND(X171&lt;&gt;"",X171&gt;Inputs!$B$17),G171&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A171="","",IF(OR(U171&gt;1,AND(X171&lt;&gt;"",X171&lt;Inputs!$B$16),AND(X171&lt;&gt;"",X171&gt;Inputs!$B$17),G171&lt;Inputs!$B$18,AH171="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB171" s="4" t="n"/>
+      <c r="AC171" s="7" t="n"/>
+      <c r="AD171" s="8">
+        <f>IF(A171="","",IF(AC171&lt;&gt;"",AC171,IF(E171="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE171" s="8">
+        <f>IF(OR(AD171="",F171="",G171=""),"",AD171+F171*G171)</f>
+        <v/>
+      </c>
+      <c r="AF171" s="8">
+        <f>IF(OR(E171="",A171=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG171" s="8">
+        <f>IF(OR(AD171="",AF171=""),"",AD171-AF171)</f>
+        <v/>
+      </c>
+      <c r="AH171" s="4">
+        <f>IF(A171="","",IF(E171="","TERMINAL",IF(AG171="","INFO",IF(ABS(AG171)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -20011,10 +23710,31 @@
         <v/>
       </c>
       <c r="AA172" s="4">
-        <f>IF(A172="","",IF(OR(U172&gt;1,AND(X172&lt;&gt;"",X172&lt;Inputs!$B$16),AND(X172&lt;&gt;"",X172&gt;Inputs!$B$17),G172&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A172="","",IF(OR(U172&gt;1,AND(X172&lt;&gt;"",X172&lt;Inputs!$B$16),AND(X172&lt;&gt;"",X172&gt;Inputs!$B$17),G172&lt;Inputs!$B$18,AH172="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB172" s="4" t="n"/>
+      <c r="AC172" s="7" t="n"/>
+      <c r="AD172" s="8">
+        <f>IF(A172="","",IF(AC172&lt;&gt;"",AC172,IF(E172="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE172" s="8">
+        <f>IF(OR(AD172="",F172="",G172=""),"",AD172+F172*G172)</f>
+        <v/>
+      </c>
+      <c r="AF172" s="8">
+        <f>IF(OR(E172="",A172=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG172" s="8">
+        <f>IF(OR(AD172="",AF172=""),"",AD172-AF172)</f>
+        <v/>
+      </c>
+      <c r="AH172" s="4">
+        <f>IF(A172="","",IF(E172="","TERMINAL",IF(AG172="","INFO",IF(ABS(AG172)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -20085,10 +23805,31 @@
         <v/>
       </c>
       <c r="AA173" s="4">
-        <f>IF(A173="","",IF(OR(U173&gt;1,AND(X173&lt;&gt;"",X173&lt;Inputs!$B$16),AND(X173&lt;&gt;"",X173&gt;Inputs!$B$17),G173&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A173="","",IF(OR(U173&gt;1,AND(X173&lt;&gt;"",X173&lt;Inputs!$B$16),AND(X173&lt;&gt;"",X173&gt;Inputs!$B$17),G173&lt;Inputs!$B$18,AH173="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB173" s="4" t="n"/>
+      <c r="AC173" s="7" t="n"/>
+      <c r="AD173" s="8">
+        <f>IF(A173="","",IF(AC173&lt;&gt;"",AC173,IF(E173="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE173" s="8">
+        <f>IF(OR(AD173="",F173="",G173=""),"",AD173+F173*G173)</f>
+        <v/>
+      </c>
+      <c r="AF173" s="8">
+        <f>IF(OR(E173="",A173=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG173" s="8">
+        <f>IF(OR(AD173="",AF173=""),"",AD173-AF173)</f>
+        <v/>
+      </c>
+      <c r="AH173" s="4">
+        <f>IF(A173="","",IF(E173="","TERMINAL",IF(AG173="","INFO",IF(ABS(AG173)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
@@ -20159,10 +23900,31 @@
         <v/>
       </c>
       <c r="AA174" s="4">
-        <f>IF(A174="","",IF(OR(U174&gt;1,AND(X174&lt;&gt;"",X174&lt;Inputs!$B$16),AND(X174&lt;&gt;"",X174&gt;Inputs!$B$17),G174&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A174="","",IF(OR(U174&gt;1,AND(X174&lt;&gt;"",X174&lt;Inputs!$B$16),AND(X174&lt;&gt;"",X174&gt;Inputs!$B$17),G174&lt;Inputs!$B$18,AH174="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB174" s="4" t="n"/>
+      <c r="AC174" s="7" t="n"/>
+      <c r="AD174" s="8">
+        <f>IF(A174="","",IF(AC174&lt;&gt;"",AC174,IF(E174="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE174" s="8">
+        <f>IF(OR(AD174="",F174="",G174=""),"",AD174+F174*G174)</f>
+        <v/>
+      </c>
+      <c r="AF174" s="8">
+        <f>IF(OR(E174="",A174=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG174" s="8">
+        <f>IF(OR(AD174="",AF174=""),"",AD174-AF174)</f>
+        <v/>
+      </c>
+      <c r="AH174" s="4">
+        <f>IF(A174="","",IF(E174="","TERMINAL",IF(AG174="","INFO",IF(ABS(AG174)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -20233,10 +23995,31 @@
         <v/>
       </c>
       <c r="AA175" s="4">
-        <f>IF(A175="","",IF(OR(U175&gt;1,AND(X175&lt;&gt;"",X175&lt;Inputs!$B$16),AND(X175&lt;&gt;"",X175&gt;Inputs!$B$17),G175&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A175="","",IF(OR(U175&gt;1,AND(X175&lt;&gt;"",X175&lt;Inputs!$B$16),AND(X175&lt;&gt;"",X175&gt;Inputs!$B$17),G175&lt;Inputs!$B$18,AH175="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB175" s="4" t="n"/>
+      <c r="AC175" s="7" t="n"/>
+      <c r="AD175" s="8">
+        <f>IF(A175="","",IF(AC175&lt;&gt;"",AC175,IF(E175="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE175" s="8">
+        <f>IF(OR(AD175="",F175="",G175=""),"",AD175+F175*G175)</f>
+        <v/>
+      </c>
+      <c r="AF175" s="8">
+        <f>IF(OR(E175="",A175=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG175" s="8">
+        <f>IF(OR(AD175="",AF175=""),"",AD175-AF175)</f>
+        <v/>
+      </c>
+      <c r="AH175" s="4">
+        <f>IF(A175="","",IF(E175="","TERMINAL",IF(AG175="","INFO",IF(ABS(AG175)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -20307,10 +24090,31 @@
         <v/>
       </c>
       <c r="AA176" s="4">
-        <f>IF(A176="","",IF(OR(U176&gt;1,AND(X176&lt;&gt;"",X176&lt;Inputs!$B$16),AND(X176&lt;&gt;"",X176&gt;Inputs!$B$17),G176&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A176="","",IF(OR(U176&gt;1,AND(X176&lt;&gt;"",X176&lt;Inputs!$B$16),AND(X176&lt;&gt;"",X176&gt;Inputs!$B$17),G176&lt;Inputs!$B$18,AH176="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB176" s="4" t="n"/>
+      <c r="AC176" s="7" t="n"/>
+      <c r="AD176" s="8">
+        <f>IF(A176="","",IF(AC176&lt;&gt;"",AC176,IF(E176="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE176" s="8">
+        <f>IF(OR(AD176="",F176="",G176=""),"",AD176+F176*G176)</f>
+        <v/>
+      </c>
+      <c r="AF176" s="8">
+        <f>IF(OR(E176="",A176=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG176" s="8">
+        <f>IF(OR(AD176="",AF176=""),"",AD176-AF176)</f>
+        <v/>
+      </c>
+      <c r="AH176" s="4">
+        <f>IF(A176="","",IF(E176="","TERMINAL",IF(AG176="","INFO",IF(ABS(AG176)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -20381,10 +24185,31 @@
         <v/>
       </c>
       <c r="AA177" s="4">
-        <f>IF(A177="","",IF(OR(U177&gt;1,AND(X177&lt;&gt;"",X177&lt;Inputs!$B$16),AND(X177&lt;&gt;"",X177&gt;Inputs!$B$17),G177&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A177="","",IF(OR(U177&gt;1,AND(X177&lt;&gt;"",X177&lt;Inputs!$B$16),AND(X177&lt;&gt;"",X177&gt;Inputs!$B$17),G177&lt;Inputs!$B$18,AH177="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB177" s="4" t="n"/>
+      <c r="AC177" s="7" t="n"/>
+      <c r="AD177" s="8">
+        <f>IF(A177="","",IF(AC177&lt;&gt;"",AC177,IF(E177="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE177" s="8">
+        <f>IF(OR(AD177="",F177="",G177=""),"",AD177+F177*G177)</f>
+        <v/>
+      </c>
+      <c r="AF177" s="8">
+        <f>IF(OR(E177="",A177=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG177" s="8">
+        <f>IF(OR(AD177="",AF177=""),"",AD177-AF177)</f>
+        <v/>
+      </c>
+      <c r="AH177" s="4">
+        <f>IF(A177="","",IF(E177="","TERMINAL",IF(AG177="","INFO",IF(ABS(AG177)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n"/>
@@ -20455,10 +24280,31 @@
         <v/>
       </c>
       <c r="AA178" s="4">
-        <f>IF(A178="","",IF(OR(U178&gt;1,AND(X178&lt;&gt;"",X178&lt;Inputs!$B$16),AND(X178&lt;&gt;"",X178&gt;Inputs!$B$17),G178&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A178="","",IF(OR(U178&gt;1,AND(X178&lt;&gt;"",X178&lt;Inputs!$B$16),AND(X178&lt;&gt;"",X178&gt;Inputs!$B$17),G178&lt;Inputs!$B$18,AH178="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB178" s="4" t="n"/>
+      <c r="AC178" s="7" t="n"/>
+      <c r="AD178" s="8">
+        <f>IF(A178="","",IF(AC178&lt;&gt;"",AC178,IF(E178="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE178" s="8">
+        <f>IF(OR(AD178="",F178="",G178=""),"",AD178+F178*G178)</f>
+        <v/>
+      </c>
+      <c r="AF178" s="8">
+        <f>IF(OR(E178="",A178=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG178" s="8">
+        <f>IF(OR(AD178="",AF178=""),"",AD178-AF178)</f>
+        <v/>
+      </c>
+      <c r="AH178" s="4">
+        <f>IF(A178="","",IF(E178="","TERMINAL",IF(AG178="","INFO",IF(ABS(AG178)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -20529,10 +24375,31 @@
         <v/>
       </c>
       <c r="AA179" s="4">
-        <f>IF(A179="","",IF(OR(U179&gt;1,AND(X179&lt;&gt;"",X179&lt;Inputs!$B$16),AND(X179&lt;&gt;"",X179&gt;Inputs!$B$17),G179&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A179="","",IF(OR(U179&gt;1,AND(X179&lt;&gt;"",X179&lt;Inputs!$B$16),AND(X179&lt;&gt;"",X179&gt;Inputs!$B$17),G179&lt;Inputs!$B$18,AH179="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB179" s="4" t="n"/>
+      <c r="AC179" s="7" t="n"/>
+      <c r="AD179" s="8">
+        <f>IF(A179="","",IF(AC179&lt;&gt;"",AC179,IF(E179="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE179" s="8">
+        <f>IF(OR(AD179="",F179="",G179=""),"",AD179+F179*G179)</f>
+        <v/>
+      </c>
+      <c r="AF179" s="8">
+        <f>IF(OR(E179="",A179=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG179" s="8">
+        <f>IF(OR(AD179="",AF179=""),"",AD179-AF179)</f>
+        <v/>
+      </c>
+      <c r="AH179" s="4">
+        <f>IF(A179="","",IF(E179="","TERMINAL",IF(AG179="","INFO",IF(ABS(AG179)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n"/>
@@ -20603,10 +24470,31 @@
         <v/>
       </c>
       <c r="AA180" s="4">
-        <f>IF(A180="","",IF(OR(U180&gt;1,AND(X180&lt;&gt;"",X180&lt;Inputs!$B$16),AND(X180&lt;&gt;"",X180&gt;Inputs!$B$17),G180&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A180="","",IF(OR(U180&gt;1,AND(X180&lt;&gt;"",X180&lt;Inputs!$B$16),AND(X180&lt;&gt;"",X180&gt;Inputs!$B$17),G180&lt;Inputs!$B$18,AH180="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB180" s="4" t="n"/>
+      <c r="AC180" s="7" t="n"/>
+      <c r="AD180" s="8">
+        <f>IF(A180="","",IF(AC180&lt;&gt;"",AC180,IF(E180="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE180" s="8">
+        <f>IF(OR(AD180="",F180="",G180=""),"",AD180+F180*G180)</f>
+        <v/>
+      </c>
+      <c r="AF180" s="8">
+        <f>IF(OR(E180="",A180=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG180" s="8">
+        <f>IF(OR(AD180="",AF180=""),"",AD180-AF180)</f>
+        <v/>
+      </c>
+      <c r="AH180" s="4">
+        <f>IF(A180="","",IF(E180="","TERMINAL",IF(AG180="","INFO",IF(ABS(AG180)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -20677,10 +24565,31 @@
         <v/>
       </c>
       <c r="AA181" s="4">
-        <f>IF(A181="","",IF(OR(U181&gt;1,AND(X181&lt;&gt;"",X181&lt;Inputs!$B$16),AND(X181&lt;&gt;"",X181&gt;Inputs!$B$17),G181&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A181="","",IF(OR(U181&gt;1,AND(X181&lt;&gt;"",X181&lt;Inputs!$B$16),AND(X181&lt;&gt;"",X181&gt;Inputs!$B$17),G181&lt;Inputs!$B$18,AH181="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB181" s="4" t="n"/>
+      <c r="AC181" s="7" t="n"/>
+      <c r="AD181" s="8">
+        <f>IF(A181="","",IF(AC181&lt;&gt;"",AC181,IF(E181="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE181" s="8">
+        <f>IF(OR(AD181="",F181="",G181=""),"",AD181+F181*G181)</f>
+        <v/>
+      </c>
+      <c r="AF181" s="8">
+        <f>IF(OR(E181="",A181=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG181" s="8">
+        <f>IF(OR(AD181="",AF181=""),"",AD181-AF181)</f>
+        <v/>
+      </c>
+      <c r="AH181" s="4">
+        <f>IF(A181="","",IF(E181="","TERMINAL",IF(AG181="","INFO",IF(ABS(AG181)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -20751,10 +24660,31 @@
         <v/>
       </c>
       <c r="AA182" s="4">
-        <f>IF(A182="","",IF(OR(U182&gt;1,AND(X182&lt;&gt;"",X182&lt;Inputs!$B$16),AND(X182&lt;&gt;"",X182&gt;Inputs!$B$17),G182&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A182="","",IF(OR(U182&gt;1,AND(X182&lt;&gt;"",X182&lt;Inputs!$B$16),AND(X182&lt;&gt;"",X182&gt;Inputs!$B$17),G182&lt;Inputs!$B$18,AH182="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB182" s="4" t="n"/>
+      <c r="AC182" s="7" t="n"/>
+      <c r="AD182" s="8">
+        <f>IF(A182="","",IF(AC182&lt;&gt;"",AC182,IF(E182="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE182" s="8">
+        <f>IF(OR(AD182="",F182="",G182=""),"",AD182+F182*G182)</f>
+        <v/>
+      </c>
+      <c r="AF182" s="8">
+        <f>IF(OR(E182="",A182=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG182" s="8">
+        <f>IF(OR(AD182="",AF182=""),"",AD182-AF182)</f>
+        <v/>
+      </c>
+      <c r="AH182" s="4">
+        <f>IF(A182="","",IF(E182="","TERMINAL",IF(AG182="","INFO",IF(ABS(AG182)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -20825,10 +24755,31 @@
         <v/>
       </c>
       <c r="AA183" s="4">
-        <f>IF(A183="","",IF(OR(U183&gt;1,AND(X183&lt;&gt;"",X183&lt;Inputs!$B$16),AND(X183&lt;&gt;"",X183&gt;Inputs!$B$17),G183&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A183="","",IF(OR(U183&gt;1,AND(X183&lt;&gt;"",X183&lt;Inputs!$B$16),AND(X183&lt;&gt;"",X183&gt;Inputs!$B$17),G183&lt;Inputs!$B$18,AH183="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB183" s="4" t="n"/>
+      <c r="AC183" s="7" t="n"/>
+      <c r="AD183" s="8">
+        <f>IF(A183="","",IF(AC183&lt;&gt;"",AC183,IF(E183="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE183" s="8">
+        <f>IF(OR(AD183="",F183="",G183=""),"",AD183+F183*G183)</f>
+        <v/>
+      </c>
+      <c r="AF183" s="8">
+        <f>IF(OR(E183="",A183=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG183" s="8">
+        <f>IF(OR(AD183="",AF183=""),"",AD183-AF183)</f>
+        <v/>
+      </c>
+      <c r="AH183" s="4">
+        <f>IF(A183="","",IF(E183="","TERMINAL",IF(AG183="","INFO",IF(ABS(AG183)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -20899,10 +24850,31 @@
         <v/>
       </c>
       <c r="AA184" s="4">
-        <f>IF(A184="","",IF(OR(U184&gt;1,AND(X184&lt;&gt;"",X184&lt;Inputs!$B$16),AND(X184&lt;&gt;"",X184&gt;Inputs!$B$17),G184&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A184="","",IF(OR(U184&gt;1,AND(X184&lt;&gt;"",X184&lt;Inputs!$B$16),AND(X184&lt;&gt;"",X184&gt;Inputs!$B$17),G184&lt;Inputs!$B$18,AH184="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB184" s="4" t="n"/>
+      <c r="AC184" s="7" t="n"/>
+      <c r="AD184" s="8">
+        <f>IF(A184="","",IF(AC184&lt;&gt;"",AC184,IF(E184="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE184" s="8">
+        <f>IF(OR(AD184="",F184="",G184=""),"",AD184+F184*G184)</f>
+        <v/>
+      </c>
+      <c r="AF184" s="8">
+        <f>IF(OR(E184="",A184=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG184" s="8">
+        <f>IF(OR(AD184="",AF184=""),"",AD184-AF184)</f>
+        <v/>
+      </c>
+      <c r="AH184" s="4">
+        <f>IF(A184="","",IF(E184="","TERMINAL",IF(AG184="","INFO",IF(ABS(AG184)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -20973,10 +24945,31 @@
         <v/>
       </c>
       <c r="AA185" s="4">
-        <f>IF(A185="","",IF(OR(U185&gt;1,AND(X185&lt;&gt;"",X185&lt;Inputs!$B$16),AND(X185&lt;&gt;"",X185&gt;Inputs!$B$17),G185&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A185="","",IF(OR(U185&gt;1,AND(X185&lt;&gt;"",X185&lt;Inputs!$B$16),AND(X185&lt;&gt;"",X185&gt;Inputs!$B$17),G185&lt;Inputs!$B$18,AH185="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB185" s="4" t="n"/>
+      <c r="AC185" s="7" t="n"/>
+      <c r="AD185" s="8">
+        <f>IF(A185="","",IF(AC185&lt;&gt;"",AC185,IF(E185="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE185" s="8">
+        <f>IF(OR(AD185="",F185="",G185=""),"",AD185+F185*G185)</f>
+        <v/>
+      </c>
+      <c r="AF185" s="8">
+        <f>IF(OR(E185="",A185=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG185" s="8">
+        <f>IF(OR(AD185="",AF185=""),"",AD185-AF185)</f>
+        <v/>
+      </c>
+      <c r="AH185" s="4">
+        <f>IF(A185="","",IF(E185="","TERMINAL",IF(AG185="","INFO",IF(ABS(AG185)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n"/>
@@ -21047,10 +25040,31 @@
         <v/>
       </c>
       <c r="AA186" s="4">
-        <f>IF(A186="","",IF(OR(U186&gt;1,AND(X186&lt;&gt;"",X186&lt;Inputs!$B$16),AND(X186&lt;&gt;"",X186&gt;Inputs!$B$17),G186&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A186="","",IF(OR(U186&gt;1,AND(X186&lt;&gt;"",X186&lt;Inputs!$B$16),AND(X186&lt;&gt;"",X186&gt;Inputs!$B$17),G186&lt;Inputs!$B$18,AH186="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB186" s="4" t="n"/>
+      <c r="AC186" s="7" t="n"/>
+      <c r="AD186" s="8">
+        <f>IF(A186="","",IF(AC186&lt;&gt;"",AC186,IF(E186="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE186" s="8">
+        <f>IF(OR(AD186="",F186="",G186=""),"",AD186+F186*G186)</f>
+        <v/>
+      </c>
+      <c r="AF186" s="8">
+        <f>IF(OR(E186="",A186=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG186" s="8">
+        <f>IF(OR(AD186="",AF186=""),"",AD186-AF186)</f>
+        <v/>
+      </c>
+      <c r="AH186" s="4">
+        <f>IF(A186="","",IF(E186="","TERMINAL",IF(AG186="","INFO",IF(ABS(AG186)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -21121,10 +25135,31 @@
         <v/>
       </c>
       <c r="AA187" s="4">
-        <f>IF(A187="","",IF(OR(U187&gt;1,AND(X187&lt;&gt;"",X187&lt;Inputs!$B$16),AND(X187&lt;&gt;"",X187&gt;Inputs!$B$17),G187&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A187="","",IF(OR(U187&gt;1,AND(X187&lt;&gt;"",X187&lt;Inputs!$B$16),AND(X187&lt;&gt;"",X187&gt;Inputs!$B$17),G187&lt;Inputs!$B$18,AH187="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB187" s="4" t="n"/>
+      <c r="AC187" s="7" t="n"/>
+      <c r="AD187" s="8">
+        <f>IF(A187="","",IF(AC187&lt;&gt;"",AC187,IF(E187="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE187" s="8">
+        <f>IF(OR(AD187="",F187="",G187=""),"",AD187+F187*G187)</f>
+        <v/>
+      </c>
+      <c r="AF187" s="8">
+        <f>IF(OR(E187="",A187=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG187" s="8">
+        <f>IF(OR(AD187="",AF187=""),"",AD187-AF187)</f>
+        <v/>
+      </c>
+      <c r="AH187" s="4">
+        <f>IF(A187="","",IF(E187="","TERMINAL",IF(AG187="","INFO",IF(ABS(AG187)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -21195,10 +25230,31 @@
         <v/>
       </c>
       <c r="AA188" s="4">
-        <f>IF(A188="","",IF(OR(U188&gt;1,AND(X188&lt;&gt;"",X188&lt;Inputs!$B$16),AND(X188&lt;&gt;"",X188&gt;Inputs!$B$17),G188&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A188="","",IF(OR(U188&gt;1,AND(X188&lt;&gt;"",X188&lt;Inputs!$B$16),AND(X188&lt;&gt;"",X188&gt;Inputs!$B$17),G188&lt;Inputs!$B$18,AH188="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB188" s="4" t="n"/>
+      <c r="AC188" s="7" t="n"/>
+      <c r="AD188" s="8">
+        <f>IF(A188="","",IF(AC188&lt;&gt;"",AC188,IF(E188="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE188" s="8">
+        <f>IF(OR(AD188="",F188="",G188=""),"",AD188+F188*G188)</f>
+        <v/>
+      </c>
+      <c r="AF188" s="8">
+        <f>IF(OR(E188="",A188=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG188" s="8">
+        <f>IF(OR(AD188="",AF188=""),"",AD188-AF188)</f>
+        <v/>
+      </c>
+      <c r="AH188" s="4">
+        <f>IF(A188="","",IF(E188="","TERMINAL",IF(AG188="","INFO",IF(ABS(AG188)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -21269,10 +25325,31 @@
         <v/>
       </c>
       <c r="AA189" s="4">
-        <f>IF(A189="","",IF(OR(U189&gt;1,AND(X189&lt;&gt;"",X189&lt;Inputs!$B$16),AND(X189&lt;&gt;"",X189&gt;Inputs!$B$17),G189&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A189="","",IF(OR(U189&gt;1,AND(X189&lt;&gt;"",X189&lt;Inputs!$B$16),AND(X189&lt;&gt;"",X189&gt;Inputs!$B$17),G189&lt;Inputs!$B$18,AH189="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB189" s="4" t="n"/>
+      <c r="AC189" s="7" t="n"/>
+      <c r="AD189" s="8">
+        <f>IF(A189="","",IF(AC189&lt;&gt;"",AC189,IF(E189="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE189" s="8">
+        <f>IF(OR(AD189="",F189="",G189=""),"",AD189+F189*G189)</f>
+        <v/>
+      </c>
+      <c r="AF189" s="8">
+        <f>IF(OR(E189="",A189=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG189" s="8">
+        <f>IF(OR(AD189="",AF189=""),"",AD189-AF189)</f>
+        <v/>
+      </c>
+      <c r="AH189" s="4">
+        <f>IF(A189="","",IF(E189="","TERMINAL",IF(AG189="","INFO",IF(ABS(AG189)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -21343,10 +25420,31 @@
         <v/>
       </c>
       <c r="AA190" s="4">
-        <f>IF(A190="","",IF(OR(U190&gt;1,AND(X190&lt;&gt;"",X190&lt;Inputs!$B$16),AND(X190&lt;&gt;"",X190&gt;Inputs!$B$17),G190&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A190="","",IF(OR(U190&gt;1,AND(X190&lt;&gt;"",X190&lt;Inputs!$B$16),AND(X190&lt;&gt;"",X190&gt;Inputs!$B$17),G190&lt;Inputs!$B$18,AH190="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB190" s="4" t="n"/>
+      <c r="AC190" s="7" t="n"/>
+      <c r="AD190" s="8">
+        <f>IF(A190="","",IF(AC190&lt;&gt;"",AC190,IF(E190="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE190" s="8">
+        <f>IF(OR(AD190="",F190="",G190=""),"",AD190+F190*G190)</f>
+        <v/>
+      </c>
+      <c r="AF190" s="8">
+        <f>IF(OR(E190="",A190=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG190" s="8">
+        <f>IF(OR(AD190="",AF190=""),"",AD190-AF190)</f>
+        <v/>
+      </c>
+      <c r="AH190" s="4">
+        <f>IF(A190="","",IF(E190="","TERMINAL",IF(AG190="","INFO",IF(ABS(AG190)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -21417,10 +25515,31 @@
         <v/>
       </c>
       <c r="AA191" s="4">
-        <f>IF(A191="","",IF(OR(U191&gt;1,AND(X191&lt;&gt;"",X191&lt;Inputs!$B$16),AND(X191&lt;&gt;"",X191&gt;Inputs!$B$17),G191&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A191="","",IF(OR(U191&gt;1,AND(X191&lt;&gt;"",X191&lt;Inputs!$B$16),AND(X191&lt;&gt;"",X191&gt;Inputs!$B$17),G191&lt;Inputs!$B$18,AH191="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB191" s="4" t="n"/>
+      <c r="AC191" s="7" t="n"/>
+      <c r="AD191" s="8">
+        <f>IF(A191="","",IF(AC191&lt;&gt;"",AC191,IF(E191="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE191" s="8">
+        <f>IF(OR(AD191="",F191="",G191=""),"",AD191+F191*G191)</f>
+        <v/>
+      </c>
+      <c r="AF191" s="8">
+        <f>IF(OR(E191="",A191=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG191" s="8">
+        <f>IF(OR(AD191="",AF191=""),"",AD191-AF191)</f>
+        <v/>
+      </c>
+      <c r="AH191" s="4">
+        <f>IF(A191="","",IF(E191="","TERMINAL",IF(AG191="","INFO",IF(ABS(AG191)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -21491,10 +25610,31 @@
         <v/>
       </c>
       <c r="AA192" s="4">
-        <f>IF(A192="","",IF(OR(U192&gt;1,AND(X192&lt;&gt;"",X192&lt;Inputs!$B$16),AND(X192&lt;&gt;"",X192&gt;Inputs!$B$17),G192&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A192="","",IF(OR(U192&gt;1,AND(X192&lt;&gt;"",X192&lt;Inputs!$B$16),AND(X192&lt;&gt;"",X192&gt;Inputs!$B$17),G192&lt;Inputs!$B$18,AH192="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB192" s="4" t="n"/>
+      <c r="AC192" s="7" t="n"/>
+      <c r="AD192" s="8">
+        <f>IF(A192="","",IF(AC192&lt;&gt;"",AC192,IF(E192="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE192" s="8">
+        <f>IF(OR(AD192="",F192="",G192=""),"",AD192+F192*G192)</f>
+        <v/>
+      </c>
+      <c r="AF192" s="8">
+        <f>IF(OR(E192="",A192=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG192" s="8">
+        <f>IF(OR(AD192="",AF192=""),"",AD192-AF192)</f>
+        <v/>
+      </c>
+      <c r="AH192" s="4">
+        <f>IF(A192="","",IF(E192="","TERMINAL",IF(AG192="","INFO",IF(ABS(AG192)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -21565,10 +25705,31 @@
         <v/>
       </c>
       <c r="AA193" s="4">
-        <f>IF(A193="","",IF(OR(U193&gt;1,AND(X193&lt;&gt;"",X193&lt;Inputs!$B$16),AND(X193&lt;&gt;"",X193&gt;Inputs!$B$17),G193&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A193="","",IF(OR(U193&gt;1,AND(X193&lt;&gt;"",X193&lt;Inputs!$B$16),AND(X193&lt;&gt;"",X193&gt;Inputs!$B$17),G193&lt;Inputs!$B$18,AH193="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB193" s="4" t="n"/>
+      <c r="AC193" s="7" t="n"/>
+      <c r="AD193" s="8">
+        <f>IF(A193="","",IF(AC193&lt;&gt;"",AC193,IF(E193="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE193" s="8">
+        <f>IF(OR(AD193="",F193="",G193=""),"",AD193+F193*G193)</f>
+        <v/>
+      </c>
+      <c r="AF193" s="8">
+        <f>IF(OR(E193="",A193=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG193" s="8">
+        <f>IF(OR(AD193="",AF193=""),"",AD193-AF193)</f>
+        <v/>
+      </c>
+      <c r="AH193" s="4">
+        <f>IF(A193="","",IF(E193="","TERMINAL",IF(AG193="","INFO",IF(ABS(AG193)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n"/>
@@ -21639,10 +25800,31 @@
         <v/>
       </c>
       <c r="AA194" s="4">
-        <f>IF(A194="","",IF(OR(U194&gt;1,AND(X194&lt;&gt;"",X194&lt;Inputs!$B$16),AND(X194&lt;&gt;"",X194&gt;Inputs!$B$17),G194&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A194="","",IF(OR(U194&gt;1,AND(X194&lt;&gt;"",X194&lt;Inputs!$B$16),AND(X194&lt;&gt;"",X194&gt;Inputs!$B$17),G194&lt;Inputs!$B$18,AH194="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB194" s="4" t="n"/>
+      <c r="AC194" s="7" t="n"/>
+      <c r="AD194" s="8">
+        <f>IF(A194="","",IF(AC194&lt;&gt;"",AC194,IF(E194="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE194" s="8">
+        <f>IF(OR(AD194="",F194="",G194=""),"",AD194+F194*G194)</f>
+        <v/>
+      </c>
+      <c r="AF194" s="8">
+        <f>IF(OR(E194="",A194=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG194" s="8">
+        <f>IF(OR(AD194="",AF194=""),"",AD194-AF194)</f>
+        <v/>
+      </c>
+      <c r="AH194" s="4">
+        <f>IF(A194="","",IF(E194="","TERMINAL",IF(AG194="","INFO",IF(ABS(AG194)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -21713,10 +25895,31 @@
         <v/>
       </c>
       <c r="AA195" s="4">
-        <f>IF(A195="","",IF(OR(U195&gt;1,AND(X195&lt;&gt;"",X195&lt;Inputs!$B$16),AND(X195&lt;&gt;"",X195&gt;Inputs!$B$17),G195&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A195="","",IF(OR(U195&gt;1,AND(X195&lt;&gt;"",X195&lt;Inputs!$B$16),AND(X195&lt;&gt;"",X195&gt;Inputs!$B$17),G195&lt;Inputs!$B$18,AH195="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB195" s="4" t="n"/>
+      <c r="AC195" s="7" t="n"/>
+      <c r="AD195" s="8">
+        <f>IF(A195="","",IF(AC195&lt;&gt;"",AC195,IF(E195="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE195" s="8">
+        <f>IF(OR(AD195="",F195="",G195=""),"",AD195+F195*G195)</f>
+        <v/>
+      </c>
+      <c r="AF195" s="8">
+        <f>IF(OR(E195="",A195=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG195" s="8">
+        <f>IF(OR(AD195="",AF195=""),"",AD195-AF195)</f>
+        <v/>
+      </c>
+      <c r="AH195" s="4">
+        <f>IF(A195="","",IF(E195="","TERMINAL",IF(AG195="","INFO",IF(ABS(AG195)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -21787,10 +25990,31 @@
         <v/>
       </c>
       <c r="AA196" s="4">
-        <f>IF(A196="","",IF(OR(U196&gt;1,AND(X196&lt;&gt;"",X196&lt;Inputs!$B$16),AND(X196&lt;&gt;"",X196&gt;Inputs!$B$17),G196&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A196="","",IF(OR(U196&gt;1,AND(X196&lt;&gt;"",X196&lt;Inputs!$B$16),AND(X196&lt;&gt;"",X196&gt;Inputs!$B$17),G196&lt;Inputs!$B$18,AH196="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB196" s="4" t="n"/>
+      <c r="AC196" s="7" t="n"/>
+      <c r="AD196" s="8">
+        <f>IF(A196="","",IF(AC196&lt;&gt;"",AC196,IF(E196="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE196" s="8">
+        <f>IF(OR(AD196="",F196="",G196=""),"",AD196+F196*G196)</f>
+        <v/>
+      </c>
+      <c r="AF196" s="8">
+        <f>IF(OR(E196="",A196=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG196" s="8">
+        <f>IF(OR(AD196="",AF196=""),"",AD196-AF196)</f>
+        <v/>
+      </c>
+      <c r="AH196" s="4">
+        <f>IF(A196="","",IF(E196="","TERMINAL",IF(AG196="","INFO",IF(ABS(AG196)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -21861,10 +26085,31 @@
         <v/>
       </c>
       <c r="AA197" s="4">
-        <f>IF(A197="","",IF(OR(U197&gt;1,AND(X197&lt;&gt;"",X197&lt;Inputs!$B$16),AND(X197&lt;&gt;"",X197&gt;Inputs!$B$17),G197&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A197="","",IF(OR(U197&gt;1,AND(X197&lt;&gt;"",X197&lt;Inputs!$B$16),AND(X197&lt;&gt;"",X197&gt;Inputs!$B$17),G197&lt;Inputs!$B$18,AH197="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB197" s="4" t="n"/>
+      <c r="AC197" s="7" t="n"/>
+      <c r="AD197" s="8">
+        <f>IF(A197="","",IF(AC197&lt;&gt;"",AC197,IF(E197="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE197" s="8">
+        <f>IF(OR(AD197="",F197="",G197=""),"",AD197+F197*G197)</f>
+        <v/>
+      </c>
+      <c r="AF197" s="8">
+        <f>IF(OR(E197="",A197=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG197" s="8">
+        <f>IF(OR(AD197="",AF197=""),"",AD197-AF197)</f>
+        <v/>
+      </c>
+      <c r="AH197" s="4">
+        <f>IF(A197="","",IF(E197="","TERMINAL",IF(AG197="","INFO",IF(ABS(AG197)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -21935,10 +26180,31 @@
         <v/>
       </c>
       <c r="AA198" s="4">
-        <f>IF(A198="","",IF(OR(U198&gt;1,AND(X198&lt;&gt;"",X198&lt;Inputs!$B$16),AND(X198&lt;&gt;"",X198&gt;Inputs!$B$17),G198&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A198="","",IF(OR(U198&gt;1,AND(X198&lt;&gt;"",X198&lt;Inputs!$B$16),AND(X198&lt;&gt;"",X198&gt;Inputs!$B$17),G198&lt;Inputs!$B$18,AH198="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB198" s="4" t="n"/>
+      <c r="AC198" s="7" t="n"/>
+      <c r="AD198" s="8">
+        <f>IF(A198="","",IF(AC198&lt;&gt;"",AC198,IF(E198="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE198" s="8">
+        <f>IF(OR(AD198="",F198="",G198=""),"",AD198+F198*G198)</f>
+        <v/>
+      </c>
+      <c r="AF198" s="8">
+        <f>IF(OR(E198="",A198=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG198" s="8">
+        <f>IF(OR(AD198="",AF198=""),"",AD198-AF198)</f>
+        <v/>
+      </c>
+      <c r="AH198" s="4">
+        <f>IF(A198="","",IF(E198="","TERMINAL",IF(AG198="","INFO",IF(ABS(AG198)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -22009,10 +26275,31 @@
         <v/>
       </c>
       <c r="AA199" s="4">
-        <f>IF(A199="","",IF(OR(U199&gt;1,AND(X199&lt;&gt;"",X199&lt;Inputs!$B$16),AND(X199&lt;&gt;"",X199&gt;Inputs!$B$17),G199&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A199="","",IF(OR(U199&gt;1,AND(X199&lt;&gt;"",X199&lt;Inputs!$B$16),AND(X199&lt;&gt;"",X199&gt;Inputs!$B$17),G199&lt;Inputs!$B$18,AH199="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB199" s="4" t="n"/>
+      <c r="AC199" s="7" t="n"/>
+      <c r="AD199" s="8">
+        <f>IF(A199="","",IF(AC199&lt;&gt;"",AC199,IF(E199="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE199" s="8">
+        <f>IF(OR(AD199="",F199="",G199=""),"",AD199+F199*G199)</f>
+        <v/>
+      </c>
+      <c r="AF199" s="8">
+        <f>IF(OR(E199="",A199=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG199" s="8">
+        <f>IF(OR(AD199="",AF199=""),"",AD199-AF199)</f>
+        <v/>
+      </c>
+      <c r="AH199" s="4">
+        <f>IF(A199="","",IF(E199="","TERMINAL",IF(AG199="","INFO",IF(ABS(AG199)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n"/>
@@ -22083,10 +26370,31 @@
         <v/>
       </c>
       <c r="AA200" s="4">
-        <f>IF(A200="","",IF(OR(U200&gt;1,AND(X200&lt;&gt;"",X200&lt;Inputs!$B$16),AND(X200&lt;&gt;"",X200&gt;Inputs!$B$17),G200&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A200="","",IF(OR(U200&gt;1,AND(X200&lt;&gt;"",X200&lt;Inputs!$B$16),AND(X200&lt;&gt;"",X200&gt;Inputs!$B$17),G200&lt;Inputs!$B$18,AH200="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB200" s="4" t="n"/>
+      <c r="AC200" s="7" t="n"/>
+      <c r="AD200" s="8">
+        <f>IF(A200="","",IF(AC200&lt;&gt;"",AC200,IF(E200="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE200" s="8">
+        <f>IF(OR(AD200="",F200="",G200=""),"",AD200+F200*G200)</f>
+        <v/>
+      </c>
+      <c r="AF200" s="8">
+        <f>IF(OR(E200="",A200=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG200" s="8">
+        <f>IF(OR(AD200="",AF200=""),"",AD200-AF200)</f>
+        <v/>
+      </c>
+      <c r="AH200" s="4">
+        <f>IF(A200="","",IF(E200="","TERMINAL",IF(AG200="","INFO",IF(ABS(AG200)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -22157,10 +26465,31 @@
         <v/>
       </c>
       <c r="AA201" s="4">
-        <f>IF(A201="","",IF(OR(U201&gt;1,AND(X201&lt;&gt;"",X201&lt;Inputs!$B$16),AND(X201&lt;&gt;"",X201&gt;Inputs!$B$17),G201&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A201="","",IF(OR(U201&gt;1,AND(X201&lt;&gt;"",X201&lt;Inputs!$B$16),AND(X201&lt;&gt;"",X201&gt;Inputs!$B$17),G201&lt;Inputs!$B$18,AH201="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB201" s="4" t="n"/>
+      <c r="AC201" s="7" t="n"/>
+      <c r="AD201" s="8">
+        <f>IF(A201="","",IF(AC201&lt;&gt;"",AC201,IF(E201="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE201" s="8">
+        <f>IF(OR(AD201="",F201="",G201=""),"",AD201+F201*G201)</f>
+        <v/>
+      </c>
+      <c r="AF201" s="8">
+        <f>IF(OR(E201="",A201=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG201" s="8">
+        <f>IF(OR(AD201="",AF201=""),"",AD201-AF201)</f>
+        <v/>
+      </c>
+      <c r="AH201" s="4">
+        <f>IF(A201="","",IF(E201="","TERMINAL",IF(AG201="","INFO",IF(ABS(AG201)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -22231,10 +26560,31 @@
         <v/>
       </c>
       <c r="AA202" s="4">
-        <f>IF(A202="","",IF(OR(U202&gt;1,AND(X202&lt;&gt;"",X202&lt;Inputs!$B$16),AND(X202&lt;&gt;"",X202&gt;Inputs!$B$17),G202&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A202="","",IF(OR(U202&gt;1,AND(X202&lt;&gt;"",X202&lt;Inputs!$B$16),AND(X202&lt;&gt;"",X202&gt;Inputs!$B$17),G202&lt;Inputs!$B$18,AH202="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB202" s="4" t="n"/>
+      <c r="AC202" s="7" t="n"/>
+      <c r="AD202" s="8">
+        <f>IF(A202="","",IF(AC202&lt;&gt;"",AC202,IF(E202="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE202" s="8">
+        <f>IF(OR(AD202="",F202="",G202=""),"",AD202+F202*G202)</f>
+        <v/>
+      </c>
+      <c r="AF202" s="8">
+        <f>IF(OR(E202="",A202=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG202" s="8">
+        <f>IF(OR(AD202="",AF202=""),"",AD202-AF202)</f>
+        <v/>
+      </c>
+      <c r="AH202" s="4">
+        <f>IF(A202="","",IF(E202="","TERMINAL",IF(AG202="","INFO",IF(ABS(AG202)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -22305,10 +26655,31 @@
         <v/>
       </c>
       <c r="AA203" s="4">
-        <f>IF(A203="","",IF(OR(U203&gt;1,AND(X203&lt;&gt;"",X203&lt;Inputs!$B$16),AND(X203&lt;&gt;"",X203&gt;Inputs!$B$17),G203&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A203="","",IF(OR(U203&gt;1,AND(X203&lt;&gt;"",X203&lt;Inputs!$B$16),AND(X203&lt;&gt;"",X203&gt;Inputs!$B$17),G203&lt;Inputs!$B$18,AH203="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB203" s="4" t="n"/>
+      <c r="AC203" s="7" t="n"/>
+      <c r="AD203" s="8">
+        <f>IF(A203="","",IF(AC203&lt;&gt;"",AC203,IF(E203="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE203" s="8">
+        <f>IF(OR(AD203="",F203="",G203=""),"",AD203+F203*G203)</f>
+        <v/>
+      </c>
+      <c r="AF203" s="8">
+        <f>IF(OR(E203="",A203=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG203" s="8">
+        <f>IF(OR(AD203="",AF203=""),"",AD203-AF203)</f>
+        <v/>
+      </c>
+      <c r="AH203" s="4">
+        <f>IF(A203="","",IF(E203="","TERMINAL",IF(AG203="","INFO",IF(ABS(AG203)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -22379,35 +26750,56 @@
         <v/>
       </c>
       <c r="AA204" s="4">
-        <f>IF(A204="","",IF(OR(U204&gt;1,AND(X204&lt;&gt;"",X204&lt;Inputs!$B$16),AND(X204&lt;&gt;"",X204&gt;Inputs!$B$17),G204&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A204="","",IF(OR(U204&gt;1,AND(X204&lt;&gt;"",X204&lt;Inputs!$B$16),AND(X204&lt;&gt;"",X204&gt;Inputs!$B$17),G204&lt;Inputs!$B$18,AH204="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB204" s="4" t="n"/>
+      <c r="AC204" s="7" t="n"/>
+      <c r="AD204" s="8">
+        <f>IF(A204="","",IF(AC204&lt;&gt;"",AC204,IF(E204="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE204" s="8">
+        <f>IF(OR(AD204="",F204="",G204=""),"",AD204+F204*G204)</f>
+        <v/>
+      </c>
+      <c r="AF204" s="8">
+        <f>IF(OR(E204="",A204=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG204" s="8">
+        <f>IF(OR(AD204="",AF204=""),"",AD204-AF204)</f>
+        <v/>
+      </c>
+      <c r="AH204" s="4">
+        <f>IF(A204="","",IF(E204="","TERMINAL",IF(AG204="","INFO",IF(ABS(AG204)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:AB204">
-    <cfRule type="expression" priority="1" dxfId="0">
+  <conditionalFormatting sqref="A4:AH204">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>=$B4="PIPE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>=$B4="SWALE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>=$B4="TRENCH"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA204">
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>=$AA4="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U204">
-    <cfRule type="expression" priority="5" dxfId="3">
-      <formula>=$U4&gt;1</formula>
+  <conditionalFormatting sqref="AH4:AH204">
+    <cfRule type="expression" priority="10" dxfId="3">
+      <formula>=$AH4="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22523,8 +26915,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="8">
         <f>IF(OR(C4="",D4=""),"",MAX(0,C4-D4))</f>
         <v/>
@@ -22570,8 +26962,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
       <c r="E5" s="8">
         <f>IF(OR(C5="",D5=""),"",MAX(0,C5-D5))</f>
         <v/>
@@ -22617,8 +27009,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="8">
         <f>IF(OR(C6="",D6=""),"",MAX(0,C6-D6))</f>
         <v/>
@@ -22664,8 +27056,8 @@
           <t>SWALE_NODE</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="8">
         <f>IF(OR(C7="",D7=""),"",MAX(0,C7-D7))</f>
         <v/>
@@ -22713,8 +27105,8 @@
           <t>SWALE_NODE</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="8">
         <f>IF(OR(C8="",D8=""),"",MAX(0,C8-D8))</f>
         <v/>
@@ -22762,8 +27154,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="8">
         <f>IF(OR(C9="",D9=""),"",MAX(0,C9-D9))</f>
         <v/>
@@ -22801,16 +27193,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="8">
         <f>IF(OR(C10="",D10=""),"",MAX(0,C10-D10))</f>
         <v/>
@@ -22848,7 +27240,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -22856,8 +27248,8 @@
           <t>MH</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="8">
         <f>IF(OR(C11="",D11=""),"",MAX(0,C11-D11))</f>
         <v/>
@@ -22868,7 +27260,7 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
@@ -22895,45 +27287,36 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BASSIN-RET</t>
+          <t>J-OUEST-PU3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>RETENTION</t>
-        </is>
-      </c>
-      <c r="C12" s="7">
-        <f>Inputs!$B$37</f>
-        <v/>
-      </c>
-      <c r="D12" s="7">
-        <f>Inputs!$B$38</f>
-        <v/>
-      </c>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="8">
         <f>IF(OR(C12="",D12=""),"",MAX(0,C12-D12))</f>
         <v/>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>RECT</t>
-        </is>
-      </c>
-      <c r="G12" s="7">
-        <f>Inputs!$B$34</f>
-        <v/>
-      </c>
-      <c r="H12" s="7">
-        <f>Inputs!$B$35</f>
-        <v/>
-      </c>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="8">
         <f>IF(A12="","",IF(UPPER(TRIM(F12))="CIRC",PI()*(G12/2)^2*E12,IF(UPPER(TRIM(F12))="RECT",G12*H12*E12,"")))</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>30</v>
+      <c r="J12" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
       </c>
       <c r="K12" s="8">
         <f>IF(A12="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A12))</f>
@@ -22949,22 +27332,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="8">
         <f>IF(OR(C13="",D13=""),"",MAX(0,C13-D13))</f>
         <v/>
       </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="8">
         <f>IF(A13="","",IF(UPPER(TRIM(F13))="CIRC",PI()*(G13/2)^2*E13,IF(UPPER(TRIM(F13))="RECT",G13*H13*E13,"")))</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K13" s="8">
         <f>IF(A13="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A13))</f>
         <v/>
@@ -22979,22 +27379,39 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="8">
         <f>IF(OR(C14="",D14=""),"",MAX(0,C14-D14))</f>
         <v/>
       </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
         <f>IF(A14="","",IF(UPPER(TRIM(F14))="CIRC",PI()*(G14/2)^2*E14,IF(UPPER(TRIM(F14))="RECT",G14*H14*E14,"")))</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="n"/>
+      <c r="J14" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K14" s="8">
         <f>IF(A14="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A14))</f>
         <v/>
@@ -23009,22 +27426,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="8">
         <f>IF(OR(C15="",D15=""),"",MAX(0,C15-D15))</f>
         <v/>
       </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="8">
         <f>IF(A15="","",IF(UPPER(TRIM(F15))="CIRC",PI()*(G15/2)^2*E15,IF(UPPER(TRIM(F15))="RECT",G15*H15*E15,"")))</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="n"/>
+      <c r="J15" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K15" s="8">
         <f>IF(A15="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A15))</f>
         <v/>
@@ -23039,22 +27473,48 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>RETENTION</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>Inputs!$B$37</f>
+        <v/>
+      </c>
+      <c r="D16" s="7">
+        <f>Inputs!$B$38</f>
+        <v/>
+      </c>
       <c r="E16" s="8">
         <f>IF(OR(C16="",D16=""),"",MAX(0,C16-D16))</f>
         <v/>
       </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>RECT</t>
+        </is>
+      </c>
+      <c r="G16" s="7">
+        <f>Inputs!$B$34</f>
+        <v/>
+      </c>
+      <c r="H16" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
       <c r="I16" s="8">
         <f>IF(A16="","",IF(UPPER(TRIM(F16))="CIRC",PI()*(G16/2)^2*E16,IF(UPPER(TRIM(F16))="RECT",G16*H16*E16,"")))</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="n"/>
+      <c r="J16" s="7" t="n">
+        <v>30</v>
+      </c>
       <c r="K16" s="8">
         <f>IF(A16="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A16))</f>
         <v/>
@@ -29487,7 +33947,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Ouest haut</t>
+          <t>Ouest haut (grass 12.5 m2)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -29497,125 +33957,157 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Privilegier ecoulement de surface (noue peu profonde)</t>
+          <t>Ecoulement de surface peu profond</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>E05 (SWALE)</t>
+          <t>E05A (SWALE)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>profondeur ~0.20 m</t>
+          <t>depth ~0.15-0.20 m</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Limiter fouille profonde dans emprise chargee.</t>
+          <t>Eviter fouille profonde.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Traverse vers bassin</t>
+          <t>Traverse pave-uni 1 (6.7 m2)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Croisement inevitable</t>
+          <t>Traverse pietonne courte</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Croiser perpendiculaire + gaine + pente mini</t>
+          <t>Caniveau grille + pipe DN250</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>E06 (PIPE)</t>
+          <t>E05B (PIPE)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>slope 0.8%</t>
+          <t>slope ~1.0%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Verifier degagement vertical avec as-built.</t>
+          <t>Raccorder aux noeuds MH.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bande sud 2m</t>
+          <t>Ouest milieu (27.2 m2)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Emprise contrainte</t>
+          <t>Zone vegetale</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Bassin lineaire + noue/tranchee compacte</t>
+          <t>Noue de surface</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>E04 + BASSIN-RET</t>
+          <t>E05C (SWALE)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>width 2.0 m</t>
+          <t>depth ~0.15-0.20 m</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Stockage distribue + transfert au bassin.</t>
+          <t>Conduire vers traverse 2.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bande est arbres</t>
+          <t>Traverse pave-uni 2 (37.5 m2)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Zone racinaire</t>
+          <t>Traverse mineralisee</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Tranchee drainante + underdrain + barriere racinaire</t>
+          <t>Caniveau grille + pipe DN300</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>E01/E02 (TRENCH)</t>
+          <t>E05D (PIPE)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>offset &gt;=1.0 m</t>
+          <t>slope ~0.9%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Eviter conduite profonde continue en pied d arbres.</t>
+          <t>Verifier degagement lateraux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ouest aval grass (21.9 m2)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Approche bassin</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Noue de surface</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>E05E (SWALE)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>vers J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Transition vers E06.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Note: Les degagements finaux avec lateraux existants doivent etre confirmes par releves terrain/TQC avant IFC.</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Note: verifier elevations utilites existantes et degagements minimaux avant IFC (TQC obligatoire).</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -45,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -104,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -123,6 +128,8 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -665,6 +672,34 @@
       <c r="A22" t="inlineStr">
         <is>
           <t>Presentation pass added: row color coding in Elements_hybrides and one-page Decision_Summary tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mise a jour ouest: sequence grass/pave-uni/grass/pave-uni/grass modelee en E05A..E05E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Connexion entre types d elements implementee via AC:AH (controle continuité d invert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Geometrie J-OUEST pilotee par cotes plan dans Inputs!B40:B50 (23.58 m total; 11.1 m amont; 2.3 m pave1; 5.1 m pave2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E05A/E05C sont repartis proportionnellement aux aires (12.5 vs 27.2 m2); E05E est le solde vers le coin sud-ouest (21.9 m2).</t>
         </is>
       </c>
     </row>
@@ -1439,9 +1474,9 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
@@ -1473,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2288,230 @@
       <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Profondeur max recommandee dans zone lateraux ouest (approche conservatrice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>West_chain_total_m</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Somme E05A..E05E (chaine J-OUEST).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>West_amont_to_PU2_chain_m</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Cote plan visible (J-OUEST-AMONT jusqu'a fin zone amont avant troncon pave inferieur).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>West_pave1_short_span_m</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Traverse pave-uni courte (amont).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>West_pave2_span_m</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Traverse pave-uni inferieure (cote plan visible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>West_grass1_area_m2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 1 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>West_grass2_area_m2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 2 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>West_grass3_area_m2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 3 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>West_grass12_total_m</t>
+        </is>
+      </c>
+      <c r="B47" s="9">
+        <f>B41-B42</f>
+        <v/>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Longueur gazon amont+milieu (derivee).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>West_grass1_len_m</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>IFERROR(B47*B44/(B44+B45),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05A (repartition proportionnelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>West_grass2_len_m</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>IFERROR(B47*B45/(B44+B45),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05C (repartition proportionnelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>West_grass3_len_m</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>B40-B41-B43</f>
+        <v/>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05E (solde vers coin sud-ouest).</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2791,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05A</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -2578,7 +2837,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05B</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -2624,7 +2883,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05C</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -2670,7 +2929,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05D</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -2716,7 +2975,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05E</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -7081,7 +7340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB204"/>
+  <dimension ref="A1:AH204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7112,6 +7371,12 @@
     <col width="11" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
     <col width="34" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7269,6 +7534,36 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="AC3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_down_override_m</t>
+        </is>
+      </c>
+      <c r="AD3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_down_used_m</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>Invert_up_m</t>
+        </is>
+      </c>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>Downstream_invert_up_m</t>
+        </is>
+      </c>
+      <c r="AG3" s="6" t="inlineStr">
+        <is>
+          <t>Connection_delta_m</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="inlineStr">
+        <is>
+          <t>Connection_status</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -7376,13 +7671,34 @@
         <v/>
       </c>
       <c r="AA4" s="4">
-        <f>IF(A4="","",IF(OR(U4&gt;1,AND(X4&lt;&gt;"",X4&lt;Inputs!$B$16),AND(X4&lt;&gt;"",X4&gt;Inputs!$B$17),G4&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A4="","",IF(OR(U4&gt;1,AND(X4&lt;&gt;"",X4&lt;Inputs!$B$16),AND(X4&lt;&gt;"",X4&gt;Inputs!$B$17),G4&lt;Inputs!$B$18,AH4="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Bande est amont: tranchee drainante sous arbres (segment 1).</t>
-        </is>
+          <t>Bande est amont (arbres) - underdrain segment 1.</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="n"/>
+      <c r="AD4" s="8">
+        <f>IF(A4="","",IF(AC4&lt;&gt;"",AC4,IF(E4="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="8">
+        <f>IF(OR(AD4="",F4="",G4=""),"",AD4+F4*G4)</f>
+        <v/>
+      </c>
+      <c r="AF4" s="8">
+        <f>IF(OR(E4="",A4=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="8">
+        <f>IF(OR(AD4="",AF4=""),"",AD4-AF4)</f>
+        <v/>
+      </c>
+      <c r="AH4" s="4">
+        <f>IF(A4="","",IF(E4="","TERMINAL",IF(AG4="","INFO",IF(ABS(AG4)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -7491,13 +7807,34 @@
         <v/>
       </c>
       <c r="AA5" s="4">
-        <f>IF(A5="","",IF(OR(U5&gt;1,AND(X5&lt;&gt;"",X5&lt;Inputs!$B$16),AND(X5&lt;&gt;"",X5&gt;Inputs!$B$17),G5&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A5="","",IF(OR(U5&gt;1,AND(X5&lt;&gt;"",X5&lt;Inputs!$B$16),AND(X5&lt;&gt;"",X5&gt;Inputs!$B$17),G5&lt;Inputs!$B$18,AH5="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Bande est aval: tranchee drainante sous arbres (segment 2).</t>
-        </is>
+          <t>Bande est aval (arbres) - underdrain segment 2.</t>
+        </is>
+      </c>
+      <c r="AC5" s="7" t="n"/>
+      <c r="AD5" s="8">
+        <f>IF(A5="","",IF(AC5&lt;&gt;"",AC5,IF(E5="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="8">
+        <f>IF(OR(AD5="",F5="",G5=""),"",AD5+F5*G5)</f>
+        <v/>
+      </c>
+      <c r="AF5" s="8">
+        <f>IF(OR(E5="",A5=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="8">
+        <f>IF(OR(AD5="",AF5=""),"",AD5-AF5)</f>
+        <v/>
+      </c>
+      <c r="AH5" s="4">
+        <f>IF(A5="","",IF(E5="","TERMINAL",IF(AG5="","INFO",IF(ABS(AG5)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -7542,7 +7879,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
-      <c r="M6" s="7" t="n"/>
+      <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="n">
         <v>0</v>
       </c>
@@ -7595,13 +7932,34 @@
         <v/>
       </c>
       <c r="AA6" s="4">
-        <f>IF(A6="","",IF(OR(U6&gt;1,AND(X6&lt;&gt;"",X6&lt;Inputs!$B$16),AND(X6&lt;&gt;"",X6&gt;Inputs!$B$17),G6&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A6="","",IF(OR(U6&gt;1,AND(X6&lt;&gt;"",X6&lt;Inputs!$B$16),AND(X6&lt;&gt;"",X6&gt;Inputs!$B$17),G6&lt;Inputs!$B$18,AH6="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Collecteur est vers J-BASSIN-IN (hors zone racinaire dense).</t>
-        </is>
+          <t>Collecteur est vers entree bassin.</t>
+        </is>
+      </c>
+      <c r="AC6" s="7" t="n"/>
+      <c r="AD6" s="8">
+        <f>IF(A6="","",IF(AC6&lt;&gt;"",AC6,IF(E6="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="8">
+        <f>IF(OR(AD6="",F6="",G6=""),"",AD6+F6*G6)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="8">
+        <f>IF(OR(E6="",A6=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="8">
+        <f>IF(OR(AD6="",AF6=""),"",AD6-AF6)</f>
+        <v/>
+      </c>
+      <c r="AH6" s="4">
+        <f>IF(A6="","",IF(E6="","TERMINAL",IF(AG6="","INFO",IF(ABS(AG6)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -7630,9 +7988,8 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="F7" s="7">
-        <f>Inputs!$B$35</f>
-        <v/>
+      <c r="F7" s="7" t="n">
+        <v>16.1</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.008</v>
@@ -7707,19 +8064,40 @@
         <v/>
       </c>
       <c r="AA7" s="4">
-        <f>IF(A7="","",IF(OR(U7&gt;1,AND(X7&lt;&gt;"",X7&lt;Inputs!$B$16),AND(X7&lt;&gt;"",X7&gt;Inputs!$B$17),G7&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A7="","",IF(OR(U7&gt;1,AND(X7&lt;&gt;"",X7&lt;Inputs!$B$16),AND(X7&lt;&gt;"",X7&gt;Inputs!$B$17),G7&lt;Inputs!$B$18,AH7="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue/tranchee sud dans bande 2.0m vers bassin lineaire.</t>
-        </is>
+          <t>Noue sud principale (corridor 2 m).</t>
+        </is>
+      </c>
+      <c r="AC7" s="7" t="n"/>
+      <c r="AD7" s="8">
+        <f>IF(A7="","",IF(AC7&lt;&gt;"",AC7,IF(E7="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="8">
+        <f>IF(OR(AD7="",F7="",G7=""),"",AD7+F7*G7)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="8">
+        <f>IF(OR(E7="",A7=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="8">
+        <f>IF(OR(AD7="",AF7=""),"",AD7-AF7)</f>
+        <v/>
+      </c>
+      <c r="AH7" s="4">
+        <f>IF(A7="","",IF(E7="","TERMINAL",IF(AG7="","INFO",IF(ABS(AG7)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E05A</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -7734,31 +8112,32 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>16</v>
+          <t>E05B</t>
+        </is>
+      </c>
+      <c r="F8" s="15">
+        <f>Inputs!$B$48</f>
+        <v/>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8">
         <f>IF(A8="","",IF(H8&lt;&gt;"",H8,IF(UPPER(TRIM(B8))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B8))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="n"/>
+      <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="n">
         <v>0.8</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>3</v>
@@ -7815,19 +8194,40 @@
         <v/>
       </c>
       <c r="AA8" s="4">
-        <f>IF(A8="","",IF(OR(U8&gt;1,AND(X8&lt;&gt;"",X8&lt;Inputs!$B$16),AND(X8&lt;&gt;"",X8&gt;Inputs!$B$17),G8&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A8="","",IF(OR(U8&gt;1,AND(X8&lt;&gt;"",X8&lt;Inputs!$B$16),AND(X8&lt;&gt;"",X8&gt;Inputs!$B$17),G8&lt;Inputs!$B$18,AH8="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Collecte ouest avec conduite peu profonde/element lineaire compatible utilites.</t>
-        </is>
+          <t>Ouest gazon amont - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
+        </is>
+      </c>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="8">
+        <f>IF(A8="","",IF(AC8&lt;&gt;"",AC8,IF(E8="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="8">
+        <f>IF(OR(AD8="",F8="",G8=""),"",AD8+F8*G8)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="8">
+        <f>IF(OR(E8="",A8=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="8">
+        <f>IF(OR(AD8="",AF8=""),"",AD8-AF8)</f>
+        <v/>
+      </c>
+      <c r="AH8" s="4">
+        <f>IF(A8="","",IF(E8="","TERMINAL",IF(AG8="","INFO",IF(ABS(AG8)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05B</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -7837,24 +8237,25 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>8</v>
+          <t>E05C</t>
+        </is>
+      </c>
+      <c r="F9" s="15">
+        <f>Inputs!$B$42</f>
+        <v/>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8">
@@ -7862,11 +8263,11 @@
         <v/>
       </c>
       <c r="J9" s="7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="n"/>
+      <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
@@ -7919,54 +8320,84 @@
         <v/>
       </c>
       <c r="AA9" s="4">
-        <f>IF(A9="","",IF(OR(U9&gt;1,AND(X9&lt;&gt;"",X9&lt;Inputs!$B$16),AND(X9&lt;&gt;"",X9&gt;Inputs!$B$17),G9&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A9="","",IF(OR(U9&gt;1,AND(X9&lt;&gt;"",X9&lt;Inputs!$B$16),AND(X9&lt;&gt;"",X9&gt;Inputs!$B$17),G9&lt;Inputs!$B$18,AH9="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Branche ouest vers J-BASSIN-IN (traverse utilites avec precautions).</t>
-        </is>
+          <t>Ouest pave-uni court - longueur cotee 2.3 m.</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="n"/>
+      <c r="AD9" s="8">
+        <f>IF(A9="","",IF(AC9&lt;&gt;"",AC9,IF(E9="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="8">
+        <f>IF(OR(AD9="",F9="",G9=""),"",AD9+F9*G9)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="8">
+        <f>IF(OR(E9="",A9=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="8">
+        <f>IF(OR(AD9="",AF9=""),"",AD9-AF9)</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>IF(A9="","",IF(E9="","TERMINAL",IF(AG9="","INFO",IF(ABS(AG9)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05C</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>SWALE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BASSIN-RET</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="7" t="n">
-        <v>6</v>
+          <t>J-OUEST-PU3</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>E05D</t>
+        </is>
+      </c>
+      <c r="F10" s="15">
+        <f>Inputs!$B$49</f>
+        <v/>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8">
         <f>IF(A10="","",IF(H10&lt;&gt;"",H10,IF(UPPER(TRIM(B10))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B10))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>525</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="n"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
@@ -8019,32 +8450,80 @@
         <v/>
       </c>
       <c r="AA10" s="4">
-        <f>IF(A10="","",IF(OR(U10&gt;1,AND(X10&lt;&gt;"",X10&lt;Inputs!$B$16),AND(X10&lt;&gt;"",X10&gt;Inputs!$B$17),G10&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A10="","",IF(OR(U10&gt;1,AND(X10&lt;&gt;"",X10&lt;Inputs!$B$16),AND(X10&lt;&gt;"",X10&gt;Inputs!$B$17),G10&lt;Inputs!$B$18,AH10="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Injection finale vers BASSIN-RET lineaire sud.</t>
-        </is>
+          <t>Ouest gazon milieu - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
+        </is>
+      </c>
+      <c r="AC10" s="7" t="n"/>
+      <c r="AD10" s="8">
+        <f>IF(A10="","",IF(AC10&lt;&gt;"",AC10,IF(E10="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="8">
+        <f>IF(OR(AD10="",F10="",G10=""),"",AD10+F10*G10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="8">
+        <f>IF(OR(E10="",A10=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG10" s="8">
+        <f>IF(OR(AD10="",AF10=""),"",AD10-AF10)</f>
+        <v/>
+      </c>
+      <c r="AH10" s="4">
+        <f>IF(A10="","",IF(E10="","TERMINAL",IF(AG10="","INFO",IF(ABS(AG10)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E05D</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>E05E</t>
+        </is>
+      </c>
+      <c r="F11" s="15">
+        <f>Inputs!$B$43</f>
+        <v/>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
         <f>IF(A11="","",IF(H11&lt;&gt;"",H11,IF(UPPER(TRIM(B11))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B11))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
+      <c r="J11" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
@@ -8097,28 +8576,84 @@
         <v/>
       </c>
       <c r="AA11" s="4">
-        <f>IF(A11="","",IF(OR(U11&gt;1,AND(X11&lt;&gt;"",X11&lt;Inputs!$B$16),AND(X11&lt;&gt;"",X11&gt;Inputs!$B$17),G11&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB11" s="4" t="n"/>
+        <f>IF(A11="","",IF(OR(U11&gt;1,AND(X11&lt;&gt;"",X11&lt;Inputs!$B$16),AND(X11&lt;&gt;"",X11&gt;Inputs!$B$17),G11&lt;Inputs!$B$18,AH11="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>Ouest pave-uni inferieur - longueur cotee 5.1 m.</t>
+        </is>
+      </c>
+      <c r="AC11" s="7" t="n"/>
+      <c r="AD11" s="8">
+        <f>IF(A11="","",IF(AC11&lt;&gt;"",AC11,IF(E11="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="8">
+        <f>IF(OR(AD11="",F11="",G11=""),"",AD11+F11*G11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="8">
+        <f>IF(OR(E11="",A11=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG11" s="8">
+        <f>IF(OR(AD11="",AF11=""),"",AD11-AF11)</f>
+        <v/>
+      </c>
+      <c r="AH11" s="4">
+        <f>IF(A11="","",IF(E11="","TERMINAL",IF(AG11="","INFO",IF(ABS(AG11)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E05E</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SWALE</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="F12" s="15">
+        <f>Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="8">
         <f>IF(A12="","",IF(H12&lt;&gt;"",H12,IF(UPPER(TRIM(B12))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B12))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
@@ -8171,28 +8706,79 @@
         <v/>
       </c>
       <c r="AA12" s="4">
-        <f>IF(A12="","",IF(OR(U12&gt;1,AND(X12&lt;&gt;"",X12&lt;Inputs!$B$16),AND(X12&lt;&gt;"",X12&gt;Inputs!$B$17),G12&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB12" s="4" t="n"/>
+        <f>IF(A12="","",IF(OR(U12&gt;1,AND(X12&lt;&gt;"",X12&lt;Inputs!$B$16),AND(X12&lt;&gt;"",X12&gt;Inputs!$B$17),G12&lt;Inputs!$B$18,AH12="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>Ouest gazon aval - longueur solde sur chaine totale 23.58 m.</t>
+        </is>
+      </c>
+      <c r="AC12" s="7" t="n"/>
+      <c r="AD12" s="8">
+        <f>IF(A12="","",IF(AC12&lt;&gt;"",AC12,IF(E12="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="8">
+        <f>IF(OR(AD12="",F12="",G12=""),"",AD12+F12*G12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="8">
+        <f>IF(OR(E12="",A12=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG12" s="8">
+        <f>IF(OR(AD12="",AF12=""),"",AD12-AF12)</f>
+        <v/>
+      </c>
+      <c r="AH12" s="4">
+        <f>IF(A12="","",IF(E12="","TERMINAL",IF(AG12="","INFO",IF(ABS(AG12)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="8">
         <f>IF(A13="","",IF(H13&lt;&gt;"",H13,IF(UPPER(TRIM(B13))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B13))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
+      <c r="J13" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
@@ -8245,28 +8831,75 @@
         <v/>
       </c>
       <c r="AA13" s="4">
-        <f>IF(A13="","",IF(OR(U13&gt;1,AND(X13&lt;&gt;"",X13&lt;Inputs!$B$16),AND(X13&lt;&gt;"",X13&gt;Inputs!$B$17),G13&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB13" s="4" t="n"/>
+        <f>IF(A13="","",IF(OR(U13&gt;1,AND(X13&lt;&gt;"",X13&lt;Inputs!$B$16),AND(X13&lt;&gt;"",X13&gt;Inputs!$B$17),G13&lt;Inputs!$B$18,AH13="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>Branche ouest vers entree bassin.</t>
+        </is>
+      </c>
+      <c r="AC13" s="7" t="n"/>
+      <c r="AD13" s="8">
+        <f>IF(A13="","",IF(AC13&lt;&gt;"",AC13,IF(E13="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="8">
+        <f>IF(OR(AD13="",F13="",G13=""),"",AD13+F13*G13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="8">
+        <f>IF(OR(E13="",A13=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG13" s="8">
+        <f>IF(OR(AD13="",AF13=""),"",AD13-AF13)</f>
+        <v/>
+      </c>
+      <c r="AH13" s="4">
+        <f>IF(A13="","",IF(E13="","TERMINAL",IF(AG13="","INFO",IF(ABS(AG13)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
         <f>IF(A14="","",IF(H14&lt;&gt;"",H14,IF(UPPER(TRIM(B14))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B14))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
+      <c r="J14" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="n">
         <v>0</v>
       </c>
@@ -8319,10 +8952,35 @@
         <v/>
       </c>
       <c r="AA14" s="4">
-        <f>IF(A14="","",IF(OR(U14&gt;1,AND(X14&lt;&gt;"",X14&lt;Inputs!$B$16),AND(X14&lt;&gt;"",X14&gt;Inputs!$B$17),G14&lt;Inputs!$B$18),"CHECK","OK"))</f>
-        <v/>
-      </c>
-      <c r="AB14" s="4" t="n"/>
+        <f>IF(A14="","",IF(OR(U14&gt;1,AND(X14&lt;&gt;"",X14&lt;Inputs!$B$16),AND(X14&lt;&gt;"",X14&gt;Inputs!$B$17),G14&lt;Inputs!$B$18,AH14="CHECK"),"CHECK","OK"))</f>
+        <v/>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>Injection finale vers bassin retention.</t>
+        </is>
+      </c>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="8">
+        <f>IF(A14="","",IF(AC14&lt;&gt;"",AC14,IF(E14="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="8">
+        <f>IF(OR(AD14="",F14="",G14=""),"",AD14+F14*G14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="8">
+        <f>IF(OR(E14="",A14=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="8">
+        <f>IF(OR(AD14="",AF14=""),"",AD14-AF14)</f>
+        <v/>
+      </c>
+      <c r="AH14" s="4">
+        <f>IF(A14="","",IF(E14="","TERMINAL",IF(AG14="","INFO",IF(ABS(AG14)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
@@ -8341,9 +8999,7 @@
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" s="7" t="n"/>
       <c r="O15" s="8">
         <f>IF(A15="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A15))</f>
         <v/>
@@ -8393,10 +9049,31 @@
         <v/>
       </c>
       <c r="AA15" s="4">
-        <f>IF(A15="","",IF(OR(U15&gt;1,AND(X15&lt;&gt;"",X15&lt;Inputs!$B$16),AND(X15&lt;&gt;"",X15&gt;Inputs!$B$17),G15&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A15="","",IF(OR(U15&gt;1,AND(X15&lt;&gt;"",X15&lt;Inputs!$B$16),AND(X15&lt;&gt;"",X15&gt;Inputs!$B$17),G15&lt;Inputs!$B$18,AH15="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="8">
+        <f>IF(A15="","",IF(AC15&lt;&gt;"",AC15,IF(E15="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="8">
+        <f>IF(OR(AD15="",F15="",G15=""),"",AD15+F15*G15)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="8">
+        <f>IF(OR(E15="",A15=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="8">
+        <f>IF(OR(AD15="",AF15=""),"",AD15-AF15)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="4">
+        <f>IF(A15="","",IF(E15="","TERMINAL",IF(AG15="","INFO",IF(ABS(AG15)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -8415,9 +9092,7 @@
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" s="7" t="n"/>
       <c r="O16" s="8">
         <f>IF(A16="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A16))</f>
         <v/>
@@ -8467,10 +9142,31 @@
         <v/>
       </c>
       <c r="AA16" s="4">
-        <f>IF(A16="","",IF(OR(U16&gt;1,AND(X16&lt;&gt;"",X16&lt;Inputs!$B$16),AND(X16&lt;&gt;"",X16&gt;Inputs!$B$17),G16&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A16="","",IF(OR(U16&gt;1,AND(X16&lt;&gt;"",X16&lt;Inputs!$B$16),AND(X16&lt;&gt;"",X16&gt;Inputs!$B$17),G16&lt;Inputs!$B$18,AH16="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="7" t="n"/>
+      <c r="AD16" s="8">
+        <f>IF(A16="","",IF(AC16&lt;&gt;"",AC16,IF(E16="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="8">
+        <f>IF(OR(AD16="",F16="",G16=""),"",AD16+F16*G16)</f>
+        <v/>
+      </c>
+      <c r="AF16" s="8">
+        <f>IF(OR(E16="",A16=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="8">
+        <f>IF(OR(AD16="",AF16=""),"",AD16-AF16)</f>
+        <v/>
+      </c>
+      <c r="AH16" s="4">
+        <f>IF(A16="","",IF(E16="","TERMINAL",IF(AG16="","INFO",IF(ABS(AG16)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -8489,9 +9185,7 @@
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" s="7" t="n"/>
       <c r="O17" s="8">
         <f>IF(A17="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A17))</f>
         <v/>
@@ -8541,10 +9235,31 @@
         <v/>
       </c>
       <c r="AA17" s="4">
-        <f>IF(A17="","",IF(OR(U17&gt;1,AND(X17&lt;&gt;"",X17&lt;Inputs!$B$16),AND(X17&lt;&gt;"",X17&gt;Inputs!$B$17),G17&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A17="","",IF(OR(U17&gt;1,AND(X17&lt;&gt;"",X17&lt;Inputs!$B$16),AND(X17&lt;&gt;"",X17&gt;Inputs!$B$17),G17&lt;Inputs!$B$18,AH17="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="7" t="n"/>
+      <c r="AD17" s="8">
+        <f>IF(A17="","",IF(AC17&lt;&gt;"",AC17,IF(E17="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="8">
+        <f>IF(OR(AD17="",F17="",G17=""),"",AD17+F17*G17)</f>
+        <v/>
+      </c>
+      <c r="AF17" s="8">
+        <f>IF(OR(E17="",A17=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="8">
+        <f>IF(OR(AD17="",AF17=""),"",AD17-AF17)</f>
+        <v/>
+      </c>
+      <c r="AH17" s="4">
+        <f>IF(A17="","",IF(E17="","TERMINAL",IF(AG17="","INFO",IF(ABS(AG17)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -8563,9 +9278,7 @@
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" s="7" t="n"/>
       <c r="O18" s="8">
         <f>IF(A18="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A18))</f>
         <v/>
@@ -8615,10 +9328,31 @@
         <v/>
       </c>
       <c r="AA18" s="4">
-        <f>IF(A18="","",IF(OR(U18&gt;1,AND(X18&lt;&gt;"",X18&lt;Inputs!$B$16),AND(X18&lt;&gt;"",X18&gt;Inputs!$B$17),G18&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A18="","",IF(OR(U18&gt;1,AND(X18&lt;&gt;"",X18&lt;Inputs!$B$16),AND(X18&lt;&gt;"",X18&gt;Inputs!$B$17),G18&lt;Inputs!$B$18,AH18="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB18" s="4" t="n"/>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="8">
+        <f>IF(A18="","",IF(AC18&lt;&gt;"",AC18,IF(E18="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="8">
+        <f>IF(OR(AD18="",F18="",G18=""),"",AD18+F18*G18)</f>
+        <v/>
+      </c>
+      <c r="AF18" s="8">
+        <f>IF(OR(E18="",A18=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="8">
+        <f>IF(OR(AD18="",AF18=""),"",AD18-AF18)</f>
+        <v/>
+      </c>
+      <c r="AH18" s="4">
+        <f>IF(A18="","",IF(E18="","TERMINAL",IF(AG18="","INFO",IF(ABS(AG18)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -8637,9 +9371,7 @@
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" s="7" t="n"/>
       <c r="O19" s="8">
         <f>IF(A19="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A19))</f>
         <v/>
@@ -8689,10 +9421,31 @@
         <v/>
       </c>
       <c r="AA19" s="4">
-        <f>IF(A19="","",IF(OR(U19&gt;1,AND(X19&lt;&gt;"",X19&lt;Inputs!$B$16),AND(X19&lt;&gt;"",X19&gt;Inputs!$B$17),G19&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A19="","",IF(OR(U19&gt;1,AND(X19&lt;&gt;"",X19&lt;Inputs!$B$16),AND(X19&lt;&gt;"",X19&gt;Inputs!$B$17),G19&lt;Inputs!$B$18,AH19="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB19" s="4" t="n"/>
+      <c r="AC19" s="7" t="n"/>
+      <c r="AD19" s="8">
+        <f>IF(A19="","",IF(AC19&lt;&gt;"",AC19,IF(E19="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="8">
+        <f>IF(OR(AD19="",F19="",G19=""),"",AD19+F19*G19)</f>
+        <v/>
+      </c>
+      <c r="AF19" s="8">
+        <f>IF(OR(E19="",A19=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="8">
+        <f>IF(OR(AD19="",AF19=""),"",AD19-AF19)</f>
+        <v/>
+      </c>
+      <c r="AH19" s="4">
+        <f>IF(A19="","",IF(E19="","TERMINAL",IF(AG19="","INFO",IF(ABS(AG19)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -8711,9 +9464,7 @@
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" s="7" t="n"/>
       <c r="O20" s="8">
         <f>IF(A20="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A20))</f>
         <v/>
@@ -8763,10 +9514,31 @@
         <v/>
       </c>
       <c r="AA20" s="4">
-        <f>IF(A20="","",IF(OR(U20&gt;1,AND(X20&lt;&gt;"",X20&lt;Inputs!$B$16),AND(X20&lt;&gt;"",X20&gt;Inputs!$B$17),G20&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A20="","",IF(OR(U20&gt;1,AND(X20&lt;&gt;"",X20&lt;Inputs!$B$16),AND(X20&lt;&gt;"",X20&gt;Inputs!$B$17),G20&lt;Inputs!$B$18,AH20="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="7" t="n"/>
+      <c r="AD20" s="8">
+        <f>IF(A20="","",IF(AC20&lt;&gt;"",AC20,IF(E20="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="8">
+        <f>IF(OR(AD20="",F20="",G20=""),"",AD20+F20*G20)</f>
+        <v/>
+      </c>
+      <c r="AF20" s="8">
+        <f>IF(OR(E20="",A20=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="8">
+        <f>IF(OR(AD20="",AF20=""),"",AD20-AF20)</f>
+        <v/>
+      </c>
+      <c r="AH20" s="4">
+        <f>IF(A20="","",IF(E20="","TERMINAL",IF(AG20="","INFO",IF(ABS(AG20)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -8837,10 +9609,31 @@
         <v/>
       </c>
       <c r="AA21" s="4">
-        <f>IF(A21="","",IF(OR(U21&gt;1,AND(X21&lt;&gt;"",X21&lt;Inputs!$B$16),AND(X21&lt;&gt;"",X21&gt;Inputs!$B$17),G21&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A21="","",IF(OR(U21&gt;1,AND(X21&lt;&gt;"",X21&lt;Inputs!$B$16),AND(X21&lt;&gt;"",X21&gt;Inputs!$B$17),G21&lt;Inputs!$B$18,AH21="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB21" s="4" t="n"/>
+      <c r="AC21" s="7" t="n"/>
+      <c r="AD21" s="8">
+        <f>IF(A21="","",IF(AC21&lt;&gt;"",AC21,IF(E21="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="8">
+        <f>IF(OR(AD21="",F21="",G21=""),"",AD21+F21*G21)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="8">
+        <f>IF(OR(E21="",A21=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="8">
+        <f>IF(OR(AD21="",AF21=""),"",AD21-AF21)</f>
+        <v/>
+      </c>
+      <c r="AH21" s="4">
+        <f>IF(A21="","",IF(E21="","TERMINAL",IF(AG21="","INFO",IF(ABS(AG21)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -8911,10 +9704,31 @@
         <v/>
       </c>
       <c r="AA22" s="4">
-        <f>IF(A22="","",IF(OR(U22&gt;1,AND(X22&lt;&gt;"",X22&lt;Inputs!$B$16),AND(X22&lt;&gt;"",X22&gt;Inputs!$B$17),G22&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A22="","",IF(OR(U22&gt;1,AND(X22&lt;&gt;"",X22&lt;Inputs!$B$16),AND(X22&lt;&gt;"",X22&gt;Inputs!$B$17),G22&lt;Inputs!$B$18,AH22="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB22" s="4" t="n"/>
+      <c r="AC22" s="7" t="n"/>
+      <c r="AD22" s="8">
+        <f>IF(A22="","",IF(AC22&lt;&gt;"",AC22,IF(E22="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="8">
+        <f>IF(OR(AD22="",F22="",G22=""),"",AD22+F22*G22)</f>
+        <v/>
+      </c>
+      <c r="AF22" s="8">
+        <f>IF(OR(E22="",A22=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="8">
+        <f>IF(OR(AD22="",AF22=""),"",AD22-AF22)</f>
+        <v/>
+      </c>
+      <c r="AH22" s="4">
+        <f>IF(A22="","",IF(E22="","TERMINAL",IF(AG22="","INFO",IF(ABS(AG22)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -8985,10 +9799,31 @@
         <v/>
       </c>
       <c r="AA23" s="4">
-        <f>IF(A23="","",IF(OR(U23&gt;1,AND(X23&lt;&gt;"",X23&lt;Inputs!$B$16),AND(X23&lt;&gt;"",X23&gt;Inputs!$B$17),G23&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A23="","",IF(OR(U23&gt;1,AND(X23&lt;&gt;"",X23&lt;Inputs!$B$16),AND(X23&lt;&gt;"",X23&gt;Inputs!$B$17),G23&lt;Inputs!$B$18,AH23="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB23" s="4" t="n"/>
+      <c r="AC23" s="7" t="n"/>
+      <c r="AD23" s="8">
+        <f>IF(A23="","",IF(AC23&lt;&gt;"",AC23,IF(E23="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="8">
+        <f>IF(OR(AD23="",F23="",G23=""),"",AD23+F23*G23)</f>
+        <v/>
+      </c>
+      <c r="AF23" s="8">
+        <f>IF(OR(E23="",A23=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="8">
+        <f>IF(OR(AD23="",AF23=""),"",AD23-AF23)</f>
+        <v/>
+      </c>
+      <c r="AH23" s="4">
+        <f>IF(A23="","",IF(E23="","TERMINAL",IF(AG23="","INFO",IF(ABS(AG23)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -9059,10 +9894,31 @@
         <v/>
       </c>
       <c r="AA24" s="4">
-        <f>IF(A24="","",IF(OR(U24&gt;1,AND(X24&lt;&gt;"",X24&lt;Inputs!$B$16),AND(X24&lt;&gt;"",X24&gt;Inputs!$B$17),G24&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A24="","",IF(OR(U24&gt;1,AND(X24&lt;&gt;"",X24&lt;Inputs!$B$16),AND(X24&lt;&gt;"",X24&gt;Inputs!$B$17),G24&lt;Inputs!$B$18,AH24="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB24" s="4" t="n"/>
+      <c r="AC24" s="7" t="n"/>
+      <c r="AD24" s="8">
+        <f>IF(A24="","",IF(AC24&lt;&gt;"",AC24,IF(E24="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="8">
+        <f>IF(OR(AD24="",F24="",G24=""),"",AD24+F24*G24)</f>
+        <v/>
+      </c>
+      <c r="AF24" s="8">
+        <f>IF(OR(E24="",A24=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="8">
+        <f>IF(OR(AD24="",AF24=""),"",AD24-AF24)</f>
+        <v/>
+      </c>
+      <c r="AH24" s="4">
+        <f>IF(A24="","",IF(E24="","TERMINAL",IF(AG24="","INFO",IF(ABS(AG24)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -9133,10 +9989,31 @@
         <v/>
       </c>
       <c r="AA25" s="4">
-        <f>IF(A25="","",IF(OR(U25&gt;1,AND(X25&lt;&gt;"",X25&lt;Inputs!$B$16),AND(X25&lt;&gt;"",X25&gt;Inputs!$B$17),G25&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A25="","",IF(OR(U25&gt;1,AND(X25&lt;&gt;"",X25&lt;Inputs!$B$16),AND(X25&lt;&gt;"",X25&gt;Inputs!$B$17),G25&lt;Inputs!$B$18,AH25="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB25" s="4" t="n"/>
+      <c r="AC25" s="7" t="n"/>
+      <c r="AD25" s="8">
+        <f>IF(A25="","",IF(AC25&lt;&gt;"",AC25,IF(E25="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="8">
+        <f>IF(OR(AD25="",F25="",G25=""),"",AD25+F25*G25)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="8">
+        <f>IF(OR(E25="",A25=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="8">
+        <f>IF(OR(AD25="",AF25=""),"",AD25-AF25)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="4">
+        <f>IF(A25="","",IF(E25="","TERMINAL",IF(AG25="","INFO",IF(ABS(AG25)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -9207,10 +10084,31 @@
         <v/>
       </c>
       <c r="AA26" s="4">
-        <f>IF(A26="","",IF(OR(U26&gt;1,AND(X26&lt;&gt;"",X26&lt;Inputs!$B$16),AND(X26&lt;&gt;"",X26&gt;Inputs!$B$17),G26&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A26="","",IF(OR(U26&gt;1,AND(X26&lt;&gt;"",X26&lt;Inputs!$B$16),AND(X26&lt;&gt;"",X26&gt;Inputs!$B$17),G26&lt;Inputs!$B$18,AH26="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB26" s="4" t="n"/>
+      <c r="AC26" s="7" t="n"/>
+      <c r="AD26" s="8">
+        <f>IF(A26="","",IF(AC26&lt;&gt;"",AC26,IF(E26="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="8">
+        <f>IF(OR(AD26="",F26="",G26=""),"",AD26+F26*G26)</f>
+        <v/>
+      </c>
+      <c r="AF26" s="8">
+        <f>IF(OR(E26="",A26=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="8">
+        <f>IF(OR(AD26="",AF26=""),"",AD26-AF26)</f>
+        <v/>
+      </c>
+      <c r="AH26" s="4">
+        <f>IF(A26="","",IF(E26="","TERMINAL",IF(AG26="","INFO",IF(ABS(AG26)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -9281,10 +10179,31 @@
         <v/>
       </c>
       <c r="AA27" s="4">
-        <f>IF(A27="","",IF(OR(U27&gt;1,AND(X27&lt;&gt;"",X27&lt;Inputs!$B$16),AND(X27&lt;&gt;"",X27&gt;Inputs!$B$17),G27&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A27="","",IF(OR(U27&gt;1,AND(X27&lt;&gt;"",X27&lt;Inputs!$B$16),AND(X27&lt;&gt;"",X27&gt;Inputs!$B$17),G27&lt;Inputs!$B$18,AH27="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB27" s="4" t="n"/>
+      <c r="AC27" s="7" t="n"/>
+      <c r="AD27" s="8">
+        <f>IF(A27="","",IF(AC27&lt;&gt;"",AC27,IF(E27="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="8">
+        <f>IF(OR(AD27="",F27="",G27=""),"",AD27+F27*G27)</f>
+        <v/>
+      </c>
+      <c r="AF27" s="8">
+        <f>IF(OR(E27="",A27=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="8">
+        <f>IF(OR(AD27="",AF27=""),"",AD27-AF27)</f>
+        <v/>
+      </c>
+      <c r="AH27" s="4">
+        <f>IF(A27="","",IF(E27="","TERMINAL",IF(AG27="","INFO",IF(ABS(AG27)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -9355,10 +10274,31 @@
         <v/>
       </c>
       <c r="AA28" s="4">
-        <f>IF(A28="","",IF(OR(U28&gt;1,AND(X28&lt;&gt;"",X28&lt;Inputs!$B$16),AND(X28&lt;&gt;"",X28&gt;Inputs!$B$17),G28&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A28="","",IF(OR(U28&gt;1,AND(X28&lt;&gt;"",X28&lt;Inputs!$B$16),AND(X28&lt;&gt;"",X28&gt;Inputs!$B$17),G28&lt;Inputs!$B$18,AH28="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB28" s="4" t="n"/>
+      <c r="AC28" s="7" t="n"/>
+      <c r="AD28" s="8">
+        <f>IF(A28="","",IF(AC28&lt;&gt;"",AC28,IF(E28="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="8">
+        <f>IF(OR(AD28="",F28="",G28=""),"",AD28+F28*G28)</f>
+        <v/>
+      </c>
+      <c r="AF28" s="8">
+        <f>IF(OR(E28="",A28=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="8">
+        <f>IF(OR(AD28="",AF28=""),"",AD28-AF28)</f>
+        <v/>
+      </c>
+      <c r="AH28" s="4">
+        <f>IF(A28="","",IF(E28="","TERMINAL",IF(AG28="","INFO",IF(ABS(AG28)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -9429,10 +10369,31 @@
         <v/>
       </c>
       <c r="AA29" s="4">
-        <f>IF(A29="","",IF(OR(U29&gt;1,AND(X29&lt;&gt;"",X29&lt;Inputs!$B$16),AND(X29&lt;&gt;"",X29&gt;Inputs!$B$17),G29&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A29="","",IF(OR(U29&gt;1,AND(X29&lt;&gt;"",X29&lt;Inputs!$B$16),AND(X29&lt;&gt;"",X29&gt;Inputs!$B$17),G29&lt;Inputs!$B$18,AH29="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB29" s="4" t="n"/>
+      <c r="AC29" s="7" t="n"/>
+      <c r="AD29" s="8">
+        <f>IF(A29="","",IF(AC29&lt;&gt;"",AC29,IF(E29="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="8">
+        <f>IF(OR(AD29="",F29="",G29=""),"",AD29+F29*G29)</f>
+        <v/>
+      </c>
+      <c r="AF29" s="8">
+        <f>IF(OR(E29="",A29=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="8">
+        <f>IF(OR(AD29="",AF29=""),"",AD29-AF29)</f>
+        <v/>
+      </c>
+      <c r="AH29" s="4">
+        <f>IF(A29="","",IF(E29="","TERMINAL",IF(AG29="","INFO",IF(ABS(AG29)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -9503,10 +10464,31 @@
         <v/>
       </c>
       <c r="AA30" s="4">
-        <f>IF(A30="","",IF(OR(U30&gt;1,AND(X30&lt;&gt;"",X30&lt;Inputs!$B$16),AND(X30&lt;&gt;"",X30&gt;Inputs!$B$17),G30&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A30="","",IF(OR(U30&gt;1,AND(X30&lt;&gt;"",X30&lt;Inputs!$B$16),AND(X30&lt;&gt;"",X30&gt;Inputs!$B$17),G30&lt;Inputs!$B$18,AH30="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB30" s="4" t="n"/>
+      <c r="AC30" s="7" t="n"/>
+      <c r="AD30" s="8">
+        <f>IF(A30="","",IF(AC30&lt;&gt;"",AC30,IF(E30="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="8">
+        <f>IF(OR(AD30="",F30="",G30=""),"",AD30+F30*G30)</f>
+        <v/>
+      </c>
+      <c r="AF30" s="8">
+        <f>IF(OR(E30="",A30=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="8">
+        <f>IF(OR(AD30="",AF30=""),"",AD30-AF30)</f>
+        <v/>
+      </c>
+      <c r="AH30" s="4">
+        <f>IF(A30="","",IF(E30="","TERMINAL",IF(AG30="","INFO",IF(ABS(AG30)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -9577,10 +10559,31 @@
         <v/>
       </c>
       <c r="AA31" s="4">
-        <f>IF(A31="","",IF(OR(U31&gt;1,AND(X31&lt;&gt;"",X31&lt;Inputs!$B$16),AND(X31&lt;&gt;"",X31&gt;Inputs!$B$17),G31&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A31="","",IF(OR(U31&gt;1,AND(X31&lt;&gt;"",X31&lt;Inputs!$B$16),AND(X31&lt;&gt;"",X31&gt;Inputs!$B$17),G31&lt;Inputs!$B$18,AH31="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB31" s="4" t="n"/>
+      <c r="AC31" s="7" t="n"/>
+      <c r="AD31" s="8">
+        <f>IF(A31="","",IF(AC31&lt;&gt;"",AC31,IF(E31="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="8">
+        <f>IF(OR(AD31="",F31="",G31=""),"",AD31+F31*G31)</f>
+        <v/>
+      </c>
+      <c r="AF31" s="8">
+        <f>IF(OR(E31="",A31=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="8">
+        <f>IF(OR(AD31="",AF31=""),"",AD31-AF31)</f>
+        <v/>
+      </c>
+      <c r="AH31" s="4">
+        <f>IF(A31="","",IF(E31="","TERMINAL",IF(AG31="","INFO",IF(ABS(AG31)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -9651,10 +10654,31 @@
         <v/>
       </c>
       <c r="AA32" s="4">
-        <f>IF(A32="","",IF(OR(U32&gt;1,AND(X32&lt;&gt;"",X32&lt;Inputs!$B$16),AND(X32&lt;&gt;"",X32&gt;Inputs!$B$17),G32&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A32="","",IF(OR(U32&gt;1,AND(X32&lt;&gt;"",X32&lt;Inputs!$B$16),AND(X32&lt;&gt;"",X32&gt;Inputs!$B$17),G32&lt;Inputs!$B$18,AH32="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB32" s="4" t="n"/>
+      <c r="AC32" s="7" t="n"/>
+      <c r="AD32" s="8">
+        <f>IF(A32="","",IF(AC32&lt;&gt;"",AC32,IF(E32="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="8">
+        <f>IF(OR(AD32="",F32="",G32=""),"",AD32+F32*G32)</f>
+        <v/>
+      </c>
+      <c r="AF32" s="8">
+        <f>IF(OR(E32="",A32=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="8">
+        <f>IF(OR(AD32="",AF32=""),"",AD32-AF32)</f>
+        <v/>
+      </c>
+      <c r="AH32" s="4">
+        <f>IF(A32="","",IF(E32="","TERMINAL",IF(AG32="","INFO",IF(ABS(AG32)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -9725,10 +10749,31 @@
         <v/>
       </c>
       <c r="AA33" s="4">
-        <f>IF(A33="","",IF(OR(U33&gt;1,AND(X33&lt;&gt;"",X33&lt;Inputs!$B$16),AND(X33&lt;&gt;"",X33&gt;Inputs!$B$17),G33&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A33="","",IF(OR(U33&gt;1,AND(X33&lt;&gt;"",X33&lt;Inputs!$B$16),AND(X33&lt;&gt;"",X33&gt;Inputs!$B$17),G33&lt;Inputs!$B$18,AH33="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB33" s="4" t="n"/>
+      <c r="AC33" s="7" t="n"/>
+      <c r="AD33" s="8">
+        <f>IF(A33="","",IF(AC33&lt;&gt;"",AC33,IF(E33="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="8">
+        <f>IF(OR(AD33="",F33="",G33=""),"",AD33+F33*G33)</f>
+        <v/>
+      </c>
+      <c r="AF33" s="8">
+        <f>IF(OR(E33="",A33=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="8">
+        <f>IF(OR(AD33="",AF33=""),"",AD33-AF33)</f>
+        <v/>
+      </c>
+      <c r="AH33" s="4">
+        <f>IF(A33="","",IF(E33="","TERMINAL",IF(AG33="","INFO",IF(ABS(AG33)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -9799,10 +10844,31 @@
         <v/>
       </c>
       <c r="AA34" s="4">
-        <f>IF(A34="","",IF(OR(U34&gt;1,AND(X34&lt;&gt;"",X34&lt;Inputs!$B$16),AND(X34&lt;&gt;"",X34&gt;Inputs!$B$17),G34&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A34="","",IF(OR(U34&gt;1,AND(X34&lt;&gt;"",X34&lt;Inputs!$B$16),AND(X34&lt;&gt;"",X34&gt;Inputs!$B$17),G34&lt;Inputs!$B$18,AH34="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB34" s="4" t="n"/>
+      <c r="AC34" s="7" t="n"/>
+      <c r="AD34" s="8">
+        <f>IF(A34="","",IF(AC34&lt;&gt;"",AC34,IF(E34="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="8">
+        <f>IF(OR(AD34="",F34="",G34=""),"",AD34+F34*G34)</f>
+        <v/>
+      </c>
+      <c r="AF34" s="8">
+        <f>IF(OR(E34="",A34=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="8">
+        <f>IF(OR(AD34="",AF34=""),"",AD34-AF34)</f>
+        <v/>
+      </c>
+      <c r="AH34" s="4">
+        <f>IF(A34="","",IF(E34="","TERMINAL",IF(AG34="","INFO",IF(ABS(AG34)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -9873,10 +10939,31 @@
         <v/>
       </c>
       <c r="AA35" s="4">
-        <f>IF(A35="","",IF(OR(U35&gt;1,AND(X35&lt;&gt;"",X35&lt;Inputs!$B$16),AND(X35&lt;&gt;"",X35&gt;Inputs!$B$17),G35&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A35="","",IF(OR(U35&gt;1,AND(X35&lt;&gt;"",X35&lt;Inputs!$B$16),AND(X35&lt;&gt;"",X35&gt;Inputs!$B$17),G35&lt;Inputs!$B$18,AH35="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB35" s="4" t="n"/>
+      <c r="AC35" s="7" t="n"/>
+      <c r="AD35" s="8">
+        <f>IF(A35="","",IF(AC35&lt;&gt;"",AC35,IF(E35="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="8">
+        <f>IF(OR(AD35="",F35="",G35=""),"",AD35+F35*G35)</f>
+        <v/>
+      </c>
+      <c r="AF35" s="8">
+        <f>IF(OR(E35="",A35=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="8">
+        <f>IF(OR(AD35="",AF35=""),"",AD35-AF35)</f>
+        <v/>
+      </c>
+      <c r="AH35" s="4">
+        <f>IF(A35="","",IF(E35="","TERMINAL",IF(AG35="","INFO",IF(ABS(AG35)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -9947,10 +11034,31 @@
         <v/>
       </c>
       <c r="AA36" s="4">
-        <f>IF(A36="","",IF(OR(U36&gt;1,AND(X36&lt;&gt;"",X36&lt;Inputs!$B$16),AND(X36&lt;&gt;"",X36&gt;Inputs!$B$17),G36&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A36="","",IF(OR(U36&gt;1,AND(X36&lt;&gt;"",X36&lt;Inputs!$B$16),AND(X36&lt;&gt;"",X36&gt;Inputs!$B$17),G36&lt;Inputs!$B$18,AH36="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB36" s="4" t="n"/>
+      <c r="AC36" s="7" t="n"/>
+      <c r="AD36" s="8">
+        <f>IF(A36="","",IF(AC36&lt;&gt;"",AC36,IF(E36="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="8">
+        <f>IF(OR(AD36="",F36="",G36=""),"",AD36+F36*G36)</f>
+        <v/>
+      </c>
+      <c r="AF36" s="8">
+        <f>IF(OR(E36="",A36=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="8">
+        <f>IF(OR(AD36="",AF36=""),"",AD36-AF36)</f>
+        <v/>
+      </c>
+      <c r="AH36" s="4">
+        <f>IF(A36="","",IF(E36="","TERMINAL",IF(AG36="","INFO",IF(ABS(AG36)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -10021,10 +11129,31 @@
         <v/>
       </c>
       <c r="AA37" s="4">
-        <f>IF(A37="","",IF(OR(U37&gt;1,AND(X37&lt;&gt;"",X37&lt;Inputs!$B$16),AND(X37&lt;&gt;"",X37&gt;Inputs!$B$17),G37&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A37="","",IF(OR(U37&gt;1,AND(X37&lt;&gt;"",X37&lt;Inputs!$B$16),AND(X37&lt;&gt;"",X37&gt;Inputs!$B$17),G37&lt;Inputs!$B$18,AH37="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB37" s="4" t="n"/>
+      <c r="AC37" s="7" t="n"/>
+      <c r="AD37" s="8">
+        <f>IF(A37="","",IF(AC37&lt;&gt;"",AC37,IF(E37="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="8">
+        <f>IF(OR(AD37="",F37="",G37=""),"",AD37+F37*G37)</f>
+        <v/>
+      </c>
+      <c r="AF37" s="8">
+        <f>IF(OR(E37="",A37=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="8">
+        <f>IF(OR(AD37="",AF37=""),"",AD37-AF37)</f>
+        <v/>
+      </c>
+      <c r="AH37" s="4">
+        <f>IF(A37="","",IF(E37="","TERMINAL",IF(AG37="","INFO",IF(ABS(AG37)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -10095,10 +11224,31 @@
         <v/>
       </c>
       <c r="AA38" s="4">
-        <f>IF(A38="","",IF(OR(U38&gt;1,AND(X38&lt;&gt;"",X38&lt;Inputs!$B$16),AND(X38&lt;&gt;"",X38&gt;Inputs!$B$17),G38&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A38="","",IF(OR(U38&gt;1,AND(X38&lt;&gt;"",X38&lt;Inputs!$B$16),AND(X38&lt;&gt;"",X38&gt;Inputs!$B$17),G38&lt;Inputs!$B$18,AH38="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB38" s="4" t="n"/>
+      <c r="AC38" s="7" t="n"/>
+      <c r="AD38" s="8">
+        <f>IF(A38="","",IF(AC38&lt;&gt;"",AC38,IF(E38="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE38" s="8">
+        <f>IF(OR(AD38="",F38="",G38=""),"",AD38+F38*G38)</f>
+        <v/>
+      </c>
+      <c r="AF38" s="8">
+        <f>IF(OR(E38="",A38=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG38" s="8">
+        <f>IF(OR(AD38="",AF38=""),"",AD38-AF38)</f>
+        <v/>
+      </c>
+      <c r="AH38" s="4">
+        <f>IF(A38="","",IF(E38="","TERMINAL",IF(AG38="","INFO",IF(ABS(AG38)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -10169,10 +11319,31 @@
         <v/>
       </c>
       <c r="AA39" s="4">
-        <f>IF(A39="","",IF(OR(U39&gt;1,AND(X39&lt;&gt;"",X39&lt;Inputs!$B$16),AND(X39&lt;&gt;"",X39&gt;Inputs!$B$17),G39&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A39="","",IF(OR(U39&gt;1,AND(X39&lt;&gt;"",X39&lt;Inputs!$B$16),AND(X39&lt;&gt;"",X39&gt;Inputs!$B$17),G39&lt;Inputs!$B$18,AH39="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB39" s="4" t="n"/>
+      <c r="AC39" s="7" t="n"/>
+      <c r="AD39" s="8">
+        <f>IF(A39="","",IF(AC39&lt;&gt;"",AC39,IF(E39="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE39" s="8">
+        <f>IF(OR(AD39="",F39="",G39=""),"",AD39+F39*G39)</f>
+        <v/>
+      </c>
+      <c r="AF39" s="8">
+        <f>IF(OR(E39="",A39=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG39" s="8">
+        <f>IF(OR(AD39="",AF39=""),"",AD39-AF39)</f>
+        <v/>
+      </c>
+      <c r="AH39" s="4">
+        <f>IF(A39="","",IF(E39="","TERMINAL",IF(AG39="","INFO",IF(ABS(AG39)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -10243,10 +11414,31 @@
         <v/>
       </c>
       <c r="AA40" s="4">
-        <f>IF(A40="","",IF(OR(U40&gt;1,AND(X40&lt;&gt;"",X40&lt;Inputs!$B$16),AND(X40&lt;&gt;"",X40&gt;Inputs!$B$17),G40&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A40="","",IF(OR(U40&gt;1,AND(X40&lt;&gt;"",X40&lt;Inputs!$B$16),AND(X40&lt;&gt;"",X40&gt;Inputs!$B$17),G40&lt;Inputs!$B$18,AH40="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB40" s="4" t="n"/>
+      <c r="AC40" s="7" t="n"/>
+      <c r="AD40" s="8">
+        <f>IF(A40="","",IF(AC40&lt;&gt;"",AC40,IF(E40="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE40" s="8">
+        <f>IF(OR(AD40="",F40="",G40=""),"",AD40+F40*G40)</f>
+        <v/>
+      </c>
+      <c r="AF40" s="8">
+        <f>IF(OR(E40="",A40=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG40" s="8">
+        <f>IF(OR(AD40="",AF40=""),"",AD40-AF40)</f>
+        <v/>
+      </c>
+      <c r="AH40" s="4">
+        <f>IF(A40="","",IF(E40="","TERMINAL",IF(AG40="","INFO",IF(ABS(AG40)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -10317,10 +11509,31 @@
         <v/>
       </c>
       <c r="AA41" s="4">
-        <f>IF(A41="","",IF(OR(U41&gt;1,AND(X41&lt;&gt;"",X41&lt;Inputs!$B$16),AND(X41&lt;&gt;"",X41&gt;Inputs!$B$17),G41&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A41="","",IF(OR(U41&gt;1,AND(X41&lt;&gt;"",X41&lt;Inputs!$B$16),AND(X41&lt;&gt;"",X41&gt;Inputs!$B$17),G41&lt;Inputs!$B$18,AH41="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB41" s="4" t="n"/>
+      <c r="AC41" s="7" t="n"/>
+      <c r="AD41" s="8">
+        <f>IF(A41="","",IF(AC41&lt;&gt;"",AC41,IF(E41="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE41" s="8">
+        <f>IF(OR(AD41="",F41="",G41=""),"",AD41+F41*G41)</f>
+        <v/>
+      </c>
+      <c r="AF41" s="8">
+        <f>IF(OR(E41="",A41=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG41" s="8">
+        <f>IF(OR(AD41="",AF41=""),"",AD41-AF41)</f>
+        <v/>
+      </c>
+      <c r="AH41" s="4">
+        <f>IF(A41="","",IF(E41="","TERMINAL",IF(AG41="","INFO",IF(ABS(AG41)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -10391,10 +11604,31 @@
         <v/>
       </c>
       <c r="AA42" s="4">
-        <f>IF(A42="","",IF(OR(U42&gt;1,AND(X42&lt;&gt;"",X42&lt;Inputs!$B$16),AND(X42&lt;&gt;"",X42&gt;Inputs!$B$17),G42&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A42="","",IF(OR(U42&gt;1,AND(X42&lt;&gt;"",X42&lt;Inputs!$B$16),AND(X42&lt;&gt;"",X42&gt;Inputs!$B$17),G42&lt;Inputs!$B$18,AH42="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB42" s="4" t="n"/>
+      <c r="AC42" s="7" t="n"/>
+      <c r="AD42" s="8">
+        <f>IF(A42="","",IF(AC42&lt;&gt;"",AC42,IF(E42="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE42" s="8">
+        <f>IF(OR(AD42="",F42="",G42=""),"",AD42+F42*G42)</f>
+        <v/>
+      </c>
+      <c r="AF42" s="8">
+        <f>IF(OR(E42="",A42=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG42" s="8">
+        <f>IF(OR(AD42="",AF42=""),"",AD42-AF42)</f>
+        <v/>
+      </c>
+      <c r="AH42" s="4">
+        <f>IF(A42="","",IF(E42="","TERMINAL",IF(AG42="","INFO",IF(ABS(AG42)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -10465,10 +11699,31 @@
         <v/>
       </c>
       <c r="AA43" s="4">
-        <f>IF(A43="","",IF(OR(U43&gt;1,AND(X43&lt;&gt;"",X43&lt;Inputs!$B$16),AND(X43&lt;&gt;"",X43&gt;Inputs!$B$17),G43&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A43="","",IF(OR(U43&gt;1,AND(X43&lt;&gt;"",X43&lt;Inputs!$B$16),AND(X43&lt;&gt;"",X43&gt;Inputs!$B$17),G43&lt;Inputs!$B$18,AH43="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB43" s="4" t="n"/>
+      <c r="AC43" s="7" t="n"/>
+      <c r="AD43" s="8">
+        <f>IF(A43="","",IF(AC43&lt;&gt;"",AC43,IF(E43="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE43" s="8">
+        <f>IF(OR(AD43="",F43="",G43=""),"",AD43+F43*G43)</f>
+        <v/>
+      </c>
+      <c r="AF43" s="8">
+        <f>IF(OR(E43="",A43=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG43" s="8">
+        <f>IF(OR(AD43="",AF43=""),"",AD43-AF43)</f>
+        <v/>
+      </c>
+      <c r="AH43" s="4">
+        <f>IF(A43="","",IF(E43="","TERMINAL",IF(AG43="","INFO",IF(ABS(AG43)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -10539,10 +11794,31 @@
         <v/>
       </c>
       <c r="AA44" s="4">
-        <f>IF(A44="","",IF(OR(U44&gt;1,AND(X44&lt;&gt;"",X44&lt;Inputs!$B$16),AND(X44&lt;&gt;"",X44&gt;Inputs!$B$17),G44&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A44="","",IF(OR(U44&gt;1,AND(X44&lt;&gt;"",X44&lt;Inputs!$B$16),AND(X44&lt;&gt;"",X44&gt;Inputs!$B$17),G44&lt;Inputs!$B$18,AH44="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB44" s="4" t="n"/>
+      <c r="AC44" s="7" t="n"/>
+      <c r="AD44" s="8">
+        <f>IF(A44="","",IF(AC44&lt;&gt;"",AC44,IF(E44="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE44" s="8">
+        <f>IF(OR(AD44="",F44="",G44=""),"",AD44+F44*G44)</f>
+        <v/>
+      </c>
+      <c r="AF44" s="8">
+        <f>IF(OR(E44="",A44=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG44" s="8">
+        <f>IF(OR(AD44="",AF44=""),"",AD44-AF44)</f>
+        <v/>
+      </c>
+      <c r="AH44" s="4">
+        <f>IF(A44="","",IF(E44="","TERMINAL",IF(AG44="","INFO",IF(ABS(AG44)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -10613,10 +11889,31 @@
         <v/>
       </c>
       <c r="AA45" s="4">
-        <f>IF(A45="","",IF(OR(U45&gt;1,AND(X45&lt;&gt;"",X45&lt;Inputs!$B$16),AND(X45&lt;&gt;"",X45&gt;Inputs!$B$17),G45&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A45="","",IF(OR(U45&gt;1,AND(X45&lt;&gt;"",X45&lt;Inputs!$B$16),AND(X45&lt;&gt;"",X45&gt;Inputs!$B$17),G45&lt;Inputs!$B$18,AH45="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB45" s="4" t="n"/>
+      <c r="AC45" s="7" t="n"/>
+      <c r="AD45" s="8">
+        <f>IF(A45="","",IF(AC45&lt;&gt;"",AC45,IF(E45="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE45" s="8">
+        <f>IF(OR(AD45="",F45="",G45=""),"",AD45+F45*G45)</f>
+        <v/>
+      </c>
+      <c r="AF45" s="8">
+        <f>IF(OR(E45="",A45=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG45" s="8">
+        <f>IF(OR(AD45="",AF45=""),"",AD45-AF45)</f>
+        <v/>
+      </c>
+      <c r="AH45" s="4">
+        <f>IF(A45="","",IF(E45="","TERMINAL",IF(AG45="","INFO",IF(ABS(AG45)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -10687,10 +11984,31 @@
         <v/>
       </c>
       <c r="AA46" s="4">
-        <f>IF(A46="","",IF(OR(U46&gt;1,AND(X46&lt;&gt;"",X46&lt;Inputs!$B$16),AND(X46&lt;&gt;"",X46&gt;Inputs!$B$17),G46&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A46="","",IF(OR(U46&gt;1,AND(X46&lt;&gt;"",X46&lt;Inputs!$B$16),AND(X46&lt;&gt;"",X46&gt;Inputs!$B$17),G46&lt;Inputs!$B$18,AH46="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB46" s="4" t="n"/>
+      <c r="AC46" s="7" t="n"/>
+      <c r="AD46" s="8">
+        <f>IF(A46="","",IF(AC46&lt;&gt;"",AC46,IF(E46="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE46" s="8">
+        <f>IF(OR(AD46="",F46="",G46=""),"",AD46+F46*G46)</f>
+        <v/>
+      </c>
+      <c r="AF46" s="8">
+        <f>IF(OR(E46="",A46=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG46" s="8">
+        <f>IF(OR(AD46="",AF46=""),"",AD46-AF46)</f>
+        <v/>
+      </c>
+      <c r="AH46" s="4">
+        <f>IF(A46="","",IF(E46="","TERMINAL",IF(AG46="","INFO",IF(ABS(AG46)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -10761,10 +12079,31 @@
         <v/>
       </c>
       <c r="AA47" s="4">
-        <f>IF(A47="","",IF(OR(U47&gt;1,AND(X47&lt;&gt;"",X47&lt;Inputs!$B$16),AND(X47&lt;&gt;"",X47&gt;Inputs!$B$17),G47&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A47="","",IF(OR(U47&gt;1,AND(X47&lt;&gt;"",X47&lt;Inputs!$B$16),AND(X47&lt;&gt;"",X47&gt;Inputs!$B$17),G47&lt;Inputs!$B$18,AH47="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB47" s="4" t="n"/>
+      <c r="AC47" s="7" t="n"/>
+      <c r="AD47" s="8">
+        <f>IF(A47="","",IF(AC47&lt;&gt;"",AC47,IF(E47="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE47" s="8">
+        <f>IF(OR(AD47="",F47="",G47=""),"",AD47+F47*G47)</f>
+        <v/>
+      </c>
+      <c r="AF47" s="8">
+        <f>IF(OR(E47="",A47=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG47" s="8">
+        <f>IF(OR(AD47="",AF47=""),"",AD47-AF47)</f>
+        <v/>
+      </c>
+      <c r="AH47" s="4">
+        <f>IF(A47="","",IF(E47="","TERMINAL",IF(AG47="","INFO",IF(ABS(AG47)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -10835,10 +12174,31 @@
         <v/>
       </c>
       <c r="AA48" s="4">
-        <f>IF(A48="","",IF(OR(U48&gt;1,AND(X48&lt;&gt;"",X48&lt;Inputs!$B$16),AND(X48&lt;&gt;"",X48&gt;Inputs!$B$17),G48&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A48="","",IF(OR(U48&gt;1,AND(X48&lt;&gt;"",X48&lt;Inputs!$B$16),AND(X48&lt;&gt;"",X48&gt;Inputs!$B$17),G48&lt;Inputs!$B$18,AH48="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB48" s="4" t="n"/>
+      <c r="AC48" s="7" t="n"/>
+      <c r="AD48" s="8">
+        <f>IF(A48="","",IF(AC48&lt;&gt;"",AC48,IF(E48="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE48" s="8">
+        <f>IF(OR(AD48="",F48="",G48=""),"",AD48+F48*G48)</f>
+        <v/>
+      </c>
+      <c r="AF48" s="8">
+        <f>IF(OR(E48="",A48=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG48" s="8">
+        <f>IF(OR(AD48="",AF48=""),"",AD48-AF48)</f>
+        <v/>
+      </c>
+      <c r="AH48" s="4">
+        <f>IF(A48="","",IF(E48="","TERMINAL",IF(AG48="","INFO",IF(ABS(AG48)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -10909,10 +12269,31 @@
         <v/>
       </c>
       <c r="AA49" s="4">
-        <f>IF(A49="","",IF(OR(U49&gt;1,AND(X49&lt;&gt;"",X49&lt;Inputs!$B$16),AND(X49&lt;&gt;"",X49&gt;Inputs!$B$17),G49&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A49="","",IF(OR(U49&gt;1,AND(X49&lt;&gt;"",X49&lt;Inputs!$B$16),AND(X49&lt;&gt;"",X49&gt;Inputs!$B$17),G49&lt;Inputs!$B$18,AH49="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB49" s="4" t="n"/>
+      <c r="AC49" s="7" t="n"/>
+      <c r="AD49" s="8">
+        <f>IF(A49="","",IF(AC49&lt;&gt;"",AC49,IF(E49="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE49" s="8">
+        <f>IF(OR(AD49="",F49="",G49=""),"",AD49+F49*G49)</f>
+        <v/>
+      </c>
+      <c r="AF49" s="8">
+        <f>IF(OR(E49="",A49=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG49" s="8">
+        <f>IF(OR(AD49="",AF49=""),"",AD49-AF49)</f>
+        <v/>
+      </c>
+      <c r="AH49" s="4">
+        <f>IF(A49="","",IF(E49="","TERMINAL",IF(AG49="","INFO",IF(ABS(AG49)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -10983,10 +12364,31 @@
         <v/>
       </c>
       <c r="AA50" s="4">
-        <f>IF(A50="","",IF(OR(U50&gt;1,AND(X50&lt;&gt;"",X50&lt;Inputs!$B$16),AND(X50&lt;&gt;"",X50&gt;Inputs!$B$17),G50&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A50="","",IF(OR(U50&gt;1,AND(X50&lt;&gt;"",X50&lt;Inputs!$B$16),AND(X50&lt;&gt;"",X50&gt;Inputs!$B$17),G50&lt;Inputs!$B$18,AH50="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB50" s="4" t="n"/>
+      <c r="AC50" s="7" t="n"/>
+      <c r="AD50" s="8">
+        <f>IF(A50="","",IF(AC50&lt;&gt;"",AC50,IF(E50="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE50" s="8">
+        <f>IF(OR(AD50="",F50="",G50=""),"",AD50+F50*G50)</f>
+        <v/>
+      </c>
+      <c r="AF50" s="8">
+        <f>IF(OR(E50="",A50=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG50" s="8">
+        <f>IF(OR(AD50="",AF50=""),"",AD50-AF50)</f>
+        <v/>
+      </c>
+      <c r="AH50" s="4">
+        <f>IF(A50="","",IF(E50="","TERMINAL",IF(AG50="","INFO",IF(ABS(AG50)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -11057,10 +12459,31 @@
         <v/>
       </c>
       <c r="AA51" s="4">
-        <f>IF(A51="","",IF(OR(U51&gt;1,AND(X51&lt;&gt;"",X51&lt;Inputs!$B$16),AND(X51&lt;&gt;"",X51&gt;Inputs!$B$17),G51&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A51="","",IF(OR(U51&gt;1,AND(X51&lt;&gt;"",X51&lt;Inputs!$B$16),AND(X51&lt;&gt;"",X51&gt;Inputs!$B$17),G51&lt;Inputs!$B$18,AH51="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB51" s="4" t="n"/>
+      <c r="AC51" s="7" t="n"/>
+      <c r="AD51" s="8">
+        <f>IF(A51="","",IF(AC51&lt;&gt;"",AC51,IF(E51="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE51" s="8">
+        <f>IF(OR(AD51="",F51="",G51=""),"",AD51+F51*G51)</f>
+        <v/>
+      </c>
+      <c r="AF51" s="8">
+        <f>IF(OR(E51="",A51=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG51" s="8">
+        <f>IF(OR(AD51="",AF51=""),"",AD51-AF51)</f>
+        <v/>
+      </c>
+      <c r="AH51" s="4">
+        <f>IF(A51="","",IF(E51="","TERMINAL",IF(AG51="","INFO",IF(ABS(AG51)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -11131,10 +12554,31 @@
         <v/>
       </c>
       <c r="AA52" s="4">
-        <f>IF(A52="","",IF(OR(U52&gt;1,AND(X52&lt;&gt;"",X52&lt;Inputs!$B$16),AND(X52&lt;&gt;"",X52&gt;Inputs!$B$17),G52&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A52="","",IF(OR(U52&gt;1,AND(X52&lt;&gt;"",X52&lt;Inputs!$B$16),AND(X52&lt;&gt;"",X52&gt;Inputs!$B$17),G52&lt;Inputs!$B$18,AH52="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB52" s="4" t="n"/>
+      <c r="AC52" s="7" t="n"/>
+      <c r="AD52" s="8">
+        <f>IF(A52="","",IF(AC52&lt;&gt;"",AC52,IF(E52="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE52" s="8">
+        <f>IF(OR(AD52="",F52="",G52=""),"",AD52+F52*G52)</f>
+        <v/>
+      </c>
+      <c r="AF52" s="8">
+        <f>IF(OR(E52="",A52=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG52" s="8">
+        <f>IF(OR(AD52="",AF52=""),"",AD52-AF52)</f>
+        <v/>
+      </c>
+      <c r="AH52" s="4">
+        <f>IF(A52="","",IF(E52="","TERMINAL",IF(AG52="","INFO",IF(ABS(AG52)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -11205,10 +12649,31 @@
         <v/>
       </c>
       <c r="AA53" s="4">
-        <f>IF(A53="","",IF(OR(U53&gt;1,AND(X53&lt;&gt;"",X53&lt;Inputs!$B$16),AND(X53&lt;&gt;"",X53&gt;Inputs!$B$17),G53&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A53="","",IF(OR(U53&gt;1,AND(X53&lt;&gt;"",X53&lt;Inputs!$B$16),AND(X53&lt;&gt;"",X53&gt;Inputs!$B$17),G53&lt;Inputs!$B$18,AH53="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB53" s="4" t="n"/>
+      <c r="AC53" s="7" t="n"/>
+      <c r="AD53" s="8">
+        <f>IF(A53="","",IF(AC53&lt;&gt;"",AC53,IF(E53="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE53" s="8">
+        <f>IF(OR(AD53="",F53="",G53=""),"",AD53+F53*G53)</f>
+        <v/>
+      </c>
+      <c r="AF53" s="8">
+        <f>IF(OR(E53="",A53=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG53" s="8">
+        <f>IF(OR(AD53="",AF53=""),"",AD53-AF53)</f>
+        <v/>
+      </c>
+      <c r="AH53" s="4">
+        <f>IF(A53="","",IF(E53="","TERMINAL",IF(AG53="","INFO",IF(ABS(AG53)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -11279,10 +12744,31 @@
         <v/>
       </c>
       <c r="AA54" s="4">
-        <f>IF(A54="","",IF(OR(U54&gt;1,AND(X54&lt;&gt;"",X54&lt;Inputs!$B$16),AND(X54&lt;&gt;"",X54&gt;Inputs!$B$17),G54&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A54="","",IF(OR(U54&gt;1,AND(X54&lt;&gt;"",X54&lt;Inputs!$B$16),AND(X54&lt;&gt;"",X54&gt;Inputs!$B$17),G54&lt;Inputs!$B$18,AH54="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB54" s="4" t="n"/>
+      <c r="AC54" s="7" t="n"/>
+      <c r="AD54" s="8">
+        <f>IF(A54="","",IF(AC54&lt;&gt;"",AC54,IF(E54="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE54" s="8">
+        <f>IF(OR(AD54="",F54="",G54=""),"",AD54+F54*G54)</f>
+        <v/>
+      </c>
+      <c r="AF54" s="8">
+        <f>IF(OR(E54="",A54=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG54" s="8">
+        <f>IF(OR(AD54="",AF54=""),"",AD54-AF54)</f>
+        <v/>
+      </c>
+      <c r="AH54" s="4">
+        <f>IF(A54="","",IF(E54="","TERMINAL",IF(AG54="","INFO",IF(ABS(AG54)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -11353,10 +12839,31 @@
         <v/>
       </c>
       <c r="AA55" s="4">
-        <f>IF(A55="","",IF(OR(U55&gt;1,AND(X55&lt;&gt;"",X55&lt;Inputs!$B$16),AND(X55&lt;&gt;"",X55&gt;Inputs!$B$17),G55&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A55="","",IF(OR(U55&gt;1,AND(X55&lt;&gt;"",X55&lt;Inputs!$B$16),AND(X55&lt;&gt;"",X55&gt;Inputs!$B$17),G55&lt;Inputs!$B$18,AH55="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB55" s="4" t="n"/>
+      <c r="AC55" s="7" t="n"/>
+      <c r="AD55" s="8">
+        <f>IF(A55="","",IF(AC55&lt;&gt;"",AC55,IF(E55="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE55" s="8">
+        <f>IF(OR(AD55="",F55="",G55=""),"",AD55+F55*G55)</f>
+        <v/>
+      </c>
+      <c r="AF55" s="8">
+        <f>IF(OR(E55="",A55=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG55" s="8">
+        <f>IF(OR(AD55="",AF55=""),"",AD55-AF55)</f>
+        <v/>
+      </c>
+      <c r="AH55" s="4">
+        <f>IF(A55="","",IF(E55="","TERMINAL",IF(AG55="","INFO",IF(ABS(AG55)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -11427,10 +12934,31 @@
         <v/>
       </c>
       <c r="AA56" s="4">
-        <f>IF(A56="","",IF(OR(U56&gt;1,AND(X56&lt;&gt;"",X56&lt;Inputs!$B$16),AND(X56&lt;&gt;"",X56&gt;Inputs!$B$17),G56&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A56="","",IF(OR(U56&gt;1,AND(X56&lt;&gt;"",X56&lt;Inputs!$B$16),AND(X56&lt;&gt;"",X56&gt;Inputs!$B$17),G56&lt;Inputs!$B$18,AH56="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB56" s="4" t="n"/>
+      <c r="AC56" s="7" t="n"/>
+      <c r="AD56" s="8">
+        <f>IF(A56="","",IF(AC56&lt;&gt;"",AC56,IF(E56="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE56" s="8">
+        <f>IF(OR(AD56="",F56="",G56=""),"",AD56+F56*G56)</f>
+        <v/>
+      </c>
+      <c r="AF56" s="8">
+        <f>IF(OR(E56="",A56=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG56" s="8">
+        <f>IF(OR(AD56="",AF56=""),"",AD56-AF56)</f>
+        <v/>
+      </c>
+      <c r="AH56" s="4">
+        <f>IF(A56="","",IF(E56="","TERMINAL",IF(AG56="","INFO",IF(ABS(AG56)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -11501,10 +13029,31 @@
         <v/>
       </c>
       <c r="AA57" s="4">
-        <f>IF(A57="","",IF(OR(U57&gt;1,AND(X57&lt;&gt;"",X57&lt;Inputs!$B$16),AND(X57&lt;&gt;"",X57&gt;Inputs!$B$17),G57&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A57="","",IF(OR(U57&gt;1,AND(X57&lt;&gt;"",X57&lt;Inputs!$B$16),AND(X57&lt;&gt;"",X57&gt;Inputs!$B$17),G57&lt;Inputs!$B$18,AH57="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB57" s="4" t="n"/>
+      <c r="AC57" s="7" t="n"/>
+      <c r="AD57" s="8">
+        <f>IF(A57="","",IF(AC57&lt;&gt;"",AC57,IF(E57="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE57" s="8">
+        <f>IF(OR(AD57="",F57="",G57=""),"",AD57+F57*G57)</f>
+        <v/>
+      </c>
+      <c r="AF57" s="8">
+        <f>IF(OR(E57="",A57=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG57" s="8">
+        <f>IF(OR(AD57="",AF57=""),"",AD57-AF57)</f>
+        <v/>
+      </c>
+      <c r="AH57" s="4">
+        <f>IF(A57="","",IF(E57="","TERMINAL",IF(AG57="","INFO",IF(ABS(AG57)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -11575,10 +13124,31 @@
         <v/>
       </c>
       <c r="AA58" s="4">
-        <f>IF(A58="","",IF(OR(U58&gt;1,AND(X58&lt;&gt;"",X58&lt;Inputs!$B$16),AND(X58&lt;&gt;"",X58&gt;Inputs!$B$17),G58&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A58="","",IF(OR(U58&gt;1,AND(X58&lt;&gt;"",X58&lt;Inputs!$B$16),AND(X58&lt;&gt;"",X58&gt;Inputs!$B$17),G58&lt;Inputs!$B$18,AH58="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB58" s="4" t="n"/>
+      <c r="AC58" s="7" t="n"/>
+      <c r="AD58" s="8">
+        <f>IF(A58="","",IF(AC58&lt;&gt;"",AC58,IF(E58="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE58" s="8">
+        <f>IF(OR(AD58="",F58="",G58=""),"",AD58+F58*G58)</f>
+        <v/>
+      </c>
+      <c r="AF58" s="8">
+        <f>IF(OR(E58="",A58=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG58" s="8">
+        <f>IF(OR(AD58="",AF58=""),"",AD58-AF58)</f>
+        <v/>
+      </c>
+      <c r="AH58" s="4">
+        <f>IF(A58="","",IF(E58="","TERMINAL",IF(AG58="","INFO",IF(ABS(AG58)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -11649,10 +13219,31 @@
         <v/>
       </c>
       <c r="AA59" s="4">
-        <f>IF(A59="","",IF(OR(U59&gt;1,AND(X59&lt;&gt;"",X59&lt;Inputs!$B$16),AND(X59&lt;&gt;"",X59&gt;Inputs!$B$17),G59&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A59="","",IF(OR(U59&gt;1,AND(X59&lt;&gt;"",X59&lt;Inputs!$B$16),AND(X59&lt;&gt;"",X59&gt;Inputs!$B$17),G59&lt;Inputs!$B$18,AH59="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB59" s="4" t="n"/>
+      <c r="AC59" s="7" t="n"/>
+      <c r="AD59" s="8">
+        <f>IF(A59="","",IF(AC59&lt;&gt;"",AC59,IF(E59="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE59" s="8">
+        <f>IF(OR(AD59="",F59="",G59=""),"",AD59+F59*G59)</f>
+        <v/>
+      </c>
+      <c r="AF59" s="8">
+        <f>IF(OR(E59="",A59=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG59" s="8">
+        <f>IF(OR(AD59="",AF59=""),"",AD59-AF59)</f>
+        <v/>
+      </c>
+      <c r="AH59" s="4">
+        <f>IF(A59="","",IF(E59="","TERMINAL",IF(AG59="","INFO",IF(ABS(AG59)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -11723,10 +13314,31 @@
         <v/>
       </c>
       <c r="AA60" s="4">
-        <f>IF(A60="","",IF(OR(U60&gt;1,AND(X60&lt;&gt;"",X60&lt;Inputs!$B$16),AND(X60&lt;&gt;"",X60&gt;Inputs!$B$17),G60&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A60="","",IF(OR(U60&gt;1,AND(X60&lt;&gt;"",X60&lt;Inputs!$B$16),AND(X60&lt;&gt;"",X60&gt;Inputs!$B$17),G60&lt;Inputs!$B$18,AH60="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB60" s="4" t="n"/>
+      <c r="AC60" s="7" t="n"/>
+      <c r="AD60" s="8">
+        <f>IF(A60="","",IF(AC60&lt;&gt;"",AC60,IF(E60="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE60" s="8">
+        <f>IF(OR(AD60="",F60="",G60=""),"",AD60+F60*G60)</f>
+        <v/>
+      </c>
+      <c r="AF60" s="8">
+        <f>IF(OR(E60="",A60=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG60" s="8">
+        <f>IF(OR(AD60="",AF60=""),"",AD60-AF60)</f>
+        <v/>
+      </c>
+      <c r="AH60" s="4">
+        <f>IF(A60="","",IF(E60="","TERMINAL",IF(AG60="","INFO",IF(ABS(AG60)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -11797,10 +13409,31 @@
         <v/>
       </c>
       <c r="AA61" s="4">
-        <f>IF(A61="","",IF(OR(U61&gt;1,AND(X61&lt;&gt;"",X61&lt;Inputs!$B$16),AND(X61&lt;&gt;"",X61&gt;Inputs!$B$17),G61&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A61="","",IF(OR(U61&gt;1,AND(X61&lt;&gt;"",X61&lt;Inputs!$B$16),AND(X61&lt;&gt;"",X61&gt;Inputs!$B$17),G61&lt;Inputs!$B$18,AH61="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB61" s="4" t="n"/>
+      <c r="AC61" s="7" t="n"/>
+      <c r="AD61" s="8">
+        <f>IF(A61="","",IF(AC61&lt;&gt;"",AC61,IF(E61="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE61" s="8">
+        <f>IF(OR(AD61="",F61="",G61=""),"",AD61+F61*G61)</f>
+        <v/>
+      </c>
+      <c r="AF61" s="8">
+        <f>IF(OR(E61="",A61=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG61" s="8">
+        <f>IF(OR(AD61="",AF61=""),"",AD61-AF61)</f>
+        <v/>
+      </c>
+      <c r="AH61" s="4">
+        <f>IF(A61="","",IF(E61="","TERMINAL",IF(AG61="","INFO",IF(ABS(AG61)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -11871,10 +13504,31 @@
         <v/>
       </c>
       <c r="AA62" s="4">
-        <f>IF(A62="","",IF(OR(U62&gt;1,AND(X62&lt;&gt;"",X62&lt;Inputs!$B$16),AND(X62&lt;&gt;"",X62&gt;Inputs!$B$17),G62&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A62="","",IF(OR(U62&gt;1,AND(X62&lt;&gt;"",X62&lt;Inputs!$B$16),AND(X62&lt;&gt;"",X62&gt;Inputs!$B$17),G62&lt;Inputs!$B$18,AH62="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB62" s="4" t="n"/>
+      <c r="AC62" s="7" t="n"/>
+      <c r="AD62" s="8">
+        <f>IF(A62="","",IF(AC62&lt;&gt;"",AC62,IF(E62="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE62" s="8">
+        <f>IF(OR(AD62="",F62="",G62=""),"",AD62+F62*G62)</f>
+        <v/>
+      </c>
+      <c r="AF62" s="8">
+        <f>IF(OR(E62="",A62=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG62" s="8">
+        <f>IF(OR(AD62="",AF62=""),"",AD62-AF62)</f>
+        <v/>
+      </c>
+      <c r="AH62" s="4">
+        <f>IF(A62="","",IF(E62="","TERMINAL",IF(AG62="","INFO",IF(ABS(AG62)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -11945,10 +13599,31 @@
         <v/>
       </c>
       <c r="AA63" s="4">
-        <f>IF(A63="","",IF(OR(U63&gt;1,AND(X63&lt;&gt;"",X63&lt;Inputs!$B$16),AND(X63&lt;&gt;"",X63&gt;Inputs!$B$17),G63&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A63="","",IF(OR(U63&gt;1,AND(X63&lt;&gt;"",X63&lt;Inputs!$B$16),AND(X63&lt;&gt;"",X63&gt;Inputs!$B$17),G63&lt;Inputs!$B$18,AH63="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB63" s="4" t="n"/>
+      <c r="AC63" s="7" t="n"/>
+      <c r="AD63" s="8">
+        <f>IF(A63="","",IF(AC63&lt;&gt;"",AC63,IF(E63="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE63" s="8">
+        <f>IF(OR(AD63="",F63="",G63=""),"",AD63+F63*G63)</f>
+        <v/>
+      </c>
+      <c r="AF63" s="8">
+        <f>IF(OR(E63="",A63=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG63" s="8">
+        <f>IF(OR(AD63="",AF63=""),"",AD63-AF63)</f>
+        <v/>
+      </c>
+      <c r="AH63" s="4">
+        <f>IF(A63="","",IF(E63="","TERMINAL",IF(AG63="","INFO",IF(ABS(AG63)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -12019,10 +13694,31 @@
         <v/>
       </c>
       <c r="AA64" s="4">
-        <f>IF(A64="","",IF(OR(U64&gt;1,AND(X64&lt;&gt;"",X64&lt;Inputs!$B$16),AND(X64&lt;&gt;"",X64&gt;Inputs!$B$17),G64&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A64="","",IF(OR(U64&gt;1,AND(X64&lt;&gt;"",X64&lt;Inputs!$B$16),AND(X64&lt;&gt;"",X64&gt;Inputs!$B$17),G64&lt;Inputs!$B$18,AH64="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB64" s="4" t="n"/>
+      <c r="AC64" s="7" t="n"/>
+      <c r="AD64" s="8">
+        <f>IF(A64="","",IF(AC64&lt;&gt;"",AC64,IF(E64="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE64" s="8">
+        <f>IF(OR(AD64="",F64="",G64=""),"",AD64+F64*G64)</f>
+        <v/>
+      </c>
+      <c r="AF64" s="8">
+        <f>IF(OR(E64="",A64=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG64" s="8">
+        <f>IF(OR(AD64="",AF64=""),"",AD64-AF64)</f>
+        <v/>
+      </c>
+      <c r="AH64" s="4">
+        <f>IF(A64="","",IF(E64="","TERMINAL",IF(AG64="","INFO",IF(ABS(AG64)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -12093,10 +13789,31 @@
         <v/>
       </c>
       <c r="AA65" s="4">
-        <f>IF(A65="","",IF(OR(U65&gt;1,AND(X65&lt;&gt;"",X65&lt;Inputs!$B$16),AND(X65&lt;&gt;"",X65&gt;Inputs!$B$17),G65&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A65="","",IF(OR(U65&gt;1,AND(X65&lt;&gt;"",X65&lt;Inputs!$B$16),AND(X65&lt;&gt;"",X65&gt;Inputs!$B$17),G65&lt;Inputs!$B$18,AH65="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB65" s="4" t="n"/>
+      <c r="AC65" s="7" t="n"/>
+      <c r="AD65" s="8">
+        <f>IF(A65="","",IF(AC65&lt;&gt;"",AC65,IF(E65="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE65" s="8">
+        <f>IF(OR(AD65="",F65="",G65=""),"",AD65+F65*G65)</f>
+        <v/>
+      </c>
+      <c r="AF65" s="8">
+        <f>IF(OR(E65="",A65=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG65" s="8">
+        <f>IF(OR(AD65="",AF65=""),"",AD65-AF65)</f>
+        <v/>
+      </c>
+      <c r="AH65" s="4">
+        <f>IF(A65="","",IF(E65="","TERMINAL",IF(AG65="","INFO",IF(ABS(AG65)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n"/>
@@ -12167,10 +13884,31 @@
         <v/>
       </c>
       <c r="AA66" s="4">
-        <f>IF(A66="","",IF(OR(U66&gt;1,AND(X66&lt;&gt;"",X66&lt;Inputs!$B$16),AND(X66&lt;&gt;"",X66&gt;Inputs!$B$17),G66&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A66="","",IF(OR(U66&gt;1,AND(X66&lt;&gt;"",X66&lt;Inputs!$B$16),AND(X66&lt;&gt;"",X66&gt;Inputs!$B$17),G66&lt;Inputs!$B$18,AH66="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB66" s="4" t="n"/>
+      <c r="AC66" s="7" t="n"/>
+      <c r="AD66" s="8">
+        <f>IF(A66="","",IF(AC66&lt;&gt;"",AC66,IF(E66="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE66" s="8">
+        <f>IF(OR(AD66="",F66="",G66=""),"",AD66+F66*G66)</f>
+        <v/>
+      </c>
+      <c r="AF66" s="8">
+        <f>IF(OR(E66="",A66=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG66" s="8">
+        <f>IF(OR(AD66="",AF66=""),"",AD66-AF66)</f>
+        <v/>
+      </c>
+      <c r="AH66" s="4">
+        <f>IF(A66="","",IF(E66="","TERMINAL",IF(AG66="","INFO",IF(ABS(AG66)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -12241,10 +13979,31 @@
         <v/>
       </c>
       <c r="AA67" s="4">
-        <f>IF(A67="","",IF(OR(U67&gt;1,AND(X67&lt;&gt;"",X67&lt;Inputs!$B$16),AND(X67&lt;&gt;"",X67&gt;Inputs!$B$17),G67&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A67="","",IF(OR(U67&gt;1,AND(X67&lt;&gt;"",X67&lt;Inputs!$B$16),AND(X67&lt;&gt;"",X67&gt;Inputs!$B$17),G67&lt;Inputs!$B$18,AH67="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB67" s="4" t="n"/>
+      <c r="AC67" s="7" t="n"/>
+      <c r="AD67" s="8">
+        <f>IF(A67="","",IF(AC67&lt;&gt;"",AC67,IF(E67="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE67" s="8">
+        <f>IF(OR(AD67="",F67="",G67=""),"",AD67+F67*G67)</f>
+        <v/>
+      </c>
+      <c r="AF67" s="8">
+        <f>IF(OR(E67="",A67=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG67" s="8">
+        <f>IF(OR(AD67="",AF67=""),"",AD67-AF67)</f>
+        <v/>
+      </c>
+      <c r="AH67" s="4">
+        <f>IF(A67="","",IF(E67="","TERMINAL",IF(AG67="","INFO",IF(ABS(AG67)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n"/>
@@ -12315,10 +14074,31 @@
         <v/>
       </c>
       <c r="AA68" s="4">
-        <f>IF(A68="","",IF(OR(U68&gt;1,AND(X68&lt;&gt;"",X68&lt;Inputs!$B$16),AND(X68&lt;&gt;"",X68&gt;Inputs!$B$17),G68&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A68="","",IF(OR(U68&gt;1,AND(X68&lt;&gt;"",X68&lt;Inputs!$B$16),AND(X68&lt;&gt;"",X68&gt;Inputs!$B$17),G68&lt;Inputs!$B$18,AH68="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB68" s="4" t="n"/>
+      <c r="AC68" s="7" t="n"/>
+      <c r="AD68" s="8">
+        <f>IF(A68="","",IF(AC68&lt;&gt;"",AC68,IF(E68="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE68" s="8">
+        <f>IF(OR(AD68="",F68="",G68=""),"",AD68+F68*G68)</f>
+        <v/>
+      </c>
+      <c r="AF68" s="8">
+        <f>IF(OR(E68="",A68=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG68" s="8">
+        <f>IF(OR(AD68="",AF68=""),"",AD68-AF68)</f>
+        <v/>
+      </c>
+      <c r="AH68" s="4">
+        <f>IF(A68="","",IF(E68="","TERMINAL",IF(AG68="","INFO",IF(ABS(AG68)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -12389,10 +14169,31 @@
         <v/>
       </c>
       <c r="AA69" s="4">
-        <f>IF(A69="","",IF(OR(U69&gt;1,AND(X69&lt;&gt;"",X69&lt;Inputs!$B$16),AND(X69&lt;&gt;"",X69&gt;Inputs!$B$17),G69&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A69="","",IF(OR(U69&gt;1,AND(X69&lt;&gt;"",X69&lt;Inputs!$B$16),AND(X69&lt;&gt;"",X69&gt;Inputs!$B$17),G69&lt;Inputs!$B$18,AH69="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB69" s="4" t="n"/>
+      <c r="AC69" s="7" t="n"/>
+      <c r="AD69" s="8">
+        <f>IF(A69="","",IF(AC69&lt;&gt;"",AC69,IF(E69="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE69" s="8">
+        <f>IF(OR(AD69="",F69="",G69=""),"",AD69+F69*G69)</f>
+        <v/>
+      </c>
+      <c r="AF69" s="8">
+        <f>IF(OR(E69="",A69=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG69" s="8">
+        <f>IF(OR(AD69="",AF69=""),"",AD69-AF69)</f>
+        <v/>
+      </c>
+      <c r="AH69" s="4">
+        <f>IF(A69="","",IF(E69="","TERMINAL",IF(AG69="","INFO",IF(ABS(AG69)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n"/>
@@ -12463,10 +14264,31 @@
         <v/>
       </c>
       <c r="AA70" s="4">
-        <f>IF(A70="","",IF(OR(U70&gt;1,AND(X70&lt;&gt;"",X70&lt;Inputs!$B$16),AND(X70&lt;&gt;"",X70&gt;Inputs!$B$17),G70&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A70="","",IF(OR(U70&gt;1,AND(X70&lt;&gt;"",X70&lt;Inputs!$B$16),AND(X70&lt;&gt;"",X70&gt;Inputs!$B$17),G70&lt;Inputs!$B$18,AH70="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB70" s="4" t="n"/>
+      <c r="AC70" s="7" t="n"/>
+      <c r="AD70" s="8">
+        <f>IF(A70="","",IF(AC70&lt;&gt;"",AC70,IF(E70="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE70" s="8">
+        <f>IF(OR(AD70="",F70="",G70=""),"",AD70+F70*G70)</f>
+        <v/>
+      </c>
+      <c r="AF70" s="8">
+        <f>IF(OR(E70="",A70=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG70" s="8">
+        <f>IF(OR(AD70="",AF70=""),"",AD70-AF70)</f>
+        <v/>
+      </c>
+      <c r="AH70" s="4">
+        <f>IF(A70="","",IF(E70="","TERMINAL",IF(AG70="","INFO",IF(ABS(AG70)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -12537,10 +14359,31 @@
         <v/>
       </c>
       <c r="AA71" s="4">
-        <f>IF(A71="","",IF(OR(U71&gt;1,AND(X71&lt;&gt;"",X71&lt;Inputs!$B$16),AND(X71&lt;&gt;"",X71&gt;Inputs!$B$17),G71&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A71="","",IF(OR(U71&gt;1,AND(X71&lt;&gt;"",X71&lt;Inputs!$B$16),AND(X71&lt;&gt;"",X71&gt;Inputs!$B$17),G71&lt;Inputs!$B$18,AH71="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB71" s="4" t="n"/>
+      <c r="AC71" s="7" t="n"/>
+      <c r="AD71" s="8">
+        <f>IF(A71="","",IF(AC71&lt;&gt;"",AC71,IF(E71="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE71" s="8">
+        <f>IF(OR(AD71="",F71="",G71=""),"",AD71+F71*G71)</f>
+        <v/>
+      </c>
+      <c r="AF71" s="8">
+        <f>IF(OR(E71="",A71=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG71" s="8">
+        <f>IF(OR(AD71="",AF71=""),"",AD71-AF71)</f>
+        <v/>
+      </c>
+      <c r="AH71" s="4">
+        <f>IF(A71="","",IF(E71="","TERMINAL",IF(AG71="","INFO",IF(ABS(AG71)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n"/>
@@ -12611,10 +14454,31 @@
         <v/>
       </c>
       <c r="AA72" s="4">
-        <f>IF(A72="","",IF(OR(U72&gt;1,AND(X72&lt;&gt;"",X72&lt;Inputs!$B$16),AND(X72&lt;&gt;"",X72&gt;Inputs!$B$17),G72&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A72="","",IF(OR(U72&gt;1,AND(X72&lt;&gt;"",X72&lt;Inputs!$B$16),AND(X72&lt;&gt;"",X72&gt;Inputs!$B$17),G72&lt;Inputs!$B$18,AH72="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB72" s="4" t="n"/>
+      <c r="AC72" s="7" t="n"/>
+      <c r="AD72" s="8">
+        <f>IF(A72="","",IF(AC72&lt;&gt;"",AC72,IF(E72="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE72" s="8">
+        <f>IF(OR(AD72="",F72="",G72=""),"",AD72+F72*G72)</f>
+        <v/>
+      </c>
+      <c r="AF72" s="8">
+        <f>IF(OR(E72="",A72=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG72" s="8">
+        <f>IF(OR(AD72="",AF72=""),"",AD72-AF72)</f>
+        <v/>
+      </c>
+      <c r="AH72" s="4">
+        <f>IF(A72="","",IF(E72="","TERMINAL",IF(AG72="","INFO",IF(ABS(AG72)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -12685,10 +14549,31 @@
         <v/>
       </c>
       <c r="AA73" s="4">
-        <f>IF(A73="","",IF(OR(U73&gt;1,AND(X73&lt;&gt;"",X73&lt;Inputs!$B$16),AND(X73&lt;&gt;"",X73&gt;Inputs!$B$17),G73&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A73="","",IF(OR(U73&gt;1,AND(X73&lt;&gt;"",X73&lt;Inputs!$B$16),AND(X73&lt;&gt;"",X73&gt;Inputs!$B$17),G73&lt;Inputs!$B$18,AH73="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB73" s="4" t="n"/>
+      <c r="AC73" s="7" t="n"/>
+      <c r="AD73" s="8">
+        <f>IF(A73="","",IF(AC73&lt;&gt;"",AC73,IF(E73="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE73" s="8">
+        <f>IF(OR(AD73="",F73="",G73=""),"",AD73+F73*G73)</f>
+        <v/>
+      </c>
+      <c r="AF73" s="8">
+        <f>IF(OR(E73="",A73=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG73" s="8">
+        <f>IF(OR(AD73="",AF73=""),"",AD73-AF73)</f>
+        <v/>
+      </c>
+      <c r="AH73" s="4">
+        <f>IF(A73="","",IF(E73="","TERMINAL",IF(AG73="","INFO",IF(ABS(AG73)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
@@ -12759,10 +14644,31 @@
         <v/>
       </c>
       <c r="AA74" s="4">
-        <f>IF(A74="","",IF(OR(U74&gt;1,AND(X74&lt;&gt;"",X74&lt;Inputs!$B$16),AND(X74&lt;&gt;"",X74&gt;Inputs!$B$17),G74&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A74="","",IF(OR(U74&gt;1,AND(X74&lt;&gt;"",X74&lt;Inputs!$B$16),AND(X74&lt;&gt;"",X74&gt;Inputs!$B$17),G74&lt;Inputs!$B$18,AH74="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB74" s="4" t="n"/>
+      <c r="AC74" s="7" t="n"/>
+      <c r="AD74" s="8">
+        <f>IF(A74="","",IF(AC74&lt;&gt;"",AC74,IF(E74="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE74" s="8">
+        <f>IF(OR(AD74="",F74="",G74=""),"",AD74+F74*G74)</f>
+        <v/>
+      </c>
+      <c r="AF74" s="8">
+        <f>IF(OR(E74="",A74=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG74" s="8">
+        <f>IF(OR(AD74="",AF74=""),"",AD74-AF74)</f>
+        <v/>
+      </c>
+      <c r="AH74" s="4">
+        <f>IF(A74="","",IF(E74="","TERMINAL",IF(AG74="","INFO",IF(ABS(AG74)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -12833,10 +14739,31 @@
         <v/>
       </c>
       <c r="AA75" s="4">
-        <f>IF(A75="","",IF(OR(U75&gt;1,AND(X75&lt;&gt;"",X75&lt;Inputs!$B$16),AND(X75&lt;&gt;"",X75&gt;Inputs!$B$17),G75&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A75="","",IF(OR(U75&gt;1,AND(X75&lt;&gt;"",X75&lt;Inputs!$B$16),AND(X75&lt;&gt;"",X75&gt;Inputs!$B$17),G75&lt;Inputs!$B$18,AH75="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB75" s="4" t="n"/>
+      <c r="AC75" s="7" t="n"/>
+      <c r="AD75" s="8">
+        <f>IF(A75="","",IF(AC75&lt;&gt;"",AC75,IF(E75="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE75" s="8">
+        <f>IF(OR(AD75="",F75="",G75=""),"",AD75+F75*G75)</f>
+        <v/>
+      </c>
+      <c r="AF75" s="8">
+        <f>IF(OR(E75="",A75=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG75" s="8">
+        <f>IF(OR(AD75="",AF75=""),"",AD75-AF75)</f>
+        <v/>
+      </c>
+      <c r="AH75" s="4">
+        <f>IF(A75="","",IF(E75="","TERMINAL",IF(AG75="","INFO",IF(ABS(AG75)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
@@ -12907,10 +14834,31 @@
         <v/>
       </c>
       <c r="AA76" s="4">
-        <f>IF(A76="","",IF(OR(U76&gt;1,AND(X76&lt;&gt;"",X76&lt;Inputs!$B$16),AND(X76&lt;&gt;"",X76&gt;Inputs!$B$17),G76&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A76="","",IF(OR(U76&gt;1,AND(X76&lt;&gt;"",X76&lt;Inputs!$B$16),AND(X76&lt;&gt;"",X76&gt;Inputs!$B$17),G76&lt;Inputs!$B$18,AH76="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB76" s="4" t="n"/>
+      <c r="AC76" s="7" t="n"/>
+      <c r="AD76" s="8">
+        <f>IF(A76="","",IF(AC76&lt;&gt;"",AC76,IF(E76="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE76" s="8">
+        <f>IF(OR(AD76="",F76="",G76=""),"",AD76+F76*G76)</f>
+        <v/>
+      </c>
+      <c r="AF76" s="8">
+        <f>IF(OR(E76="",A76=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG76" s="8">
+        <f>IF(OR(AD76="",AF76=""),"",AD76-AF76)</f>
+        <v/>
+      </c>
+      <c r="AH76" s="4">
+        <f>IF(A76="","",IF(E76="","TERMINAL",IF(AG76="","INFO",IF(ABS(AG76)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -12981,10 +14929,31 @@
         <v/>
       </c>
       <c r="AA77" s="4">
-        <f>IF(A77="","",IF(OR(U77&gt;1,AND(X77&lt;&gt;"",X77&lt;Inputs!$B$16),AND(X77&lt;&gt;"",X77&gt;Inputs!$B$17),G77&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A77="","",IF(OR(U77&gt;1,AND(X77&lt;&gt;"",X77&lt;Inputs!$B$16),AND(X77&lt;&gt;"",X77&gt;Inputs!$B$17),G77&lt;Inputs!$B$18,AH77="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB77" s="4" t="n"/>
+      <c r="AC77" s="7" t="n"/>
+      <c r="AD77" s="8">
+        <f>IF(A77="","",IF(AC77&lt;&gt;"",AC77,IF(E77="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE77" s="8">
+        <f>IF(OR(AD77="",F77="",G77=""),"",AD77+F77*G77)</f>
+        <v/>
+      </c>
+      <c r="AF77" s="8">
+        <f>IF(OR(E77="",A77=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG77" s="8">
+        <f>IF(OR(AD77="",AF77=""),"",AD77-AF77)</f>
+        <v/>
+      </c>
+      <c r="AH77" s="4">
+        <f>IF(A77="","",IF(E77="","TERMINAL",IF(AG77="","INFO",IF(ABS(AG77)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n"/>
@@ -13055,10 +15024,31 @@
         <v/>
       </c>
       <c r="AA78" s="4">
-        <f>IF(A78="","",IF(OR(U78&gt;1,AND(X78&lt;&gt;"",X78&lt;Inputs!$B$16),AND(X78&lt;&gt;"",X78&gt;Inputs!$B$17),G78&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A78="","",IF(OR(U78&gt;1,AND(X78&lt;&gt;"",X78&lt;Inputs!$B$16),AND(X78&lt;&gt;"",X78&gt;Inputs!$B$17),G78&lt;Inputs!$B$18,AH78="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB78" s="4" t="n"/>
+      <c r="AC78" s="7" t="n"/>
+      <c r="AD78" s="8">
+        <f>IF(A78="","",IF(AC78&lt;&gt;"",AC78,IF(E78="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE78" s="8">
+        <f>IF(OR(AD78="",F78="",G78=""),"",AD78+F78*G78)</f>
+        <v/>
+      </c>
+      <c r="AF78" s="8">
+        <f>IF(OR(E78="",A78=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG78" s="8">
+        <f>IF(OR(AD78="",AF78=""),"",AD78-AF78)</f>
+        <v/>
+      </c>
+      <c r="AH78" s="4">
+        <f>IF(A78="","",IF(E78="","TERMINAL",IF(AG78="","INFO",IF(ABS(AG78)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -13129,10 +15119,31 @@
         <v/>
       </c>
       <c r="AA79" s="4">
-        <f>IF(A79="","",IF(OR(U79&gt;1,AND(X79&lt;&gt;"",X79&lt;Inputs!$B$16),AND(X79&lt;&gt;"",X79&gt;Inputs!$B$17),G79&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A79="","",IF(OR(U79&gt;1,AND(X79&lt;&gt;"",X79&lt;Inputs!$B$16),AND(X79&lt;&gt;"",X79&gt;Inputs!$B$17),G79&lt;Inputs!$B$18,AH79="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB79" s="4" t="n"/>
+      <c r="AC79" s="7" t="n"/>
+      <c r="AD79" s="8">
+        <f>IF(A79="","",IF(AC79&lt;&gt;"",AC79,IF(E79="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE79" s="8">
+        <f>IF(OR(AD79="",F79="",G79=""),"",AD79+F79*G79)</f>
+        <v/>
+      </c>
+      <c r="AF79" s="8">
+        <f>IF(OR(E79="",A79=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG79" s="8">
+        <f>IF(OR(AD79="",AF79=""),"",AD79-AF79)</f>
+        <v/>
+      </c>
+      <c r="AH79" s="4">
+        <f>IF(A79="","",IF(E79="","TERMINAL",IF(AG79="","INFO",IF(ABS(AG79)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n"/>
@@ -13203,10 +15214,31 @@
         <v/>
       </c>
       <c r="AA80" s="4">
-        <f>IF(A80="","",IF(OR(U80&gt;1,AND(X80&lt;&gt;"",X80&lt;Inputs!$B$16),AND(X80&lt;&gt;"",X80&gt;Inputs!$B$17),G80&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A80="","",IF(OR(U80&gt;1,AND(X80&lt;&gt;"",X80&lt;Inputs!$B$16),AND(X80&lt;&gt;"",X80&gt;Inputs!$B$17),G80&lt;Inputs!$B$18,AH80="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB80" s="4" t="n"/>
+      <c r="AC80" s="7" t="n"/>
+      <c r="AD80" s="8">
+        <f>IF(A80="","",IF(AC80&lt;&gt;"",AC80,IF(E80="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE80" s="8">
+        <f>IF(OR(AD80="",F80="",G80=""),"",AD80+F80*G80)</f>
+        <v/>
+      </c>
+      <c r="AF80" s="8">
+        <f>IF(OR(E80="",A80=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG80" s="8">
+        <f>IF(OR(AD80="",AF80=""),"",AD80-AF80)</f>
+        <v/>
+      </c>
+      <c r="AH80" s="4">
+        <f>IF(A80="","",IF(E80="","TERMINAL",IF(AG80="","INFO",IF(ABS(AG80)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -13277,10 +15309,31 @@
         <v/>
       </c>
       <c r="AA81" s="4">
-        <f>IF(A81="","",IF(OR(U81&gt;1,AND(X81&lt;&gt;"",X81&lt;Inputs!$B$16),AND(X81&lt;&gt;"",X81&gt;Inputs!$B$17),G81&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A81="","",IF(OR(U81&gt;1,AND(X81&lt;&gt;"",X81&lt;Inputs!$B$16),AND(X81&lt;&gt;"",X81&gt;Inputs!$B$17),G81&lt;Inputs!$B$18,AH81="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB81" s="4" t="n"/>
+      <c r="AC81" s="7" t="n"/>
+      <c r="AD81" s="8">
+        <f>IF(A81="","",IF(AC81&lt;&gt;"",AC81,IF(E81="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE81" s="8">
+        <f>IF(OR(AD81="",F81="",G81=""),"",AD81+F81*G81)</f>
+        <v/>
+      </c>
+      <c r="AF81" s="8">
+        <f>IF(OR(E81="",A81=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG81" s="8">
+        <f>IF(OR(AD81="",AF81=""),"",AD81-AF81)</f>
+        <v/>
+      </c>
+      <c r="AH81" s="4">
+        <f>IF(A81="","",IF(E81="","TERMINAL",IF(AG81="","INFO",IF(ABS(AG81)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
@@ -13351,10 +15404,31 @@
         <v/>
       </c>
       <c r="AA82" s="4">
-        <f>IF(A82="","",IF(OR(U82&gt;1,AND(X82&lt;&gt;"",X82&lt;Inputs!$B$16),AND(X82&lt;&gt;"",X82&gt;Inputs!$B$17),G82&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A82="","",IF(OR(U82&gt;1,AND(X82&lt;&gt;"",X82&lt;Inputs!$B$16),AND(X82&lt;&gt;"",X82&gt;Inputs!$B$17),G82&lt;Inputs!$B$18,AH82="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB82" s="4" t="n"/>
+      <c r="AC82" s="7" t="n"/>
+      <c r="AD82" s="8">
+        <f>IF(A82="","",IF(AC82&lt;&gt;"",AC82,IF(E82="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE82" s="8">
+        <f>IF(OR(AD82="",F82="",G82=""),"",AD82+F82*G82)</f>
+        <v/>
+      </c>
+      <c r="AF82" s="8">
+        <f>IF(OR(E82="",A82=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG82" s="8">
+        <f>IF(OR(AD82="",AF82=""),"",AD82-AF82)</f>
+        <v/>
+      </c>
+      <c r="AH82" s="4">
+        <f>IF(A82="","",IF(E82="","TERMINAL",IF(AG82="","INFO",IF(ABS(AG82)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -13425,10 +15499,31 @@
         <v/>
       </c>
       <c r="AA83" s="4">
-        <f>IF(A83="","",IF(OR(U83&gt;1,AND(X83&lt;&gt;"",X83&lt;Inputs!$B$16),AND(X83&lt;&gt;"",X83&gt;Inputs!$B$17),G83&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A83="","",IF(OR(U83&gt;1,AND(X83&lt;&gt;"",X83&lt;Inputs!$B$16),AND(X83&lt;&gt;"",X83&gt;Inputs!$B$17),G83&lt;Inputs!$B$18,AH83="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB83" s="4" t="n"/>
+      <c r="AC83" s="7" t="n"/>
+      <c r="AD83" s="8">
+        <f>IF(A83="","",IF(AC83&lt;&gt;"",AC83,IF(E83="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE83" s="8">
+        <f>IF(OR(AD83="",F83="",G83=""),"",AD83+F83*G83)</f>
+        <v/>
+      </c>
+      <c r="AF83" s="8">
+        <f>IF(OR(E83="",A83=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG83" s="8">
+        <f>IF(OR(AD83="",AF83=""),"",AD83-AF83)</f>
+        <v/>
+      </c>
+      <c r="AH83" s="4">
+        <f>IF(A83="","",IF(E83="","TERMINAL",IF(AG83="","INFO",IF(ABS(AG83)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
@@ -13499,10 +15594,31 @@
         <v/>
       </c>
       <c r="AA84" s="4">
-        <f>IF(A84="","",IF(OR(U84&gt;1,AND(X84&lt;&gt;"",X84&lt;Inputs!$B$16),AND(X84&lt;&gt;"",X84&gt;Inputs!$B$17),G84&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A84="","",IF(OR(U84&gt;1,AND(X84&lt;&gt;"",X84&lt;Inputs!$B$16),AND(X84&lt;&gt;"",X84&gt;Inputs!$B$17),G84&lt;Inputs!$B$18,AH84="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB84" s="4" t="n"/>
+      <c r="AC84" s="7" t="n"/>
+      <c r="AD84" s="8">
+        <f>IF(A84="","",IF(AC84&lt;&gt;"",AC84,IF(E84="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE84" s="8">
+        <f>IF(OR(AD84="",F84="",G84=""),"",AD84+F84*G84)</f>
+        <v/>
+      </c>
+      <c r="AF84" s="8">
+        <f>IF(OR(E84="",A84=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG84" s="8">
+        <f>IF(OR(AD84="",AF84=""),"",AD84-AF84)</f>
+        <v/>
+      </c>
+      <c r="AH84" s="4">
+        <f>IF(A84="","",IF(E84="","TERMINAL",IF(AG84="","INFO",IF(ABS(AG84)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -13573,10 +15689,31 @@
         <v/>
       </c>
       <c r="AA85" s="4">
-        <f>IF(A85="","",IF(OR(U85&gt;1,AND(X85&lt;&gt;"",X85&lt;Inputs!$B$16),AND(X85&lt;&gt;"",X85&gt;Inputs!$B$17),G85&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A85="","",IF(OR(U85&gt;1,AND(X85&lt;&gt;"",X85&lt;Inputs!$B$16),AND(X85&lt;&gt;"",X85&gt;Inputs!$B$17),G85&lt;Inputs!$B$18,AH85="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB85" s="4" t="n"/>
+      <c r="AC85" s="7" t="n"/>
+      <c r="AD85" s="8">
+        <f>IF(A85="","",IF(AC85&lt;&gt;"",AC85,IF(E85="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE85" s="8">
+        <f>IF(OR(AD85="",F85="",G85=""),"",AD85+F85*G85)</f>
+        <v/>
+      </c>
+      <c r="AF85" s="8">
+        <f>IF(OR(E85="",A85=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG85" s="8">
+        <f>IF(OR(AD85="",AF85=""),"",AD85-AF85)</f>
+        <v/>
+      </c>
+      <c r="AH85" s="4">
+        <f>IF(A85="","",IF(E85="","TERMINAL",IF(AG85="","INFO",IF(ABS(AG85)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -13647,10 +15784,31 @@
         <v/>
       </c>
       <c r="AA86" s="4">
-        <f>IF(A86="","",IF(OR(U86&gt;1,AND(X86&lt;&gt;"",X86&lt;Inputs!$B$16),AND(X86&lt;&gt;"",X86&gt;Inputs!$B$17),G86&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A86="","",IF(OR(U86&gt;1,AND(X86&lt;&gt;"",X86&lt;Inputs!$B$16),AND(X86&lt;&gt;"",X86&gt;Inputs!$B$17),G86&lt;Inputs!$B$18,AH86="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB86" s="4" t="n"/>
+      <c r="AC86" s="7" t="n"/>
+      <c r="AD86" s="8">
+        <f>IF(A86="","",IF(AC86&lt;&gt;"",AC86,IF(E86="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE86" s="8">
+        <f>IF(OR(AD86="",F86="",G86=""),"",AD86+F86*G86)</f>
+        <v/>
+      </c>
+      <c r="AF86" s="8">
+        <f>IF(OR(E86="",A86=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG86" s="8">
+        <f>IF(OR(AD86="",AF86=""),"",AD86-AF86)</f>
+        <v/>
+      </c>
+      <c r="AH86" s="4">
+        <f>IF(A86="","",IF(E86="","TERMINAL",IF(AG86="","INFO",IF(ABS(AG86)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -13721,10 +15879,31 @@
         <v/>
       </c>
       <c r="AA87" s="4">
-        <f>IF(A87="","",IF(OR(U87&gt;1,AND(X87&lt;&gt;"",X87&lt;Inputs!$B$16),AND(X87&lt;&gt;"",X87&gt;Inputs!$B$17),G87&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A87="","",IF(OR(U87&gt;1,AND(X87&lt;&gt;"",X87&lt;Inputs!$B$16),AND(X87&lt;&gt;"",X87&gt;Inputs!$B$17),G87&lt;Inputs!$B$18,AH87="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB87" s="4" t="n"/>
+      <c r="AC87" s="7" t="n"/>
+      <c r="AD87" s="8">
+        <f>IF(A87="","",IF(AC87&lt;&gt;"",AC87,IF(E87="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE87" s="8">
+        <f>IF(OR(AD87="",F87="",G87=""),"",AD87+F87*G87)</f>
+        <v/>
+      </c>
+      <c r="AF87" s="8">
+        <f>IF(OR(E87="",A87=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG87" s="8">
+        <f>IF(OR(AD87="",AF87=""),"",AD87-AF87)</f>
+        <v/>
+      </c>
+      <c r="AH87" s="4">
+        <f>IF(A87="","",IF(E87="","TERMINAL",IF(AG87="","INFO",IF(ABS(AG87)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
@@ -13795,10 +15974,31 @@
         <v/>
       </c>
       <c r="AA88" s="4">
-        <f>IF(A88="","",IF(OR(U88&gt;1,AND(X88&lt;&gt;"",X88&lt;Inputs!$B$16),AND(X88&lt;&gt;"",X88&gt;Inputs!$B$17),G88&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A88="","",IF(OR(U88&gt;1,AND(X88&lt;&gt;"",X88&lt;Inputs!$B$16),AND(X88&lt;&gt;"",X88&gt;Inputs!$B$17),G88&lt;Inputs!$B$18,AH88="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB88" s="4" t="n"/>
+      <c r="AC88" s="7" t="n"/>
+      <c r="AD88" s="8">
+        <f>IF(A88="","",IF(AC88&lt;&gt;"",AC88,IF(E88="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE88" s="8">
+        <f>IF(OR(AD88="",F88="",G88=""),"",AD88+F88*G88)</f>
+        <v/>
+      </c>
+      <c r="AF88" s="8">
+        <f>IF(OR(E88="",A88=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG88" s="8">
+        <f>IF(OR(AD88="",AF88=""),"",AD88-AF88)</f>
+        <v/>
+      </c>
+      <c r="AH88" s="4">
+        <f>IF(A88="","",IF(E88="","TERMINAL",IF(AG88="","INFO",IF(ABS(AG88)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -13869,10 +16069,31 @@
         <v/>
       </c>
       <c r="AA89" s="4">
-        <f>IF(A89="","",IF(OR(U89&gt;1,AND(X89&lt;&gt;"",X89&lt;Inputs!$B$16),AND(X89&lt;&gt;"",X89&gt;Inputs!$B$17),G89&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A89="","",IF(OR(U89&gt;1,AND(X89&lt;&gt;"",X89&lt;Inputs!$B$16),AND(X89&lt;&gt;"",X89&gt;Inputs!$B$17),G89&lt;Inputs!$B$18,AH89="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB89" s="4" t="n"/>
+      <c r="AC89" s="7" t="n"/>
+      <c r="AD89" s="8">
+        <f>IF(A89="","",IF(AC89&lt;&gt;"",AC89,IF(E89="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE89" s="8">
+        <f>IF(OR(AD89="",F89="",G89=""),"",AD89+F89*G89)</f>
+        <v/>
+      </c>
+      <c r="AF89" s="8">
+        <f>IF(OR(E89="",A89=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG89" s="8">
+        <f>IF(OR(AD89="",AF89=""),"",AD89-AF89)</f>
+        <v/>
+      </c>
+      <c r="AH89" s="4">
+        <f>IF(A89="","",IF(E89="","TERMINAL",IF(AG89="","INFO",IF(ABS(AG89)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
@@ -13943,10 +16164,31 @@
         <v/>
       </c>
       <c r="AA90" s="4">
-        <f>IF(A90="","",IF(OR(U90&gt;1,AND(X90&lt;&gt;"",X90&lt;Inputs!$B$16),AND(X90&lt;&gt;"",X90&gt;Inputs!$B$17),G90&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A90="","",IF(OR(U90&gt;1,AND(X90&lt;&gt;"",X90&lt;Inputs!$B$16),AND(X90&lt;&gt;"",X90&gt;Inputs!$B$17),G90&lt;Inputs!$B$18,AH90="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB90" s="4" t="n"/>
+      <c r="AC90" s="7" t="n"/>
+      <c r="AD90" s="8">
+        <f>IF(A90="","",IF(AC90&lt;&gt;"",AC90,IF(E90="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE90" s="8">
+        <f>IF(OR(AD90="",F90="",G90=""),"",AD90+F90*G90)</f>
+        <v/>
+      </c>
+      <c r="AF90" s="8">
+        <f>IF(OR(E90="",A90=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG90" s="8">
+        <f>IF(OR(AD90="",AF90=""),"",AD90-AF90)</f>
+        <v/>
+      </c>
+      <c r="AH90" s="4">
+        <f>IF(A90="","",IF(E90="","TERMINAL",IF(AG90="","INFO",IF(ABS(AG90)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -14017,10 +16259,31 @@
         <v/>
       </c>
       <c r="AA91" s="4">
-        <f>IF(A91="","",IF(OR(U91&gt;1,AND(X91&lt;&gt;"",X91&lt;Inputs!$B$16),AND(X91&lt;&gt;"",X91&gt;Inputs!$B$17),G91&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A91="","",IF(OR(U91&gt;1,AND(X91&lt;&gt;"",X91&lt;Inputs!$B$16),AND(X91&lt;&gt;"",X91&gt;Inputs!$B$17),G91&lt;Inputs!$B$18,AH91="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB91" s="4" t="n"/>
+      <c r="AC91" s="7" t="n"/>
+      <c r="AD91" s="8">
+        <f>IF(A91="","",IF(AC91&lt;&gt;"",AC91,IF(E91="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE91" s="8">
+        <f>IF(OR(AD91="",F91="",G91=""),"",AD91+F91*G91)</f>
+        <v/>
+      </c>
+      <c r="AF91" s="8">
+        <f>IF(OR(E91="",A91=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG91" s="8">
+        <f>IF(OR(AD91="",AF91=""),"",AD91-AF91)</f>
+        <v/>
+      </c>
+      <c r="AH91" s="4">
+        <f>IF(A91="","",IF(E91="","TERMINAL",IF(AG91="","INFO",IF(ABS(AG91)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -14091,10 +16354,31 @@
         <v/>
       </c>
       <c r="AA92" s="4">
-        <f>IF(A92="","",IF(OR(U92&gt;1,AND(X92&lt;&gt;"",X92&lt;Inputs!$B$16),AND(X92&lt;&gt;"",X92&gt;Inputs!$B$17),G92&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A92="","",IF(OR(U92&gt;1,AND(X92&lt;&gt;"",X92&lt;Inputs!$B$16),AND(X92&lt;&gt;"",X92&gt;Inputs!$B$17),G92&lt;Inputs!$B$18,AH92="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB92" s="4" t="n"/>
+      <c r="AC92" s="7" t="n"/>
+      <c r="AD92" s="8">
+        <f>IF(A92="","",IF(AC92&lt;&gt;"",AC92,IF(E92="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE92" s="8">
+        <f>IF(OR(AD92="",F92="",G92=""),"",AD92+F92*G92)</f>
+        <v/>
+      </c>
+      <c r="AF92" s="8">
+        <f>IF(OR(E92="",A92=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG92" s="8">
+        <f>IF(OR(AD92="",AF92=""),"",AD92-AF92)</f>
+        <v/>
+      </c>
+      <c r="AH92" s="4">
+        <f>IF(A92="","",IF(E92="","TERMINAL",IF(AG92="","INFO",IF(ABS(AG92)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -14165,10 +16449,31 @@
         <v/>
       </c>
       <c r="AA93" s="4">
-        <f>IF(A93="","",IF(OR(U93&gt;1,AND(X93&lt;&gt;"",X93&lt;Inputs!$B$16),AND(X93&lt;&gt;"",X93&gt;Inputs!$B$17),G93&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A93="","",IF(OR(U93&gt;1,AND(X93&lt;&gt;"",X93&lt;Inputs!$B$16),AND(X93&lt;&gt;"",X93&gt;Inputs!$B$17),G93&lt;Inputs!$B$18,AH93="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB93" s="4" t="n"/>
+      <c r="AC93" s="7" t="n"/>
+      <c r="AD93" s="8">
+        <f>IF(A93="","",IF(AC93&lt;&gt;"",AC93,IF(E93="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE93" s="8">
+        <f>IF(OR(AD93="",F93="",G93=""),"",AD93+F93*G93)</f>
+        <v/>
+      </c>
+      <c r="AF93" s="8">
+        <f>IF(OR(E93="",A93=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG93" s="8">
+        <f>IF(OR(AD93="",AF93=""),"",AD93-AF93)</f>
+        <v/>
+      </c>
+      <c r="AH93" s="4">
+        <f>IF(A93="","",IF(E93="","TERMINAL",IF(AG93="","INFO",IF(ABS(AG93)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
@@ -14239,10 +16544,31 @@
         <v/>
       </c>
       <c r="AA94" s="4">
-        <f>IF(A94="","",IF(OR(U94&gt;1,AND(X94&lt;&gt;"",X94&lt;Inputs!$B$16),AND(X94&lt;&gt;"",X94&gt;Inputs!$B$17),G94&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A94="","",IF(OR(U94&gt;1,AND(X94&lt;&gt;"",X94&lt;Inputs!$B$16),AND(X94&lt;&gt;"",X94&gt;Inputs!$B$17),G94&lt;Inputs!$B$18,AH94="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB94" s="4" t="n"/>
+      <c r="AC94" s="7" t="n"/>
+      <c r="AD94" s="8">
+        <f>IF(A94="","",IF(AC94&lt;&gt;"",AC94,IF(E94="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE94" s="8">
+        <f>IF(OR(AD94="",F94="",G94=""),"",AD94+F94*G94)</f>
+        <v/>
+      </c>
+      <c r="AF94" s="8">
+        <f>IF(OR(E94="",A94=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG94" s="8">
+        <f>IF(OR(AD94="",AF94=""),"",AD94-AF94)</f>
+        <v/>
+      </c>
+      <c r="AH94" s="4">
+        <f>IF(A94="","",IF(E94="","TERMINAL",IF(AG94="","INFO",IF(ABS(AG94)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -14313,10 +16639,31 @@
         <v/>
       </c>
       <c r="AA95" s="4">
-        <f>IF(A95="","",IF(OR(U95&gt;1,AND(X95&lt;&gt;"",X95&lt;Inputs!$B$16),AND(X95&lt;&gt;"",X95&gt;Inputs!$B$17),G95&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A95="","",IF(OR(U95&gt;1,AND(X95&lt;&gt;"",X95&lt;Inputs!$B$16),AND(X95&lt;&gt;"",X95&gt;Inputs!$B$17),G95&lt;Inputs!$B$18,AH95="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB95" s="4" t="n"/>
+      <c r="AC95" s="7" t="n"/>
+      <c r="AD95" s="8">
+        <f>IF(A95="","",IF(AC95&lt;&gt;"",AC95,IF(E95="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE95" s="8">
+        <f>IF(OR(AD95="",F95="",G95=""),"",AD95+F95*G95)</f>
+        <v/>
+      </c>
+      <c r="AF95" s="8">
+        <f>IF(OR(E95="",A95=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG95" s="8">
+        <f>IF(OR(AD95="",AF95=""),"",AD95-AF95)</f>
+        <v/>
+      </c>
+      <c r="AH95" s="4">
+        <f>IF(A95="","",IF(E95="","TERMINAL",IF(AG95="","INFO",IF(ABS(AG95)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
@@ -14387,10 +16734,31 @@
         <v/>
       </c>
       <c r="AA96" s="4">
-        <f>IF(A96="","",IF(OR(U96&gt;1,AND(X96&lt;&gt;"",X96&lt;Inputs!$B$16),AND(X96&lt;&gt;"",X96&gt;Inputs!$B$17),G96&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A96="","",IF(OR(U96&gt;1,AND(X96&lt;&gt;"",X96&lt;Inputs!$B$16),AND(X96&lt;&gt;"",X96&gt;Inputs!$B$17),G96&lt;Inputs!$B$18,AH96="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB96" s="4" t="n"/>
+      <c r="AC96" s="7" t="n"/>
+      <c r="AD96" s="8">
+        <f>IF(A96="","",IF(AC96&lt;&gt;"",AC96,IF(E96="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE96" s="8">
+        <f>IF(OR(AD96="",F96="",G96=""),"",AD96+F96*G96)</f>
+        <v/>
+      </c>
+      <c r="AF96" s="8">
+        <f>IF(OR(E96="",A96=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG96" s="8">
+        <f>IF(OR(AD96="",AF96=""),"",AD96-AF96)</f>
+        <v/>
+      </c>
+      <c r="AH96" s="4">
+        <f>IF(A96="","",IF(E96="","TERMINAL",IF(AG96="","INFO",IF(ABS(AG96)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -14461,10 +16829,31 @@
         <v/>
       </c>
       <c r="AA97" s="4">
-        <f>IF(A97="","",IF(OR(U97&gt;1,AND(X97&lt;&gt;"",X97&lt;Inputs!$B$16),AND(X97&lt;&gt;"",X97&gt;Inputs!$B$17),G97&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A97="","",IF(OR(U97&gt;1,AND(X97&lt;&gt;"",X97&lt;Inputs!$B$16),AND(X97&lt;&gt;"",X97&gt;Inputs!$B$17),G97&lt;Inputs!$B$18,AH97="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB97" s="4" t="n"/>
+      <c r="AC97" s="7" t="n"/>
+      <c r="AD97" s="8">
+        <f>IF(A97="","",IF(AC97&lt;&gt;"",AC97,IF(E97="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE97" s="8">
+        <f>IF(OR(AD97="",F97="",G97=""),"",AD97+F97*G97)</f>
+        <v/>
+      </c>
+      <c r="AF97" s="8">
+        <f>IF(OR(E97="",A97=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG97" s="8">
+        <f>IF(OR(AD97="",AF97=""),"",AD97-AF97)</f>
+        <v/>
+      </c>
+      <c r="AH97" s="4">
+        <f>IF(A97="","",IF(E97="","TERMINAL",IF(AG97="","INFO",IF(ABS(AG97)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -14535,10 +16924,31 @@
         <v/>
       </c>
       <c r="AA98" s="4">
-        <f>IF(A98="","",IF(OR(U98&gt;1,AND(X98&lt;&gt;"",X98&lt;Inputs!$B$16),AND(X98&lt;&gt;"",X98&gt;Inputs!$B$17),G98&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A98="","",IF(OR(U98&gt;1,AND(X98&lt;&gt;"",X98&lt;Inputs!$B$16),AND(X98&lt;&gt;"",X98&gt;Inputs!$B$17),G98&lt;Inputs!$B$18,AH98="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB98" s="4" t="n"/>
+      <c r="AC98" s="7" t="n"/>
+      <c r="AD98" s="8">
+        <f>IF(A98="","",IF(AC98&lt;&gt;"",AC98,IF(E98="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE98" s="8">
+        <f>IF(OR(AD98="",F98="",G98=""),"",AD98+F98*G98)</f>
+        <v/>
+      </c>
+      <c r="AF98" s="8">
+        <f>IF(OR(E98="",A98=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG98" s="8">
+        <f>IF(OR(AD98="",AF98=""),"",AD98-AF98)</f>
+        <v/>
+      </c>
+      <c r="AH98" s="4">
+        <f>IF(A98="","",IF(E98="","TERMINAL",IF(AG98="","INFO",IF(ABS(AG98)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -14609,10 +17019,31 @@
         <v/>
       </c>
       <c r="AA99" s="4">
-        <f>IF(A99="","",IF(OR(U99&gt;1,AND(X99&lt;&gt;"",X99&lt;Inputs!$B$16),AND(X99&lt;&gt;"",X99&gt;Inputs!$B$17),G99&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A99="","",IF(OR(U99&gt;1,AND(X99&lt;&gt;"",X99&lt;Inputs!$B$16),AND(X99&lt;&gt;"",X99&gt;Inputs!$B$17),G99&lt;Inputs!$B$18,AH99="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB99" s="4" t="n"/>
+      <c r="AC99" s="7" t="n"/>
+      <c r="AD99" s="8">
+        <f>IF(A99="","",IF(AC99&lt;&gt;"",AC99,IF(E99="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE99" s="8">
+        <f>IF(OR(AD99="",F99="",G99=""),"",AD99+F99*G99)</f>
+        <v/>
+      </c>
+      <c r="AF99" s="8">
+        <f>IF(OR(E99="",A99=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG99" s="8">
+        <f>IF(OR(AD99="",AF99=""),"",AD99-AF99)</f>
+        <v/>
+      </c>
+      <c r="AH99" s="4">
+        <f>IF(A99="","",IF(E99="","TERMINAL",IF(AG99="","INFO",IF(ABS(AG99)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
@@ -14683,10 +17114,31 @@
         <v/>
       </c>
       <c r="AA100" s="4">
-        <f>IF(A100="","",IF(OR(U100&gt;1,AND(X100&lt;&gt;"",X100&lt;Inputs!$B$16),AND(X100&lt;&gt;"",X100&gt;Inputs!$B$17),G100&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A100="","",IF(OR(U100&gt;1,AND(X100&lt;&gt;"",X100&lt;Inputs!$B$16),AND(X100&lt;&gt;"",X100&gt;Inputs!$B$17),G100&lt;Inputs!$B$18,AH100="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB100" s="4" t="n"/>
+      <c r="AC100" s="7" t="n"/>
+      <c r="AD100" s="8">
+        <f>IF(A100="","",IF(AC100&lt;&gt;"",AC100,IF(E100="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE100" s="8">
+        <f>IF(OR(AD100="",F100="",G100=""),"",AD100+F100*G100)</f>
+        <v/>
+      </c>
+      <c r="AF100" s="8">
+        <f>IF(OR(E100="",A100=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG100" s="8">
+        <f>IF(OR(AD100="",AF100=""),"",AD100-AF100)</f>
+        <v/>
+      </c>
+      <c r="AH100" s="4">
+        <f>IF(A100="","",IF(E100="","TERMINAL",IF(AG100="","INFO",IF(ABS(AG100)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -14757,10 +17209,31 @@
         <v/>
       </c>
       <c r="AA101" s="4">
-        <f>IF(A101="","",IF(OR(U101&gt;1,AND(X101&lt;&gt;"",X101&lt;Inputs!$B$16),AND(X101&lt;&gt;"",X101&gt;Inputs!$B$17),G101&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A101="","",IF(OR(U101&gt;1,AND(X101&lt;&gt;"",X101&lt;Inputs!$B$16),AND(X101&lt;&gt;"",X101&gt;Inputs!$B$17),G101&lt;Inputs!$B$18,AH101="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB101" s="4" t="n"/>
+      <c r="AC101" s="7" t="n"/>
+      <c r="AD101" s="8">
+        <f>IF(A101="","",IF(AC101&lt;&gt;"",AC101,IF(E101="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE101" s="8">
+        <f>IF(OR(AD101="",F101="",G101=""),"",AD101+F101*G101)</f>
+        <v/>
+      </c>
+      <c r="AF101" s="8">
+        <f>IF(OR(E101="",A101=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG101" s="8">
+        <f>IF(OR(AD101="",AF101=""),"",AD101-AF101)</f>
+        <v/>
+      </c>
+      <c r="AH101" s="4">
+        <f>IF(A101="","",IF(E101="","TERMINAL",IF(AG101="","INFO",IF(ABS(AG101)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
@@ -14831,10 +17304,31 @@
         <v/>
       </c>
       <c r="AA102" s="4">
-        <f>IF(A102="","",IF(OR(U102&gt;1,AND(X102&lt;&gt;"",X102&lt;Inputs!$B$16),AND(X102&lt;&gt;"",X102&gt;Inputs!$B$17),G102&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A102="","",IF(OR(U102&gt;1,AND(X102&lt;&gt;"",X102&lt;Inputs!$B$16),AND(X102&lt;&gt;"",X102&gt;Inputs!$B$17),G102&lt;Inputs!$B$18,AH102="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB102" s="4" t="n"/>
+      <c r="AC102" s="7" t="n"/>
+      <c r="AD102" s="8">
+        <f>IF(A102="","",IF(AC102&lt;&gt;"",AC102,IF(E102="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE102" s="8">
+        <f>IF(OR(AD102="",F102="",G102=""),"",AD102+F102*G102)</f>
+        <v/>
+      </c>
+      <c r="AF102" s="8">
+        <f>IF(OR(E102="",A102=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG102" s="8">
+        <f>IF(OR(AD102="",AF102=""),"",AD102-AF102)</f>
+        <v/>
+      </c>
+      <c r="AH102" s="4">
+        <f>IF(A102="","",IF(E102="","TERMINAL",IF(AG102="","INFO",IF(ABS(AG102)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -14905,10 +17399,31 @@
         <v/>
       </c>
       <c r="AA103" s="4">
-        <f>IF(A103="","",IF(OR(U103&gt;1,AND(X103&lt;&gt;"",X103&lt;Inputs!$B$16),AND(X103&lt;&gt;"",X103&gt;Inputs!$B$17),G103&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A103="","",IF(OR(U103&gt;1,AND(X103&lt;&gt;"",X103&lt;Inputs!$B$16),AND(X103&lt;&gt;"",X103&gt;Inputs!$B$17),G103&lt;Inputs!$B$18,AH103="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB103" s="4" t="n"/>
+      <c r="AC103" s="7" t="n"/>
+      <c r="AD103" s="8">
+        <f>IF(A103="","",IF(AC103&lt;&gt;"",AC103,IF(E103="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE103" s="8">
+        <f>IF(OR(AD103="",F103="",G103=""),"",AD103+F103*G103)</f>
+        <v/>
+      </c>
+      <c r="AF103" s="8">
+        <f>IF(OR(E103="",A103=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG103" s="8">
+        <f>IF(OR(AD103="",AF103=""),"",AD103-AF103)</f>
+        <v/>
+      </c>
+      <c r="AH103" s="4">
+        <f>IF(A103="","",IF(E103="","TERMINAL",IF(AG103="","INFO",IF(ABS(AG103)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -14979,10 +17494,31 @@
         <v/>
       </c>
       <c r="AA104" s="4">
-        <f>IF(A104="","",IF(OR(U104&gt;1,AND(X104&lt;&gt;"",X104&lt;Inputs!$B$16),AND(X104&lt;&gt;"",X104&gt;Inputs!$B$17),G104&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A104="","",IF(OR(U104&gt;1,AND(X104&lt;&gt;"",X104&lt;Inputs!$B$16),AND(X104&lt;&gt;"",X104&gt;Inputs!$B$17),G104&lt;Inputs!$B$18,AH104="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB104" s="4" t="n"/>
+      <c r="AC104" s="7" t="n"/>
+      <c r="AD104" s="8">
+        <f>IF(A104="","",IF(AC104&lt;&gt;"",AC104,IF(E104="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE104" s="8">
+        <f>IF(OR(AD104="",F104="",G104=""),"",AD104+F104*G104)</f>
+        <v/>
+      </c>
+      <c r="AF104" s="8">
+        <f>IF(OR(E104="",A104=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG104" s="8">
+        <f>IF(OR(AD104="",AF104=""),"",AD104-AF104)</f>
+        <v/>
+      </c>
+      <c r="AH104" s="4">
+        <f>IF(A104="","",IF(E104="","TERMINAL",IF(AG104="","INFO",IF(ABS(AG104)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -15053,10 +17589,31 @@
         <v/>
       </c>
       <c r="AA105" s="4">
-        <f>IF(A105="","",IF(OR(U105&gt;1,AND(X105&lt;&gt;"",X105&lt;Inputs!$B$16),AND(X105&lt;&gt;"",X105&gt;Inputs!$B$17),G105&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A105="","",IF(OR(U105&gt;1,AND(X105&lt;&gt;"",X105&lt;Inputs!$B$16),AND(X105&lt;&gt;"",X105&gt;Inputs!$B$17),G105&lt;Inputs!$B$18,AH105="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB105" s="4" t="n"/>
+      <c r="AC105" s="7" t="n"/>
+      <c r="AD105" s="8">
+        <f>IF(A105="","",IF(AC105&lt;&gt;"",AC105,IF(E105="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE105" s="8">
+        <f>IF(OR(AD105="",F105="",G105=""),"",AD105+F105*G105)</f>
+        <v/>
+      </c>
+      <c r="AF105" s="8">
+        <f>IF(OR(E105="",A105=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG105" s="8">
+        <f>IF(OR(AD105="",AF105=""),"",AD105-AF105)</f>
+        <v/>
+      </c>
+      <c r="AH105" s="4">
+        <f>IF(A105="","",IF(E105="","TERMINAL",IF(AG105="","INFO",IF(ABS(AG105)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
@@ -15127,10 +17684,31 @@
         <v/>
       </c>
       <c r="AA106" s="4">
-        <f>IF(A106="","",IF(OR(U106&gt;1,AND(X106&lt;&gt;"",X106&lt;Inputs!$B$16),AND(X106&lt;&gt;"",X106&gt;Inputs!$B$17),G106&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A106="","",IF(OR(U106&gt;1,AND(X106&lt;&gt;"",X106&lt;Inputs!$B$16),AND(X106&lt;&gt;"",X106&gt;Inputs!$B$17),G106&lt;Inputs!$B$18,AH106="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB106" s="4" t="n"/>
+      <c r="AC106" s="7" t="n"/>
+      <c r="AD106" s="8">
+        <f>IF(A106="","",IF(AC106&lt;&gt;"",AC106,IF(E106="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE106" s="8">
+        <f>IF(OR(AD106="",F106="",G106=""),"",AD106+F106*G106)</f>
+        <v/>
+      </c>
+      <c r="AF106" s="8">
+        <f>IF(OR(E106="",A106=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG106" s="8">
+        <f>IF(OR(AD106="",AF106=""),"",AD106-AF106)</f>
+        <v/>
+      </c>
+      <c r="AH106" s="4">
+        <f>IF(A106="","",IF(E106="","TERMINAL",IF(AG106="","INFO",IF(ABS(AG106)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -15201,10 +17779,31 @@
         <v/>
       </c>
       <c r="AA107" s="4">
-        <f>IF(A107="","",IF(OR(U107&gt;1,AND(X107&lt;&gt;"",X107&lt;Inputs!$B$16),AND(X107&lt;&gt;"",X107&gt;Inputs!$B$17),G107&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A107="","",IF(OR(U107&gt;1,AND(X107&lt;&gt;"",X107&lt;Inputs!$B$16),AND(X107&lt;&gt;"",X107&gt;Inputs!$B$17),G107&lt;Inputs!$B$18,AH107="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB107" s="4" t="n"/>
+      <c r="AC107" s="7" t="n"/>
+      <c r="AD107" s="8">
+        <f>IF(A107="","",IF(AC107&lt;&gt;"",AC107,IF(E107="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE107" s="8">
+        <f>IF(OR(AD107="",F107="",G107=""),"",AD107+F107*G107)</f>
+        <v/>
+      </c>
+      <c r="AF107" s="8">
+        <f>IF(OR(E107="",A107=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG107" s="8">
+        <f>IF(OR(AD107="",AF107=""),"",AD107-AF107)</f>
+        <v/>
+      </c>
+      <c r="AH107" s="4">
+        <f>IF(A107="","",IF(E107="","TERMINAL",IF(AG107="","INFO",IF(ABS(AG107)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
@@ -15275,10 +17874,31 @@
         <v/>
       </c>
       <c r="AA108" s="4">
-        <f>IF(A108="","",IF(OR(U108&gt;1,AND(X108&lt;&gt;"",X108&lt;Inputs!$B$16),AND(X108&lt;&gt;"",X108&gt;Inputs!$B$17),G108&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A108="","",IF(OR(U108&gt;1,AND(X108&lt;&gt;"",X108&lt;Inputs!$B$16),AND(X108&lt;&gt;"",X108&gt;Inputs!$B$17),G108&lt;Inputs!$B$18,AH108="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB108" s="4" t="n"/>
+      <c r="AC108" s="7" t="n"/>
+      <c r="AD108" s="8">
+        <f>IF(A108="","",IF(AC108&lt;&gt;"",AC108,IF(E108="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE108" s="8">
+        <f>IF(OR(AD108="",F108="",G108=""),"",AD108+F108*G108)</f>
+        <v/>
+      </c>
+      <c r="AF108" s="8">
+        <f>IF(OR(E108="",A108=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG108" s="8">
+        <f>IF(OR(AD108="",AF108=""),"",AD108-AF108)</f>
+        <v/>
+      </c>
+      <c r="AH108" s="4">
+        <f>IF(A108="","",IF(E108="","TERMINAL",IF(AG108="","INFO",IF(ABS(AG108)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -15349,10 +17969,31 @@
         <v/>
       </c>
       <c r="AA109" s="4">
-        <f>IF(A109="","",IF(OR(U109&gt;1,AND(X109&lt;&gt;"",X109&lt;Inputs!$B$16),AND(X109&lt;&gt;"",X109&gt;Inputs!$B$17),G109&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A109="","",IF(OR(U109&gt;1,AND(X109&lt;&gt;"",X109&lt;Inputs!$B$16),AND(X109&lt;&gt;"",X109&gt;Inputs!$B$17),G109&lt;Inputs!$B$18,AH109="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB109" s="4" t="n"/>
+      <c r="AC109" s="7" t="n"/>
+      <c r="AD109" s="8">
+        <f>IF(A109="","",IF(AC109&lt;&gt;"",AC109,IF(E109="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE109" s="8">
+        <f>IF(OR(AD109="",F109="",G109=""),"",AD109+F109*G109)</f>
+        <v/>
+      </c>
+      <c r="AF109" s="8">
+        <f>IF(OR(E109="",A109=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG109" s="8">
+        <f>IF(OR(AD109="",AF109=""),"",AD109-AF109)</f>
+        <v/>
+      </c>
+      <c r="AH109" s="4">
+        <f>IF(A109="","",IF(E109="","TERMINAL",IF(AG109="","INFO",IF(ABS(AG109)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n"/>
@@ -15423,10 +18064,31 @@
         <v/>
       </c>
       <c r="AA110" s="4">
-        <f>IF(A110="","",IF(OR(U110&gt;1,AND(X110&lt;&gt;"",X110&lt;Inputs!$B$16),AND(X110&lt;&gt;"",X110&gt;Inputs!$B$17),G110&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A110="","",IF(OR(U110&gt;1,AND(X110&lt;&gt;"",X110&lt;Inputs!$B$16),AND(X110&lt;&gt;"",X110&gt;Inputs!$B$17),G110&lt;Inputs!$B$18,AH110="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB110" s="4" t="n"/>
+      <c r="AC110" s="7" t="n"/>
+      <c r="AD110" s="8">
+        <f>IF(A110="","",IF(AC110&lt;&gt;"",AC110,IF(E110="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE110" s="8">
+        <f>IF(OR(AD110="",F110="",G110=""),"",AD110+F110*G110)</f>
+        <v/>
+      </c>
+      <c r="AF110" s="8">
+        <f>IF(OR(E110="",A110=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG110" s="8">
+        <f>IF(OR(AD110="",AF110=""),"",AD110-AF110)</f>
+        <v/>
+      </c>
+      <c r="AH110" s="4">
+        <f>IF(A110="","",IF(E110="","TERMINAL",IF(AG110="","INFO",IF(ABS(AG110)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -15497,10 +18159,31 @@
         <v/>
       </c>
       <c r="AA111" s="4">
-        <f>IF(A111="","",IF(OR(U111&gt;1,AND(X111&lt;&gt;"",X111&lt;Inputs!$B$16),AND(X111&lt;&gt;"",X111&gt;Inputs!$B$17),G111&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A111="","",IF(OR(U111&gt;1,AND(X111&lt;&gt;"",X111&lt;Inputs!$B$16),AND(X111&lt;&gt;"",X111&gt;Inputs!$B$17),G111&lt;Inputs!$B$18,AH111="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB111" s="4" t="n"/>
+      <c r="AC111" s="7" t="n"/>
+      <c r="AD111" s="8">
+        <f>IF(A111="","",IF(AC111&lt;&gt;"",AC111,IF(E111="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE111" s="8">
+        <f>IF(OR(AD111="",F111="",G111=""),"",AD111+F111*G111)</f>
+        <v/>
+      </c>
+      <c r="AF111" s="8">
+        <f>IF(OR(E111="",A111=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG111" s="8">
+        <f>IF(OR(AD111="",AF111=""),"",AD111-AF111)</f>
+        <v/>
+      </c>
+      <c r="AH111" s="4">
+        <f>IF(A111="","",IF(E111="","TERMINAL",IF(AG111="","INFO",IF(ABS(AG111)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -15571,10 +18254,31 @@
         <v/>
       </c>
       <c r="AA112" s="4">
-        <f>IF(A112="","",IF(OR(U112&gt;1,AND(X112&lt;&gt;"",X112&lt;Inputs!$B$16),AND(X112&lt;&gt;"",X112&gt;Inputs!$B$17),G112&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A112="","",IF(OR(U112&gt;1,AND(X112&lt;&gt;"",X112&lt;Inputs!$B$16),AND(X112&lt;&gt;"",X112&gt;Inputs!$B$17),G112&lt;Inputs!$B$18,AH112="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB112" s="4" t="n"/>
+      <c r="AC112" s="7" t="n"/>
+      <c r="AD112" s="8">
+        <f>IF(A112="","",IF(AC112&lt;&gt;"",AC112,IF(E112="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE112" s="8">
+        <f>IF(OR(AD112="",F112="",G112=""),"",AD112+F112*G112)</f>
+        <v/>
+      </c>
+      <c r="AF112" s="8">
+        <f>IF(OR(E112="",A112=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG112" s="8">
+        <f>IF(OR(AD112="",AF112=""),"",AD112-AF112)</f>
+        <v/>
+      </c>
+      <c r="AH112" s="4">
+        <f>IF(A112="","",IF(E112="","TERMINAL",IF(AG112="","INFO",IF(ABS(AG112)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -15645,10 +18349,31 @@
         <v/>
       </c>
       <c r="AA113" s="4">
-        <f>IF(A113="","",IF(OR(U113&gt;1,AND(X113&lt;&gt;"",X113&lt;Inputs!$B$16),AND(X113&lt;&gt;"",X113&gt;Inputs!$B$17),G113&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A113="","",IF(OR(U113&gt;1,AND(X113&lt;&gt;"",X113&lt;Inputs!$B$16),AND(X113&lt;&gt;"",X113&gt;Inputs!$B$17),G113&lt;Inputs!$B$18,AH113="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB113" s="4" t="n"/>
+      <c r="AC113" s="7" t="n"/>
+      <c r="AD113" s="8">
+        <f>IF(A113="","",IF(AC113&lt;&gt;"",AC113,IF(E113="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE113" s="8">
+        <f>IF(OR(AD113="",F113="",G113=""),"",AD113+F113*G113)</f>
+        <v/>
+      </c>
+      <c r="AF113" s="8">
+        <f>IF(OR(E113="",A113=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG113" s="8">
+        <f>IF(OR(AD113="",AF113=""),"",AD113-AF113)</f>
+        <v/>
+      </c>
+      <c r="AH113" s="4">
+        <f>IF(A113="","",IF(E113="","TERMINAL",IF(AG113="","INFO",IF(ABS(AG113)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
@@ -15719,10 +18444,31 @@
         <v/>
       </c>
       <c r="AA114" s="4">
-        <f>IF(A114="","",IF(OR(U114&gt;1,AND(X114&lt;&gt;"",X114&lt;Inputs!$B$16),AND(X114&lt;&gt;"",X114&gt;Inputs!$B$17),G114&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A114="","",IF(OR(U114&gt;1,AND(X114&lt;&gt;"",X114&lt;Inputs!$B$16),AND(X114&lt;&gt;"",X114&gt;Inputs!$B$17),G114&lt;Inputs!$B$18,AH114="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB114" s="4" t="n"/>
+      <c r="AC114" s="7" t="n"/>
+      <c r="AD114" s="8">
+        <f>IF(A114="","",IF(AC114&lt;&gt;"",AC114,IF(E114="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE114" s="8">
+        <f>IF(OR(AD114="",F114="",G114=""),"",AD114+F114*G114)</f>
+        <v/>
+      </c>
+      <c r="AF114" s="8">
+        <f>IF(OR(E114="",A114=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG114" s="8">
+        <f>IF(OR(AD114="",AF114=""),"",AD114-AF114)</f>
+        <v/>
+      </c>
+      <c r="AH114" s="4">
+        <f>IF(A114="","",IF(E114="","TERMINAL",IF(AG114="","INFO",IF(ABS(AG114)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -15793,10 +18539,31 @@
         <v/>
       </c>
       <c r="AA115" s="4">
-        <f>IF(A115="","",IF(OR(U115&gt;1,AND(X115&lt;&gt;"",X115&lt;Inputs!$B$16),AND(X115&lt;&gt;"",X115&gt;Inputs!$B$17),G115&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A115="","",IF(OR(U115&gt;1,AND(X115&lt;&gt;"",X115&lt;Inputs!$B$16),AND(X115&lt;&gt;"",X115&gt;Inputs!$B$17),G115&lt;Inputs!$B$18,AH115="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB115" s="4" t="n"/>
+      <c r="AC115" s="7" t="n"/>
+      <c r="AD115" s="8">
+        <f>IF(A115="","",IF(AC115&lt;&gt;"",AC115,IF(E115="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE115" s="8">
+        <f>IF(OR(AD115="",F115="",G115=""),"",AD115+F115*G115)</f>
+        <v/>
+      </c>
+      <c r="AF115" s="8">
+        <f>IF(OR(E115="",A115=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG115" s="8">
+        <f>IF(OR(AD115="",AF115=""),"",AD115-AF115)</f>
+        <v/>
+      </c>
+      <c r="AH115" s="4">
+        <f>IF(A115="","",IF(E115="","TERMINAL",IF(AG115="","INFO",IF(ABS(AG115)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -15867,10 +18634,31 @@
         <v/>
       </c>
       <c r="AA116" s="4">
-        <f>IF(A116="","",IF(OR(U116&gt;1,AND(X116&lt;&gt;"",X116&lt;Inputs!$B$16),AND(X116&lt;&gt;"",X116&gt;Inputs!$B$17),G116&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A116="","",IF(OR(U116&gt;1,AND(X116&lt;&gt;"",X116&lt;Inputs!$B$16),AND(X116&lt;&gt;"",X116&gt;Inputs!$B$17),G116&lt;Inputs!$B$18,AH116="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB116" s="4" t="n"/>
+      <c r="AC116" s="7" t="n"/>
+      <c r="AD116" s="8">
+        <f>IF(A116="","",IF(AC116&lt;&gt;"",AC116,IF(E116="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE116" s="8">
+        <f>IF(OR(AD116="",F116="",G116=""),"",AD116+F116*G116)</f>
+        <v/>
+      </c>
+      <c r="AF116" s="8">
+        <f>IF(OR(E116="",A116=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG116" s="8">
+        <f>IF(OR(AD116="",AF116=""),"",AD116-AF116)</f>
+        <v/>
+      </c>
+      <c r="AH116" s="4">
+        <f>IF(A116="","",IF(E116="","TERMINAL",IF(AG116="","INFO",IF(ABS(AG116)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -15941,10 +18729,31 @@
         <v/>
       </c>
       <c r="AA117" s="4">
-        <f>IF(A117="","",IF(OR(U117&gt;1,AND(X117&lt;&gt;"",X117&lt;Inputs!$B$16),AND(X117&lt;&gt;"",X117&gt;Inputs!$B$17),G117&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A117="","",IF(OR(U117&gt;1,AND(X117&lt;&gt;"",X117&lt;Inputs!$B$16),AND(X117&lt;&gt;"",X117&gt;Inputs!$B$17),G117&lt;Inputs!$B$18,AH117="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB117" s="4" t="n"/>
+      <c r="AC117" s="7" t="n"/>
+      <c r="AD117" s="8">
+        <f>IF(A117="","",IF(AC117&lt;&gt;"",AC117,IF(E117="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE117" s="8">
+        <f>IF(OR(AD117="",F117="",G117=""),"",AD117+F117*G117)</f>
+        <v/>
+      </c>
+      <c r="AF117" s="8">
+        <f>IF(OR(E117="",A117=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG117" s="8">
+        <f>IF(OR(AD117="",AF117=""),"",AD117-AF117)</f>
+        <v/>
+      </c>
+      <c r="AH117" s="4">
+        <f>IF(A117="","",IF(E117="","TERMINAL",IF(AG117="","INFO",IF(ABS(AG117)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n"/>
@@ -16015,10 +18824,31 @@
         <v/>
       </c>
       <c r="AA118" s="4">
-        <f>IF(A118="","",IF(OR(U118&gt;1,AND(X118&lt;&gt;"",X118&lt;Inputs!$B$16),AND(X118&lt;&gt;"",X118&gt;Inputs!$B$17),G118&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A118="","",IF(OR(U118&gt;1,AND(X118&lt;&gt;"",X118&lt;Inputs!$B$16),AND(X118&lt;&gt;"",X118&gt;Inputs!$B$17),G118&lt;Inputs!$B$18,AH118="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB118" s="4" t="n"/>
+      <c r="AC118" s="7" t="n"/>
+      <c r="AD118" s="8">
+        <f>IF(A118="","",IF(AC118&lt;&gt;"",AC118,IF(E118="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE118" s="8">
+        <f>IF(OR(AD118="",F118="",G118=""),"",AD118+F118*G118)</f>
+        <v/>
+      </c>
+      <c r="AF118" s="8">
+        <f>IF(OR(E118="",A118=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG118" s="8">
+        <f>IF(OR(AD118="",AF118=""),"",AD118-AF118)</f>
+        <v/>
+      </c>
+      <c r="AH118" s="4">
+        <f>IF(A118="","",IF(E118="","TERMINAL",IF(AG118="","INFO",IF(ABS(AG118)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -16089,10 +18919,31 @@
         <v/>
       </c>
       <c r="AA119" s="4">
-        <f>IF(A119="","",IF(OR(U119&gt;1,AND(X119&lt;&gt;"",X119&lt;Inputs!$B$16),AND(X119&lt;&gt;"",X119&gt;Inputs!$B$17),G119&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A119="","",IF(OR(U119&gt;1,AND(X119&lt;&gt;"",X119&lt;Inputs!$B$16),AND(X119&lt;&gt;"",X119&gt;Inputs!$B$17),G119&lt;Inputs!$B$18,AH119="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB119" s="4" t="n"/>
+      <c r="AC119" s="7" t="n"/>
+      <c r="AD119" s="8">
+        <f>IF(A119="","",IF(AC119&lt;&gt;"",AC119,IF(E119="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE119" s="8">
+        <f>IF(OR(AD119="",F119="",G119=""),"",AD119+F119*G119)</f>
+        <v/>
+      </c>
+      <c r="AF119" s="8">
+        <f>IF(OR(E119="",A119=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG119" s="8">
+        <f>IF(OR(AD119="",AF119=""),"",AD119-AF119)</f>
+        <v/>
+      </c>
+      <c r="AH119" s="4">
+        <f>IF(A119="","",IF(E119="","TERMINAL",IF(AG119="","INFO",IF(ABS(AG119)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n"/>
@@ -16163,10 +19014,31 @@
         <v/>
       </c>
       <c r="AA120" s="4">
-        <f>IF(A120="","",IF(OR(U120&gt;1,AND(X120&lt;&gt;"",X120&lt;Inputs!$B$16),AND(X120&lt;&gt;"",X120&gt;Inputs!$B$17),G120&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A120="","",IF(OR(U120&gt;1,AND(X120&lt;&gt;"",X120&lt;Inputs!$B$16),AND(X120&lt;&gt;"",X120&gt;Inputs!$B$17),G120&lt;Inputs!$B$18,AH120="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB120" s="4" t="n"/>
+      <c r="AC120" s="7" t="n"/>
+      <c r="AD120" s="8">
+        <f>IF(A120="","",IF(AC120&lt;&gt;"",AC120,IF(E120="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE120" s="8">
+        <f>IF(OR(AD120="",F120="",G120=""),"",AD120+F120*G120)</f>
+        <v/>
+      </c>
+      <c r="AF120" s="8">
+        <f>IF(OR(E120="",A120=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG120" s="8">
+        <f>IF(OR(AD120="",AF120=""),"",AD120-AF120)</f>
+        <v/>
+      </c>
+      <c r="AH120" s="4">
+        <f>IF(A120="","",IF(E120="","TERMINAL",IF(AG120="","INFO",IF(ABS(AG120)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -16237,10 +19109,31 @@
         <v/>
       </c>
       <c r="AA121" s="4">
-        <f>IF(A121="","",IF(OR(U121&gt;1,AND(X121&lt;&gt;"",X121&lt;Inputs!$B$16),AND(X121&lt;&gt;"",X121&gt;Inputs!$B$17),G121&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A121="","",IF(OR(U121&gt;1,AND(X121&lt;&gt;"",X121&lt;Inputs!$B$16),AND(X121&lt;&gt;"",X121&gt;Inputs!$B$17),G121&lt;Inputs!$B$18,AH121="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB121" s="4" t="n"/>
+      <c r="AC121" s="7" t="n"/>
+      <c r="AD121" s="8">
+        <f>IF(A121="","",IF(AC121&lt;&gt;"",AC121,IF(E121="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE121" s="8">
+        <f>IF(OR(AD121="",F121="",G121=""),"",AD121+F121*G121)</f>
+        <v/>
+      </c>
+      <c r="AF121" s="8">
+        <f>IF(OR(E121="",A121=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG121" s="8">
+        <f>IF(OR(AD121="",AF121=""),"",AD121-AF121)</f>
+        <v/>
+      </c>
+      <c r="AH121" s="4">
+        <f>IF(A121="","",IF(E121="","TERMINAL",IF(AG121="","INFO",IF(ABS(AG121)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -16311,10 +19204,31 @@
         <v/>
       </c>
       <c r="AA122" s="4">
-        <f>IF(A122="","",IF(OR(U122&gt;1,AND(X122&lt;&gt;"",X122&lt;Inputs!$B$16),AND(X122&lt;&gt;"",X122&gt;Inputs!$B$17),G122&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A122="","",IF(OR(U122&gt;1,AND(X122&lt;&gt;"",X122&lt;Inputs!$B$16),AND(X122&lt;&gt;"",X122&gt;Inputs!$B$17),G122&lt;Inputs!$B$18,AH122="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB122" s="4" t="n"/>
+      <c r="AC122" s="7" t="n"/>
+      <c r="AD122" s="8">
+        <f>IF(A122="","",IF(AC122&lt;&gt;"",AC122,IF(E122="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE122" s="8">
+        <f>IF(OR(AD122="",F122="",G122=""),"",AD122+F122*G122)</f>
+        <v/>
+      </c>
+      <c r="AF122" s="8">
+        <f>IF(OR(E122="",A122=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG122" s="8">
+        <f>IF(OR(AD122="",AF122=""),"",AD122-AF122)</f>
+        <v/>
+      </c>
+      <c r="AH122" s="4">
+        <f>IF(A122="","",IF(E122="","TERMINAL",IF(AG122="","INFO",IF(ABS(AG122)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -16385,10 +19299,31 @@
         <v/>
       </c>
       <c r="AA123" s="4">
-        <f>IF(A123="","",IF(OR(U123&gt;1,AND(X123&lt;&gt;"",X123&lt;Inputs!$B$16),AND(X123&lt;&gt;"",X123&gt;Inputs!$B$17),G123&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A123="","",IF(OR(U123&gt;1,AND(X123&lt;&gt;"",X123&lt;Inputs!$B$16),AND(X123&lt;&gt;"",X123&gt;Inputs!$B$17),G123&lt;Inputs!$B$18,AH123="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB123" s="4" t="n"/>
+      <c r="AC123" s="7" t="n"/>
+      <c r="AD123" s="8">
+        <f>IF(A123="","",IF(AC123&lt;&gt;"",AC123,IF(E123="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE123" s="8">
+        <f>IF(OR(AD123="",F123="",G123=""),"",AD123+F123*G123)</f>
+        <v/>
+      </c>
+      <c r="AF123" s="8">
+        <f>IF(OR(E123="",A123=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG123" s="8">
+        <f>IF(OR(AD123="",AF123=""),"",AD123-AF123)</f>
+        <v/>
+      </c>
+      <c r="AH123" s="4">
+        <f>IF(A123="","",IF(E123="","TERMINAL",IF(AG123="","INFO",IF(ABS(AG123)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n"/>
@@ -16459,10 +19394,31 @@
         <v/>
       </c>
       <c r="AA124" s="4">
-        <f>IF(A124="","",IF(OR(U124&gt;1,AND(X124&lt;&gt;"",X124&lt;Inputs!$B$16),AND(X124&lt;&gt;"",X124&gt;Inputs!$B$17),G124&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A124="","",IF(OR(U124&gt;1,AND(X124&lt;&gt;"",X124&lt;Inputs!$B$16),AND(X124&lt;&gt;"",X124&gt;Inputs!$B$17),G124&lt;Inputs!$B$18,AH124="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB124" s="4" t="n"/>
+      <c r="AC124" s="7" t="n"/>
+      <c r="AD124" s="8">
+        <f>IF(A124="","",IF(AC124&lt;&gt;"",AC124,IF(E124="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE124" s="8">
+        <f>IF(OR(AD124="",F124="",G124=""),"",AD124+F124*G124)</f>
+        <v/>
+      </c>
+      <c r="AF124" s="8">
+        <f>IF(OR(E124="",A124=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG124" s="8">
+        <f>IF(OR(AD124="",AF124=""),"",AD124-AF124)</f>
+        <v/>
+      </c>
+      <c r="AH124" s="4">
+        <f>IF(A124="","",IF(E124="","TERMINAL",IF(AG124="","INFO",IF(ABS(AG124)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -16533,10 +19489,31 @@
         <v/>
       </c>
       <c r="AA125" s="4">
-        <f>IF(A125="","",IF(OR(U125&gt;1,AND(X125&lt;&gt;"",X125&lt;Inputs!$B$16),AND(X125&lt;&gt;"",X125&gt;Inputs!$B$17),G125&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A125="","",IF(OR(U125&gt;1,AND(X125&lt;&gt;"",X125&lt;Inputs!$B$16),AND(X125&lt;&gt;"",X125&gt;Inputs!$B$17),G125&lt;Inputs!$B$18,AH125="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB125" s="4" t="n"/>
+      <c r="AC125" s="7" t="n"/>
+      <c r="AD125" s="8">
+        <f>IF(A125="","",IF(AC125&lt;&gt;"",AC125,IF(E125="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE125" s="8">
+        <f>IF(OR(AD125="",F125="",G125=""),"",AD125+F125*G125)</f>
+        <v/>
+      </c>
+      <c r="AF125" s="8">
+        <f>IF(OR(E125="",A125=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG125" s="8">
+        <f>IF(OR(AD125="",AF125=""),"",AD125-AF125)</f>
+        <v/>
+      </c>
+      <c r="AH125" s="4">
+        <f>IF(A125="","",IF(E125="","TERMINAL",IF(AG125="","INFO",IF(ABS(AG125)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -16607,10 +19584,31 @@
         <v/>
       </c>
       <c r="AA126" s="4">
-        <f>IF(A126="","",IF(OR(U126&gt;1,AND(X126&lt;&gt;"",X126&lt;Inputs!$B$16),AND(X126&lt;&gt;"",X126&gt;Inputs!$B$17),G126&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A126="","",IF(OR(U126&gt;1,AND(X126&lt;&gt;"",X126&lt;Inputs!$B$16),AND(X126&lt;&gt;"",X126&gt;Inputs!$B$17),G126&lt;Inputs!$B$18,AH126="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB126" s="4" t="n"/>
+      <c r="AC126" s="7" t="n"/>
+      <c r="AD126" s="8">
+        <f>IF(A126="","",IF(AC126&lt;&gt;"",AC126,IF(E126="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE126" s="8">
+        <f>IF(OR(AD126="",F126="",G126=""),"",AD126+F126*G126)</f>
+        <v/>
+      </c>
+      <c r="AF126" s="8">
+        <f>IF(OR(E126="",A126=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG126" s="8">
+        <f>IF(OR(AD126="",AF126=""),"",AD126-AF126)</f>
+        <v/>
+      </c>
+      <c r="AH126" s="4">
+        <f>IF(A126="","",IF(E126="","TERMINAL",IF(AG126="","INFO",IF(ABS(AG126)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -16681,10 +19679,31 @@
         <v/>
       </c>
       <c r="AA127" s="4">
-        <f>IF(A127="","",IF(OR(U127&gt;1,AND(X127&lt;&gt;"",X127&lt;Inputs!$B$16),AND(X127&lt;&gt;"",X127&gt;Inputs!$B$17),G127&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A127="","",IF(OR(U127&gt;1,AND(X127&lt;&gt;"",X127&lt;Inputs!$B$16),AND(X127&lt;&gt;"",X127&gt;Inputs!$B$17),G127&lt;Inputs!$B$18,AH127="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB127" s="4" t="n"/>
+      <c r="AC127" s="7" t="n"/>
+      <c r="AD127" s="8">
+        <f>IF(A127="","",IF(AC127&lt;&gt;"",AC127,IF(E127="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE127" s="8">
+        <f>IF(OR(AD127="",F127="",G127=""),"",AD127+F127*G127)</f>
+        <v/>
+      </c>
+      <c r="AF127" s="8">
+        <f>IF(OR(E127="",A127=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG127" s="8">
+        <f>IF(OR(AD127="",AF127=""),"",AD127-AF127)</f>
+        <v/>
+      </c>
+      <c r="AH127" s="4">
+        <f>IF(A127="","",IF(E127="","TERMINAL",IF(AG127="","INFO",IF(ABS(AG127)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n"/>
@@ -16755,10 +19774,31 @@
         <v/>
       </c>
       <c r="AA128" s="4">
-        <f>IF(A128="","",IF(OR(U128&gt;1,AND(X128&lt;&gt;"",X128&lt;Inputs!$B$16),AND(X128&lt;&gt;"",X128&gt;Inputs!$B$17),G128&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A128="","",IF(OR(U128&gt;1,AND(X128&lt;&gt;"",X128&lt;Inputs!$B$16),AND(X128&lt;&gt;"",X128&gt;Inputs!$B$17),G128&lt;Inputs!$B$18,AH128="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB128" s="4" t="n"/>
+      <c r="AC128" s="7" t="n"/>
+      <c r="AD128" s="8">
+        <f>IF(A128="","",IF(AC128&lt;&gt;"",AC128,IF(E128="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE128" s="8">
+        <f>IF(OR(AD128="",F128="",G128=""),"",AD128+F128*G128)</f>
+        <v/>
+      </c>
+      <c r="AF128" s="8">
+        <f>IF(OR(E128="",A128=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG128" s="8">
+        <f>IF(OR(AD128="",AF128=""),"",AD128-AF128)</f>
+        <v/>
+      </c>
+      <c r="AH128" s="4">
+        <f>IF(A128="","",IF(E128="","TERMINAL",IF(AG128="","INFO",IF(ABS(AG128)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -16829,10 +19869,31 @@
         <v/>
       </c>
       <c r="AA129" s="4">
-        <f>IF(A129="","",IF(OR(U129&gt;1,AND(X129&lt;&gt;"",X129&lt;Inputs!$B$16),AND(X129&lt;&gt;"",X129&gt;Inputs!$B$17),G129&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A129="","",IF(OR(U129&gt;1,AND(X129&lt;&gt;"",X129&lt;Inputs!$B$16),AND(X129&lt;&gt;"",X129&gt;Inputs!$B$17),G129&lt;Inputs!$B$18,AH129="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB129" s="4" t="n"/>
+      <c r="AC129" s="7" t="n"/>
+      <c r="AD129" s="8">
+        <f>IF(A129="","",IF(AC129&lt;&gt;"",AC129,IF(E129="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE129" s="8">
+        <f>IF(OR(AD129="",F129="",G129=""),"",AD129+F129*G129)</f>
+        <v/>
+      </c>
+      <c r="AF129" s="8">
+        <f>IF(OR(E129="",A129=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG129" s="8">
+        <f>IF(OR(AD129="",AF129=""),"",AD129-AF129)</f>
+        <v/>
+      </c>
+      <c r="AH129" s="4">
+        <f>IF(A129="","",IF(E129="","TERMINAL",IF(AG129="","INFO",IF(ABS(AG129)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n"/>
@@ -16903,10 +19964,31 @@
         <v/>
       </c>
       <c r="AA130" s="4">
-        <f>IF(A130="","",IF(OR(U130&gt;1,AND(X130&lt;&gt;"",X130&lt;Inputs!$B$16),AND(X130&lt;&gt;"",X130&gt;Inputs!$B$17),G130&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A130="","",IF(OR(U130&gt;1,AND(X130&lt;&gt;"",X130&lt;Inputs!$B$16),AND(X130&lt;&gt;"",X130&gt;Inputs!$B$17),G130&lt;Inputs!$B$18,AH130="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB130" s="4" t="n"/>
+      <c r="AC130" s="7" t="n"/>
+      <c r="AD130" s="8">
+        <f>IF(A130="","",IF(AC130&lt;&gt;"",AC130,IF(E130="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE130" s="8">
+        <f>IF(OR(AD130="",F130="",G130=""),"",AD130+F130*G130)</f>
+        <v/>
+      </c>
+      <c r="AF130" s="8">
+        <f>IF(OR(E130="",A130=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG130" s="8">
+        <f>IF(OR(AD130="",AF130=""),"",AD130-AF130)</f>
+        <v/>
+      </c>
+      <c r="AH130" s="4">
+        <f>IF(A130="","",IF(E130="","TERMINAL",IF(AG130="","INFO",IF(ABS(AG130)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -16977,10 +20059,31 @@
         <v/>
       </c>
       <c r="AA131" s="4">
-        <f>IF(A131="","",IF(OR(U131&gt;1,AND(X131&lt;&gt;"",X131&lt;Inputs!$B$16),AND(X131&lt;&gt;"",X131&gt;Inputs!$B$17),G131&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A131="","",IF(OR(U131&gt;1,AND(X131&lt;&gt;"",X131&lt;Inputs!$B$16),AND(X131&lt;&gt;"",X131&gt;Inputs!$B$17),G131&lt;Inputs!$B$18,AH131="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB131" s="4" t="n"/>
+      <c r="AC131" s="7" t="n"/>
+      <c r="AD131" s="8">
+        <f>IF(A131="","",IF(AC131&lt;&gt;"",AC131,IF(E131="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE131" s="8">
+        <f>IF(OR(AD131="",F131="",G131=""),"",AD131+F131*G131)</f>
+        <v/>
+      </c>
+      <c r="AF131" s="8">
+        <f>IF(OR(E131="",A131=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG131" s="8">
+        <f>IF(OR(AD131="",AF131=""),"",AD131-AF131)</f>
+        <v/>
+      </c>
+      <c r="AH131" s="4">
+        <f>IF(A131="","",IF(E131="","TERMINAL",IF(AG131="","INFO",IF(ABS(AG131)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n"/>
@@ -17051,10 +20154,31 @@
         <v/>
       </c>
       <c r="AA132" s="4">
-        <f>IF(A132="","",IF(OR(U132&gt;1,AND(X132&lt;&gt;"",X132&lt;Inputs!$B$16),AND(X132&lt;&gt;"",X132&gt;Inputs!$B$17),G132&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A132="","",IF(OR(U132&gt;1,AND(X132&lt;&gt;"",X132&lt;Inputs!$B$16),AND(X132&lt;&gt;"",X132&gt;Inputs!$B$17),G132&lt;Inputs!$B$18,AH132="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB132" s="4" t="n"/>
+      <c r="AC132" s="7" t="n"/>
+      <c r="AD132" s="8">
+        <f>IF(A132="","",IF(AC132&lt;&gt;"",AC132,IF(E132="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE132" s="8">
+        <f>IF(OR(AD132="",F132="",G132=""),"",AD132+F132*G132)</f>
+        <v/>
+      </c>
+      <c r="AF132" s="8">
+        <f>IF(OR(E132="",A132=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG132" s="8">
+        <f>IF(OR(AD132="",AF132=""),"",AD132-AF132)</f>
+        <v/>
+      </c>
+      <c r="AH132" s="4">
+        <f>IF(A132="","",IF(E132="","TERMINAL",IF(AG132="","INFO",IF(ABS(AG132)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -17125,10 +20249,31 @@
         <v/>
       </c>
       <c r="AA133" s="4">
-        <f>IF(A133="","",IF(OR(U133&gt;1,AND(X133&lt;&gt;"",X133&lt;Inputs!$B$16),AND(X133&lt;&gt;"",X133&gt;Inputs!$B$17),G133&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A133="","",IF(OR(U133&gt;1,AND(X133&lt;&gt;"",X133&lt;Inputs!$B$16),AND(X133&lt;&gt;"",X133&gt;Inputs!$B$17),G133&lt;Inputs!$B$18,AH133="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB133" s="4" t="n"/>
+      <c r="AC133" s="7" t="n"/>
+      <c r="AD133" s="8">
+        <f>IF(A133="","",IF(AC133&lt;&gt;"",AC133,IF(E133="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE133" s="8">
+        <f>IF(OR(AD133="",F133="",G133=""),"",AD133+F133*G133)</f>
+        <v/>
+      </c>
+      <c r="AF133" s="8">
+        <f>IF(OR(E133="",A133=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG133" s="8">
+        <f>IF(OR(AD133="",AF133=""),"",AD133-AF133)</f>
+        <v/>
+      </c>
+      <c r="AH133" s="4">
+        <f>IF(A133="","",IF(E133="","TERMINAL",IF(AG133="","INFO",IF(ABS(AG133)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n"/>
@@ -17199,10 +20344,31 @@
         <v/>
       </c>
       <c r="AA134" s="4">
-        <f>IF(A134="","",IF(OR(U134&gt;1,AND(X134&lt;&gt;"",X134&lt;Inputs!$B$16),AND(X134&lt;&gt;"",X134&gt;Inputs!$B$17),G134&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A134="","",IF(OR(U134&gt;1,AND(X134&lt;&gt;"",X134&lt;Inputs!$B$16),AND(X134&lt;&gt;"",X134&gt;Inputs!$B$17),G134&lt;Inputs!$B$18,AH134="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB134" s="4" t="n"/>
+      <c r="AC134" s="7" t="n"/>
+      <c r="AD134" s="8">
+        <f>IF(A134="","",IF(AC134&lt;&gt;"",AC134,IF(E134="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE134" s="8">
+        <f>IF(OR(AD134="",F134="",G134=""),"",AD134+F134*G134)</f>
+        <v/>
+      </c>
+      <c r="AF134" s="8">
+        <f>IF(OR(E134="",A134=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG134" s="8">
+        <f>IF(OR(AD134="",AF134=""),"",AD134-AF134)</f>
+        <v/>
+      </c>
+      <c r="AH134" s="4">
+        <f>IF(A134="","",IF(E134="","TERMINAL",IF(AG134="","INFO",IF(ABS(AG134)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -17273,10 +20439,31 @@
         <v/>
       </c>
       <c r="AA135" s="4">
-        <f>IF(A135="","",IF(OR(U135&gt;1,AND(X135&lt;&gt;"",X135&lt;Inputs!$B$16),AND(X135&lt;&gt;"",X135&gt;Inputs!$B$17),G135&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A135="","",IF(OR(U135&gt;1,AND(X135&lt;&gt;"",X135&lt;Inputs!$B$16),AND(X135&lt;&gt;"",X135&gt;Inputs!$B$17),G135&lt;Inputs!$B$18,AH135="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB135" s="4" t="n"/>
+      <c r="AC135" s="7" t="n"/>
+      <c r="AD135" s="8">
+        <f>IF(A135="","",IF(AC135&lt;&gt;"",AC135,IF(E135="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE135" s="8">
+        <f>IF(OR(AD135="",F135="",G135=""),"",AD135+F135*G135)</f>
+        <v/>
+      </c>
+      <c r="AF135" s="8">
+        <f>IF(OR(E135="",A135=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG135" s="8">
+        <f>IF(OR(AD135="",AF135=""),"",AD135-AF135)</f>
+        <v/>
+      </c>
+      <c r="AH135" s="4">
+        <f>IF(A135="","",IF(E135="","TERMINAL",IF(AG135="","INFO",IF(ABS(AG135)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n"/>
@@ -17347,10 +20534,31 @@
         <v/>
       </c>
       <c r="AA136" s="4">
-        <f>IF(A136="","",IF(OR(U136&gt;1,AND(X136&lt;&gt;"",X136&lt;Inputs!$B$16),AND(X136&lt;&gt;"",X136&gt;Inputs!$B$17),G136&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A136="","",IF(OR(U136&gt;1,AND(X136&lt;&gt;"",X136&lt;Inputs!$B$16),AND(X136&lt;&gt;"",X136&gt;Inputs!$B$17),G136&lt;Inputs!$B$18,AH136="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB136" s="4" t="n"/>
+      <c r="AC136" s="7" t="n"/>
+      <c r="AD136" s="8">
+        <f>IF(A136="","",IF(AC136&lt;&gt;"",AC136,IF(E136="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE136" s="8">
+        <f>IF(OR(AD136="",F136="",G136=""),"",AD136+F136*G136)</f>
+        <v/>
+      </c>
+      <c r="AF136" s="8">
+        <f>IF(OR(E136="",A136=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG136" s="8">
+        <f>IF(OR(AD136="",AF136=""),"",AD136-AF136)</f>
+        <v/>
+      </c>
+      <c r="AH136" s="4">
+        <f>IF(A136="","",IF(E136="","TERMINAL",IF(AG136="","INFO",IF(ABS(AG136)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -17421,10 +20629,31 @@
         <v/>
       </c>
       <c r="AA137" s="4">
-        <f>IF(A137="","",IF(OR(U137&gt;1,AND(X137&lt;&gt;"",X137&lt;Inputs!$B$16),AND(X137&lt;&gt;"",X137&gt;Inputs!$B$17),G137&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A137="","",IF(OR(U137&gt;1,AND(X137&lt;&gt;"",X137&lt;Inputs!$B$16),AND(X137&lt;&gt;"",X137&gt;Inputs!$B$17),G137&lt;Inputs!$B$18,AH137="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB137" s="4" t="n"/>
+      <c r="AC137" s="7" t="n"/>
+      <c r="AD137" s="8">
+        <f>IF(A137="","",IF(AC137&lt;&gt;"",AC137,IF(E137="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE137" s="8">
+        <f>IF(OR(AD137="",F137="",G137=""),"",AD137+F137*G137)</f>
+        <v/>
+      </c>
+      <c r="AF137" s="8">
+        <f>IF(OR(E137="",A137=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG137" s="8">
+        <f>IF(OR(AD137="",AF137=""),"",AD137-AF137)</f>
+        <v/>
+      </c>
+      <c r="AH137" s="4">
+        <f>IF(A137="","",IF(E137="","TERMINAL",IF(AG137="","INFO",IF(ABS(AG137)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -17495,10 +20724,31 @@
         <v/>
       </c>
       <c r="AA138" s="4">
-        <f>IF(A138="","",IF(OR(U138&gt;1,AND(X138&lt;&gt;"",X138&lt;Inputs!$B$16),AND(X138&lt;&gt;"",X138&gt;Inputs!$B$17),G138&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A138="","",IF(OR(U138&gt;1,AND(X138&lt;&gt;"",X138&lt;Inputs!$B$16),AND(X138&lt;&gt;"",X138&gt;Inputs!$B$17),G138&lt;Inputs!$B$18,AH138="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB138" s="4" t="n"/>
+      <c r="AC138" s="7" t="n"/>
+      <c r="AD138" s="8">
+        <f>IF(A138="","",IF(AC138&lt;&gt;"",AC138,IF(E138="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE138" s="8">
+        <f>IF(OR(AD138="",F138="",G138=""),"",AD138+F138*G138)</f>
+        <v/>
+      </c>
+      <c r="AF138" s="8">
+        <f>IF(OR(E138="",A138=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG138" s="8">
+        <f>IF(OR(AD138="",AF138=""),"",AD138-AF138)</f>
+        <v/>
+      </c>
+      <c r="AH138" s="4">
+        <f>IF(A138="","",IF(E138="","TERMINAL",IF(AG138="","INFO",IF(ABS(AG138)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -17569,10 +20819,31 @@
         <v/>
       </c>
       <c r="AA139" s="4">
-        <f>IF(A139="","",IF(OR(U139&gt;1,AND(X139&lt;&gt;"",X139&lt;Inputs!$B$16),AND(X139&lt;&gt;"",X139&gt;Inputs!$B$17),G139&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A139="","",IF(OR(U139&gt;1,AND(X139&lt;&gt;"",X139&lt;Inputs!$B$16),AND(X139&lt;&gt;"",X139&gt;Inputs!$B$17),G139&lt;Inputs!$B$18,AH139="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB139" s="4" t="n"/>
+      <c r="AC139" s="7" t="n"/>
+      <c r="AD139" s="8">
+        <f>IF(A139="","",IF(AC139&lt;&gt;"",AC139,IF(E139="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE139" s="8">
+        <f>IF(OR(AD139="",F139="",G139=""),"",AD139+F139*G139)</f>
+        <v/>
+      </c>
+      <c r="AF139" s="8">
+        <f>IF(OR(E139="",A139=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG139" s="8">
+        <f>IF(OR(AD139="",AF139=""),"",AD139-AF139)</f>
+        <v/>
+      </c>
+      <c r="AH139" s="4">
+        <f>IF(A139="","",IF(E139="","TERMINAL",IF(AG139="","INFO",IF(ABS(AG139)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n"/>
@@ -17643,10 +20914,31 @@
         <v/>
       </c>
       <c r="AA140" s="4">
-        <f>IF(A140="","",IF(OR(U140&gt;1,AND(X140&lt;&gt;"",X140&lt;Inputs!$B$16),AND(X140&lt;&gt;"",X140&gt;Inputs!$B$17),G140&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A140="","",IF(OR(U140&gt;1,AND(X140&lt;&gt;"",X140&lt;Inputs!$B$16),AND(X140&lt;&gt;"",X140&gt;Inputs!$B$17),G140&lt;Inputs!$B$18,AH140="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB140" s="4" t="n"/>
+      <c r="AC140" s="7" t="n"/>
+      <c r="AD140" s="8">
+        <f>IF(A140="","",IF(AC140&lt;&gt;"",AC140,IF(E140="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE140" s="8">
+        <f>IF(OR(AD140="",F140="",G140=""),"",AD140+F140*G140)</f>
+        <v/>
+      </c>
+      <c r="AF140" s="8">
+        <f>IF(OR(E140="",A140=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG140" s="8">
+        <f>IF(OR(AD140="",AF140=""),"",AD140-AF140)</f>
+        <v/>
+      </c>
+      <c r="AH140" s="4">
+        <f>IF(A140="","",IF(E140="","TERMINAL",IF(AG140="","INFO",IF(ABS(AG140)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -17717,10 +21009,31 @@
         <v/>
       </c>
       <c r="AA141" s="4">
-        <f>IF(A141="","",IF(OR(U141&gt;1,AND(X141&lt;&gt;"",X141&lt;Inputs!$B$16),AND(X141&lt;&gt;"",X141&gt;Inputs!$B$17),G141&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A141="","",IF(OR(U141&gt;1,AND(X141&lt;&gt;"",X141&lt;Inputs!$B$16),AND(X141&lt;&gt;"",X141&gt;Inputs!$B$17),G141&lt;Inputs!$B$18,AH141="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB141" s="4" t="n"/>
+      <c r="AC141" s="7" t="n"/>
+      <c r="AD141" s="8">
+        <f>IF(A141="","",IF(AC141&lt;&gt;"",AC141,IF(E141="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE141" s="8">
+        <f>IF(OR(AD141="",F141="",G141=""),"",AD141+F141*G141)</f>
+        <v/>
+      </c>
+      <c r="AF141" s="8">
+        <f>IF(OR(E141="",A141=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG141" s="8">
+        <f>IF(OR(AD141="",AF141=""),"",AD141-AF141)</f>
+        <v/>
+      </c>
+      <c r="AH141" s="4">
+        <f>IF(A141="","",IF(E141="","TERMINAL",IF(AG141="","INFO",IF(ABS(AG141)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
@@ -17791,10 +21104,31 @@
         <v/>
       </c>
       <c r="AA142" s="4">
-        <f>IF(A142="","",IF(OR(U142&gt;1,AND(X142&lt;&gt;"",X142&lt;Inputs!$B$16),AND(X142&lt;&gt;"",X142&gt;Inputs!$B$17),G142&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A142="","",IF(OR(U142&gt;1,AND(X142&lt;&gt;"",X142&lt;Inputs!$B$16),AND(X142&lt;&gt;"",X142&gt;Inputs!$B$17),G142&lt;Inputs!$B$18,AH142="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB142" s="4" t="n"/>
+      <c r="AC142" s="7" t="n"/>
+      <c r="AD142" s="8">
+        <f>IF(A142="","",IF(AC142&lt;&gt;"",AC142,IF(E142="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE142" s="8">
+        <f>IF(OR(AD142="",F142="",G142=""),"",AD142+F142*G142)</f>
+        <v/>
+      </c>
+      <c r="AF142" s="8">
+        <f>IF(OR(E142="",A142=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG142" s="8">
+        <f>IF(OR(AD142="",AF142=""),"",AD142-AF142)</f>
+        <v/>
+      </c>
+      <c r="AH142" s="4">
+        <f>IF(A142="","",IF(E142="","TERMINAL",IF(AG142="","INFO",IF(ABS(AG142)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -17865,10 +21199,31 @@
         <v/>
       </c>
       <c r="AA143" s="4">
-        <f>IF(A143="","",IF(OR(U143&gt;1,AND(X143&lt;&gt;"",X143&lt;Inputs!$B$16),AND(X143&lt;&gt;"",X143&gt;Inputs!$B$17),G143&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A143="","",IF(OR(U143&gt;1,AND(X143&lt;&gt;"",X143&lt;Inputs!$B$16),AND(X143&lt;&gt;"",X143&gt;Inputs!$B$17),G143&lt;Inputs!$B$18,AH143="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB143" s="4" t="n"/>
+      <c r="AC143" s="7" t="n"/>
+      <c r="AD143" s="8">
+        <f>IF(A143="","",IF(AC143&lt;&gt;"",AC143,IF(E143="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE143" s="8">
+        <f>IF(OR(AD143="",F143="",G143=""),"",AD143+F143*G143)</f>
+        <v/>
+      </c>
+      <c r="AF143" s="8">
+        <f>IF(OR(E143="",A143=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG143" s="8">
+        <f>IF(OR(AD143="",AF143=""),"",AD143-AF143)</f>
+        <v/>
+      </c>
+      <c r="AH143" s="4">
+        <f>IF(A143="","",IF(E143="","TERMINAL",IF(AG143="","INFO",IF(ABS(AG143)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
@@ -17939,10 +21294,31 @@
         <v/>
       </c>
       <c r="AA144" s="4">
-        <f>IF(A144="","",IF(OR(U144&gt;1,AND(X144&lt;&gt;"",X144&lt;Inputs!$B$16),AND(X144&lt;&gt;"",X144&gt;Inputs!$B$17),G144&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A144="","",IF(OR(U144&gt;1,AND(X144&lt;&gt;"",X144&lt;Inputs!$B$16),AND(X144&lt;&gt;"",X144&gt;Inputs!$B$17),G144&lt;Inputs!$B$18,AH144="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB144" s="4" t="n"/>
+      <c r="AC144" s="7" t="n"/>
+      <c r="AD144" s="8">
+        <f>IF(A144="","",IF(AC144&lt;&gt;"",AC144,IF(E144="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE144" s="8">
+        <f>IF(OR(AD144="",F144="",G144=""),"",AD144+F144*G144)</f>
+        <v/>
+      </c>
+      <c r="AF144" s="8">
+        <f>IF(OR(E144="",A144=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG144" s="8">
+        <f>IF(OR(AD144="",AF144=""),"",AD144-AF144)</f>
+        <v/>
+      </c>
+      <c r="AH144" s="4">
+        <f>IF(A144="","",IF(E144="","TERMINAL",IF(AG144="","INFO",IF(ABS(AG144)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -18013,10 +21389,31 @@
         <v/>
       </c>
       <c r="AA145" s="4">
-        <f>IF(A145="","",IF(OR(U145&gt;1,AND(X145&lt;&gt;"",X145&lt;Inputs!$B$16),AND(X145&lt;&gt;"",X145&gt;Inputs!$B$17),G145&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A145="","",IF(OR(U145&gt;1,AND(X145&lt;&gt;"",X145&lt;Inputs!$B$16),AND(X145&lt;&gt;"",X145&gt;Inputs!$B$17),G145&lt;Inputs!$B$18,AH145="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB145" s="4" t="n"/>
+      <c r="AC145" s="7" t="n"/>
+      <c r="AD145" s="8">
+        <f>IF(A145="","",IF(AC145&lt;&gt;"",AC145,IF(E145="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE145" s="8">
+        <f>IF(OR(AD145="",F145="",G145=""),"",AD145+F145*G145)</f>
+        <v/>
+      </c>
+      <c r="AF145" s="8">
+        <f>IF(OR(E145="",A145=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG145" s="8">
+        <f>IF(OR(AD145="",AF145=""),"",AD145-AF145)</f>
+        <v/>
+      </c>
+      <c r="AH145" s="4">
+        <f>IF(A145="","",IF(E145="","TERMINAL",IF(AG145="","INFO",IF(ABS(AG145)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -18087,10 +21484,31 @@
         <v/>
       </c>
       <c r="AA146" s="4">
-        <f>IF(A146="","",IF(OR(U146&gt;1,AND(X146&lt;&gt;"",X146&lt;Inputs!$B$16),AND(X146&lt;&gt;"",X146&gt;Inputs!$B$17),G146&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A146="","",IF(OR(U146&gt;1,AND(X146&lt;&gt;"",X146&lt;Inputs!$B$16),AND(X146&lt;&gt;"",X146&gt;Inputs!$B$17),G146&lt;Inputs!$B$18,AH146="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB146" s="4" t="n"/>
+      <c r="AC146" s="7" t="n"/>
+      <c r="AD146" s="8">
+        <f>IF(A146="","",IF(AC146&lt;&gt;"",AC146,IF(E146="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE146" s="8">
+        <f>IF(OR(AD146="",F146="",G146=""),"",AD146+F146*G146)</f>
+        <v/>
+      </c>
+      <c r="AF146" s="8">
+        <f>IF(OR(E146="",A146=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG146" s="8">
+        <f>IF(OR(AD146="",AF146=""),"",AD146-AF146)</f>
+        <v/>
+      </c>
+      <c r="AH146" s="4">
+        <f>IF(A146="","",IF(E146="","TERMINAL",IF(AG146="","INFO",IF(ABS(AG146)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -18161,10 +21579,31 @@
         <v/>
       </c>
       <c r="AA147" s="4">
-        <f>IF(A147="","",IF(OR(U147&gt;1,AND(X147&lt;&gt;"",X147&lt;Inputs!$B$16),AND(X147&lt;&gt;"",X147&gt;Inputs!$B$17),G147&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A147="","",IF(OR(U147&gt;1,AND(X147&lt;&gt;"",X147&lt;Inputs!$B$16),AND(X147&lt;&gt;"",X147&gt;Inputs!$B$17),G147&lt;Inputs!$B$18,AH147="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB147" s="4" t="n"/>
+      <c r="AC147" s="7" t="n"/>
+      <c r="AD147" s="8">
+        <f>IF(A147="","",IF(AC147&lt;&gt;"",AC147,IF(E147="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE147" s="8">
+        <f>IF(OR(AD147="",F147="",G147=""),"",AD147+F147*G147)</f>
+        <v/>
+      </c>
+      <c r="AF147" s="8">
+        <f>IF(OR(E147="",A147=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG147" s="8">
+        <f>IF(OR(AD147="",AF147=""),"",AD147-AF147)</f>
+        <v/>
+      </c>
+      <c r="AH147" s="4">
+        <f>IF(A147="","",IF(E147="","TERMINAL",IF(AG147="","INFO",IF(ABS(AG147)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n"/>
@@ -18235,10 +21674,31 @@
         <v/>
       </c>
       <c r="AA148" s="4">
-        <f>IF(A148="","",IF(OR(U148&gt;1,AND(X148&lt;&gt;"",X148&lt;Inputs!$B$16),AND(X148&lt;&gt;"",X148&gt;Inputs!$B$17),G148&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A148="","",IF(OR(U148&gt;1,AND(X148&lt;&gt;"",X148&lt;Inputs!$B$16),AND(X148&lt;&gt;"",X148&gt;Inputs!$B$17),G148&lt;Inputs!$B$18,AH148="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB148" s="4" t="n"/>
+      <c r="AC148" s="7" t="n"/>
+      <c r="AD148" s="8">
+        <f>IF(A148="","",IF(AC148&lt;&gt;"",AC148,IF(E148="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE148" s="8">
+        <f>IF(OR(AD148="",F148="",G148=""),"",AD148+F148*G148)</f>
+        <v/>
+      </c>
+      <c r="AF148" s="8">
+        <f>IF(OR(E148="",A148=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG148" s="8">
+        <f>IF(OR(AD148="",AF148=""),"",AD148-AF148)</f>
+        <v/>
+      </c>
+      <c r="AH148" s="4">
+        <f>IF(A148="","",IF(E148="","TERMINAL",IF(AG148="","INFO",IF(ABS(AG148)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -18309,10 +21769,31 @@
         <v/>
       </c>
       <c r="AA149" s="4">
-        <f>IF(A149="","",IF(OR(U149&gt;1,AND(X149&lt;&gt;"",X149&lt;Inputs!$B$16),AND(X149&lt;&gt;"",X149&gt;Inputs!$B$17),G149&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A149="","",IF(OR(U149&gt;1,AND(X149&lt;&gt;"",X149&lt;Inputs!$B$16),AND(X149&lt;&gt;"",X149&gt;Inputs!$B$17),G149&lt;Inputs!$B$18,AH149="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB149" s="4" t="n"/>
+      <c r="AC149" s="7" t="n"/>
+      <c r="AD149" s="8">
+        <f>IF(A149="","",IF(AC149&lt;&gt;"",AC149,IF(E149="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE149" s="8">
+        <f>IF(OR(AD149="",F149="",G149=""),"",AD149+F149*G149)</f>
+        <v/>
+      </c>
+      <c r="AF149" s="8">
+        <f>IF(OR(E149="",A149=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG149" s="8">
+        <f>IF(OR(AD149="",AF149=""),"",AD149-AF149)</f>
+        <v/>
+      </c>
+      <c r="AH149" s="4">
+        <f>IF(A149="","",IF(E149="","TERMINAL",IF(AG149="","INFO",IF(ABS(AG149)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n"/>
@@ -18383,10 +21864,31 @@
         <v/>
       </c>
       <c r="AA150" s="4">
-        <f>IF(A150="","",IF(OR(U150&gt;1,AND(X150&lt;&gt;"",X150&lt;Inputs!$B$16),AND(X150&lt;&gt;"",X150&gt;Inputs!$B$17),G150&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A150="","",IF(OR(U150&gt;1,AND(X150&lt;&gt;"",X150&lt;Inputs!$B$16),AND(X150&lt;&gt;"",X150&gt;Inputs!$B$17),G150&lt;Inputs!$B$18,AH150="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB150" s="4" t="n"/>
+      <c r="AC150" s="7" t="n"/>
+      <c r="AD150" s="8">
+        <f>IF(A150="","",IF(AC150&lt;&gt;"",AC150,IF(E150="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE150" s="8">
+        <f>IF(OR(AD150="",F150="",G150=""),"",AD150+F150*G150)</f>
+        <v/>
+      </c>
+      <c r="AF150" s="8">
+        <f>IF(OR(E150="",A150=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG150" s="8">
+        <f>IF(OR(AD150="",AF150=""),"",AD150-AF150)</f>
+        <v/>
+      </c>
+      <c r="AH150" s="4">
+        <f>IF(A150="","",IF(E150="","TERMINAL",IF(AG150="","INFO",IF(ABS(AG150)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -18457,10 +21959,31 @@
         <v/>
       </c>
       <c r="AA151" s="4">
-        <f>IF(A151="","",IF(OR(U151&gt;1,AND(X151&lt;&gt;"",X151&lt;Inputs!$B$16),AND(X151&lt;&gt;"",X151&gt;Inputs!$B$17),G151&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A151="","",IF(OR(U151&gt;1,AND(X151&lt;&gt;"",X151&lt;Inputs!$B$16),AND(X151&lt;&gt;"",X151&gt;Inputs!$B$17),G151&lt;Inputs!$B$18,AH151="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB151" s="4" t="n"/>
+      <c r="AC151" s="7" t="n"/>
+      <c r="AD151" s="8">
+        <f>IF(A151="","",IF(AC151&lt;&gt;"",AC151,IF(E151="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE151" s="8">
+        <f>IF(OR(AD151="",F151="",G151=""),"",AD151+F151*G151)</f>
+        <v/>
+      </c>
+      <c r="AF151" s="8">
+        <f>IF(OR(E151="",A151=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG151" s="8">
+        <f>IF(OR(AD151="",AF151=""),"",AD151-AF151)</f>
+        <v/>
+      </c>
+      <c r="AH151" s="4">
+        <f>IF(A151="","",IF(E151="","TERMINAL",IF(AG151="","INFO",IF(ABS(AG151)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -18531,10 +22054,31 @@
         <v/>
       </c>
       <c r="AA152" s="4">
-        <f>IF(A152="","",IF(OR(U152&gt;1,AND(X152&lt;&gt;"",X152&lt;Inputs!$B$16),AND(X152&lt;&gt;"",X152&gt;Inputs!$B$17),G152&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A152="","",IF(OR(U152&gt;1,AND(X152&lt;&gt;"",X152&lt;Inputs!$B$16),AND(X152&lt;&gt;"",X152&gt;Inputs!$B$17),G152&lt;Inputs!$B$18,AH152="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB152" s="4" t="n"/>
+      <c r="AC152" s="7" t="n"/>
+      <c r="AD152" s="8">
+        <f>IF(A152="","",IF(AC152&lt;&gt;"",AC152,IF(E152="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE152" s="8">
+        <f>IF(OR(AD152="",F152="",G152=""),"",AD152+F152*G152)</f>
+        <v/>
+      </c>
+      <c r="AF152" s="8">
+        <f>IF(OR(E152="",A152=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG152" s="8">
+        <f>IF(OR(AD152="",AF152=""),"",AD152-AF152)</f>
+        <v/>
+      </c>
+      <c r="AH152" s="4">
+        <f>IF(A152="","",IF(E152="","TERMINAL",IF(AG152="","INFO",IF(ABS(AG152)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -18605,10 +22149,31 @@
         <v/>
       </c>
       <c r="AA153" s="4">
-        <f>IF(A153="","",IF(OR(U153&gt;1,AND(X153&lt;&gt;"",X153&lt;Inputs!$B$16),AND(X153&lt;&gt;"",X153&gt;Inputs!$B$17),G153&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A153="","",IF(OR(U153&gt;1,AND(X153&lt;&gt;"",X153&lt;Inputs!$B$16),AND(X153&lt;&gt;"",X153&gt;Inputs!$B$17),G153&lt;Inputs!$B$18,AH153="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB153" s="4" t="n"/>
+      <c r="AC153" s="7" t="n"/>
+      <c r="AD153" s="8">
+        <f>IF(A153="","",IF(AC153&lt;&gt;"",AC153,IF(E153="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE153" s="8">
+        <f>IF(OR(AD153="",F153="",G153=""),"",AD153+F153*G153)</f>
+        <v/>
+      </c>
+      <c r="AF153" s="8">
+        <f>IF(OR(E153="",A153=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG153" s="8">
+        <f>IF(OR(AD153="",AF153=""),"",AD153-AF153)</f>
+        <v/>
+      </c>
+      <c r="AH153" s="4">
+        <f>IF(A153="","",IF(E153="","TERMINAL",IF(AG153="","INFO",IF(ABS(AG153)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
@@ -18679,10 +22244,31 @@
         <v/>
       </c>
       <c r="AA154" s="4">
-        <f>IF(A154="","",IF(OR(U154&gt;1,AND(X154&lt;&gt;"",X154&lt;Inputs!$B$16),AND(X154&lt;&gt;"",X154&gt;Inputs!$B$17),G154&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A154="","",IF(OR(U154&gt;1,AND(X154&lt;&gt;"",X154&lt;Inputs!$B$16),AND(X154&lt;&gt;"",X154&gt;Inputs!$B$17),G154&lt;Inputs!$B$18,AH154="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB154" s="4" t="n"/>
+      <c r="AC154" s="7" t="n"/>
+      <c r="AD154" s="8">
+        <f>IF(A154="","",IF(AC154&lt;&gt;"",AC154,IF(E154="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE154" s="8">
+        <f>IF(OR(AD154="",F154="",G154=""),"",AD154+F154*G154)</f>
+        <v/>
+      </c>
+      <c r="AF154" s="8">
+        <f>IF(OR(E154="",A154=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG154" s="8">
+        <f>IF(OR(AD154="",AF154=""),"",AD154-AF154)</f>
+        <v/>
+      </c>
+      <c r="AH154" s="4">
+        <f>IF(A154="","",IF(E154="","TERMINAL",IF(AG154="","INFO",IF(ABS(AG154)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -18753,10 +22339,31 @@
         <v/>
       </c>
       <c r="AA155" s="4">
-        <f>IF(A155="","",IF(OR(U155&gt;1,AND(X155&lt;&gt;"",X155&lt;Inputs!$B$16),AND(X155&lt;&gt;"",X155&gt;Inputs!$B$17),G155&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A155="","",IF(OR(U155&gt;1,AND(X155&lt;&gt;"",X155&lt;Inputs!$B$16),AND(X155&lt;&gt;"",X155&gt;Inputs!$B$17),G155&lt;Inputs!$B$18,AH155="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB155" s="4" t="n"/>
+      <c r="AC155" s="7" t="n"/>
+      <c r="AD155" s="8">
+        <f>IF(A155="","",IF(AC155&lt;&gt;"",AC155,IF(E155="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE155" s="8">
+        <f>IF(OR(AD155="",F155="",G155=""),"",AD155+F155*G155)</f>
+        <v/>
+      </c>
+      <c r="AF155" s="8">
+        <f>IF(OR(E155="",A155=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG155" s="8">
+        <f>IF(OR(AD155="",AF155=""),"",AD155-AF155)</f>
+        <v/>
+      </c>
+      <c r="AH155" s="4">
+        <f>IF(A155="","",IF(E155="","TERMINAL",IF(AG155="","INFO",IF(ABS(AG155)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -18827,10 +22434,31 @@
         <v/>
       </c>
       <c r="AA156" s="4">
-        <f>IF(A156="","",IF(OR(U156&gt;1,AND(X156&lt;&gt;"",X156&lt;Inputs!$B$16),AND(X156&lt;&gt;"",X156&gt;Inputs!$B$17),G156&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A156="","",IF(OR(U156&gt;1,AND(X156&lt;&gt;"",X156&lt;Inputs!$B$16),AND(X156&lt;&gt;"",X156&gt;Inputs!$B$17),G156&lt;Inputs!$B$18,AH156="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB156" s="4" t="n"/>
+      <c r="AC156" s="7" t="n"/>
+      <c r="AD156" s="8">
+        <f>IF(A156="","",IF(AC156&lt;&gt;"",AC156,IF(E156="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE156" s="8">
+        <f>IF(OR(AD156="",F156="",G156=""),"",AD156+F156*G156)</f>
+        <v/>
+      </c>
+      <c r="AF156" s="8">
+        <f>IF(OR(E156="",A156=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG156" s="8">
+        <f>IF(OR(AD156="",AF156=""),"",AD156-AF156)</f>
+        <v/>
+      </c>
+      <c r="AH156" s="4">
+        <f>IF(A156="","",IF(E156="","TERMINAL",IF(AG156="","INFO",IF(ABS(AG156)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -18901,10 +22529,31 @@
         <v/>
       </c>
       <c r="AA157" s="4">
-        <f>IF(A157="","",IF(OR(U157&gt;1,AND(X157&lt;&gt;"",X157&lt;Inputs!$B$16),AND(X157&lt;&gt;"",X157&gt;Inputs!$B$17),G157&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A157="","",IF(OR(U157&gt;1,AND(X157&lt;&gt;"",X157&lt;Inputs!$B$16),AND(X157&lt;&gt;"",X157&gt;Inputs!$B$17),G157&lt;Inputs!$B$18,AH157="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB157" s="4" t="n"/>
+      <c r="AC157" s="7" t="n"/>
+      <c r="AD157" s="8">
+        <f>IF(A157="","",IF(AC157&lt;&gt;"",AC157,IF(E157="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE157" s="8">
+        <f>IF(OR(AD157="",F157="",G157=""),"",AD157+F157*G157)</f>
+        <v/>
+      </c>
+      <c r="AF157" s="8">
+        <f>IF(OR(E157="",A157=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG157" s="8">
+        <f>IF(OR(AD157="",AF157=""),"",AD157-AF157)</f>
+        <v/>
+      </c>
+      <c r="AH157" s="4">
+        <f>IF(A157="","",IF(E157="","TERMINAL",IF(AG157="","INFO",IF(ABS(AG157)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -18975,10 +22624,31 @@
         <v/>
       </c>
       <c r="AA158" s="4">
-        <f>IF(A158="","",IF(OR(U158&gt;1,AND(X158&lt;&gt;"",X158&lt;Inputs!$B$16),AND(X158&lt;&gt;"",X158&gt;Inputs!$B$17),G158&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A158="","",IF(OR(U158&gt;1,AND(X158&lt;&gt;"",X158&lt;Inputs!$B$16),AND(X158&lt;&gt;"",X158&gt;Inputs!$B$17),G158&lt;Inputs!$B$18,AH158="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB158" s="4" t="n"/>
+      <c r="AC158" s="7" t="n"/>
+      <c r="AD158" s="8">
+        <f>IF(A158="","",IF(AC158&lt;&gt;"",AC158,IF(E158="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE158" s="8">
+        <f>IF(OR(AD158="",F158="",G158=""),"",AD158+F158*G158)</f>
+        <v/>
+      </c>
+      <c r="AF158" s="8">
+        <f>IF(OR(E158="",A158=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG158" s="8">
+        <f>IF(OR(AD158="",AF158=""),"",AD158-AF158)</f>
+        <v/>
+      </c>
+      <c r="AH158" s="4">
+        <f>IF(A158="","",IF(E158="","TERMINAL",IF(AG158="","INFO",IF(ABS(AG158)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -19049,10 +22719,31 @@
         <v/>
       </c>
       <c r="AA159" s="4">
-        <f>IF(A159="","",IF(OR(U159&gt;1,AND(X159&lt;&gt;"",X159&lt;Inputs!$B$16),AND(X159&lt;&gt;"",X159&gt;Inputs!$B$17),G159&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A159="","",IF(OR(U159&gt;1,AND(X159&lt;&gt;"",X159&lt;Inputs!$B$16),AND(X159&lt;&gt;"",X159&gt;Inputs!$B$17),G159&lt;Inputs!$B$18,AH159="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB159" s="4" t="n"/>
+      <c r="AC159" s="7" t="n"/>
+      <c r="AD159" s="8">
+        <f>IF(A159="","",IF(AC159&lt;&gt;"",AC159,IF(E159="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE159" s="8">
+        <f>IF(OR(AD159="",F159="",G159=""),"",AD159+F159*G159)</f>
+        <v/>
+      </c>
+      <c r="AF159" s="8">
+        <f>IF(OR(E159="",A159=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG159" s="8">
+        <f>IF(OR(AD159="",AF159=""),"",AD159-AF159)</f>
+        <v/>
+      </c>
+      <c r="AH159" s="4">
+        <f>IF(A159="","",IF(E159="","TERMINAL",IF(AG159="","INFO",IF(ABS(AG159)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
@@ -19123,10 +22814,31 @@
         <v/>
       </c>
       <c r="AA160" s="4">
-        <f>IF(A160="","",IF(OR(U160&gt;1,AND(X160&lt;&gt;"",X160&lt;Inputs!$B$16),AND(X160&lt;&gt;"",X160&gt;Inputs!$B$17),G160&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A160="","",IF(OR(U160&gt;1,AND(X160&lt;&gt;"",X160&lt;Inputs!$B$16),AND(X160&lt;&gt;"",X160&gt;Inputs!$B$17),G160&lt;Inputs!$B$18,AH160="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB160" s="4" t="n"/>
+      <c r="AC160" s="7" t="n"/>
+      <c r="AD160" s="8">
+        <f>IF(A160="","",IF(AC160&lt;&gt;"",AC160,IF(E160="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE160" s="8">
+        <f>IF(OR(AD160="",F160="",G160=""),"",AD160+F160*G160)</f>
+        <v/>
+      </c>
+      <c r="AF160" s="8">
+        <f>IF(OR(E160="",A160=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG160" s="8">
+        <f>IF(OR(AD160="",AF160=""),"",AD160-AF160)</f>
+        <v/>
+      </c>
+      <c r="AH160" s="4">
+        <f>IF(A160="","",IF(E160="","TERMINAL",IF(AG160="","INFO",IF(ABS(AG160)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -19197,10 +22909,31 @@
         <v/>
       </c>
       <c r="AA161" s="4">
-        <f>IF(A161="","",IF(OR(U161&gt;1,AND(X161&lt;&gt;"",X161&lt;Inputs!$B$16),AND(X161&lt;&gt;"",X161&gt;Inputs!$B$17),G161&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A161="","",IF(OR(U161&gt;1,AND(X161&lt;&gt;"",X161&lt;Inputs!$B$16),AND(X161&lt;&gt;"",X161&gt;Inputs!$B$17),G161&lt;Inputs!$B$18,AH161="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB161" s="4" t="n"/>
+      <c r="AC161" s="7" t="n"/>
+      <c r="AD161" s="8">
+        <f>IF(A161="","",IF(AC161&lt;&gt;"",AC161,IF(E161="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE161" s="8">
+        <f>IF(OR(AD161="",F161="",G161=""),"",AD161+F161*G161)</f>
+        <v/>
+      </c>
+      <c r="AF161" s="8">
+        <f>IF(OR(E161="",A161=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG161" s="8">
+        <f>IF(OR(AD161="",AF161=""),"",AD161-AF161)</f>
+        <v/>
+      </c>
+      <c r="AH161" s="4">
+        <f>IF(A161="","",IF(E161="","TERMINAL",IF(AG161="","INFO",IF(ABS(AG161)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -19271,10 +23004,31 @@
         <v/>
       </c>
       <c r="AA162" s="4">
-        <f>IF(A162="","",IF(OR(U162&gt;1,AND(X162&lt;&gt;"",X162&lt;Inputs!$B$16),AND(X162&lt;&gt;"",X162&gt;Inputs!$B$17),G162&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A162="","",IF(OR(U162&gt;1,AND(X162&lt;&gt;"",X162&lt;Inputs!$B$16),AND(X162&lt;&gt;"",X162&gt;Inputs!$B$17),G162&lt;Inputs!$B$18,AH162="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB162" s="4" t="n"/>
+      <c r="AC162" s="7" t="n"/>
+      <c r="AD162" s="8">
+        <f>IF(A162="","",IF(AC162&lt;&gt;"",AC162,IF(E162="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE162" s="8">
+        <f>IF(OR(AD162="",F162="",G162=""),"",AD162+F162*G162)</f>
+        <v/>
+      </c>
+      <c r="AF162" s="8">
+        <f>IF(OR(E162="",A162=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG162" s="8">
+        <f>IF(OR(AD162="",AF162=""),"",AD162-AF162)</f>
+        <v/>
+      </c>
+      <c r="AH162" s="4">
+        <f>IF(A162="","",IF(E162="","TERMINAL",IF(AG162="","INFO",IF(ABS(AG162)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -19345,10 +23099,31 @@
         <v/>
       </c>
       <c r="AA163" s="4">
-        <f>IF(A163="","",IF(OR(U163&gt;1,AND(X163&lt;&gt;"",X163&lt;Inputs!$B$16),AND(X163&lt;&gt;"",X163&gt;Inputs!$B$17),G163&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A163="","",IF(OR(U163&gt;1,AND(X163&lt;&gt;"",X163&lt;Inputs!$B$16),AND(X163&lt;&gt;"",X163&gt;Inputs!$B$17),G163&lt;Inputs!$B$18,AH163="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB163" s="4" t="n"/>
+      <c r="AC163" s="7" t="n"/>
+      <c r="AD163" s="8">
+        <f>IF(A163="","",IF(AC163&lt;&gt;"",AC163,IF(E163="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE163" s="8">
+        <f>IF(OR(AD163="",F163="",G163=""),"",AD163+F163*G163)</f>
+        <v/>
+      </c>
+      <c r="AF163" s="8">
+        <f>IF(OR(E163="",A163=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG163" s="8">
+        <f>IF(OR(AD163="",AF163=""),"",AD163-AF163)</f>
+        <v/>
+      </c>
+      <c r="AH163" s="4">
+        <f>IF(A163="","",IF(E163="","TERMINAL",IF(AG163="","INFO",IF(ABS(AG163)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -19419,10 +23194,31 @@
         <v/>
       </c>
       <c r="AA164" s="4">
-        <f>IF(A164="","",IF(OR(U164&gt;1,AND(X164&lt;&gt;"",X164&lt;Inputs!$B$16),AND(X164&lt;&gt;"",X164&gt;Inputs!$B$17),G164&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A164="","",IF(OR(U164&gt;1,AND(X164&lt;&gt;"",X164&lt;Inputs!$B$16),AND(X164&lt;&gt;"",X164&gt;Inputs!$B$17),G164&lt;Inputs!$B$18,AH164="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB164" s="4" t="n"/>
+      <c r="AC164" s="7" t="n"/>
+      <c r="AD164" s="8">
+        <f>IF(A164="","",IF(AC164&lt;&gt;"",AC164,IF(E164="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE164" s="8">
+        <f>IF(OR(AD164="",F164="",G164=""),"",AD164+F164*G164)</f>
+        <v/>
+      </c>
+      <c r="AF164" s="8">
+        <f>IF(OR(E164="",A164=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG164" s="8">
+        <f>IF(OR(AD164="",AF164=""),"",AD164-AF164)</f>
+        <v/>
+      </c>
+      <c r="AH164" s="4">
+        <f>IF(A164="","",IF(E164="","TERMINAL",IF(AG164="","INFO",IF(ABS(AG164)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -19493,10 +23289,31 @@
         <v/>
       </c>
       <c r="AA165" s="4">
-        <f>IF(A165="","",IF(OR(U165&gt;1,AND(X165&lt;&gt;"",X165&lt;Inputs!$B$16),AND(X165&lt;&gt;"",X165&gt;Inputs!$B$17),G165&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A165="","",IF(OR(U165&gt;1,AND(X165&lt;&gt;"",X165&lt;Inputs!$B$16),AND(X165&lt;&gt;"",X165&gt;Inputs!$B$17),G165&lt;Inputs!$B$18,AH165="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB165" s="4" t="n"/>
+      <c r="AC165" s="7" t="n"/>
+      <c r="AD165" s="8">
+        <f>IF(A165="","",IF(AC165&lt;&gt;"",AC165,IF(E165="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE165" s="8">
+        <f>IF(OR(AD165="",F165="",G165=""),"",AD165+F165*G165)</f>
+        <v/>
+      </c>
+      <c r="AF165" s="8">
+        <f>IF(OR(E165="",A165=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG165" s="8">
+        <f>IF(OR(AD165="",AF165=""),"",AD165-AF165)</f>
+        <v/>
+      </c>
+      <c r="AH165" s="4">
+        <f>IF(A165="","",IF(E165="","TERMINAL",IF(AG165="","INFO",IF(ABS(AG165)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -19567,10 +23384,31 @@
         <v/>
       </c>
       <c r="AA166" s="4">
-        <f>IF(A166="","",IF(OR(U166&gt;1,AND(X166&lt;&gt;"",X166&lt;Inputs!$B$16),AND(X166&lt;&gt;"",X166&gt;Inputs!$B$17),G166&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A166="","",IF(OR(U166&gt;1,AND(X166&lt;&gt;"",X166&lt;Inputs!$B$16),AND(X166&lt;&gt;"",X166&gt;Inputs!$B$17),G166&lt;Inputs!$B$18,AH166="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB166" s="4" t="n"/>
+      <c r="AC166" s="7" t="n"/>
+      <c r="AD166" s="8">
+        <f>IF(A166="","",IF(AC166&lt;&gt;"",AC166,IF(E166="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE166" s="8">
+        <f>IF(OR(AD166="",F166="",G166=""),"",AD166+F166*G166)</f>
+        <v/>
+      </c>
+      <c r="AF166" s="8">
+        <f>IF(OR(E166="",A166=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG166" s="8">
+        <f>IF(OR(AD166="",AF166=""),"",AD166-AF166)</f>
+        <v/>
+      </c>
+      <c r="AH166" s="4">
+        <f>IF(A166="","",IF(E166="","TERMINAL",IF(AG166="","INFO",IF(ABS(AG166)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -19641,10 +23479,31 @@
         <v/>
       </c>
       <c r="AA167" s="4">
-        <f>IF(A167="","",IF(OR(U167&gt;1,AND(X167&lt;&gt;"",X167&lt;Inputs!$B$16),AND(X167&lt;&gt;"",X167&gt;Inputs!$B$17),G167&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A167="","",IF(OR(U167&gt;1,AND(X167&lt;&gt;"",X167&lt;Inputs!$B$16),AND(X167&lt;&gt;"",X167&gt;Inputs!$B$17),G167&lt;Inputs!$B$18,AH167="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB167" s="4" t="n"/>
+      <c r="AC167" s="7" t="n"/>
+      <c r="AD167" s="8">
+        <f>IF(A167="","",IF(AC167&lt;&gt;"",AC167,IF(E167="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE167" s="8">
+        <f>IF(OR(AD167="",F167="",G167=""),"",AD167+F167*G167)</f>
+        <v/>
+      </c>
+      <c r="AF167" s="8">
+        <f>IF(OR(E167="",A167=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG167" s="8">
+        <f>IF(OR(AD167="",AF167=""),"",AD167-AF167)</f>
+        <v/>
+      </c>
+      <c r="AH167" s="4">
+        <f>IF(A167="","",IF(E167="","TERMINAL",IF(AG167="","INFO",IF(ABS(AG167)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
@@ -19715,10 +23574,31 @@
         <v/>
       </c>
       <c r="AA168" s="4">
-        <f>IF(A168="","",IF(OR(U168&gt;1,AND(X168&lt;&gt;"",X168&lt;Inputs!$B$16),AND(X168&lt;&gt;"",X168&gt;Inputs!$B$17),G168&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A168="","",IF(OR(U168&gt;1,AND(X168&lt;&gt;"",X168&lt;Inputs!$B$16),AND(X168&lt;&gt;"",X168&gt;Inputs!$B$17),G168&lt;Inputs!$B$18,AH168="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB168" s="4" t="n"/>
+      <c r="AC168" s="7" t="n"/>
+      <c r="AD168" s="8">
+        <f>IF(A168="","",IF(AC168&lt;&gt;"",AC168,IF(E168="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE168" s="8">
+        <f>IF(OR(AD168="",F168="",G168=""),"",AD168+F168*G168)</f>
+        <v/>
+      </c>
+      <c r="AF168" s="8">
+        <f>IF(OR(E168="",A168=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG168" s="8">
+        <f>IF(OR(AD168="",AF168=""),"",AD168-AF168)</f>
+        <v/>
+      </c>
+      <c r="AH168" s="4">
+        <f>IF(A168="","",IF(E168="","TERMINAL",IF(AG168="","INFO",IF(ABS(AG168)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -19789,10 +23669,31 @@
         <v/>
       </c>
       <c r="AA169" s="4">
-        <f>IF(A169="","",IF(OR(U169&gt;1,AND(X169&lt;&gt;"",X169&lt;Inputs!$B$16),AND(X169&lt;&gt;"",X169&gt;Inputs!$B$17),G169&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A169="","",IF(OR(U169&gt;1,AND(X169&lt;&gt;"",X169&lt;Inputs!$B$16),AND(X169&lt;&gt;"",X169&gt;Inputs!$B$17),G169&lt;Inputs!$B$18,AH169="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB169" s="4" t="n"/>
+      <c r="AC169" s="7" t="n"/>
+      <c r="AD169" s="8">
+        <f>IF(A169="","",IF(AC169&lt;&gt;"",AC169,IF(E169="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE169" s="8">
+        <f>IF(OR(AD169="",F169="",G169=""),"",AD169+F169*G169)</f>
+        <v/>
+      </c>
+      <c r="AF169" s="8">
+        <f>IF(OR(E169="",A169=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG169" s="8">
+        <f>IF(OR(AD169="",AF169=""),"",AD169-AF169)</f>
+        <v/>
+      </c>
+      <c r="AH169" s="4">
+        <f>IF(A169="","",IF(E169="","TERMINAL",IF(AG169="","INFO",IF(ABS(AG169)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -19863,10 +23764,31 @@
         <v/>
       </c>
       <c r="AA170" s="4">
-        <f>IF(A170="","",IF(OR(U170&gt;1,AND(X170&lt;&gt;"",X170&lt;Inputs!$B$16),AND(X170&lt;&gt;"",X170&gt;Inputs!$B$17),G170&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A170="","",IF(OR(U170&gt;1,AND(X170&lt;&gt;"",X170&lt;Inputs!$B$16),AND(X170&lt;&gt;"",X170&gt;Inputs!$B$17),G170&lt;Inputs!$B$18,AH170="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB170" s="4" t="n"/>
+      <c r="AC170" s="7" t="n"/>
+      <c r="AD170" s="8">
+        <f>IF(A170="","",IF(AC170&lt;&gt;"",AC170,IF(E170="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE170" s="8">
+        <f>IF(OR(AD170="",F170="",G170=""),"",AD170+F170*G170)</f>
+        <v/>
+      </c>
+      <c r="AF170" s="8">
+        <f>IF(OR(E170="",A170=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG170" s="8">
+        <f>IF(OR(AD170="",AF170=""),"",AD170-AF170)</f>
+        <v/>
+      </c>
+      <c r="AH170" s="4">
+        <f>IF(A170="","",IF(E170="","TERMINAL",IF(AG170="","INFO",IF(ABS(AG170)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -19937,10 +23859,31 @@
         <v/>
       </c>
       <c r="AA171" s="4">
-        <f>IF(A171="","",IF(OR(U171&gt;1,AND(X171&lt;&gt;"",X171&lt;Inputs!$B$16),AND(X171&lt;&gt;"",X171&gt;Inputs!$B$17),G171&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A171="","",IF(OR(U171&gt;1,AND(X171&lt;&gt;"",X171&lt;Inputs!$B$16),AND(X171&lt;&gt;"",X171&gt;Inputs!$B$17),G171&lt;Inputs!$B$18,AH171="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB171" s="4" t="n"/>
+      <c r="AC171" s="7" t="n"/>
+      <c r="AD171" s="8">
+        <f>IF(A171="","",IF(AC171&lt;&gt;"",AC171,IF(E171="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE171" s="8">
+        <f>IF(OR(AD171="",F171="",G171=""),"",AD171+F171*G171)</f>
+        <v/>
+      </c>
+      <c r="AF171" s="8">
+        <f>IF(OR(E171="",A171=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG171" s="8">
+        <f>IF(OR(AD171="",AF171=""),"",AD171-AF171)</f>
+        <v/>
+      </c>
+      <c r="AH171" s="4">
+        <f>IF(A171="","",IF(E171="","TERMINAL",IF(AG171="","INFO",IF(ABS(AG171)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -20011,10 +23954,31 @@
         <v/>
       </c>
       <c r="AA172" s="4">
-        <f>IF(A172="","",IF(OR(U172&gt;1,AND(X172&lt;&gt;"",X172&lt;Inputs!$B$16),AND(X172&lt;&gt;"",X172&gt;Inputs!$B$17),G172&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A172="","",IF(OR(U172&gt;1,AND(X172&lt;&gt;"",X172&lt;Inputs!$B$16),AND(X172&lt;&gt;"",X172&gt;Inputs!$B$17),G172&lt;Inputs!$B$18,AH172="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB172" s="4" t="n"/>
+      <c r="AC172" s="7" t="n"/>
+      <c r="AD172" s="8">
+        <f>IF(A172="","",IF(AC172&lt;&gt;"",AC172,IF(E172="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE172" s="8">
+        <f>IF(OR(AD172="",F172="",G172=""),"",AD172+F172*G172)</f>
+        <v/>
+      </c>
+      <c r="AF172" s="8">
+        <f>IF(OR(E172="",A172=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG172" s="8">
+        <f>IF(OR(AD172="",AF172=""),"",AD172-AF172)</f>
+        <v/>
+      </c>
+      <c r="AH172" s="4">
+        <f>IF(A172="","",IF(E172="","TERMINAL",IF(AG172="","INFO",IF(ABS(AG172)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -20085,10 +24049,31 @@
         <v/>
       </c>
       <c r="AA173" s="4">
-        <f>IF(A173="","",IF(OR(U173&gt;1,AND(X173&lt;&gt;"",X173&lt;Inputs!$B$16),AND(X173&lt;&gt;"",X173&gt;Inputs!$B$17),G173&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A173="","",IF(OR(U173&gt;1,AND(X173&lt;&gt;"",X173&lt;Inputs!$B$16),AND(X173&lt;&gt;"",X173&gt;Inputs!$B$17),G173&lt;Inputs!$B$18,AH173="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB173" s="4" t="n"/>
+      <c r="AC173" s="7" t="n"/>
+      <c r="AD173" s="8">
+        <f>IF(A173="","",IF(AC173&lt;&gt;"",AC173,IF(E173="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE173" s="8">
+        <f>IF(OR(AD173="",F173="",G173=""),"",AD173+F173*G173)</f>
+        <v/>
+      </c>
+      <c r="AF173" s="8">
+        <f>IF(OR(E173="",A173=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG173" s="8">
+        <f>IF(OR(AD173="",AF173=""),"",AD173-AF173)</f>
+        <v/>
+      </c>
+      <c r="AH173" s="4">
+        <f>IF(A173="","",IF(E173="","TERMINAL",IF(AG173="","INFO",IF(ABS(AG173)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
@@ -20159,10 +24144,31 @@
         <v/>
       </c>
       <c r="AA174" s="4">
-        <f>IF(A174="","",IF(OR(U174&gt;1,AND(X174&lt;&gt;"",X174&lt;Inputs!$B$16),AND(X174&lt;&gt;"",X174&gt;Inputs!$B$17),G174&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A174="","",IF(OR(U174&gt;1,AND(X174&lt;&gt;"",X174&lt;Inputs!$B$16),AND(X174&lt;&gt;"",X174&gt;Inputs!$B$17),G174&lt;Inputs!$B$18,AH174="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB174" s="4" t="n"/>
+      <c r="AC174" s="7" t="n"/>
+      <c r="AD174" s="8">
+        <f>IF(A174="","",IF(AC174&lt;&gt;"",AC174,IF(E174="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE174" s="8">
+        <f>IF(OR(AD174="",F174="",G174=""),"",AD174+F174*G174)</f>
+        <v/>
+      </c>
+      <c r="AF174" s="8">
+        <f>IF(OR(E174="",A174=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG174" s="8">
+        <f>IF(OR(AD174="",AF174=""),"",AD174-AF174)</f>
+        <v/>
+      </c>
+      <c r="AH174" s="4">
+        <f>IF(A174="","",IF(E174="","TERMINAL",IF(AG174="","INFO",IF(ABS(AG174)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -20233,10 +24239,31 @@
         <v/>
       </c>
       <c r="AA175" s="4">
-        <f>IF(A175="","",IF(OR(U175&gt;1,AND(X175&lt;&gt;"",X175&lt;Inputs!$B$16),AND(X175&lt;&gt;"",X175&gt;Inputs!$B$17),G175&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A175="","",IF(OR(U175&gt;1,AND(X175&lt;&gt;"",X175&lt;Inputs!$B$16),AND(X175&lt;&gt;"",X175&gt;Inputs!$B$17),G175&lt;Inputs!$B$18,AH175="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB175" s="4" t="n"/>
+      <c r="AC175" s="7" t="n"/>
+      <c r="AD175" s="8">
+        <f>IF(A175="","",IF(AC175&lt;&gt;"",AC175,IF(E175="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE175" s="8">
+        <f>IF(OR(AD175="",F175="",G175=""),"",AD175+F175*G175)</f>
+        <v/>
+      </c>
+      <c r="AF175" s="8">
+        <f>IF(OR(E175="",A175=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG175" s="8">
+        <f>IF(OR(AD175="",AF175=""),"",AD175-AF175)</f>
+        <v/>
+      </c>
+      <c r="AH175" s="4">
+        <f>IF(A175="","",IF(E175="","TERMINAL",IF(AG175="","INFO",IF(ABS(AG175)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -20307,10 +24334,31 @@
         <v/>
       </c>
       <c r="AA176" s="4">
-        <f>IF(A176="","",IF(OR(U176&gt;1,AND(X176&lt;&gt;"",X176&lt;Inputs!$B$16),AND(X176&lt;&gt;"",X176&gt;Inputs!$B$17),G176&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A176="","",IF(OR(U176&gt;1,AND(X176&lt;&gt;"",X176&lt;Inputs!$B$16),AND(X176&lt;&gt;"",X176&gt;Inputs!$B$17),G176&lt;Inputs!$B$18,AH176="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB176" s="4" t="n"/>
+      <c r="AC176" s="7" t="n"/>
+      <c r="AD176" s="8">
+        <f>IF(A176="","",IF(AC176&lt;&gt;"",AC176,IF(E176="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE176" s="8">
+        <f>IF(OR(AD176="",F176="",G176=""),"",AD176+F176*G176)</f>
+        <v/>
+      </c>
+      <c r="AF176" s="8">
+        <f>IF(OR(E176="",A176=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG176" s="8">
+        <f>IF(OR(AD176="",AF176=""),"",AD176-AF176)</f>
+        <v/>
+      </c>
+      <c r="AH176" s="4">
+        <f>IF(A176="","",IF(E176="","TERMINAL",IF(AG176="","INFO",IF(ABS(AG176)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -20381,10 +24429,31 @@
         <v/>
       </c>
       <c r="AA177" s="4">
-        <f>IF(A177="","",IF(OR(U177&gt;1,AND(X177&lt;&gt;"",X177&lt;Inputs!$B$16),AND(X177&lt;&gt;"",X177&gt;Inputs!$B$17),G177&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A177="","",IF(OR(U177&gt;1,AND(X177&lt;&gt;"",X177&lt;Inputs!$B$16),AND(X177&lt;&gt;"",X177&gt;Inputs!$B$17),G177&lt;Inputs!$B$18,AH177="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB177" s="4" t="n"/>
+      <c r="AC177" s="7" t="n"/>
+      <c r="AD177" s="8">
+        <f>IF(A177="","",IF(AC177&lt;&gt;"",AC177,IF(E177="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE177" s="8">
+        <f>IF(OR(AD177="",F177="",G177=""),"",AD177+F177*G177)</f>
+        <v/>
+      </c>
+      <c r="AF177" s="8">
+        <f>IF(OR(E177="",A177=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG177" s="8">
+        <f>IF(OR(AD177="",AF177=""),"",AD177-AF177)</f>
+        <v/>
+      </c>
+      <c r="AH177" s="4">
+        <f>IF(A177="","",IF(E177="","TERMINAL",IF(AG177="","INFO",IF(ABS(AG177)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n"/>
@@ -20455,10 +24524,31 @@
         <v/>
       </c>
       <c r="AA178" s="4">
-        <f>IF(A178="","",IF(OR(U178&gt;1,AND(X178&lt;&gt;"",X178&lt;Inputs!$B$16),AND(X178&lt;&gt;"",X178&gt;Inputs!$B$17),G178&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A178="","",IF(OR(U178&gt;1,AND(X178&lt;&gt;"",X178&lt;Inputs!$B$16),AND(X178&lt;&gt;"",X178&gt;Inputs!$B$17),G178&lt;Inputs!$B$18,AH178="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB178" s="4" t="n"/>
+      <c r="AC178" s="7" t="n"/>
+      <c r="AD178" s="8">
+        <f>IF(A178="","",IF(AC178&lt;&gt;"",AC178,IF(E178="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE178" s="8">
+        <f>IF(OR(AD178="",F178="",G178=""),"",AD178+F178*G178)</f>
+        <v/>
+      </c>
+      <c r="AF178" s="8">
+        <f>IF(OR(E178="",A178=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG178" s="8">
+        <f>IF(OR(AD178="",AF178=""),"",AD178-AF178)</f>
+        <v/>
+      </c>
+      <c r="AH178" s="4">
+        <f>IF(A178="","",IF(E178="","TERMINAL",IF(AG178="","INFO",IF(ABS(AG178)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -20529,10 +24619,31 @@
         <v/>
       </c>
       <c r="AA179" s="4">
-        <f>IF(A179="","",IF(OR(U179&gt;1,AND(X179&lt;&gt;"",X179&lt;Inputs!$B$16),AND(X179&lt;&gt;"",X179&gt;Inputs!$B$17),G179&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A179="","",IF(OR(U179&gt;1,AND(X179&lt;&gt;"",X179&lt;Inputs!$B$16),AND(X179&lt;&gt;"",X179&gt;Inputs!$B$17),G179&lt;Inputs!$B$18,AH179="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB179" s="4" t="n"/>
+      <c r="AC179" s="7" t="n"/>
+      <c r="AD179" s="8">
+        <f>IF(A179="","",IF(AC179&lt;&gt;"",AC179,IF(E179="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE179" s="8">
+        <f>IF(OR(AD179="",F179="",G179=""),"",AD179+F179*G179)</f>
+        <v/>
+      </c>
+      <c r="AF179" s="8">
+        <f>IF(OR(E179="",A179=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG179" s="8">
+        <f>IF(OR(AD179="",AF179=""),"",AD179-AF179)</f>
+        <v/>
+      </c>
+      <c r="AH179" s="4">
+        <f>IF(A179="","",IF(E179="","TERMINAL",IF(AG179="","INFO",IF(ABS(AG179)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n"/>
@@ -20603,10 +24714,31 @@
         <v/>
       </c>
       <c r="AA180" s="4">
-        <f>IF(A180="","",IF(OR(U180&gt;1,AND(X180&lt;&gt;"",X180&lt;Inputs!$B$16),AND(X180&lt;&gt;"",X180&gt;Inputs!$B$17),G180&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A180="","",IF(OR(U180&gt;1,AND(X180&lt;&gt;"",X180&lt;Inputs!$B$16),AND(X180&lt;&gt;"",X180&gt;Inputs!$B$17),G180&lt;Inputs!$B$18,AH180="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB180" s="4" t="n"/>
+      <c r="AC180" s="7" t="n"/>
+      <c r="AD180" s="8">
+        <f>IF(A180="","",IF(AC180&lt;&gt;"",AC180,IF(E180="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE180" s="8">
+        <f>IF(OR(AD180="",F180="",G180=""),"",AD180+F180*G180)</f>
+        <v/>
+      </c>
+      <c r="AF180" s="8">
+        <f>IF(OR(E180="",A180=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG180" s="8">
+        <f>IF(OR(AD180="",AF180=""),"",AD180-AF180)</f>
+        <v/>
+      </c>
+      <c r="AH180" s="4">
+        <f>IF(A180="","",IF(E180="","TERMINAL",IF(AG180="","INFO",IF(ABS(AG180)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -20677,10 +24809,31 @@
         <v/>
       </c>
       <c r="AA181" s="4">
-        <f>IF(A181="","",IF(OR(U181&gt;1,AND(X181&lt;&gt;"",X181&lt;Inputs!$B$16),AND(X181&lt;&gt;"",X181&gt;Inputs!$B$17),G181&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A181="","",IF(OR(U181&gt;1,AND(X181&lt;&gt;"",X181&lt;Inputs!$B$16),AND(X181&lt;&gt;"",X181&gt;Inputs!$B$17),G181&lt;Inputs!$B$18,AH181="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB181" s="4" t="n"/>
+      <c r="AC181" s="7" t="n"/>
+      <c r="AD181" s="8">
+        <f>IF(A181="","",IF(AC181&lt;&gt;"",AC181,IF(E181="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE181" s="8">
+        <f>IF(OR(AD181="",F181="",G181=""),"",AD181+F181*G181)</f>
+        <v/>
+      </c>
+      <c r="AF181" s="8">
+        <f>IF(OR(E181="",A181=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG181" s="8">
+        <f>IF(OR(AD181="",AF181=""),"",AD181-AF181)</f>
+        <v/>
+      </c>
+      <c r="AH181" s="4">
+        <f>IF(A181="","",IF(E181="","TERMINAL",IF(AG181="","INFO",IF(ABS(AG181)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -20751,10 +24904,31 @@
         <v/>
       </c>
       <c r="AA182" s="4">
-        <f>IF(A182="","",IF(OR(U182&gt;1,AND(X182&lt;&gt;"",X182&lt;Inputs!$B$16),AND(X182&lt;&gt;"",X182&gt;Inputs!$B$17),G182&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A182="","",IF(OR(U182&gt;1,AND(X182&lt;&gt;"",X182&lt;Inputs!$B$16),AND(X182&lt;&gt;"",X182&gt;Inputs!$B$17),G182&lt;Inputs!$B$18,AH182="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB182" s="4" t="n"/>
+      <c r="AC182" s="7" t="n"/>
+      <c r="AD182" s="8">
+        <f>IF(A182="","",IF(AC182&lt;&gt;"",AC182,IF(E182="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE182" s="8">
+        <f>IF(OR(AD182="",F182="",G182=""),"",AD182+F182*G182)</f>
+        <v/>
+      </c>
+      <c r="AF182" s="8">
+        <f>IF(OR(E182="",A182=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG182" s="8">
+        <f>IF(OR(AD182="",AF182=""),"",AD182-AF182)</f>
+        <v/>
+      </c>
+      <c r="AH182" s="4">
+        <f>IF(A182="","",IF(E182="","TERMINAL",IF(AG182="","INFO",IF(ABS(AG182)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -20825,10 +24999,31 @@
         <v/>
       </c>
       <c r="AA183" s="4">
-        <f>IF(A183="","",IF(OR(U183&gt;1,AND(X183&lt;&gt;"",X183&lt;Inputs!$B$16),AND(X183&lt;&gt;"",X183&gt;Inputs!$B$17),G183&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A183="","",IF(OR(U183&gt;1,AND(X183&lt;&gt;"",X183&lt;Inputs!$B$16),AND(X183&lt;&gt;"",X183&gt;Inputs!$B$17),G183&lt;Inputs!$B$18,AH183="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB183" s="4" t="n"/>
+      <c r="AC183" s="7" t="n"/>
+      <c r="AD183" s="8">
+        <f>IF(A183="","",IF(AC183&lt;&gt;"",AC183,IF(E183="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE183" s="8">
+        <f>IF(OR(AD183="",F183="",G183=""),"",AD183+F183*G183)</f>
+        <v/>
+      </c>
+      <c r="AF183" s="8">
+        <f>IF(OR(E183="",A183=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG183" s="8">
+        <f>IF(OR(AD183="",AF183=""),"",AD183-AF183)</f>
+        <v/>
+      </c>
+      <c r="AH183" s="4">
+        <f>IF(A183="","",IF(E183="","TERMINAL",IF(AG183="","INFO",IF(ABS(AG183)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -20899,10 +25094,31 @@
         <v/>
       </c>
       <c r="AA184" s="4">
-        <f>IF(A184="","",IF(OR(U184&gt;1,AND(X184&lt;&gt;"",X184&lt;Inputs!$B$16),AND(X184&lt;&gt;"",X184&gt;Inputs!$B$17),G184&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A184="","",IF(OR(U184&gt;1,AND(X184&lt;&gt;"",X184&lt;Inputs!$B$16),AND(X184&lt;&gt;"",X184&gt;Inputs!$B$17),G184&lt;Inputs!$B$18,AH184="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB184" s="4" t="n"/>
+      <c r="AC184" s="7" t="n"/>
+      <c r="AD184" s="8">
+        <f>IF(A184="","",IF(AC184&lt;&gt;"",AC184,IF(E184="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE184" s="8">
+        <f>IF(OR(AD184="",F184="",G184=""),"",AD184+F184*G184)</f>
+        <v/>
+      </c>
+      <c r="AF184" s="8">
+        <f>IF(OR(E184="",A184=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG184" s="8">
+        <f>IF(OR(AD184="",AF184=""),"",AD184-AF184)</f>
+        <v/>
+      </c>
+      <c r="AH184" s="4">
+        <f>IF(A184="","",IF(E184="","TERMINAL",IF(AG184="","INFO",IF(ABS(AG184)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -20973,10 +25189,31 @@
         <v/>
       </c>
       <c r="AA185" s="4">
-        <f>IF(A185="","",IF(OR(U185&gt;1,AND(X185&lt;&gt;"",X185&lt;Inputs!$B$16),AND(X185&lt;&gt;"",X185&gt;Inputs!$B$17),G185&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A185="","",IF(OR(U185&gt;1,AND(X185&lt;&gt;"",X185&lt;Inputs!$B$16),AND(X185&lt;&gt;"",X185&gt;Inputs!$B$17),G185&lt;Inputs!$B$18,AH185="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB185" s="4" t="n"/>
+      <c r="AC185" s="7" t="n"/>
+      <c r="AD185" s="8">
+        <f>IF(A185="","",IF(AC185&lt;&gt;"",AC185,IF(E185="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE185" s="8">
+        <f>IF(OR(AD185="",F185="",G185=""),"",AD185+F185*G185)</f>
+        <v/>
+      </c>
+      <c r="AF185" s="8">
+        <f>IF(OR(E185="",A185=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG185" s="8">
+        <f>IF(OR(AD185="",AF185=""),"",AD185-AF185)</f>
+        <v/>
+      </c>
+      <c r="AH185" s="4">
+        <f>IF(A185="","",IF(E185="","TERMINAL",IF(AG185="","INFO",IF(ABS(AG185)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n"/>
@@ -21047,10 +25284,31 @@
         <v/>
       </c>
       <c r="AA186" s="4">
-        <f>IF(A186="","",IF(OR(U186&gt;1,AND(X186&lt;&gt;"",X186&lt;Inputs!$B$16),AND(X186&lt;&gt;"",X186&gt;Inputs!$B$17),G186&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A186="","",IF(OR(U186&gt;1,AND(X186&lt;&gt;"",X186&lt;Inputs!$B$16),AND(X186&lt;&gt;"",X186&gt;Inputs!$B$17),G186&lt;Inputs!$B$18,AH186="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB186" s="4" t="n"/>
+      <c r="AC186" s="7" t="n"/>
+      <c r="AD186" s="8">
+        <f>IF(A186="","",IF(AC186&lt;&gt;"",AC186,IF(E186="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE186" s="8">
+        <f>IF(OR(AD186="",F186="",G186=""),"",AD186+F186*G186)</f>
+        <v/>
+      </c>
+      <c r="AF186" s="8">
+        <f>IF(OR(E186="",A186=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG186" s="8">
+        <f>IF(OR(AD186="",AF186=""),"",AD186-AF186)</f>
+        <v/>
+      </c>
+      <c r="AH186" s="4">
+        <f>IF(A186="","",IF(E186="","TERMINAL",IF(AG186="","INFO",IF(ABS(AG186)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -21121,10 +25379,31 @@
         <v/>
       </c>
       <c r="AA187" s="4">
-        <f>IF(A187="","",IF(OR(U187&gt;1,AND(X187&lt;&gt;"",X187&lt;Inputs!$B$16),AND(X187&lt;&gt;"",X187&gt;Inputs!$B$17),G187&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A187="","",IF(OR(U187&gt;1,AND(X187&lt;&gt;"",X187&lt;Inputs!$B$16),AND(X187&lt;&gt;"",X187&gt;Inputs!$B$17),G187&lt;Inputs!$B$18,AH187="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB187" s="4" t="n"/>
+      <c r="AC187" s="7" t="n"/>
+      <c r="AD187" s="8">
+        <f>IF(A187="","",IF(AC187&lt;&gt;"",AC187,IF(E187="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE187" s="8">
+        <f>IF(OR(AD187="",F187="",G187=""),"",AD187+F187*G187)</f>
+        <v/>
+      </c>
+      <c r="AF187" s="8">
+        <f>IF(OR(E187="",A187=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG187" s="8">
+        <f>IF(OR(AD187="",AF187=""),"",AD187-AF187)</f>
+        <v/>
+      </c>
+      <c r="AH187" s="4">
+        <f>IF(A187="","",IF(E187="","TERMINAL",IF(AG187="","INFO",IF(ABS(AG187)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -21195,10 +25474,31 @@
         <v/>
       </c>
       <c r="AA188" s="4">
-        <f>IF(A188="","",IF(OR(U188&gt;1,AND(X188&lt;&gt;"",X188&lt;Inputs!$B$16),AND(X188&lt;&gt;"",X188&gt;Inputs!$B$17),G188&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A188="","",IF(OR(U188&gt;1,AND(X188&lt;&gt;"",X188&lt;Inputs!$B$16),AND(X188&lt;&gt;"",X188&gt;Inputs!$B$17),G188&lt;Inputs!$B$18,AH188="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB188" s="4" t="n"/>
+      <c r="AC188" s="7" t="n"/>
+      <c r="AD188" s="8">
+        <f>IF(A188="","",IF(AC188&lt;&gt;"",AC188,IF(E188="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE188" s="8">
+        <f>IF(OR(AD188="",F188="",G188=""),"",AD188+F188*G188)</f>
+        <v/>
+      </c>
+      <c r="AF188" s="8">
+        <f>IF(OR(E188="",A188=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG188" s="8">
+        <f>IF(OR(AD188="",AF188=""),"",AD188-AF188)</f>
+        <v/>
+      </c>
+      <c r="AH188" s="4">
+        <f>IF(A188="","",IF(E188="","TERMINAL",IF(AG188="","INFO",IF(ABS(AG188)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -21269,10 +25569,31 @@
         <v/>
       </c>
       <c r="AA189" s="4">
-        <f>IF(A189="","",IF(OR(U189&gt;1,AND(X189&lt;&gt;"",X189&lt;Inputs!$B$16),AND(X189&lt;&gt;"",X189&gt;Inputs!$B$17),G189&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A189="","",IF(OR(U189&gt;1,AND(X189&lt;&gt;"",X189&lt;Inputs!$B$16),AND(X189&lt;&gt;"",X189&gt;Inputs!$B$17),G189&lt;Inputs!$B$18,AH189="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB189" s="4" t="n"/>
+      <c r="AC189" s="7" t="n"/>
+      <c r="AD189" s="8">
+        <f>IF(A189="","",IF(AC189&lt;&gt;"",AC189,IF(E189="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE189" s="8">
+        <f>IF(OR(AD189="",F189="",G189=""),"",AD189+F189*G189)</f>
+        <v/>
+      </c>
+      <c r="AF189" s="8">
+        <f>IF(OR(E189="",A189=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG189" s="8">
+        <f>IF(OR(AD189="",AF189=""),"",AD189-AF189)</f>
+        <v/>
+      </c>
+      <c r="AH189" s="4">
+        <f>IF(A189="","",IF(E189="","TERMINAL",IF(AG189="","INFO",IF(ABS(AG189)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -21343,10 +25664,31 @@
         <v/>
       </c>
       <c r="AA190" s="4">
-        <f>IF(A190="","",IF(OR(U190&gt;1,AND(X190&lt;&gt;"",X190&lt;Inputs!$B$16),AND(X190&lt;&gt;"",X190&gt;Inputs!$B$17),G190&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A190="","",IF(OR(U190&gt;1,AND(X190&lt;&gt;"",X190&lt;Inputs!$B$16),AND(X190&lt;&gt;"",X190&gt;Inputs!$B$17),G190&lt;Inputs!$B$18,AH190="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB190" s="4" t="n"/>
+      <c r="AC190" s="7" t="n"/>
+      <c r="AD190" s="8">
+        <f>IF(A190="","",IF(AC190&lt;&gt;"",AC190,IF(E190="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE190" s="8">
+        <f>IF(OR(AD190="",F190="",G190=""),"",AD190+F190*G190)</f>
+        <v/>
+      </c>
+      <c r="AF190" s="8">
+        <f>IF(OR(E190="",A190=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG190" s="8">
+        <f>IF(OR(AD190="",AF190=""),"",AD190-AF190)</f>
+        <v/>
+      </c>
+      <c r="AH190" s="4">
+        <f>IF(A190="","",IF(E190="","TERMINAL",IF(AG190="","INFO",IF(ABS(AG190)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -21417,10 +25759,31 @@
         <v/>
       </c>
       <c r="AA191" s="4">
-        <f>IF(A191="","",IF(OR(U191&gt;1,AND(X191&lt;&gt;"",X191&lt;Inputs!$B$16),AND(X191&lt;&gt;"",X191&gt;Inputs!$B$17),G191&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A191="","",IF(OR(U191&gt;1,AND(X191&lt;&gt;"",X191&lt;Inputs!$B$16),AND(X191&lt;&gt;"",X191&gt;Inputs!$B$17),G191&lt;Inputs!$B$18,AH191="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB191" s="4" t="n"/>
+      <c r="AC191" s="7" t="n"/>
+      <c r="AD191" s="8">
+        <f>IF(A191="","",IF(AC191&lt;&gt;"",AC191,IF(E191="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE191" s="8">
+        <f>IF(OR(AD191="",F191="",G191=""),"",AD191+F191*G191)</f>
+        <v/>
+      </c>
+      <c r="AF191" s="8">
+        <f>IF(OR(E191="",A191=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG191" s="8">
+        <f>IF(OR(AD191="",AF191=""),"",AD191-AF191)</f>
+        <v/>
+      </c>
+      <c r="AH191" s="4">
+        <f>IF(A191="","",IF(E191="","TERMINAL",IF(AG191="","INFO",IF(ABS(AG191)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -21491,10 +25854,31 @@
         <v/>
       </c>
       <c r="AA192" s="4">
-        <f>IF(A192="","",IF(OR(U192&gt;1,AND(X192&lt;&gt;"",X192&lt;Inputs!$B$16),AND(X192&lt;&gt;"",X192&gt;Inputs!$B$17),G192&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A192="","",IF(OR(U192&gt;1,AND(X192&lt;&gt;"",X192&lt;Inputs!$B$16),AND(X192&lt;&gt;"",X192&gt;Inputs!$B$17),G192&lt;Inputs!$B$18,AH192="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB192" s="4" t="n"/>
+      <c r="AC192" s="7" t="n"/>
+      <c r="AD192" s="8">
+        <f>IF(A192="","",IF(AC192&lt;&gt;"",AC192,IF(E192="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE192" s="8">
+        <f>IF(OR(AD192="",F192="",G192=""),"",AD192+F192*G192)</f>
+        <v/>
+      </c>
+      <c r="AF192" s="8">
+        <f>IF(OR(E192="",A192=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG192" s="8">
+        <f>IF(OR(AD192="",AF192=""),"",AD192-AF192)</f>
+        <v/>
+      </c>
+      <c r="AH192" s="4">
+        <f>IF(A192="","",IF(E192="","TERMINAL",IF(AG192="","INFO",IF(ABS(AG192)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -21565,10 +25949,31 @@
         <v/>
       </c>
       <c r="AA193" s="4">
-        <f>IF(A193="","",IF(OR(U193&gt;1,AND(X193&lt;&gt;"",X193&lt;Inputs!$B$16),AND(X193&lt;&gt;"",X193&gt;Inputs!$B$17),G193&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A193="","",IF(OR(U193&gt;1,AND(X193&lt;&gt;"",X193&lt;Inputs!$B$16),AND(X193&lt;&gt;"",X193&gt;Inputs!$B$17),G193&lt;Inputs!$B$18,AH193="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB193" s="4" t="n"/>
+      <c r="AC193" s="7" t="n"/>
+      <c r="AD193" s="8">
+        <f>IF(A193="","",IF(AC193&lt;&gt;"",AC193,IF(E193="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE193" s="8">
+        <f>IF(OR(AD193="",F193="",G193=""),"",AD193+F193*G193)</f>
+        <v/>
+      </c>
+      <c r="AF193" s="8">
+        <f>IF(OR(E193="",A193=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG193" s="8">
+        <f>IF(OR(AD193="",AF193=""),"",AD193-AF193)</f>
+        <v/>
+      </c>
+      <c r="AH193" s="4">
+        <f>IF(A193="","",IF(E193="","TERMINAL",IF(AG193="","INFO",IF(ABS(AG193)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n"/>
@@ -21639,10 +26044,31 @@
         <v/>
       </c>
       <c r="AA194" s="4">
-        <f>IF(A194="","",IF(OR(U194&gt;1,AND(X194&lt;&gt;"",X194&lt;Inputs!$B$16),AND(X194&lt;&gt;"",X194&gt;Inputs!$B$17),G194&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A194="","",IF(OR(U194&gt;1,AND(X194&lt;&gt;"",X194&lt;Inputs!$B$16),AND(X194&lt;&gt;"",X194&gt;Inputs!$B$17),G194&lt;Inputs!$B$18,AH194="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB194" s="4" t="n"/>
+      <c r="AC194" s="7" t="n"/>
+      <c r="AD194" s="8">
+        <f>IF(A194="","",IF(AC194&lt;&gt;"",AC194,IF(E194="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE194" s="8">
+        <f>IF(OR(AD194="",F194="",G194=""),"",AD194+F194*G194)</f>
+        <v/>
+      </c>
+      <c r="AF194" s="8">
+        <f>IF(OR(E194="",A194=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG194" s="8">
+        <f>IF(OR(AD194="",AF194=""),"",AD194-AF194)</f>
+        <v/>
+      </c>
+      <c r="AH194" s="4">
+        <f>IF(A194="","",IF(E194="","TERMINAL",IF(AG194="","INFO",IF(ABS(AG194)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -21713,10 +26139,31 @@
         <v/>
       </c>
       <c r="AA195" s="4">
-        <f>IF(A195="","",IF(OR(U195&gt;1,AND(X195&lt;&gt;"",X195&lt;Inputs!$B$16),AND(X195&lt;&gt;"",X195&gt;Inputs!$B$17),G195&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A195="","",IF(OR(U195&gt;1,AND(X195&lt;&gt;"",X195&lt;Inputs!$B$16),AND(X195&lt;&gt;"",X195&gt;Inputs!$B$17),G195&lt;Inputs!$B$18,AH195="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB195" s="4" t="n"/>
+      <c r="AC195" s="7" t="n"/>
+      <c r="AD195" s="8">
+        <f>IF(A195="","",IF(AC195&lt;&gt;"",AC195,IF(E195="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE195" s="8">
+        <f>IF(OR(AD195="",F195="",G195=""),"",AD195+F195*G195)</f>
+        <v/>
+      </c>
+      <c r="AF195" s="8">
+        <f>IF(OR(E195="",A195=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG195" s="8">
+        <f>IF(OR(AD195="",AF195=""),"",AD195-AF195)</f>
+        <v/>
+      </c>
+      <c r="AH195" s="4">
+        <f>IF(A195="","",IF(E195="","TERMINAL",IF(AG195="","INFO",IF(ABS(AG195)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -21787,10 +26234,31 @@
         <v/>
       </c>
       <c r="AA196" s="4">
-        <f>IF(A196="","",IF(OR(U196&gt;1,AND(X196&lt;&gt;"",X196&lt;Inputs!$B$16),AND(X196&lt;&gt;"",X196&gt;Inputs!$B$17),G196&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A196="","",IF(OR(U196&gt;1,AND(X196&lt;&gt;"",X196&lt;Inputs!$B$16),AND(X196&lt;&gt;"",X196&gt;Inputs!$B$17),G196&lt;Inputs!$B$18,AH196="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB196" s="4" t="n"/>
+      <c r="AC196" s="7" t="n"/>
+      <c r="AD196" s="8">
+        <f>IF(A196="","",IF(AC196&lt;&gt;"",AC196,IF(E196="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE196" s="8">
+        <f>IF(OR(AD196="",F196="",G196=""),"",AD196+F196*G196)</f>
+        <v/>
+      </c>
+      <c r="AF196" s="8">
+        <f>IF(OR(E196="",A196=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG196" s="8">
+        <f>IF(OR(AD196="",AF196=""),"",AD196-AF196)</f>
+        <v/>
+      </c>
+      <c r="AH196" s="4">
+        <f>IF(A196="","",IF(E196="","TERMINAL",IF(AG196="","INFO",IF(ABS(AG196)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -21861,10 +26329,31 @@
         <v/>
       </c>
       <c r="AA197" s="4">
-        <f>IF(A197="","",IF(OR(U197&gt;1,AND(X197&lt;&gt;"",X197&lt;Inputs!$B$16),AND(X197&lt;&gt;"",X197&gt;Inputs!$B$17),G197&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A197="","",IF(OR(U197&gt;1,AND(X197&lt;&gt;"",X197&lt;Inputs!$B$16),AND(X197&lt;&gt;"",X197&gt;Inputs!$B$17),G197&lt;Inputs!$B$18,AH197="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB197" s="4" t="n"/>
+      <c r="AC197" s="7" t="n"/>
+      <c r="AD197" s="8">
+        <f>IF(A197="","",IF(AC197&lt;&gt;"",AC197,IF(E197="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE197" s="8">
+        <f>IF(OR(AD197="",F197="",G197=""),"",AD197+F197*G197)</f>
+        <v/>
+      </c>
+      <c r="AF197" s="8">
+        <f>IF(OR(E197="",A197=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG197" s="8">
+        <f>IF(OR(AD197="",AF197=""),"",AD197-AF197)</f>
+        <v/>
+      </c>
+      <c r="AH197" s="4">
+        <f>IF(A197="","",IF(E197="","TERMINAL",IF(AG197="","INFO",IF(ABS(AG197)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -21935,10 +26424,31 @@
         <v/>
       </c>
       <c r="AA198" s="4">
-        <f>IF(A198="","",IF(OR(U198&gt;1,AND(X198&lt;&gt;"",X198&lt;Inputs!$B$16),AND(X198&lt;&gt;"",X198&gt;Inputs!$B$17),G198&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A198="","",IF(OR(U198&gt;1,AND(X198&lt;&gt;"",X198&lt;Inputs!$B$16),AND(X198&lt;&gt;"",X198&gt;Inputs!$B$17),G198&lt;Inputs!$B$18,AH198="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB198" s="4" t="n"/>
+      <c r="AC198" s="7" t="n"/>
+      <c r="AD198" s="8">
+        <f>IF(A198="","",IF(AC198&lt;&gt;"",AC198,IF(E198="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE198" s="8">
+        <f>IF(OR(AD198="",F198="",G198=""),"",AD198+F198*G198)</f>
+        <v/>
+      </c>
+      <c r="AF198" s="8">
+        <f>IF(OR(E198="",A198=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG198" s="8">
+        <f>IF(OR(AD198="",AF198=""),"",AD198-AF198)</f>
+        <v/>
+      </c>
+      <c r="AH198" s="4">
+        <f>IF(A198="","",IF(E198="","TERMINAL",IF(AG198="","INFO",IF(ABS(AG198)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -22009,10 +26519,31 @@
         <v/>
       </c>
       <c r="AA199" s="4">
-        <f>IF(A199="","",IF(OR(U199&gt;1,AND(X199&lt;&gt;"",X199&lt;Inputs!$B$16),AND(X199&lt;&gt;"",X199&gt;Inputs!$B$17),G199&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A199="","",IF(OR(U199&gt;1,AND(X199&lt;&gt;"",X199&lt;Inputs!$B$16),AND(X199&lt;&gt;"",X199&gt;Inputs!$B$17),G199&lt;Inputs!$B$18,AH199="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB199" s="4" t="n"/>
+      <c r="AC199" s="7" t="n"/>
+      <c r="AD199" s="8">
+        <f>IF(A199="","",IF(AC199&lt;&gt;"",AC199,IF(E199="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE199" s="8">
+        <f>IF(OR(AD199="",F199="",G199=""),"",AD199+F199*G199)</f>
+        <v/>
+      </c>
+      <c r="AF199" s="8">
+        <f>IF(OR(E199="",A199=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG199" s="8">
+        <f>IF(OR(AD199="",AF199=""),"",AD199-AF199)</f>
+        <v/>
+      </c>
+      <c r="AH199" s="4">
+        <f>IF(A199="","",IF(E199="","TERMINAL",IF(AG199="","INFO",IF(ABS(AG199)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n"/>
@@ -22083,10 +26614,31 @@
         <v/>
       </c>
       <c r="AA200" s="4">
-        <f>IF(A200="","",IF(OR(U200&gt;1,AND(X200&lt;&gt;"",X200&lt;Inputs!$B$16),AND(X200&lt;&gt;"",X200&gt;Inputs!$B$17),G200&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A200="","",IF(OR(U200&gt;1,AND(X200&lt;&gt;"",X200&lt;Inputs!$B$16),AND(X200&lt;&gt;"",X200&gt;Inputs!$B$17),G200&lt;Inputs!$B$18,AH200="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB200" s="4" t="n"/>
+      <c r="AC200" s="7" t="n"/>
+      <c r="AD200" s="8">
+        <f>IF(A200="","",IF(AC200&lt;&gt;"",AC200,IF(E200="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE200" s="8">
+        <f>IF(OR(AD200="",F200="",G200=""),"",AD200+F200*G200)</f>
+        <v/>
+      </c>
+      <c r="AF200" s="8">
+        <f>IF(OR(E200="",A200=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG200" s="8">
+        <f>IF(OR(AD200="",AF200=""),"",AD200-AF200)</f>
+        <v/>
+      </c>
+      <c r="AH200" s="4">
+        <f>IF(A200="","",IF(E200="","TERMINAL",IF(AG200="","INFO",IF(ABS(AG200)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -22157,10 +26709,31 @@
         <v/>
       </c>
       <c r="AA201" s="4">
-        <f>IF(A201="","",IF(OR(U201&gt;1,AND(X201&lt;&gt;"",X201&lt;Inputs!$B$16),AND(X201&lt;&gt;"",X201&gt;Inputs!$B$17),G201&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A201="","",IF(OR(U201&gt;1,AND(X201&lt;&gt;"",X201&lt;Inputs!$B$16),AND(X201&lt;&gt;"",X201&gt;Inputs!$B$17),G201&lt;Inputs!$B$18,AH201="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB201" s="4" t="n"/>
+      <c r="AC201" s="7" t="n"/>
+      <c r="AD201" s="8">
+        <f>IF(A201="","",IF(AC201&lt;&gt;"",AC201,IF(E201="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE201" s="8">
+        <f>IF(OR(AD201="",F201="",G201=""),"",AD201+F201*G201)</f>
+        <v/>
+      </c>
+      <c r="AF201" s="8">
+        <f>IF(OR(E201="",A201=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG201" s="8">
+        <f>IF(OR(AD201="",AF201=""),"",AD201-AF201)</f>
+        <v/>
+      </c>
+      <c r="AH201" s="4">
+        <f>IF(A201="","",IF(E201="","TERMINAL",IF(AG201="","INFO",IF(ABS(AG201)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -22231,10 +26804,31 @@
         <v/>
       </c>
       <c r="AA202" s="4">
-        <f>IF(A202="","",IF(OR(U202&gt;1,AND(X202&lt;&gt;"",X202&lt;Inputs!$B$16),AND(X202&lt;&gt;"",X202&gt;Inputs!$B$17),G202&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A202="","",IF(OR(U202&gt;1,AND(X202&lt;&gt;"",X202&lt;Inputs!$B$16),AND(X202&lt;&gt;"",X202&gt;Inputs!$B$17),G202&lt;Inputs!$B$18,AH202="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB202" s="4" t="n"/>
+      <c r="AC202" s="7" t="n"/>
+      <c r="AD202" s="8">
+        <f>IF(A202="","",IF(AC202&lt;&gt;"",AC202,IF(E202="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE202" s="8">
+        <f>IF(OR(AD202="",F202="",G202=""),"",AD202+F202*G202)</f>
+        <v/>
+      </c>
+      <c r="AF202" s="8">
+        <f>IF(OR(E202="",A202=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG202" s="8">
+        <f>IF(OR(AD202="",AF202=""),"",AD202-AF202)</f>
+        <v/>
+      </c>
+      <c r="AH202" s="4">
+        <f>IF(A202="","",IF(E202="","TERMINAL",IF(AG202="","INFO",IF(ABS(AG202)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -22305,10 +26899,31 @@
         <v/>
       </c>
       <c r="AA203" s="4">
-        <f>IF(A203="","",IF(OR(U203&gt;1,AND(X203&lt;&gt;"",X203&lt;Inputs!$B$16),AND(X203&lt;&gt;"",X203&gt;Inputs!$B$17),G203&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A203="","",IF(OR(U203&gt;1,AND(X203&lt;&gt;"",X203&lt;Inputs!$B$16),AND(X203&lt;&gt;"",X203&gt;Inputs!$B$17),G203&lt;Inputs!$B$18,AH203="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB203" s="4" t="n"/>
+      <c r="AC203" s="7" t="n"/>
+      <c r="AD203" s="8">
+        <f>IF(A203="","",IF(AC203&lt;&gt;"",AC203,IF(E203="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE203" s="8">
+        <f>IF(OR(AD203="",F203="",G203=""),"",AD203+F203*G203)</f>
+        <v/>
+      </c>
+      <c r="AF203" s="8">
+        <f>IF(OR(E203="",A203=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG203" s="8">
+        <f>IF(OR(AD203="",AF203=""),"",AD203-AF203)</f>
+        <v/>
+      </c>
+      <c r="AH203" s="4">
+        <f>IF(A203="","",IF(E203="","TERMINAL",IF(AG203="","INFO",IF(ABS(AG203)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -22379,35 +26994,56 @@
         <v/>
       </c>
       <c r="AA204" s="4">
-        <f>IF(A204="","",IF(OR(U204&gt;1,AND(X204&lt;&gt;"",X204&lt;Inputs!$B$16),AND(X204&lt;&gt;"",X204&gt;Inputs!$B$17),G204&lt;Inputs!$B$18),"CHECK","OK"))</f>
+        <f>IF(A204="","",IF(OR(U204&gt;1,AND(X204&lt;&gt;"",X204&lt;Inputs!$B$16),AND(X204&lt;&gt;"",X204&gt;Inputs!$B$17),G204&lt;Inputs!$B$18,AH204="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
       <c r="AB204" s="4" t="n"/>
+      <c r="AC204" s="7" t="n"/>
+      <c r="AD204" s="8">
+        <f>IF(A204="","",IF(AC204&lt;&gt;"",AC204,IF(E204="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0)),""))))</f>
+        <v/>
+      </c>
+      <c r="AE204" s="8">
+        <f>IF(OR(AD204="",F204="",G204=""),"",AD204+F204*G204)</f>
+        <v/>
+      </c>
+      <c r="AF204" s="8">
+        <f>IF(OR(E204="",A204=""),"",IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0)),""))</f>
+        <v/>
+      </c>
+      <c r="AG204" s="8">
+        <f>IF(OR(AD204="",AF204=""),"",AD204-AF204)</f>
+        <v/>
+      </c>
+      <c r="AH204" s="4">
+        <f>IF(A204="","",IF(E204="","TERMINAL",IF(AG204="","INFO",IF(ABS(AG204)&lt;=0.01,"OK","CHECK"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:AB2"/>
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4:AB204">
-    <cfRule type="expression" priority="1" dxfId="0">
+  <conditionalFormatting sqref="A4:AH204">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>=$B4="PIPE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>=$B4="SWALE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>=$B4="TRENCH"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA204">
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="9" dxfId="3">
       <formula>=$AA4="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U204">
-    <cfRule type="expression" priority="5" dxfId="3">
-      <formula>=$U4&gt;1</formula>
+  <conditionalFormatting sqref="AH4:AH204">
+    <cfRule type="expression" priority="10" dxfId="3">
+      <formula>=$AH4="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22523,8 +27159,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="8">
         <f>IF(OR(C4="",D4=""),"",MAX(0,C4-D4))</f>
         <v/>
@@ -22570,8 +27206,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
       <c r="E5" s="8">
         <f>IF(OR(C5="",D5=""),"",MAX(0,C5-D5))</f>
         <v/>
@@ -22617,8 +27253,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
       <c r="E6" s="8">
         <f>IF(OR(C6="",D6=""),"",MAX(0,C6-D6))</f>
         <v/>
@@ -22664,8 +27300,8 @@
           <t>SWALE_NODE</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
       <c r="E7" s="8">
         <f>IF(OR(C7="",D7=""),"",MAX(0,C7-D7))</f>
         <v/>
@@ -22713,8 +27349,8 @@
           <t>SWALE_NODE</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="8">
         <f>IF(OR(C8="",D8=""),"",MAX(0,C8-D8))</f>
         <v/>
@@ -22762,8 +27398,8 @@
           <t>CB</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
       <c r="E9" s="8">
         <f>IF(OR(C9="",D9=""),"",MAX(0,C9-D9))</f>
         <v/>
@@ -22801,16 +27437,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>J-OUEST-AVAL</t>
+          <t>J-OUEST-PU1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
       <c r="E10" s="8">
         <f>IF(OR(C10="",D10=""),"",MAX(0,C10-D10))</f>
         <v/>
@@ -22848,7 +27484,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-OUEST-PU2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -22856,8 +27492,8 @@
           <t>MH</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="8">
         <f>IF(OR(C11="",D11=""),"",MAX(0,C11-D11))</f>
         <v/>
@@ -22868,7 +27504,7 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
@@ -22895,45 +27531,36 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>BASSIN-RET</t>
+          <t>J-OUEST-PU3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>RETENTION</t>
-        </is>
-      </c>
-      <c r="C12" s="7">
-        <f>Inputs!$B$37</f>
-        <v/>
-      </c>
-      <c r="D12" s="7">
-        <f>Inputs!$B$38</f>
-        <v/>
-      </c>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
       <c r="E12" s="8">
         <f>IF(OR(C12="",D12=""),"",MAX(0,C12-D12))</f>
         <v/>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>RECT</t>
-        </is>
-      </c>
-      <c r="G12" s="7">
-        <f>Inputs!$B$34</f>
-        <v/>
-      </c>
-      <c r="H12" s="7">
-        <f>Inputs!$B$35</f>
-        <v/>
-      </c>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="8">
         <f>IF(A12="","",IF(UPPER(TRIM(F12))="CIRC",PI()*(G12/2)^2*E12,IF(UPPER(TRIM(F12))="RECT",G12*H12*E12,"")))</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>30</v>
+      <c r="J12" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
       </c>
       <c r="K12" s="8">
         <f>IF(A12="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A12))</f>
@@ -22949,22 +27576,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-PU4</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="8">
         <f>IF(OR(C13="",D13=""),"",MAX(0,C13-D13))</f>
         <v/>
       </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="8">
         <f>IF(A13="","",IF(UPPER(TRIM(F13))="CIRC",PI()*(G13/2)^2*E13,IF(UPPER(TRIM(F13))="RECT",G13*H13*E13,"")))</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K13" s="8">
         <f>IF(A13="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A13))</f>
         <v/>
@@ -22979,22 +27623,39 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="8">
         <f>IF(OR(C14="",D14=""),"",MAX(0,C14-D14))</f>
         <v/>
       </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
         <f>IF(A14="","",IF(UPPER(TRIM(F14))="CIRC",PI()*(G14/2)^2*E14,IF(UPPER(TRIM(F14))="RECT",G14*H14*E14,"")))</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="n"/>
+      <c r="J14" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K14" s="8">
         <f>IF(A14="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A14))</f>
         <v/>
@@ -23009,22 +27670,39 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-IN</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="8">
         <f>IF(OR(C15="",D15=""),"",MAX(0,C15-D15))</f>
         <v/>
       </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="8">
         <f>IF(A15="","",IF(UPPER(TRIM(F15))="CIRC",PI()*(G15/2)^2*E15,IF(UPPER(TRIM(F15))="RECT",G15*H15*E15,"")))</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="n"/>
+      <c r="J15" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K15" s="8">
         <f>IF(A15="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A15))</f>
         <v/>
@@ -23039,22 +27717,48 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>RETENTION</t>
+        </is>
+      </c>
+      <c r="C16" s="7">
+        <f>Inputs!$B$37</f>
+        <v/>
+      </c>
+      <c r="D16" s="7">
+        <f>Inputs!$B$38</f>
+        <v/>
+      </c>
       <c r="E16" s="8">
         <f>IF(OR(C16="",D16=""),"",MAX(0,C16-D16))</f>
         <v/>
       </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>RECT</t>
+        </is>
+      </c>
+      <c r="G16" s="7">
+        <f>Inputs!$B$34</f>
+        <v/>
+      </c>
+      <c r="H16" s="7">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
       <c r="I16" s="8">
         <f>IF(A16="","",IF(UPPER(TRIM(F16))="CIRC",PI()*(G16/2)^2*E16,IF(UPPER(TRIM(F16))="RECT",G16*H16*E16,"")))</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="n"/>
+      <c r="J16" s="7" t="n">
+        <v>30</v>
+      </c>
       <c r="K16" s="8">
         <f>IF(A16="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A16))</f>
         <v/>
@@ -29487,7 +34191,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Ouest haut</t>
+          <t>Ouest haut (grass 12.5 m2)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -29497,125 +34201,157 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Privilegier ecoulement de surface (noue peu profonde)</t>
+          <t>Ecoulement de surface peu profond</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>E05 (SWALE)</t>
+          <t>E05A (SWALE)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>profondeur ~0.20 m</t>
+          <t>depth ~0.15-0.20 m</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Limiter fouille profonde dans emprise chargee.</t>
+          <t>Eviter fouille profonde.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Traverse vers bassin</t>
+          <t>Traverse pave-uni 1 (6.7 m2)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Croisement inevitable</t>
+          <t>Traverse pietonne courte</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Croiser perpendiculaire + gaine + pente mini</t>
+          <t>Caniveau grille + pipe DN250</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>E06 (PIPE)</t>
+          <t>E05B (PIPE)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>slope 0.8%</t>
+          <t>slope ~1.0%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Verifier degagement vertical avec as-built.</t>
+          <t>Raccorder aux noeuds MH.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bande sud 2m</t>
+          <t>Ouest milieu (27.2 m2)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Emprise contrainte</t>
+          <t>Zone vegetale</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Bassin lineaire + noue/tranchee compacte</t>
+          <t>Noue de surface</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>E04 + BASSIN-RET</t>
+          <t>E05C (SWALE)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>width 2.0 m</t>
+          <t>depth ~0.15-0.20 m</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Stockage distribue + transfert au bassin.</t>
+          <t>Conduire vers traverse 2.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bande est arbres</t>
+          <t>Traverse pave-uni 2 (37.5 m2)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Zone racinaire</t>
+          <t>Traverse mineralisee</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Tranchee drainante + underdrain + barriere racinaire</t>
+          <t>Caniveau grille + pipe DN300</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>E01/E02 (TRENCH)</t>
+          <t>E05D (PIPE)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>offset &gt;=1.0 m</t>
+          <t>slope ~0.9%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Eviter conduite profonde continue en pied d arbres.</t>
+          <t>Verifier degagement lateraux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ouest aval grass (21.9 m2)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Approche bassin</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Noue de surface</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>E05E (SWALE)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>vers J-OUEST-AVAL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Transition vers E06.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Note: Les degagements finaux avec lateraux existants doivent etre confirmes par releves terrain/TQC avant IFC.</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Note: verifier elevations utilites existantes et degagements minimaux avant IFC (TQC obligatoire).</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -129,6 +129,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -685,6 +686,20 @@
       <c r="A24" t="inlineStr">
         <is>
           <t>Connexion entre types d elements implementee via AC:AH (controle continuité d invert).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Geometrie J-OUEST pilotee par cotes plan dans Inputs!B40:B50 (23.58 m total; 11.1 m amont; 2.3 m pave1; 5.1 m pave2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E05A/E05C sont repartis proportionnellement aux aires (12.5 vs 27.2 m2); E05E est le solde vers le coin sud-ouest (21.9 m2).</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2273,6 +2288,230 @@
       <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Profondeur max recommandee dans zone lateraux ouest (approche conservatrice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>West_chain_total_m</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Somme E05A..E05E (chaine J-OUEST).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>West_amont_to_PU2_chain_m</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Cote plan visible (J-OUEST-AMONT jusqu'a fin zone amont avant troncon pave inferieur).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>West_pave1_short_span_m</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Traverse pave-uni courte (amont).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>West_pave2_span_m</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Traverse pave-uni inferieure (cote plan visible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>West_grass1_area_m2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 1 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>West_grass2_area_m2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 2 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>West_grass3_area_m2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Aire zone gazon 3 (image).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>West_grass12_total_m</t>
+        </is>
+      </c>
+      <c r="B47" s="9">
+        <f>B41-B42</f>
+        <v/>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Longueur gazon amont+milieu (derivee).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>West_grass1_len_m</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>IFERROR(B47*B44/(B44+B45),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05A (repartition proportionnelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>West_grass2_len_m</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>IFERROR(B47*B45/(B44+B45),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05C (repartition proportionnelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>West_grass3_len_m</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>B40-B41-B43</f>
+        <v/>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Longueur E05E (solde vers coin sud-ouest).</t>
         </is>
       </c>
     </row>
@@ -7881,8 +8120,9 @@
           <t>E05B</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>4</v>
+      <c r="F8" s="15">
+        <f>Inputs!$B$48</f>
+        <v/>
       </c>
       <c r="G8" s="7" t="n">
         <v>0.01</v>
@@ -7959,7 +8199,7 @@
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Ouest grass 12.5 m2 (surface).</t>
+          <t>Ouest gazon amont - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
         </is>
       </c>
       <c r="AC8" s="7" t="n"/>
@@ -8010,8 +8250,9 @@
           <t>E05C</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>2</v>
+      <c r="F9" s="15">
+        <f>Inputs!$B$42</f>
+        <v/>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.01</v>
@@ -8084,7 +8325,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni 6.7 m2 (caniveau/pipe).</t>
+          <t>Ouest pave-uni court - longueur cotee 2.3 m.</t>
         </is>
       </c>
       <c r="AC9" s="7" t="n"/>
@@ -8135,8 +8376,9 @@
           <t>E05D</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>8.5</v>
+      <c r="F10" s="15">
+        <f>Inputs!$B$49</f>
+        <v/>
       </c>
       <c r="G10" s="7" t="n">
         <v>0.008999999999999999</v>
@@ -8213,7 +8455,7 @@
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Ouest grass 27.2 m2 (surface).</t>
+          <t>Ouest gazon milieu - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
         </is>
       </c>
       <c r="AC10" s="7" t="n"/>
@@ -8264,8 +8506,9 @@
           <t>E05E</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>5.5</v>
+      <c r="F11" s="15">
+        <f>Inputs!$B$43</f>
+        <v/>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.008999999999999999</v>
@@ -8338,7 +8581,7 @@
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni 37.5 m2 (caniveau/pipe).</t>
+          <t>Ouest pave-uni inferieur - longueur cotee 5.1 m.</t>
         </is>
       </c>
       <c r="AC11" s="7" t="n"/>
@@ -8389,8 +8632,9 @@
           <t>E06</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>3.6</v>
+      <c r="F12" s="15">
+        <f>Inputs!$B$50</f>
+        <v/>
       </c>
       <c r="G12" s="7" t="n">
         <v>0.008</v>
@@ -8467,7 +8711,7 @@
       </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
-          <t>Ouest grass 21.9 m2 (surface vers aval).</t>
+          <t>Ouest gazon aval - longueur solde sur chaine totale 23.58 m.</t>
         </is>
       </c>
       <c r="AC12" s="7" t="n"/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -700,6 +700,20 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>E05A/E05C sont repartis proportionnellement aux aires (12.5 vs 27.2 m2); E05E est le solde vers le coin sud-ouest (21.9 m2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Clarification labels image: Z08 = pave-uni principal 37.5 m2 (entre Z05 et Z06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zone ajoutee: Z13 = tresfond haut central (aire via Inputs!B51, route E01).</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2512,6 +2526,26 @@
       <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Longueur E05E (solde vers coin sud-ouest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Top_central_tresfond_area_m2</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>A renseigner depuis plan releve. Zone tresfond bande haute centrale.</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2796,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ouest vert 1</t>
+          <t>Ouest gazon amont (12.5 m2)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2796,24 +2830,24 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Vers collecte ouest</t>
+          <t>Image: zone verte amont gauche.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Z05</t>
+          <t>Z07</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ouest vert 2</t>
+          <t>Ouest pave-uni court (6.7 m2)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>GRASS</t>
+          <t>TRESFOND</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
@@ -2842,19 +2876,19 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Vers collecte ouest</t>
+          <t>Image: petit troncon pave entre zones gazon.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Z06</t>
+          <t>Z05</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Ouest vert 3</t>
+          <t>Ouest gazon milieu (27.2 m2)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2888,19 +2922,19 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Vers collecte ouest</t>
+          <t>Image: bande verte milieu ouest.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Z07</t>
+          <t>Z08</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ouest pave-uni</t>
+          <t>Ouest pave-uni principal (37.5 m2)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2934,19 +2968,19 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Surface mineralisee ouest</t>
+          <t>LOCALISATION: zone pavee entre Z05 et Z06 (pas l'entree pavee externe).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Z08</t>
+          <t>Z06</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ouest vert 4</t>
+          <t>Ouest gazon aval coin sud-ouest (21.9 m2)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2980,7 +3014,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Vers collecte ouest</t>
+          <t>Image: zone verte pres J-OUEST-AVAL.</t>
         </is>
       </c>
     </row>
@@ -3169,16 +3203,33 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Z13</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tresfond haut central (bande nord centrale)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>TRESFOND</t>
+        </is>
+      </c>
+      <c r="D16" s="7">
+        <f>Inputs!$B$51</f>
+        <v/>
+      </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8">
         <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
         <v/>
       </c>
-      <c r="G16" s="7" t="n"/>
+      <c r="G16" s="7" t="n">
+        <v>8</v>
+      </c>
       <c r="H16" s="8">
         <f>IF(A16="","",Inputs!$B$3/((IF(G16="",Inputs!$B$14,G16)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3187,8 +3238,16 @@
         <f>IF(A16="","",2.78E-7*F16*D16*H16)</f>
         <v/>
       </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Ajoute pour inclure le tresfond central haut; saisir aire exacte Inputs!B51.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -714,6 +714,34 @@
       <c r="A28" t="inlineStr">
         <is>
           <t>Zone ajoutee: Z13 = tresfond haut central (aire via Inputs!B51, route E01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Correction topologie: E03 (P-03-&gt;J-BASSIN-IN) = 16.1 m; E04 = 20 m (J-OUEST-AVAL-&gt;J-BASSIN-IN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E04 ne superpose plus E03; E06 desactive pour eviter double chemin parallelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Z09 est defini BASIN (empreinte bassin), non contributif par defaut (Inputs!B52=NO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bassin retention longueur mise a 20 m (Inputs!B35) selon releve plan.</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2211,7 +2239,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>29.4</v>
+        <v>20</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
@@ -2220,7 +2248,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Longueur exploitable du bassin lineaire sud.</t>
+          <t>Longueur bassin retention (plan utilisateur) - remplace valeur preliminaire 29.4 m.</t>
         </is>
       </c>
     </row>
@@ -2546,6 +2574,28 @@
       <c r="D51" s="4" t="inlineStr">
         <is>
           <t>A renseigner depuis plan releve. Zone tresfond bande haute centrale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Include_basin_footprint_runoff (YES/NO)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>NO recommande: empreinte bassin n'est pas contributive au bassin lui-meme.</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2721,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="8">
-        <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G4" s="7" t="n">
@@ -2717,7 +2767,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="8">
-        <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G5" s="7" t="n">
@@ -2733,7 +2783,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -2763,7 +2813,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="8">
-        <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G6" s="7" t="n">
@@ -2809,7 +2859,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="8">
-        <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G7" s="7" t="n">
@@ -2855,7 +2905,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="8">
-        <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G8" s="7" t="n">
@@ -2901,7 +2951,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="8">
-        <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G9" s="7" t="n">
@@ -2947,7 +2997,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="8">
-        <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G10" s="7" t="n">
@@ -2993,7 +3043,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="8">
-        <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G11" s="7" t="n">
@@ -3026,12 +3076,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Bande sud verte centrale</t>
+          <t>Empreinte bassin retention (zone de stockage)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GRASS</t>
+          <t>BASIN</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -3039,7 +3089,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="8">
-        <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G12" s="7" t="n">
@@ -3053,14 +3103,10 @@
         <f>IF(A12="","",2.78E-7*F12*D12*H12)</f>
         <v/>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
+      <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Vers noue sud</t>
+          <t>Non contributive par defaut (Inputs!B52=NO). Mettre YES pour sensibilité si requis.</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3131,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="8">
-        <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G13" s="7" t="n">
@@ -3131,7 +3177,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="8">
-        <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G14" s="7" t="n">
@@ -3147,7 +3193,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -3177,7 +3223,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="8">
-        <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G15" s="7" t="n">
@@ -3193,7 +3239,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -3224,7 +3270,7 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8">
-        <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G16" s="7" t="n">
@@ -3240,7 +3286,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -3256,7 +3302,7 @@
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8">
-        <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G17" s="7" t="n"/>
@@ -3278,7 +3324,7 @@
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8">
-        <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G18" s="7" t="n"/>
@@ -3300,7 +3346,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8">
-        <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G19" s="7" t="n"/>
@@ -3322,7 +3368,7 @@
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8">
-        <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G20" s="7" t="n"/>
@@ -3344,7 +3390,7 @@
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8">
-        <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G21" s="7" t="n"/>
@@ -3366,7 +3412,7 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="8">
-        <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -3388,7 +3434,7 @@
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8">
-        <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -3410,7 +3456,7 @@
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="8">
-        <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G24" s="7" t="n"/>
@@ -3432,7 +3478,7 @@
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8">
-        <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -3454,7 +3500,7 @@
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="8">
-        <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -3476,7 +3522,7 @@
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8">
-        <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G27" s="7" t="n"/>
@@ -3498,7 +3544,7 @@
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="8">
-        <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G28" s="7" t="n"/>
@@ -3520,7 +3566,7 @@
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8">
-        <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G29" s="7" t="n"/>
@@ -3542,7 +3588,7 @@
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="8">
-        <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G30" s="7" t="n"/>
@@ -3564,7 +3610,7 @@
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8">
-        <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G31" s="7" t="n"/>
@@ -3586,7 +3632,7 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="8">
-        <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G32" s="7" t="n"/>
@@ -3608,7 +3654,7 @@
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="8">
-        <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G33" s="7" t="n"/>
@@ -3630,7 +3676,7 @@
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="8">
-        <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G34" s="7" t="n"/>
@@ -3652,7 +3698,7 @@
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="8">
-        <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G35" s="7" t="n"/>
@@ -3674,7 +3720,7 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="8">
-        <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G36" s="7" t="n"/>
@@ -3696,7 +3742,7 @@
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="8">
-        <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -3718,7 +3764,7 @@
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="8">
-        <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G38" s="7" t="n"/>
@@ -3740,7 +3786,7 @@
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="8">
-        <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G39" s="7" t="n"/>
@@ -3762,7 +3808,7 @@
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="8">
-        <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G40" s="7" t="n"/>
@@ -3784,7 +3830,7 @@
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="8">
-        <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G41" s="7" t="n"/>
@@ -3806,7 +3852,7 @@
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="8">
-        <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G42" s="7" t="n"/>
@@ -3828,7 +3874,7 @@
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="8">
-        <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G43" s="7" t="n"/>
@@ -3850,7 +3896,7 @@
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="8">
-        <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G44" s="7" t="n"/>
@@ -3872,7 +3918,7 @@
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="8">
-        <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G45" s="7" t="n"/>
@@ -3894,7 +3940,7 @@
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="8">
-        <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G46" s="7" t="n"/>
@@ -3916,7 +3962,7 @@
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="8">
-        <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G47" s="7" t="n"/>
@@ -3938,7 +3984,7 @@
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="8">
-        <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G48" s="7" t="n"/>
@@ -3960,7 +4006,7 @@
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="8">
-        <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G49" s="7" t="n"/>
@@ -3982,7 +4028,7 @@
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="8">
-        <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G50" s="7" t="n"/>
@@ -4004,7 +4050,7 @@
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="8">
-        <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G51" s="7" t="n"/>
@@ -4026,7 +4072,7 @@
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="8">
-        <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -4048,7 +4094,7 @@
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="8">
-        <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -4070,7 +4116,7 @@
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="8">
-        <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G54" s="7" t="n"/>
@@ -4092,7 +4138,7 @@
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="8">
-        <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -4114,7 +4160,7 @@
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="8">
-        <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -4136,7 +4182,7 @@
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="8">
-        <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G57" s="7" t="n"/>
@@ -4158,7 +4204,7 @@
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="8">
-        <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G58" s="7" t="n"/>
@@ -4180,7 +4226,7 @@
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="8">
-        <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G59" s="7" t="n"/>
@@ -4202,7 +4248,7 @@
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="8">
-        <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G60" s="7" t="n"/>
@@ -4224,7 +4270,7 @@
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="8">
-        <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G61" s="7" t="n"/>
@@ -4246,7 +4292,7 @@
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="8">
-        <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G62" s="7" t="n"/>
@@ -4268,7 +4314,7 @@
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="8">
-        <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G63" s="7" t="n"/>
@@ -4290,7 +4336,7 @@
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="8">
-        <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G64" s="7" t="n"/>
@@ -4312,7 +4358,7 @@
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="8">
-        <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -4334,7 +4380,7 @@
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="8">
-        <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -4356,7 +4402,7 @@
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="8">
-        <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G67" s="7" t="n"/>
@@ -4378,7 +4424,7 @@
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="8">
-        <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G68" s="7" t="n"/>
@@ -4400,7 +4446,7 @@
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="8">
-        <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G69" s="7" t="n"/>
@@ -4422,7 +4468,7 @@
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="8">
-        <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G70" s="7" t="n"/>
@@ -4444,7 +4490,7 @@
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="8">
-        <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G71" s="7" t="n"/>
@@ -4466,7 +4512,7 @@
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="8">
-        <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G72" s="7" t="n"/>
@@ -4488,7 +4534,7 @@
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="8">
-        <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G73" s="7" t="n"/>
@@ -4510,7 +4556,7 @@
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="8">
-        <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G74" s="7" t="n"/>
@@ -4532,7 +4578,7 @@
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="8">
-        <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -4554,7 +4600,7 @@
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="8">
-        <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G76" s="7" t="n"/>
@@ -4576,7 +4622,7 @@
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="8">
-        <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G77" s="7" t="n"/>
@@ -4598,7 +4644,7 @@
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="8">
-        <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G78" s="7" t="n"/>
@@ -4620,7 +4666,7 @@
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="8">
-        <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G79" s="7" t="n"/>
@@ -4642,7 +4688,7 @@
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="8">
-        <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G80" s="7" t="n"/>
@@ -4664,7 +4710,7 @@
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="8">
-        <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G81" s="7" t="n"/>
@@ -4686,7 +4732,7 @@
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="8">
-        <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G82" s="7" t="n"/>
@@ -4708,7 +4754,7 @@
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="8">
-        <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G83" s="7" t="n"/>
@@ -4730,7 +4776,7 @@
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="8">
-        <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G84" s="7" t="n"/>
@@ -4752,7 +4798,7 @@
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="8">
-        <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G85" s="7" t="n"/>
@@ -4774,7 +4820,7 @@
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="8">
-        <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G86" s="7" t="n"/>
@@ -4796,7 +4842,7 @@
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="8">
-        <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G87" s="7" t="n"/>
@@ -4818,7 +4864,7 @@
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="8">
-        <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G88" s="7" t="n"/>
@@ -4840,7 +4886,7 @@
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="8">
-        <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G89" s="7" t="n"/>
@@ -4862,7 +4908,7 @@
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="8">
-        <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G90" s="7" t="n"/>
@@ -4884,7 +4930,7 @@
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="8">
-        <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G91" s="7" t="n"/>
@@ -4906,7 +4952,7 @@
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="8">
-        <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G92" s="7" t="n"/>
@@ -4928,7 +4974,7 @@
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="8">
-        <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G93" s="7" t="n"/>
@@ -4950,7 +4996,7 @@
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="8">
-        <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G94" s="7" t="n"/>
@@ -4972,7 +5018,7 @@
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="8">
-        <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G95" s="7" t="n"/>
@@ -4994,7 +5040,7 @@
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="8">
-        <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G96" s="7" t="n"/>
@@ -5016,7 +5062,7 @@
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="8">
-        <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G97" s="7" t="n"/>
@@ -5038,7 +5084,7 @@
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="8">
-        <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -5060,7 +5106,7 @@
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="8">
-        <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G99" s="7" t="n"/>
@@ -5082,7 +5128,7 @@
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="8">
-        <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G100" s="7" t="n"/>
@@ -5104,7 +5150,7 @@
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="8">
-        <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G101" s="7" t="n"/>
@@ -5126,7 +5172,7 @@
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="8">
-        <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G102" s="7" t="n"/>
@@ -5148,7 +5194,7 @@
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="8">
-        <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G103" s="7" t="n"/>
@@ -5170,7 +5216,7 @@
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="8">
-        <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -5192,7 +5238,7 @@
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="8">
-        <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -5214,7 +5260,7 @@
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="8">
-        <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G106" s="7" t="n"/>
@@ -5236,7 +5282,7 @@
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="8">
-        <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G107" s="7" t="n"/>
@@ -5258,7 +5304,7 @@
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="8">
-        <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G108" s="7" t="n"/>
@@ -5280,7 +5326,7 @@
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
       <c r="F109" s="8">
-        <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -5302,7 +5348,7 @@
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="8">
-        <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G110" s="7" t="n"/>
@@ -5324,7 +5370,7 @@
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
       <c r="F111" s="8">
-        <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -5346,7 +5392,7 @@
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="8">
-        <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -5368,7 +5414,7 @@
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
       <c r="F113" s="8">
-        <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -5390,7 +5436,7 @@
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
       <c r="F114" s="8">
-        <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -5412,7 +5458,7 @@
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
       <c r="F115" s="8">
-        <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -5434,7 +5480,7 @@
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
       <c r="F116" s="8">
-        <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -5456,7 +5502,7 @@
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
       <c r="F117" s="8">
-        <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -5478,7 +5524,7 @@
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
       <c r="F118" s="8">
-        <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5500,7 +5546,7 @@
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
       <c r="F119" s="8">
-        <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G119" s="7" t="n"/>
@@ -5522,7 +5568,7 @@
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="8">
-        <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -5544,7 +5590,7 @@
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
       <c r="F121" s="8">
-        <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G121" s="7" t="n"/>
@@ -5566,7 +5612,7 @@
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="8">
-        <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -5588,7 +5634,7 @@
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
       <c r="F123" s="8">
-        <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G123" s="7" t="n"/>
@@ -5610,7 +5656,7 @@
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="8">
-        <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G124" s="7" t="n"/>
@@ -5632,7 +5678,7 @@
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
       <c r="F125" s="8">
-        <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G125" s="7" t="n"/>
@@ -5654,7 +5700,7 @@
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
       <c r="F126" s="8">
-        <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G126" s="7" t="n"/>
@@ -5676,7 +5722,7 @@
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
       <c r="F127" s="8">
-        <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G127" s="7" t="n"/>
@@ -5698,7 +5744,7 @@
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="8">
-        <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G128" s="7" t="n"/>
@@ -5720,7 +5766,7 @@
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
       <c r="F129" s="8">
-        <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G129" s="7" t="n"/>
@@ -5742,7 +5788,7 @@
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="8">
-        <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G130" s="7" t="n"/>
@@ -5764,7 +5810,7 @@
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
       <c r="F131" s="8">
-        <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G131" s="7" t="n"/>
@@ -5786,7 +5832,7 @@
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="8">
-        <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G132" s="7" t="n"/>
@@ -5808,7 +5854,7 @@
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
       <c r="F133" s="8">
-        <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G133" s="7" t="n"/>
@@ -5830,7 +5876,7 @@
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="8">
-        <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G134" s="7" t="n"/>
@@ -5852,7 +5898,7 @@
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
       <c r="F135" s="8">
-        <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G135" s="7" t="n"/>
@@ -5874,7 +5920,7 @@
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="8">
-        <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G136" s="7" t="n"/>
@@ -5896,7 +5942,7 @@
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
       <c r="F137" s="8">
-        <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G137" s="7" t="n"/>
@@ -5918,7 +5964,7 @@
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="8">
-        <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G138" s="7" t="n"/>
@@ -5940,7 +5986,7 @@
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
       <c r="F139" s="8">
-        <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G139" s="7" t="n"/>
@@ -5962,7 +6008,7 @@
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="8">
-        <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G140" s="7" t="n"/>
@@ -5984,7 +6030,7 @@
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
       <c r="F141" s="8">
-        <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G141" s="7" t="n"/>
@@ -6006,7 +6052,7 @@
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="8">
-        <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G142" s="7" t="n"/>
@@ -6028,7 +6074,7 @@
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
       <c r="F143" s="8">
-        <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G143" s="7" t="n"/>
@@ -6050,7 +6096,7 @@
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="8">
-        <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G144" s="7" t="n"/>
@@ -6072,7 +6118,7 @@
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
       <c r="F145" s="8">
-        <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G145" s="7" t="n"/>
@@ -6094,7 +6140,7 @@
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
       <c r="F146" s="8">
-        <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G146" s="7" t="n"/>
@@ -6116,7 +6162,7 @@
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
       <c r="F147" s="8">
-        <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G147" s="7" t="n"/>
@@ -6138,7 +6184,7 @@
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
       <c r="F148" s="8">
-        <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G148" s="7" t="n"/>
@@ -6160,7 +6206,7 @@
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
       <c r="F149" s="8">
-        <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G149" s="7" t="n"/>
@@ -6182,7 +6228,7 @@
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="8">
-        <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G150" s="7" t="n"/>
@@ -6204,7 +6250,7 @@
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
       <c r="F151" s="8">
-        <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G151" s="7" t="n"/>
@@ -6226,7 +6272,7 @@
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="8">
-        <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G152" s="7" t="n"/>
@@ -6248,7 +6294,7 @@
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
       <c r="F153" s="8">
-        <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G153" s="7" t="n"/>
@@ -6270,7 +6316,7 @@
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
       <c r="F154" s="8">
-        <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G154" s="7" t="n"/>
@@ -6292,7 +6338,7 @@
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
       <c r="F155" s="8">
-        <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G155" s="7" t="n"/>
@@ -6314,7 +6360,7 @@
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="8">
-        <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G156" s="7" t="n"/>
@@ -6336,7 +6382,7 @@
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
       <c r="F157" s="8">
-        <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G157" s="7" t="n"/>
@@ -6358,7 +6404,7 @@
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
       <c r="F158" s="8">
-        <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G158" s="7" t="n"/>
@@ -6380,7 +6426,7 @@
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
       <c r="F159" s="8">
-        <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G159" s="7" t="n"/>
@@ -6402,7 +6448,7 @@
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
       <c r="F160" s="8">
-        <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G160" s="7" t="n"/>
@@ -6424,7 +6470,7 @@
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
       <c r="F161" s="8">
-        <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G161" s="7" t="n"/>
@@ -6446,7 +6492,7 @@
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="8">
-        <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G162" s="7" t="n"/>
@@ -6468,7 +6514,7 @@
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
       <c r="F163" s="8">
-        <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G163" s="7" t="n"/>
@@ -6490,7 +6536,7 @@
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
       <c r="F164" s="8">
-        <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G164" s="7" t="n"/>
@@ -6512,7 +6558,7 @@
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
       <c r="F165" s="8">
-        <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G165" s="7" t="n"/>
@@ -6534,7 +6580,7 @@
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="8">
-        <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G166" s="7" t="n"/>
@@ -6556,7 +6602,7 @@
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
       <c r="F167" s="8">
-        <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G167" s="7" t="n"/>
@@ -6578,7 +6624,7 @@
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
       <c r="F168" s="8">
-        <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G168" s="7" t="n"/>
@@ -6600,7 +6646,7 @@
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
       <c r="F169" s="8">
-        <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G169" s="7" t="n"/>
@@ -6622,7 +6668,7 @@
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="8">
-        <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G170" s="7" t="n"/>
@@ -6644,7 +6690,7 @@
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
       <c r="F171" s="8">
-        <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G171" s="7" t="n"/>
@@ -6666,7 +6712,7 @@
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="8">
-        <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G172" s="7" t="n"/>
@@ -6688,7 +6734,7 @@
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
       <c r="F173" s="8">
-        <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G173" s="7" t="n"/>
@@ -6710,7 +6756,7 @@
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
       <c r="F174" s="8">
-        <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G174" s="7" t="n"/>
@@ -6732,7 +6778,7 @@
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
       <c r="F175" s="8">
-        <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G175" s="7" t="n"/>
@@ -6754,7 +6800,7 @@
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="8">
-        <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G176" s="7" t="n"/>
@@ -6776,7 +6822,7 @@
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
       <c r="F177" s="8">
-        <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G177" s="7" t="n"/>
@@ -6798,7 +6844,7 @@
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="8">
-        <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G178" s="7" t="n"/>
@@ -6820,7 +6866,7 @@
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
       <c r="F179" s="8">
-        <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G179" s="7" t="n"/>
@@ -6842,7 +6888,7 @@
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="8">
-        <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G180" s="7" t="n"/>
@@ -6864,7 +6910,7 @@
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
       <c r="F181" s="8">
-        <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G181" s="7" t="n"/>
@@ -6886,7 +6932,7 @@
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="8">
-        <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G182" s="7" t="n"/>
@@ -6908,7 +6954,7 @@
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
       <c r="F183" s="8">
-        <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G183" s="7" t="n"/>
@@ -6930,7 +6976,7 @@
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="8">
-        <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G184" s="7" t="n"/>
@@ -6952,7 +6998,7 @@
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
       <c r="F185" s="8">
-        <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G185" s="7" t="n"/>
@@ -6974,7 +7020,7 @@
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="8">
-        <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G186" s="7" t="n"/>
@@ -6996,7 +7042,7 @@
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
       <c r="F187" s="8">
-        <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G187" s="7" t="n"/>
@@ -7018,7 +7064,7 @@
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="8">
-        <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G188" s="7" t="n"/>
@@ -7040,7 +7086,7 @@
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
       <c r="F189" s="8">
-        <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G189" s="7" t="n"/>
@@ -7062,7 +7108,7 @@
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="8">
-        <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G190" s="7" t="n"/>
@@ -7084,7 +7130,7 @@
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
       <c r="F191" s="8">
-        <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G191" s="7" t="n"/>
@@ -7106,7 +7152,7 @@
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="8">
-        <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G192" s="7" t="n"/>
@@ -7128,7 +7174,7 @@
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
       <c r="F193" s="8">
-        <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G193" s="7" t="n"/>
@@ -7150,7 +7196,7 @@
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="8">
-        <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G194" s="7" t="n"/>
@@ -7172,7 +7218,7 @@
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
       <c r="F195" s="8">
-        <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G195" s="7" t="n"/>
@@ -7194,7 +7240,7 @@
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="8">
-        <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G196" s="7" t="n"/>
@@ -7216,7 +7262,7 @@
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
       <c r="F197" s="8">
-        <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G197" s="7" t="n"/>
@@ -7238,7 +7284,7 @@
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="8">
-        <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G198" s="7" t="n"/>
@@ -7260,7 +7306,7 @@
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
       <c r="F199" s="8">
-        <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G199" s="7" t="n"/>
@@ -7282,7 +7328,7 @@
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="8">
-        <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G200" s="7" t="n"/>
@@ -7304,7 +7350,7 @@
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
       <c r="F201" s="8">
-        <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G201" s="7" t="n"/>
@@ -7326,7 +7372,7 @@
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
       <c r="F202" s="8">
-        <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G202" s="7" t="n"/>
@@ -7348,7 +7394,7 @@
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
       <c r="F203" s="8">
-        <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G203" s="7" t="n"/>
@@ -7370,7 +7416,7 @@
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
       <c r="F204" s="8">
-        <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13))))</f>
+        <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
         <v/>
       </c>
       <c r="G204" s="7" t="n"/>
@@ -7923,7 +7969,7 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>20</v>
+        <v>16.1</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0.006</v>
@@ -7996,7 +8042,7 @@
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Collecteur est vers entree bassin.</t>
+          <t>Corrige: P-03 -&gt; J-BASSIN-IN = 16.1 m (pas 20 m).</t>
         </is>
       </c>
       <c r="AC6" s="7" t="n"/>
@@ -8034,12 +8080,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>J-SUD-EST</t>
+          <t>J-OUEST-AVAL</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>J-SUD-OUEST</t>
+          <t>J-BASSIN-IN</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -8048,10 +8094,10 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>16.1</v>
+        <v>20</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8">
@@ -8060,19 +8106,22 @@
       </c>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7">
-        <f>Inputs!$B$25</f>
+        <f>Inputs!$B$34</f>
         <v/>
       </c>
       <c r="L7" s="7">
-        <f>Inputs!$B$26</f>
-        <v/>
-      </c>
-      <c r="M7" s="7">
-        <f>Inputs!$B$20</f>
-        <v/>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>0</v>
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="O7" s="8">
         <f>IF(A7="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A7))</f>
@@ -8128,7 +8177,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Noue sud principale (corridor 2 m).</t>
+          <t>Segment sud 20 m correspondant a l'emprise du bassin lineaire (pas superpose a E03).</t>
         </is>
       </c>
       <c r="AC7" s="7" t="n"/>
@@ -8688,7 +8737,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="F12" s="15">
@@ -8796,51 +8845,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>J-OUEST-AVAL</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>J-BASSIN-IN</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
       <c r="I13" s="8">
         <f>IF(A13="","",IF(H13&lt;&gt;"",H13,IF(UPPER(TRIM(B13))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B13))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
       <c r="O13" s="8">
         <f>IF(A13="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A13))</f>
         <v/>
@@ -8893,11 +8914,7 @@
         <f>IF(A13="","",IF(OR(U13&gt;1,AND(X13&lt;&gt;"",X13&lt;Inputs!$B$16),AND(X13&lt;&gt;"",X13&gt;Inputs!$B$17),G13&lt;Inputs!$B$18,AH13="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>Branche ouest vers entree bassin.</t>
-        </is>
-      </c>
+      <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="7" t="n"/>
       <c r="AD13" s="8">
         <f>IF(A13="","",IF(AC13&lt;&gt;"",AC13,IF(E13="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))))</f>
@@ -8943,10 +8960,10 @@
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8">
@@ -8954,7 +8971,7 @@
         <v/>
       </c>
       <c r="J14" s="7" t="n">
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
@@ -9016,7 +9033,7 @@
       </c>
       <c r="AB14" s="4" t="inlineStr">
         <is>
-          <t>Injection finale vers bassin retention.</t>
+          <t>Courte liaison d'entree/ouvrage de regulation vers noeud de stockage BASSIN-RET.</t>
         </is>
       </c>
       <c r="AC14" s="7" t="n"/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -742,6 +742,34 @@
       <c r="A32" t="inlineStr">
         <is>
           <t>Bassin retention longueur mise a 20 m (Inputs!B35) selon releve plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Deux entrees bassin implementees: EST via E03-&gt;E07 et OUEST via E04-&gt;E08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E04 corrige a 4.7 m (J-OUEST-AVAL -&gt; J-BASSIN-OUEST), sans superposition avec E03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Traverses pave-uni ouest conservees en caniveau + conduite (E05B, E05D).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Principe invert: fond swale a l'entree doit rester au-dessus de l'invert du tuyau d'entree + chute locale (drop).</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2596,6 +2624,26 @@
       <c r="D52" s="4" t="inlineStr">
         <is>
           <t>NO recommande: empreinte bassin n'est pas contributive au bassin lui-meme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>West_swale_to_basin_inlet_m</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Distance mesuree J-OUEST-AVAL -&gt; entree ouest bassin (image utilisateur).</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2785,12 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Toiture vers collecte sud</t>
+          <t>Routage provisoire vers entree EST; scinder est/ouest plus tard si detail aval disponible.</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3195,12 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Vers noue sud</t>
+          <t>Routage vers entree EST (courbe cote est sur plan).</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8090,7 @@
       </c>
       <c r="AB6" s="4" t="inlineStr">
         <is>
-          <t>Corrige: P-03 -&gt; J-BASSIN-IN = 16.1 m (pas 20 m).</t>
+          <t>Entree EST: P-03 -&gt; J-BASSIN-IN (16.1 m).</t>
         </is>
       </c>
       <c r="AC6" s="7" t="n"/>
@@ -8085,16 +8133,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>J-BASSIN-IN</t>
+          <t>J-BASSIN-OUEST</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>20</v>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="F7" s="7">
+        <f>Inputs!$B$53</f>
+        <v/>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.004</v>
@@ -8105,23 +8154,17 @@
         <v/>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7">
-        <f>Inputs!$B$34</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>Inputs!$B$36</f>
-        <v/>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K7" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O7" s="8">
         <f>IF(A7="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A7))</f>
@@ -8177,7 +8220,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Segment sud 20 m correspondant a l'emprise du bassin lineaire (pas superpose a E03).</t>
+          <t>Corrige: liaison ouest courte vers entree ouest bassin (4.7 m mesure).</t>
         </is>
       </c>
       <c r="AC7" s="7" t="n"/>
@@ -8433,7 +8476,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Ouest pave-uni court - longueur cotee 2.3 m.</t>
+          <t>Traverse pave-uni court via caniveau/grille + conduite (DN250).</t>
         </is>
       </c>
       <c r="AC9" s="7" t="n"/>
@@ -8689,7 +8732,7 @@
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
-          <t>Ouest pave-uni inferieur - longueur cotee 5.1 m.</t>
+          <t>Traverse pave-uni principal via caniveau/grille + conduite (DN300).</t>
         </is>
       </c>
       <c r="AC11" s="7" t="n"/>
@@ -9059,23 +9102,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-OUEST</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.005</v>
+      </c>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="8">
         <f>IF(A15="","",IF(H15&lt;&gt;"",H15,IF(UPPER(TRIM(B15))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B15))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
+      <c r="J15" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="O15" s="8">
         <f>IF(A15="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A15))</f>
         <v/>
@@ -9128,7 +9195,11 @@
         <f>IF(A15="","",IF(OR(U15&gt;1,AND(X15&lt;&gt;"",X15&lt;Inputs!$B$16),AND(X15&lt;&gt;"",X15&gt;Inputs!$B$17),G15&lt;Inputs!$B$18,AH15="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
-      <c r="AB15" s="4" t="n"/>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>Entree OUEST: liaison caniveau/ouvrage vers bassin (2e entree).</t>
+        </is>
+      </c>
       <c r="AC15" s="7" t="n"/>
       <c r="AD15" s="8">
         <f>IF(A15="","",IF(AC15&lt;&gt;"",AC15,IF(E15="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))))</f>
@@ -27849,22 +27920,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-OUEST</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="8">
         <f>IF(OR(C17="",D17=""),"",MAX(0,C17-D17))</f>
         <v/>
       </c>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="8">
         <f>IF(A17="","",IF(UPPER(TRIM(F17))="CIRC",PI()*(G17/2)^2*E17,IF(UPPER(TRIM(F17))="RECT",G17*H17*E17,"")))</f>
         <v/>
       </c>
-      <c r="J17" s="7" t="n"/>
+      <c r="J17" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K17" s="8">
         <f>IF(A17="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A17))</f>
         <v/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -26,8 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[&lt;1]0.000;0.00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -109,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -130,6 +131,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -529,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -770,6 +773,34 @@
       <c r="A36" t="inlineStr">
         <is>
           <t>Principe invert: fond swale a l'entree doit rester au-dessus de l'invert du tuyau d'entree + chute locale (drop).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nouveau controle de chute: Inputs!B54:B56 definissent tolerance et plage de drop SWALE/TRENCH -&gt; PIPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Elements_hybrides: AI (type aval), AJ/AK (plage de drop), AL (Drop_check_status).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pour une entree bassin depuis noue/tranchee, viser AG autour de Inputs!B57 (ex. 0.10 m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Si AL=CHECK: ajuster invert aval/amont (AC override ou pente/longueur) ou ajouter ouvrage de chute.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2644,6 +2675,86 @@
       <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Distance mesuree J-OUEST-AVAL -&gt; entree ouest bassin (image utilisateur).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Connection_equal_tolerance_m</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Tolerance pour raccord sans chute (PIPE-&gt;PIPE ou SWALE-&gt;SWALE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Drop_min_swale_trench_to_pipe_m</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Chute minimale recommandee pour SWALE/TRENCH vers PIPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Drop_max_swale_trench_to_pipe_m</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Chute maximale recommandee avant ouvrage de chute dedie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Basin_inlet_target_drop_m</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Valeur cible pratique pour entree swale/trench vers conduite bassin.</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH204"/>
+  <dimension ref="A1:AL204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7530,6 +7641,10 @@
     <col width="14" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7542,7 +7657,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Legend: PIPE=blue, SWALE=green, TRENCH=orange, CHECK=red.</t>
+          <t>Legend: PIPE=blue, SWALE=green, TRENCH=orange, CHECK=red; AH connection status and AL drop check use Inputs!B54:B56 thresholds.</t>
         </is>
       </c>
     </row>
@@ -7715,6 +7830,26 @@
       <c r="AH3" s="6" t="inlineStr">
         <is>
           <t>Connection_status</t>
+        </is>
+      </c>
+      <c r="AI3" s="6" t="inlineStr">
+        <is>
+          <t>Downstream_type</t>
+        </is>
+      </c>
+      <c r="AJ3" s="6" t="inlineStr">
+        <is>
+          <t>Drop_min_req_m</t>
+        </is>
+      </c>
+      <c r="AK3" s="6" t="inlineStr">
+        <is>
+          <t>Drop_max_req_m</t>
+        </is>
+      </c>
+      <c r="AL3" s="6" t="inlineStr">
+        <is>
+          <t>Drop_check_status</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7985,23 @@
         <v/>
       </c>
       <c r="AH4" s="4">
-        <f>IF(A4="","",IF(E4="","TERMINAL",IF(AG4="","INFO",IF(ABS(AG4)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A4="","",IF(E4="","TERMINAL",IF(OR(AND(UPPER(TRIM(B4))="SWALE",UPPER(TRIM(AI4))="PIPE"),AND(UPPER(TRIM(B4))="TRENCH",UPPER(TRIM(AI4))="PIPE")),IF(OR(AG4="",AJ4="",AK4=""),"INFO",IF(AND(AG4&gt;=AJ4,AG4&lt;=AK4),"OK","CHECK")),IF(AG4="","INFO",IF(ABS(AG4)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI4" s="17">
+        <f>IF(A4="","",IF(E4="","",IFERROR(INDEX($B$4:$B$204,MATCH(E4,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="17">
+        <f>IF(A4="","",IF(OR(AND(UPPER(TRIM(B4))="SWALE",UPPER(TRIM(AI4))="PIPE"),AND(UPPER(TRIM(B4))="TRENCH",UPPER(TRIM(AI4))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK4" s="17">
+        <f>IF(A4="","",IF(OR(AND(UPPER(TRIM(B4))="SWALE",UPPER(TRIM(AI4))="PIPE"),AND(UPPER(TRIM(B4))="TRENCH",UPPER(TRIM(AI4))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL4" s="4">
+        <f>IF(A4="","",IF(E4="","TERMINAL",IF(OR(AND(UPPER(TRIM(B4))="SWALE",UPPER(TRIM(AI4))="PIPE"),AND(UPPER(TRIM(B4))="TRENCH",UPPER(TRIM(AI4))="PIPE")),IF(OR(AG4="",AJ4="",AK4=""),"INFO",IF(AND(AG4&gt;=AJ4,AG4&lt;=AK4),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -7986,7 +8137,23 @@
         <v/>
       </c>
       <c r="AH5" s="4">
-        <f>IF(A5="","",IF(E5="","TERMINAL",IF(AG5="","INFO",IF(ABS(AG5)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A5="","",IF(E5="","TERMINAL",IF(OR(AND(UPPER(TRIM(B5))="SWALE",UPPER(TRIM(AI5))="PIPE"),AND(UPPER(TRIM(B5))="TRENCH",UPPER(TRIM(AI5))="PIPE")),IF(OR(AG5="",AJ5="",AK5=""),"INFO",IF(AND(AG5&gt;=AJ5,AG5&lt;=AK5),"OK","CHECK")),IF(AG5="","INFO",IF(ABS(AG5)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI5" s="17">
+        <f>IF(A5="","",IF(E5="","",IFERROR(INDEX($B$4:$B$204,MATCH(E5,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="17">
+        <f>IF(A5="","",IF(OR(AND(UPPER(TRIM(B5))="SWALE",UPPER(TRIM(AI5))="PIPE"),AND(UPPER(TRIM(B5))="TRENCH",UPPER(TRIM(AI5))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK5" s="17">
+        <f>IF(A5="","",IF(OR(AND(UPPER(TRIM(B5))="SWALE",UPPER(TRIM(AI5))="PIPE"),AND(UPPER(TRIM(B5))="TRENCH",UPPER(TRIM(AI5))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL5" s="4">
+        <f>IF(A5="","",IF(E5="","TERMINAL",IF(OR(AND(UPPER(TRIM(B5))="SWALE",UPPER(TRIM(AI5))="PIPE"),AND(UPPER(TRIM(B5))="TRENCH",UPPER(TRIM(AI5))="PIPE")),IF(OR(AG5="",AJ5="",AK5=""),"INFO",IF(AND(AG5&gt;=AJ5,AG5&lt;=AK5),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8111,7 +8278,23 @@
         <v/>
       </c>
       <c r="AH6" s="4">
-        <f>IF(A6="","",IF(E6="","TERMINAL",IF(AG6="","INFO",IF(ABS(AG6)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A6="","",IF(E6="","TERMINAL",IF(OR(AND(UPPER(TRIM(B6))="SWALE",UPPER(TRIM(AI6))="PIPE"),AND(UPPER(TRIM(B6))="TRENCH",UPPER(TRIM(AI6))="PIPE")),IF(OR(AG6="",AJ6="",AK6=""),"INFO",IF(AND(AG6&gt;=AJ6,AG6&lt;=AK6),"OK","CHECK")),IF(AG6="","INFO",IF(ABS(AG6)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI6" s="17">
+        <f>IF(A6="","",IF(E6="","",IFERROR(INDEX($B$4:$B$204,MATCH(E6,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="17">
+        <f>IF(A6="","",IF(OR(AND(UPPER(TRIM(B6))="SWALE",UPPER(TRIM(AI6))="PIPE"),AND(UPPER(TRIM(B6))="TRENCH",UPPER(TRIM(AI6))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK6" s="17">
+        <f>IF(A6="","",IF(OR(AND(UPPER(TRIM(B6))="SWALE",UPPER(TRIM(AI6))="PIPE"),AND(UPPER(TRIM(B6))="TRENCH",UPPER(TRIM(AI6))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL6" s="4">
+        <f>IF(A6="","",IF(E6="","TERMINAL",IF(OR(AND(UPPER(TRIM(B6))="SWALE",UPPER(TRIM(AI6))="PIPE"),AND(UPPER(TRIM(B6))="TRENCH",UPPER(TRIM(AI6))="PIPE")),IF(OR(AG6="",AJ6="",AK6=""),"INFO",IF(AND(AG6&gt;=AJ6,AG6&lt;=AK6),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8241,7 +8424,23 @@
         <v/>
       </c>
       <c r="AH7" s="4">
-        <f>IF(A7="","",IF(E7="","TERMINAL",IF(AG7="","INFO",IF(ABS(AG7)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A7="","",IF(E7="","TERMINAL",IF(OR(AND(UPPER(TRIM(B7))="SWALE",UPPER(TRIM(AI7))="PIPE"),AND(UPPER(TRIM(B7))="TRENCH",UPPER(TRIM(AI7))="PIPE")),IF(OR(AG7="",AJ7="",AK7=""),"INFO",IF(AND(AG7&gt;=AJ7,AG7&lt;=AK7),"OK","CHECK")),IF(AG7="","INFO",IF(ABS(AG7)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI7" s="17">
+        <f>IF(A7="","",IF(E7="","",IFERROR(INDEX($B$4:$B$204,MATCH(E7,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="17">
+        <f>IF(A7="","",IF(OR(AND(UPPER(TRIM(B7))="SWALE",UPPER(TRIM(AI7))="PIPE"),AND(UPPER(TRIM(B7))="TRENCH",UPPER(TRIM(AI7))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK7" s="17">
+        <f>IF(A7="","",IF(OR(AND(UPPER(TRIM(B7))="SWALE",UPPER(TRIM(AI7))="PIPE"),AND(UPPER(TRIM(B7))="TRENCH",UPPER(TRIM(AI7))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL7" s="4">
+        <f>IF(A7="","",IF(E7="","TERMINAL",IF(OR(AND(UPPER(TRIM(B7))="SWALE",UPPER(TRIM(AI7))="PIPE"),AND(UPPER(TRIM(B7))="TRENCH",UPPER(TRIM(AI7))="PIPE")),IF(OR(AG7="",AJ7="",AK7=""),"INFO",IF(AND(AG7&gt;=AJ7,AG7&lt;=AK7),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8371,7 +8570,23 @@
         <v/>
       </c>
       <c r="AH8" s="4">
-        <f>IF(A8="","",IF(E8="","TERMINAL",IF(AG8="","INFO",IF(ABS(AG8)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A8="","",IF(E8="","TERMINAL",IF(OR(AND(UPPER(TRIM(B8))="SWALE",UPPER(TRIM(AI8))="PIPE"),AND(UPPER(TRIM(B8))="TRENCH",UPPER(TRIM(AI8))="PIPE")),IF(OR(AG8="",AJ8="",AK8=""),"INFO",IF(AND(AG8&gt;=AJ8,AG8&lt;=AK8),"OK","CHECK")),IF(AG8="","INFO",IF(ABS(AG8)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI8" s="17">
+        <f>IF(A8="","",IF(E8="","",IFERROR(INDEX($B$4:$B$204,MATCH(E8,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="17">
+        <f>IF(A8="","",IF(OR(AND(UPPER(TRIM(B8))="SWALE",UPPER(TRIM(AI8))="PIPE"),AND(UPPER(TRIM(B8))="TRENCH",UPPER(TRIM(AI8))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK8" s="17">
+        <f>IF(A8="","",IF(OR(AND(UPPER(TRIM(B8))="SWALE",UPPER(TRIM(AI8))="PIPE"),AND(UPPER(TRIM(B8))="TRENCH",UPPER(TRIM(AI8))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL8" s="4">
+        <f>IF(A8="","",IF(E8="","TERMINAL",IF(OR(AND(UPPER(TRIM(B8))="SWALE",UPPER(TRIM(AI8))="PIPE"),AND(UPPER(TRIM(B8))="TRENCH",UPPER(TRIM(AI8))="PIPE")),IF(OR(AG8="",AJ8="",AK8=""),"INFO",IF(AND(AG8&gt;=AJ8,AG8&lt;=AK8),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8497,7 +8712,23 @@
         <v/>
       </c>
       <c r="AH9" s="4">
-        <f>IF(A9="","",IF(E9="","TERMINAL",IF(AG9="","INFO",IF(ABS(AG9)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A9="","",IF(E9="","TERMINAL",IF(OR(AND(UPPER(TRIM(B9))="SWALE",UPPER(TRIM(AI9))="PIPE"),AND(UPPER(TRIM(B9))="TRENCH",UPPER(TRIM(AI9))="PIPE")),IF(OR(AG9="",AJ9="",AK9=""),"INFO",IF(AND(AG9&gt;=AJ9,AG9&lt;=AK9),"OK","CHECK")),IF(AG9="","INFO",IF(ABS(AG9)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="17">
+        <f>IF(A9="","",IF(E9="","",IFERROR(INDEX($B$4:$B$204,MATCH(E9,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="17">
+        <f>IF(A9="","",IF(OR(AND(UPPER(TRIM(B9))="SWALE",UPPER(TRIM(AI9))="PIPE"),AND(UPPER(TRIM(B9))="TRENCH",UPPER(TRIM(AI9))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK9" s="17">
+        <f>IF(A9="","",IF(OR(AND(UPPER(TRIM(B9))="SWALE",UPPER(TRIM(AI9))="PIPE"),AND(UPPER(TRIM(B9))="TRENCH",UPPER(TRIM(AI9))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL9" s="4">
+        <f>IF(A9="","",IF(E9="","TERMINAL",IF(OR(AND(UPPER(TRIM(B9))="SWALE",UPPER(TRIM(AI9))="PIPE"),AND(UPPER(TRIM(B9))="TRENCH",UPPER(TRIM(AI9))="PIPE")),IF(OR(AG9="",AJ9="",AK9=""),"INFO",IF(AND(AG9&gt;=AJ9,AG9&lt;=AK9),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8627,7 +8858,23 @@
         <v/>
       </c>
       <c r="AH10" s="4">
-        <f>IF(A10="","",IF(E10="","TERMINAL",IF(AG10="","INFO",IF(ABS(AG10)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A10="","",IF(E10="","TERMINAL",IF(OR(AND(UPPER(TRIM(B10))="SWALE",UPPER(TRIM(AI10))="PIPE"),AND(UPPER(TRIM(B10))="TRENCH",UPPER(TRIM(AI10))="PIPE")),IF(OR(AG10="",AJ10="",AK10=""),"INFO",IF(AND(AG10&gt;=AJ10,AG10&lt;=AK10),"OK","CHECK")),IF(AG10="","INFO",IF(ABS(AG10)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="17">
+        <f>IF(A10="","",IF(E10="","",IFERROR(INDEX($B$4:$B$204,MATCH(E10,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="17">
+        <f>IF(A10="","",IF(OR(AND(UPPER(TRIM(B10))="SWALE",UPPER(TRIM(AI10))="PIPE"),AND(UPPER(TRIM(B10))="TRENCH",UPPER(TRIM(AI10))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK10" s="17">
+        <f>IF(A10="","",IF(OR(AND(UPPER(TRIM(B10))="SWALE",UPPER(TRIM(AI10))="PIPE"),AND(UPPER(TRIM(B10))="TRENCH",UPPER(TRIM(AI10))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL10" s="4">
+        <f>IF(A10="","",IF(E10="","TERMINAL",IF(OR(AND(UPPER(TRIM(B10))="SWALE",UPPER(TRIM(AI10))="PIPE"),AND(UPPER(TRIM(B10))="TRENCH",UPPER(TRIM(AI10))="PIPE")),IF(OR(AG10="",AJ10="",AK10=""),"INFO",IF(AND(AG10&gt;=AJ10,AG10&lt;=AK10),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8753,7 +9000,23 @@
         <v/>
       </c>
       <c r="AH11" s="4">
-        <f>IF(A11="","",IF(E11="","TERMINAL",IF(AG11="","INFO",IF(ABS(AG11)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A11="","",IF(E11="","TERMINAL",IF(OR(AND(UPPER(TRIM(B11))="SWALE",UPPER(TRIM(AI11))="PIPE"),AND(UPPER(TRIM(B11))="TRENCH",UPPER(TRIM(AI11))="PIPE")),IF(OR(AG11="",AJ11="",AK11=""),"INFO",IF(AND(AG11&gt;=AJ11,AG11&lt;=AK11),"OK","CHECK")),IF(AG11="","INFO",IF(ABS(AG11)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="17">
+        <f>IF(A11="","",IF(E11="","",IFERROR(INDEX($B$4:$B$204,MATCH(E11,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="17">
+        <f>IF(A11="","",IF(OR(AND(UPPER(TRIM(B11))="SWALE",UPPER(TRIM(AI11))="PIPE"),AND(UPPER(TRIM(B11))="TRENCH",UPPER(TRIM(AI11))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK11" s="17">
+        <f>IF(A11="","",IF(OR(AND(UPPER(TRIM(B11))="SWALE",UPPER(TRIM(AI11))="PIPE"),AND(UPPER(TRIM(B11))="TRENCH",UPPER(TRIM(AI11))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL11" s="4">
+        <f>IF(A11="","",IF(E11="","TERMINAL",IF(OR(AND(UPPER(TRIM(B11))="SWALE",UPPER(TRIM(AI11))="PIPE"),AND(UPPER(TRIM(B11))="TRENCH",UPPER(TRIM(AI11))="PIPE")),IF(OR(AG11="",AJ11="",AK11=""),"INFO",IF(AND(AG11&gt;=AJ11,AG11&lt;=AK11),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8883,7 +9146,23 @@
         <v/>
       </c>
       <c r="AH12" s="4">
-        <f>IF(A12="","",IF(E12="","TERMINAL",IF(AG12="","INFO",IF(ABS(AG12)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A12="","",IF(E12="","TERMINAL",IF(OR(AND(UPPER(TRIM(B12))="SWALE",UPPER(TRIM(AI12))="PIPE"),AND(UPPER(TRIM(B12))="TRENCH",UPPER(TRIM(AI12))="PIPE")),IF(OR(AG12="",AJ12="",AK12=""),"INFO",IF(AND(AG12&gt;=AJ12,AG12&lt;=AK12),"OK","CHECK")),IF(AG12="","INFO",IF(ABS(AG12)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="17">
+        <f>IF(A12="","",IF(E12="","",IFERROR(INDEX($B$4:$B$204,MATCH(E12,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="17">
+        <f>IF(A12="","",IF(OR(AND(UPPER(TRIM(B12))="SWALE",UPPER(TRIM(AI12))="PIPE"),AND(UPPER(TRIM(B12))="TRENCH",UPPER(TRIM(AI12))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK12" s="17">
+        <f>IF(A12="","",IF(OR(AND(UPPER(TRIM(B12))="SWALE",UPPER(TRIM(AI12))="PIPE"),AND(UPPER(TRIM(B12))="TRENCH",UPPER(TRIM(AI12))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL12" s="4">
+        <f>IF(A12="","",IF(E12="","TERMINAL",IF(OR(AND(UPPER(TRIM(B12))="SWALE",UPPER(TRIM(AI12))="PIPE"),AND(UPPER(TRIM(B12))="TRENCH",UPPER(TRIM(AI12))="PIPE")),IF(OR(AG12="",AJ12="",AK12=""),"INFO",IF(AND(AG12&gt;=AJ12,AG12&lt;=AK12),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -8976,7 +9255,23 @@
         <v/>
       </c>
       <c r="AH13" s="4">
-        <f>IF(A13="","",IF(E13="","TERMINAL",IF(AG13="","INFO",IF(ABS(AG13)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A13="","",IF(E13="","TERMINAL",IF(OR(AND(UPPER(TRIM(B13))="SWALE",UPPER(TRIM(AI13))="PIPE"),AND(UPPER(TRIM(B13))="TRENCH",UPPER(TRIM(AI13))="PIPE")),IF(OR(AG13="",AJ13="",AK13=""),"INFO",IF(AND(AG13&gt;=AJ13,AG13&lt;=AK13),"OK","CHECK")),IF(AG13="","INFO",IF(ABS(AG13)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="17">
+        <f>IF(A13="","",IF(E13="","",IFERROR(INDEX($B$4:$B$204,MATCH(E13,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="17">
+        <f>IF(A13="","",IF(OR(AND(UPPER(TRIM(B13))="SWALE",UPPER(TRIM(AI13))="PIPE"),AND(UPPER(TRIM(B13))="TRENCH",UPPER(TRIM(AI13))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK13" s="17">
+        <f>IF(A13="","",IF(OR(AND(UPPER(TRIM(B13))="SWALE",UPPER(TRIM(AI13))="PIPE"),AND(UPPER(TRIM(B13))="TRENCH",UPPER(TRIM(AI13))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL13" s="4">
+        <f>IF(A13="","",IF(E13="","TERMINAL",IF(OR(AND(UPPER(TRIM(B13))="SWALE",UPPER(TRIM(AI13))="PIPE"),AND(UPPER(TRIM(B13))="TRENCH",UPPER(TRIM(AI13))="PIPE")),IF(OR(AG13="",AJ13="",AK13=""),"INFO",IF(AND(AG13&gt;=AJ13,AG13&lt;=AK13),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9097,7 +9392,23 @@
         <v/>
       </c>
       <c r="AH14" s="4">
-        <f>IF(A14="","",IF(E14="","TERMINAL",IF(AG14="","INFO",IF(ABS(AG14)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A14="","",IF(E14="","TERMINAL",IF(OR(AND(UPPER(TRIM(B14))="SWALE",UPPER(TRIM(AI14))="PIPE"),AND(UPPER(TRIM(B14))="TRENCH",UPPER(TRIM(AI14))="PIPE")),IF(OR(AG14="",AJ14="",AK14=""),"INFO",IF(AND(AG14&gt;=AJ14,AG14&lt;=AK14),"OK","CHECK")),IF(AG14="","INFO",IF(ABS(AG14)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="17">
+        <f>IF(A14="","",IF(E14="","",IFERROR(INDEX($B$4:$B$204,MATCH(E14,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="17">
+        <f>IF(A14="","",IF(OR(AND(UPPER(TRIM(B14))="SWALE",UPPER(TRIM(AI14))="PIPE"),AND(UPPER(TRIM(B14))="TRENCH",UPPER(TRIM(AI14))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK14" s="17">
+        <f>IF(A14="","",IF(OR(AND(UPPER(TRIM(B14))="SWALE",UPPER(TRIM(AI14))="PIPE"),AND(UPPER(TRIM(B14))="TRENCH",UPPER(TRIM(AI14))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL14" s="4">
+        <f>IF(A14="","",IF(E14="","TERMINAL",IF(OR(AND(UPPER(TRIM(B14))="SWALE",UPPER(TRIM(AI14))="PIPE"),AND(UPPER(TRIM(B14))="TRENCH",UPPER(TRIM(AI14))="PIPE")),IF(OR(AG14="",AJ14="",AK14=""),"INFO",IF(AND(AG14&gt;=AJ14,AG14&lt;=AK14),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9218,7 +9529,23 @@
         <v/>
       </c>
       <c r="AH15" s="4">
-        <f>IF(A15="","",IF(E15="","TERMINAL",IF(AG15="","INFO",IF(ABS(AG15)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A15="","",IF(E15="","TERMINAL",IF(OR(AND(UPPER(TRIM(B15))="SWALE",UPPER(TRIM(AI15))="PIPE"),AND(UPPER(TRIM(B15))="TRENCH",UPPER(TRIM(AI15))="PIPE")),IF(OR(AG15="",AJ15="",AK15=""),"INFO",IF(AND(AG15&gt;=AJ15,AG15&lt;=AK15),"OK","CHECK")),IF(AG15="","INFO",IF(ABS(AG15)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="17">
+        <f>IF(A15="","",IF(E15="","",IFERROR(INDEX($B$4:$B$204,MATCH(E15,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="17">
+        <f>IF(A15="","",IF(OR(AND(UPPER(TRIM(B15))="SWALE",UPPER(TRIM(AI15))="PIPE"),AND(UPPER(TRIM(B15))="TRENCH",UPPER(TRIM(AI15))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK15" s="17">
+        <f>IF(A15="","",IF(OR(AND(UPPER(TRIM(B15))="SWALE",UPPER(TRIM(AI15))="PIPE"),AND(UPPER(TRIM(B15))="TRENCH",UPPER(TRIM(AI15))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL15" s="4">
+        <f>IF(A15="","",IF(E15="","TERMINAL",IF(OR(AND(UPPER(TRIM(B15))="SWALE",UPPER(TRIM(AI15))="PIPE"),AND(UPPER(TRIM(B15))="TRENCH",UPPER(TRIM(AI15))="PIPE")),IF(OR(AG15="",AJ15="",AK15=""),"INFO",IF(AND(AG15&gt;=AJ15,AG15&lt;=AK15),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9311,7 +9638,23 @@
         <v/>
       </c>
       <c r="AH16" s="4">
-        <f>IF(A16="","",IF(E16="","TERMINAL",IF(AG16="","INFO",IF(ABS(AG16)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A16="","",IF(E16="","TERMINAL",IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),IF(OR(AG16="",AJ16="",AK16=""),"INFO",IF(AND(AG16&gt;=AJ16,AG16&lt;=AK16),"OK","CHECK")),IF(AG16="","INFO",IF(ABS(AG16)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="17">
+        <f>IF(A16="","",IF(E16="","",IFERROR(INDEX($B$4:$B$204,MATCH(E16,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="17">
+        <f>IF(A16="","",IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK16" s="17">
+        <f>IF(A16="","",IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL16" s="4">
+        <f>IF(A16="","",IF(E16="","TERMINAL",IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),IF(OR(AG16="",AJ16="",AK16=""),"INFO",IF(AND(AG16&gt;=AJ16,AG16&lt;=AK16),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9404,7 +9747,23 @@
         <v/>
       </c>
       <c r="AH17" s="4">
-        <f>IF(A17="","",IF(E17="","TERMINAL",IF(AG17="","INFO",IF(ABS(AG17)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A17="","",IF(E17="","TERMINAL",IF(OR(AND(UPPER(TRIM(B17))="SWALE",UPPER(TRIM(AI17))="PIPE"),AND(UPPER(TRIM(B17))="TRENCH",UPPER(TRIM(AI17))="PIPE")),IF(OR(AG17="",AJ17="",AK17=""),"INFO",IF(AND(AG17&gt;=AJ17,AG17&lt;=AK17),"OK","CHECK")),IF(AG17="","INFO",IF(ABS(AG17)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="17">
+        <f>IF(A17="","",IF(E17="","",IFERROR(INDEX($B$4:$B$204,MATCH(E17,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="17">
+        <f>IF(A17="","",IF(OR(AND(UPPER(TRIM(B17))="SWALE",UPPER(TRIM(AI17))="PIPE"),AND(UPPER(TRIM(B17))="TRENCH",UPPER(TRIM(AI17))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK17" s="17">
+        <f>IF(A17="","",IF(OR(AND(UPPER(TRIM(B17))="SWALE",UPPER(TRIM(AI17))="PIPE"),AND(UPPER(TRIM(B17))="TRENCH",UPPER(TRIM(AI17))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL17" s="4">
+        <f>IF(A17="","",IF(E17="","TERMINAL",IF(OR(AND(UPPER(TRIM(B17))="SWALE",UPPER(TRIM(AI17))="PIPE"),AND(UPPER(TRIM(B17))="TRENCH",UPPER(TRIM(AI17))="PIPE")),IF(OR(AG17="",AJ17="",AK17=""),"INFO",IF(AND(AG17&gt;=AJ17,AG17&lt;=AK17),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9497,7 +9856,23 @@
         <v/>
       </c>
       <c r="AH18" s="4">
-        <f>IF(A18="","",IF(E18="","TERMINAL",IF(AG18="","INFO",IF(ABS(AG18)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A18="","",IF(E18="","TERMINAL",IF(OR(AND(UPPER(TRIM(B18))="SWALE",UPPER(TRIM(AI18))="PIPE"),AND(UPPER(TRIM(B18))="TRENCH",UPPER(TRIM(AI18))="PIPE")),IF(OR(AG18="",AJ18="",AK18=""),"INFO",IF(AND(AG18&gt;=AJ18,AG18&lt;=AK18),"OK","CHECK")),IF(AG18="","INFO",IF(ABS(AG18)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="17">
+        <f>IF(A18="","",IF(E18="","",IFERROR(INDEX($B$4:$B$204,MATCH(E18,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="17">
+        <f>IF(A18="","",IF(OR(AND(UPPER(TRIM(B18))="SWALE",UPPER(TRIM(AI18))="PIPE"),AND(UPPER(TRIM(B18))="TRENCH",UPPER(TRIM(AI18))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK18" s="17">
+        <f>IF(A18="","",IF(OR(AND(UPPER(TRIM(B18))="SWALE",UPPER(TRIM(AI18))="PIPE"),AND(UPPER(TRIM(B18))="TRENCH",UPPER(TRIM(AI18))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL18" s="4">
+        <f>IF(A18="","",IF(E18="","TERMINAL",IF(OR(AND(UPPER(TRIM(B18))="SWALE",UPPER(TRIM(AI18))="PIPE"),AND(UPPER(TRIM(B18))="TRENCH",UPPER(TRIM(AI18))="PIPE")),IF(OR(AG18="",AJ18="",AK18=""),"INFO",IF(AND(AG18&gt;=AJ18,AG18&lt;=AK18),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9590,7 +9965,23 @@
         <v/>
       </c>
       <c r="AH19" s="4">
-        <f>IF(A19="","",IF(E19="","TERMINAL",IF(AG19="","INFO",IF(ABS(AG19)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A19="","",IF(E19="","TERMINAL",IF(OR(AND(UPPER(TRIM(B19))="SWALE",UPPER(TRIM(AI19))="PIPE"),AND(UPPER(TRIM(B19))="TRENCH",UPPER(TRIM(AI19))="PIPE")),IF(OR(AG19="",AJ19="",AK19=""),"INFO",IF(AND(AG19&gt;=AJ19,AG19&lt;=AK19),"OK","CHECK")),IF(AG19="","INFO",IF(ABS(AG19)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="17">
+        <f>IF(A19="","",IF(E19="","",IFERROR(INDEX($B$4:$B$204,MATCH(E19,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="17">
+        <f>IF(A19="","",IF(OR(AND(UPPER(TRIM(B19))="SWALE",UPPER(TRIM(AI19))="PIPE"),AND(UPPER(TRIM(B19))="TRENCH",UPPER(TRIM(AI19))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK19" s="17">
+        <f>IF(A19="","",IF(OR(AND(UPPER(TRIM(B19))="SWALE",UPPER(TRIM(AI19))="PIPE"),AND(UPPER(TRIM(B19))="TRENCH",UPPER(TRIM(AI19))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL19" s="4">
+        <f>IF(A19="","",IF(E19="","TERMINAL",IF(OR(AND(UPPER(TRIM(B19))="SWALE",UPPER(TRIM(AI19))="PIPE"),AND(UPPER(TRIM(B19))="TRENCH",UPPER(TRIM(AI19))="PIPE")),IF(OR(AG19="",AJ19="",AK19=""),"INFO",IF(AND(AG19&gt;=AJ19,AG19&lt;=AK19),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9683,7 +10074,23 @@
         <v/>
       </c>
       <c r="AH20" s="4">
-        <f>IF(A20="","",IF(E20="","TERMINAL",IF(AG20="","INFO",IF(ABS(AG20)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A20="","",IF(E20="","TERMINAL",IF(OR(AND(UPPER(TRIM(B20))="SWALE",UPPER(TRIM(AI20))="PIPE"),AND(UPPER(TRIM(B20))="TRENCH",UPPER(TRIM(AI20))="PIPE")),IF(OR(AG20="",AJ20="",AK20=""),"INFO",IF(AND(AG20&gt;=AJ20,AG20&lt;=AK20),"OK","CHECK")),IF(AG20="","INFO",IF(ABS(AG20)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="17">
+        <f>IF(A20="","",IF(E20="","",IFERROR(INDEX($B$4:$B$204,MATCH(E20,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="17">
+        <f>IF(A20="","",IF(OR(AND(UPPER(TRIM(B20))="SWALE",UPPER(TRIM(AI20))="PIPE"),AND(UPPER(TRIM(B20))="TRENCH",UPPER(TRIM(AI20))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK20" s="17">
+        <f>IF(A20="","",IF(OR(AND(UPPER(TRIM(B20))="SWALE",UPPER(TRIM(AI20))="PIPE"),AND(UPPER(TRIM(B20))="TRENCH",UPPER(TRIM(AI20))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL20" s="4">
+        <f>IF(A20="","",IF(E20="","TERMINAL",IF(OR(AND(UPPER(TRIM(B20))="SWALE",UPPER(TRIM(AI20))="PIPE"),AND(UPPER(TRIM(B20))="TRENCH",UPPER(TRIM(AI20))="PIPE")),IF(OR(AG20="",AJ20="",AK20=""),"INFO",IF(AND(AG20&gt;=AJ20,AG20&lt;=AK20),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9778,7 +10185,23 @@
         <v/>
       </c>
       <c r="AH21" s="4">
-        <f>IF(A21="","",IF(E21="","TERMINAL",IF(AG21="","INFO",IF(ABS(AG21)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A21="","",IF(E21="","TERMINAL",IF(OR(AND(UPPER(TRIM(B21))="SWALE",UPPER(TRIM(AI21))="PIPE"),AND(UPPER(TRIM(B21))="TRENCH",UPPER(TRIM(AI21))="PIPE")),IF(OR(AG21="",AJ21="",AK21=""),"INFO",IF(AND(AG21&gt;=AJ21,AG21&lt;=AK21),"OK","CHECK")),IF(AG21="","INFO",IF(ABS(AG21)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI21" s="17">
+        <f>IF(A21="","",IF(E21="","",IFERROR(INDEX($B$4:$B$204,MATCH(E21,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="17">
+        <f>IF(A21="","",IF(OR(AND(UPPER(TRIM(B21))="SWALE",UPPER(TRIM(AI21))="PIPE"),AND(UPPER(TRIM(B21))="TRENCH",UPPER(TRIM(AI21))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK21" s="17">
+        <f>IF(A21="","",IF(OR(AND(UPPER(TRIM(B21))="SWALE",UPPER(TRIM(AI21))="PIPE"),AND(UPPER(TRIM(B21))="TRENCH",UPPER(TRIM(AI21))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL21" s="4">
+        <f>IF(A21="","",IF(E21="","TERMINAL",IF(OR(AND(UPPER(TRIM(B21))="SWALE",UPPER(TRIM(AI21))="PIPE"),AND(UPPER(TRIM(B21))="TRENCH",UPPER(TRIM(AI21))="PIPE")),IF(OR(AG21="",AJ21="",AK21=""),"INFO",IF(AND(AG21&gt;=AJ21,AG21&lt;=AK21),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9873,7 +10296,23 @@
         <v/>
       </c>
       <c r="AH22" s="4">
-        <f>IF(A22="","",IF(E22="","TERMINAL",IF(AG22="","INFO",IF(ABS(AG22)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A22="","",IF(E22="","TERMINAL",IF(OR(AND(UPPER(TRIM(B22))="SWALE",UPPER(TRIM(AI22))="PIPE"),AND(UPPER(TRIM(B22))="TRENCH",UPPER(TRIM(AI22))="PIPE")),IF(OR(AG22="",AJ22="",AK22=""),"INFO",IF(AND(AG22&gt;=AJ22,AG22&lt;=AK22),"OK","CHECK")),IF(AG22="","INFO",IF(ABS(AG22)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI22" s="17">
+        <f>IF(A22="","",IF(E22="","",IFERROR(INDEX($B$4:$B$204,MATCH(E22,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="17">
+        <f>IF(A22="","",IF(OR(AND(UPPER(TRIM(B22))="SWALE",UPPER(TRIM(AI22))="PIPE"),AND(UPPER(TRIM(B22))="TRENCH",UPPER(TRIM(AI22))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK22" s="17">
+        <f>IF(A22="","",IF(OR(AND(UPPER(TRIM(B22))="SWALE",UPPER(TRIM(AI22))="PIPE"),AND(UPPER(TRIM(B22))="TRENCH",UPPER(TRIM(AI22))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL22" s="4">
+        <f>IF(A22="","",IF(E22="","TERMINAL",IF(OR(AND(UPPER(TRIM(B22))="SWALE",UPPER(TRIM(AI22))="PIPE"),AND(UPPER(TRIM(B22))="TRENCH",UPPER(TRIM(AI22))="PIPE")),IF(OR(AG22="",AJ22="",AK22=""),"INFO",IF(AND(AG22&gt;=AJ22,AG22&lt;=AK22),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -9968,7 +10407,23 @@
         <v/>
       </c>
       <c r="AH23" s="4">
-        <f>IF(A23="","",IF(E23="","TERMINAL",IF(AG23="","INFO",IF(ABS(AG23)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A23="","",IF(E23="","TERMINAL",IF(OR(AND(UPPER(TRIM(B23))="SWALE",UPPER(TRIM(AI23))="PIPE"),AND(UPPER(TRIM(B23))="TRENCH",UPPER(TRIM(AI23))="PIPE")),IF(OR(AG23="",AJ23="",AK23=""),"INFO",IF(AND(AG23&gt;=AJ23,AG23&lt;=AK23),"OK","CHECK")),IF(AG23="","INFO",IF(ABS(AG23)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI23" s="17">
+        <f>IF(A23="","",IF(E23="","",IFERROR(INDEX($B$4:$B$204,MATCH(E23,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="17">
+        <f>IF(A23="","",IF(OR(AND(UPPER(TRIM(B23))="SWALE",UPPER(TRIM(AI23))="PIPE"),AND(UPPER(TRIM(B23))="TRENCH",UPPER(TRIM(AI23))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK23" s="17">
+        <f>IF(A23="","",IF(OR(AND(UPPER(TRIM(B23))="SWALE",UPPER(TRIM(AI23))="PIPE"),AND(UPPER(TRIM(B23))="TRENCH",UPPER(TRIM(AI23))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL23" s="4">
+        <f>IF(A23="","",IF(E23="","TERMINAL",IF(OR(AND(UPPER(TRIM(B23))="SWALE",UPPER(TRIM(AI23))="PIPE"),AND(UPPER(TRIM(B23))="TRENCH",UPPER(TRIM(AI23))="PIPE")),IF(OR(AG23="",AJ23="",AK23=""),"INFO",IF(AND(AG23&gt;=AJ23,AG23&lt;=AK23),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10063,7 +10518,23 @@
         <v/>
       </c>
       <c r="AH24" s="4">
-        <f>IF(A24="","",IF(E24="","TERMINAL",IF(AG24="","INFO",IF(ABS(AG24)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A24="","",IF(E24="","TERMINAL",IF(OR(AND(UPPER(TRIM(B24))="SWALE",UPPER(TRIM(AI24))="PIPE"),AND(UPPER(TRIM(B24))="TRENCH",UPPER(TRIM(AI24))="PIPE")),IF(OR(AG24="",AJ24="",AK24=""),"INFO",IF(AND(AG24&gt;=AJ24,AG24&lt;=AK24),"OK","CHECK")),IF(AG24="","INFO",IF(ABS(AG24)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI24" s="17">
+        <f>IF(A24="","",IF(E24="","",IFERROR(INDEX($B$4:$B$204,MATCH(E24,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="17">
+        <f>IF(A24="","",IF(OR(AND(UPPER(TRIM(B24))="SWALE",UPPER(TRIM(AI24))="PIPE"),AND(UPPER(TRIM(B24))="TRENCH",UPPER(TRIM(AI24))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK24" s="17">
+        <f>IF(A24="","",IF(OR(AND(UPPER(TRIM(B24))="SWALE",UPPER(TRIM(AI24))="PIPE"),AND(UPPER(TRIM(B24))="TRENCH",UPPER(TRIM(AI24))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL24" s="4">
+        <f>IF(A24="","",IF(E24="","TERMINAL",IF(OR(AND(UPPER(TRIM(B24))="SWALE",UPPER(TRIM(AI24))="PIPE"),AND(UPPER(TRIM(B24))="TRENCH",UPPER(TRIM(AI24))="PIPE")),IF(OR(AG24="",AJ24="",AK24=""),"INFO",IF(AND(AG24&gt;=AJ24,AG24&lt;=AK24),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10158,7 +10629,23 @@
         <v/>
       </c>
       <c r="AH25" s="4">
-        <f>IF(A25="","",IF(E25="","TERMINAL",IF(AG25="","INFO",IF(ABS(AG25)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A25="","",IF(E25="","TERMINAL",IF(OR(AND(UPPER(TRIM(B25))="SWALE",UPPER(TRIM(AI25))="PIPE"),AND(UPPER(TRIM(B25))="TRENCH",UPPER(TRIM(AI25))="PIPE")),IF(OR(AG25="",AJ25="",AK25=""),"INFO",IF(AND(AG25&gt;=AJ25,AG25&lt;=AK25),"OK","CHECK")),IF(AG25="","INFO",IF(ABS(AG25)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI25" s="17">
+        <f>IF(A25="","",IF(E25="","",IFERROR(INDEX($B$4:$B$204,MATCH(E25,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="17">
+        <f>IF(A25="","",IF(OR(AND(UPPER(TRIM(B25))="SWALE",UPPER(TRIM(AI25))="PIPE"),AND(UPPER(TRIM(B25))="TRENCH",UPPER(TRIM(AI25))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK25" s="17">
+        <f>IF(A25="","",IF(OR(AND(UPPER(TRIM(B25))="SWALE",UPPER(TRIM(AI25))="PIPE"),AND(UPPER(TRIM(B25))="TRENCH",UPPER(TRIM(AI25))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL25" s="4">
+        <f>IF(A25="","",IF(E25="","TERMINAL",IF(OR(AND(UPPER(TRIM(B25))="SWALE",UPPER(TRIM(AI25))="PIPE"),AND(UPPER(TRIM(B25))="TRENCH",UPPER(TRIM(AI25))="PIPE")),IF(OR(AG25="",AJ25="",AK25=""),"INFO",IF(AND(AG25&gt;=AJ25,AG25&lt;=AK25),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10253,7 +10740,23 @@
         <v/>
       </c>
       <c r="AH26" s="4">
-        <f>IF(A26="","",IF(E26="","TERMINAL",IF(AG26="","INFO",IF(ABS(AG26)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A26="","",IF(E26="","TERMINAL",IF(OR(AND(UPPER(TRIM(B26))="SWALE",UPPER(TRIM(AI26))="PIPE"),AND(UPPER(TRIM(B26))="TRENCH",UPPER(TRIM(AI26))="PIPE")),IF(OR(AG26="",AJ26="",AK26=""),"INFO",IF(AND(AG26&gt;=AJ26,AG26&lt;=AK26),"OK","CHECK")),IF(AG26="","INFO",IF(ABS(AG26)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI26" s="17">
+        <f>IF(A26="","",IF(E26="","",IFERROR(INDEX($B$4:$B$204,MATCH(E26,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="17">
+        <f>IF(A26="","",IF(OR(AND(UPPER(TRIM(B26))="SWALE",UPPER(TRIM(AI26))="PIPE"),AND(UPPER(TRIM(B26))="TRENCH",UPPER(TRIM(AI26))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK26" s="17">
+        <f>IF(A26="","",IF(OR(AND(UPPER(TRIM(B26))="SWALE",UPPER(TRIM(AI26))="PIPE"),AND(UPPER(TRIM(B26))="TRENCH",UPPER(TRIM(AI26))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL26" s="4">
+        <f>IF(A26="","",IF(E26="","TERMINAL",IF(OR(AND(UPPER(TRIM(B26))="SWALE",UPPER(TRIM(AI26))="PIPE"),AND(UPPER(TRIM(B26))="TRENCH",UPPER(TRIM(AI26))="PIPE")),IF(OR(AG26="",AJ26="",AK26=""),"INFO",IF(AND(AG26&gt;=AJ26,AG26&lt;=AK26),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10348,7 +10851,23 @@
         <v/>
       </c>
       <c r="AH27" s="4">
-        <f>IF(A27="","",IF(E27="","TERMINAL",IF(AG27="","INFO",IF(ABS(AG27)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A27="","",IF(E27="","TERMINAL",IF(OR(AND(UPPER(TRIM(B27))="SWALE",UPPER(TRIM(AI27))="PIPE"),AND(UPPER(TRIM(B27))="TRENCH",UPPER(TRIM(AI27))="PIPE")),IF(OR(AG27="",AJ27="",AK27=""),"INFO",IF(AND(AG27&gt;=AJ27,AG27&lt;=AK27),"OK","CHECK")),IF(AG27="","INFO",IF(ABS(AG27)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI27" s="17">
+        <f>IF(A27="","",IF(E27="","",IFERROR(INDEX($B$4:$B$204,MATCH(E27,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="17">
+        <f>IF(A27="","",IF(OR(AND(UPPER(TRIM(B27))="SWALE",UPPER(TRIM(AI27))="PIPE"),AND(UPPER(TRIM(B27))="TRENCH",UPPER(TRIM(AI27))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK27" s="17">
+        <f>IF(A27="","",IF(OR(AND(UPPER(TRIM(B27))="SWALE",UPPER(TRIM(AI27))="PIPE"),AND(UPPER(TRIM(B27))="TRENCH",UPPER(TRIM(AI27))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL27" s="4">
+        <f>IF(A27="","",IF(E27="","TERMINAL",IF(OR(AND(UPPER(TRIM(B27))="SWALE",UPPER(TRIM(AI27))="PIPE"),AND(UPPER(TRIM(B27))="TRENCH",UPPER(TRIM(AI27))="PIPE")),IF(OR(AG27="",AJ27="",AK27=""),"INFO",IF(AND(AG27&gt;=AJ27,AG27&lt;=AK27),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10443,7 +10962,23 @@
         <v/>
       </c>
       <c r="AH28" s="4">
-        <f>IF(A28="","",IF(E28="","TERMINAL",IF(AG28="","INFO",IF(ABS(AG28)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A28="","",IF(E28="","TERMINAL",IF(OR(AND(UPPER(TRIM(B28))="SWALE",UPPER(TRIM(AI28))="PIPE"),AND(UPPER(TRIM(B28))="TRENCH",UPPER(TRIM(AI28))="PIPE")),IF(OR(AG28="",AJ28="",AK28=""),"INFO",IF(AND(AG28&gt;=AJ28,AG28&lt;=AK28),"OK","CHECK")),IF(AG28="","INFO",IF(ABS(AG28)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI28" s="17">
+        <f>IF(A28="","",IF(E28="","",IFERROR(INDEX($B$4:$B$204,MATCH(E28,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="17">
+        <f>IF(A28="","",IF(OR(AND(UPPER(TRIM(B28))="SWALE",UPPER(TRIM(AI28))="PIPE"),AND(UPPER(TRIM(B28))="TRENCH",UPPER(TRIM(AI28))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK28" s="17">
+        <f>IF(A28="","",IF(OR(AND(UPPER(TRIM(B28))="SWALE",UPPER(TRIM(AI28))="PIPE"),AND(UPPER(TRIM(B28))="TRENCH",UPPER(TRIM(AI28))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL28" s="4">
+        <f>IF(A28="","",IF(E28="","TERMINAL",IF(OR(AND(UPPER(TRIM(B28))="SWALE",UPPER(TRIM(AI28))="PIPE"),AND(UPPER(TRIM(B28))="TRENCH",UPPER(TRIM(AI28))="PIPE")),IF(OR(AG28="",AJ28="",AK28=""),"INFO",IF(AND(AG28&gt;=AJ28,AG28&lt;=AK28),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10538,7 +11073,23 @@
         <v/>
       </c>
       <c r="AH29" s="4">
-        <f>IF(A29="","",IF(E29="","TERMINAL",IF(AG29="","INFO",IF(ABS(AG29)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A29="","",IF(E29="","TERMINAL",IF(OR(AND(UPPER(TRIM(B29))="SWALE",UPPER(TRIM(AI29))="PIPE"),AND(UPPER(TRIM(B29))="TRENCH",UPPER(TRIM(AI29))="PIPE")),IF(OR(AG29="",AJ29="",AK29=""),"INFO",IF(AND(AG29&gt;=AJ29,AG29&lt;=AK29),"OK","CHECK")),IF(AG29="","INFO",IF(ABS(AG29)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI29" s="17">
+        <f>IF(A29="","",IF(E29="","",IFERROR(INDEX($B$4:$B$204,MATCH(E29,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="17">
+        <f>IF(A29="","",IF(OR(AND(UPPER(TRIM(B29))="SWALE",UPPER(TRIM(AI29))="PIPE"),AND(UPPER(TRIM(B29))="TRENCH",UPPER(TRIM(AI29))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK29" s="17">
+        <f>IF(A29="","",IF(OR(AND(UPPER(TRIM(B29))="SWALE",UPPER(TRIM(AI29))="PIPE"),AND(UPPER(TRIM(B29))="TRENCH",UPPER(TRIM(AI29))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL29" s="4">
+        <f>IF(A29="","",IF(E29="","TERMINAL",IF(OR(AND(UPPER(TRIM(B29))="SWALE",UPPER(TRIM(AI29))="PIPE"),AND(UPPER(TRIM(B29))="TRENCH",UPPER(TRIM(AI29))="PIPE")),IF(OR(AG29="",AJ29="",AK29=""),"INFO",IF(AND(AG29&gt;=AJ29,AG29&lt;=AK29),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10633,7 +11184,23 @@
         <v/>
       </c>
       <c r="AH30" s="4">
-        <f>IF(A30="","",IF(E30="","TERMINAL",IF(AG30="","INFO",IF(ABS(AG30)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A30="","",IF(E30="","TERMINAL",IF(OR(AND(UPPER(TRIM(B30))="SWALE",UPPER(TRIM(AI30))="PIPE"),AND(UPPER(TRIM(B30))="TRENCH",UPPER(TRIM(AI30))="PIPE")),IF(OR(AG30="",AJ30="",AK30=""),"INFO",IF(AND(AG30&gt;=AJ30,AG30&lt;=AK30),"OK","CHECK")),IF(AG30="","INFO",IF(ABS(AG30)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI30" s="17">
+        <f>IF(A30="","",IF(E30="","",IFERROR(INDEX($B$4:$B$204,MATCH(E30,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="17">
+        <f>IF(A30="","",IF(OR(AND(UPPER(TRIM(B30))="SWALE",UPPER(TRIM(AI30))="PIPE"),AND(UPPER(TRIM(B30))="TRENCH",UPPER(TRIM(AI30))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK30" s="17">
+        <f>IF(A30="","",IF(OR(AND(UPPER(TRIM(B30))="SWALE",UPPER(TRIM(AI30))="PIPE"),AND(UPPER(TRIM(B30))="TRENCH",UPPER(TRIM(AI30))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL30" s="4">
+        <f>IF(A30="","",IF(E30="","TERMINAL",IF(OR(AND(UPPER(TRIM(B30))="SWALE",UPPER(TRIM(AI30))="PIPE"),AND(UPPER(TRIM(B30))="TRENCH",UPPER(TRIM(AI30))="PIPE")),IF(OR(AG30="",AJ30="",AK30=""),"INFO",IF(AND(AG30&gt;=AJ30,AG30&lt;=AK30),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10728,7 +11295,23 @@
         <v/>
       </c>
       <c r="AH31" s="4">
-        <f>IF(A31="","",IF(E31="","TERMINAL",IF(AG31="","INFO",IF(ABS(AG31)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A31="","",IF(E31="","TERMINAL",IF(OR(AND(UPPER(TRIM(B31))="SWALE",UPPER(TRIM(AI31))="PIPE"),AND(UPPER(TRIM(B31))="TRENCH",UPPER(TRIM(AI31))="PIPE")),IF(OR(AG31="",AJ31="",AK31=""),"INFO",IF(AND(AG31&gt;=AJ31,AG31&lt;=AK31),"OK","CHECK")),IF(AG31="","INFO",IF(ABS(AG31)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI31" s="17">
+        <f>IF(A31="","",IF(E31="","",IFERROR(INDEX($B$4:$B$204,MATCH(E31,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="17">
+        <f>IF(A31="","",IF(OR(AND(UPPER(TRIM(B31))="SWALE",UPPER(TRIM(AI31))="PIPE"),AND(UPPER(TRIM(B31))="TRENCH",UPPER(TRIM(AI31))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK31" s="17">
+        <f>IF(A31="","",IF(OR(AND(UPPER(TRIM(B31))="SWALE",UPPER(TRIM(AI31))="PIPE"),AND(UPPER(TRIM(B31))="TRENCH",UPPER(TRIM(AI31))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL31" s="4">
+        <f>IF(A31="","",IF(E31="","TERMINAL",IF(OR(AND(UPPER(TRIM(B31))="SWALE",UPPER(TRIM(AI31))="PIPE"),AND(UPPER(TRIM(B31))="TRENCH",UPPER(TRIM(AI31))="PIPE")),IF(OR(AG31="",AJ31="",AK31=""),"INFO",IF(AND(AG31&gt;=AJ31,AG31&lt;=AK31),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10823,7 +11406,23 @@
         <v/>
       </c>
       <c r="AH32" s="4">
-        <f>IF(A32="","",IF(E32="","TERMINAL",IF(AG32="","INFO",IF(ABS(AG32)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A32="","",IF(E32="","TERMINAL",IF(OR(AND(UPPER(TRIM(B32))="SWALE",UPPER(TRIM(AI32))="PIPE"),AND(UPPER(TRIM(B32))="TRENCH",UPPER(TRIM(AI32))="PIPE")),IF(OR(AG32="",AJ32="",AK32=""),"INFO",IF(AND(AG32&gt;=AJ32,AG32&lt;=AK32),"OK","CHECK")),IF(AG32="","INFO",IF(ABS(AG32)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI32" s="17">
+        <f>IF(A32="","",IF(E32="","",IFERROR(INDEX($B$4:$B$204,MATCH(E32,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="17">
+        <f>IF(A32="","",IF(OR(AND(UPPER(TRIM(B32))="SWALE",UPPER(TRIM(AI32))="PIPE"),AND(UPPER(TRIM(B32))="TRENCH",UPPER(TRIM(AI32))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK32" s="17">
+        <f>IF(A32="","",IF(OR(AND(UPPER(TRIM(B32))="SWALE",UPPER(TRIM(AI32))="PIPE"),AND(UPPER(TRIM(B32))="TRENCH",UPPER(TRIM(AI32))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL32" s="4">
+        <f>IF(A32="","",IF(E32="","TERMINAL",IF(OR(AND(UPPER(TRIM(B32))="SWALE",UPPER(TRIM(AI32))="PIPE"),AND(UPPER(TRIM(B32))="TRENCH",UPPER(TRIM(AI32))="PIPE")),IF(OR(AG32="",AJ32="",AK32=""),"INFO",IF(AND(AG32&gt;=AJ32,AG32&lt;=AK32),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -10918,7 +11517,23 @@
         <v/>
       </c>
       <c r="AH33" s="4">
-        <f>IF(A33="","",IF(E33="","TERMINAL",IF(AG33="","INFO",IF(ABS(AG33)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A33="","",IF(E33="","TERMINAL",IF(OR(AND(UPPER(TRIM(B33))="SWALE",UPPER(TRIM(AI33))="PIPE"),AND(UPPER(TRIM(B33))="TRENCH",UPPER(TRIM(AI33))="PIPE")),IF(OR(AG33="",AJ33="",AK33=""),"INFO",IF(AND(AG33&gt;=AJ33,AG33&lt;=AK33),"OK","CHECK")),IF(AG33="","INFO",IF(ABS(AG33)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI33" s="17">
+        <f>IF(A33="","",IF(E33="","",IFERROR(INDEX($B$4:$B$204,MATCH(E33,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="17">
+        <f>IF(A33="","",IF(OR(AND(UPPER(TRIM(B33))="SWALE",UPPER(TRIM(AI33))="PIPE"),AND(UPPER(TRIM(B33))="TRENCH",UPPER(TRIM(AI33))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK33" s="17">
+        <f>IF(A33="","",IF(OR(AND(UPPER(TRIM(B33))="SWALE",UPPER(TRIM(AI33))="PIPE"),AND(UPPER(TRIM(B33))="TRENCH",UPPER(TRIM(AI33))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL33" s="4">
+        <f>IF(A33="","",IF(E33="","TERMINAL",IF(OR(AND(UPPER(TRIM(B33))="SWALE",UPPER(TRIM(AI33))="PIPE"),AND(UPPER(TRIM(B33))="TRENCH",UPPER(TRIM(AI33))="PIPE")),IF(OR(AG33="",AJ33="",AK33=""),"INFO",IF(AND(AG33&gt;=AJ33,AG33&lt;=AK33),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11013,7 +11628,23 @@
         <v/>
       </c>
       <c r="AH34" s="4">
-        <f>IF(A34="","",IF(E34="","TERMINAL",IF(AG34="","INFO",IF(ABS(AG34)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A34="","",IF(E34="","TERMINAL",IF(OR(AND(UPPER(TRIM(B34))="SWALE",UPPER(TRIM(AI34))="PIPE"),AND(UPPER(TRIM(B34))="TRENCH",UPPER(TRIM(AI34))="PIPE")),IF(OR(AG34="",AJ34="",AK34=""),"INFO",IF(AND(AG34&gt;=AJ34,AG34&lt;=AK34),"OK","CHECK")),IF(AG34="","INFO",IF(ABS(AG34)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI34" s="17">
+        <f>IF(A34="","",IF(E34="","",IFERROR(INDEX($B$4:$B$204,MATCH(E34,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="17">
+        <f>IF(A34="","",IF(OR(AND(UPPER(TRIM(B34))="SWALE",UPPER(TRIM(AI34))="PIPE"),AND(UPPER(TRIM(B34))="TRENCH",UPPER(TRIM(AI34))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK34" s="17">
+        <f>IF(A34="","",IF(OR(AND(UPPER(TRIM(B34))="SWALE",UPPER(TRIM(AI34))="PIPE"),AND(UPPER(TRIM(B34))="TRENCH",UPPER(TRIM(AI34))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL34" s="4">
+        <f>IF(A34="","",IF(E34="","TERMINAL",IF(OR(AND(UPPER(TRIM(B34))="SWALE",UPPER(TRIM(AI34))="PIPE"),AND(UPPER(TRIM(B34))="TRENCH",UPPER(TRIM(AI34))="PIPE")),IF(OR(AG34="",AJ34="",AK34=""),"INFO",IF(AND(AG34&gt;=AJ34,AG34&lt;=AK34),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11108,7 +11739,23 @@
         <v/>
       </c>
       <c r="AH35" s="4">
-        <f>IF(A35="","",IF(E35="","TERMINAL",IF(AG35="","INFO",IF(ABS(AG35)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A35="","",IF(E35="","TERMINAL",IF(OR(AND(UPPER(TRIM(B35))="SWALE",UPPER(TRIM(AI35))="PIPE"),AND(UPPER(TRIM(B35))="TRENCH",UPPER(TRIM(AI35))="PIPE")),IF(OR(AG35="",AJ35="",AK35=""),"INFO",IF(AND(AG35&gt;=AJ35,AG35&lt;=AK35),"OK","CHECK")),IF(AG35="","INFO",IF(ABS(AG35)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI35" s="17">
+        <f>IF(A35="","",IF(E35="","",IFERROR(INDEX($B$4:$B$204,MATCH(E35,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="17">
+        <f>IF(A35="","",IF(OR(AND(UPPER(TRIM(B35))="SWALE",UPPER(TRIM(AI35))="PIPE"),AND(UPPER(TRIM(B35))="TRENCH",UPPER(TRIM(AI35))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK35" s="17">
+        <f>IF(A35="","",IF(OR(AND(UPPER(TRIM(B35))="SWALE",UPPER(TRIM(AI35))="PIPE"),AND(UPPER(TRIM(B35))="TRENCH",UPPER(TRIM(AI35))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL35" s="4">
+        <f>IF(A35="","",IF(E35="","TERMINAL",IF(OR(AND(UPPER(TRIM(B35))="SWALE",UPPER(TRIM(AI35))="PIPE"),AND(UPPER(TRIM(B35))="TRENCH",UPPER(TRIM(AI35))="PIPE")),IF(OR(AG35="",AJ35="",AK35=""),"INFO",IF(AND(AG35&gt;=AJ35,AG35&lt;=AK35),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11203,7 +11850,23 @@
         <v/>
       </c>
       <c r="AH36" s="4">
-        <f>IF(A36="","",IF(E36="","TERMINAL",IF(AG36="","INFO",IF(ABS(AG36)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A36="","",IF(E36="","TERMINAL",IF(OR(AND(UPPER(TRIM(B36))="SWALE",UPPER(TRIM(AI36))="PIPE"),AND(UPPER(TRIM(B36))="TRENCH",UPPER(TRIM(AI36))="PIPE")),IF(OR(AG36="",AJ36="",AK36=""),"INFO",IF(AND(AG36&gt;=AJ36,AG36&lt;=AK36),"OK","CHECK")),IF(AG36="","INFO",IF(ABS(AG36)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI36" s="17">
+        <f>IF(A36="","",IF(E36="","",IFERROR(INDEX($B$4:$B$204,MATCH(E36,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="17">
+        <f>IF(A36="","",IF(OR(AND(UPPER(TRIM(B36))="SWALE",UPPER(TRIM(AI36))="PIPE"),AND(UPPER(TRIM(B36))="TRENCH",UPPER(TRIM(AI36))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK36" s="17">
+        <f>IF(A36="","",IF(OR(AND(UPPER(TRIM(B36))="SWALE",UPPER(TRIM(AI36))="PIPE"),AND(UPPER(TRIM(B36))="TRENCH",UPPER(TRIM(AI36))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL36" s="4">
+        <f>IF(A36="","",IF(E36="","TERMINAL",IF(OR(AND(UPPER(TRIM(B36))="SWALE",UPPER(TRIM(AI36))="PIPE"),AND(UPPER(TRIM(B36))="TRENCH",UPPER(TRIM(AI36))="PIPE")),IF(OR(AG36="",AJ36="",AK36=""),"INFO",IF(AND(AG36&gt;=AJ36,AG36&lt;=AK36),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11298,7 +11961,23 @@
         <v/>
       </c>
       <c r="AH37" s="4">
-        <f>IF(A37="","",IF(E37="","TERMINAL",IF(AG37="","INFO",IF(ABS(AG37)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A37="","",IF(E37="","TERMINAL",IF(OR(AND(UPPER(TRIM(B37))="SWALE",UPPER(TRIM(AI37))="PIPE"),AND(UPPER(TRIM(B37))="TRENCH",UPPER(TRIM(AI37))="PIPE")),IF(OR(AG37="",AJ37="",AK37=""),"INFO",IF(AND(AG37&gt;=AJ37,AG37&lt;=AK37),"OK","CHECK")),IF(AG37="","INFO",IF(ABS(AG37)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI37" s="17">
+        <f>IF(A37="","",IF(E37="","",IFERROR(INDEX($B$4:$B$204,MATCH(E37,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="17">
+        <f>IF(A37="","",IF(OR(AND(UPPER(TRIM(B37))="SWALE",UPPER(TRIM(AI37))="PIPE"),AND(UPPER(TRIM(B37))="TRENCH",UPPER(TRIM(AI37))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK37" s="17">
+        <f>IF(A37="","",IF(OR(AND(UPPER(TRIM(B37))="SWALE",UPPER(TRIM(AI37))="PIPE"),AND(UPPER(TRIM(B37))="TRENCH",UPPER(TRIM(AI37))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL37" s="4">
+        <f>IF(A37="","",IF(E37="","TERMINAL",IF(OR(AND(UPPER(TRIM(B37))="SWALE",UPPER(TRIM(AI37))="PIPE"),AND(UPPER(TRIM(B37))="TRENCH",UPPER(TRIM(AI37))="PIPE")),IF(OR(AG37="",AJ37="",AK37=""),"INFO",IF(AND(AG37&gt;=AJ37,AG37&lt;=AK37),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11393,7 +12072,23 @@
         <v/>
       </c>
       <c r="AH38" s="4">
-        <f>IF(A38="","",IF(E38="","TERMINAL",IF(AG38="","INFO",IF(ABS(AG38)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A38="","",IF(E38="","TERMINAL",IF(OR(AND(UPPER(TRIM(B38))="SWALE",UPPER(TRIM(AI38))="PIPE"),AND(UPPER(TRIM(B38))="TRENCH",UPPER(TRIM(AI38))="PIPE")),IF(OR(AG38="",AJ38="",AK38=""),"INFO",IF(AND(AG38&gt;=AJ38,AG38&lt;=AK38),"OK","CHECK")),IF(AG38="","INFO",IF(ABS(AG38)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI38" s="17">
+        <f>IF(A38="","",IF(E38="","",IFERROR(INDEX($B$4:$B$204,MATCH(E38,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="17">
+        <f>IF(A38="","",IF(OR(AND(UPPER(TRIM(B38))="SWALE",UPPER(TRIM(AI38))="PIPE"),AND(UPPER(TRIM(B38))="TRENCH",UPPER(TRIM(AI38))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK38" s="17">
+        <f>IF(A38="","",IF(OR(AND(UPPER(TRIM(B38))="SWALE",UPPER(TRIM(AI38))="PIPE"),AND(UPPER(TRIM(B38))="TRENCH",UPPER(TRIM(AI38))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL38" s="4">
+        <f>IF(A38="","",IF(E38="","TERMINAL",IF(OR(AND(UPPER(TRIM(B38))="SWALE",UPPER(TRIM(AI38))="PIPE"),AND(UPPER(TRIM(B38))="TRENCH",UPPER(TRIM(AI38))="PIPE")),IF(OR(AG38="",AJ38="",AK38=""),"INFO",IF(AND(AG38&gt;=AJ38,AG38&lt;=AK38),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11488,7 +12183,23 @@
         <v/>
       </c>
       <c r="AH39" s="4">
-        <f>IF(A39="","",IF(E39="","TERMINAL",IF(AG39="","INFO",IF(ABS(AG39)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A39="","",IF(E39="","TERMINAL",IF(OR(AND(UPPER(TRIM(B39))="SWALE",UPPER(TRIM(AI39))="PIPE"),AND(UPPER(TRIM(B39))="TRENCH",UPPER(TRIM(AI39))="PIPE")),IF(OR(AG39="",AJ39="",AK39=""),"INFO",IF(AND(AG39&gt;=AJ39,AG39&lt;=AK39),"OK","CHECK")),IF(AG39="","INFO",IF(ABS(AG39)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI39" s="17">
+        <f>IF(A39="","",IF(E39="","",IFERROR(INDEX($B$4:$B$204,MATCH(E39,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="17">
+        <f>IF(A39="","",IF(OR(AND(UPPER(TRIM(B39))="SWALE",UPPER(TRIM(AI39))="PIPE"),AND(UPPER(TRIM(B39))="TRENCH",UPPER(TRIM(AI39))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK39" s="17">
+        <f>IF(A39="","",IF(OR(AND(UPPER(TRIM(B39))="SWALE",UPPER(TRIM(AI39))="PIPE"),AND(UPPER(TRIM(B39))="TRENCH",UPPER(TRIM(AI39))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL39" s="4">
+        <f>IF(A39="","",IF(E39="","TERMINAL",IF(OR(AND(UPPER(TRIM(B39))="SWALE",UPPER(TRIM(AI39))="PIPE"),AND(UPPER(TRIM(B39))="TRENCH",UPPER(TRIM(AI39))="PIPE")),IF(OR(AG39="",AJ39="",AK39=""),"INFO",IF(AND(AG39&gt;=AJ39,AG39&lt;=AK39),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11583,7 +12294,23 @@
         <v/>
       </c>
       <c r="AH40" s="4">
-        <f>IF(A40="","",IF(E40="","TERMINAL",IF(AG40="","INFO",IF(ABS(AG40)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A40="","",IF(E40="","TERMINAL",IF(OR(AND(UPPER(TRIM(B40))="SWALE",UPPER(TRIM(AI40))="PIPE"),AND(UPPER(TRIM(B40))="TRENCH",UPPER(TRIM(AI40))="PIPE")),IF(OR(AG40="",AJ40="",AK40=""),"INFO",IF(AND(AG40&gt;=AJ40,AG40&lt;=AK40),"OK","CHECK")),IF(AG40="","INFO",IF(ABS(AG40)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI40" s="17">
+        <f>IF(A40="","",IF(E40="","",IFERROR(INDEX($B$4:$B$204,MATCH(E40,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="17">
+        <f>IF(A40="","",IF(OR(AND(UPPER(TRIM(B40))="SWALE",UPPER(TRIM(AI40))="PIPE"),AND(UPPER(TRIM(B40))="TRENCH",UPPER(TRIM(AI40))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK40" s="17">
+        <f>IF(A40="","",IF(OR(AND(UPPER(TRIM(B40))="SWALE",UPPER(TRIM(AI40))="PIPE"),AND(UPPER(TRIM(B40))="TRENCH",UPPER(TRIM(AI40))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL40" s="4">
+        <f>IF(A40="","",IF(E40="","TERMINAL",IF(OR(AND(UPPER(TRIM(B40))="SWALE",UPPER(TRIM(AI40))="PIPE"),AND(UPPER(TRIM(B40))="TRENCH",UPPER(TRIM(AI40))="PIPE")),IF(OR(AG40="",AJ40="",AK40=""),"INFO",IF(AND(AG40&gt;=AJ40,AG40&lt;=AK40),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11678,7 +12405,23 @@
         <v/>
       </c>
       <c r="AH41" s="4">
-        <f>IF(A41="","",IF(E41="","TERMINAL",IF(AG41="","INFO",IF(ABS(AG41)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A41="","",IF(E41="","TERMINAL",IF(OR(AND(UPPER(TRIM(B41))="SWALE",UPPER(TRIM(AI41))="PIPE"),AND(UPPER(TRIM(B41))="TRENCH",UPPER(TRIM(AI41))="PIPE")),IF(OR(AG41="",AJ41="",AK41=""),"INFO",IF(AND(AG41&gt;=AJ41,AG41&lt;=AK41),"OK","CHECK")),IF(AG41="","INFO",IF(ABS(AG41)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI41" s="17">
+        <f>IF(A41="","",IF(E41="","",IFERROR(INDEX($B$4:$B$204,MATCH(E41,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="17">
+        <f>IF(A41="","",IF(OR(AND(UPPER(TRIM(B41))="SWALE",UPPER(TRIM(AI41))="PIPE"),AND(UPPER(TRIM(B41))="TRENCH",UPPER(TRIM(AI41))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK41" s="17">
+        <f>IF(A41="","",IF(OR(AND(UPPER(TRIM(B41))="SWALE",UPPER(TRIM(AI41))="PIPE"),AND(UPPER(TRIM(B41))="TRENCH",UPPER(TRIM(AI41))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL41" s="4">
+        <f>IF(A41="","",IF(E41="","TERMINAL",IF(OR(AND(UPPER(TRIM(B41))="SWALE",UPPER(TRIM(AI41))="PIPE"),AND(UPPER(TRIM(B41))="TRENCH",UPPER(TRIM(AI41))="PIPE")),IF(OR(AG41="",AJ41="",AK41=""),"INFO",IF(AND(AG41&gt;=AJ41,AG41&lt;=AK41),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11773,7 +12516,23 @@
         <v/>
       </c>
       <c r="AH42" s="4">
-        <f>IF(A42="","",IF(E42="","TERMINAL",IF(AG42="","INFO",IF(ABS(AG42)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A42="","",IF(E42="","TERMINAL",IF(OR(AND(UPPER(TRIM(B42))="SWALE",UPPER(TRIM(AI42))="PIPE"),AND(UPPER(TRIM(B42))="TRENCH",UPPER(TRIM(AI42))="PIPE")),IF(OR(AG42="",AJ42="",AK42=""),"INFO",IF(AND(AG42&gt;=AJ42,AG42&lt;=AK42),"OK","CHECK")),IF(AG42="","INFO",IF(ABS(AG42)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI42" s="17">
+        <f>IF(A42="","",IF(E42="","",IFERROR(INDEX($B$4:$B$204,MATCH(E42,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ42" s="17">
+        <f>IF(A42="","",IF(OR(AND(UPPER(TRIM(B42))="SWALE",UPPER(TRIM(AI42))="PIPE"),AND(UPPER(TRIM(B42))="TRENCH",UPPER(TRIM(AI42))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK42" s="17">
+        <f>IF(A42="","",IF(OR(AND(UPPER(TRIM(B42))="SWALE",UPPER(TRIM(AI42))="PIPE"),AND(UPPER(TRIM(B42))="TRENCH",UPPER(TRIM(AI42))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL42" s="4">
+        <f>IF(A42="","",IF(E42="","TERMINAL",IF(OR(AND(UPPER(TRIM(B42))="SWALE",UPPER(TRIM(AI42))="PIPE"),AND(UPPER(TRIM(B42))="TRENCH",UPPER(TRIM(AI42))="PIPE")),IF(OR(AG42="",AJ42="",AK42=""),"INFO",IF(AND(AG42&gt;=AJ42,AG42&lt;=AK42),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11868,7 +12627,23 @@
         <v/>
       </c>
       <c r="AH43" s="4">
-        <f>IF(A43="","",IF(E43="","TERMINAL",IF(AG43="","INFO",IF(ABS(AG43)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A43="","",IF(E43="","TERMINAL",IF(OR(AND(UPPER(TRIM(B43))="SWALE",UPPER(TRIM(AI43))="PIPE"),AND(UPPER(TRIM(B43))="TRENCH",UPPER(TRIM(AI43))="PIPE")),IF(OR(AG43="",AJ43="",AK43=""),"INFO",IF(AND(AG43&gt;=AJ43,AG43&lt;=AK43),"OK","CHECK")),IF(AG43="","INFO",IF(ABS(AG43)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI43" s="17">
+        <f>IF(A43="","",IF(E43="","",IFERROR(INDEX($B$4:$B$204,MATCH(E43,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ43" s="17">
+        <f>IF(A43="","",IF(OR(AND(UPPER(TRIM(B43))="SWALE",UPPER(TRIM(AI43))="PIPE"),AND(UPPER(TRIM(B43))="TRENCH",UPPER(TRIM(AI43))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK43" s="17">
+        <f>IF(A43="","",IF(OR(AND(UPPER(TRIM(B43))="SWALE",UPPER(TRIM(AI43))="PIPE"),AND(UPPER(TRIM(B43))="TRENCH",UPPER(TRIM(AI43))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL43" s="4">
+        <f>IF(A43="","",IF(E43="","TERMINAL",IF(OR(AND(UPPER(TRIM(B43))="SWALE",UPPER(TRIM(AI43))="PIPE"),AND(UPPER(TRIM(B43))="TRENCH",UPPER(TRIM(AI43))="PIPE")),IF(OR(AG43="",AJ43="",AK43=""),"INFO",IF(AND(AG43&gt;=AJ43,AG43&lt;=AK43),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -11963,7 +12738,23 @@
         <v/>
       </c>
       <c r="AH44" s="4">
-        <f>IF(A44="","",IF(E44="","TERMINAL",IF(AG44="","INFO",IF(ABS(AG44)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A44="","",IF(E44="","TERMINAL",IF(OR(AND(UPPER(TRIM(B44))="SWALE",UPPER(TRIM(AI44))="PIPE"),AND(UPPER(TRIM(B44))="TRENCH",UPPER(TRIM(AI44))="PIPE")),IF(OR(AG44="",AJ44="",AK44=""),"INFO",IF(AND(AG44&gt;=AJ44,AG44&lt;=AK44),"OK","CHECK")),IF(AG44="","INFO",IF(ABS(AG44)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI44" s="17">
+        <f>IF(A44="","",IF(E44="","",IFERROR(INDEX($B$4:$B$204,MATCH(E44,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="17">
+        <f>IF(A44="","",IF(OR(AND(UPPER(TRIM(B44))="SWALE",UPPER(TRIM(AI44))="PIPE"),AND(UPPER(TRIM(B44))="TRENCH",UPPER(TRIM(AI44))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK44" s="17">
+        <f>IF(A44="","",IF(OR(AND(UPPER(TRIM(B44))="SWALE",UPPER(TRIM(AI44))="PIPE"),AND(UPPER(TRIM(B44))="TRENCH",UPPER(TRIM(AI44))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL44" s="4">
+        <f>IF(A44="","",IF(E44="","TERMINAL",IF(OR(AND(UPPER(TRIM(B44))="SWALE",UPPER(TRIM(AI44))="PIPE"),AND(UPPER(TRIM(B44))="TRENCH",UPPER(TRIM(AI44))="PIPE")),IF(OR(AG44="",AJ44="",AK44=""),"INFO",IF(AND(AG44&gt;=AJ44,AG44&lt;=AK44),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12058,7 +12849,23 @@
         <v/>
       </c>
       <c r="AH45" s="4">
-        <f>IF(A45="","",IF(E45="","TERMINAL",IF(AG45="","INFO",IF(ABS(AG45)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A45="","",IF(E45="","TERMINAL",IF(OR(AND(UPPER(TRIM(B45))="SWALE",UPPER(TRIM(AI45))="PIPE"),AND(UPPER(TRIM(B45))="TRENCH",UPPER(TRIM(AI45))="PIPE")),IF(OR(AG45="",AJ45="",AK45=""),"INFO",IF(AND(AG45&gt;=AJ45,AG45&lt;=AK45),"OK","CHECK")),IF(AG45="","INFO",IF(ABS(AG45)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI45" s="17">
+        <f>IF(A45="","",IF(E45="","",IFERROR(INDEX($B$4:$B$204,MATCH(E45,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ45" s="17">
+        <f>IF(A45="","",IF(OR(AND(UPPER(TRIM(B45))="SWALE",UPPER(TRIM(AI45))="PIPE"),AND(UPPER(TRIM(B45))="TRENCH",UPPER(TRIM(AI45))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK45" s="17">
+        <f>IF(A45="","",IF(OR(AND(UPPER(TRIM(B45))="SWALE",UPPER(TRIM(AI45))="PIPE"),AND(UPPER(TRIM(B45))="TRENCH",UPPER(TRIM(AI45))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL45" s="4">
+        <f>IF(A45="","",IF(E45="","TERMINAL",IF(OR(AND(UPPER(TRIM(B45))="SWALE",UPPER(TRIM(AI45))="PIPE"),AND(UPPER(TRIM(B45))="TRENCH",UPPER(TRIM(AI45))="PIPE")),IF(OR(AG45="",AJ45="",AK45=""),"INFO",IF(AND(AG45&gt;=AJ45,AG45&lt;=AK45),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12153,7 +12960,23 @@
         <v/>
       </c>
       <c r="AH46" s="4">
-        <f>IF(A46="","",IF(E46="","TERMINAL",IF(AG46="","INFO",IF(ABS(AG46)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A46="","",IF(E46="","TERMINAL",IF(OR(AND(UPPER(TRIM(B46))="SWALE",UPPER(TRIM(AI46))="PIPE"),AND(UPPER(TRIM(B46))="TRENCH",UPPER(TRIM(AI46))="PIPE")),IF(OR(AG46="",AJ46="",AK46=""),"INFO",IF(AND(AG46&gt;=AJ46,AG46&lt;=AK46),"OK","CHECK")),IF(AG46="","INFO",IF(ABS(AG46)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI46" s="17">
+        <f>IF(A46="","",IF(E46="","",IFERROR(INDEX($B$4:$B$204,MATCH(E46,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ46" s="17">
+        <f>IF(A46="","",IF(OR(AND(UPPER(TRIM(B46))="SWALE",UPPER(TRIM(AI46))="PIPE"),AND(UPPER(TRIM(B46))="TRENCH",UPPER(TRIM(AI46))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK46" s="17">
+        <f>IF(A46="","",IF(OR(AND(UPPER(TRIM(B46))="SWALE",UPPER(TRIM(AI46))="PIPE"),AND(UPPER(TRIM(B46))="TRENCH",UPPER(TRIM(AI46))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL46" s="4">
+        <f>IF(A46="","",IF(E46="","TERMINAL",IF(OR(AND(UPPER(TRIM(B46))="SWALE",UPPER(TRIM(AI46))="PIPE"),AND(UPPER(TRIM(B46))="TRENCH",UPPER(TRIM(AI46))="PIPE")),IF(OR(AG46="",AJ46="",AK46=""),"INFO",IF(AND(AG46&gt;=AJ46,AG46&lt;=AK46),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12248,7 +13071,23 @@
         <v/>
       </c>
       <c r="AH47" s="4">
-        <f>IF(A47="","",IF(E47="","TERMINAL",IF(AG47="","INFO",IF(ABS(AG47)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A47="","",IF(E47="","TERMINAL",IF(OR(AND(UPPER(TRIM(B47))="SWALE",UPPER(TRIM(AI47))="PIPE"),AND(UPPER(TRIM(B47))="TRENCH",UPPER(TRIM(AI47))="PIPE")),IF(OR(AG47="",AJ47="",AK47=""),"INFO",IF(AND(AG47&gt;=AJ47,AG47&lt;=AK47),"OK","CHECK")),IF(AG47="","INFO",IF(ABS(AG47)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI47" s="17">
+        <f>IF(A47="","",IF(E47="","",IFERROR(INDEX($B$4:$B$204,MATCH(E47,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ47" s="17">
+        <f>IF(A47="","",IF(OR(AND(UPPER(TRIM(B47))="SWALE",UPPER(TRIM(AI47))="PIPE"),AND(UPPER(TRIM(B47))="TRENCH",UPPER(TRIM(AI47))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK47" s="17">
+        <f>IF(A47="","",IF(OR(AND(UPPER(TRIM(B47))="SWALE",UPPER(TRIM(AI47))="PIPE"),AND(UPPER(TRIM(B47))="TRENCH",UPPER(TRIM(AI47))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL47" s="4">
+        <f>IF(A47="","",IF(E47="","TERMINAL",IF(OR(AND(UPPER(TRIM(B47))="SWALE",UPPER(TRIM(AI47))="PIPE"),AND(UPPER(TRIM(B47))="TRENCH",UPPER(TRIM(AI47))="PIPE")),IF(OR(AG47="",AJ47="",AK47=""),"INFO",IF(AND(AG47&gt;=AJ47,AG47&lt;=AK47),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12343,7 +13182,23 @@
         <v/>
       </c>
       <c r="AH48" s="4">
-        <f>IF(A48="","",IF(E48="","TERMINAL",IF(AG48="","INFO",IF(ABS(AG48)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A48="","",IF(E48="","TERMINAL",IF(OR(AND(UPPER(TRIM(B48))="SWALE",UPPER(TRIM(AI48))="PIPE"),AND(UPPER(TRIM(B48))="TRENCH",UPPER(TRIM(AI48))="PIPE")),IF(OR(AG48="",AJ48="",AK48=""),"INFO",IF(AND(AG48&gt;=AJ48,AG48&lt;=AK48),"OK","CHECK")),IF(AG48="","INFO",IF(ABS(AG48)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI48" s="17">
+        <f>IF(A48="","",IF(E48="","",IFERROR(INDEX($B$4:$B$204,MATCH(E48,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ48" s="17">
+        <f>IF(A48="","",IF(OR(AND(UPPER(TRIM(B48))="SWALE",UPPER(TRIM(AI48))="PIPE"),AND(UPPER(TRIM(B48))="TRENCH",UPPER(TRIM(AI48))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK48" s="17">
+        <f>IF(A48="","",IF(OR(AND(UPPER(TRIM(B48))="SWALE",UPPER(TRIM(AI48))="PIPE"),AND(UPPER(TRIM(B48))="TRENCH",UPPER(TRIM(AI48))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL48" s="4">
+        <f>IF(A48="","",IF(E48="","TERMINAL",IF(OR(AND(UPPER(TRIM(B48))="SWALE",UPPER(TRIM(AI48))="PIPE"),AND(UPPER(TRIM(B48))="TRENCH",UPPER(TRIM(AI48))="PIPE")),IF(OR(AG48="",AJ48="",AK48=""),"INFO",IF(AND(AG48&gt;=AJ48,AG48&lt;=AK48),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12438,7 +13293,23 @@
         <v/>
       </c>
       <c r="AH49" s="4">
-        <f>IF(A49="","",IF(E49="","TERMINAL",IF(AG49="","INFO",IF(ABS(AG49)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A49="","",IF(E49="","TERMINAL",IF(OR(AND(UPPER(TRIM(B49))="SWALE",UPPER(TRIM(AI49))="PIPE"),AND(UPPER(TRIM(B49))="TRENCH",UPPER(TRIM(AI49))="PIPE")),IF(OR(AG49="",AJ49="",AK49=""),"INFO",IF(AND(AG49&gt;=AJ49,AG49&lt;=AK49),"OK","CHECK")),IF(AG49="","INFO",IF(ABS(AG49)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI49" s="17">
+        <f>IF(A49="","",IF(E49="","",IFERROR(INDEX($B$4:$B$204,MATCH(E49,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ49" s="17">
+        <f>IF(A49="","",IF(OR(AND(UPPER(TRIM(B49))="SWALE",UPPER(TRIM(AI49))="PIPE"),AND(UPPER(TRIM(B49))="TRENCH",UPPER(TRIM(AI49))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK49" s="17">
+        <f>IF(A49="","",IF(OR(AND(UPPER(TRIM(B49))="SWALE",UPPER(TRIM(AI49))="PIPE"),AND(UPPER(TRIM(B49))="TRENCH",UPPER(TRIM(AI49))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL49" s="4">
+        <f>IF(A49="","",IF(E49="","TERMINAL",IF(OR(AND(UPPER(TRIM(B49))="SWALE",UPPER(TRIM(AI49))="PIPE"),AND(UPPER(TRIM(B49))="TRENCH",UPPER(TRIM(AI49))="PIPE")),IF(OR(AG49="",AJ49="",AK49=""),"INFO",IF(AND(AG49&gt;=AJ49,AG49&lt;=AK49),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12533,7 +13404,23 @@
         <v/>
       </c>
       <c r="AH50" s="4">
-        <f>IF(A50="","",IF(E50="","TERMINAL",IF(AG50="","INFO",IF(ABS(AG50)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A50="","",IF(E50="","TERMINAL",IF(OR(AND(UPPER(TRIM(B50))="SWALE",UPPER(TRIM(AI50))="PIPE"),AND(UPPER(TRIM(B50))="TRENCH",UPPER(TRIM(AI50))="PIPE")),IF(OR(AG50="",AJ50="",AK50=""),"INFO",IF(AND(AG50&gt;=AJ50,AG50&lt;=AK50),"OK","CHECK")),IF(AG50="","INFO",IF(ABS(AG50)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI50" s="17">
+        <f>IF(A50="","",IF(E50="","",IFERROR(INDEX($B$4:$B$204,MATCH(E50,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ50" s="17">
+        <f>IF(A50="","",IF(OR(AND(UPPER(TRIM(B50))="SWALE",UPPER(TRIM(AI50))="PIPE"),AND(UPPER(TRIM(B50))="TRENCH",UPPER(TRIM(AI50))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK50" s="17">
+        <f>IF(A50="","",IF(OR(AND(UPPER(TRIM(B50))="SWALE",UPPER(TRIM(AI50))="PIPE"),AND(UPPER(TRIM(B50))="TRENCH",UPPER(TRIM(AI50))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL50" s="4">
+        <f>IF(A50="","",IF(E50="","TERMINAL",IF(OR(AND(UPPER(TRIM(B50))="SWALE",UPPER(TRIM(AI50))="PIPE"),AND(UPPER(TRIM(B50))="TRENCH",UPPER(TRIM(AI50))="PIPE")),IF(OR(AG50="",AJ50="",AK50=""),"INFO",IF(AND(AG50&gt;=AJ50,AG50&lt;=AK50),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12628,7 +13515,23 @@
         <v/>
       </c>
       <c r="AH51" s="4">
-        <f>IF(A51="","",IF(E51="","TERMINAL",IF(AG51="","INFO",IF(ABS(AG51)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A51="","",IF(E51="","TERMINAL",IF(OR(AND(UPPER(TRIM(B51))="SWALE",UPPER(TRIM(AI51))="PIPE"),AND(UPPER(TRIM(B51))="TRENCH",UPPER(TRIM(AI51))="PIPE")),IF(OR(AG51="",AJ51="",AK51=""),"INFO",IF(AND(AG51&gt;=AJ51,AG51&lt;=AK51),"OK","CHECK")),IF(AG51="","INFO",IF(ABS(AG51)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI51" s="17">
+        <f>IF(A51="","",IF(E51="","",IFERROR(INDEX($B$4:$B$204,MATCH(E51,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="17">
+        <f>IF(A51="","",IF(OR(AND(UPPER(TRIM(B51))="SWALE",UPPER(TRIM(AI51))="PIPE"),AND(UPPER(TRIM(B51))="TRENCH",UPPER(TRIM(AI51))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK51" s="17">
+        <f>IF(A51="","",IF(OR(AND(UPPER(TRIM(B51))="SWALE",UPPER(TRIM(AI51))="PIPE"),AND(UPPER(TRIM(B51))="TRENCH",UPPER(TRIM(AI51))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL51" s="4">
+        <f>IF(A51="","",IF(E51="","TERMINAL",IF(OR(AND(UPPER(TRIM(B51))="SWALE",UPPER(TRIM(AI51))="PIPE"),AND(UPPER(TRIM(B51))="TRENCH",UPPER(TRIM(AI51))="PIPE")),IF(OR(AG51="",AJ51="",AK51=""),"INFO",IF(AND(AG51&gt;=AJ51,AG51&lt;=AK51),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12723,7 +13626,23 @@
         <v/>
       </c>
       <c r="AH52" s="4">
-        <f>IF(A52="","",IF(E52="","TERMINAL",IF(AG52="","INFO",IF(ABS(AG52)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A52="","",IF(E52="","TERMINAL",IF(OR(AND(UPPER(TRIM(B52))="SWALE",UPPER(TRIM(AI52))="PIPE"),AND(UPPER(TRIM(B52))="TRENCH",UPPER(TRIM(AI52))="PIPE")),IF(OR(AG52="",AJ52="",AK52=""),"INFO",IF(AND(AG52&gt;=AJ52,AG52&lt;=AK52),"OK","CHECK")),IF(AG52="","INFO",IF(ABS(AG52)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI52" s="17">
+        <f>IF(A52="","",IF(E52="","",IFERROR(INDEX($B$4:$B$204,MATCH(E52,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ52" s="17">
+        <f>IF(A52="","",IF(OR(AND(UPPER(TRIM(B52))="SWALE",UPPER(TRIM(AI52))="PIPE"),AND(UPPER(TRIM(B52))="TRENCH",UPPER(TRIM(AI52))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK52" s="17">
+        <f>IF(A52="","",IF(OR(AND(UPPER(TRIM(B52))="SWALE",UPPER(TRIM(AI52))="PIPE"),AND(UPPER(TRIM(B52))="TRENCH",UPPER(TRIM(AI52))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL52" s="4">
+        <f>IF(A52="","",IF(E52="","TERMINAL",IF(OR(AND(UPPER(TRIM(B52))="SWALE",UPPER(TRIM(AI52))="PIPE"),AND(UPPER(TRIM(B52))="TRENCH",UPPER(TRIM(AI52))="PIPE")),IF(OR(AG52="",AJ52="",AK52=""),"INFO",IF(AND(AG52&gt;=AJ52,AG52&lt;=AK52),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12818,7 +13737,23 @@
         <v/>
       </c>
       <c r="AH53" s="4">
-        <f>IF(A53="","",IF(E53="","TERMINAL",IF(AG53="","INFO",IF(ABS(AG53)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A53="","",IF(E53="","TERMINAL",IF(OR(AND(UPPER(TRIM(B53))="SWALE",UPPER(TRIM(AI53))="PIPE"),AND(UPPER(TRIM(B53))="TRENCH",UPPER(TRIM(AI53))="PIPE")),IF(OR(AG53="",AJ53="",AK53=""),"INFO",IF(AND(AG53&gt;=AJ53,AG53&lt;=AK53),"OK","CHECK")),IF(AG53="","INFO",IF(ABS(AG53)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI53" s="17">
+        <f>IF(A53="","",IF(E53="","",IFERROR(INDEX($B$4:$B$204,MATCH(E53,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ53" s="17">
+        <f>IF(A53="","",IF(OR(AND(UPPER(TRIM(B53))="SWALE",UPPER(TRIM(AI53))="PIPE"),AND(UPPER(TRIM(B53))="TRENCH",UPPER(TRIM(AI53))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK53" s="17">
+        <f>IF(A53="","",IF(OR(AND(UPPER(TRIM(B53))="SWALE",UPPER(TRIM(AI53))="PIPE"),AND(UPPER(TRIM(B53))="TRENCH",UPPER(TRIM(AI53))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL53" s="4">
+        <f>IF(A53="","",IF(E53="","TERMINAL",IF(OR(AND(UPPER(TRIM(B53))="SWALE",UPPER(TRIM(AI53))="PIPE"),AND(UPPER(TRIM(B53))="TRENCH",UPPER(TRIM(AI53))="PIPE")),IF(OR(AG53="",AJ53="",AK53=""),"INFO",IF(AND(AG53&gt;=AJ53,AG53&lt;=AK53),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -12913,7 +13848,23 @@
         <v/>
       </c>
       <c r="AH54" s="4">
-        <f>IF(A54="","",IF(E54="","TERMINAL",IF(AG54="","INFO",IF(ABS(AG54)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A54="","",IF(E54="","TERMINAL",IF(OR(AND(UPPER(TRIM(B54))="SWALE",UPPER(TRIM(AI54))="PIPE"),AND(UPPER(TRIM(B54))="TRENCH",UPPER(TRIM(AI54))="PIPE")),IF(OR(AG54="",AJ54="",AK54=""),"INFO",IF(AND(AG54&gt;=AJ54,AG54&lt;=AK54),"OK","CHECK")),IF(AG54="","INFO",IF(ABS(AG54)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI54" s="17">
+        <f>IF(A54="","",IF(E54="","",IFERROR(INDEX($B$4:$B$204,MATCH(E54,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ54" s="17">
+        <f>IF(A54="","",IF(OR(AND(UPPER(TRIM(B54))="SWALE",UPPER(TRIM(AI54))="PIPE"),AND(UPPER(TRIM(B54))="TRENCH",UPPER(TRIM(AI54))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK54" s="17">
+        <f>IF(A54="","",IF(OR(AND(UPPER(TRIM(B54))="SWALE",UPPER(TRIM(AI54))="PIPE"),AND(UPPER(TRIM(B54))="TRENCH",UPPER(TRIM(AI54))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL54" s="4">
+        <f>IF(A54="","",IF(E54="","TERMINAL",IF(OR(AND(UPPER(TRIM(B54))="SWALE",UPPER(TRIM(AI54))="PIPE"),AND(UPPER(TRIM(B54))="TRENCH",UPPER(TRIM(AI54))="PIPE")),IF(OR(AG54="",AJ54="",AK54=""),"INFO",IF(AND(AG54&gt;=AJ54,AG54&lt;=AK54),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13008,7 +13959,23 @@
         <v/>
       </c>
       <c r="AH55" s="4">
-        <f>IF(A55="","",IF(E55="","TERMINAL",IF(AG55="","INFO",IF(ABS(AG55)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A55="","",IF(E55="","TERMINAL",IF(OR(AND(UPPER(TRIM(B55))="SWALE",UPPER(TRIM(AI55))="PIPE"),AND(UPPER(TRIM(B55))="TRENCH",UPPER(TRIM(AI55))="PIPE")),IF(OR(AG55="",AJ55="",AK55=""),"INFO",IF(AND(AG55&gt;=AJ55,AG55&lt;=AK55),"OK","CHECK")),IF(AG55="","INFO",IF(ABS(AG55)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI55" s="17">
+        <f>IF(A55="","",IF(E55="","",IFERROR(INDEX($B$4:$B$204,MATCH(E55,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ55" s="17">
+        <f>IF(A55="","",IF(OR(AND(UPPER(TRIM(B55))="SWALE",UPPER(TRIM(AI55))="PIPE"),AND(UPPER(TRIM(B55))="TRENCH",UPPER(TRIM(AI55))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK55" s="17">
+        <f>IF(A55="","",IF(OR(AND(UPPER(TRIM(B55))="SWALE",UPPER(TRIM(AI55))="PIPE"),AND(UPPER(TRIM(B55))="TRENCH",UPPER(TRIM(AI55))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL55" s="4">
+        <f>IF(A55="","",IF(E55="","TERMINAL",IF(OR(AND(UPPER(TRIM(B55))="SWALE",UPPER(TRIM(AI55))="PIPE"),AND(UPPER(TRIM(B55))="TRENCH",UPPER(TRIM(AI55))="PIPE")),IF(OR(AG55="",AJ55="",AK55=""),"INFO",IF(AND(AG55&gt;=AJ55,AG55&lt;=AK55),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13103,7 +14070,23 @@
         <v/>
       </c>
       <c r="AH56" s="4">
-        <f>IF(A56="","",IF(E56="","TERMINAL",IF(AG56="","INFO",IF(ABS(AG56)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A56="","",IF(E56="","TERMINAL",IF(OR(AND(UPPER(TRIM(B56))="SWALE",UPPER(TRIM(AI56))="PIPE"),AND(UPPER(TRIM(B56))="TRENCH",UPPER(TRIM(AI56))="PIPE")),IF(OR(AG56="",AJ56="",AK56=""),"INFO",IF(AND(AG56&gt;=AJ56,AG56&lt;=AK56),"OK","CHECK")),IF(AG56="","INFO",IF(ABS(AG56)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI56" s="17">
+        <f>IF(A56="","",IF(E56="","",IFERROR(INDEX($B$4:$B$204,MATCH(E56,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ56" s="17">
+        <f>IF(A56="","",IF(OR(AND(UPPER(TRIM(B56))="SWALE",UPPER(TRIM(AI56))="PIPE"),AND(UPPER(TRIM(B56))="TRENCH",UPPER(TRIM(AI56))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK56" s="17">
+        <f>IF(A56="","",IF(OR(AND(UPPER(TRIM(B56))="SWALE",UPPER(TRIM(AI56))="PIPE"),AND(UPPER(TRIM(B56))="TRENCH",UPPER(TRIM(AI56))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL56" s="4">
+        <f>IF(A56="","",IF(E56="","TERMINAL",IF(OR(AND(UPPER(TRIM(B56))="SWALE",UPPER(TRIM(AI56))="PIPE"),AND(UPPER(TRIM(B56))="TRENCH",UPPER(TRIM(AI56))="PIPE")),IF(OR(AG56="",AJ56="",AK56=""),"INFO",IF(AND(AG56&gt;=AJ56,AG56&lt;=AK56),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13198,7 +14181,23 @@
         <v/>
       </c>
       <c r="AH57" s="4">
-        <f>IF(A57="","",IF(E57="","TERMINAL",IF(AG57="","INFO",IF(ABS(AG57)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A57="","",IF(E57="","TERMINAL",IF(OR(AND(UPPER(TRIM(B57))="SWALE",UPPER(TRIM(AI57))="PIPE"),AND(UPPER(TRIM(B57))="TRENCH",UPPER(TRIM(AI57))="PIPE")),IF(OR(AG57="",AJ57="",AK57=""),"INFO",IF(AND(AG57&gt;=AJ57,AG57&lt;=AK57),"OK","CHECK")),IF(AG57="","INFO",IF(ABS(AG57)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI57" s="17">
+        <f>IF(A57="","",IF(E57="","",IFERROR(INDEX($B$4:$B$204,MATCH(E57,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ57" s="17">
+        <f>IF(A57="","",IF(OR(AND(UPPER(TRIM(B57))="SWALE",UPPER(TRIM(AI57))="PIPE"),AND(UPPER(TRIM(B57))="TRENCH",UPPER(TRIM(AI57))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK57" s="17">
+        <f>IF(A57="","",IF(OR(AND(UPPER(TRIM(B57))="SWALE",UPPER(TRIM(AI57))="PIPE"),AND(UPPER(TRIM(B57))="TRENCH",UPPER(TRIM(AI57))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL57" s="4">
+        <f>IF(A57="","",IF(E57="","TERMINAL",IF(OR(AND(UPPER(TRIM(B57))="SWALE",UPPER(TRIM(AI57))="PIPE"),AND(UPPER(TRIM(B57))="TRENCH",UPPER(TRIM(AI57))="PIPE")),IF(OR(AG57="",AJ57="",AK57=""),"INFO",IF(AND(AG57&gt;=AJ57,AG57&lt;=AK57),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13293,7 +14292,23 @@
         <v/>
       </c>
       <c r="AH58" s="4">
-        <f>IF(A58="","",IF(E58="","TERMINAL",IF(AG58="","INFO",IF(ABS(AG58)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A58="","",IF(E58="","TERMINAL",IF(OR(AND(UPPER(TRIM(B58))="SWALE",UPPER(TRIM(AI58))="PIPE"),AND(UPPER(TRIM(B58))="TRENCH",UPPER(TRIM(AI58))="PIPE")),IF(OR(AG58="",AJ58="",AK58=""),"INFO",IF(AND(AG58&gt;=AJ58,AG58&lt;=AK58),"OK","CHECK")),IF(AG58="","INFO",IF(ABS(AG58)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI58" s="17">
+        <f>IF(A58="","",IF(E58="","",IFERROR(INDEX($B$4:$B$204,MATCH(E58,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ58" s="17">
+        <f>IF(A58="","",IF(OR(AND(UPPER(TRIM(B58))="SWALE",UPPER(TRIM(AI58))="PIPE"),AND(UPPER(TRIM(B58))="TRENCH",UPPER(TRIM(AI58))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK58" s="17">
+        <f>IF(A58="","",IF(OR(AND(UPPER(TRIM(B58))="SWALE",UPPER(TRIM(AI58))="PIPE"),AND(UPPER(TRIM(B58))="TRENCH",UPPER(TRIM(AI58))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL58" s="4">
+        <f>IF(A58="","",IF(E58="","TERMINAL",IF(OR(AND(UPPER(TRIM(B58))="SWALE",UPPER(TRIM(AI58))="PIPE"),AND(UPPER(TRIM(B58))="TRENCH",UPPER(TRIM(AI58))="PIPE")),IF(OR(AG58="",AJ58="",AK58=""),"INFO",IF(AND(AG58&gt;=AJ58,AG58&lt;=AK58),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13388,7 +14403,23 @@
         <v/>
       </c>
       <c r="AH59" s="4">
-        <f>IF(A59="","",IF(E59="","TERMINAL",IF(AG59="","INFO",IF(ABS(AG59)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A59="","",IF(E59="","TERMINAL",IF(OR(AND(UPPER(TRIM(B59))="SWALE",UPPER(TRIM(AI59))="PIPE"),AND(UPPER(TRIM(B59))="TRENCH",UPPER(TRIM(AI59))="PIPE")),IF(OR(AG59="",AJ59="",AK59=""),"INFO",IF(AND(AG59&gt;=AJ59,AG59&lt;=AK59),"OK","CHECK")),IF(AG59="","INFO",IF(ABS(AG59)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI59" s="17">
+        <f>IF(A59="","",IF(E59="","",IFERROR(INDEX($B$4:$B$204,MATCH(E59,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ59" s="17">
+        <f>IF(A59="","",IF(OR(AND(UPPER(TRIM(B59))="SWALE",UPPER(TRIM(AI59))="PIPE"),AND(UPPER(TRIM(B59))="TRENCH",UPPER(TRIM(AI59))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK59" s="17">
+        <f>IF(A59="","",IF(OR(AND(UPPER(TRIM(B59))="SWALE",UPPER(TRIM(AI59))="PIPE"),AND(UPPER(TRIM(B59))="TRENCH",UPPER(TRIM(AI59))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL59" s="4">
+        <f>IF(A59="","",IF(E59="","TERMINAL",IF(OR(AND(UPPER(TRIM(B59))="SWALE",UPPER(TRIM(AI59))="PIPE"),AND(UPPER(TRIM(B59))="TRENCH",UPPER(TRIM(AI59))="PIPE")),IF(OR(AG59="",AJ59="",AK59=""),"INFO",IF(AND(AG59&gt;=AJ59,AG59&lt;=AK59),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13483,7 +14514,23 @@
         <v/>
       </c>
       <c r="AH60" s="4">
-        <f>IF(A60="","",IF(E60="","TERMINAL",IF(AG60="","INFO",IF(ABS(AG60)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A60="","",IF(E60="","TERMINAL",IF(OR(AND(UPPER(TRIM(B60))="SWALE",UPPER(TRIM(AI60))="PIPE"),AND(UPPER(TRIM(B60))="TRENCH",UPPER(TRIM(AI60))="PIPE")),IF(OR(AG60="",AJ60="",AK60=""),"INFO",IF(AND(AG60&gt;=AJ60,AG60&lt;=AK60),"OK","CHECK")),IF(AG60="","INFO",IF(ABS(AG60)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI60" s="17">
+        <f>IF(A60="","",IF(E60="","",IFERROR(INDEX($B$4:$B$204,MATCH(E60,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ60" s="17">
+        <f>IF(A60="","",IF(OR(AND(UPPER(TRIM(B60))="SWALE",UPPER(TRIM(AI60))="PIPE"),AND(UPPER(TRIM(B60))="TRENCH",UPPER(TRIM(AI60))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK60" s="17">
+        <f>IF(A60="","",IF(OR(AND(UPPER(TRIM(B60))="SWALE",UPPER(TRIM(AI60))="PIPE"),AND(UPPER(TRIM(B60))="TRENCH",UPPER(TRIM(AI60))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL60" s="4">
+        <f>IF(A60="","",IF(E60="","TERMINAL",IF(OR(AND(UPPER(TRIM(B60))="SWALE",UPPER(TRIM(AI60))="PIPE"),AND(UPPER(TRIM(B60))="TRENCH",UPPER(TRIM(AI60))="PIPE")),IF(OR(AG60="",AJ60="",AK60=""),"INFO",IF(AND(AG60&gt;=AJ60,AG60&lt;=AK60),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13578,7 +14625,23 @@
         <v/>
       </c>
       <c r="AH61" s="4">
-        <f>IF(A61="","",IF(E61="","TERMINAL",IF(AG61="","INFO",IF(ABS(AG61)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A61="","",IF(E61="","TERMINAL",IF(OR(AND(UPPER(TRIM(B61))="SWALE",UPPER(TRIM(AI61))="PIPE"),AND(UPPER(TRIM(B61))="TRENCH",UPPER(TRIM(AI61))="PIPE")),IF(OR(AG61="",AJ61="",AK61=""),"INFO",IF(AND(AG61&gt;=AJ61,AG61&lt;=AK61),"OK","CHECK")),IF(AG61="","INFO",IF(ABS(AG61)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI61" s="17">
+        <f>IF(A61="","",IF(E61="","",IFERROR(INDEX($B$4:$B$204,MATCH(E61,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ61" s="17">
+        <f>IF(A61="","",IF(OR(AND(UPPER(TRIM(B61))="SWALE",UPPER(TRIM(AI61))="PIPE"),AND(UPPER(TRIM(B61))="TRENCH",UPPER(TRIM(AI61))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK61" s="17">
+        <f>IF(A61="","",IF(OR(AND(UPPER(TRIM(B61))="SWALE",UPPER(TRIM(AI61))="PIPE"),AND(UPPER(TRIM(B61))="TRENCH",UPPER(TRIM(AI61))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL61" s="4">
+        <f>IF(A61="","",IF(E61="","TERMINAL",IF(OR(AND(UPPER(TRIM(B61))="SWALE",UPPER(TRIM(AI61))="PIPE"),AND(UPPER(TRIM(B61))="TRENCH",UPPER(TRIM(AI61))="PIPE")),IF(OR(AG61="",AJ61="",AK61=""),"INFO",IF(AND(AG61&gt;=AJ61,AG61&lt;=AK61),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13673,7 +14736,23 @@
         <v/>
       </c>
       <c r="AH62" s="4">
-        <f>IF(A62="","",IF(E62="","TERMINAL",IF(AG62="","INFO",IF(ABS(AG62)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A62="","",IF(E62="","TERMINAL",IF(OR(AND(UPPER(TRIM(B62))="SWALE",UPPER(TRIM(AI62))="PIPE"),AND(UPPER(TRIM(B62))="TRENCH",UPPER(TRIM(AI62))="PIPE")),IF(OR(AG62="",AJ62="",AK62=""),"INFO",IF(AND(AG62&gt;=AJ62,AG62&lt;=AK62),"OK","CHECK")),IF(AG62="","INFO",IF(ABS(AG62)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI62" s="17">
+        <f>IF(A62="","",IF(E62="","",IFERROR(INDEX($B$4:$B$204,MATCH(E62,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ62" s="17">
+        <f>IF(A62="","",IF(OR(AND(UPPER(TRIM(B62))="SWALE",UPPER(TRIM(AI62))="PIPE"),AND(UPPER(TRIM(B62))="TRENCH",UPPER(TRIM(AI62))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK62" s="17">
+        <f>IF(A62="","",IF(OR(AND(UPPER(TRIM(B62))="SWALE",UPPER(TRIM(AI62))="PIPE"),AND(UPPER(TRIM(B62))="TRENCH",UPPER(TRIM(AI62))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL62" s="4">
+        <f>IF(A62="","",IF(E62="","TERMINAL",IF(OR(AND(UPPER(TRIM(B62))="SWALE",UPPER(TRIM(AI62))="PIPE"),AND(UPPER(TRIM(B62))="TRENCH",UPPER(TRIM(AI62))="PIPE")),IF(OR(AG62="",AJ62="",AK62=""),"INFO",IF(AND(AG62&gt;=AJ62,AG62&lt;=AK62),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13768,7 +14847,23 @@
         <v/>
       </c>
       <c r="AH63" s="4">
-        <f>IF(A63="","",IF(E63="","TERMINAL",IF(AG63="","INFO",IF(ABS(AG63)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A63="","",IF(E63="","TERMINAL",IF(OR(AND(UPPER(TRIM(B63))="SWALE",UPPER(TRIM(AI63))="PIPE"),AND(UPPER(TRIM(B63))="TRENCH",UPPER(TRIM(AI63))="PIPE")),IF(OR(AG63="",AJ63="",AK63=""),"INFO",IF(AND(AG63&gt;=AJ63,AG63&lt;=AK63),"OK","CHECK")),IF(AG63="","INFO",IF(ABS(AG63)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI63" s="17">
+        <f>IF(A63="","",IF(E63="","",IFERROR(INDEX($B$4:$B$204,MATCH(E63,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ63" s="17">
+        <f>IF(A63="","",IF(OR(AND(UPPER(TRIM(B63))="SWALE",UPPER(TRIM(AI63))="PIPE"),AND(UPPER(TRIM(B63))="TRENCH",UPPER(TRIM(AI63))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK63" s="17">
+        <f>IF(A63="","",IF(OR(AND(UPPER(TRIM(B63))="SWALE",UPPER(TRIM(AI63))="PIPE"),AND(UPPER(TRIM(B63))="TRENCH",UPPER(TRIM(AI63))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL63" s="4">
+        <f>IF(A63="","",IF(E63="","TERMINAL",IF(OR(AND(UPPER(TRIM(B63))="SWALE",UPPER(TRIM(AI63))="PIPE"),AND(UPPER(TRIM(B63))="TRENCH",UPPER(TRIM(AI63))="PIPE")),IF(OR(AG63="",AJ63="",AK63=""),"INFO",IF(AND(AG63&gt;=AJ63,AG63&lt;=AK63),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13863,7 +14958,23 @@
         <v/>
       </c>
       <c r="AH64" s="4">
-        <f>IF(A64="","",IF(E64="","TERMINAL",IF(AG64="","INFO",IF(ABS(AG64)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A64="","",IF(E64="","TERMINAL",IF(OR(AND(UPPER(TRIM(B64))="SWALE",UPPER(TRIM(AI64))="PIPE"),AND(UPPER(TRIM(B64))="TRENCH",UPPER(TRIM(AI64))="PIPE")),IF(OR(AG64="",AJ64="",AK64=""),"INFO",IF(AND(AG64&gt;=AJ64,AG64&lt;=AK64),"OK","CHECK")),IF(AG64="","INFO",IF(ABS(AG64)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI64" s="17">
+        <f>IF(A64="","",IF(E64="","",IFERROR(INDEX($B$4:$B$204,MATCH(E64,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ64" s="17">
+        <f>IF(A64="","",IF(OR(AND(UPPER(TRIM(B64))="SWALE",UPPER(TRIM(AI64))="PIPE"),AND(UPPER(TRIM(B64))="TRENCH",UPPER(TRIM(AI64))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK64" s="17">
+        <f>IF(A64="","",IF(OR(AND(UPPER(TRIM(B64))="SWALE",UPPER(TRIM(AI64))="PIPE"),AND(UPPER(TRIM(B64))="TRENCH",UPPER(TRIM(AI64))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL64" s="4">
+        <f>IF(A64="","",IF(E64="","TERMINAL",IF(OR(AND(UPPER(TRIM(B64))="SWALE",UPPER(TRIM(AI64))="PIPE"),AND(UPPER(TRIM(B64))="TRENCH",UPPER(TRIM(AI64))="PIPE")),IF(OR(AG64="",AJ64="",AK64=""),"INFO",IF(AND(AG64&gt;=AJ64,AG64&lt;=AK64),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -13958,7 +15069,23 @@
         <v/>
       </c>
       <c r="AH65" s="4">
-        <f>IF(A65="","",IF(E65="","TERMINAL",IF(AG65="","INFO",IF(ABS(AG65)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A65="","",IF(E65="","TERMINAL",IF(OR(AND(UPPER(TRIM(B65))="SWALE",UPPER(TRIM(AI65))="PIPE"),AND(UPPER(TRIM(B65))="TRENCH",UPPER(TRIM(AI65))="PIPE")),IF(OR(AG65="",AJ65="",AK65=""),"INFO",IF(AND(AG65&gt;=AJ65,AG65&lt;=AK65),"OK","CHECK")),IF(AG65="","INFO",IF(ABS(AG65)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI65" s="17">
+        <f>IF(A65="","",IF(E65="","",IFERROR(INDEX($B$4:$B$204,MATCH(E65,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ65" s="17">
+        <f>IF(A65="","",IF(OR(AND(UPPER(TRIM(B65))="SWALE",UPPER(TRIM(AI65))="PIPE"),AND(UPPER(TRIM(B65))="TRENCH",UPPER(TRIM(AI65))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK65" s="17">
+        <f>IF(A65="","",IF(OR(AND(UPPER(TRIM(B65))="SWALE",UPPER(TRIM(AI65))="PIPE"),AND(UPPER(TRIM(B65))="TRENCH",UPPER(TRIM(AI65))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL65" s="4">
+        <f>IF(A65="","",IF(E65="","TERMINAL",IF(OR(AND(UPPER(TRIM(B65))="SWALE",UPPER(TRIM(AI65))="PIPE"),AND(UPPER(TRIM(B65))="TRENCH",UPPER(TRIM(AI65))="PIPE")),IF(OR(AG65="",AJ65="",AK65=""),"INFO",IF(AND(AG65&gt;=AJ65,AG65&lt;=AK65),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14053,7 +15180,23 @@
         <v/>
       </c>
       <c r="AH66" s="4">
-        <f>IF(A66="","",IF(E66="","TERMINAL",IF(AG66="","INFO",IF(ABS(AG66)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A66="","",IF(E66="","TERMINAL",IF(OR(AND(UPPER(TRIM(B66))="SWALE",UPPER(TRIM(AI66))="PIPE"),AND(UPPER(TRIM(B66))="TRENCH",UPPER(TRIM(AI66))="PIPE")),IF(OR(AG66="",AJ66="",AK66=""),"INFO",IF(AND(AG66&gt;=AJ66,AG66&lt;=AK66),"OK","CHECK")),IF(AG66="","INFO",IF(ABS(AG66)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI66" s="17">
+        <f>IF(A66="","",IF(E66="","",IFERROR(INDEX($B$4:$B$204,MATCH(E66,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ66" s="17">
+        <f>IF(A66="","",IF(OR(AND(UPPER(TRIM(B66))="SWALE",UPPER(TRIM(AI66))="PIPE"),AND(UPPER(TRIM(B66))="TRENCH",UPPER(TRIM(AI66))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK66" s="17">
+        <f>IF(A66="","",IF(OR(AND(UPPER(TRIM(B66))="SWALE",UPPER(TRIM(AI66))="PIPE"),AND(UPPER(TRIM(B66))="TRENCH",UPPER(TRIM(AI66))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL66" s="4">
+        <f>IF(A66="","",IF(E66="","TERMINAL",IF(OR(AND(UPPER(TRIM(B66))="SWALE",UPPER(TRIM(AI66))="PIPE"),AND(UPPER(TRIM(B66))="TRENCH",UPPER(TRIM(AI66))="PIPE")),IF(OR(AG66="",AJ66="",AK66=""),"INFO",IF(AND(AG66&gt;=AJ66,AG66&lt;=AK66),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14148,7 +15291,23 @@
         <v/>
       </c>
       <c r="AH67" s="4">
-        <f>IF(A67="","",IF(E67="","TERMINAL",IF(AG67="","INFO",IF(ABS(AG67)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A67="","",IF(E67="","TERMINAL",IF(OR(AND(UPPER(TRIM(B67))="SWALE",UPPER(TRIM(AI67))="PIPE"),AND(UPPER(TRIM(B67))="TRENCH",UPPER(TRIM(AI67))="PIPE")),IF(OR(AG67="",AJ67="",AK67=""),"INFO",IF(AND(AG67&gt;=AJ67,AG67&lt;=AK67),"OK","CHECK")),IF(AG67="","INFO",IF(ABS(AG67)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI67" s="17">
+        <f>IF(A67="","",IF(E67="","",IFERROR(INDEX($B$4:$B$204,MATCH(E67,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ67" s="17">
+        <f>IF(A67="","",IF(OR(AND(UPPER(TRIM(B67))="SWALE",UPPER(TRIM(AI67))="PIPE"),AND(UPPER(TRIM(B67))="TRENCH",UPPER(TRIM(AI67))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK67" s="17">
+        <f>IF(A67="","",IF(OR(AND(UPPER(TRIM(B67))="SWALE",UPPER(TRIM(AI67))="PIPE"),AND(UPPER(TRIM(B67))="TRENCH",UPPER(TRIM(AI67))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL67" s="4">
+        <f>IF(A67="","",IF(E67="","TERMINAL",IF(OR(AND(UPPER(TRIM(B67))="SWALE",UPPER(TRIM(AI67))="PIPE"),AND(UPPER(TRIM(B67))="TRENCH",UPPER(TRIM(AI67))="PIPE")),IF(OR(AG67="",AJ67="",AK67=""),"INFO",IF(AND(AG67&gt;=AJ67,AG67&lt;=AK67),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14243,7 +15402,23 @@
         <v/>
       </c>
       <c r="AH68" s="4">
-        <f>IF(A68="","",IF(E68="","TERMINAL",IF(AG68="","INFO",IF(ABS(AG68)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A68="","",IF(E68="","TERMINAL",IF(OR(AND(UPPER(TRIM(B68))="SWALE",UPPER(TRIM(AI68))="PIPE"),AND(UPPER(TRIM(B68))="TRENCH",UPPER(TRIM(AI68))="PIPE")),IF(OR(AG68="",AJ68="",AK68=""),"INFO",IF(AND(AG68&gt;=AJ68,AG68&lt;=AK68),"OK","CHECK")),IF(AG68="","INFO",IF(ABS(AG68)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI68" s="17">
+        <f>IF(A68="","",IF(E68="","",IFERROR(INDEX($B$4:$B$204,MATCH(E68,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ68" s="17">
+        <f>IF(A68="","",IF(OR(AND(UPPER(TRIM(B68))="SWALE",UPPER(TRIM(AI68))="PIPE"),AND(UPPER(TRIM(B68))="TRENCH",UPPER(TRIM(AI68))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK68" s="17">
+        <f>IF(A68="","",IF(OR(AND(UPPER(TRIM(B68))="SWALE",UPPER(TRIM(AI68))="PIPE"),AND(UPPER(TRIM(B68))="TRENCH",UPPER(TRIM(AI68))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL68" s="4">
+        <f>IF(A68="","",IF(E68="","TERMINAL",IF(OR(AND(UPPER(TRIM(B68))="SWALE",UPPER(TRIM(AI68))="PIPE"),AND(UPPER(TRIM(B68))="TRENCH",UPPER(TRIM(AI68))="PIPE")),IF(OR(AG68="",AJ68="",AK68=""),"INFO",IF(AND(AG68&gt;=AJ68,AG68&lt;=AK68),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14338,7 +15513,23 @@
         <v/>
       </c>
       <c r="AH69" s="4">
-        <f>IF(A69="","",IF(E69="","TERMINAL",IF(AG69="","INFO",IF(ABS(AG69)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A69="","",IF(E69="","TERMINAL",IF(OR(AND(UPPER(TRIM(B69))="SWALE",UPPER(TRIM(AI69))="PIPE"),AND(UPPER(TRIM(B69))="TRENCH",UPPER(TRIM(AI69))="PIPE")),IF(OR(AG69="",AJ69="",AK69=""),"INFO",IF(AND(AG69&gt;=AJ69,AG69&lt;=AK69),"OK","CHECK")),IF(AG69="","INFO",IF(ABS(AG69)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI69" s="17">
+        <f>IF(A69="","",IF(E69="","",IFERROR(INDEX($B$4:$B$204,MATCH(E69,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ69" s="17">
+        <f>IF(A69="","",IF(OR(AND(UPPER(TRIM(B69))="SWALE",UPPER(TRIM(AI69))="PIPE"),AND(UPPER(TRIM(B69))="TRENCH",UPPER(TRIM(AI69))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK69" s="17">
+        <f>IF(A69="","",IF(OR(AND(UPPER(TRIM(B69))="SWALE",UPPER(TRIM(AI69))="PIPE"),AND(UPPER(TRIM(B69))="TRENCH",UPPER(TRIM(AI69))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL69" s="4">
+        <f>IF(A69="","",IF(E69="","TERMINAL",IF(OR(AND(UPPER(TRIM(B69))="SWALE",UPPER(TRIM(AI69))="PIPE"),AND(UPPER(TRIM(B69))="TRENCH",UPPER(TRIM(AI69))="PIPE")),IF(OR(AG69="",AJ69="",AK69=""),"INFO",IF(AND(AG69&gt;=AJ69,AG69&lt;=AK69),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14433,7 +15624,23 @@
         <v/>
       </c>
       <c r="AH70" s="4">
-        <f>IF(A70="","",IF(E70="","TERMINAL",IF(AG70="","INFO",IF(ABS(AG70)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A70="","",IF(E70="","TERMINAL",IF(OR(AND(UPPER(TRIM(B70))="SWALE",UPPER(TRIM(AI70))="PIPE"),AND(UPPER(TRIM(B70))="TRENCH",UPPER(TRIM(AI70))="PIPE")),IF(OR(AG70="",AJ70="",AK70=""),"INFO",IF(AND(AG70&gt;=AJ70,AG70&lt;=AK70),"OK","CHECK")),IF(AG70="","INFO",IF(ABS(AG70)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI70" s="17">
+        <f>IF(A70="","",IF(E70="","",IFERROR(INDEX($B$4:$B$204,MATCH(E70,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ70" s="17">
+        <f>IF(A70="","",IF(OR(AND(UPPER(TRIM(B70))="SWALE",UPPER(TRIM(AI70))="PIPE"),AND(UPPER(TRIM(B70))="TRENCH",UPPER(TRIM(AI70))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK70" s="17">
+        <f>IF(A70="","",IF(OR(AND(UPPER(TRIM(B70))="SWALE",UPPER(TRIM(AI70))="PIPE"),AND(UPPER(TRIM(B70))="TRENCH",UPPER(TRIM(AI70))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL70" s="4">
+        <f>IF(A70="","",IF(E70="","TERMINAL",IF(OR(AND(UPPER(TRIM(B70))="SWALE",UPPER(TRIM(AI70))="PIPE"),AND(UPPER(TRIM(B70))="TRENCH",UPPER(TRIM(AI70))="PIPE")),IF(OR(AG70="",AJ70="",AK70=""),"INFO",IF(AND(AG70&gt;=AJ70,AG70&lt;=AK70),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14528,7 +15735,23 @@
         <v/>
       </c>
       <c r="AH71" s="4">
-        <f>IF(A71="","",IF(E71="","TERMINAL",IF(AG71="","INFO",IF(ABS(AG71)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A71="","",IF(E71="","TERMINAL",IF(OR(AND(UPPER(TRIM(B71))="SWALE",UPPER(TRIM(AI71))="PIPE"),AND(UPPER(TRIM(B71))="TRENCH",UPPER(TRIM(AI71))="PIPE")),IF(OR(AG71="",AJ71="",AK71=""),"INFO",IF(AND(AG71&gt;=AJ71,AG71&lt;=AK71),"OK","CHECK")),IF(AG71="","INFO",IF(ABS(AG71)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI71" s="17">
+        <f>IF(A71="","",IF(E71="","",IFERROR(INDEX($B$4:$B$204,MATCH(E71,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ71" s="17">
+        <f>IF(A71="","",IF(OR(AND(UPPER(TRIM(B71))="SWALE",UPPER(TRIM(AI71))="PIPE"),AND(UPPER(TRIM(B71))="TRENCH",UPPER(TRIM(AI71))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK71" s="17">
+        <f>IF(A71="","",IF(OR(AND(UPPER(TRIM(B71))="SWALE",UPPER(TRIM(AI71))="PIPE"),AND(UPPER(TRIM(B71))="TRENCH",UPPER(TRIM(AI71))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL71" s="4">
+        <f>IF(A71="","",IF(E71="","TERMINAL",IF(OR(AND(UPPER(TRIM(B71))="SWALE",UPPER(TRIM(AI71))="PIPE"),AND(UPPER(TRIM(B71))="TRENCH",UPPER(TRIM(AI71))="PIPE")),IF(OR(AG71="",AJ71="",AK71=""),"INFO",IF(AND(AG71&gt;=AJ71,AG71&lt;=AK71),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14623,7 +15846,23 @@
         <v/>
       </c>
       <c r="AH72" s="4">
-        <f>IF(A72="","",IF(E72="","TERMINAL",IF(AG72="","INFO",IF(ABS(AG72)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A72="","",IF(E72="","TERMINAL",IF(OR(AND(UPPER(TRIM(B72))="SWALE",UPPER(TRIM(AI72))="PIPE"),AND(UPPER(TRIM(B72))="TRENCH",UPPER(TRIM(AI72))="PIPE")),IF(OR(AG72="",AJ72="",AK72=""),"INFO",IF(AND(AG72&gt;=AJ72,AG72&lt;=AK72),"OK","CHECK")),IF(AG72="","INFO",IF(ABS(AG72)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI72" s="17">
+        <f>IF(A72="","",IF(E72="","",IFERROR(INDEX($B$4:$B$204,MATCH(E72,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ72" s="17">
+        <f>IF(A72="","",IF(OR(AND(UPPER(TRIM(B72))="SWALE",UPPER(TRIM(AI72))="PIPE"),AND(UPPER(TRIM(B72))="TRENCH",UPPER(TRIM(AI72))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK72" s="17">
+        <f>IF(A72="","",IF(OR(AND(UPPER(TRIM(B72))="SWALE",UPPER(TRIM(AI72))="PIPE"),AND(UPPER(TRIM(B72))="TRENCH",UPPER(TRIM(AI72))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL72" s="4">
+        <f>IF(A72="","",IF(E72="","TERMINAL",IF(OR(AND(UPPER(TRIM(B72))="SWALE",UPPER(TRIM(AI72))="PIPE"),AND(UPPER(TRIM(B72))="TRENCH",UPPER(TRIM(AI72))="PIPE")),IF(OR(AG72="",AJ72="",AK72=""),"INFO",IF(AND(AG72&gt;=AJ72,AG72&lt;=AK72),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14718,7 +15957,23 @@
         <v/>
       </c>
       <c r="AH73" s="4">
-        <f>IF(A73="","",IF(E73="","TERMINAL",IF(AG73="","INFO",IF(ABS(AG73)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A73="","",IF(E73="","TERMINAL",IF(OR(AND(UPPER(TRIM(B73))="SWALE",UPPER(TRIM(AI73))="PIPE"),AND(UPPER(TRIM(B73))="TRENCH",UPPER(TRIM(AI73))="PIPE")),IF(OR(AG73="",AJ73="",AK73=""),"INFO",IF(AND(AG73&gt;=AJ73,AG73&lt;=AK73),"OK","CHECK")),IF(AG73="","INFO",IF(ABS(AG73)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI73" s="17">
+        <f>IF(A73="","",IF(E73="","",IFERROR(INDEX($B$4:$B$204,MATCH(E73,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ73" s="17">
+        <f>IF(A73="","",IF(OR(AND(UPPER(TRIM(B73))="SWALE",UPPER(TRIM(AI73))="PIPE"),AND(UPPER(TRIM(B73))="TRENCH",UPPER(TRIM(AI73))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK73" s="17">
+        <f>IF(A73="","",IF(OR(AND(UPPER(TRIM(B73))="SWALE",UPPER(TRIM(AI73))="PIPE"),AND(UPPER(TRIM(B73))="TRENCH",UPPER(TRIM(AI73))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL73" s="4">
+        <f>IF(A73="","",IF(E73="","TERMINAL",IF(OR(AND(UPPER(TRIM(B73))="SWALE",UPPER(TRIM(AI73))="PIPE"),AND(UPPER(TRIM(B73))="TRENCH",UPPER(TRIM(AI73))="PIPE")),IF(OR(AG73="",AJ73="",AK73=""),"INFO",IF(AND(AG73&gt;=AJ73,AG73&lt;=AK73),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14813,7 +16068,23 @@
         <v/>
       </c>
       <c r="AH74" s="4">
-        <f>IF(A74="","",IF(E74="","TERMINAL",IF(AG74="","INFO",IF(ABS(AG74)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A74="","",IF(E74="","TERMINAL",IF(OR(AND(UPPER(TRIM(B74))="SWALE",UPPER(TRIM(AI74))="PIPE"),AND(UPPER(TRIM(B74))="TRENCH",UPPER(TRIM(AI74))="PIPE")),IF(OR(AG74="",AJ74="",AK74=""),"INFO",IF(AND(AG74&gt;=AJ74,AG74&lt;=AK74),"OK","CHECK")),IF(AG74="","INFO",IF(ABS(AG74)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI74" s="17">
+        <f>IF(A74="","",IF(E74="","",IFERROR(INDEX($B$4:$B$204,MATCH(E74,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ74" s="17">
+        <f>IF(A74="","",IF(OR(AND(UPPER(TRIM(B74))="SWALE",UPPER(TRIM(AI74))="PIPE"),AND(UPPER(TRIM(B74))="TRENCH",UPPER(TRIM(AI74))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK74" s="17">
+        <f>IF(A74="","",IF(OR(AND(UPPER(TRIM(B74))="SWALE",UPPER(TRIM(AI74))="PIPE"),AND(UPPER(TRIM(B74))="TRENCH",UPPER(TRIM(AI74))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL74" s="4">
+        <f>IF(A74="","",IF(E74="","TERMINAL",IF(OR(AND(UPPER(TRIM(B74))="SWALE",UPPER(TRIM(AI74))="PIPE"),AND(UPPER(TRIM(B74))="TRENCH",UPPER(TRIM(AI74))="PIPE")),IF(OR(AG74="",AJ74="",AK74=""),"INFO",IF(AND(AG74&gt;=AJ74,AG74&lt;=AK74),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -14908,7 +16179,23 @@
         <v/>
       </c>
       <c r="AH75" s="4">
-        <f>IF(A75="","",IF(E75="","TERMINAL",IF(AG75="","INFO",IF(ABS(AG75)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A75="","",IF(E75="","TERMINAL",IF(OR(AND(UPPER(TRIM(B75))="SWALE",UPPER(TRIM(AI75))="PIPE"),AND(UPPER(TRIM(B75))="TRENCH",UPPER(TRIM(AI75))="PIPE")),IF(OR(AG75="",AJ75="",AK75=""),"INFO",IF(AND(AG75&gt;=AJ75,AG75&lt;=AK75),"OK","CHECK")),IF(AG75="","INFO",IF(ABS(AG75)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI75" s="17">
+        <f>IF(A75="","",IF(E75="","",IFERROR(INDEX($B$4:$B$204,MATCH(E75,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ75" s="17">
+        <f>IF(A75="","",IF(OR(AND(UPPER(TRIM(B75))="SWALE",UPPER(TRIM(AI75))="PIPE"),AND(UPPER(TRIM(B75))="TRENCH",UPPER(TRIM(AI75))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK75" s="17">
+        <f>IF(A75="","",IF(OR(AND(UPPER(TRIM(B75))="SWALE",UPPER(TRIM(AI75))="PIPE"),AND(UPPER(TRIM(B75))="TRENCH",UPPER(TRIM(AI75))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL75" s="4">
+        <f>IF(A75="","",IF(E75="","TERMINAL",IF(OR(AND(UPPER(TRIM(B75))="SWALE",UPPER(TRIM(AI75))="PIPE"),AND(UPPER(TRIM(B75))="TRENCH",UPPER(TRIM(AI75))="PIPE")),IF(OR(AG75="",AJ75="",AK75=""),"INFO",IF(AND(AG75&gt;=AJ75,AG75&lt;=AK75),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15003,7 +16290,23 @@
         <v/>
       </c>
       <c r="AH76" s="4">
-        <f>IF(A76="","",IF(E76="","TERMINAL",IF(AG76="","INFO",IF(ABS(AG76)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A76="","",IF(E76="","TERMINAL",IF(OR(AND(UPPER(TRIM(B76))="SWALE",UPPER(TRIM(AI76))="PIPE"),AND(UPPER(TRIM(B76))="TRENCH",UPPER(TRIM(AI76))="PIPE")),IF(OR(AG76="",AJ76="",AK76=""),"INFO",IF(AND(AG76&gt;=AJ76,AG76&lt;=AK76),"OK","CHECK")),IF(AG76="","INFO",IF(ABS(AG76)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI76" s="17">
+        <f>IF(A76="","",IF(E76="","",IFERROR(INDEX($B$4:$B$204,MATCH(E76,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ76" s="17">
+        <f>IF(A76="","",IF(OR(AND(UPPER(TRIM(B76))="SWALE",UPPER(TRIM(AI76))="PIPE"),AND(UPPER(TRIM(B76))="TRENCH",UPPER(TRIM(AI76))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK76" s="17">
+        <f>IF(A76="","",IF(OR(AND(UPPER(TRIM(B76))="SWALE",UPPER(TRIM(AI76))="PIPE"),AND(UPPER(TRIM(B76))="TRENCH",UPPER(TRIM(AI76))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL76" s="4">
+        <f>IF(A76="","",IF(E76="","TERMINAL",IF(OR(AND(UPPER(TRIM(B76))="SWALE",UPPER(TRIM(AI76))="PIPE"),AND(UPPER(TRIM(B76))="TRENCH",UPPER(TRIM(AI76))="PIPE")),IF(OR(AG76="",AJ76="",AK76=""),"INFO",IF(AND(AG76&gt;=AJ76,AG76&lt;=AK76),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15098,7 +16401,23 @@
         <v/>
       </c>
       <c r="AH77" s="4">
-        <f>IF(A77="","",IF(E77="","TERMINAL",IF(AG77="","INFO",IF(ABS(AG77)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A77="","",IF(E77="","TERMINAL",IF(OR(AND(UPPER(TRIM(B77))="SWALE",UPPER(TRIM(AI77))="PIPE"),AND(UPPER(TRIM(B77))="TRENCH",UPPER(TRIM(AI77))="PIPE")),IF(OR(AG77="",AJ77="",AK77=""),"INFO",IF(AND(AG77&gt;=AJ77,AG77&lt;=AK77),"OK","CHECK")),IF(AG77="","INFO",IF(ABS(AG77)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI77" s="17">
+        <f>IF(A77="","",IF(E77="","",IFERROR(INDEX($B$4:$B$204,MATCH(E77,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ77" s="17">
+        <f>IF(A77="","",IF(OR(AND(UPPER(TRIM(B77))="SWALE",UPPER(TRIM(AI77))="PIPE"),AND(UPPER(TRIM(B77))="TRENCH",UPPER(TRIM(AI77))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK77" s="17">
+        <f>IF(A77="","",IF(OR(AND(UPPER(TRIM(B77))="SWALE",UPPER(TRIM(AI77))="PIPE"),AND(UPPER(TRIM(B77))="TRENCH",UPPER(TRIM(AI77))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL77" s="4">
+        <f>IF(A77="","",IF(E77="","TERMINAL",IF(OR(AND(UPPER(TRIM(B77))="SWALE",UPPER(TRIM(AI77))="PIPE"),AND(UPPER(TRIM(B77))="TRENCH",UPPER(TRIM(AI77))="PIPE")),IF(OR(AG77="",AJ77="",AK77=""),"INFO",IF(AND(AG77&gt;=AJ77,AG77&lt;=AK77),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15193,7 +16512,23 @@
         <v/>
       </c>
       <c r="AH78" s="4">
-        <f>IF(A78="","",IF(E78="","TERMINAL",IF(AG78="","INFO",IF(ABS(AG78)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A78="","",IF(E78="","TERMINAL",IF(OR(AND(UPPER(TRIM(B78))="SWALE",UPPER(TRIM(AI78))="PIPE"),AND(UPPER(TRIM(B78))="TRENCH",UPPER(TRIM(AI78))="PIPE")),IF(OR(AG78="",AJ78="",AK78=""),"INFO",IF(AND(AG78&gt;=AJ78,AG78&lt;=AK78),"OK","CHECK")),IF(AG78="","INFO",IF(ABS(AG78)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI78" s="17">
+        <f>IF(A78="","",IF(E78="","",IFERROR(INDEX($B$4:$B$204,MATCH(E78,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ78" s="17">
+        <f>IF(A78="","",IF(OR(AND(UPPER(TRIM(B78))="SWALE",UPPER(TRIM(AI78))="PIPE"),AND(UPPER(TRIM(B78))="TRENCH",UPPER(TRIM(AI78))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK78" s="17">
+        <f>IF(A78="","",IF(OR(AND(UPPER(TRIM(B78))="SWALE",UPPER(TRIM(AI78))="PIPE"),AND(UPPER(TRIM(B78))="TRENCH",UPPER(TRIM(AI78))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL78" s="4">
+        <f>IF(A78="","",IF(E78="","TERMINAL",IF(OR(AND(UPPER(TRIM(B78))="SWALE",UPPER(TRIM(AI78))="PIPE"),AND(UPPER(TRIM(B78))="TRENCH",UPPER(TRIM(AI78))="PIPE")),IF(OR(AG78="",AJ78="",AK78=""),"INFO",IF(AND(AG78&gt;=AJ78,AG78&lt;=AK78),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15288,7 +16623,23 @@
         <v/>
       </c>
       <c r="AH79" s="4">
-        <f>IF(A79="","",IF(E79="","TERMINAL",IF(AG79="","INFO",IF(ABS(AG79)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A79="","",IF(E79="","TERMINAL",IF(OR(AND(UPPER(TRIM(B79))="SWALE",UPPER(TRIM(AI79))="PIPE"),AND(UPPER(TRIM(B79))="TRENCH",UPPER(TRIM(AI79))="PIPE")),IF(OR(AG79="",AJ79="",AK79=""),"INFO",IF(AND(AG79&gt;=AJ79,AG79&lt;=AK79),"OK","CHECK")),IF(AG79="","INFO",IF(ABS(AG79)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI79" s="17">
+        <f>IF(A79="","",IF(E79="","",IFERROR(INDEX($B$4:$B$204,MATCH(E79,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ79" s="17">
+        <f>IF(A79="","",IF(OR(AND(UPPER(TRIM(B79))="SWALE",UPPER(TRIM(AI79))="PIPE"),AND(UPPER(TRIM(B79))="TRENCH",UPPER(TRIM(AI79))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK79" s="17">
+        <f>IF(A79="","",IF(OR(AND(UPPER(TRIM(B79))="SWALE",UPPER(TRIM(AI79))="PIPE"),AND(UPPER(TRIM(B79))="TRENCH",UPPER(TRIM(AI79))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL79" s="4">
+        <f>IF(A79="","",IF(E79="","TERMINAL",IF(OR(AND(UPPER(TRIM(B79))="SWALE",UPPER(TRIM(AI79))="PIPE"),AND(UPPER(TRIM(B79))="TRENCH",UPPER(TRIM(AI79))="PIPE")),IF(OR(AG79="",AJ79="",AK79=""),"INFO",IF(AND(AG79&gt;=AJ79,AG79&lt;=AK79),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15383,7 +16734,23 @@
         <v/>
       </c>
       <c r="AH80" s="4">
-        <f>IF(A80="","",IF(E80="","TERMINAL",IF(AG80="","INFO",IF(ABS(AG80)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A80="","",IF(E80="","TERMINAL",IF(OR(AND(UPPER(TRIM(B80))="SWALE",UPPER(TRIM(AI80))="PIPE"),AND(UPPER(TRIM(B80))="TRENCH",UPPER(TRIM(AI80))="PIPE")),IF(OR(AG80="",AJ80="",AK80=""),"INFO",IF(AND(AG80&gt;=AJ80,AG80&lt;=AK80),"OK","CHECK")),IF(AG80="","INFO",IF(ABS(AG80)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI80" s="17">
+        <f>IF(A80="","",IF(E80="","",IFERROR(INDEX($B$4:$B$204,MATCH(E80,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ80" s="17">
+        <f>IF(A80="","",IF(OR(AND(UPPER(TRIM(B80))="SWALE",UPPER(TRIM(AI80))="PIPE"),AND(UPPER(TRIM(B80))="TRENCH",UPPER(TRIM(AI80))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK80" s="17">
+        <f>IF(A80="","",IF(OR(AND(UPPER(TRIM(B80))="SWALE",UPPER(TRIM(AI80))="PIPE"),AND(UPPER(TRIM(B80))="TRENCH",UPPER(TRIM(AI80))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL80" s="4">
+        <f>IF(A80="","",IF(E80="","TERMINAL",IF(OR(AND(UPPER(TRIM(B80))="SWALE",UPPER(TRIM(AI80))="PIPE"),AND(UPPER(TRIM(B80))="TRENCH",UPPER(TRIM(AI80))="PIPE")),IF(OR(AG80="",AJ80="",AK80=""),"INFO",IF(AND(AG80&gt;=AJ80,AG80&lt;=AK80),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15478,7 +16845,23 @@
         <v/>
       </c>
       <c r="AH81" s="4">
-        <f>IF(A81="","",IF(E81="","TERMINAL",IF(AG81="","INFO",IF(ABS(AG81)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A81="","",IF(E81="","TERMINAL",IF(OR(AND(UPPER(TRIM(B81))="SWALE",UPPER(TRIM(AI81))="PIPE"),AND(UPPER(TRIM(B81))="TRENCH",UPPER(TRIM(AI81))="PIPE")),IF(OR(AG81="",AJ81="",AK81=""),"INFO",IF(AND(AG81&gt;=AJ81,AG81&lt;=AK81),"OK","CHECK")),IF(AG81="","INFO",IF(ABS(AG81)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI81" s="17">
+        <f>IF(A81="","",IF(E81="","",IFERROR(INDEX($B$4:$B$204,MATCH(E81,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ81" s="17">
+        <f>IF(A81="","",IF(OR(AND(UPPER(TRIM(B81))="SWALE",UPPER(TRIM(AI81))="PIPE"),AND(UPPER(TRIM(B81))="TRENCH",UPPER(TRIM(AI81))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK81" s="17">
+        <f>IF(A81="","",IF(OR(AND(UPPER(TRIM(B81))="SWALE",UPPER(TRIM(AI81))="PIPE"),AND(UPPER(TRIM(B81))="TRENCH",UPPER(TRIM(AI81))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL81" s="4">
+        <f>IF(A81="","",IF(E81="","TERMINAL",IF(OR(AND(UPPER(TRIM(B81))="SWALE",UPPER(TRIM(AI81))="PIPE"),AND(UPPER(TRIM(B81))="TRENCH",UPPER(TRIM(AI81))="PIPE")),IF(OR(AG81="",AJ81="",AK81=""),"INFO",IF(AND(AG81&gt;=AJ81,AG81&lt;=AK81),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15573,7 +16956,23 @@
         <v/>
       </c>
       <c r="AH82" s="4">
-        <f>IF(A82="","",IF(E82="","TERMINAL",IF(AG82="","INFO",IF(ABS(AG82)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A82="","",IF(E82="","TERMINAL",IF(OR(AND(UPPER(TRIM(B82))="SWALE",UPPER(TRIM(AI82))="PIPE"),AND(UPPER(TRIM(B82))="TRENCH",UPPER(TRIM(AI82))="PIPE")),IF(OR(AG82="",AJ82="",AK82=""),"INFO",IF(AND(AG82&gt;=AJ82,AG82&lt;=AK82),"OK","CHECK")),IF(AG82="","INFO",IF(ABS(AG82)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI82" s="17">
+        <f>IF(A82="","",IF(E82="","",IFERROR(INDEX($B$4:$B$204,MATCH(E82,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ82" s="17">
+        <f>IF(A82="","",IF(OR(AND(UPPER(TRIM(B82))="SWALE",UPPER(TRIM(AI82))="PIPE"),AND(UPPER(TRIM(B82))="TRENCH",UPPER(TRIM(AI82))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK82" s="17">
+        <f>IF(A82="","",IF(OR(AND(UPPER(TRIM(B82))="SWALE",UPPER(TRIM(AI82))="PIPE"),AND(UPPER(TRIM(B82))="TRENCH",UPPER(TRIM(AI82))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL82" s="4">
+        <f>IF(A82="","",IF(E82="","TERMINAL",IF(OR(AND(UPPER(TRIM(B82))="SWALE",UPPER(TRIM(AI82))="PIPE"),AND(UPPER(TRIM(B82))="TRENCH",UPPER(TRIM(AI82))="PIPE")),IF(OR(AG82="",AJ82="",AK82=""),"INFO",IF(AND(AG82&gt;=AJ82,AG82&lt;=AK82),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15668,7 +17067,23 @@
         <v/>
       </c>
       <c r="AH83" s="4">
-        <f>IF(A83="","",IF(E83="","TERMINAL",IF(AG83="","INFO",IF(ABS(AG83)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A83="","",IF(E83="","TERMINAL",IF(OR(AND(UPPER(TRIM(B83))="SWALE",UPPER(TRIM(AI83))="PIPE"),AND(UPPER(TRIM(B83))="TRENCH",UPPER(TRIM(AI83))="PIPE")),IF(OR(AG83="",AJ83="",AK83=""),"INFO",IF(AND(AG83&gt;=AJ83,AG83&lt;=AK83),"OK","CHECK")),IF(AG83="","INFO",IF(ABS(AG83)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI83" s="17">
+        <f>IF(A83="","",IF(E83="","",IFERROR(INDEX($B$4:$B$204,MATCH(E83,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ83" s="17">
+        <f>IF(A83="","",IF(OR(AND(UPPER(TRIM(B83))="SWALE",UPPER(TRIM(AI83))="PIPE"),AND(UPPER(TRIM(B83))="TRENCH",UPPER(TRIM(AI83))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK83" s="17">
+        <f>IF(A83="","",IF(OR(AND(UPPER(TRIM(B83))="SWALE",UPPER(TRIM(AI83))="PIPE"),AND(UPPER(TRIM(B83))="TRENCH",UPPER(TRIM(AI83))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL83" s="4">
+        <f>IF(A83="","",IF(E83="","TERMINAL",IF(OR(AND(UPPER(TRIM(B83))="SWALE",UPPER(TRIM(AI83))="PIPE"),AND(UPPER(TRIM(B83))="TRENCH",UPPER(TRIM(AI83))="PIPE")),IF(OR(AG83="",AJ83="",AK83=""),"INFO",IF(AND(AG83&gt;=AJ83,AG83&lt;=AK83),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15763,7 +17178,23 @@
         <v/>
       </c>
       <c r="AH84" s="4">
-        <f>IF(A84="","",IF(E84="","TERMINAL",IF(AG84="","INFO",IF(ABS(AG84)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A84="","",IF(E84="","TERMINAL",IF(OR(AND(UPPER(TRIM(B84))="SWALE",UPPER(TRIM(AI84))="PIPE"),AND(UPPER(TRIM(B84))="TRENCH",UPPER(TRIM(AI84))="PIPE")),IF(OR(AG84="",AJ84="",AK84=""),"INFO",IF(AND(AG84&gt;=AJ84,AG84&lt;=AK84),"OK","CHECK")),IF(AG84="","INFO",IF(ABS(AG84)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI84" s="17">
+        <f>IF(A84="","",IF(E84="","",IFERROR(INDEX($B$4:$B$204,MATCH(E84,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ84" s="17">
+        <f>IF(A84="","",IF(OR(AND(UPPER(TRIM(B84))="SWALE",UPPER(TRIM(AI84))="PIPE"),AND(UPPER(TRIM(B84))="TRENCH",UPPER(TRIM(AI84))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK84" s="17">
+        <f>IF(A84="","",IF(OR(AND(UPPER(TRIM(B84))="SWALE",UPPER(TRIM(AI84))="PIPE"),AND(UPPER(TRIM(B84))="TRENCH",UPPER(TRIM(AI84))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL84" s="4">
+        <f>IF(A84="","",IF(E84="","TERMINAL",IF(OR(AND(UPPER(TRIM(B84))="SWALE",UPPER(TRIM(AI84))="PIPE"),AND(UPPER(TRIM(B84))="TRENCH",UPPER(TRIM(AI84))="PIPE")),IF(OR(AG84="",AJ84="",AK84=""),"INFO",IF(AND(AG84&gt;=AJ84,AG84&lt;=AK84),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15858,7 +17289,23 @@
         <v/>
       </c>
       <c r="AH85" s="4">
-        <f>IF(A85="","",IF(E85="","TERMINAL",IF(AG85="","INFO",IF(ABS(AG85)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A85="","",IF(E85="","TERMINAL",IF(OR(AND(UPPER(TRIM(B85))="SWALE",UPPER(TRIM(AI85))="PIPE"),AND(UPPER(TRIM(B85))="TRENCH",UPPER(TRIM(AI85))="PIPE")),IF(OR(AG85="",AJ85="",AK85=""),"INFO",IF(AND(AG85&gt;=AJ85,AG85&lt;=AK85),"OK","CHECK")),IF(AG85="","INFO",IF(ABS(AG85)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI85" s="17">
+        <f>IF(A85="","",IF(E85="","",IFERROR(INDEX($B$4:$B$204,MATCH(E85,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ85" s="17">
+        <f>IF(A85="","",IF(OR(AND(UPPER(TRIM(B85))="SWALE",UPPER(TRIM(AI85))="PIPE"),AND(UPPER(TRIM(B85))="TRENCH",UPPER(TRIM(AI85))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK85" s="17">
+        <f>IF(A85="","",IF(OR(AND(UPPER(TRIM(B85))="SWALE",UPPER(TRIM(AI85))="PIPE"),AND(UPPER(TRIM(B85))="TRENCH",UPPER(TRIM(AI85))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL85" s="4">
+        <f>IF(A85="","",IF(E85="","TERMINAL",IF(OR(AND(UPPER(TRIM(B85))="SWALE",UPPER(TRIM(AI85))="PIPE"),AND(UPPER(TRIM(B85))="TRENCH",UPPER(TRIM(AI85))="PIPE")),IF(OR(AG85="",AJ85="",AK85=""),"INFO",IF(AND(AG85&gt;=AJ85,AG85&lt;=AK85),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -15953,7 +17400,23 @@
         <v/>
       </c>
       <c r="AH86" s="4">
-        <f>IF(A86="","",IF(E86="","TERMINAL",IF(AG86="","INFO",IF(ABS(AG86)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A86="","",IF(E86="","TERMINAL",IF(OR(AND(UPPER(TRIM(B86))="SWALE",UPPER(TRIM(AI86))="PIPE"),AND(UPPER(TRIM(B86))="TRENCH",UPPER(TRIM(AI86))="PIPE")),IF(OR(AG86="",AJ86="",AK86=""),"INFO",IF(AND(AG86&gt;=AJ86,AG86&lt;=AK86),"OK","CHECK")),IF(AG86="","INFO",IF(ABS(AG86)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI86" s="17">
+        <f>IF(A86="","",IF(E86="","",IFERROR(INDEX($B$4:$B$204,MATCH(E86,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ86" s="17">
+        <f>IF(A86="","",IF(OR(AND(UPPER(TRIM(B86))="SWALE",UPPER(TRIM(AI86))="PIPE"),AND(UPPER(TRIM(B86))="TRENCH",UPPER(TRIM(AI86))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK86" s="17">
+        <f>IF(A86="","",IF(OR(AND(UPPER(TRIM(B86))="SWALE",UPPER(TRIM(AI86))="PIPE"),AND(UPPER(TRIM(B86))="TRENCH",UPPER(TRIM(AI86))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL86" s="4">
+        <f>IF(A86="","",IF(E86="","TERMINAL",IF(OR(AND(UPPER(TRIM(B86))="SWALE",UPPER(TRIM(AI86))="PIPE"),AND(UPPER(TRIM(B86))="TRENCH",UPPER(TRIM(AI86))="PIPE")),IF(OR(AG86="",AJ86="",AK86=""),"INFO",IF(AND(AG86&gt;=AJ86,AG86&lt;=AK86),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16048,7 +17511,23 @@
         <v/>
       </c>
       <c r="AH87" s="4">
-        <f>IF(A87="","",IF(E87="","TERMINAL",IF(AG87="","INFO",IF(ABS(AG87)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A87="","",IF(E87="","TERMINAL",IF(OR(AND(UPPER(TRIM(B87))="SWALE",UPPER(TRIM(AI87))="PIPE"),AND(UPPER(TRIM(B87))="TRENCH",UPPER(TRIM(AI87))="PIPE")),IF(OR(AG87="",AJ87="",AK87=""),"INFO",IF(AND(AG87&gt;=AJ87,AG87&lt;=AK87),"OK","CHECK")),IF(AG87="","INFO",IF(ABS(AG87)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI87" s="17">
+        <f>IF(A87="","",IF(E87="","",IFERROR(INDEX($B$4:$B$204,MATCH(E87,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ87" s="17">
+        <f>IF(A87="","",IF(OR(AND(UPPER(TRIM(B87))="SWALE",UPPER(TRIM(AI87))="PIPE"),AND(UPPER(TRIM(B87))="TRENCH",UPPER(TRIM(AI87))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK87" s="17">
+        <f>IF(A87="","",IF(OR(AND(UPPER(TRIM(B87))="SWALE",UPPER(TRIM(AI87))="PIPE"),AND(UPPER(TRIM(B87))="TRENCH",UPPER(TRIM(AI87))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL87" s="4">
+        <f>IF(A87="","",IF(E87="","TERMINAL",IF(OR(AND(UPPER(TRIM(B87))="SWALE",UPPER(TRIM(AI87))="PIPE"),AND(UPPER(TRIM(B87))="TRENCH",UPPER(TRIM(AI87))="PIPE")),IF(OR(AG87="",AJ87="",AK87=""),"INFO",IF(AND(AG87&gt;=AJ87,AG87&lt;=AK87),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16143,7 +17622,23 @@
         <v/>
       </c>
       <c r="AH88" s="4">
-        <f>IF(A88="","",IF(E88="","TERMINAL",IF(AG88="","INFO",IF(ABS(AG88)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A88="","",IF(E88="","TERMINAL",IF(OR(AND(UPPER(TRIM(B88))="SWALE",UPPER(TRIM(AI88))="PIPE"),AND(UPPER(TRIM(B88))="TRENCH",UPPER(TRIM(AI88))="PIPE")),IF(OR(AG88="",AJ88="",AK88=""),"INFO",IF(AND(AG88&gt;=AJ88,AG88&lt;=AK88),"OK","CHECK")),IF(AG88="","INFO",IF(ABS(AG88)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI88" s="17">
+        <f>IF(A88="","",IF(E88="","",IFERROR(INDEX($B$4:$B$204,MATCH(E88,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ88" s="17">
+        <f>IF(A88="","",IF(OR(AND(UPPER(TRIM(B88))="SWALE",UPPER(TRIM(AI88))="PIPE"),AND(UPPER(TRIM(B88))="TRENCH",UPPER(TRIM(AI88))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK88" s="17">
+        <f>IF(A88="","",IF(OR(AND(UPPER(TRIM(B88))="SWALE",UPPER(TRIM(AI88))="PIPE"),AND(UPPER(TRIM(B88))="TRENCH",UPPER(TRIM(AI88))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL88" s="4">
+        <f>IF(A88="","",IF(E88="","TERMINAL",IF(OR(AND(UPPER(TRIM(B88))="SWALE",UPPER(TRIM(AI88))="PIPE"),AND(UPPER(TRIM(B88))="TRENCH",UPPER(TRIM(AI88))="PIPE")),IF(OR(AG88="",AJ88="",AK88=""),"INFO",IF(AND(AG88&gt;=AJ88,AG88&lt;=AK88),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16238,7 +17733,23 @@
         <v/>
       </c>
       <c r="AH89" s="4">
-        <f>IF(A89="","",IF(E89="","TERMINAL",IF(AG89="","INFO",IF(ABS(AG89)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A89="","",IF(E89="","TERMINAL",IF(OR(AND(UPPER(TRIM(B89))="SWALE",UPPER(TRIM(AI89))="PIPE"),AND(UPPER(TRIM(B89))="TRENCH",UPPER(TRIM(AI89))="PIPE")),IF(OR(AG89="",AJ89="",AK89=""),"INFO",IF(AND(AG89&gt;=AJ89,AG89&lt;=AK89),"OK","CHECK")),IF(AG89="","INFO",IF(ABS(AG89)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI89" s="17">
+        <f>IF(A89="","",IF(E89="","",IFERROR(INDEX($B$4:$B$204,MATCH(E89,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ89" s="17">
+        <f>IF(A89="","",IF(OR(AND(UPPER(TRIM(B89))="SWALE",UPPER(TRIM(AI89))="PIPE"),AND(UPPER(TRIM(B89))="TRENCH",UPPER(TRIM(AI89))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK89" s="17">
+        <f>IF(A89="","",IF(OR(AND(UPPER(TRIM(B89))="SWALE",UPPER(TRIM(AI89))="PIPE"),AND(UPPER(TRIM(B89))="TRENCH",UPPER(TRIM(AI89))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL89" s="4">
+        <f>IF(A89="","",IF(E89="","TERMINAL",IF(OR(AND(UPPER(TRIM(B89))="SWALE",UPPER(TRIM(AI89))="PIPE"),AND(UPPER(TRIM(B89))="TRENCH",UPPER(TRIM(AI89))="PIPE")),IF(OR(AG89="",AJ89="",AK89=""),"INFO",IF(AND(AG89&gt;=AJ89,AG89&lt;=AK89),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16333,7 +17844,23 @@
         <v/>
       </c>
       <c r="AH90" s="4">
-        <f>IF(A90="","",IF(E90="","TERMINAL",IF(AG90="","INFO",IF(ABS(AG90)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A90="","",IF(E90="","TERMINAL",IF(OR(AND(UPPER(TRIM(B90))="SWALE",UPPER(TRIM(AI90))="PIPE"),AND(UPPER(TRIM(B90))="TRENCH",UPPER(TRIM(AI90))="PIPE")),IF(OR(AG90="",AJ90="",AK90=""),"INFO",IF(AND(AG90&gt;=AJ90,AG90&lt;=AK90),"OK","CHECK")),IF(AG90="","INFO",IF(ABS(AG90)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI90" s="17">
+        <f>IF(A90="","",IF(E90="","",IFERROR(INDEX($B$4:$B$204,MATCH(E90,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ90" s="17">
+        <f>IF(A90="","",IF(OR(AND(UPPER(TRIM(B90))="SWALE",UPPER(TRIM(AI90))="PIPE"),AND(UPPER(TRIM(B90))="TRENCH",UPPER(TRIM(AI90))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK90" s="17">
+        <f>IF(A90="","",IF(OR(AND(UPPER(TRIM(B90))="SWALE",UPPER(TRIM(AI90))="PIPE"),AND(UPPER(TRIM(B90))="TRENCH",UPPER(TRIM(AI90))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL90" s="4">
+        <f>IF(A90="","",IF(E90="","TERMINAL",IF(OR(AND(UPPER(TRIM(B90))="SWALE",UPPER(TRIM(AI90))="PIPE"),AND(UPPER(TRIM(B90))="TRENCH",UPPER(TRIM(AI90))="PIPE")),IF(OR(AG90="",AJ90="",AK90=""),"INFO",IF(AND(AG90&gt;=AJ90,AG90&lt;=AK90),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16428,7 +17955,23 @@
         <v/>
       </c>
       <c r="AH91" s="4">
-        <f>IF(A91="","",IF(E91="","TERMINAL",IF(AG91="","INFO",IF(ABS(AG91)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A91="","",IF(E91="","TERMINAL",IF(OR(AND(UPPER(TRIM(B91))="SWALE",UPPER(TRIM(AI91))="PIPE"),AND(UPPER(TRIM(B91))="TRENCH",UPPER(TRIM(AI91))="PIPE")),IF(OR(AG91="",AJ91="",AK91=""),"INFO",IF(AND(AG91&gt;=AJ91,AG91&lt;=AK91),"OK","CHECK")),IF(AG91="","INFO",IF(ABS(AG91)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI91" s="17">
+        <f>IF(A91="","",IF(E91="","",IFERROR(INDEX($B$4:$B$204,MATCH(E91,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ91" s="17">
+        <f>IF(A91="","",IF(OR(AND(UPPER(TRIM(B91))="SWALE",UPPER(TRIM(AI91))="PIPE"),AND(UPPER(TRIM(B91))="TRENCH",UPPER(TRIM(AI91))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK91" s="17">
+        <f>IF(A91="","",IF(OR(AND(UPPER(TRIM(B91))="SWALE",UPPER(TRIM(AI91))="PIPE"),AND(UPPER(TRIM(B91))="TRENCH",UPPER(TRIM(AI91))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL91" s="4">
+        <f>IF(A91="","",IF(E91="","TERMINAL",IF(OR(AND(UPPER(TRIM(B91))="SWALE",UPPER(TRIM(AI91))="PIPE"),AND(UPPER(TRIM(B91))="TRENCH",UPPER(TRIM(AI91))="PIPE")),IF(OR(AG91="",AJ91="",AK91=""),"INFO",IF(AND(AG91&gt;=AJ91,AG91&lt;=AK91),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16523,7 +18066,23 @@
         <v/>
       </c>
       <c r="AH92" s="4">
-        <f>IF(A92="","",IF(E92="","TERMINAL",IF(AG92="","INFO",IF(ABS(AG92)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A92="","",IF(E92="","TERMINAL",IF(OR(AND(UPPER(TRIM(B92))="SWALE",UPPER(TRIM(AI92))="PIPE"),AND(UPPER(TRIM(B92))="TRENCH",UPPER(TRIM(AI92))="PIPE")),IF(OR(AG92="",AJ92="",AK92=""),"INFO",IF(AND(AG92&gt;=AJ92,AG92&lt;=AK92),"OK","CHECK")),IF(AG92="","INFO",IF(ABS(AG92)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI92" s="17">
+        <f>IF(A92="","",IF(E92="","",IFERROR(INDEX($B$4:$B$204,MATCH(E92,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ92" s="17">
+        <f>IF(A92="","",IF(OR(AND(UPPER(TRIM(B92))="SWALE",UPPER(TRIM(AI92))="PIPE"),AND(UPPER(TRIM(B92))="TRENCH",UPPER(TRIM(AI92))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK92" s="17">
+        <f>IF(A92="","",IF(OR(AND(UPPER(TRIM(B92))="SWALE",UPPER(TRIM(AI92))="PIPE"),AND(UPPER(TRIM(B92))="TRENCH",UPPER(TRIM(AI92))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL92" s="4">
+        <f>IF(A92="","",IF(E92="","TERMINAL",IF(OR(AND(UPPER(TRIM(B92))="SWALE",UPPER(TRIM(AI92))="PIPE"),AND(UPPER(TRIM(B92))="TRENCH",UPPER(TRIM(AI92))="PIPE")),IF(OR(AG92="",AJ92="",AK92=""),"INFO",IF(AND(AG92&gt;=AJ92,AG92&lt;=AK92),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16618,7 +18177,23 @@
         <v/>
       </c>
       <c r="AH93" s="4">
-        <f>IF(A93="","",IF(E93="","TERMINAL",IF(AG93="","INFO",IF(ABS(AG93)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A93="","",IF(E93="","TERMINAL",IF(OR(AND(UPPER(TRIM(B93))="SWALE",UPPER(TRIM(AI93))="PIPE"),AND(UPPER(TRIM(B93))="TRENCH",UPPER(TRIM(AI93))="PIPE")),IF(OR(AG93="",AJ93="",AK93=""),"INFO",IF(AND(AG93&gt;=AJ93,AG93&lt;=AK93),"OK","CHECK")),IF(AG93="","INFO",IF(ABS(AG93)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI93" s="17">
+        <f>IF(A93="","",IF(E93="","",IFERROR(INDEX($B$4:$B$204,MATCH(E93,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ93" s="17">
+        <f>IF(A93="","",IF(OR(AND(UPPER(TRIM(B93))="SWALE",UPPER(TRIM(AI93))="PIPE"),AND(UPPER(TRIM(B93))="TRENCH",UPPER(TRIM(AI93))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK93" s="17">
+        <f>IF(A93="","",IF(OR(AND(UPPER(TRIM(B93))="SWALE",UPPER(TRIM(AI93))="PIPE"),AND(UPPER(TRIM(B93))="TRENCH",UPPER(TRIM(AI93))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL93" s="4">
+        <f>IF(A93="","",IF(E93="","TERMINAL",IF(OR(AND(UPPER(TRIM(B93))="SWALE",UPPER(TRIM(AI93))="PIPE"),AND(UPPER(TRIM(B93))="TRENCH",UPPER(TRIM(AI93))="PIPE")),IF(OR(AG93="",AJ93="",AK93=""),"INFO",IF(AND(AG93&gt;=AJ93,AG93&lt;=AK93),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16713,7 +18288,23 @@
         <v/>
       </c>
       <c r="AH94" s="4">
-        <f>IF(A94="","",IF(E94="","TERMINAL",IF(AG94="","INFO",IF(ABS(AG94)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A94="","",IF(E94="","TERMINAL",IF(OR(AND(UPPER(TRIM(B94))="SWALE",UPPER(TRIM(AI94))="PIPE"),AND(UPPER(TRIM(B94))="TRENCH",UPPER(TRIM(AI94))="PIPE")),IF(OR(AG94="",AJ94="",AK94=""),"INFO",IF(AND(AG94&gt;=AJ94,AG94&lt;=AK94),"OK","CHECK")),IF(AG94="","INFO",IF(ABS(AG94)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI94" s="17">
+        <f>IF(A94="","",IF(E94="","",IFERROR(INDEX($B$4:$B$204,MATCH(E94,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ94" s="17">
+        <f>IF(A94="","",IF(OR(AND(UPPER(TRIM(B94))="SWALE",UPPER(TRIM(AI94))="PIPE"),AND(UPPER(TRIM(B94))="TRENCH",UPPER(TRIM(AI94))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK94" s="17">
+        <f>IF(A94="","",IF(OR(AND(UPPER(TRIM(B94))="SWALE",UPPER(TRIM(AI94))="PIPE"),AND(UPPER(TRIM(B94))="TRENCH",UPPER(TRIM(AI94))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL94" s="4">
+        <f>IF(A94="","",IF(E94="","TERMINAL",IF(OR(AND(UPPER(TRIM(B94))="SWALE",UPPER(TRIM(AI94))="PIPE"),AND(UPPER(TRIM(B94))="TRENCH",UPPER(TRIM(AI94))="PIPE")),IF(OR(AG94="",AJ94="",AK94=""),"INFO",IF(AND(AG94&gt;=AJ94,AG94&lt;=AK94),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16808,7 +18399,23 @@
         <v/>
       </c>
       <c r="AH95" s="4">
-        <f>IF(A95="","",IF(E95="","TERMINAL",IF(AG95="","INFO",IF(ABS(AG95)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A95="","",IF(E95="","TERMINAL",IF(OR(AND(UPPER(TRIM(B95))="SWALE",UPPER(TRIM(AI95))="PIPE"),AND(UPPER(TRIM(B95))="TRENCH",UPPER(TRIM(AI95))="PIPE")),IF(OR(AG95="",AJ95="",AK95=""),"INFO",IF(AND(AG95&gt;=AJ95,AG95&lt;=AK95),"OK","CHECK")),IF(AG95="","INFO",IF(ABS(AG95)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI95" s="17">
+        <f>IF(A95="","",IF(E95="","",IFERROR(INDEX($B$4:$B$204,MATCH(E95,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ95" s="17">
+        <f>IF(A95="","",IF(OR(AND(UPPER(TRIM(B95))="SWALE",UPPER(TRIM(AI95))="PIPE"),AND(UPPER(TRIM(B95))="TRENCH",UPPER(TRIM(AI95))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK95" s="17">
+        <f>IF(A95="","",IF(OR(AND(UPPER(TRIM(B95))="SWALE",UPPER(TRIM(AI95))="PIPE"),AND(UPPER(TRIM(B95))="TRENCH",UPPER(TRIM(AI95))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL95" s="4">
+        <f>IF(A95="","",IF(E95="","TERMINAL",IF(OR(AND(UPPER(TRIM(B95))="SWALE",UPPER(TRIM(AI95))="PIPE"),AND(UPPER(TRIM(B95))="TRENCH",UPPER(TRIM(AI95))="PIPE")),IF(OR(AG95="",AJ95="",AK95=""),"INFO",IF(AND(AG95&gt;=AJ95,AG95&lt;=AK95),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16903,7 +18510,23 @@
         <v/>
       </c>
       <c r="AH96" s="4">
-        <f>IF(A96="","",IF(E96="","TERMINAL",IF(AG96="","INFO",IF(ABS(AG96)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A96="","",IF(E96="","TERMINAL",IF(OR(AND(UPPER(TRIM(B96))="SWALE",UPPER(TRIM(AI96))="PIPE"),AND(UPPER(TRIM(B96))="TRENCH",UPPER(TRIM(AI96))="PIPE")),IF(OR(AG96="",AJ96="",AK96=""),"INFO",IF(AND(AG96&gt;=AJ96,AG96&lt;=AK96),"OK","CHECK")),IF(AG96="","INFO",IF(ABS(AG96)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI96" s="17">
+        <f>IF(A96="","",IF(E96="","",IFERROR(INDEX($B$4:$B$204,MATCH(E96,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ96" s="17">
+        <f>IF(A96="","",IF(OR(AND(UPPER(TRIM(B96))="SWALE",UPPER(TRIM(AI96))="PIPE"),AND(UPPER(TRIM(B96))="TRENCH",UPPER(TRIM(AI96))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK96" s="17">
+        <f>IF(A96="","",IF(OR(AND(UPPER(TRIM(B96))="SWALE",UPPER(TRIM(AI96))="PIPE"),AND(UPPER(TRIM(B96))="TRENCH",UPPER(TRIM(AI96))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL96" s="4">
+        <f>IF(A96="","",IF(E96="","TERMINAL",IF(OR(AND(UPPER(TRIM(B96))="SWALE",UPPER(TRIM(AI96))="PIPE"),AND(UPPER(TRIM(B96))="TRENCH",UPPER(TRIM(AI96))="PIPE")),IF(OR(AG96="",AJ96="",AK96=""),"INFO",IF(AND(AG96&gt;=AJ96,AG96&lt;=AK96),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -16998,7 +18621,23 @@
         <v/>
       </c>
       <c r="AH97" s="4">
-        <f>IF(A97="","",IF(E97="","TERMINAL",IF(AG97="","INFO",IF(ABS(AG97)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A97="","",IF(E97="","TERMINAL",IF(OR(AND(UPPER(TRIM(B97))="SWALE",UPPER(TRIM(AI97))="PIPE"),AND(UPPER(TRIM(B97))="TRENCH",UPPER(TRIM(AI97))="PIPE")),IF(OR(AG97="",AJ97="",AK97=""),"INFO",IF(AND(AG97&gt;=AJ97,AG97&lt;=AK97),"OK","CHECK")),IF(AG97="","INFO",IF(ABS(AG97)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI97" s="17">
+        <f>IF(A97="","",IF(E97="","",IFERROR(INDEX($B$4:$B$204,MATCH(E97,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ97" s="17">
+        <f>IF(A97="","",IF(OR(AND(UPPER(TRIM(B97))="SWALE",UPPER(TRIM(AI97))="PIPE"),AND(UPPER(TRIM(B97))="TRENCH",UPPER(TRIM(AI97))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK97" s="17">
+        <f>IF(A97="","",IF(OR(AND(UPPER(TRIM(B97))="SWALE",UPPER(TRIM(AI97))="PIPE"),AND(UPPER(TRIM(B97))="TRENCH",UPPER(TRIM(AI97))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL97" s="4">
+        <f>IF(A97="","",IF(E97="","TERMINAL",IF(OR(AND(UPPER(TRIM(B97))="SWALE",UPPER(TRIM(AI97))="PIPE"),AND(UPPER(TRIM(B97))="TRENCH",UPPER(TRIM(AI97))="PIPE")),IF(OR(AG97="",AJ97="",AK97=""),"INFO",IF(AND(AG97&gt;=AJ97,AG97&lt;=AK97),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17093,7 +18732,23 @@
         <v/>
       </c>
       <c r="AH98" s="4">
-        <f>IF(A98="","",IF(E98="","TERMINAL",IF(AG98="","INFO",IF(ABS(AG98)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A98="","",IF(E98="","TERMINAL",IF(OR(AND(UPPER(TRIM(B98))="SWALE",UPPER(TRIM(AI98))="PIPE"),AND(UPPER(TRIM(B98))="TRENCH",UPPER(TRIM(AI98))="PIPE")),IF(OR(AG98="",AJ98="",AK98=""),"INFO",IF(AND(AG98&gt;=AJ98,AG98&lt;=AK98),"OK","CHECK")),IF(AG98="","INFO",IF(ABS(AG98)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI98" s="17">
+        <f>IF(A98="","",IF(E98="","",IFERROR(INDEX($B$4:$B$204,MATCH(E98,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ98" s="17">
+        <f>IF(A98="","",IF(OR(AND(UPPER(TRIM(B98))="SWALE",UPPER(TRIM(AI98))="PIPE"),AND(UPPER(TRIM(B98))="TRENCH",UPPER(TRIM(AI98))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK98" s="17">
+        <f>IF(A98="","",IF(OR(AND(UPPER(TRIM(B98))="SWALE",UPPER(TRIM(AI98))="PIPE"),AND(UPPER(TRIM(B98))="TRENCH",UPPER(TRIM(AI98))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL98" s="4">
+        <f>IF(A98="","",IF(E98="","TERMINAL",IF(OR(AND(UPPER(TRIM(B98))="SWALE",UPPER(TRIM(AI98))="PIPE"),AND(UPPER(TRIM(B98))="TRENCH",UPPER(TRIM(AI98))="PIPE")),IF(OR(AG98="",AJ98="",AK98=""),"INFO",IF(AND(AG98&gt;=AJ98,AG98&lt;=AK98),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17188,7 +18843,23 @@
         <v/>
       </c>
       <c r="AH99" s="4">
-        <f>IF(A99="","",IF(E99="","TERMINAL",IF(AG99="","INFO",IF(ABS(AG99)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A99="","",IF(E99="","TERMINAL",IF(OR(AND(UPPER(TRIM(B99))="SWALE",UPPER(TRIM(AI99))="PIPE"),AND(UPPER(TRIM(B99))="TRENCH",UPPER(TRIM(AI99))="PIPE")),IF(OR(AG99="",AJ99="",AK99=""),"INFO",IF(AND(AG99&gt;=AJ99,AG99&lt;=AK99),"OK","CHECK")),IF(AG99="","INFO",IF(ABS(AG99)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI99" s="17">
+        <f>IF(A99="","",IF(E99="","",IFERROR(INDEX($B$4:$B$204,MATCH(E99,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ99" s="17">
+        <f>IF(A99="","",IF(OR(AND(UPPER(TRIM(B99))="SWALE",UPPER(TRIM(AI99))="PIPE"),AND(UPPER(TRIM(B99))="TRENCH",UPPER(TRIM(AI99))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK99" s="17">
+        <f>IF(A99="","",IF(OR(AND(UPPER(TRIM(B99))="SWALE",UPPER(TRIM(AI99))="PIPE"),AND(UPPER(TRIM(B99))="TRENCH",UPPER(TRIM(AI99))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL99" s="4">
+        <f>IF(A99="","",IF(E99="","TERMINAL",IF(OR(AND(UPPER(TRIM(B99))="SWALE",UPPER(TRIM(AI99))="PIPE"),AND(UPPER(TRIM(B99))="TRENCH",UPPER(TRIM(AI99))="PIPE")),IF(OR(AG99="",AJ99="",AK99=""),"INFO",IF(AND(AG99&gt;=AJ99,AG99&lt;=AK99),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17283,7 +18954,23 @@
         <v/>
       </c>
       <c r="AH100" s="4">
-        <f>IF(A100="","",IF(E100="","TERMINAL",IF(AG100="","INFO",IF(ABS(AG100)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A100="","",IF(E100="","TERMINAL",IF(OR(AND(UPPER(TRIM(B100))="SWALE",UPPER(TRIM(AI100))="PIPE"),AND(UPPER(TRIM(B100))="TRENCH",UPPER(TRIM(AI100))="PIPE")),IF(OR(AG100="",AJ100="",AK100=""),"INFO",IF(AND(AG100&gt;=AJ100,AG100&lt;=AK100),"OK","CHECK")),IF(AG100="","INFO",IF(ABS(AG100)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI100" s="17">
+        <f>IF(A100="","",IF(E100="","",IFERROR(INDEX($B$4:$B$204,MATCH(E100,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ100" s="17">
+        <f>IF(A100="","",IF(OR(AND(UPPER(TRIM(B100))="SWALE",UPPER(TRIM(AI100))="PIPE"),AND(UPPER(TRIM(B100))="TRENCH",UPPER(TRIM(AI100))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK100" s="17">
+        <f>IF(A100="","",IF(OR(AND(UPPER(TRIM(B100))="SWALE",UPPER(TRIM(AI100))="PIPE"),AND(UPPER(TRIM(B100))="TRENCH",UPPER(TRIM(AI100))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL100" s="4">
+        <f>IF(A100="","",IF(E100="","TERMINAL",IF(OR(AND(UPPER(TRIM(B100))="SWALE",UPPER(TRIM(AI100))="PIPE"),AND(UPPER(TRIM(B100))="TRENCH",UPPER(TRIM(AI100))="PIPE")),IF(OR(AG100="",AJ100="",AK100=""),"INFO",IF(AND(AG100&gt;=AJ100,AG100&lt;=AK100),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17378,7 +19065,23 @@
         <v/>
       </c>
       <c r="AH101" s="4">
-        <f>IF(A101="","",IF(E101="","TERMINAL",IF(AG101="","INFO",IF(ABS(AG101)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A101="","",IF(E101="","TERMINAL",IF(OR(AND(UPPER(TRIM(B101))="SWALE",UPPER(TRIM(AI101))="PIPE"),AND(UPPER(TRIM(B101))="TRENCH",UPPER(TRIM(AI101))="PIPE")),IF(OR(AG101="",AJ101="",AK101=""),"INFO",IF(AND(AG101&gt;=AJ101,AG101&lt;=AK101),"OK","CHECK")),IF(AG101="","INFO",IF(ABS(AG101)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI101" s="17">
+        <f>IF(A101="","",IF(E101="","",IFERROR(INDEX($B$4:$B$204,MATCH(E101,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ101" s="17">
+        <f>IF(A101="","",IF(OR(AND(UPPER(TRIM(B101))="SWALE",UPPER(TRIM(AI101))="PIPE"),AND(UPPER(TRIM(B101))="TRENCH",UPPER(TRIM(AI101))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK101" s="17">
+        <f>IF(A101="","",IF(OR(AND(UPPER(TRIM(B101))="SWALE",UPPER(TRIM(AI101))="PIPE"),AND(UPPER(TRIM(B101))="TRENCH",UPPER(TRIM(AI101))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL101" s="4">
+        <f>IF(A101="","",IF(E101="","TERMINAL",IF(OR(AND(UPPER(TRIM(B101))="SWALE",UPPER(TRIM(AI101))="PIPE"),AND(UPPER(TRIM(B101))="TRENCH",UPPER(TRIM(AI101))="PIPE")),IF(OR(AG101="",AJ101="",AK101=""),"INFO",IF(AND(AG101&gt;=AJ101,AG101&lt;=AK101),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17473,7 +19176,23 @@
         <v/>
       </c>
       <c r="AH102" s="4">
-        <f>IF(A102="","",IF(E102="","TERMINAL",IF(AG102="","INFO",IF(ABS(AG102)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A102="","",IF(E102="","TERMINAL",IF(OR(AND(UPPER(TRIM(B102))="SWALE",UPPER(TRIM(AI102))="PIPE"),AND(UPPER(TRIM(B102))="TRENCH",UPPER(TRIM(AI102))="PIPE")),IF(OR(AG102="",AJ102="",AK102=""),"INFO",IF(AND(AG102&gt;=AJ102,AG102&lt;=AK102),"OK","CHECK")),IF(AG102="","INFO",IF(ABS(AG102)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI102" s="17">
+        <f>IF(A102="","",IF(E102="","",IFERROR(INDEX($B$4:$B$204,MATCH(E102,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ102" s="17">
+        <f>IF(A102="","",IF(OR(AND(UPPER(TRIM(B102))="SWALE",UPPER(TRIM(AI102))="PIPE"),AND(UPPER(TRIM(B102))="TRENCH",UPPER(TRIM(AI102))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK102" s="17">
+        <f>IF(A102="","",IF(OR(AND(UPPER(TRIM(B102))="SWALE",UPPER(TRIM(AI102))="PIPE"),AND(UPPER(TRIM(B102))="TRENCH",UPPER(TRIM(AI102))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL102" s="4">
+        <f>IF(A102="","",IF(E102="","TERMINAL",IF(OR(AND(UPPER(TRIM(B102))="SWALE",UPPER(TRIM(AI102))="PIPE"),AND(UPPER(TRIM(B102))="TRENCH",UPPER(TRIM(AI102))="PIPE")),IF(OR(AG102="",AJ102="",AK102=""),"INFO",IF(AND(AG102&gt;=AJ102,AG102&lt;=AK102),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17568,7 +19287,23 @@
         <v/>
       </c>
       <c r="AH103" s="4">
-        <f>IF(A103="","",IF(E103="","TERMINAL",IF(AG103="","INFO",IF(ABS(AG103)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A103="","",IF(E103="","TERMINAL",IF(OR(AND(UPPER(TRIM(B103))="SWALE",UPPER(TRIM(AI103))="PIPE"),AND(UPPER(TRIM(B103))="TRENCH",UPPER(TRIM(AI103))="PIPE")),IF(OR(AG103="",AJ103="",AK103=""),"INFO",IF(AND(AG103&gt;=AJ103,AG103&lt;=AK103),"OK","CHECK")),IF(AG103="","INFO",IF(ABS(AG103)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI103" s="17">
+        <f>IF(A103="","",IF(E103="","",IFERROR(INDEX($B$4:$B$204,MATCH(E103,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ103" s="17">
+        <f>IF(A103="","",IF(OR(AND(UPPER(TRIM(B103))="SWALE",UPPER(TRIM(AI103))="PIPE"),AND(UPPER(TRIM(B103))="TRENCH",UPPER(TRIM(AI103))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK103" s="17">
+        <f>IF(A103="","",IF(OR(AND(UPPER(TRIM(B103))="SWALE",UPPER(TRIM(AI103))="PIPE"),AND(UPPER(TRIM(B103))="TRENCH",UPPER(TRIM(AI103))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL103" s="4">
+        <f>IF(A103="","",IF(E103="","TERMINAL",IF(OR(AND(UPPER(TRIM(B103))="SWALE",UPPER(TRIM(AI103))="PIPE"),AND(UPPER(TRIM(B103))="TRENCH",UPPER(TRIM(AI103))="PIPE")),IF(OR(AG103="",AJ103="",AK103=""),"INFO",IF(AND(AG103&gt;=AJ103,AG103&lt;=AK103),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17663,7 +19398,23 @@
         <v/>
       </c>
       <c r="AH104" s="4">
-        <f>IF(A104="","",IF(E104="","TERMINAL",IF(AG104="","INFO",IF(ABS(AG104)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A104="","",IF(E104="","TERMINAL",IF(OR(AND(UPPER(TRIM(B104))="SWALE",UPPER(TRIM(AI104))="PIPE"),AND(UPPER(TRIM(B104))="TRENCH",UPPER(TRIM(AI104))="PIPE")),IF(OR(AG104="",AJ104="",AK104=""),"INFO",IF(AND(AG104&gt;=AJ104,AG104&lt;=AK104),"OK","CHECK")),IF(AG104="","INFO",IF(ABS(AG104)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI104" s="17">
+        <f>IF(A104="","",IF(E104="","",IFERROR(INDEX($B$4:$B$204,MATCH(E104,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ104" s="17">
+        <f>IF(A104="","",IF(OR(AND(UPPER(TRIM(B104))="SWALE",UPPER(TRIM(AI104))="PIPE"),AND(UPPER(TRIM(B104))="TRENCH",UPPER(TRIM(AI104))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK104" s="17">
+        <f>IF(A104="","",IF(OR(AND(UPPER(TRIM(B104))="SWALE",UPPER(TRIM(AI104))="PIPE"),AND(UPPER(TRIM(B104))="TRENCH",UPPER(TRIM(AI104))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL104" s="4">
+        <f>IF(A104="","",IF(E104="","TERMINAL",IF(OR(AND(UPPER(TRIM(B104))="SWALE",UPPER(TRIM(AI104))="PIPE"),AND(UPPER(TRIM(B104))="TRENCH",UPPER(TRIM(AI104))="PIPE")),IF(OR(AG104="",AJ104="",AK104=""),"INFO",IF(AND(AG104&gt;=AJ104,AG104&lt;=AK104),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17758,7 +19509,23 @@
         <v/>
       </c>
       <c r="AH105" s="4">
-        <f>IF(A105="","",IF(E105="","TERMINAL",IF(AG105="","INFO",IF(ABS(AG105)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A105="","",IF(E105="","TERMINAL",IF(OR(AND(UPPER(TRIM(B105))="SWALE",UPPER(TRIM(AI105))="PIPE"),AND(UPPER(TRIM(B105))="TRENCH",UPPER(TRIM(AI105))="PIPE")),IF(OR(AG105="",AJ105="",AK105=""),"INFO",IF(AND(AG105&gt;=AJ105,AG105&lt;=AK105),"OK","CHECK")),IF(AG105="","INFO",IF(ABS(AG105)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI105" s="17">
+        <f>IF(A105="","",IF(E105="","",IFERROR(INDEX($B$4:$B$204,MATCH(E105,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ105" s="17">
+        <f>IF(A105="","",IF(OR(AND(UPPER(TRIM(B105))="SWALE",UPPER(TRIM(AI105))="PIPE"),AND(UPPER(TRIM(B105))="TRENCH",UPPER(TRIM(AI105))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK105" s="17">
+        <f>IF(A105="","",IF(OR(AND(UPPER(TRIM(B105))="SWALE",UPPER(TRIM(AI105))="PIPE"),AND(UPPER(TRIM(B105))="TRENCH",UPPER(TRIM(AI105))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL105" s="4">
+        <f>IF(A105="","",IF(E105="","TERMINAL",IF(OR(AND(UPPER(TRIM(B105))="SWALE",UPPER(TRIM(AI105))="PIPE"),AND(UPPER(TRIM(B105))="TRENCH",UPPER(TRIM(AI105))="PIPE")),IF(OR(AG105="",AJ105="",AK105=""),"INFO",IF(AND(AG105&gt;=AJ105,AG105&lt;=AK105),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17853,7 +19620,23 @@
         <v/>
       </c>
       <c r="AH106" s="4">
-        <f>IF(A106="","",IF(E106="","TERMINAL",IF(AG106="","INFO",IF(ABS(AG106)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A106="","",IF(E106="","TERMINAL",IF(OR(AND(UPPER(TRIM(B106))="SWALE",UPPER(TRIM(AI106))="PIPE"),AND(UPPER(TRIM(B106))="TRENCH",UPPER(TRIM(AI106))="PIPE")),IF(OR(AG106="",AJ106="",AK106=""),"INFO",IF(AND(AG106&gt;=AJ106,AG106&lt;=AK106),"OK","CHECK")),IF(AG106="","INFO",IF(ABS(AG106)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI106" s="17">
+        <f>IF(A106="","",IF(E106="","",IFERROR(INDEX($B$4:$B$204,MATCH(E106,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ106" s="17">
+        <f>IF(A106="","",IF(OR(AND(UPPER(TRIM(B106))="SWALE",UPPER(TRIM(AI106))="PIPE"),AND(UPPER(TRIM(B106))="TRENCH",UPPER(TRIM(AI106))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK106" s="17">
+        <f>IF(A106="","",IF(OR(AND(UPPER(TRIM(B106))="SWALE",UPPER(TRIM(AI106))="PIPE"),AND(UPPER(TRIM(B106))="TRENCH",UPPER(TRIM(AI106))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL106" s="4">
+        <f>IF(A106="","",IF(E106="","TERMINAL",IF(OR(AND(UPPER(TRIM(B106))="SWALE",UPPER(TRIM(AI106))="PIPE"),AND(UPPER(TRIM(B106))="TRENCH",UPPER(TRIM(AI106))="PIPE")),IF(OR(AG106="",AJ106="",AK106=""),"INFO",IF(AND(AG106&gt;=AJ106,AG106&lt;=AK106),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -17948,7 +19731,23 @@
         <v/>
       </c>
       <c r="AH107" s="4">
-        <f>IF(A107="","",IF(E107="","TERMINAL",IF(AG107="","INFO",IF(ABS(AG107)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A107="","",IF(E107="","TERMINAL",IF(OR(AND(UPPER(TRIM(B107))="SWALE",UPPER(TRIM(AI107))="PIPE"),AND(UPPER(TRIM(B107))="TRENCH",UPPER(TRIM(AI107))="PIPE")),IF(OR(AG107="",AJ107="",AK107=""),"INFO",IF(AND(AG107&gt;=AJ107,AG107&lt;=AK107),"OK","CHECK")),IF(AG107="","INFO",IF(ABS(AG107)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI107" s="17">
+        <f>IF(A107="","",IF(E107="","",IFERROR(INDEX($B$4:$B$204,MATCH(E107,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ107" s="17">
+        <f>IF(A107="","",IF(OR(AND(UPPER(TRIM(B107))="SWALE",UPPER(TRIM(AI107))="PIPE"),AND(UPPER(TRIM(B107))="TRENCH",UPPER(TRIM(AI107))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK107" s="17">
+        <f>IF(A107="","",IF(OR(AND(UPPER(TRIM(B107))="SWALE",UPPER(TRIM(AI107))="PIPE"),AND(UPPER(TRIM(B107))="TRENCH",UPPER(TRIM(AI107))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL107" s="4">
+        <f>IF(A107="","",IF(E107="","TERMINAL",IF(OR(AND(UPPER(TRIM(B107))="SWALE",UPPER(TRIM(AI107))="PIPE"),AND(UPPER(TRIM(B107))="TRENCH",UPPER(TRIM(AI107))="PIPE")),IF(OR(AG107="",AJ107="",AK107=""),"INFO",IF(AND(AG107&gt;=AJ107,AG107&lt;=AK107),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18043,7 +19842,23 @@
         <v/>
       </c>
       <c r="AH108" s="4">
-        <f>IF(A108="","",IF(E108="","TERMINAL",IF(AG108="","INFO",IF(ABS(AG108)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A108="","",IF(E108="","TERMINAL",IF(OR(AND(UPPER(TRIM(B108))="SWALE",UPPER(TRIM(AI108))="PIPE"),AND(UPPER(TRIM(B108))="TRENCH",UPPER(TRIM(AI108))="PIPE")),IF(OR(AG108="",AJ108="",AK108=""),"INFO",IF(AND(AG108&gt;=AJ108,AG108&lt;=AK108),"OK","CHECK")),IF(AG108="","INFO",IF(ABS(AG108)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI108" s="17">
+        <f>IF(A108="","",IF(E108="","",IFERROR(INDEX($B$4:$B$204,MATCH(E108,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ108" s="17">
+        <f>IF(A108="","",IF(OR(AND(UPPER(TRIM(B108))="SWALE",UPPER(TRIM(AI108))="PIPE"),AND(UPPER(TRIM(B108))="TRENCH",UPPER(TRIM(AI108))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK108" s="17">
+        <f>IF(A108="","",IF(OR(AND(UPPER(TRIM(B108))="SWALE",UPPER(TRIM(AI108))="PIPE"),AND(UPPER(TRIM(B108))="TRENCH",UPPER(TRIM(AI108))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL108" s="4">
+        <f>IF(A108="","",IF(E108="","TERMINAL",IF(OR(AND(UPPER(TRIM(B108))="SWALE",UPPER(TRIM(AI108))="PIPE"),AND(UPPER(TRIM(B108))="TRENCH",UPPER(TRIM(AI108))="PIPE")),IF(OR(AG108="",AJ108="",AK108=""),"INFO",IF(AND(AG108&gt;=AJ108,AG108&lt;=AK108),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18138,7 +19953,23 @@
         <v/>
       </c>
       <c r="AH109" s="4">
-        <f>IF(A109="","",IF(E109="","TERMINAL",IF(AG109="","INFO",IF(ABS(AG109)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A109="","",IF(E109="","TERMINAL",IF(OR(AND(UPPER(TRIM(B109))="SWALE",UPPER(TRIM(AI109))="PIPE"),AND(UPPER(TRIM(B109))="TRENCH",UPPER(TRIM(AI109))="PIPE")),IF(OR(AG109="",AJ109="",AK109=""),"INFO",IF(AND(AG109&gt;=AJ109,AG109&lt;=AK109),"OK","CHECK")),IF(AG109="","INFO",IF(ABS(AG109)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI109" s="17">
+        <f>IF(A109="","",IF(E109="","",IFERROR(INDEX($B$4:$B$204,MATCH(E109,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ109" s="17">
+        <f>IF(A109="","",IF(OR(AND(UPPER(TRIM(B109))="SWALE",UPPER(TRIM(AI109))="PIPE"),AND(UPPER(TRIM(B109))="TRENCH",UPPER(TRIM(AI109))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK109" s="17">
+        <f>IF(A109="","",IF(OR(AND(UPPER(TRIM(B109))="SWALE",UPPER(TRIM(AI109))="PIPE"),AND(UPPER(TRIM(B109))="TRENCH",UPPER(TRIM(AI109))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL109" s="4">
+        <f>IF(A109="","",IF(E109="","TERMINAL",IF(OR(AND(UPPER(TRIM(B109))="SWALE",UPPER(TRIM(AI109))="PIPE"),AND(UPPER(TRIM(B109))="TRENCH",UPPER(TRIM(AI109))="PIPE")),IF(OR(AG109="",AJ109="",AK109=""),"INFO",IF(AND(AG109&gt;=AJ109,AG109&lt;=AK109),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18233,7 +20064,23 @@
         <v/>
       </c>
       <c r="AH110" s="4">
-        <f>IF(A110="","",IF(E110="","TERMINAL",IF(AG110="","INFO",IF(ABS(AG110)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A110="","",IF(E110="","TERMINAL",IF(OR(AND(UPPER(TRIM(B110))="SWALE",UPPER(TRIM(AI110))="PIPE"),AND(UPPER(TRIM(B110))="TRENCH",UPPER(TRIM(AI110))="PIPE")),IF(OR(AG110="",AJ110="",AK110=""),"INFO",IF(AND(AG110&gt;=AJ110,AG110&lt;=AK110),"OK","CHECK")),IF(AG110="","INFO",IF(ABS(AG110)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI110" s="17">
+        <f>IF(A110="","",IF(E110="","",IFERROR(INDEX($B$4:$B$204,MATCH(E110,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ110" s="17">
+        <f>IF(A110="","",IF(OR(AND(UPPER(TRIM(B110))="SWALE",UPPER(TRIM(AI110))="PIPE"),AND(UPPER(TRIM(B110))="TRENCH",UPPER(TRIM(AI110))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK110" s="17">
+        <f>IF(A110="","",IF(OR(AND(UPPER(TRIM(B110))="SWALE",UPPER(TRIM(AI110))="PIPE"),AND(UPPER(TRIM(B110))="TRENCH",UPPER(TRIM(AI110))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL110" s="4">
+        <f>IF(A110="","",IF(E110="","TERMINAL",IF(OR(AND(UPPER(TRIM(B110))="SWALE",UPPER(TRIM(AI110))="PIPE"),AND(UPPER(TRIM(B110))="TRENCH",UPPER(TRIM(AI110))="PIPE")),IF(OR(AG110="",AJ110="",AK110=""),"INFO",IF(AND(AG110&gt;=AJ110,AG110&lt;=AK110),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18328,7 +20175,23 @@
         <v/>
       </c>
       <c r="AH111" s="4">
-        <f>IF(A111="","",IF(E111="","TERMINAL",IF(AG111="","INFO",IF(ABS(AG111)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A111="","",IF(E111="","TERMINAL",IF(OR(AND(UPPER(TRIM(B111))="SWALE",UPPER(TRIM(AI111))="PIPE"),AND(UPPER(TRIM(B111))="TRENCH",UPPER(TRIM(AI111))="PIPE")),IF(OR(AG111="",AJ111="",AK111=""),"INFO",IF(AND(AG111&gt;=AJ111,AG111&lt;=AK111),"OK","CHECK")),IF(AG111="","INFO",IF(ABS(AG111)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI111" s="17">
+        <f>IF(A111="","",IF(E111="","",IFERROR(INDEX($B$4:$B$204,MATCH(E111,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ111" s="17">
+        <f>IF(A111="","",IF(OR(AND(UPPER(TRIM(B111))="SWALE",UPPER(TRIM(AI111))="PIPE"),AND(UPPER(TRIM(B111))="TRENCH",UPPER(TRIM(AI111))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK111" s="17">
+        <f>IF(A111="","",IF(OR(AND(UPPER(TRIM(B111))="SWALE",UPPER(TRIM(AI111))="PIPE"),AND(UPPER(TRIM(B111))="TRENCH",UPPER(TRIM(AI111))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL111" s="4">
+        <f>IF(A111="","",IF(E111="","TERMINAL",IF(OR(AND(UPPER(TRIM(B111))="SWALE",UPPER(TRIM(AI111))="PIPE"),AND(UPPER(TRIM(B111))="TRENCH",UPPER(TRIM(AI111))="PIPE")),IF(OR(AG111="",AJ111="",AK111=""),"INFO",IF(AND(AG111&gt;=AJ111,AG111&lt;=AK111),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18423,7 +20286,23 @@
         <v/>
       </c>
       <c r="AH112" s="4">
-        <f>IF(A112="","",IF(E112="","TERMINAL",IF(AG112="","INFO",IF(ABS(AG112)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A112="","",IF(E112="","TERMINAL",IF(OR(AND(UPPER(TRIM(B112))="SWALE",UPPER(TRIM(AI112))="PIPE"),AND(UPPER(TRIM(B112))="TRENCH",UPPER(TRIM(AI112))="PIPE")),IF(OR(AG112="",AJ112="",AK112=""),"INFO",IF(AND(AG112&gt;=AJ112,AG112&lt;=AK112),"OK","CHECK")),IF(AG112="","INFO",IF(ABS(AG112)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI112" s="17">
+        <f>IF(A112="","",IF(E112="","",IFERROR(INDEX($B$4:$B$204,MATCH(E112,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ112" s="17">
+        <f>IF(A112="","",IF(OR(AND(UPPER(TRIM(B112))="SWALE",UPPER(TRIM(AI112))="PIPE"),AND(UPPER(TRIM(B112))="TRENCH",UPPER(TRIM(AI112))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK112" s="17">
+        <f>IF(A112="","",IF(OR(AND(UPPER(TRIM(B112))="SWALE",UPPER(TRIM(AI112))="PIPE"),AND(UPPER(TRIM(B112))="TRENCH",UPPER(TRIM(AI112))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL112" s="4">
+        <f>IF(A112="","",IF(E112="","TERMINAL",IF(OR(AND(UPPER(TRIM(B112))="SWALE",UPPER(TRIM(AI112))="PIPE"),AND(UPPER(TRIM(B112))="TRENCH",UPPER(TRIM(AI112))="PIPE")),IF(OR(AG112="",AJ112="",AK112=""),"INFO",IF(AND(AG112&gt;=AJ112,AG112&lt;=AK112),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18518,7 +20397,23 @@
         <v/>
       </c>
       <c r="AH113" s="4">
-        <f>IF(A113="","",IF(E113="","TERMINAL",IF(AG113="","INFO",IF(ABS(AG113)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A113="","",IF(E113="","TERMINAL",IF(OR(AND(UPPER(TRIM(B113))="SWALE",UPPER(TRIM(AI113))="PIPE"),AND(UPPER(TRIM(B113))="TRENCH",UPPER(TRIM(AI113))="PIPE")),IF(OR(AG113="",AJ113="",AK113=""),"INFO",IF(AND(AG113&gt;=AJ113,AG113&lt;=AK113),"OK","CHECK")),IF(AG113="","INFO",IF(ABS(AG113)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI113" s="17">
+        <f>IF(A113="","",IF(E113="","",IFERROR(INDEX($B$4:$B$204,MATCH(E113,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ113" s="17">
+        <f>IF(A113="","",IF(OR(AND(UPPER(TRIM(B113))="SWALE",UPPER(TRIM(AI113))="PIPE"),AND(UPPER(TRIM(B113))="TRENCH",UPPER(TRIM(AI113))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK113" s="17">
+        <f>IF(A113="","",IF(OR(AND(UPPER(TRIM(B113))="SWALE",UPPER(TRIM(AI113))="PIPE"),AND(UPPER(TRIM(B113))="TRENCH",UPPER(TRIM(AI113))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL113" s="4">
+        <f>IF(A113="","",IF(E113="","TERMINAL",IF(OR(AND(UPPER(TRIM(B113))="SWALE",UPPER(TRIM(AI113))="PIPE"),AND(UPPER(TRIM(B113))="TRENCH",UPPER(TRIM(AI113))="PIPE")),IF(OR(AG113="",AJ113="",AK113=""),"INFO",IF(AND(AG113&gt;=AJ113,AG113&lt;=AK113),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18613,7 +20508,23 @@
         <v/>
       </c>
       <c r="AH114" s="4">
-        <f>IF(A114="","",IF(E114="","TERMINAL",IF(AG114="","INFO",IF(ABS(AG114)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A114="","",IF(E114="","TERMINAL",IF(OR(AND(UPPER(TRIM(B114))="SWALE",UPPER(TRIM(AI114))="PIPE"),AND(UPPER(TRIM(B114))="TRENCH",UPPER(TRIM(AI114))="PIPE")),IF(OR(AG114="",AJ114="",AK114=""),"INFO",IF(AND(AG114&gt;=AJ114,AG114&lt;=AK114),"OK","CHECK")),IF(AG114="","INFO",IF(ABS(AG114)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI114" s="17">
+        <f>IF(A114="","",IF(E114="","",IFERROR(INDEX($B$4:$B$204,MATCH(E114,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ114" s="17">
+        <f>IF(A114="","",IF(OR(AND(UPPER(TRIM(B114))="SWALE",UPPER(TRIM(AI114))="PIPE"),AND(UPPER(TRIM(B114))="TRENCH",UPPER(TRIM(AI114))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK114" s="17">
+        <f>IF(A114="","",IF(OR(AND(UPPER(TRIM(B114))="SWALE",UPPER(TRIM(AI114))="PIPE"),AND(UPPER(TRIM(B114))="TRENCH",UPPER(TRIM(AI114))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL114" s="4">
+        <f>IF(A114="","",IF(E114="","TERMINAL",IF(OR(AND(UPPER(TRIM(B114))="SWALE",UPPER(TRIM(AI114))="PIPE"),AND(UPPER(TRIM(B114))="TRENCH",UPPER(TRIM(AI114))="PIPE")),IF(OR(AG114="",AJ114="",AK114=""),"INFO",IF(AND(AG114&gt;=AJ114,AG114&lt;=AK114),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18708,7 +20619,23 @@
         <v/>
       </c>
       <c r="AH115" s="4">
-        <f>IF(A115="","",IF(E115="","TERMINAL",IF(AG115="","INFO",IF(ABS(AG115)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A115="","",IF(E115="","TERMINAL",IF(OR(AND(UPPER(TRIM(B115))="SWALE",UPPER(TRIM(AI115))="PIPE"),AND(UPPER(TRIM(B115))="TRENCH",UPPER(TRIM(AI115))="PIPE")),IF(OR(AG115="",AJ115="",AK115=""),"INFO",IF(AND(AG115&gt;=AJ115,AG115&lt;=AK115),"OK","CHECK")),IF(AG115="","INFO",IF(ABS(AG115)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI115" s="17">
+        <f>IF(A115="","",IF(E115="","",IFERROR(INDEX($B$4:$B$204,MATCH(E115,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ115" s="17">
+        <f>IF(A115="","",IF(OR(AND(UPPER(TRIM(B115))="SWALE",UPPER(TRIM(AI115))="PIPE"),AND(UPPER(TRIM(B115))="TRENCH",UPPER(TRIM(AI115))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK115" s="17">
+        <f>IF(A115="","",IF(OR(AND(UPPER(TRIM(B115))="SWALE",UPPER(TRIM(AI115))="PIPE"),AND(UPPER(TRIM(B115))="TRENCH",UPPER(TRIM(AI115))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL115" s="4">
+        <f>IF(A115="","",IF(E115="","TERMINAL",IF(OR(AND(UPPER(TRIM(B115))="SWALE",UPPER(TRIM(AI115))="PIPE"),AND(UPPER(TRIM(B115))="TRENCH",UPPER(TRIM(AI115))="PIPE")),IF(OR(AG115="",AJ115="",AK115=""),"INFO",IF(AND(AG115&gt;=AJ115,AG115&lt;=AK115),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18803,7 +20730,23 @@
         <v/>
       </c>
       <c r="AH116" s="4">
-        <f>IF(A116="","",IF(E116="","TERMINAL",IF(AG116="","INFO",IF(ABS(AG116)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A116="","",IF(E116="","TERMINAL",IF(OR(AND(UPPER(TRIM(B116))="SWALE",UPPER(TRIM(AI116))="PIPE"),AND(UPPER(TRIM(B116))="TRENCH",UPPER(TRIM(AI116))="PIPE")),IF(OR(AG116="",AJ116="",AK116=""),"INFO",IF(AND(AG116&gt;=AJ116,AG116&lt;=AK116),"OK","CHECK")),IF(AG116="","INFO",IF(ABS(AG116)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI116" s="17">
+        <f>IF(A116="","",IF(E116="","",IFERROR(INDEX($B$4:$B$204,MATCH(E116,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ116" s="17">
+        <f>IF(A116="","",IF(OR(AND(UPPER(TRIM(B116))="SWALE",UPPER(TRIM(AI116))="PIPE"),AND(UPPER(TRIM(B116))="TRENCH",UPPER(TRIM(AI116))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK116" s="17">
+        <f>IF(A116="","",IF(OR(AND(UPPER(TRIM(B116))="SWALE",UPPER(TRIM(AI116))="PIPE"),AND(UPPER(TRIM(B116))="TRENCH",UPPER(TRIM(AI116))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL116" s="4">
+        <f>IF(A116="","",IF(E116="","TERMINAL",IF(OR(AND(UPPER(TRIM(B116))="SWALE",UPPER(TRIM(AI116))="PIPE"),AND(UPPER(TRIM(B116))="TRENCH",UPPER(TRIM(AI116))="PIPE")),IF(OR(AG116="",AJ116="",AK116=""),"INFO",IF(AND(AG116&gt;=AJ116,AG116&lt;=AK116),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18898,7 +20841,23 @@
         <v/>
       </c>
       <c r="AH117" s="4">
-        <f>IF(A117="","",IF(E117="","TERMINAL",IF(AG117="","INFO",IF(ABS(AG117)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A117="","",IF(E117="","TERMINAL",IF(OR(AND(UPPER(TRIM(B117))="SWALE",UPPER(TRIM(AI117))="PIPE"),AND(UPPER(TRIM(B117))="TRENCH",UPPER(TRIM(AI117))="PIPE")),IF(OR(AG117="",AJ117="",AK117=""),"INFO",IF(AND(AG117&gt;=AJ117,AG117&lt;=AK117),"OK","CHECK")),IF(AG117="","INFO",IF(ABS(AG117)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI117" s="17">
+        <f>IF(A117="","",IF(E117="","",IFERROR(INDEX($B$4:$B$204,MATCH(E117,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ117" s="17">
+        <f>IF(A117="","",IF(OR(AND(UPPER(TRIM(B117))="SWALE",UPPER(TRIM(AI117))="PIPE"),AND(UPPER(TRIM(B117))="TRENCH",UPPER(TRIM(AI117))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK117" s="17">
+        <f>IF(A117="","",IF(OR(AND(UPPER(TRIM(B117))="SWALE",UPPER(TRIM(AI117))="PIPE"),AND(UPPER(TRIM(B117))="TRENCH",UPPER(TRIM(AI117))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL117" s="4">
+        <f>IF(A117="","",IF(E117="","TERMINAL",IF(OR(AND(UPPER(TRIM(B117))="SWALE",UPPER(TRIM(AI117))="PIPE"),AND(UPPER(TRIM(B117))="TRENCH",UPPER(TRIM(AI117))="PIPE")),IF(OR(AG117="",AJ117="",AK117=""),"INFO",IF(AND(AG117&gt;=AJ117,AG117&lt;=AK117),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -18993,7 +20952,23 @@
         <v/>
       </c>
       <c r="AH118" s="4">
-        <f>IF(A118="","",IF(E118="","TERMINAL",IF(AG118="","INFO",IF(ABS(AG118)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A118="","",IF(E118="","TERMINAL",IF(OR(AND(UPPER(TRIM(B118))="SWALE",UPPER(TRIM(AI118))="PIPE"),AND(UPPER(TRIM(B118))="TRENCH",UPPER(TRIM(AI118))="PIPE")),IF(OR(AG118="",AJ118="",AK118=""),"INFO",IF(AND(AG118&gt;=AJ118,AG118&lt;=AK118),"OK","CHECK")),IF(AG118="","INFO",IF(ABS(AG118)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI118" s="17">
+        <f>IF(A118="","",IF(E118="","",IFERROR(INDEX($B$4:$B$204,MATCH(E118,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ118" s="17">
+        <f>IF(A118="","",IF(OR(AND(UPPER(TRIM(B118))="SWALE",UPPER(TRIM(AI118))="PIPE"),AND(UPPER(TRIM(B118))="TRENCH",UPPER(TRIM(AI118))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK118" s="17">
+        <f>IF(A118="","",IF(OR(AND(UPPER(TRIM(B118))="SWALE",UPPER(TRIM(AI118))="PIPE"),AND(UPPER(TRIM(B118))="TRENCH",UPPER(TRIM(AI118))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL118" s="4">
+        <f>IF(A118="","",IF(E118="","TERMINAL",IF(OR(AND(UPPER(TRIM(B118))="SWALE",UPPER(TRIM(AI118))="PIPE"),AND(UPPER(TRIM(B118))="TRENCH",UPPER(TRIM(AI118))="PIPE")),IF(OR(AG118="",AJ118="",AK118=""),"INFO",IF(AND(AG118&gt;=AJ118,AG118&lt;=AK118),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19088,7 +21063,23 @@
         <v/>
       </c>
       <c r="AH119" s="4">
-        <f>IF(A119="","",IF(E119="","TERMINAL",IF(AG119="","INFO",IF(ABS(AG119)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A119="","",IF(E119="","TERMINAL",IF(OR(AND(UPPER(TRIM(B119))="SWALE",UPPER(TRIM(AI119))="PIPE"),AND(UPPER(TRIM(B119))="TRENCH",UPPER(TRIM(AI119))="PIPE")),IF(OR(AG119="",AJ119="",AK119=""),"INFO",IF(AND(AG119&gt;=AJ119,AG119&lt;=AK119),"OK","CHECK")),IF(AG119="","INFO",IF(ABS(AG119)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI119" s="17">
+        <f>IF(A119="","",IF(E119="","",IFERROR(INDEX($B$4:$B$204,MATCH(E119,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ119" s="17">
+        <f>IF(A119="","",IF(OR(AND(UPPER(TRIM(B119))="SWALE",UPPER(TRIM(AI119))="PIPE"),AND(UPPER(TRIM(B119))="TRENCH",UPPER(TRIM(AI119))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK119" s="17">
+        <f>IF(A119="","",IF(OR(AND(UPPER(TRIM(B119))="SWALE",UPPER(TRIM(AI119))="PIPE"),AND(UPPER(TRIM(B119))="TRENCH",UPPER(TRIM(AI119))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL119" s="4">
+        <f>IF(A119="","",IF(E119="","TERMINAL",IF(OR(AND(UPPER(TRIM(B119))="SWALE",UPPER(TRIM(AI119))="PIPE"),AND(UPPER(TRIM(B119))="TRENCH",UPPER(TRIM(AI119))="PIPE")),IF(OR(AG119="",AJ119="",AK119=""),"INFO",IF(AND(AG119&gt;=AJ119,AG119&lt;=AK119),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19183,7 +21174,23 @@
         <v/>
       </c>
       <c r="AH120" s="4">
-        <f>IF(A120="","",IF(E120="","TERMINAL",IF(AG120="","INFO",IF(ABS(AG120)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A120="","",IF(E120="","TERMINAL",IF(OR(AND(UPPER(TRIM(B120))="SWALE",UPPER(TRIM(AI120))="PIPE"),AND(UPPER(TRIM(B120))="TRENCH",UPPER(TRIM(AI120))="PIPE")),IF(OR(AG120="",AJ120="",AK120=""),"INFO",IF(AND(AG120&gt;=AJ120,AG120&lt;=AK120),"OK","CHECK")),IF(AG120="","INFO",IF(ABS(AG120)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI120" s="17">
+        <f>IF(A120="","",IF(E120="","",IFERROR(INDEX($B$4:$B$204,MATCH(E120,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ120" s="17">
+        <f>IF(A120="","",IF(OR(AND(UPPER(TRIM(B120))="SWALE",UPPER(TRIM(AI120))="PIPE"),AND(UPPER(TRIM(B120))="TRENCH",UPPER(TRIM(AI120))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK120" s="17">
+        <f>IF(A120="","",IF(OR(AND(UPPER(TRIM(B120))="SWALE",UPPER(TRIM(AI120))="PIPE"),AND(UPPER(TRIM(B120))="TRENCH",UPPER(TRIM(AI120))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL120" s="4">
+        <f>IF(A120="","",IF(E120="","TERMINAL",IF(OR(AND(UPPER(TRIM(B120))="SWALE",UPPER(TRIM(AI120))="PIPE"),AND(UPPER(TRIM(B120))="TRENCH",UPPER(TRIM(AI120))="PIPE")),IF(OR(AG120="",AJ120="",AK120=""),"INFO",IF(AND(AG120&gt;=AJ120,AG120&lt;=AK120),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19278,7 +21285,23 @@
         <v/>
       </c>
       <c r="AH121" s="4">
-        <f>IF(A121="","",IF(E121="","TERMINAL",IF(AG121="","INFO",IF(ABS(AG121)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A121="","",IF(E121="","TERMINAL",IF(OR(AND(UPPER(TRIM(B121))="SWALE",UPPER(TRIM(AI121))="PIPE"),AND(UPPER(TRIM(B121))="TRENCH",UPPER(TRIM(AI121))="PIPE")),IF(OR(AG121="",AJ121="",AK121=""),"INFO",IF(AND(AG121&gt;=AJ121,AG121&lt;=AK121),"OK","CHECK")),IF(AG121="","INFO",IF(ABS(AG121)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI121" s="17">
+        <f>IF(A121="","",IF(E121="","",IFERROR(INDEX($B$4:$B$204,MATCH(E121,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ121" s="17">
+        <f>IF(A121="","",IF(OR(AND(UPPER(TRIM(B121))="SWALE",UPPER(TRIM(AI121))="PIPE"),AND(UPPER(TRIM(B121))="TRENCH",UPPER(TRIM(AI121))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK121" s="17">
+        <f>IF(A121="","",IF(OR(AND(UPPER(TRIM(B121))="SWALE",UPPER(TRIM(AI121))="PIPE"),AND(UPPER(TRIM(B121))="TRENCH",UPPER(TRIM(AI121))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL121" s="4">
+        <f>IF(A121="","",IF(E121="","TERMINAL",IF(OR(AND(UPPER(TRIM(B121))="SWALE",UPPER(TRIM(AI121))="PIPE"),AND(UPPER(TRIM(B121))="TRENCH",UPPER(TRIM(AI121))="PIPE")),IF(OR(AG121="",AJ121="",AK121=""),"INFO",IF(AND(AG121&gt;=AJ121,AG121&lt;=AK121),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19373,7 +21396,23 @@
         <v/>
       </c>
       <c r="AH122" s="4">
-        <f>IF(A122="","",IF(E122="","TERMINAL",IF(AG122="","INFO",IF(ABS(AG122)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A122="","",IF(E122="","TERMINAL",IF(OR(AND(UPPER(TRIM(B122))="SWALE",UPPER(TRIM(AI122))="PIPE"),AND(UPPER(TRIM(B122))="TRENCH",UPPER(TRIM(AI122))="PIPE")),IF(OR(AG122="",AJ122="",AK122=""),"INFO",IF(AND(AG122&gt;=AJ122,AG122&lt;=AK122),"OK","CHECK")),IF(AG122="","INFO",IF(ABS(AG122)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI122" s="17">
+        <f>IF(A122="","",IF(E122="","",IFERROR(INDEX($B$4:$B$204,MATCH(E122,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ122" s="17">
+        <f>IF(A122="","",IF(OR(AND(UPPER(TRIM(B122))="SWALE",UPPER(TRIM(AI122))="PIPE"),AND(UPPER(TRIM(B122))="TRENCH",UPPER(TRIM(AI122))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK122" s="17">
+        <f>IF(A122="","",IF(OR(AND(UPPER(TRIM(B122))="SWALE",UPPER(TRIM(AI122))="PIPE"),AND(UPPER(TRIM(B122))="TRENCH",UPPER(TRIM(AI122))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL122" s="4">
+        <f>IF(A122="","",IF(E122="","TERMINAL",IF(OR(AND(UPPER(TRIM(B122))="SWALE",UPPER(TRIM(AI122))="PIPE"),AND(UPPER(TRIM(B122))="TRENCH",UPPER(TRIM(AI122))="PIPE")),IF(OR(AG122="",AJ122="",AK122=""),"INFO",IF(AND(AG122&gt;=AJ122,AG122&lt;=AK122),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19468,7 +21507,23 @@
         <v/>
       </c>
       <c r="AH123" s="4">
-        <f>IF(A123="","",IF(E123="","TERMINAL",IF(AG123="","INFO",IF(ABS(AG123)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A123="","",IF(E123="","TERMINAL",IF(OR(AND(UPPER(TRIM(B123))="SWALE",UPPER(TRIM(AI123))="PIPE"),AND(UPPER(TRIM(B123))="TRENCH",UPPER(TRIM(AI123))="PIPE")),IF(OR(AG123="",AJ123="",AK123=""),"INFO",IF(AND(AG123&gt;=AJ123,AG123&lt;=AK123),"OK","CHECK")),IF(AG123="","INFO",IF(ABS(AG123)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI123" s="17">
+        <f>IF(A123="","",IF(E123="","",IFERROR(INDEX($B$4:$B$204,MATCH(E123,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ123" s="17">
+        <f>IF(A123="","",IF(OR(AND(UPPER(TRIM(B123))="SWALE",UPPER(TRIM(AI123))="PIPE"),AND(UPPER(TRIM(B123))="TRENCH",UPPER(TRIM(AI123))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK123" s="17">
+        <f>IF(A123="","",IF(OR(AND(UPPER(TRIM(B123))="SWALE",UPPER(TRIM(AI123))="PIPE"),AND(UPPER(TRIM(B123))="TRENCH",UPPER(TRIM(AI123))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL123" s="4">
+        <f>IF(A123="","",IF(E123="","TERMINAL",IF(OR(AND(UPPER(TRIM(B123))="SWALE",UPPER(TRIM(AI123))="PIPE"),AND(UPPER(TRIM(B123))="TRENCH",UPPER(TRIM(AI123))="PIPE")),IF(OR(AG123="",AJ123="",AK123=""),"INFO",IF(AND(AG123&gt;=AJ123,AG123&lt;=AK123),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19563,7 +21618,23 @@
         <v/>
       </c>
       <c r="AH124" s="4">
-        <f>IF(A124="","",IF(E124="","TERMINAL",IF(AG124="","INFO",IF(ABS(AG124)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A124="","",IF(E124="","TERMINAL",IF(OR(AND(UPPER(TRIM(B124))="SWALE",UPPER(TRIM(AI124))="PIPE"),AND(UPPER(TRIM(B124))="TRENCH",UPPER(TRIM(AI124))="PIPE")),IF(OR(AG124="",AJ124="",AK124=""),"INFO",IF(AND(AG124&gt;=AJ124,AG124&lt;=AK124),"OK","CHECK")),IF(AG124="","INFO",IF(ABS(AG124)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI124" s="17">
+        <f>IF(A124="","",IF(E124="","",IFERROR(INDEX($B$4:$B$204,MATCH(E124,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ124" s="17">
+        <f>IF(A124="","",IF(OR(AND(UPPER(TRIM(B124))="SWALE",UPPER(TRIM(AI124))="PIPE"),AND(UPPER(TRIM(B124))="TRENCH",UPPER(TRIM(AI124))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK124" s="17">
+        <f>IF(A124="","",IF(OR(AND(UPPER(TRIM(B124))="SWALE",UPPER(TRIM(AI124))="PIPE"),AND(UPPER(TRIM(B124))="TRENCH",UPPER(TRIM(AI124))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL124" s="4">
+        <f>IF(A124="","",IF(E124="","TERMINAL",IF(OR(AND(UPPER(TRIM(B124))="SWALE",UPPER(TRIM(AI124))="PIPE"),AND(UPPER(TRIM(B124))="TRENCH",UPPER(TRIM(AI124))="PIPE")),IF(OR(AG124="",AJ124="",AK124=""),"INFO",IF(AND(AG124&gt;=AJ124,AG124&lt;=AK124),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19658,7 +21729,23 @@
         <v/>
       </c>
       <c r="AH125" s="4">
-        <f>IF(A125="","",IF(E125="","TERMINAL",IF(AG125="","INFO",IF(ABS(AG125)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A125="","",IF(E125="","TERMINAL",IF(OR(AND(UPPER(TRIM(B125))="SWALE",UPPER(TRIM(AI125))="PIPE"),AND(UPPER(TRIM(B125))="TRENCH",UPPER(TRIM(AI125))="PIPE")),IF(OR(AG125="",AJ125="",AK125=""),"INFO",IF(AND(AG125&gt;=AJ125,AG125&lt;=AK125),"OK","CHECK")),IF(AG125="","INFO",IF(ABS(AG125)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI125" s="17">
+        <f>IF(A125="","",IF(E125="","",IFERROR(INDEX($B$4:$B$204,MATCH(E125,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ125" s="17">
+        <f>IF(A125="","",IF(OR(AND(UPPER(TRIM(B125))="SWALE",UPPER(TRIM(AI125))="PIPE"),AND(UPPER(TRIM(B125))="TRENCH",UPPER(TRIM(AI125))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK125" s="17">
+        <f>IF(A125="","",IF(OR(AND(UPPER(TRIM(B125))="SWALE",UPPER(TRIM(AI125))="PIPE"),AND(UPPER(TRIM(B125))="TRENCH",UPPER(TRIM(AI125))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL125" s="4">
+        <f>IF(A125="","",IF(E125="","TERMINAL",IF(OR(AND(UPPER(TRIM(B125))="SWALE",UPPER(TRIM(AI125))="PIPE"),AND(UPPER(TRIM(B125))="TRENCH",UPPER(TRIM(AI125))="PIPE")),IF(OR(AG125="",AJ125="",AK125=""),"INFO",IF(AND(AG125&gt;=AJ125,AG125&lt;=AK125),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19753,7 +21840,23 @@
         <v/>
       </c>
       <c r="AH126" s="4">
-        <f>IF(A126="","",IF(E126="","TERMINAL",IF(AG126="","INFO",IF(ABS(AG126)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A126="","",IF(E126="","TERMINAL",IF(OR(AND(UPPER(TRIM(B126))="SWALE",UPPER(TRIM(AI126))="PIPE"),AND(UPPER(TRIM(B126))="TRENCH",UPPER(TRIM(AI126))="PIPE")),IF(OR(AG126="",AJ126="",AK126=""),"INFO",IF(AND(AG126&gt;=AJ126,AG126&lt;=AK126),"OK","CHECK")),IF(AG126="","INFO",IF(ABS(AG126)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI126" s="17">
+        <f>IF(A126="","",IF(E126="","",IFERROR(INDEX($B$4:$B$204,MATCH(E126,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ126" s="17">
+        <f>IF(A126="","",IF(OR(AND(UPPER(TRIM(B126))="SWALE",UPPER(TRIM(AI126))="PIPE"),AND(UPPER(TRIM(B126))="TRENCH",UPPER(TRIM(AI126))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK126" s="17">
+        <f>IF(A126="","",IF(OR(AND(UPPER(TRIM(B126))="SWALE",UPPER(TRIM(AI126))="PIPE"),AND(UPPER(TRIM(B126))="TRENCH",UPPER(TRIM(AI126))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL126" s="4">
+        <f>IF(A126="","",IF(E126="","TERMINAL",IF(OR(AND(UPPER(TRIM(B126))="SWALE",UPPER(TRIM(AI126))="PIPE"),AND(UPPER(TRIM(B126))="TRENCH",UPPER(TRIM(AI126))="PIPE")),IF(OR(AG126="",AJ126="",AK126=""),"INFO",IF(AND(AG126&gt;=AJ126,AG126&lt;=AK126),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19848,7 +21951,23 @@
         <v/>
       </c>
       <c r="AH127" s="4">
-        <f>IF(A127="","",IF(E127="","TERMINAL",IF(AG127="","INFO",IF(ABS(AG127)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A127="","",IF(E127="","TERMINAL",IF(OR(AND(UPPER(TRIM(B127))="SWALE",UPPER(TRIM(AI127))="PIPE"),AND(UPPER(TRIM(B127))="TRENCH",UPPER(TRIM(AI127))="PIPE")),IF(OR(AG127="",AJ127="",AK127=""),"INFO",IF(AND(AG127&gt;=AJ127,AG127&lt;=AK127),"OK","CHECK")),IF(AG127="","INFO",IF(ABS(AG127)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI127" s="17">
+        <f>IF(A127="","",IF(E127="","",IFERROR(INDEX($B$4:$B$204,MATCH(E127,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ127" s="17">
+        <f>IF(A127="","",IF(OR(AND(UPPER(TRIM(B127))="SWALE",UPPER(TRIM(AI127))="PIPE"),AND(UPPER(TRIM(B127))="TRENCH",UPPER(TRIM(AI127))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK127" s="17">
+        <f>IF(A127="","",IF(OR(AND(UPPER(TRIM(B127))="SWALE",UPPER(TRIM(AI127))="PIPE"),AND(UPPER(TRIM(B127))="TRENCH",UPPER(TRIM(AI127))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL127" s="4">
+        <f>IF(A127="","",IF(E127="","TERMINAL",IF(OR(AND(UPPER(TRIM(B127))="SWALE",UPPER(TRIM(AI127))="PIPE"),AND(UPPER(TRIM(B127))="TRENCH",UPPER(TRIM(AI127))="PIPE")),IF(OR(AG127="",AJ127="",AK127=""),"INFO",IF(AND(AG127&gt;=AJ127,AG127&lt;=AK127),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -19943,7 +22062,23 @@
         <v/>
       </c>
       <c r="AH128" s="4">
-        <f>IF(A128="","",IF(E128="","TERMINAL",IF(AG128="","INFO",IF(ABS(AG128)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A128="","",IF(E128="","TERMINAL",IF(OR(AND(UPPER(TRIM(B128))="SWALE",UPPER(TRIM(AI128))="PIPE"),AND(UPPER(TRIM(B128))="TRENCH",UPPER(TRIM(AI128))="PIPE")),IF(OR(AG128="",AJ128="",AK128=""),"INFO",IF(AND(AG128&gt;=AJ128,AG128&lt;=AK128),"OK","CHECK")),IF(AG128="","INFO",IF(ABS(AG128)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI128" s="17">
+        <f>IF(A128="","",IF(E128="","",IFERROR(INDEX($B$4:$B$204,MATCH(E128,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ128" s="17">
+        <f>IF(A128="","",IF(OR(AND(UPPER(TRIM(B128))="SWALE",UPPER(TRIM(AI128))="PIPE"),AND(UPPER(TRIM(B128))="TRENCH",UPPER(TRIM(AI128))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK128" s="17">
+        <f>IF(A128="","",IF(OR(AND(UPPER(TRIM(B128))="SWALE",UPPER(TRIM(AI128))="PIPE"),AND(UPPER(TRIM(B128))="TRENCH",UPPER(TRIM(AI128))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL128" s="4">
+        <f>IF(A128="","",IF(E128="","TERMINAL",IF(OR(AND(UPPER(TRIM(B128))="SWALE",UPPER(TRIM(AI128))="PIPE"),AND(UPPER(TRIM(B128))="TRENCH",UPPER(TRIM(AI128))="PIPE")),IF(OR(AG128="",AJ128="",AK128=""),"INFO",IF(AND(AG128&gt;=AJ128,AG128&lt;=AK128),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20038,7 +22173,23 @@
         <v/>
       </c>
       <c r="AH129" s="4">
-        <f>IF(A129="","",IF(E129="","TERMINAL",IF(AG129="","INFO",IF(ABS(AG129)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A129="","",IF(E129="","TERMINAL",IF(OR(AND(UPPER(TRIM(B129))="SWALE",UPPER(TRIM(AI129))="PIPE"),AND(UPPER(TRIM(B129))="TRENCH",UPPER(TRIM(AI129))="PIPE")),IF(OR(AG129="",AJ129="",AK129=""),"INFO",IF(AND(AG129&gt;=AJ129,AG129&lt;=AK129),"OK","CHECK")),IF(AG129="","INFO",IF(ABS(AG129)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI129" s="17">
+        <f>IF(A129="","",IF(E129="","",IFERROR(INDEX($B$4:$B$204,MATCH(E129,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ129" s="17">
+        <f>IF(A129="","",IF(OR(AND(UPPER(TRIM(B129))="SWALE",UPPER(TRIM(AI129))="PIPE"),AND(UPPER(TRIM(B129))="TRENCH",UPPER(TRIM(AI129))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK129" s="17">
+        <f>IF(A129="","",IF(OR(AND(UPPER(TRIM(B129))="SWALE",UPPER(TRIM(AI129))="PIPE"),AND(UPPER(TRIM(B129))="TRENCH",UPPER(TRIM(AI129))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL129" s="4">
+        <f>IF(A129="","",IF(E129="","TERMINAL",IF(OR(AND(UPPER(TRIM(B129))="SWALE",UPPER(TRIM(AI129))="PIPE"),AND(UPPER(TRIM(B129))="TRENCH",UPPER(TRIM(AI129))="PIPE")),IF(OR(AG129="",AJ129="",AK129=""),"INFO",IF(AND(AG129&gt;=AJ129,AG129&lt;=AK129),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20133,7 +22284,23 @@
         <v/>
       </c>
       <c r="AH130" s="4">
-        <f>IF(A130="","",IF(E130="","TERMINAL",IF(AG130="","INFO",IF(ABS(AG130)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A130="","",IF(E130="","TERMINAL",IF(OR(AND(UPPER(TRIM(B130))="SWALE",UPPER(TRIM(AI130))="PIPE"),AND(UPPER(TRIM(B130))="TRENCH",UPPER(TRIM(AI130))="PIPE")),IF(OR(AG130="",AJ130="",AK130=""),"INFO",IF(AND(AG130&gt;=AJ130,AG130&lt;=AK130),"OK","CHECK")),IF(AG130="","INFO",IF(ABS(AG130)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI130" s="17">
+        <f>IF(A130="","",IF(E130="","",IFERROR(INDEX($B$4:$B$204,MATCH(E130,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ130" s="17">
+        <f>IF(A130="","",IF(OR(AND(UPPER(TRIM(B130))="SWALE",UPPER(TRIM(AI130))="PIPE"),AND(UPPER(TRIM(B130))="TRENCH",UPPER(TRIM(AI130))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK130" s="17">
+        <f>IF(A130="","",IF(OR(AND(UPPER(TRIM(B130))="SWALE",UPPER(TRIM(AI130))="PIPE"),AND(UPPER(TRIM(B130))="TRENCH",UPPER(TRIM(AI130))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL130" s="4">
+        <f>IF(A130="","",IF(E130="","TERMINAL",IF(OR(AND(UPPER(TRIM(B130))="SWALE",UPPER(TRIM(AI130))="PIPE"),AND(UPPER(TRIM(B130))="TRENCH",UPPER(TRIM(AI130))="PIPE")),IF(OR(AG130="",AJ130="",AK130=""),"INFO",IF(AND(AG130&gt;=AJ130,AG130&lt;=AK130),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20228,7 +22395,23 @@
         <v/>
       </c>
       <c r="AH131" s="4">
-        <f>IF(A131="","",IF(E131="","TERMINAL",IF(AG131="","INFO",IF(ABS(AG131)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A131="","",IF(E131="","TERMINAL",IF(OR(AND(UPPER(TRIM(B131))="SWALE",UPPER(TRIM(AI131))="PIPE"),AND(UPPER(TRIM(B131))="TRENCH",UPPER(TRIM(AI131))="PIPE")),IF(OR(AG131="",AJ131="",AK131=""),"INFO",IF(AND(AG131&gt;=AJ131,AG131&lt;=AK131),"OK","CHECK")),IF(AG131="","INFO",IF(ABS(AG131)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI131" s="17">
+        <f>IF(A131="","",IF(E131="","",IFERROR(INDEX($B$4:$B$204,MATCH(E131,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ131" s="17">
+        <f>IF(A131="","",IF(OR(AND(UPPER(TRIM(B131))="SWALE",UPPER(TRIM(AI131))="PIPE"),AND(UPPER(TRIM(B131))="TRENCH",UPPER(TRIM(AI131))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK131" s="17">
+        <f>IF(A131="","",IF(OR(AND(UPPER(TRIM(B131))="SWALE",UPPER(TRIM(AI131))="PIPE"),AND(UPPER(TRIM(B131))="TRENCH",UPPER(TRIM(AI131))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL131" s="4">
+        <f>IF(A131="","",IF(E131="","TERMINAL",IF(OR(AND(UPPER(TRIM(B131))="SWALE",UPPER(TRIM(AI131))="PIPE"),AND(UPPER(TRIM(B131))="TRENCH",UPPER(TRIM(AI131))="PIPE")),IF(OR(AG131="",AJ131="",AK131=""),"INFO",IF(AND(AG131&gt;=AJ131,AG131&lt;=AK131),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20323,7 +22506,23 @@
         <v/>
       </c>
       <c r="AH132" s="4">
-        <f>IF(A132="","",IF(E132="","TERMINAL",IF(AG132="","INFO",IF(ABS(AG132)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A132="","",IF(E132="","TERMINAL",IF(OR(AND(UPPER(TRIM(B132))="SWALE",UPPER(TRIM(AI132))="PIPE"),AND(UPPER(TRIM(B132))="TRENCH",UPPER(TRIM(AI132))="PIPE")),IF(OR(AG132="",AJ132="",AK132=""),"INFO",IF(AND(AG132&gt;=AJ132,AG132&lt;=AK132),"OK","CHECK")),IF(AG132="","INFO",IF(ABS(AG132)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI132" s="17">
+        <f>IF(A132="","",IF(E132="","",IFERROR(INDEX($B$4:$B$204,MATCH(E132,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ132" s="17">
+        <f>IF(A132="","",IF(OR(AND(UPPER(TRIM(B132))="SWALE",UPPER(TRIM(AI132))="PIPE"),AND(UPPER(TRIM(B132))="TRENCH",UPPER(TRIM(AI132))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK132" s="17">
+        <f>IF(A132="","",IF(OR(AND(UPPER(TRIM(B132))="SWALE",UPPER(TRIM(AI132))="PIPE"),AND(UPPER(TRIM(B132))="TRENCH",UPPER(TRIM(AI132))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL132" s="4">
+        <f>IF(A132="","",IF(E132="","TERMINAL",IF(OR(AND(UPPER(TRIM(B132))="SWALE",UPPER(TRIM(AI132))="PIPE"),AND(UPPER(TRIM(B132))="TRENCH",UPPER(TRIM(AI132))="PIPE")),IF(OR(AG132="",AJ132="",AK132=""),"INFO",IF(AND(AG132&gt;=AJ132,AG132&lt;=AK132),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20418,7 +22617,23 @@
         <v/>
       </c>
       <c r="AH133" s="4">
-        <f>IF(A133="","",IF(E133="","TERMINAL",IF(AG133="","INFO",IF(ABS(AG133)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A133="","",IF(E133="","TERMINAL",IF(OR(AND(UPPER(TRIM(B133))="SWALE",UPPER(TRIM(AI133))="PIPE"),AND(UPPER(TRIM(B133))="TRENCH",UPPER(TRIM(AI133))="PIPE")),IF(OR(AG133="",AJ133="",AK133=""),"INFO",IF(AND(AG133&gt;=AJ133,AG133&lt;=AK133),"OK","CHECK")),IF(AG133="","INFO",IF(ABS(AG133)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI133" s="17">
+        <f>IF(A133="","",IF(E133="","",IFERROR(INDEX($B$4:$B$204,MATCH(E133,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ133" s="17">
+        <f>IF(A133="","",IF(OR(AND(UPPER(TRIM(B133))="SWALE",UPPER(TRIM(AI133))="PIPE"),AND(UPPER(TRIM(B133))="TRENCH",UPPER(TRIM(AI133))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK133" s="17">
+        <f>IF(A133="","",IF(OR(AND(UPPER(TRIM(B133))="SWALE",UPPER(TRIM(AI133))="PIPE"),AND(UPPER(TRIM(B133))="TRENCH",UPPER(TRIM(AI133))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL133" s="4">
+        <f>IF(A133="","",IF(E133="","TERMINAL",IF(OR(AND(UPPER(TRIM(B133))="SWALE",UPPER(TRIM(AI133))="PIPE"),AND(UPPER(TRIM(B133))="TRENCH",UPPER(TRIM(AI133))="PIPE")),IF(OR(AG133="",AJ133="",AK133=""),"INFO",IF(AND(AG133&gt;=AJ133,AG133&lt;=AK133),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20513,7 +22728,23 @@
         <v/>
       </c>
       <c r="AH134" s="4">
-        <f>IF(A134="","",IF(E134="","TERMINAL",IF(AG134="","INFO",IF(ABS(AG134)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A134="","",IF(E134="","TERMINAL",IF(OR(AND(UPPER(TRIM(B134))="SWALE",UPPER(TRIM(AI134))="PIPE"),AND(UPPER(TRIM(B134))="TRENCH",UPPER(TRIM(AI134))="PIPE")),IF(OR(AG134="",AJ134="",AK134=""),"INFO",IF(AND(AG134&gt;=AJ134,AG134&lt;=AK134),"OK","CHECK")),IF(AG134="","INFO",IF(ABS(AG134)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI134" s="17">
+        <f>IF(A134="","",IF(E134="","",IFERROR(INDEX($B$4:$B$204,MATCH(E134,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ134" s="17">
+        <f>IF(A134="","",IF(OR(AND(UPPER(TRIM(B134))="SWALE",UPPER(TRIM(AI134))="PIPE"),AND(UPPER(TRIM(B134))="TRENCH",UPPER(TRIM(AI134))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK134" s="17">
+        <f>IF(A134="","",IF(OR(AND(UPPER(TRIM(B134))="SWALE",UPPER(TRIM(AI134))="PIPE"),AND(UPPER(TRIM(B134))="TRENCH",UPPER(TRIM(AI134))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL134" s="4">
+        <f>IF(A134="","",IF(E134="","TERMINAL",IF(OR(AND(UPPER(TRIM(B134))="SWALE",UPPER(TRIM(AI134))="PIPE"),AND(UPPER(TRIM(B134))="TRENCH",UPPER(TRIM(AI134))="PIPE")),IF(OR(AG134="",AJ134="",AK134=""),"INFO",IF(AND(AG134&gt;=AJ134,AG134&lt;=AK134),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20608,7 +22839,23 @@
         <v/>
       </c>
       <c r="AH135" s="4">
-        <f>IF(A135="","",IF(E135="","TERMINAL",IF(AG135="","INFO",IF(ABS(AG135)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A135="","",IF(E135="","TERMINAL",IF(OR(AND(UPPER(TRIM(B135))="SWALE",UPPER(TRIM(AI135))="PIPE"),AND(UPPER(TRIM(B135))="TRENCH",UPPER(TRIM(AI135))="PIPE")),IF(OR(AG135="",AJ135="",AK135=""),"INFO",IF(AND(AG135&gt;=AJ135,AG135&lt;=AK135),"OK","CHECK")),IF(AG135="","INFO",IF(ABS(AG135)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI135" s="17">
+        <f>IF(A135="","",IF(E135="","",IFERROR(INDEX($B$4:$B$204,MATCH(E135,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ135" s="17">
+        <f>IF(A135="","",IF(OR(AND(UPPER(TRIM(B135))="SWALE",UPPER(TRIM(AI135))="PIPE"),AND(UPPER(TRIM(B135))="TRENCH",UPPER(TRIM(AI135))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK135" s="17">
+        <f>IF(A135="","",IF(OR(AND(UPPER(TRIM(B135))="SWALE",UPPER(TRIM(AI135))="PIPE"),AND(UPPER(TRIM(B135))="TRENCH",UPPER(TRIM(AI135))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL135" s="4">
+        <f>IF(A135="","",IF(E135="","TERMINAL",IF(OR(AND(UPPER(TRIM(B135))="SWALE",UPPER(TRIM(AI135))="PIPE"),AND(UPPER(TRIM(B135))="TRENCH",UPPER(TRIM(AI135))="PIPE")),IF(OR(AG135="",AJ135="",AK135=""),"INFO",IF(AND(AG135&gt;=AJ135,AG135&lt;=AK135),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20703,7 +22950,23 @@
         <v/>
       </c>
       <c r="AH136" s="4">
-        <f>IF(A136="","",IF(E136="","TERMINAL",IF(AG136="","INFO",IF(ABS(AG136)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A136="","",IF(E136="","TERMINAL",IF(OR(AND(UPPER(TRIM(B136))="SWALE",UPPER(TRIM(AI136))="PIPE"),AND(UPPER(TRIM(B136))="TRENCH",UPPER(TRIM(AI136))="PIPE")),IF(OR(AG136="",AJ136="",AK136=""),"INFO",IF(AND(AG136&gt;=AJ136,AG136&lt;=AK136),"OK","CHECK")),IF(AG136="","INFO",IF(ABS(AG136)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI136" s="17">
+        <f>IF(A136="","",IF(E136="","",IFERROR(INDEX($B$4:$B$204,MATCH(E136,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ136" s="17">
+        <f>IF(A136="","",IF(OR(AND(UPPER(TRIM(B136))="SWALE",UPPER(TRIM(AI136))="PIPE"),AND(UPPER(TRIM(B136))="TRENCH",UPPER(TRIM(AI136))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK136" s="17">
+        <f>IF(A136="","",IF(OR(AND(UPPER(TRIM(B136))="SWALE",UPPER(TRIM(AI136))="PIPE"),AND(UPPER(TRIM(B136))="TRENCH",UPPER(TRIM(AI136))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL136" s="4">
+        <f>IF(A136="","",IF(E136="","TERMINAL",IF(OR(AND(UPPER(TRIM(B136))="SWALE",UPPER(TRIM(AI136))="PIPE"),AND(UPPER(TRIM(B136))="TRENCH",UPPER(TRIM(AI136))="PIPE")),IF(OR(AG136="",AJ136="",AK136=""),"INFO",IF(AND(AG136&gt;=AJ136,AG136&lt;=AK136),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20798,7 +23061,23 @@
         <v/>
       </c>
       <c r="AH137" s="4">
-        <f>IF(A137="","",IF(E137="","TERMINAL",IF(AG137="","INFO",IF(ABS(AG137)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A137="","",IF(E137="","TERMINAL",IF(OR(AND(UPPER(TRIM(B137))="SWALE",UPPER(TRIM(AI137))="PIPE"),AND(UPPER(TRIM(B137))="TRENCH",UPPER(TRIM(AI137))="PIPE")),IF(OR(AG137="",AJ137="",AK137=""),"INFO",IF(AND(AG137&gt;=AJ137,AG137&lt;=AK137),"OK","CHECK")),IF(AG137="","INFO",IF(ABS(AG137)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI137" s="17">
+        <f>IF(A137="","",IF(E137="","",IFERROR(INDEX($B$4:$B$204,MATCH(E137,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ137" s="17">
+        <f>IF(A137="","",IF(OR(AND(UPPER(TRIM(B137))="SWALE",UPPER(TRIM(AI137))="PIPE"),AND(UPPER(TRIM(B137))="TRENCH",UPPER(TRIM(AI137))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK137" s="17">
+        <f>IF(A137="","",IF(OR(AND(UPPER(TRIM(B137))="SWALE",UPPER(TRIM(AI137))="PIPE"),AND(UPPER(TRIM(B137))="TRENCH",UPPER(TRIM(AI137))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL137" s="4">
+        <f>IF(A137="","",IF(E137="","TERMINAL",IF(OR(AND(UPPER(TRIM(B137))="SWALE",UPPER(TRIM(AI137))="PIPE"),AND(UPPER(TRIM(B137))="TRENCH",UPPER(TRIM(AI137))="PIPE")),IF(OR(AG137="",AJ137="",AK137=""),"INFO",IF(AND(AG137&gt;=AJ137,AG137&lt;=AK137),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20893,7 +23172,23 @@
         <v/>
       </c>
       <c r="AH138" s="4">
-        <f>IF(A138="","",IF(E138="","TERMINAL",IF(AG138="","INFO",IF(ABS(AG138)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A138="","",IF(E138="","TERMINAL",IF(OR(AND(UPPER(TRIM(B138))="SWALE",UPPER(TRIM(AI138))="PIPE"),AND(UPPER(TRIM(B138))="TRENCH",UPPER(TRIM(AI138))="PIPE")),IF(OR(AG138="",AJ138="",AK138=""),"INFO",IF(AND(AG138&gt;=AJ138,AG138&lt;=AK138),"OK","CHECK")),IF(AG138="","INFO",IF(ABS(AG138)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI138" s="17">
+        <f>IF(A138="","",IF(E138="","",IFERROR(INDEX($B$4:$B$204,MATCH(E138,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ138" s="17">
+        <f>IF(A138="","",IF(OR(AND(UPPER(TRIM(B138))="SWALE",UPPER(TRIM(AI138))="PIPE"),AND(UPPER(TRIM(B138))="TRENCH",UPPER(TRIM(AI138))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK138" s="17">
+        <f>IF(A138="","",IF(OR(AND(UPPER(TRIM(B138))="SWALE",UPPER(TRIM(AI138))="PIPE"),AND(UPPER(TRIM(B138))="TRENCH",UPPER(TRIM(AI138))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL138" s="4">
+        <f>IF(A138="","",IF(E138="","TERMINAL",IF(OR(AND(UPPER(TRIM(B138))="SWALE",UPPER(TRIM(AI138))="PIPE"),AND(UPPER(TRIM(B138))="TRENCH",UPPER(TRIM(AI138))="PIPE")),IF(OR(AG138="",AJ138="",AK138=""),"INFO",IF(AND(AG138&gt;=AJ138,AG138&lt;=AK138),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -20988,7 +23283,23 @@
         <v/>
       </c>
       <c r="AH139" s="4">
-        <f>IF(A139="","",IF(E139="","TERMINAL",IF(AG139="","INFO",IF(ABS(AG139)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A139="","",IF(E139="","TERMINAL",IF(OR(AND(UPPER(TRIM(B139))="SWALE",UPPER(TRIM(AI139))="PIPE"),AND(UPPER(TRIM(B139))="TRENCH",UPPER(TRIM(AI139))="PIPE")),IF(OR(AG139="",AJ139="",AK139=""),"INFO",IF(AND(AG139&gt;=AJ139,AG139&lt;=AK139),"OK","CHECK")),IF(AG139="","INFO",IF(ABS(AG139)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI139" s="17">
+        <f>IF(A139="","",IF(E139="","",IFERROR(INDEX($B$4:$B$204,MATCH(E139,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ139" s="17">
+        <f>IF(A139="","",IF(OR(AND(UPPER(TRIM(B139))="SWALE",UPPER(TRIM(AI139))="PIPE"),AND(UPPER(TRIM(B139))="TRENCH",UPPER(TRIM(AI139))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK139" s="17">
+        <f>IF(A139="","",IF(OR(AND(UPPER(TRIM(B139))="SWALE",UPPER(TRIM(AI139))="PIPE"),AND(UPPER(TRIM(B139))="TRENCH",UPPER(TRIM(AI139))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL139" s="4">
+        <f>IF(A139="","",IF(E139="","TERMINAL",IF(OR(AND(UPPER(TRIM(B139))="SWALE",UPPER(TRIM(AI139))="PIPE"),AND(UPPER(TRIM(B139))="TRENCH",UPPER(TRIM(AI139))="PIPE")),IF(OR(AG139="",AJ139="",AK139=""),"INFO",IF(AND(AG139&gt;=AJ139,AG139&lt;=AK139),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21083,7 +23394,23 @@
         <v/>
       </c>
       <c r="AH140" s="4">
-        <f>IF(A140="","",IF(E140="","TERMINAL",IF(AG140="","INFO",IF(ABS(AG140)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A140="","",IF(E140="","TERMINAL",IF(OR(AND(UPPER(TRIM(B140))="SWALE",UPPER(TRIM(AI140))="PIPE"),AND(UPPER(TRIM(B140))="TRENCH",UPPER(TRIM(AI140))="PIPE")),IF(OR(AG140="",AJ140="",AK140=""),"INFO",IF(AND(AG140&gt;=AJ140,AG140&lt;=AK140),"OK","CHECK")),IF(AG140="","INFO",IF(ABS(AG140)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI140" s="17">
+        <f>IF(A140="","",IF(E140="","",IFERROR(INDEX($B$4:$B$204,MATCH(E140,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ140" s="17">
+        <f>IF(A140="","",IF(OR(AND(UPPER(TRIM(B140))="SWALE",UPPER(TRIM(AI140))="PIPE"),AND(UPPER(TRIM(B140))="TRENCH",UPPER(TRIM(AI140))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK140" s="17">
+        <f>IF(A140="","",IF(OR(AND(UPPER(TRIM(B140))="SWALE",UPPER(TRIM(AI140))="PIPE"),AND(UPPER(TRIM(B140))="TRENCH",UPPER(TRIM(AI140))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL140" s="4">
+        <f>IF(A140="","",IF(E140="","TERMINAL",IF(OR(AND(UPPER(TRIM(B140))="SWALE",UPPER(TRIM(AI140))="PIPE"),AND(UPPER(TRIM(B140))="TRENCH",UPPER(TRIM(AI140))="PIPE")),IF(OR(AG140="",AJ140="",AK140=""),"INFO",IF(AND(AG140&gt;=AJ140,AG140&lt;=AK140),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21178,7 +23505,23 @@
         <v/>
       </c>
       <c r="AH141" s="4">
-        <f>IF(A141="","",IF(E141="","TERMINAL",IF(AG141="","INFO",IF(ABS(AG141)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A141="","",IF(E141="","TERMINAL",IF(OR(AND(UPPER(TRIM(B141))="SWALE",UPPER(TRIM(AI141))="PIPE"),AND(UPPER(TRIM(B141))="TRENCH",UPPER(TRIM(AI141))="PIPE")),IF(OR(AG141="",AJ141="",AK141=""),"INFO",IF(AND(AG141&gt;=AJ141,AG141&lt;=AK141),"OK","CHECK")),IF(AG141="","INFO",IF(ABS(AG141)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI141" s="17">
+        <f>IF(A141="","",IF(E141="","",IFERROR(INDEX($B$4:$B$204,MATCH(E141,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ141" s="17">
+        <f>IF(A141="","",IF(OR(AND(UPPER(TRIM(B141))="SWALE",UPPER(TRIM(AI141))="PIPE"),AND(UPPER(TRIM(B141))="TRENCH",UPPER(TRIM(AI141))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK141" s="17">
+        <f>IF(A141="","",IF(OR(AND(UPPER(TRIM(B141))="SWALE",UPPER(TRIM(AI141))="PIPE"),AND(UPPER(TRIM(B141))="TRENCH",UPPER(TRIM(AI141))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL141" s="4">
+        <f>IF(A141="","",IF(E141="","TERMINAL",IF(OR(AND(UPPER(TRIM(B141))="SWALE",UPPER(TRIM(AI141))="PIPE"),AND(UPPER(TRIM(B141))="TRENCH",UPPER(TRIM(AI141))="PIPE")),IF(OR(AG141="",AJ141="",AK141=""),"INFO",IF(AND(AG141&gt;=AJ141,AG141&lt;=AK141),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21273,7 +23616,23 @@
         <v/>
       </c>
       <c r="AH142" s="4">
-        <f>IF(A142="","",IF(E142="","TERMINAL",IF(AG142="","INFO",IF(ABS(AG142)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A142="","",IF(E142="","TERMINAL",IF(OR(AND(UPPER(TRIM(B142))="SWALE",UPPER(TRIM(AI142))="PIPE"),AND(UPPER(TRIM(B142))="TRENCH",UPPER(TRIM(AI142))="PIPE")),IF(OR(AG142="",AJ142="",AK142=""),"INFO",IF(AND(AG142&gt;=AJ142,AG142&lt;=AK142),"OK","CHECK")),IF(AG142="","INFO",IF(ABS(AG142)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI142" s="17">
+        <f>IF(A142="","",IF(E142="","",IFERROR(INDEX($B$4:$B$204,MATCH(E142,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ142" s="17">
+        <f>IF(A142="","",IF(OR(AND(UPPER(TRIM(B142))="SWALE",UPPER(TRIM(AI142))="PIPE"),AND(UPPER(TRIM(B142))="TRENCH",UPPER(TRIM(AI142))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK142" s="17">
+        <f>IF(A142="","",IF(OR(AND(UPPER(TRIM(B142))="SWALE",UPPER(TRIM(AI142))="PIPE"),AND(UPPER(TRIM(B142))="TRENCH",UPPER(TRIM(AI142))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL142" s="4">
+        <f>IF(A142="","",IF(E142="","TERMINAL",IF(OR(AND(UPPER(TRIM(B142))="SWALE",UPPER(TRIM(AI142))="PIPE"),AND(UPPER(TRIM(B142))="TRENCH",UPPER(TRIM(AI142))="PIPE")),IF(OR(AG142="",AJ142="",AK142=""),"INFO",IF(AND(AG142&gt;=AJ142,AG142&lt;=AK142),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21368,7 +23727,23 @@
         <v/>
       </c>
       <c r="AH143" s="4">
-        <f>IF(A143="","",IF(E143="","TERMINAL",IF(AG143="","INFO",IF(ABS(AG143)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A143="","",IF(E143="","TERMINAL",IF(OR(AND(UPPER(TRIM(B143))="SWALE",UPPER(TRIM(AI143))="PIPE"),AND(UPPER(TRIM(B143))="TRENCH",UPPER(TRIM(AI143))="PIPE")),IF(OR(AG143="",AJ143="",AK143=""),"INFO",IF(AND(AG143&gt;=AJ143,AG143&lt;=AK143),"OK","CHECK")),IF(AG143="","INFO",IF(ABS(AG143)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI143" s="17">
+        <f>IF(A143="","",IF(E143="","",IFERROR(INDEX($B$4:$B$204,MATCH(E143,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ143" s="17">
+        <f>IF(A143="","",IF(OR(AND(UPPER(TRIM(B143))="SWALE",UPPER(TRIM(AI143))="PIPE"),AND(UPPER(TRIM(B143))="TRENCH",UPPER(TRIM(AI143))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK143" s="17">
+        <f>IF(A143="","",IF(OR(AND(UPPER(TRIM(B143))="SWALE",UPPER(TRIM(AI143))="PIPE"),AND(UPPER(TRIM(B143))="TRENCH",UPPER(TRIM(AI143))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL143" s="4">
+        <f>IF(A143="","",IF(E143="","TERMINAL",IF(OR(AND(UPPER(TRIM(B143))="SWALE",UPPER(TRIM(AI143))="PIPE"),AND(UPPER(TRIM(B143))="TRENCH",UPPER(TRIM(AI143))="PIPE")),IF(OR(AG143="",AJ143="",AK143=""),"INFO",IF(AND(AG143&gt;=AJ143,AG143&lt;=AK143),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21463,7 +23838,23 @@
         <v/>
       </c>
       <c r="AH144" s="4">
-        <f>IF(A144="","",IF(E144="","TERMINAL",IF(AG144="","INFO",IF(ABS(AG144)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A144="","",IF(E144="","TERMINAL",IF(OR(AND(UPPER(TRIM(B144))="SWALE",UPPER(TRIM(AI144))="PIPE"),AND(UPPER(TRIM(B144))="TRENCH",UPPER(TRIM(AI144))="PIPE")),IF(OR(AG144="",AJ144="",AK144=""),"INFO",IF(AND(AG144&gt;=AJ144,AG144&lt;=AK144),"OK","CHECK")),IF(AG144="","INFO",IF(ABS(AG144)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI144" s="17">
+        <f>IF(A144="","",IF(E144="","",IFERROR(INDEX($B$4:$B$204,MATCH(E144,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ144" s="17">
+        <f>IF(A144="","",IF(OR(AND(UPPER(TRIM(B144))="SWALE",UPPER(TRIM(AI144))="PIPE"),AND(UPPER(TRIM(B144))="TRENCH",UPPER(TRIM(AI144))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK144" s="17">
+        <f>IF(A144="","",IF(OR(AND(UPPER(TRIM(B144))="SWALE",UPPER(TRIM(AI144))="PIPE"),AND(UPPER(TRIM(B144))="TRENCH",UPPER(TRIM(AI144))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL144" s="4">
+        <f>IF(A144="","",IF(E144="","TERMINAL",IF(OR(AND(UPPER(TRIM(B144))="SWALE",UPPER(TRIM(AI144))="PIPE"),AND(UPPER(TRIM(B144))="TRENCH",UPPER(TRIM(AI144))="PIPE")),IF(OR(AG144="",AJ144="",AK144=""),"INFO",IF(AND(AG144&gt;=AJ144,AG144&lt;=AK144),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21558,7 +23949,23 @@
         <v/>
       </c>
       <c r="AH145" s="4">
-        <f>IF(A145="","",IF(E145="","TERMINAL",IF(AG145="","INFO",IF(ABS(AG145)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A145="","",IF(E145="","TERMINAL",IF(OR(AND(UPPER(TRIM(B145))="SWALE",UPPER(TRIM(AI145))="PIPE"),AND(UPPER(TRIM(B145))="TRENCH",UPPER(TRIM(AI145))="PIPE")),IF(OR(AG145="",AJ145="",AK145=""),"INFO",IF(AND(AG145&gt;=AJ145,AG145&lt;=AK145),"OK","CHECK")),IF(AG145="","INFO",IF(ABS(AG145)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI145" s="17">
+        <f>IF(A145="","",IF(E145="","",IFERROR(INDEX($B$4:$B$204,MATCH(E145,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ145" s="17">
+        <f>IF(A145="","",IF(OR(AND(UPPER(TRIM(B145))="SWALE",UPPER(TRIM(AI145))="PIPE"),AND(UPPER(TRIM(B145))="TRENCH",UPPER(TRIM(AI145))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK145" s="17">
+        <f>IF(A145="","",IF(OR(AND(UPPER(TRIM(B145))="SWALE",UPPER(TRIM(AI145))="PIPE"),AND(UPPER(TRIM(B145))="TRENCH",UPPER(TRIM(AI145))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL145" s="4">
+        <f>IF(A145="","",IF(E145="","TERMINAL",IF(OR(AND(UPPER(TRIM(B145))="SWALE",UPPER(TRIM(AI145))="PIPE"),AND(UPPER(TRIM(B145))="TRENCH",UPPER(TRIM(AI145))="PIPE")),IF(OR(AG145="",AJ145="",AK145=""),"INFO",IF(AND(AG145&gt;=AJ145,AG145&lt;=AK145),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21653,7 +24060,23 @@
         <v/>
       </c>
       <c r="AH146" s="4">
-        <f>IF(A146="","",IF(E146="","TERMINAL",IF(AG146="","INFO",IF(ABS(AG146)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A146="","",IF(E146="","TERMINAL",IF(OR(AND(UPPER(TRIM(B146))="SWALE",UPPER(TRIM(AI146))="PIPE"),AND(UPPER(TRIM(B146))="TRENCH",UPPER(TRIM(AI146))="PIPE")),IF(OR(AG146="",AJ146="",AK146=""),"INFO",IF(AND(AG146&gt;=AJ146,AG146&lt;=AK146),"OK","CHECK")),IF(AG146="","INFO",IF(ABS(AG146)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI146" s="17">
+        <f>IF(A146="","",IF(E146="","",IFERROR(INDEX($B$4:$B$204,MATCH(E146,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ146" s="17">
+        <f>IF(A146="","",IF(OR(AND(UPPER(TRIM(B146))="SWALE",UPPER(TRIM(AI146))="PIPE"),AND(UPPER(TRIM(B146))="TRENCH",UPPER(TRIM(AI146))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK146" s="17">
+        <f>IF(A146="","",IF(OR(AND(UPPER(TRIM(B146))="SWALE",UPPER(TRIM(AI146))="PIPE"),AND(UPPER(TRIM(B146))="TRENCH",UPPER(TRIM(AI146))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL146" s="4">
+        <f>IF(A146="","",IF(E146="","TERMINAL",IF(OR(AND(UPPER(TRIM(B146))="SWALE",UPPER(TRIM(AI146))="PIPE"),AND(UPPER(TRIM(B146))="TRENCH",UPPER(TRIM(AI146))="PIPE")),IF(OR(AG146="",AJ146="",AK146=""),"INFO",IF(AND(AG146&gt;=AJ146,AG146&lt;=AK146),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21748,7 +24171,23 @@
         <v/>
       </c>
       <c r="AH147" s="4">
-        <f>IF(A147="","",IF(E147="","TERMINAL",IF(AG147="","INFO",IF(ABS(AG147)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A147="","",IF(E147="","TERMINAL",IF(OR(AND(UPPER(TRIM(B147))="SWALE",UPPER(TRIM(AI147))="PIPE"),AND(UPPER(TRIM(B147))="TRENCH",UPPER(TRIM(AI147))="PIPE")),IF(OR(AG147="",AJ147="",AK147=""),"INFO",IF(AND(AG147&gt;=AJ147,AG147&lt;=AK147),"OK","CHECK")),IF(AG147="","INFO",IF(ABS(AG147)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI147" s="17">
+        <f>IF(A147="","",IF(E147="","",IFERROR(INDEX($B$4:$B$204,MATCH(E147,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ147" s="17">
+        <f>IF(A147="","",IF(OR(AND(UPPER(TRIM(B147))="SWALE",UPPER(TRIM(AI147))="PIPE"),AND(UPPER(TRIM(B147))="TRENCH",UPPER(TRIM(AI147))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK147" s="17">
+        <f>IF(A147="","",IF(OR(AND(UPPER(TRIM(B147))="SWALE",UPPER(TRIM(AI147))="PIPE"),AND(UPPER(TRIM(B147))="TRENCH",UPPER(TRIM(AI147))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL147" s="4">
+        <f>IF(A147="","",IF(E147="","TERMINAL",IF(OR(AND(UPPER(TRIM(B147))="SWALE",UPPER(TRIM(AI147))="PIPE"),AND(UPPER(TRIM(B147))="TRENCH",UPPER(TRIM(AI147))="PIPE")),IF(OR(AG147="",AJ147="",AK147=""),"INFO",IF(AND(AG147&gt;=AJ147,AG147&lt;=AK147),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21843,7 +24282,23 @@
         <v/>
       </c>
       <c r="AH148" s="4">
-        <f>IF(A148="","",IF(E148="","TERMINAL",IF(AG148="","INFO",IF(ABS(AG148)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A148="","",IF(E148="","TERMINAL",IF(OR(AND(UPPER(TRIM(B148))="SWALE",UPPER(TRIM(AI148))="PIPE"),AND(UPPER(TRIM(B148))="TRENCH",UPPER(TRIM(AI148))="PIPE")),IF(OR(AG148="",AJ148="",AK148=""),"INFO",IF(AND(AG148&gt;=AJ148,AG148&lt;=AK148),"OK","CHECK")),IF(AG148="","INFO",IF(ABS(AG148)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI148" s="17">
+        <f>IF(A148="","",IF(E148="","",IFERROR(INDEX($B$4:$B$204,MATCH(E148,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ148" s="17">
+        <f>IF(A148="","",IF(OR(AND(UPPER(TRIM(B148))="SWALE",UPPER(TRIM(AI148))="PIPE"),AND(UPPER(TRIM(B148))="TRENCH",UPPER(TRIM(AI148))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK148" s="17">
+        <f>IF(A148="","",IF(OR(AND(UPPER(TRIM(B148))="SWALE",UPPER(TRIM(AI148))="PIPE"),AND(UPPER(TRIM(B148))="TRENCH",UPPER(TRIM(AI148))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL148" s="4">
+        <f>IF(A148="","",IF(E148="","TERMINAL",IF(OR(AND(UPPER(TRIM(B148))="SWALE",UPPER(TRIM(AI148))="PIPE"),AND(UPPER(TRIM(B148))="TRENCH",UPPER(TRIM(AI148))="PIPE")),IF(OR(AG148="",AJ148="",AK148=""),"INFO",IF(AND(AG148&gt;=AJ148,AG148&lt;=AK148),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -21938,7 +24393,23 @@
         <v/>
       </c>
       <c r="AH149" s="4">
-        <f>IF(A149="","",IF(E149="","TERMINAL",IF(AG149="","INFO",IF(ABS(AG149)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A149="","",IF(E149="","TERMINAL",IF(OR(AND(UPPER(TRIM(B149))="SWALE",UPPER(TRIM(AI149))="PIPE"),AND(UPPER(TRIM(B149))="TRENCH",UPPER(TRIM(AI149))="PIPE")),IF(OR(AG149="",AJ149="",AK149=""),"INFO",IF(AND(AG149&gt;=AJ149,AG149&lt;=AK149),"OK","CHECK")),IF(AG149="","INFO",IF(ABS(AG149)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI149" s="17">
+        <f>IF(A149="","",IF(E149="","",IFERROR(INDEX($B$4:$B$204,MATCH(E149,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ149" s="17">
+        <f>IF(A149="","",IF(OR(AND(UPPER(TRIM(B149))="SWALE",UPPER(TRIM(AI149))="PIPE"),AND(UPPER(TRIM(B149))="TRENCH",UPPER(TRIM(AI149))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK149" s="17">
+        <f>IF(A149="","",IF(OR(AND(UPPER(TRIM(B149))="SWALE",UPPER(TRIM(AI149))="PIPE"),AND(UPPER(TRIM(B149))="TRENCH",UPPER(TRIM(AI149))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL149" s="4">
+        <f>IF(A149="","",IF(E149="","TERMINAL",IF(OR(AND(UPPER(TRIM(B149))="SWALE",UPPER(TRIM(AI149))="PIPE"),AND(UPPER(TRIM(B149))="TRENCH",UPPER(TRIM(AI149))="PIPE")),IF(OR(AG149="",AJ149="",AK149=""),"INFO",IF(AND(AG149&gt;=AJ149,AG149&lt;=AK149),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22033,7 +24504,23 @@
         <v/>
       </c>
       <c r="AH150" s="4">
-        <f>IF(A150="","",IF(E150="","TERMINAL",IF(AG150="","INFO",IF(ABS(AG150)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A150="","",IF(E150="","TERMINAL",IF(OR(AND(UPPER(TRIM(B150))="SWALE",UPPER(TRIM(AI150))="PIPE"),AND(UPPER(TRIM(B150))="TRENCH",UPPER(TRIM(AI150))="PIPE")),IF(OR(AG150="",AJ150="",AK150=""),"INFO",IF(AND(AG150&gt;=AJ150,AG150&lt;=AK150),"OK","CHECK")),IF(AG150="","INFO",IF(ABS(AG150)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI150" s="17">
+        <f>IF(A150="","",IF(E150="","",IFERROR(INDEX($B$4:$B$204,MATCH(E150,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ150" s="17">
+        <f>IF(A150="","",IF(OR(AND(UPPER(TRIM(B150))="SWALE",UPPER(TRIM(AI150))="PIPE"),AND(UPPER(TRIM(B150))="TRENCH",UPPER(TRIM(AI150))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK150" s="17">
+        <f>IF(A150="","",IF(OR(AND(UPPER(TRIM(B150))="SWALE",UPPER(TRIM(AI150))="PIPE"),AND(UPPER(TRIM(B150))="TRENCH",UPPER(TRIM(AI150))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL150" s="4">
+        <f>IF(A150="","",IF(E150="","TERMINAL",IF(OR(AND(UPPER(TRIM(B150))="SWALE",UPPER(TRIM(AI150))="PIPE"),AND(UPPER(TRIM(B150))="TRENCH",UPPER(TRIM(AI150))="PIPE")),IF(OR(AG150="",AJ150="",AK150=""),"INFO",IF(AND(AG150&gt;=AJ150,AG150&lt;=AK150),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22128,7 +24615,23 @@
         <v/>
       </c>
       <c r="AH151" s="4">
-        <f>IF(A151="","",IF(E151="","TERMINAL",IF(AG151="","INFO",IF(ABS(AG151)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A151="","",IF(E151="","TERMINAL",IF(OR(AND(UPPER(TRIM(B151))="SWALE",UPPER(TRIM(AI151))="PIPE"),AND(UPPER(TRIM(B151))="TRENCH",UPPER(TRIM(AI151))="PIPE")),IF(OR(AG151="",AJ151="",AK151=""),"INFO",IF(AND(AG151&gt;=AJ151,AG151&lt;=AK151),"OK","CHECK")),IF(AG151="","INFO",IF(ABS(AG151)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI151" s="17">
+        <f>IF(A151="","",IF(E151="","",IFERROR(INDEX($B$4:$B$204,MATCH(E151,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ151" s="17">
+        <f>IF(A151="","",IF(OR(AND(UPPER(TRIM(B151))="SWALE",UPPER(TRIM(AI151))="PIPE"),AND(UPPER(TRIM(B151))="TRENCH",UPPER(TRIM(AI151))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK151" s="17">
+        <f>IF(A151="","",IF(OR(AND(UPPER(TRIM(B151))="SWALE",UPPER(TRIM(AI151))="PIPE"),AND(UPPER(TRIM(B151))="TRENCH",UPPER(TRIM(AI151))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL151" s="4">
+        <f>IF(A151="","",IF(E151="","TERMINAL",IF(OR(AND(UPPER(TRIM(B151))="SWALE",UPPER(TRIM(AI151))="PIPE"),AND(UPPER(TRIM(B151))="TRENCH",UPPER(TRIM(AI151))="PIPE")),IF(OR(AG151="",AJ151="",AK151=""),"INFO",IF(AND(AG151&gt;=AJ151,AG151&lt;=AK151),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22223,7 +24726,23 @@
         <v/>
       </c>
       <c r="AH152" s="4">
-        <f>IF(A152="","",IF(E152="","TERMINAL",IF(AG152="","INFO",IF(ABS(AG152)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A152="","",IF(E152="","TERMINAL",IF(OR(AND(UPPER(TRIM(B152))="SWALE",UPPER(TRIM(AI152))="PIPE"),AND(UPPER(TRIM(B152))="TRENCH",UPPER(TRIM(AI152))="PIPE")),IF(OR(AG152="",AJ152="",AK152=""),"INFO",IF(AND(AG152&gt;=AJ152,AG152&lt;=AK152),"OK","CHECK")),IF(AG152="","INFO",IF(ABS(AG152)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI152" s="17">
+        <f>IF(A152="","",IF(E152="","",IFERROR(INDEX($B$4:$B$204,MATCH(E152,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ152" s="17">
+        <f>IF(A152="","",IF(OR(AND(UPPER(TRIM(B152))="SWALE",UPPER(TRIM(AI152))="PIPE"),AND(UPPER(TRIM(B152))="TRENCH",UPPER(TRIM(AI152))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK152" s="17">
+        <f>IF(A152="","",IF(OR(AND(UPPER(TRIM(B152))="SWALE",UPPER(TRIM(AI152))="PIPE"),AND(UPPER(TRIM(B152))="TRENCH",UPPER(TRIM(AI152))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL152" s="4">
+        <f>IF(A152="","",IF(E152="","TERMINAL",IF(OR(AND(UPPER(TRIM(B152))="SWALE",UPPER(TRIM(AI152))="PIPE"),AND(UPPER(TRIM(B152))="TRENCH",UPPER(TRIM(AI152))="PIPE")),IF(OR(AG152="",AJ152="",AK152=""),"INFO",IF(AND(AG152&gt;=AJ152,AG152&lt;=AK152),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22318,7 +24837,23 @@
         <v/>
       </c>
       <c r="AH153" s="4">
-        <f>IF(A153="","",IF(E153="","TERMINAL",IF(AG153="","INFO",IF(ABS(AG153)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A153="","",IF(E153="","TERMINAL",IF(OR(AND(UPPER(TRIM(B153))="SWALE",UPPER(TRIM(AI153))="PIPE"),AND(UPPER(TRIM(B153))="TRENCH",UPPER(TRIM(AI153))="PIPE")),IF(OR(AG153="",AJ153="",AK153=""),"INFO",IF(AND(AG153&gt;=AJ153,AG153&lt;=AK153),"OK","CHECK")),IF(AG153="","INFO",IF(ABS(AG153)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI153" s="17">
+        <f>IF(A153="","",IF(E153="","",IFERROR(INDEX($B$4:$B$204,MATCH(E153,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ153" s="17">
+        <f>IF(A153="","",IF(OR(AND(UPPER(TRIM(B153))="SWALE",UPPER(TRIM(AI153))="PIPE"),AND(UPPER(TRIM(B153))="TRENCH",UPPER(TRIM(AI153))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK153" s="17">
+        <f>IF(A153="","",IF(OR(AND(UPPER(TRIM(B153))="SWALE",UPPER(TRIM(AI153))="PIPE"),AND(UPPER(TRIM(B153))="TRENCH",UPPER(TRIM(AI153))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL153" s="4">
+        <f>IF(A153="","",IF(E153="","TERMINAL",IF(OR(AND(UPPER(TRIM(B153))="SWALE",UPPER(TRIM(AI153))="PIPE"),AND(UPPER(TRIM(B153))="TRENCH",UPPER(TRIM(AI153))="PIPE")),IF(OR(AG153="",AJ153="",AK153=""),"INFO",IF(AND(AG153&gt;=AJ153,AG153&lt;=AK153),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22413,7 +24948,23 @@
         <v/>
       </c>
       <c r="AH154" s="4">
-        <f>IF(A154="","",IF(E154="","TERMINAL",IF(AG154="","INFO",IF(ABS(AG154)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A154="","",IF(E154="","TERMINAL",IF(OR(AND(UPPER(TRIM(B154))="SWALE",UPPER(TRIM(AI154))="PIPE"),AND(UPPER(TRIM(B154))="TRENCH",UPPER(TRIM(AI154))="PIPE")),IF(OR(AG154="",AJ154="",AK154=""),"INFO",IF(AND(AG154&gt;=AJ154,AG154&lt;=AK154),"OK","CHECK")),IF(AG154="","INFO",IF(ABS(AG154)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI154" s="17">
+        <f>IF(A154="","",IF(E154="","",IFERROR(INDEX($B$4:$B$204,MATCH(E154,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ154" s="17">
+        <f>IF(A154="","",IF(OR(AND(UPPER(TRIM(B154))="SWALE",UPPER(TRIM(AI154))="PIPE"),AND(UPPER(TRIM(B154))="TRENCH",UPPER(TRIM(AI154))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK154" s="17">
+        <f>IF(A154="","",IF(OR(AND(UPPER(TRIM(B154))="SWALE",UPPER(TRIM(AI154))="PIPE"),AND(UPPER(TRIM(B154))="TRENCH",UPPER(TRIM(AI154))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL154" s="4">
+        <f>IF(A154="","",IF(E154="","TERMINAL",IF(OR(AND(UPPER(TRIM(B154))="SWALE",UPPER(TRIM(AI154))="PIPE"),AND(UPPER(TRIM(B154))="TRENCH",UPPER(TRIM(AI154))="PIPE")),IF(OR(AG154="",AJ154="",AK154=""),"INFO",IF(AND(AG154&gt;=AJ154,AG154&lt;=AK154),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22508,7 +25059,23 @@
         <v/>
       </c>
       <c r="AH155" s="4">
-        <f>IF(A155="","",IF(E155="","TERMINAL",IF(AG155="","INFO",IF(ABS(AG155)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A155="","",IF(E155="","TERMINAL",IF(OR(AND(UPPER(TRIM(B155))="SWALE",UPPER(TRIM(AI155))="PIPE"),AND(UPPER(TRIM(B155))="TRENCH",UPPER(TRIM(AI155))="PIPE")),IF(OR(AG155="",AJ155="",AK155=""),"INFO",IF(AND(AG155&gt;=AJ155,AG155&lt;=AK155),"OK","CHECK")),IF(AG155="","INFO",IF(ABS(AG155)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI155" s="17">
+        <f>IF(A155="","",IF(E155="","",IFERROR(INDEX($B$4:$B$204,MATCH(E155,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ155" s="17">
+        <f>IF(A155="","",IF(OR(AND(UPPER(TRIM(B155))="SWALE",UPPER(TRIM(AI155))="PIPE"),AND(UPPER(TRIM(B155))="TRENCH",UPPER(TRIM(AI155))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK155" s="17">
+        <f>IF(A155="","",IF(OR(AND(UPPER(TRIM(B155))="SWALE",UPPER(TRIM(AI155))="PIPE"),AND(UPPER(TRIM(B155))="TRENCH",UPPER(TRIM(AI155))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL155" s="4">
+        <f>IF(A155="","",IF(E155="","TERMINAL",IF(OR(AND(UPPER(TRIM(B155))="SWALE",UPPER(TRIM(AI155))="PIPE"),AND(UPPER(TRIM(B155))="TRENCH",UPPER(TRIM(AI155))="PIPE")),IF(OR(AG155="",AJ155="",AK155=""),"INFO",IF(AND(AG155&gt;=AJ155,AG155&lt;=AK155),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22603,7 +25170,23 @@
         <v/>
       </c>
       <c r="AH156" s="4">
-        <f>IF(A156="","",IF(E156="","TERMINAL",IF(AG156="","INFO",IF(ABS(AG156)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A156="","",IF(E156="","TERMINAL",IF(OR(AND(UPPER(TRIM(B156))="SWALE",UPPER(TRIM(AI156))="PIPE"),AND(UPPER(TRIM(B156))="TRENCH",UPPER(TRIM(AI156))="PIPE")),IF(OR(AG156="",AJ156="",AK156=""),"INFO",IF(AND(AG156&gt;=AJ156,AG156&lt;=AK156),"OK","CHECK")),IF(AG156="","INFO",IF(ABS(AG156)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI156" s="17">
+        <f>IF(A156="","",IF(E156="","",IFERROR(INDEX($B$4:$B$204,MATCH(E156,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ156" s="17">
+        <f>IF(A156="","",IF(OR(AND(UPPER(TRIM(B156))="SWALE",UPPER(TRIM(AI156))="PIPE"),AND(UPPER(TRIM(B156))="TRENCH",UPPER(TRIM(AI156))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK156" s="17">
+        <f>IF(A156="","",IF(OR(AND(UPPER(TRIM(B156))="SWALE",UPPER(TRIM(AI156))="PIPE"),AND(UPPER(TRIM(B156))="TRENCH",UPPER(TRIM(AI156))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL156" s="4">
+        <f>IF(A156="","",IF(E156="","TERMINAL",IF(OR(AND(UPPER(TRIM(B156))="SWALE",UPPER(TRIM(AI156))="PIPE"),AND(UPPER(TRIM(B156))="TRENCH",UPPER(TRIM(AI156))="PIPE")),IF(OR(AG156="",AJ156="",AK156=""),"INFO",IF(AND(AG156&gt;=AJ156,AG156&lt;=AK156),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22698,7 +25281,23 @@
         <v/>
       </c>
       <c r="AH157" s="4">
-        <f>IF(A157="","",IF(E157="","TERMINAL",IF(AG157="","INFO",IF(ABS(AG157)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A157="","",IF(E157="","TERMINAL",IF(OR(AND(UPPER(TRIM(B157))="SWALE",UPPER(TRIM(AI157))="PIPE"),AND(UPPER(TRIM(B157))="TRENCH",UPPER(TRIM(AI157))="PIPE")),IF(OR(AG157="",AJ157="",AK157=""),"INFO",IF(AND(AG157&gt;=AJ157,AG157&lt;=AK157),"OK","CHECK")),IF(AG157="","INFO",IF(ABS(AG157)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI157" s="17">
+        <f>IF(A157="","",IF(E157="","",IFERROR(INDEX($B$4:$B$204,MATCH(E157,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ157" s="17">
+        <f>IF(A157="","",IF(OR(AND(UPPER(TRIM(B157))="SWALE",UPPER(TRIM(AI157))="PIPE"),AND(UPPER(TRIM(B157))="TRENCH",UPPER(TRIM(AI157))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK157" s="17">
+        <f>IF(A157="","",IF(OR(AND(UPPER(TRIM(B157))="SWALE",UPPER(TRIM(AI157))="PIPE"),AND(UPPER(TRIM(B157))="TRENCH",UPPER(TRIM(AI157))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL157" s="4">
+        <f>IF(A157="","",IF(E157="","TERMINAL",IF(OR(AND(UPPER(TRIM(B157))="SWALE",UPPER(TRIM(AI157))="PIPE"),AND(UPPER(TRIM(B157))="TRENCH",UPPER(TRIM(AI157))="PIPE")),IF(OR(AG157="",AJ157="",AK157=""),"INFO",IF(AND(AG157&gt;=AJ157,AG157&lt;=AK157),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22793,7 +25392,23 @@
         <v/>
       </c>
       <c r="AH158" s="4">
-        <f>IF(A158="","",IF(E158="","TERMINAL",IF(AG158="","INFO",IF(ABS(AG158)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A158="","",IF(E158="","TERMINAL",IF(OR(AND(UPPER(TRIM(B158))="SWALE",UPPER(TRIM(AI158))="PIPE"),AND(UPPER(TRIM(B158))="TRENCH",UPPER(TRIM(AI158))="PIPE")),IF(OR(AG158="",AJ158="",AK158=""),"INFO",IF(AND(AG158&gt;=AJ158,AG158&lt;=AK158),"OK","CHECK")),IF(AG158="","INFO",IF(ABS(AG158)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI158" s="17">
+        <f>IF(A158="","",IF(E158="","",IFERROR(INDEX($B$4:$B$204,MATCH(E158,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ158" s="17">
+        <f>IF(A158="","",IF(OR(AND(UPPER(TRIM(B158))="SWALE",UPPER(TRIM(AI158))="PIPE"),AND(UPPER(TRIM(B158))="TRENCH",UPPER(TRIM(AI158))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK158" s="17">
+        <f>IF(A158="","",IF(OR(AND(UPPER(TRIM(B158))="SWALE",UPPER(TRIM(AI158))="PIPE"),AND(UPPER(TRIM(B158))="TRENCH",UPPER(TRIM(AI158))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL158" s="4">
+        <f>IF(A158="","",IF(E158="","TERMINAL",IF(OR(AND(UPPER(TRIM(B158))="SWALE",UPPER(TRIM(AI158))="PIPE"),AND(UPPER(TRIM(B158))="TRENCH",UPPER(TRIM(AI158))="PIPE")),IF(OR(AG158="",AJ158="",AK158=""),"INFO",IF(AND(AG158&gt;=AJ158,AG158&lt;=AK158),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22888,7 +25503,23 @@
         <v/>
       </c>
       <c r="AH159" s="4">
-        <f>IF(A159="","",IF(E159="","TERMINAL",IF(AG159="","INFO",IF(ABS(AG159)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A159="","",IF(E159="","TERMINAL",IF(OR(AND(UPPER(TRIM(B159))="SWALE",UPPER(TRIM(AI159))="PIPE"),AND(UPPER(TRIM(B159))="TRENCH",UPPER(TRIM(AI159))="PIPE")),IF(OR(AG159="",AJ159="",AK159=""),"INFO",IF(AND(AG159&gt;=AJ159,AG159&lt;=AK159),"OK","CHECK")),IF(AG159="","INFO",IF(ABS(AG159)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI159" s="17">
+        <f>IF(A159="","",IF(E159="","",IFERROR(INDEX($B$4:$B$204,MATCH(E159,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ159" s="17">
+        <f>IF(A159="","",IF(OR(AND(UPPER(TRIM(B159))="SWALE",UPPER(TRIM(AI159))="PIPE"),AND(UPPER(TRIM(B159))="TRENCH",UPPER(TRIM(AI159))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK159" s="17">
+        <f>IF(A159="","",IF(OR(AND(UPPER(TRIM(B159))="SWALE",UPPER(TRIM(AI159))="PIPE"),AND(UPPER(TRIM(B159))="TRENCH",UPPER(TRIM(AI159))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL159" s="4">
+        <f>IF(A159="","",IF(E159="","TERMINAL",IF(OR(AND(UPPER(TRIM(B159))="SWALE",UPPER(TRIM(AI159))="PIPE"),AND(UPPER(TRIM(B159))="TRENCH",UPPER(TRIM(AI159))="PIPE")),IF(OR(AG159="",AJ159="",AK159=""),"INFO",IF(AND(AG159&gt;=AJ159,AG159&lt;=AK159),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -22983,7 +25614,23 @@
         <v/>
       </c>
       <c r="AH160" s="4">
-        <f>IF(A160="","",IF(E160="","TERMINAL",IF(AG160="","INFO",IF(ABS(AG160)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A160="","",IF(E160="","TERMINAL",IF(OR(AND(UPPER(TRIM(B160))="SWALE",UPPER(TRIM(AI160))="PIPE"),AND(UPPER(TRIM(B160))="TRENCH",UPPER(TRIM(AI160))="PIPE")),IF(OR(AG160="",AJ160="",AK160=""),"INFO",IF(AND(AG160&gt;=AJ160,AG160&lt;=AK160),"OK","CHECK")),IF(AG160="","INFO",IF(ABS(AG160)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI160" s="17">
+        <f>IF(A160="","",IF(E160="","",IFERROR(INDEX($B$4:$B$204,MATCH(E160,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ160" s="17">
+        <f>IF(A160="","",IF(OR(AND(UPPER(TRIM(B160))="SWALE",UPPER(TRIM(AI160))="PIPE"),AND(UPPER(TRIM(B160))="TRENCH",UPPER(TRIM(AI160))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK160" s="17">
+        <f>IF(A160="","",IF(OR(AND(UPPER(TRIM(B160))="SWALE",UPPER(TRIM(AI160))="PIPE"),AND(UPPER(TRIM(B160))="TRENCH",UPPER(TRIM(AI160))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL160" s="4">
+        <f>IF(A160="","",IF(E160="","TERMINAL",IF(OR(AND(UPPER(TRIM(B160))="SWALE",UPPER(TRIM(AI160))="PIPE"),AND(UPPER(TRIM(B160))="TRENCH",UPPER(TRIM(AI160))="PIPE")),IF(OR(AG160="",AJ160="",AK160=""),"INFO",IF(AND(AG160&gt;=AJ160,AG160&lt;=AK160),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23078,7 +25725,23 @@
         <v/>
       </c>
       <c r="AH161" s="4">
-        <f>IF(A161="","",IF(E161="","TERMINAL",IF(AG161="","INFO",IF(ABS(AG161)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A161="","",IF(E161="","TERMINAL",IF(OR(AND(UPPER(TRIM(B161))="SWALE",UPPER(TRIM(AI161))="PIPE"),AND(UPPER(TRIM(B161))="TRENCH",UPPER(TRIM(AI161))="PIPE")),IF(OR(AG161="",AJ161="",AK161=""),"INFO",IF(AND(AG161&gt;=AJ161,AG161&lt;=AK161),"OK","CHECK")),IF(AG161="","INFO",IF(ABS(AG161)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI161" s="17">
+        <f>IF(A161="","",IF(E161="","",IFERROR(INDEX($B$4:$B$204,MATCH(E161,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ161" s="17">
+        <f>IF(A161="","",IF(OR(AND(UPPER(TRIM(B161))="SWALE",UPPER(TRIM(AI161))="PIPE"),AND(UPPER(TRIM(B161))="TRENCH",UPPER(TRIM(AI161))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK161" s="17">
+        <f>IF(A161="","",IF(OR(AND(UPPER(TRIM(B161))="SWALE",UPPER(TRIM(AI161))="PIPE"),AND(UPPER(TRIM(B161))="TRENCH",UPPER(TRIM(AI161))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL161" s="4">
+        <f>IF(A161="","",IF(E161="","TERMINAL",IF(OR(AND(UPPER(TRIM(B161))="SWALE",UPPER(TRIM(AI161))="PIPE"),AND(UPPER(TRIM(B161))="TRENCH",UPPER(TRIM(AI161))="PIPE")),IF(OR(AG161="",AJ161="",AK161=""),"INFO",IF(AND(AG161&gt;=AJ161,AG161&lt;=AK161),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23173,7 +25836,23 @@
         <v/>
       </c>
       <c r="AH162" s="4">
-        <f>IF(A162="","",IF(E162="","TERMINAL",IF(AG162="","INFO",IF(ABS(AG162)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A162="","",IF(E162="","TERMINAL",IF(OR(AND(UPPER(TRIM(B162))="SWALE",UPPER(TRIM(AI162))="PIPE"),AND(UPPER(TRIM(B162))="TRENCH",UPPER(TRIM(AI162))="PIPE")),IF(OR(AG162="",AJ162="",AK162=""),"INFO",IF(AND(AG162&gt;=AJ162,AG162&lt;=AK162),"OK","CHECK")),IF(AG162="","INFO",IF(ABS(AG162)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI162" s="17">
+        <f>IF(A162="","",IF(E162="","",IFERROR(INDEX($B$4:$B$204,MATCH(E162,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ162" s="17">
+        <f>IF(A162="","",IF(OR(AND(UPPER(TRIM(B162))="SWALE",UPPER(TRIM(AI162))="PIPE"),AND(UPPER(TRIM(B162))="TRENCH",UPPER(TRIM(AI162))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK162" s="17">
+        <f>IF(A162="","",IF(OR(AND(UPPER(TRIM(B162))="SWALE",UPPER(TRIM(AI162))="PIPE"),AND(UPPER(TRIM(B162))="TRENCH",UPPER(TRIM(AI162))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL162" s="4">
+        <f>IF(A162="","",IF(E162="","TERMINAL",IF(OR(AND(UPPER(TRIM(B162))="SWALE",UPPER(TRIM(AI162))="PIPE"),AND(UPPER(TRIM(B162))="TRENCH",UPPER(TRIM(AI162))="PIPE")),IF(OR(AG162="",AJ162="",AK162=""),"INFO",IF(AND(AG162&gt;=AJ162,AG162&lt;=AK162),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23268,7 +25947,23 @@
         <v/>
       </c>
       <c r="AH163" s="4">
-        <f>IF(A163="","",IF(E163="","TERMINAL",IF(AG163="","INFO",IF(ABS(AG163)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A163="","",IF(E163="","TERMINAL",IF(OR(AND(UPPER(TRIM(B163))="SWALE",UPPER(TRIM(AI163))="PIPE"),AND(UPPER(TRIM(B163))="TRENCH",UPPER(TRIM(AI163))="PIPE")),IF(OR(AG163="",AJ163="",AK163=""),"INFO",IF(AND(AG163&gt;=AJ163,AG163&lt;=AK163),"OK","CHECK")),IF(AG163="","INFO",IF(ABS(AG163)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI163" s="17">
+        <f>IF(A163="","",IF(E163="","",IFERROR(INDEX($B$4:$B$204,MATCH(E163,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ163" s="17">
+        <f>IF(A163="","",IF(OR(AND(UPPER(TRIM(B163))="SWALE",UPPER(TRIM(AI163))="PIPE"),AND(UPPER(TRIM(B163))="TRENCH",UPPER(TRIM(AI163))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK163" s="17">
+        <f>IF(A163="","",IF(OR(AND(UPPER(TRIM(B163))="SWALE",UPPER(TRIM(AI163))="PIPE"),AND(UPPER(TRIM(B163))="TRENCH",UPPER(TRIM(AI163))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL163" s="4">
+        <f>IF(A163="","",IF(E163="","TERMINAL",IF(OR(AND(UPPER(TRIM(B163))="SWALE",UPPER(TRIM(AI163))="PIPE"),AND(UPPER(TRIM(B163))="TRENCH",UPPER(TRIM(AI163))="PIPE")),IF(OR(AG163="",AJ163="",AK163=""),"INFO",IF(AND(AG163&gt;=AJ163,AG163&lt;=AK163),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23363,7 +26058,23 @@
         <v/>
       </c>
       <c r="AH164" s="4">
-        <f>IF(A164="","",IF(E164="","TERMINAL",IF(AG164="","INFO",IF(ABS(AG164)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A164="","",IF(E164="","TERMINAL",IF(OR(AND(UPPER(TRIM(B164))="SWALE",UPPER(TRIM(AI164))="PIPE"),AND(UPPER(TRIM(B164))="TRENCH",UPPER(TRIM(AI164))="PIPE")),IF(OR(AG164="",AJ164="",AK164=""),"INFO",IF(AND(AG164&gt;=AJ164,AG164&lt;=AK164),"OK","CHECK")),IF(AG164="","INFO",IF(ABS(AG164)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI164" s="17">
+        <f>IF(A164="","",IF(E164="","",IFERROR(INDEX($B$4:$B$204,MATCH(E164,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ164" s="17">
+        <f>IF(A164="","",IF(OR(AND(UPPER(TRIM(B164))="SWALE",UPPER(TRIM(AI164))="PIPE"),AND(UPPER(TRIM(B164))="TRENCH",UPPER(TRIM(AI164))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK164" s="17">
+        <f>IF(A164="","",IF(OR(AND(UPPER(TRIM(B164))="SWALE",UPPER(TRIM(AI164))="PIPE"),AND(UPPER(TRIM(B164))="TRENCH",UPPER(TRIM(AI164))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL164" s="4">
+        <f>IF(A164="","",IF(E164="","TERMINAL",IF(OR(AND(UPPER(TRIM(B164))="SWALE",UPPER(TRIM(AI164))="PIPE"),AND(UPPER(TRIM(B164))="TRENCH",UPPER(TRIM(AI164))="PIPE")),IF(OR(AG164="",AJ164="",AK164=""),"INFO",IF(AND(AG164&gt;=AJ164,AG164&lt;=AK164),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23458,7 +26169,23 @@
         <v/>
       </c>
       <c r="AH165" s="4">
-        <f>IF(A165="","",IF(E165="","TERMINAL",IF(AG165="","INFO",IF(ABS(AG165)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A165="","",IF(E165="","TERMINAL",IF(OR(AND(UPPER(TRIM(B165))="SWALE",UPPER(TRIM(AI165))="PIPE"),AND(UPPER(TRIM(B165))="TRENCH",UPPER(TRIM(AI165))="PIPE")),IF(OR(AG165="",AJ165="",AK165=""),"INFO",IF(AND(AG165&gt;=AJ165,AG165&lt;=AK165),"OK","CHECK")),IF(AG165="","INFO",IF(ABS(AG165)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI165" s="17">
+        <f>IF(A165="","",IF(E165="","",IFERROR(INDEX($B$4:$B$204,MATCH(E165,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ165" s="17">
+        <f>IF(A165="","",IF(OR(AND(UPPER(TRIM(B165))="SWALE",UPPER(TRIM(AI165))="PIPE"),AND(UPPER(TRIM(B165))="TRENCH",UPPER(TRIM(AI165))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK165" s="17">
+        <f>IF(A165="","",IF(OR(AND(UPPER(TRIM(B165))="SWALE",UPPER(TRIM(AI165))="PIPE"),AND(UPPER(TRIM(B165))="TRENCH",UPPER(TRIM(AI165))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL165" s="4">
+        <f>IF(A165="","",IF(E165="","TERMINAL",IF(OR(AND(UPPER(TRIM(B165))="SWALE",UPPER(TRIM(AI165))="PIPE"),AND(UPPER(TRIM(B165))="TRENCH",UPPER(TRIM(AI165))="PIPE")),IF(OR(AG165="",AJ165="",AK165=""),"INFO",IF(AND(AG165&gt;=AJ165,AG165&lt;=AK165),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23553,7 +26280,23 @@
         <v/>
       </c>
       <c r="AH166" s="4">
-        <f>IF(A166="","",IF(E166="","TERMINAL",IF(AG166="","INFO",IF(ABS(AG166)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A166="","",IF(E166="","TERMINAL",IF(OR(AND(UPPER(TRIM(B166))="SWALE",UPPER(TRIM(AI166))="PIPE"),AND(UPPER(TRIM(B166))="TRENCH",UPPER(TRIM(AI166))="PIPE")),IF(OR(AG166="",AJ166="",AK166=""),"INFO",IF(AND(AG166&gt;=AJ166,AG166&lt;=AK166),"OK","CHECK")),IF(AG166="","INFO",IF(ABS(AG166)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI166" s="17">
+        <f>IF(A166="","",IF(E166="","",IFERROR(INDEX($B$4:$B$204,MATCH(E166,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ166" s="17">
+        <f>IF(A166="","",IF(OR(AND(UPPER(TRIM(B166))="SWALE",UPPER(TRIM(AI166))="PIPE"),AND(UPPER(TRIM(B166))="TRENCH",UPPER(TRIM(AI166))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK166" s="17">
+        <f>IF(A166="","",IF(OR(AND(UPPER(TRIM(B166))="SWALE",UPPER(TRIM(AI166))="PIPE"),AND(UPPER(TRIM(B166))="TRENCH",UPPER(TRIM(AI166))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL166" s="4">
+        <f>IF(A166="","",IF(E166="","TERMINAL",IF(OR(AND(UPPER(TRIM(B166))="SWALE",UPPER(TRIM(AI166))="PIPE"),AND(UPPER(TRIM(B166))="TRENCH",UPPER(TRIM(AI166))="PIPE")),IF(OR(AG166="",AJ166="",AK166=""),"INFO",IF(AND(AG166&gt;=AJ166,AG166&lt;=AK166),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23648,7 +26391,23 @@
         <v/>
       </c>
       <c r="AH167" s="4">
-        <f>IF(A167="","",IF(E167="","TERMINAL",IF(AG167="","INFO",IF(ABS(AG167)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A167="","",IF(E167="","TERMINAL",IF(OR(AND(UPPER(TRIM(B167))="SWALE",UPPER(TRIM(AI167))="PIPE"),AND(UPPER(TRIM(B167))="TRENCH",UPPER(TRIM(AI167))="PIPE")),IF(OR(AG167="",AJ167="",AK167=""),"INFO",IF(AND(AG167&gt;=AJ167,AG167&lt;=AK167),"OK","CHECK")),IF(AG167="","INFO",IF(ABS(AG167)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI167" s="17">
+        <f>IF(A167="","",IF(E167="","",IFERROR(INDEX($B$4:$B$204,MATCH(E167,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ167" s="17">
+        <f>IF(A167="","",IF(OR(AND(UPPER(TRIM(B167))="SWALE",UPPER(TRIM(AI167))="PIPE"),AND(UPPER(TRIM(B167))="TRENCH",UPPER(TRIM(AI167))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK167" s="17">
+        <f>IF(A167="","",IF(OR(AND(UPPER(TRIM(B167))="SWALE",UPPER(TRIM(AI167))="PIPE"),AND(UPPER(TRIM(B167))="TRENCH",UPPER(TRIM(AI167))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL167" s="4">
+        <f>IF(A167="","",IF(E167="","TERMINAL",IF(OR(AND(UPPER(TRIM(B167))="SWALE",UPPER(TRIM(AI167))="PIPE"),AND(UPPER(TRIM(B167))="TRENCH",UPPER(TRIM(AI167))="PIPE")),IF(OR(AG167="",AJ167="",AK167=""),"INFO",IF(AND(AG167&gt;=AJ167,AG167&lt;=AK167),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23743,7 +26502,23 @@
         <v/>
       </c>
       <c r="AH168" s="4">
-        <f>IF(A168="","",IF(E168="","TERMINAL",IF(AG168="","INFO",IF(ABS(AG168)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A168="","",IF(E168="","TERMINAL",IF(OR(AND(UPPER(TRIM(B168))="SWALE",UPPER(TRIM(AI168))="PIPE"),AND(UPPER(TRIM(B168))="TRENCH",UPPER(TRIM(AI168))="PIPE")),IF(OR(AG168="",AJ168="",AK168=""),"INFO",IF(AND(AG168&gt;=AJ168,AG168&lt;=AK168),"OK","CHECK")),IF(AG168="","INFO",IF(ABS(AG168)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI168" s="17">
+        <f>IF(A168="","",IF(E168="","",IFERROR(INDEX($B$4:$B$204,MATCH(E168,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ168" s="17">
+        <f>IF(A168="","",IF(OR(AND(UPPER(TRIM(B168))="SWALE",UPPER(TRIM(AI168))="PIPE"),AND(UPPER(TRIM(B168))="TRENCH",UPPER(TRIM(AI168))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK168" s="17">
+        <f>IF(A168="","",IF(OR(AND(UPPER(TRIM(B168))="SWALE",UPPER(TRIM(AI168))="PIPE"),AND(UPPER(TRIM(B168))="TRENCH",UPPER(TRIM(AI168))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL168" s="4">
+        <f>IF(A168="","",IF(E168="","TERMINAL",IF(OR(AND(UPPER(TRIM(B168))="SWALE",UPPER(TRIM(AI168))="PIPE"),AND(UPPER(TRIM(B168))="TRENCH",UPPER(TRIM(AI168))="PIPE")),IF(OR(AG168="",AJ168="",AK168=""),"INFO",IF(AND(AG168&gt;=AJ168,AG168&lt;=AK168),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23838,7 +26613,23 @@
         <v/>
       </c>
       <c r="AH169" s="4">
-        <f>IF(A169="","",IF(E169="","TERMINAL",IF(AG169="","INFO",IF(ABS(AG169)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A169="","",IF(E169="","TERMINAL",IF(OR(AND(UPPER(TRIM(B169))="SWALE",UPPER(TRIM(AI169))="PIPE"),AND(UPPER(TRIM(B169))="TRENCH",UPPER(TRIM(AI169))="PIPE")),IF(OR(AG169="",AJ169="",AK169=""),"INFO",IF(AND(AG169&gt;=AJ169,AG169&lt;=AK169),"OK","CHECK")),IF(AG169="","INFO",IF(ABS(AG169)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI169" s="17">
+        <f>IF(A169="","",IF(E169="","",IFERROR(INDEX($B$4:$B$204,MATCH(E169,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ169" s="17">
+        <f>IF(A169="","",IF(OR(AND(UPPER(TRIM(B169))="SWALE",UPPER(TRIM(AI169))="PIPE"),AND(UPPER(TRIM(B169))="TRENCH",UPPER(TRIM(AI169))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK169" s="17">
+        <f>IF(A169="","",IF(OR(AND(UPPER(TRIM(B169))="SWALE",UPPER(TRIM(AI169))="PIPE"),AND(UPPER(TRIM(B169))="TRENCH",UPPER(TRIM(AI169))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL169" s="4">
+        <f>IF(A169="","",IF(E169="","TERMINAL",IF(OR(AND(UPPER(TRIM(B169))="SWALE",UPPER(TRIM(AI169))="PIPE"),AND(UPPER(TRIM(B169))="TRENCH",UPPER(TRIM(AI169))="PIPE")),IF(OR(AG169="",AJ169="",AK169=""),"INFO",IF(AND(AG169&gt;=AJ169,AG169&lt;=AK169),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -23933,7 +26724,23 @@
         <v/>
       </c>
       <c r="AH170" s="4">
-        <f>IF(A170="","",IF(E170="","TERMINAL",IF(AG170="","INFO",IF(ABS(AG170)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A170="","",IF(E170="","TERMINAL",IF(OR(AND(UPPER(TRIM(B170))="SWALE",UPPER(TRIM(AI170))="PIPE"),AND(UPPER(TRIM(B170))="TRENCH",UPPER(TRIM(AI170))="PIPE")),IF(OR(AG170="",AJ170="",AK170=""),"INFO",IF(AND(AG170&gt;=AJ170,AG170&lt;=AK170),"OK","CHECK")),IF(AG170="","INFO",IF(ABS(AG170)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI170" s="17">
+        <f>IF(A170="","",IF(E170="","",IFERROR(INDEX($B$4:$B$204,MATCH(E170,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ170" s="17">
+        <f>IF(A170="","",IF(OR(AND(UPPER(TRIM(B170))="SWALE",UPPER(TRIM(AI170))="PIPE"),AND(UPPER(TRIM(B170))="TRENCH",UPPER(TRIM(AI170))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK170" s="17">
+        <f>IF(A170="","",IF(OR(AND(UPPER(TRIM(B170))="SWALE",UPPER(TRIM(AI170))="PIPE"),AND(UPPER(TRIM(B170))="TRENCH",UPPER(TRIM(AI170))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL170" s="4">
+        <f>IF(A170="","",IF(E170="","TERMINAL",IF(OR(AND(UPPER(TRIM(B170))="SWALE",UPPER(TRIM(AI170))="PIPE"),AND(UPPER(TRIM(B170))="TRENCH",UPPER(TRIM(AI170))="PIPE")),IF(OR(AG170="",AJ170="",AK170=""),"INFO",IF(AND(AG170&gt;=AJ170,AG170&lt;=AK170),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24028,7 +26835,23 @@
         <v/>
       </c>
       <c r="AH171" s="4">
-        <f>IF(A171="","",IF(E171="","TERMINAL",IF(AG171="","INFO",IF(ABS(AG171)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A171="","",IF(E171="","TERMINAL",IF(OR(AND(UPPER(TRIM(B171))="SWALE",UPPER(TRIM(AI171))="PIPE"),AND(UPPER(TRIM(B171))="TRENCH",UPPER(TRIM(AI171))="PIPE")),IF(OR(AG171="",AJ171="",AK171=""),"INFO",IF(AND(AG171&gt;=AJ171,AG171&lt;=AK171),"OK","CHECK")),IF(AG171="","INFO",IF(ABS(AG171)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI171" s="17">
+        <f>IF(A171="","",IF(E171="","",IFERROR(INDEX($B$4:$B$204,MATCH(E171,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ171" s="17">
+        <f>IF(A171="","",IF(OR(AND(UPPER(TRIM(B171))="SWALE",UPPER(TRIM(AI171))="PIPE"),AND(UPPER(TRIM(B171))="TRENCH",UPPER(TRIM(AI171))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK171" s="17">
+        <f>IF(A171="","",IF(OR(AND(UPPER(TRIM(B171))="SWALE",UPPER(TRIM(AI171))="PIPE"),AND(UPPER(TRIM(B171))="TRENCH",UPPER(TRIM(AI171))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL171" s="4">
+        <f>IF(A171="","",IF(E171="","TERMINAL",IF(OR(AND(UPPER(TRIM(B171))="SWALE",UPPER(TRIM(AI171))="PIPE"),AND(UPPER(TRIM(B171))="TRENCH",UPPER(TRIM(AI171))="PIPE")),IF(OR(AG171="",AJ171="",AK171=""),"INFO",IF(AND(AG171&gt;=AJ171,AG171&lt;=AK171),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24123,7 +26946,23 @@
         <v/>
       </c>
       <c r="AH172" s="4">
-        <f>IF(A172="","",IF(E172="","TERMINAL",IF(AG172="","INFO",IF(ABS(AG172)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A172="","",IF(E172="","TERMINAL",IF(OR(AND(UPPER(TRIM(B172))="SWALE",UPPER(TRIM(AI172))="PIPE"),AND(UPPER(TRIM(B172))="TRENCH",UPPER(TRIM(AI172))="PIPE")),IF(OR(AG172="",AJ172="",AK172=""),"INFO",IF(AND(AG172&gt;=AJ172,AG172&lt;=AK172),"OK","CHECK")),IF(AG172="","INFO",IF(ABS(AG172)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI172" s="17">
+        <f>IF(A172="","",IF(E172="","",IFERROR(INDEX($B$4:$B$204,MATCH(E172,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ172" s="17">
+        <f>IF(A172="","",IF(OR(AND(UPPER(TRIM(B172))="SWALE",UPPER(TRIM(AI172))="PIPE"),AND(UPPER(TRIM(B172))="TRENCH",UPPER(TRIM(AI172))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK172" s="17">
+        <f>IF(A172="","",IF(OR(AND(UPPER(TRIM(B172))="SWALE",UPPER(TRIM(AI172))="PIPE"),AND(UPPER(TRIM(B172))="TRENCH",UPPER(TRIM(AI172))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL172" s="4">
+        <f>IF(A172="","",IF(E172="","TERMINAL",IF(OR(AND(UPPER(TRIM(B172))="SWALE",UPPER(TRIM(AI172))="PIPE"),AND(UPPER(TRIM(B172))="TRENCH",UPPER(TRIM(AI172))="PIPE")),IF(OR(AG172="",AJ172="",AK172=""),"INFO",IF(AND(AG172&gt;=AJ172,AG172&lt;=AK172),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24218,7 +27057,23 @@
         <v/>
       </c>
       <c r="AH173" s="4">
-        <f>IF(A173="","",IF(E173="","TERMINAL",IF(AG173="","INFO",IF(ABS(AG173)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A173="","",IF(E173="","TERMINAL",IF(OR(AND(UPPER(TRIM(B173))="SWALE",UPPER(TRIM(AI173))="PIPE"),AND(UPPER(TRIM(B173))="TRENCH",UPPER(TRIM(AI173))="PIPE")),IF(OR(AG173="",AJ173="",AK173=""),"INFO",IF(AND(AG173&gt;=AJ173,AG173&lt;=AK173),"OK","CHECK")),IF(AG173="","INFO",IF(ABS(AG173)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI173" s="17">
+        <f>IF(A173="","",IF(E173="","",IFERROR(INDEX($B$4:$B$204,MATCH(E173,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ173" s="17">
+        <f>IF(A173="","",IF(OR(AND(UPPER(TRIM(B173))="SWALE",UPPER(TRIM(AI173))="PIPE"),AND(UPPER(TRIM(B173))="TRENCH",UPPER(TRIM(AI173))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK173" s="17">
+        <f>IF(A173="","",IF(OR(AND(UPPER(TRIM(B173))="SWALE",UPPER(TRIM(AI173))="PIPE"),AND(UPPER(TRIM(B173))="TRENCH",UPPER(TRIM(AI173))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL173" s="4">
+        <f>IF(A173="","",IF(E173="","TERMINAL",IF(OR(AND(UPPER(TRIM(B173))="SWALE",UPPER(TRIM(AI173))="PIPE"),AND(UPPER(TRIM(B173))="TRENCH",UPPER(TRIM(AI173))="PIPE")),IF(OR(AG173="",AJ173="",AK173=""),"INFO",IF(AND(AG173&gt;=AJ173,AG173&lt;=AK173),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24313,7 +27168,23 @@
         <v/>
       </c>
       <c r="AH174" s="4">
-        <f>IF(A174="","",IF(E174="","TERMINAL",IF(AG174="","INFO",IF(ABS(AG174)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A174="","",IF(E174="","TERMINAL",IF(OR(AND(UPPER(TRIM(B174))="SWALE",UPPER(TRIM(AI174))="PIPE"),AND(UPPER(TRIM(B174))="TRENCH",UPPER(TRIM(AI174))="PIPE")),IF(OR(AG174="",AJ174="",AK174=""),"INFO",IF(AND(AG174&gt;=AJ174,AG174&lt;=AK174),"OK","CHECK")),IF(AG174="","INFO",IF(ABS(AG174)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI174" s="17">
+        <f>IF(A174="","",IF(E174="","",IFERROR(INDEX($B$4:$B$204,MATCH(E174,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ174" s="17">
+        <f>IF(A174="","",IF(OR(AND(UPPER(TRIM(B174))="SWALE",UPPER(TRIM(AI174))="PIPE"),AND(UPPER(TRIM(B174))="TRENCH",UPPER(TRIM(AI174))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK174" s="17">
+        <f>IF(A174="","",IF(OR(AND(UPPER(TRIM(B174))="SWALE",UPPER(TRIM(AI174))="PIPE"),AND(UPPER(TRIM(B174))="TRENCH",UPPER(TRIM(AI174))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL174" s="4">
+        <f>IF(A174="","",IF(E174="","TERMINAL",IF(OR(AND(UPPER(TRIM(B174))="SWALE",UPPER(TRIM(AI174))="PIPE"),AND(UPPER(TRIM(B174))="TRENCH",UPPER(TRIM(AI174))="PIPE")),IF(OR(AG174="",AJ174="",AK174=""),"INFO",IF(AND(AG174&gt;=AJ174,AG174&lt;=AK174),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24408,7 +27279,23 @@
         <v/>
       </c>
       <c r="AH175" s="4">
-        <f>IF(A175="","",IF(E175="","TERMINAL",IF(AG175="","INFO",IF(ABS(AG175)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A175="","",IF(E175="","TERMINAL",IF(OR(AND(UPPER(TRIM(B175))="SWALE",UPPER(TRIM(AI175))="PIPE"),AND(UPPER(TRIM(B175))="TRENCH",UPPER(TRIM(AI175))="PIPE")),IF(OR(AG175="",AJ175="",AK175=""),"INFO",IF(AND(AG175&gt;=AJ175,AG175&lt;=AK175),"OK","CHECK")),IF(AG175="","INFO",IF(ABS(AG175)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI175" s="17">
+        <f>IF(A175="","",IF(E175="","",IFERROR(INDEX($B$4:$B$204,MATCH(E175,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ175" s="17">
+        <f>IF(A175="","",IF(OR(AND(UPPER(TRIM(B175))="SWALE",UPPER(TRIM(AI175))="PIPE"),AND(UPPER(TRIM(B175))="TRENCH",UPPER(TRIM(AI175))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK175" s="17">
+        <f>IF(A175="","",IF(OR(AND(UPPER(TRIM(B175))="SWALE",UPPER(TRIM(AI175))="PIPE"),AND(UPPER(TRIM(B175))="TRENCH",UPPER(TRIM(AI175))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL175" s="4">
+        <f>IF(A175="","",IF(E175="","TERMINAL",IF(OR(AND(UPPER(TRIM(B175))="SWALE",UPPER(TRIM(AI175))="PIPE"),AND(UPPER(TRIM(B175))="TRENCH",UPPER(TRIM(AI175))="PIPE")),IF(OR(AG175="",AJ175="",AK175=""),"INFO",IF(AND(AG175&gt;=AJ175,AG175&lt;=AK175),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24503,7 +27390,23 @@
         <v/>
       </c>
       <c r="AH176" s="4">
-        <f>IF(A176="","",IF(E176="","TERMINAL",IF(AG176="","INFO",IF(ABS(AG176)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A176="","",IF(E176="","TERMINAL",IF(OR(AND(UPPER(TRIM(B176))="SWALE",UPPER(TRIM(AI176))="PIPE"),AND(UPPER(TRIM(B176))="TRENCH",UPPER(TRIM(AI176))="PIPE")),IF(OR(AG176="",AJ176="",AK176=""),"INFO",IF(AND(AG176&gt;=AJ176,AG176&lt;=AK176),"OK","CHECK")),IF(AG176="","INFO",IF(ABS(AG176)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI176" s="17">
+        <f>IF(A176="","",IF(E176="","",IFERROR(INDEX($B$4:$B$204,MATCH(E176,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ176" s="17">
+        <f>IF(A176="","",IF(OR(AND(UPPER(TRIM(B176))="SWALE",UPPER(TRIM(AI176))="PIPE"),AND(UPPER(TRIM(B176))="TRENCH",UPPER(TRIM(AI176))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK176" s="17">
+        <f>IF(A176="","",IF(OR(AND(UPPER(TRIM(B176))="SWALE",UPPER(TRIM(AI176))="PIPE"),AND(UPPER(TRIM(B176))="TRENCH",UPPER(TRIM(AI176))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL176" s="4">
+        <f>IF(A176="","",IF(E176="","TERMINAL",IF(OR(AND(UPPER(TRIM(B176))="SWALE",UPPER(TRIM(AI176))="PIPE"),AND(UPPER(TRIM(B176))="TRENCH",UPPER(TRIM(AI176))="PIPE")),IF(OR(AG176="",AJ176="",AK176=""),"INFO",IF(AND(AG176&gt;=AJ176,AG176&lt;=AK176),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24598,7 +27501,23 @@
         <v/>
       </c>
       <c r="AH177" s="4">
-        <f>IF(A177="","",IF(E177="","TERMINAL",IF(AG177="","INFO",IF(ABS(AG177)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A177="","",IF(E177="","TERMINAL",IF(OR(AND(UPPER(TRIM(B177))="SWALE",UPPER(TRIM(AI177))="PIPE"),AND(UPPER(TRIM(B177))="TRENCH",UPPER(TRIM(AI177))="PIPE")),IF(OR(AG177="",AJ177="",AK177=""),"INFO",IF(AND(AG177&gt;=AJ177,AG177&lt;=AK177),"OK","CHECK")),IF(AG177="","INFO",IF(ABS(AG177)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI177" s="17">
+        <f>IF(A177="","",IF(E177="","",IFERROR(INDEX($B$4:$B$204,MATCH(E177,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ177" s="17">
+        <f>IF(A177="","",IF(OR(AND(UPPER(TRIM(B177))="SWALE",UPPER(TRIM(AI177))="PIPE"),AND(UPPER(TRIM(B177))="TRENCH",UPPER(TRIM(AI177))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK177" s="17">
+        <f>IF(A177="","",IF(OR(AND(UPPER(TRIM(B177))="SWALE",UPPER(TRIM(AI177))="PIPE"),AND(UPPER(TRIM(B177))="TRENCH",UPPER(TRIM(AI177))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL177" s="4">
+        <f>IF(A177="","",IF(E177="","TERMINAL",IF(OR(AND(UPPER(TRIM(B177))="SWALE",UPPER(TRIM(AI177))="PIPE"),AND(UPPER(TRIM(B177))="TRENCH",UPPER(TRIM(AI177))="PIPE")),IF(OR(AG177="",AJ177="",AK177=""),"INFO",IF(AND(AG177&gt;=AJ177,AG177&lt;=AK177),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24693,7 +27612,23 @@
         <v/>
       </c>
       <c r="AH178" s="4">
-        <f>IF(A178="","",IF(E178="","TERMINAL",IF(AG178="","INFO",IF(ABS(AG178)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A178="","",IF(E178="","TERMINAL",IF(OR(AND(UPPER(TRIM(B178))="SWALE",UPPER(TRIM(AI178))="PIPE"),AND(UPPER(TRIM(B178))="TRENCH",UPPER(TRIM(AI178))="PIPE")),IF(OR(AG178="",AJ178="",AK178=""),"INFO",IF(AND(AG178&gt;=AJ178,AG178&lt;=AK178),"OK","CHECK")),IF(AG178="","INFO",IF(ABS(AG178)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI178" s="17">
+        <f>IF(A178="","",IF(E178="","",IFERROR(INDEX($B$4:$B$204,MATCH(E178,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ178" s="17">
+        <f>IF(A178="","",IF(OR(AND(UPPER(TRIM(B178))="SWALE",UPPER(TRIM(AI178))="PIPE"),AND(UPPER(TRIM(B178))="TRENCH",UPPER(TRIM(AI178))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK178" s="17">
+        <f>IF(A178="","",IF(OR(AND(UPPER(TRIM(B178))="SWALE",UPPER(TRIM(AI178))="PIPE"),AND(UPPER(TRIM(B178))="TRENCH",UPPER(TRIM(AI178))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL178" s="4">
+        <f>IF(A178="","",IF(E178="","TERMINAL",IF(OR(AND(UPPER(TRIM(B178))="SWALE",UPPER(TRIM(AI178))="PIPE"),AND(UPPER(TRIM(B178))="TRENCH",UPPER(TRIM(AI178))="PIPE")),IF(OR(AG178="",AJ178="",AK178=""),"INFO",IF(AND(AG178&gt;=AJ178,AG178&lt;=AK178),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24788,7 +27723,23 @@
         <v/>
       </c>
       <c r="AH179" s="4">
-        <f>IF(A179="","",IF(E179="","TERMINAL",IF(AG179="","INFO",IF(ABS(AG179)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A179="","",IF(E179="","TERMINAL",IF(OR(AND(UPPER(TRIM(B179))="SWALE",UPPER(TRIM(AI179))="PIPE"),AND(UPPER(TRIM(B179))="TRENCH",UPPER(TRIM(AI179))="PIPE")),IF(OR(AG179="",AJ179="",AK179=""),"INFO",IF(AND(AG179&gt;=AJ179,AG179&lt;=AK179),"OK","CHECK")),IF(AG179="","INFO",IF(ABS(AG179)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI179" s="17">
+        <f>IF(A179="","",IF(E179="","",IFERROR(INDEX($B$4:$B$204,MATCH(E179,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ179" s="17">
+        <f>IF(A179="","",IF(OR(AND(UPPER(TRIM(B179))="SWALE",UPPER(TRIM(AI179))="PIPE"),AND(UPPER(TRIM(B179))="TRENCH",UPPER(TRIM(AI179))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK179" s="17">
+        <f>IF(A179="","",IF(OR(AND(UPPER(TRIM(B179))="SWALE",UPPER(TRIM(AI179))="PIPE"),AND(UPPER(TRIM(B179))="TRENCH",UPPER(TRIM(AI179))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL179" s="4">
+        <f>IF(A179="","",IF(E179="","TERMINAL",IF(OR(AND(UPPER(TRIM(B179))="SWALE",UPPER(TRIM(AI179))="PIPE"),AND(UPPER(TRIM(B179))="TRENCH",UPPER(TRIM(AI179))="PIPE")),IF(OR(AG179="",AJ179="",AK179=""),"INFO",IF(AND(AG179&gt;=AJ179,AG179&lt;=AK179),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24883,7 +27834,23 @@
         <v/>
       </c>
       <c r="AH180" s="4">
-        <f>IF(A180="","",IF(E180="","TERMINAL",IF(AG180="","INFO",IF(ABS(AG180)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A180="","",IF(E180="","TERMINAL",IF(OR(AND(UPPER(TRIM(B180))="SWALE",UPPER(TRIM(AI180))="PIPE"),AND(UPPER(TRIM(B180))="TRENCH",UPPER(TRIM(AI180))="PIPE")),IF(OR(AG180="",AJ180="",AK180=""),"INFO",IF(AND(AG180&gt;=AJ180,AG180&lt;=AK180),"OK","CHECK")),IF(AG180="","INFO",IF(ABS(AG180)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI180" s="17">
+        <f>IF(A180="","",IF(E180="","",IFERROR(INDEX($B$4:$B$204,MATCH(E180,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ180" s="17">
+        <f>IF(A180="","",IF(OR(AND(UPPER(TRIM(B180))="SWALE",UPPER(TRIM(AI180))="PIPE"),AND(UPPER(TRIM(B180))="TRENCH",UPPER(TRIM(AI180))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK180" s="17">
+        <f>IF(A180="","",IF(OR(AND(UPPER(TRIM(B180))="SWALE",UPPER(TRIM(AI180))="PIPE"),AND(UPPER(TRIM(B180))="TRENCH",UPPER(TRIM(AI180))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL180" s="4">
+        <f>IF(A180="","",IF(E180="","TERMINAL",IF(OR(AND(UPPER(TRIM(B180))="SWALE",UPPER(TRIM(AI180))="PIPE"),AND(UPPER(TRIM(B180))="TRENCH",UPPER(TRIM(AI180))="PIPE")),IF(OR(AG180="",AJ180="",AK180=""),"INFO",IF(AND(AG180&gt;=AJ180,AG180&lt;=AK180),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -24978,7 +27945,23 @@
         <v/>
       </c>
       <c r="AH181" s="4">
-        <f>IF(A181="","",IF(E181="","TERMINAL",IF(AG181="","INFO",IF(ABS(AG181)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A181="","",IF(E181="","TERMINAL",IF(OR(AND(UPPER(TRIM(B181))="SWALE",UPPER(TRIM(AI181))="PIPE"),AND(UPPER(TRIM(B181))="TRENCH",UPPER(TRIM(AI181))="PIPE")),IF(OR(AG181="",AJ181="",AK181=""),"INFO",IF(AND(AG181&gt;=AJ181,AG181&lt;=AK181),"OK","CHECK")),IF(AG181="","INFO",IF(ABS(AG181)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI181" s="17">
+        <f>IF(A181="","",IF(E181="","",IFERROR(INDEX($B$4:$B$204,MATCH(E181,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ181" s="17">
+        <f>IF(A181="","",IF(OR(AND(UPPER(TRIM(B181))="SWALE",UPPER(TRIM(AI181))="PIPE"),AND(UPPER(TRIM(B181))="TRENCH",UPPER(TRIM(AI181))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK181" s="17">
+        <f>IF(A181="","",IF(OR(AND(UPPER(TRIM(B181))="SWALE",UPPER(TRIM(AI181))="PIPE"),AND(UPPER(TRIM(B181))="TRENCH",UPPER(TRIM(AI181))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL181" s="4">
+        <f>IF(A181="","",IF(E181="","TERMINAL",IF(OR(AND(UPPER(TRIM(B181))="SWALE",UPPER(TRIM(AI181))="PIPE"),AND(UPPER(TRIM(B181))="TRENCH",UPPER(TRIM(AI181))="PIPE")),IF(OR(AG181="",AJ181="",AK181=""),"INFO",IF(AND(AG181&gt;=AJ181,AG181&lt;=AK181),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25073,7 +28056,23 @@
         <v/>
       </c>
       <c r="AH182" s="4">
-        <f>IF(A182="","",IF(E182="","TERMINAL",IF(AG182="","INFO",IF(ABS(AG182)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A182="","",IF(E182="","TERMINAL",IF(OR(AND(UPPER(TRIM(B182))="SWALE",UPPER(TRIM(AI182))="PIPE"),AND(UPPER(TRIM(B182))="TRENCH",UPPER(TRIM(AI182))="PIPE")),IF(OR(AG182="",AJ182="",AK182=""),"INFO",IF(AND(AG182&gt;=AJ182,AG182&lt;=AK182),"OK","CHECK")),IF(AG182="","INFO",IF(ABS(AG182)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI182" s="17">
+        <f>IF(A182="","",IF(E182="","",IFERROR(INDEX($B$4:$B$204,MATCH(E182,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ182" s="17">
+        <f>IF(A182="","",IF(OR(AND(UPPER(TRIM(B182))="SWALE",UPPER(TRIM(AI182))="PIPE"),AND(UPPER(TRIM(B182))="TRENCH",UPPER(TRIM(AI182))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK182" s="17">
+        <f>IF(A182="","",IF(OR(AND(UPPER(TRIM(B182))="SWALE",UPPER(TRIM(AI182))="PIPE"),AND(UPPER(TRIM(B182))="TRENCH",UPPER(TRIM(AI182))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL182" s="4">
+        <f>IF(A182="","",IF(E182="","TERMINAL",IF(OR(AND(UPPER(TRIM(B182))="SWALE",UPPER(TRIM(AI182))="PIPE"),AND(UPPER(TRIM(B182))="TRENCH",UPPER(TRIM(AI182))="PIPE")),IF(OR(AG182="",AJ182="",AK182=""),"INFO",IF(AND(AG182&gt;=AJ182,AG182&lt;=AK182),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25168,7 +28167,23 @@
         <v/>
       </c>
       <c r="AH183" s="4">
-        <f>IF(A183="","",IF(E183="","TERMINAL",IF(AG183="","INFO",IF(ABS(AG183)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A183="","",IF(E183="","TERMINAL",IF(OR(AND(UPPER(TRIM(B183))="SWALE",UPPER(TRIM(AI183))="PIPE"),AND(UPPER(TRIM(B183))="TRENCH",UPPER(TRIM(AI183))="PIPE")),IF(OR(AG183="",AJ183="",AK183=""),"INFO",IF(AND(AG183&gt;=AJ183,AG183&lt;=AK183),"OK","CHECK")),IF(AG183="","INFO",IF(ABS(AG183)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI183" s="17">
+        <f>IF(A183="","",IF(E183="","",IFERROR(INDEX($B$4:$B$204,MATCH(E183,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ183" s="17">
+        <f>IF(A183="","",IF(OR(AND(UPPER(TRIM(B183))="SWALE",UPPER(TRIM(AI183))="PIPE"),AND(UPPER(TRIM(B183))="TRENCH",UPPER(TRIM(AI183))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK183" s="17">
+        <f>IF(A183="","",IF(OR(AND(UPPER(TRIM(B183))="SWALE",UPPER(TRIM(AI183))="PIPE"),AND(UPPER(TRIM(B183))="TRENCH",UPPER(TRIM(AI183))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL183" s="4">
+        <f>IF(A183="","",IF(E183="","TERMINAL",IF(OR(AND(UPPER(TRIM(B183))="SWALE",UPPER(TRIM(AI183))="PIPE"),AND(UPPER(TRIM(B183))="TRENCH",UPPER(TRIM(AI183))="PIPE")),IF(OR(AG183="",AJ183="",AK183=""),"INFO",IF(AND(AG183&gt;=AJ183,AG183&lt;=AK183),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25263,7 +28278,23 @@
         <v/>
       </c>
       <c r="AH184" s="4">
-        <f>IF(A184="","",IF(E184="","TERMINAL",IF(AG184="","INFO",IF(ABS(AG184)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A184="","",IF(E184="","TERMINAL",IF(OR(AND(UPPER(TRIM(B184))="SWALE",UPPER(TRIM(AI184))="PIPE"),AND(UPPER(TRIM(B184))="TRENCH",UPPER(TRIM(AI184))="PIPE")),IF(OR(AG184="",AJ184="",AK184=""),"INFO",IF(AND(AG184&gt;=AJ184,AG184&lt;=AK184),"OK","CHECK")),IF(AG184="","INFO",IF(ABS(AG184)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI184" s="17">
+        <f>IF(A184="","",IF(E184="","",IFERROR(INDEX($B$4:$B$204,MATCH(E184,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ184" s="17">
+        <f>IF(A184="","",IF(OR(AND(UPPER(TRIM(B184))="SWALE",UPPER(TRIM(AI184))="PIPE"),AND(UPPER(TRIM(B184))="TRENCH",UPPER(TRIM(AI184))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK184" s="17">
+        <f>IF(A184="","",IF(OR(AND(UPPER(TRIM(B184))="SWALE",UPPER(TRIM(AI184))="PIPE"),AND(UPPER(TRIM(B184))="TRENCH",UPPER(TRIM(AI184))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL184" s="4">
+        <f>IF(A184="","",IF(E184="","TERMINAL",IF(OR(AND(UPPER(TRIM(B184))="SWALE",UPPER(TRIM(AI184))="PIPE"),AND(UPPER(TRIM(B184))="TRENCH",UPPER(TRIM(AI184))="PIPE")),IF(OR(AG184="",AJ184="",AK184=""),"INFO",IF(AND(AG184&gt;=AJ184,AG184&lt;=AK184),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25358,7 +28389,23 @@
         <v/>
       </c>
       <c r="AH185" s="4">
-        <f>IF(A185="","",IF(E185="","TERMINAL",IF(AG185="","INFO",IF(ABS(AG185)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A185="","",IF(E185="","TERMINAL",IF(OR(AND(UPPER(TRIM(B185))="SWALE",UPPER(TRIM(AI185))="PIPE"),AND(UPPER(TRIM(B185))="TRENCH",UPPER(TRIM(AI185))="PIPE")),IF(OR(AG185="",AJ185="",AK185=""),"INFO",IF(AND(AG185&gt;=AJ185,AG185&lt;=AK185),"OK","CHECK")),IF(AG185="","INFO",IF(ABS(AG185)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI185" s="17">
+        <f>IF(A185="","",IF(E185="","",IFERROR(INDEX($B$4:$B$204,MATCH(E185,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ185" s="17">
+        <f>IF(A185="","",IF(OR(AND(UPPER(TRIM(B185))="SWALE",UPPER(TRIM(AI185))="PIPE"),AND(UPPER(TRIM(B185))="TRENCH",UPPER(TRIM(AI185))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK185" s="17">
+        <f>IF(A185="","",IF(OR(AND(UPPER(TRIM(B185))="SWALE",UPPER(TRIM(AI185))="PIPE"),AND(UPPER(TRIM(B185))="TRENCH",UPPER(TRIM(AI185))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL185" s="4">
+        <f>IF(A185="","",IF(E185="","TERMINAL",IF(OR(AND(UPPER(TRIM(B185))="SWALE",UPPER(TRIM(AI185))="PIPE"),AND(UPPER(TRIM(B185))="TRENCH",UPPER(TRIM(AI185))="PIPE")),IF(OR(AG185="",AJ185="",AK185=""),"INFO",IF(AND(AG185&gt;=AJ185,AG185&lt;=AK185),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25453,7 +28500,23 @@
         <v/>
       </c>
       <c r="AH186" s="4">
-        <f>IF(A186="","",IF(E186="","TERMINAL",IF(AG186="","INFO",IF(ABS(AG186)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A186="","",IF(E186="","TERMINAL",IF(OR(AND(UPPER(TRIM(B186))="SWALE",UPPER(TRIM(AI186))="PIPE"),AND(UPPER(TRIM(B186))="TRENCH",UPPER(TRIM(AI186))="PIPE")),IF(OR(AG186="",AJ186="",AK186=""),"INFO",IF(AND(AG186&gt;=AJ186,AG186&lt;=AK186),"OK","CHECK")),IF(AG186="","INFO",IF(ABS(AG186)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI186" s="17">
+        <f>IF(A186="","",IF(E186="","",IFERROR(INDEX($B$4:$B$204,MATCH(E186,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ186" s="17">
+        <f>IF(A186="","",IF(OR(AND(UPPER(TRIM(B186))="SWALE",UPPER(TRIM(AI186))="PIPE"),AND(UPPER(TRIM(B186))="TRENCH",UPPER(TRIM(AI186))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK186" s="17">
+        <f>IF(A186="","",IF(OR(AND(UPPER(TRIM(B186))="SWALE",UPPER(TRIM(AI186))="PIPE"),AND(UPPER(TRIM(B186))="TRENCH",UPPER(TRIM(AI186))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL186" s="4">
+        <f>IF(A186="","",IF(E186="","TERMINAL",IF(OR(AND(UPPER(TRIM(B186))="SWALE",UPPER(TRIM(AI186))="PIPE"),AND(UPPER(TRIM(B186))="TRENCH",UPPER(TRIM(AI186))="PIPE")),IF(OR(AG186="",AJ186="",AK186=""),"INFO",IF(AND(AG186&gt;=AJ186,AG186&lt;=AK186),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25548,7 +28611,23 @@
         <v/>
       </c>
       <c r="AH187" s="4">
-        <f>IF(A187="","",IF(E187="","TERMINAL",IF(AG187="","INFO",IF(ABS(AG187)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A187="","",IF(E187="","TERMINAL",IF(OR(AND(UPPER(TRIM(B187))="SWALE",UPPER(TRIM(AI187))="PIPE"),AND(UPPER(TRIM(B187))="TRENCH",UPPER(TRIM(AI187))="PIPE")),IF(OR(AG187="",AJ187="",AK187=""),"INFO",IF(AND(AG187&gt;=AJ187,AG187&lt;=AK187),"OK","CHECK")),IF(AG187="","INFO",IF(ABS(AG187)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI187" s="17">
+        <f>IF(A187="","",IF(E187="","",IFERROR(INDEX($B$4:$B$204,MATCH(E187,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ187" s="17">
+        <f>IF(A187="","",IF(OR(AND(UPPER(TRIM(B187))="SWALE",UPPER(TRIM(AI187))="PIPE"),AND(UPPER(TRIM(B187))="TRENCH",UPPER(TRIM(AI187))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK187" s="17">
+        <f>IF(A187="","",IF(OR(AND(UPPER(TRIM(B187))="SWALE",UPPER(TRIM(AI187))="PIPE"),AND(UPPER(TRIM(B187))="TRENCH",UPPER(TRIM(AI187))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL187" s="4">
+        <f>IF(A187="","",IF(E187="","TERMINAL",IF(OR(AND(UPPER(TRIM(B187))="SWALE",UPPER(TRIM(AI187))="PIPE"),AND(UPPER(TRIM(B187))="TRENCH",UPPER(TRIM(AI187))="PIPE")),IF(OR(AG187="",AJ187="",AK187=""),"INFO",IF(AND(AG187&gt;=AJ187,AG187&lt;=AK187),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25643,7 +28722,23 @@
         <v/>
       </c>
       <c r="AH188" s="4">
-        <f>IF(A188="","",IF(E188="","TERMINAL",IF(AG188="","INFO",IF(ABS(AG188)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A188="","",IF(E188="","TERMINAL",IF(OR(AND(UPPER(TRIM(B188))="SWALE",UPPER(TRIM(AI188))="PIPE"),AND(UPPER(TRIM(B188))="TRENCH",UPPER(TRIM(AI188))="PIPE")),IF(OR(AG188="",AJ188="",AK188=""),"INFO",IF(AND(AG188&gt;=AJ188,AG188&lt;=AK188),"OK","CHECK")),IF(AG188="","INFO",IF(ABS(AG188)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI188" s="17">
+        <f>IF(A188="","",IF(E188="","",IFERROR(INDEX($B$4:$B$204,MATCH(E188,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ188" s="17">
+        <f>IF(A188="","",IF(OR(AND(UPPER(TRIM(B188))="SWALE",UPPER(TRIM(AI188))="PIPE"),AND(UPPER(TRIM(B188))="TRENCH",UPPER(TRIM(AI188))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK188" s="17">
+        <f>IF(A188="","",IF(OR(AND(UPPER(TRIM(B188))="SWALE",UPPER(TRIM(AI188))="PIPE"),AND(UPPER(TRIM(B188))="TRENCH",UPPER(TRIM(AI188))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL188" s="4">
+        <f>IF(A188="","",IF(E188="","TERMINAL",IF(OR(AND(UPPER(TRIM(B188))="SWALE",UPPER(TRIM(AI188))="PIPE"),AND(UPPER(TRIM(B188))="TRENCH",UPPER(TRIM(AI188))="PIPE")),IF(OR(AG188="",AJ188="",AK188=""),"INFO",IF(AND(AG188&gt;=AJ188,AG188&lt;=AK188),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25738,7 +28833,23 @@
         <v/>
       </c>
       <c r="AH189" s="4">
-        <f>IF(A189="","",IF(E189="","TERMINAL",IF(AG189="","INFO",IF(ABS(AG189)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A189="","",IF(E189="","TERMINAL",IF(OR(AND(UPPER(TRIM(B189))="SWALE",UPPER(TRIM(AI189))="PIPE"),AND(UPPER(TRIM(B189))="TRENCH",UPPER(TRIM(AI189))="PIPE")),IF(OR(AG189="",AJ189="",AK189=""),"INFO",IF(AND(AG189&gt;=AJ189,AG189&lt;=AK189),"OK","CHECK")),IF(AG189="","INFO",IF(ABS(AG189)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI189" s="17">
+        <f>IF(A189="","",IF(E189="","",IFERROR(INDEX($B$4:$B$204,MATCH(E189,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ189" s="17">
+        <f>IF(A189="","",IF(OR(AND(UPPER(TRIM(B189))="SWALE",UPPER(TRIM(AI189))="PIPE"),AND(UPPER(TRIM(B189))="TRENCH",UPPER(TRIM(AI189))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK189" s="17">
+        <f>IF(A189="","",IF(OR(AND(UPPER(TRIM(B189))="SWALE",UPPER(TRIM(AI189))="PIPE"),AND(UPPER(TRIM(B189))="TRENCH",UPPER(TRIM(AI189))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL189" s="4">
+        <f>IF(A189="","",IF(E189="","TERMINAL",IF(OR(AND(UPPER(TRIM(B189))="SWALE",UPPER(TRIM(AI189))="PIPE"),AND(UPPER(TRIM(B189))="TRENCH",UPPER(TRIM(AI189))="PIPE")),IF(OR(AG189="",AJ189="",AK189=""),"INFO",IF(AND(AG189&gt;=AJ189,AG189&lt;=AK189),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25833,7 +28944,23 @@
         <v/>
       </c>
       <c r="AH190" s="4">
-        <f>IF(A190="","",IF(E190="","TERMINAL",IF(AG190="","INFO",IF(ABS(AG190)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A190="","",IF(E190="","TERMINAL",IF(OR(AND(UPPER(TRIM(B190))="SWALE",UPPER(TRIM(AI190))="PIPE"),AND(UPPER(TRIM(B190))="TRENCH",UPPER(TRIM(AI190))="PIPE")),IF(OR(AG190="",AJ190="",AK190=""),"INFO",IF(AND(AG190&gt;=AJ190,AG190&lt;=AK190),"OK","CHECK")),IF(AG190="","INFO",IF(ABS(AG190)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI190" s="17">
+        <f>IF(A190="","",IF(E190="","",IFERROR(INDEX($B$4:$B$204,MATCH(E190,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ190" s="17">
+        <f>IF(A190="","",IF(OR(AND(UPPER(TRIM(B190))="SWALE",UPPER(TRIM(AI190))="PIPE"),AND(UPPER(TRIM(B190))="TRENCH",UPPER(TRIM(AI190))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK190" s="17">
+        <f>IF(A190="","",IF(OR(AND(UPPER(TRIM(B190))="SWALE",UPPER(TRIM(AI190))="PIPE"),AND(UPPER(TRIM(B190))="TRENCH",UPPER(TRIM(AI190))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL190" s="4">
+        <f>IF(A190="","",IF(E190="","TERMINAL",IF(OR(AND(UPPER(TRIM(B190))="SWALE",UPPER(TRIM(AI190))="PIPE"),AND(UPPER(TRIM(B190))="TRENCH",UPPER(TRIM(AI190))="PIPE")),IF(OR(AG190="",AJ190="",AK190=""),"INFO",IF(AND(AG190&gt;=AJ190,AG190&lt;=AK190),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -25928,7 +29055,23 @@
         <v/>
       </c>
       <c r="AH191" s="4">
-        <f>IF(A191="","",IF(E191="","TERMINAL",IF(AG191="","INFO",IF(ABS(AG191)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A191="","",IF(E191="","TERMINAL",IF(OR(AND(UPPER(TRIM(B191))="SWALE",UPPER(TRIM(AI191))="PIPE"),AND(UPPER(TRIM(B191))="TRENCH",UPPER(TRIM(AI191))="PIPE")),IF(OR(AG191="",AJ191="",AK191=""),"INFO",IF(AND(AG191&gt;=AJ191,AG191&lt;=AK191),"OK","CHECK")),IF(AG191="","INFO",IF(ABS(AG191)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI191" s="17">
+        <f>IF(A191="","",IF(E191="","",IFERROR(INDEX($B$4:$B$204,MATCH(E191,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ191" s="17">
+        <f>IF(A191="","",IF(OR(AND(UPPER(TRIM(B191))="SWALE",UPPER(TRIM(AI191))="PIPE"),AND(UPPER(TRIM(B191))="TRENCH",UPPER(TRIM(AI191))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK191" s="17">
+        <f>IF(A191="","",IF(OR(AND(UPPER(TRIM(B191))="SWALE",UPPER(TRIM(AI191))="PIPE"),AND(UPPER(TRIM(B191))="TRENCH",UPPER(TRIM(AI191))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL191" s="4">
+        <f>IF(A191="","",IF(E191="","TERMINAL",IF(OR(AND(UPPER(TRIM(B191))="SWALE",UPPER(TRIM(AI191))="PIPE"),AND(UPPER(TRIM(B191))="TRENCH",UPPER(TRIM(AI191))="PIPE")),IF(OR(AG191="",AJ191="",AK191=""),"INFO",IF(AND(AG191&gt;=AJ191,AG191&lt;=AK191),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26023,7 +29166,23 @@
         <v/>
       </c>
       <c r="AH192" s="4">
-        <f>IF(A192="","",IF(E192="","TERMINAL",IF(AG192="","INFO",IF(ABS(AG192)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A192="","",IF(E192="","TERMINAL",IF(OR(AND(UPPER(TRIM(B192))="SWALE",UPPER(TRIM(AI192))="PIPE"),AND(UPPER(TRIM(B192))="TRENCH",UPPER(TRIM(AI192))="PIPE")),IF(OR(AG192="",AJ192="",AK192=""),"INFO",IF(AND(AG192&gt;=AJ192,AG192&lt;=AK192),"OK","CHECK")),IF(AG192="","INFO",IF(ABS(AG192)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI192" s="17">
+        <f>IF(A192="","",IF(E192="","",IFERROR(INDEX($B$4:$B$204,MATCH(E192,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ192" s="17">
+        <f>IF(A192="","",IF(OR(AND(UPPER(TRIM(B192))="SWALE",UPPER(TRIM(AI192))="PIPE"),AND(UPPER(TRIM(B192))="TRENCH",UPPER(TRIM(AI192))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK192" s="17">
+        <f>IF(A192="","",IF(OR(AND(UPPER(TRIM(B192))="SWALE",UPPER(TRIM(AI192))="PIPE"),AND(UPPER(TRIM(B192))="TRENCH",UPPER(TRIM(AI192))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL192" s="4">
+        <f>IF(A192="","",IF(E192="","TERMINAL",IF(OR(AND(UPPER(TRIM(B192))="SWALE",UPPER(TRIM(AI192))="PIPE"),AND(UPPER(TRIM(B192))="TRENCH",UPPER(TRIM(AI192))="PIPE")),IF(OR(AG192="",AJ192="",AK192=""),"INFO",IF(AND(AG192&gt;=AJ192,AG192&lt;=AK192),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26118,7 +29277,23 @@
         <v/>
       </c>
       <c r="AH193" s="4">
-        <f>IF(A193="","",IF(E193="","TERMINAL",IF(AG193="","INFO",IF(ABS(AG193)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A193="","",IF(E193="","TERMINAL",IF(OR(AND(UPPER(TRIM(B193))="SWALE",UPPER(TRIM(AI193))="PIPE"),AND(UPPER(TRIM(B193))="TRENCH",UPPER(TRIM(AI193))="PIPE")),IF(OR(AG193="",AJ193="",AK193=""),"INFO",IF(AND(AG193&gt;=AJ193,AG193&lt;=AK193),"OK","CHECK")),IF(AG193="","INFO",IF(ABS(AG193)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI193" s="17">
+        <f>IF(A193="","",IF(E193="","",IFERROR(INDEX($B$4:$B$204,MATCH(E193,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ193" s="17">
+        <f>IF(A193="","",IF(OR(AND(UPPER(TRIM(B193))="SWALE",UPPER(TRIM(AI193))="PIPE"),AND(UPPER(TRIM(B193))="TRENCH",UPPER(TRIM(AI193))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK193" s="17">
+        <f>IF(A193="","",IF(OR(AND(UPPER(TRIM(B193))="SWALE",UPPER(TRIM(AI193))="PIPE"),AND(UPPER(TRIM(B193))="TRENCH",UPPER(TRIM(AI193))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL193" s="4">
+        <f>IF(A193="","",IF(E193="","TERMINAL",IF(OR(AND(UPPER(TRIM(B193))="SWALE",UPPER(TRIM(AI193))="PIPE"),AND(UPPER(TRIM(B193))="TRENCH",UPPER(TRIM(AI193))="PIPE")),IF(OR(AG193="",AJ193="",AK193=""),"INFO",IF(AND(AG193&gt;=AJ193,AG193&lt;=AK193),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26213,7 +29388,23 @@
         <v/>
       </c>
       <c r="AH194" s="4">
-        <f>IF(A194="","",IF(E194="","TERMINAL",IF(AG194="","INFO",IF(ABS(AG194)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A194="","",IF(E194="","TERMINAL",IF(OR(AND(UPPER(TRIM(B194))="SWALE",UPPER(TRIM(AI194))="PIPE"),AND(UPPER(TRIM(B194))="TRENCH",UPPER(TRIM(AI194))="PIPE")),IF(OR(AG194="",AJ194="",AK194=""),"INFO",IF(AND(AG194&gt;=AJ194,AG194&lt;=AK194),"OK","CHECK")),IF(AG194="","INFO",IF(ABS(AG194)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI194" s="17">
+        <f>IF(A194="","",IF(E194="","",IFERROR(INDEX($B$4:$B$204,MATCH(E194,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ194" s="17">
+        <f>IF(A194="","",IF(OR(AND(UPPER(TRIM(B194))="SWALE",UPPER(TRIM(AI194))="PIPE"),AND(UPPER(TRIM(B194))="TRENCH",UPPER(TRIM(AI194))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK194" s="17">
+        <f>IF(A194="","",IF(OR(AND(UPPER(TRIM(B194))="SWALE",UPPER(TRIM(AI194))="PIPE"),AND(UPPER(TRIM(B194))="TRENCH",UPPER(TRIM(AI194))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL194" s="4">
+        <f>IF(A194="","",IF(E194="","TERMINAL",IF(OR(AND(UPPER(TRIM(B194))="SWALE",UPPER(TRIM(AI194))="PIPE"),AND(UPPER(TRIM(B194))="TRENCH",UPPER(TRIM(AI194))="PIPE")),IF(OR(AG194="",AJ194="",AK194=""),"INFO",IF(AND(AG194&gt;=AJ194,AG194&lt;=AK194),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26308,7 +29499,23 @@
         <v/>
       </c>
       <c r="AH195" s="4">
-        <f>IF(A195="","",IF(E195="","TERMINAL",IF(AG195="","INFO",IF(ABS(AG195)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A195="","",IF(E195="","TERMINAL",IF(OR(AND(UPPER(TRIM(B195))="SWALE",UPPER(TRIM(AI195))="PIPE"),AND(UPPER(TRIM(B195))="TRENCH",UPPER(TRIM(AI195))="PIPE")),IF(OR(AG195="",AJ195="",AK195=""),"INFO",IF(AND(AG195&gt;=AJ195,AG195&lt;=AK195),"OK","CHECK")),IF(AG195="","INFO",IF(ABS(AG195)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI195" s="17">
+        <f>IF(A195="","",IF(E195="","",IFERROR(INDEX($B$4:$B$204,MATCH(E195,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ195" s="17">
+        <f>IF(A195="","",IF(OR(AND(UPPER(TRIM(B195))="SWALE",UPPER(TRIM(AI195))="PIPE"),AND(UPPER(TRIM(B195))="TRENCH",UPPER(TRIM(AI195))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK195" s="17">
+        <f>IF(A195="","",IF(OR(AND(UPPER(TRIM(B195))="SWALE",UPPER(TRIM(AI195))="PIPE"),AND(UPPER(TRIM(B195))="TRENCH",UPPER(TRIM(AI195))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL195" s="4">
+        <f>IF(A195="","",IF(E195="","TERMINAL",IF(OR(AND(UPPER(TRIM(B195))="SWALE",UPPER(TRIM(AI195))="PIPE"),AND(UPPER(TRIM(B195))="TRENCH",UPPER(TRIM(AI195))="PIPE")),IF(OR(AG195="",AJ195="",AK195=""),"INFO",IF(AND(AG195&gt;=AJ195,AG195&lt;=AK195),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26403,7 +29610,23 @@
         <v/>
       </c>
       <c r="AH196" s="4">
-        <f>IF(A196="","",IF(E196="","TERMINAL",IF(AG196="","INFO",IF(ABS(AG196)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A196="","",IF(E196="","TERMINAL",IF(OR(AND(UPPER(TRIM(B196))="SWALE",UPPER(TRIM(AI196))="PIPE"),AND(UPPER(TRIM(B196))="TRENCH",UPPER(TRIM(AI196))="PIPE")),IF(OR(AG196="",AJ196="",AK196=""),"INFO",IF(AND(AG196&gt;=AJ196,AG196&lt;=AK196),"OK","CHECK")),IF(AG196="","INFO",IF(ABS(AG196)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI196" s="17">
+        <f>IF(A196="","",IF(E196="","",IFERROR(INDEX($B$4:$B$204,MATCH(E196,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ196" s="17">
+        <f>IF(A196="","",IF(OR(AND(UPPER(TRIM(B196))="SWALE",UPPER(TRIM(AI196))="PIPE"),AND(UPPER(TRIM(B196))="TRENCH",UPPER(TRIM(AI196))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK196" s="17">
+        <f>IF(A196="","",IF(OR(AND(UPPER(TRIM(B196))="SWALE",UPPER(TRIM(AI196))="PIPE"),AND(UPPER(TRIM(B196))="TRENCH",UPPER(TRIM(AI196))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL196" s="4">
+        <f>IF(A196="","",IF(E196="","TERMINAL",IF(OR(AND(UPPER(TRIM(B196))="SWALE",UPPER(TRIM(AI196))="PIPE"),AND(UPPER(TRIM(B196))="TRENCH",UPPER(TRIM(AI196))="PIPE")),IF(OR(AG196="",AJ196="",AK196=""),"INFO",IF(AND(AG196&gt;=AJ196,AG196&lt;=AK196),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26498,7 +29721,23 @@
         <v/>
       </c>
       <c r="AH197" s="4">
-        <f>IF(A197="","",IF(E197="","TERMINAL",IF(AG197="","INFO",IF(ABS(AG197)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A197="","",IF(E197="","TERMINAL",IF(OR(AND(UPPER(TRIM(B197))="SWALE",UPPER(TRIM(AI197))="PIPE"),AND(UPPER(TRIM(B197))="TRENCH",UPPER(TRIM(AI197))="PIPE")),IF(OR(AG197="",AJ197="",AK197=""),"INFO",IF(AND(AG197&gt;=AJ197,AG197&lt;=AK197),"OK","CHECK")),IF(AG197="","INFO",IF(ABS(AG197)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI197" s="17">
+        <f>IF(A197="","",IF(E197="","",IFERROR(INDEX($B$4:$B$204,MATCH(E197,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ197" s="17">
+        <f>IF(A197="","",IF(OR(AND(UPPER(TRIM(B197))="SWALE",UPPER(TRIM(AI197))="PIPE"),AND(UPPER(TRIM(B197))="TRENCH",UPPER(TRIM(AI197))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK197" s="17">
+        <f>IF(A197="","",IF(OR(AND(UPPER(TRIM(B197))="SWALE",UPPER(TRIM(AI197))="PIPE"),AND(UPPER(TRIM(B197))="TRENCH",UPPER(TRIM(AI197))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL197" s="4">
+        <f>IF(A197="","",IF(E197="","TERMINAL",IF(OR(AND(UPPER(TRIM(B197))="SWALE",UPPER(TRIM(AI197))="PIPE"),AND(UPPER(TRIM(B197))="TRENCH",UPPER(TRIM(AI197))="PIPE")),IF(OR(AG197="",AJ197="",AK197=""),"INFO",IF(AND(AG197&gt;=AJ197,AG197&lt;=AK197),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26593,7 +29832,23 @@
         <v/>
       </c>
       <c r="AH198" s="4">
-        <f>IF(A198="","",IF(E198="","TERMINAL",IF(AG198="","INFO",IF(ABS(AG198)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A198="","",IF(E198="","TERMINAL",IF(OR(AND(UPPER(TRIM(B198))="SWALE",UPPER(TRIM(AI198))="PIPE"),AND(UPPER(TRIM(B198))="TRENCH",UPPER(TRIM(AI198))="PIPE")),IF(OR(AG198="",AJ198="",AK198=""),"INFO",IF(AND(AG198&gt;=AJ198,AG198&lt;=AK198),"OK","CHECK")),IF(AG198="","INFO",IF(ABS(AG198)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI198" s="17">
+        <f>IF(A198="","",IF(E198="","",IFERROR(INDEX($B$4:$B$204,MATCH(E198,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ198" s="17">
+        <f>IF(A198="","",IF(OR(AND(UPPER(TRIM(B198))="SWALE",UPPER(TRIM(AI198))="PIPE"),AND(UPPER(TRIM(B198))="TRENCH",UPPER(TRIM(AI198))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK198" s="17">
+        <f>IF(A198="","",IF(OR(AND(UPPER(TRIM(B198))="SWALE",UPPER(TRIM(AI198))="PIPE"),AND(UPPER(TRIM(B198))="TRENCH",UPPER(TRIM(AI198))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL198" s="4">
+        <f>IF(A198="","",IF(E198="","TERMINAL",IF(OR(AND(UPPER(TRIM(B198))="SWALE",UPPER(TRIM(AI198))="PIPE"),AND(UPPER(TRIM(B198))="TRENCH",UPPER(TRIM(AI198))="PIPE")),IF(OR(AG198="",AJ198="",AK198=""),"INFO",IF(AND(AG198&gt;=AJ198,AG198&lt;=AK198),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26688,7 +29943,23 @@
         <v/>
       </c>
       <c r="AH199" s="4">
-        <f>IF(A199="","",IF(E199="","TERMINAL",IF(AG199="","INFO",IF(ABS(AG199)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A199="","",IF(E199="","TERMINAL",IF(OR(AND(UPPER(TRIM(B199))="SWALE",UPPER(TRIM(AI199))="PIPE"),AND(UPPER(TRIM(B199))="TRENCH",UPPER(TRIM(AI199))="PIPE")),IF(OR(AG199="",AJ199="",AK199=""),"INFO",IF(AND(AG199&gt;=AJ199,AG199&lt;=AK199),"OK","CHECK")),IF(AG199="","INFO",IF(ABS(AG199)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI199" s="17">
+        <f>IF(A199="","",IF(E199="","",IFERROR(INDEX($B$4:$B$204,MATCH(E199,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ199" s="17">
+        <f>IF(A199="","",IF(OR(AND(UPPER(TRIM(B199))="SWALE",UPPER(TRIM(AI199))="PIPE"),AND(UPPER(TRIM(B199))="TRENCH",UPPER(TRIM(AI199))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK199" s="17">
+        <f>IF(A199="","",IF(OR(AND(UPPER(TRIM(B199))="SWALE",UPPER(TRIM(AI199))="PIPE"),AND(UPPER(TRIM(B199))="TRENCH",UPPER(TRIM(AI199))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL199" s="4">
+        <f>IF(A199="","",IF(E199="","TERMINAL",IF(OR(AND(UPPER(TRIM(B199))="SWALE",UPPER(TRIM(AI199))="PIPE"),AND(UPPER(TRIM(B199))="TRENCH",UPPER(TRIM(AI199))="PIPE")),IF(OR(AG199="",AJ199="",AK199=""),"INFO",IF(AND(AG199&gt;=AJ199,AG199&lt;=AK199),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26783,7 +30054,23 @@
         <v/>
       </c>
       <c r="AH200" s="4">
-        <f>IF(A200="","",IF(E200="","TERMINAL",IF(AG200="","INFO",IF(ABS(AG200)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A200="","",IF(E200="","TERMINAL",IF(OR(AND(UPPER(TRIM(B200))="SWALE",UPPER(TRIM(AI200))="PIPE"),AND(UPPER(TRIM(B200))="TRENCH",UPPER(TRIM(AI200))="PIPE")),IF(OR(AG200="",AJ200="",AK200=""),"INFO",IF(AND(AG200&gt;=AJ200,AG200&lt;=AK200),"OK","CHECK")),IF(AG200="","INFO",IF(ABS(AG200)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI200" s="17">
+        <f>IF(A200="","",IF(E200="","",IFERROR(INDEX($B$4:$B$204,MATCH(E200,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ200" s="17">
+        <f>IF(A200="","",IF(OR(AND(UPPER(TRIM(B200))="SWALE",UPPER(TRIM(AI200))="PIPE"),AND(UPPER(TRIM(B200))="TRENCH",UPPER(TRIM(AI200))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK200" s="17">
+        <f>IF(A200="","",IF(OR(AND(UPPER(TRIM(B200))="SWALE",UPPER(TRIM(AI200))="PIPE"),AND(UPPER(TRIM(B200))="TRENCH",UPPER(TRIM(AI200))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL200" s="4">
+        <f>IF(A200="","",IF(E200="","TERMINAL",IF(OR(AND(UPPER(TRIM(B200))="SWALE",UPPER(TRIM(AI200))="PIPE"),AND(UPPER(TRIM(B200))="TRENCH",UPPER(TRIM(AI200))="PIPE")),IF(OR(AG200="",AJ200="",AK200=""),"INFO",IF(AND(AG200&gt;=AJ200,AG200&lt;=AK200),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26878,7 +30165,23 @@
         <v/>
       </c>
       <c r="AH201" s="4">
-        <f>IF(A201="","",IF(E201="","TERMINAL",IF(AG201="","INFO",IF(ABS(AG201)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A201="","",IF(E201="","TERMINAL",IF(OR(AND(UPPER(TRIM(B201))="SWALE",UPPER(TRIM(AI201))="PIPE"),AND(UPPER(TRIM(B201))="TRENCH",UPPER(TRIM(AI201))="PIPE")),IF(OR(AG201="",AJ201="",AK201=""),"INFO",IF(AND(AG201&gt;=AJ201,AG201&lt;=AK201),"OK","CHECK")),IF(AG201="","INFO",IF(ABS(AG201)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI201" s="17">
+        <f>IF(A201="","",IF(E201="","",IFERROR(INDEX($B$4:$B$204,MATCH(E201,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ201" s="17">
+        <f>IF(A201="","",IF(OR(AND(UPPER(TRIM(B201))="SWALE",UPPER(TRIM(AI201))="PIPE"),AND(UPPER(TRIM(B201))="TRENCH",UPPER(TRIM(AI201))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK201" s="17">
+        <f>IF(A201="","",IF(OR(AND(UPPER(TRIM(B201))="SWALE",UPPER(TRIM(AI201))="PIPE"),AND(UPPER(TRIM(B201))="TRENCH",UPPER(TRIM(AI201))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL201" s="4">
+        <f>IF(A201="","",IF(E201="","TERMINAL",IF(OR(AND(UPPER(TRIM(B201))="SWALE",UPPER(TRIM(AI201))="PIPE"),AND(UPPER(TRIM(B201))="TRENCH",UPPER(TRIM(AI201))="PIPE")),IF(OR(AG201="",AJ201="",AK201=""),"INFO",IF(AND(AG201&gt;=AJ201,AG201&lt;=AK201),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -26973,7 +30276,23 @@
         <v/>
       </c>
       <c r="AH202" s="4">
-        <f>IF(A202="","",IF(E202="","TERMINAL",IF(AG202="","INFO",IF(ABS(AG202)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A202="","",IF(E202="","TERMINAL",IF(OR(AND(UPPER(TRIM(B202))="SWALE",UPPER(TRIM(AI202))="PIPE"),AND(UPPER(TRIM(B202))="TRENCH",UPPER(TRIM(AI202))="PIPE")),IF(OR(AG202="",AJ202="",AK202=""),"INFO",IF(AND(AG202&gt;=AJ202,AG202&lt;=AK202),"OK","CHECK")),IF(AG202="","INFO",IF(ABS(AG202)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI202" s="17">
+        <f>IF(A202="","",IF(E202="","",IFERROR(INDEX($B$4:$B$204,MATCH(E202,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ202" s="17">
+        <f>IF(A202="","",IF(OR(AND(UPPER(TRIM(B202))="SWALE",UPPER(TRIM(AI202))="PIPE"),AND(UPPER(TRIM(B202))="TRENCH",UPPER(TRIM(AI202))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK202" s="17">
+        <f>IF(A202="","",IF(OR(AND(UPPER(TRIM(B202))="SWALE",UPPER(TRIM(AI202))="PIPE"),AND(UPPER(TRIM(B202))="TRENCH",UPPER(TRIM(AI202))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL202" s="4">
+        <f>IF(A202="","",IF(E202="","TERMINAL",IF(OR(AND(UPPER(TRIM(B202))="SWALE",UPPER(TRIM(AI202))="PIPE"),AND(UPPER(TRIM(B202))="TRENCH",UPPER(TRIM(AI202))="PIPE")),IF(OR(AG202="",AJ202="",AK202=""),"INFO",IF(AND(AG202&gt;=AJ202,AG202&lt;=AK202),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -27068,7 +30387,23 @@
         <v/>
       </c>
       <c r="AH203" s="4">
-        <f>IF(A203="","",IF(E203="","TERMINAL",IF(AG203="","INFO",IF(ABS(AG203)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A203="","",IF(E203="","TERMINAL",IF(OR(AND(UPPER(TRIM(B203))="SWALE",UPPER(TRIM(AI203))="PIPE"),AND(UPPER(TRIM(B203))="TRENCH",UPPER(TRIM(AI203))="PIPE")),IF(OR(AG203="",AJ203="",AK203=""),"INFO",IF(AND(AG203&gt;=AJ203,AG203&lt;=AK203),"OK","CHECK")),IF(AG203="","INFO",IF(ABS(AG203)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI203" s="17">
+        <f>IF(A203="","",IF(E203="","",IFERROR(INDEX($B$4:$B$204,MATCH(E203,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ203" s="17">
+        <f>IF(A203="","",IF(OR(AND(UPPER(TRIM(B203))="SWALE",UPPER(TRIM(AI203))="PIPE"),AND(UPPER(TRIM(B203))="TRENCH",UPPER(TRIM(AI203))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK203" s="17">
+        <f>IF(A203="","",IF(OR(AND(UPPER(TRIM(B203))="SWALE",UPPER(TRIM(AI203))="PIPE"),AND(UPPER(TRIM(B203))="TRENCH",UPPER(TRIM(AI203))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL203" s="4">
+        <f>IF(A203="","",IF(E203="","TERMINAL",IF(OR(AND(UPPER(TRIM(B203))="SWALE",UPPER(TRIM(AI203))="PIPE"),AND(UPPER(TRIM(B203))="TRENCH",UPPER(TRIM(AI203))="PIPE")),IF(OR(AG203="",AJ203="",AK203=""),"INFO",IF(AND(AG203&gt;=AJ203,AG203&lt;=AK203),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -27163,7 +30498,23 @@
         <v/>
       </c>
       <c r="AH204" s="4">
-        <f>IF(A204="","",IF(E204="","TERMINAL",IF(AG204="","INFO",IF(ABS(AG204)&lt;=0.01,"OK","CHECK"))))</f>
+        <f>IF(A204="","",IF(E204="","TERMINAL",IF(OR(AND(UPPER(TRIM(B204))="SWALE",UPPER(TRIM(AI204))="PIPE"),AND(UPPER(TRIM(B204))="TRENCH",UPPER(TRIM(AI204))="PIPE")),IF(OR(AG204="",AJ204="",AK204=""),"INFO",IF(AND(AG204&gt;=AJ204,AG204&lt;=AK204),"OK","CHECK")),IF(AG204="","INFO",IF(ABS(AG204)&lt;=Inputs!$B$54,"OK","CHECK")))))</f>
+        <v/>
+      </c>
+      <c r="AI204" s="17">
+        <f>IF(A204="","",IF(E204="","",IFERROR(INDEX($B$4:$B$204,MATCH(E204,$A$4:$A$204,0)),"")))</f>
+        <v/>
+      </c>
+      <c r="AJ204" s="17">
+        <f>IF(A204="","",IF(OR(AND(UPPER(TRIM(B204))="SWALE",UPPER(TRIM(AI204))="PIPE"),AND(UPPER(TRIM(B204))="TRENCH",UPPER(TRIM(AI204))="PIPE")),Inputs!$B$55,0))</f>
+        <v/>
+      </c>
+      <c r="AK204" s="17">
+        <f>IF(A204="","",IF(OR(AND(UPPER(TRIM(B204))="SWALE",UPPER(TRIM(AI204))="PIPE"),AND(UPPER(TRIM(B204))="TRENCH",UPPER(TRIM(AI204))="PIPE")),Inputs!$B$56,Inputs!$B$54))</f>
+        <v/>
+      </c>
+      <c r="AL204" s="4">
+        <f>IF(A204="","",IF(E204="","TERMINAL",IF(OR(AND(UPPER(TRIM(B204))="SWALE",UPPER(TRIM(AI204))="PIPE"),AND(UPPER(TRIM(B204))="TRENCH",UPPER(TRIM(AI204))="PIPE")),IF(OR(AG204="",AJ204="",AK204=""),"INFO",IF(AND(AG204&gt;=AJ204,AG204&lt;=AK204),"OK","CHECK")),"N/A")))</f>
         <v/>
       </c>
     </row>
@@ -27191,6 +30542,11 @@
   <conditionalFormatting sqref="AH4:AH204">
     <cfRule type="expression" priority="10" dxfId="3">
       <formula>=$AH4="CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL4:AL204">
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>=$AL4="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -801,6 +801,34 @@
       <c r="A40" t="inlineStr">
         <is>
           <t>Si AL=CHECK: ajuster invert aval/amont (AC override ou pente/longueur) ou ajouter ouvrage de chute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Types de surface mis a jour: PAVAGE ajoute explicitement (Inputs!B58) et applique a Z07/Z08/Z10/Z12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Z13 supprime de la configuration active (ligne vide).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Raccord SWALE/TRENCH -&gt; PIPE: AD applique automatiquement une chute cible Inputs!B57 (si pas d'override AC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cela represente un raccord via regard/caniveau: fond noue plus haut que l'invert de conduite aval.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1656,7 +1684,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4156.21</v>
+        <v>7423.67</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -1676,7 +1704,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15.1</v>
+        <v>33.5</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -1696,7 +1724,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.026</v>
+        <v>1.148</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1876,7 +1904,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -2755,6 +2783,26 @@
       <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Valeur cible pratique pour entree swale/trench vers conduite bassin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>C_pavage</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Coefficient ruissellement pour surfaces pavees (pave-uni/pavage).</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2928,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="8">
-        <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G4" s="7" t="n">
@@ -2926,7 +2974,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="8">
-        <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G5" s="7" t="n">
@@ -2972,7 +3020,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="8">
-        <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G6" s="7" t="n">
@@ -3018,7 +3066,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="8">
-        <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G7" s="7" t="n">
@@ -3056,7 +3104,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>PAVAGE</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
@@ -3064,7 +3112,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="8">
-        <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G8" s="7" t="n">
@@ -3085,7 +3133,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Image: petit troncon pave entre zones gazon.</t>
+          <t>Surface pavage (pas tresfond).</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3158,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="8">
-        <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G9" s="7" t="n">
@@ -3148,7 +3196,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>PAVAGE</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
@@ -3156,7 +3204,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="8">
-        <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G10" s="7" t="n">
@@ -3177,7 +3225,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>LOCALISATION: zone pavee entre Z05 et Z06 (pas l'entree pavee externe).</t>
+          <t>Surface pavage principal (pave-uni), entre Z05 et Z06.</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3250,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="8">
-        <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G11" s="7" t="n">
@@ -3248,7 +3296,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="8">
-        <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G12" s="7" t="n">
@@ -3277,12 +3325,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Sud gris local</t>
+          <t>Sud gris local (pavage)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>PAVAGE</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -3290,7 +3338,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="8">
-        <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G13" s="7" t="n">
@@ -3311,7 +3359,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Routage vers entree EST (courbe cote est sur plan).</t>
+          <t>Surface pavage locale (pas tresfond), routage vers entree EST.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3384,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="8">
-        <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G14" s="7" t="n">
@@ -3369,12 +3417,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Sud est gris petit</t>
+          <t>Sud est gris petit (pavage)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>TRESFOND</t>
+          <t>PAVAGE</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -3382,7 +3430,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="8">
-        <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G15" s="7" t="n">
@@ -3403,38 +3451,21 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Vers noue sud</t>
+          <t>Surface pavage petite zone sud-est (pas tresfond).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Z13</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Tresfond haut central (bande nord centrale)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>TRESFOND</t>
-        </is>
-      </c>
-      <c r="D16" s="7">
-        <f>Inputs!$B$51</f>
-        <v/>
-      </c>
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8">
-        <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
-        <v/>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>8</v>
-      </c>
+        <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
+        <v/>
+      </c>
+      <c r="G16" s="7" t="n"/>
       <c r="H16" s="8">
         <f>IF(A16="","",Inputs!$B$3/((IF(G16="",Inputs!$B$14,G16)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3443,16 +3474,8 @@
         <f>IF(A16="","",2.78E-7*F16*D16*H16)</f>
         <v/>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Ajoute pour inclure le tresfond central haut; saisir aire exacte Inputs!B51.</t>
-        </is>
-      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -3461,7 +3484,7 @@
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8">
-        <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G17" s="7" t="n"/>
@@ -3483,7 +3506,7 @@
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8">
-        <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G18" s="7" t="n"/>
@@ -3505,7 +3528,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8">
-        <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G19" s="7" t="n"/>
@@ -3527,7 +3550,7 @@
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8">
-        <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G20" s="7" t="n"/>
@@ -3549,7 +3572,7 @@
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8">
-        <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G21" s="7" t="n"/>
@@ -3571,7 +3594,7 @@
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="8">
-        <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -3593,7 +3616,7 @@
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8">
-        <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -3615,7 +3638,7 @@
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="8">
-        <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G24" s="7" t="n"/>
@@ -3637,7 +3660,7 @@
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8">
-        <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -3659,7 +3682,7 @@
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="8">
-        <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -3681,7 +3704,7 @@
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8">
-        <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G27" s="7" t="n"/>
@@ -3703,7 +3726,7 @@
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="8">
-        <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G28" s="7" t="n"/>
@@ -3725,7 +3748,7 @@
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8">
-        <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G29" s="7" t="n"/>
@@ -3747,7 +3770,7 @@
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="8">
-        <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G30" s="7" t="n"/>
@@ -3769,7 +3792,7 @@
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8">
-        <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G31" s="7" t="n"/>
@@ -3791,7 +3814,7 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="8">
-        <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G32" s="7" t="n"/>
@@ -3813,7 +3836,7 @@
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="8">
-        <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G33" s="7" t="n"/>
@@ -3835,7 +3858,7 @@
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="8">
-        <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G34" s="7" t="n"/>
@@ -3857,7 +3880,7 @@
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="8">
-        <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G35" s="7" t="n"/>
@@ -3879,7 +3902,7 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="8">
-        <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G36" s="7" t="n"/>
@@ -3901,7 +3924,7 @@
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="8">
-        <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -3923,7 +3946,7 @@
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="8">
-        <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G38" s="7" t="n"/>
@@ -3945,7 +3968,7 @@
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="8">
-        <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G39" s="7" t="n"/>
@@ -3967,7 +3990,7 @@
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="8">
-        <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G40" s="7" t="n"/>
@@ -3989,7 +4012,7 @@
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="8">
-        <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G41" s="7" t="n"/>
@@ -4011,7 +4034,7 @@
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="8">
-        <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G42" s="7" t="n"/>
@@ -4033,7 +4056,7 @@
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="8">
-        <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G43" s="7" t="n"/>
@@ -4055,7 +4078,7 @@
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="8">
-        <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G44" s="7" t="n"/>
@@ -4077,7 +4100,7 @@
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
       <c r="F45" s="8">
-        <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G45" s="7" t="n"/>
@@ -4099,7 +4122,7 @@
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="8">
-        <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G46" s="7" t="n"/>
@@ -4121,7 +4144,7 @@
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="8">
-        <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G47" s="7" t="n"/>
@@ -4143,7 +4166,7 @@
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="8">
-        <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G48" s="7" t="n"/>
@@ -4165,7 +4188,7 @@
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="8">
-        <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G49" s="7" t="n"/>
@@ -4187,7 +4210,7 @@
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="8">
-        <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G50" s="7" t="n"/>
@@ -4209,7 +4232,7 @@
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="8">
-        <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G51" s="7" t="n"/>
@@ -4231,7 +4254,7 @@
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="8">
-        <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -4253,7 +4276,7 @@
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
       <c r="F53" s="8">
-        <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G53" s="7" t="n"/>
@@ -4275,7 +4298,7 @@
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="8">
-        <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G54" s="7" t="n"/>
@@ -4297,7 +4320,7 @@
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="8">
-        <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G55" s="7" t="n"/>
@@ -4319,7 +4342,7 @@
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="8">
-        <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -4341,7 +4364,7 @@
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
       <c r="F57" s="8">
-        <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G57" s="7" t="n"/>
@@ -4363,7 +4386,7 @@
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="8">
-        <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G58" s="7" t="n"/>
@@ -4385,7 +4408,7 @@
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="8">
-        <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G59" s="7" t="n"/>
@@ -4407,7 +4430,7 @@
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="8">
-        <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G60" s="7" t="n"/>
@@ -4429,7 +4452,7 @@
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="8">
-        <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G61" s="7" t="n"/>
@@ -4451,7 +4474,7 @@
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="8">
-        <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G62" s="7" t="n"/>
@@ -4473,7 +4496,7 @@
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
       <c r="F63" s="8">
-        <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G63" s="7" t="n"/>
@@ -4495,7 +4518,7 @@
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="8">
-        <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G64" s="7" t="n"/>
@@ -4517,7 +4540,7 @@
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="8">
-        <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -4539,7 +4562,7 @@
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="8">
-        <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G66" s="7" t="n"/>
@@ -4561,7 +4584,7 @@
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
       <c r="F67" s="8">
-        <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G67" s="7" t="n"/>
@@ -4583,7 +4606,7 @@
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="8">
-        <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G68" s="7" t="n"/>
@@ -4605,7 +4628,7 @@
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="8">
-        <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G69" s="7" t="n"/>
@@ -4627,7 +4650,7 @@
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="8">
-        <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G70" s="7" t="n"/>
@@ -4649,7 +4672,7 @@
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="8">
-        <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G71" s="7" t="n"/>
@@ -4671,7 +4694,7 @@
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="8">
-        <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G72" s="7" t="n"/>
@@ -4693,7 +4716,7 @@
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
       <c r="F73" s="8">
-        <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G73" s="7" t="n"/>
@@ -4715,7 +4738,7 @@
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="8">
-        <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G74" s="7" t="n"/>
@@ -4737,7 +4760,7 @@
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="8">
-        <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -4759,7 +4782,7 @@
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="8">
-        <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G76" s="7" t="n"/>
@@ -4781,7 +4804,7 @@
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="8">
-        <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G77" s="7" t="n"/>
@@ -4803,7 +4826,7 @@
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="8">
-        <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G78" s="7" t="n"/>
@@ -4825,7 +4848,7 @@
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="8">
-        <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G79" s="7" t="n"/>
@@ -4847,7 +4870,7 @@
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="8">
-        <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G80" s="7" t="n"/>
@@ -4869,7 +4892,7 @@
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="8">
-        <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G81" s="7" t="n"/>
@@ -4891,7 +4914,7 @@
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="8">
-        <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G82" s="7" t="n"/>
@@ -4913,7 +4936,7 @@
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="8">
-        <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G83" s="7" t="n"/>
@@ -4935,7 +4958,7 @@
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="8">
-        <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G84" s="7" t="n"/>
@@ -4957,7 +4980,7 @@
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="8">
-        <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G85" s="7" t="n"/>
@@ -4979,7 +5002,7 @@
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="8">
-        <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G86" s="7" t="n"/>
@@ -5001,7 +5024,7 @@
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="8">
-        <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G87" s="7" t="n"/>
@@ -5023,7 +5046,7 @@
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="8">
-        <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G88" s="7" t="n"/>
@@ -5045,7 +5068,7 @@
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="8">
-        <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G89" s="7" t="n"/>
@@ -5067,7 +5090,7 @@
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="8">
-        <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G90" s="7" t="n"/>
@@ -5089,7 +5112,7 @@
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="8">
-        <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G91" s="7" t="n"/>
@@ -5111,7 +5134,7 @@
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="8">
-        <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G92" s="7" t="n"/>
@@ -5133,7 +5156,7 @@
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="8">
-        <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G93" s="7" t="n"/>
@@ -5155,7 +5178,7 @@
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="8">
-        <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G94" s="7" t="n"/>
@@ -5177,7 +5200,7 @@
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="8">
-        <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G95" s="7" t="n"/>
@@ -5199,7 +5222,7 @@
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="8">
-        <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G96" s="7" t="n"/>
@@ -5221,7 +5244,7 @@
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="8">
-        <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G97" s="7" t="n"/>
@@ -5243,7 +5266,7 @@
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="8">
-        <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -5265,7 +5288,7 @@
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="8">
-        <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G99" s="7" t="n"/>
@@ -5287,7 +5310,7 @@
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="8">
-        <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G100" s="7" t="n"/>
@@ -5309,7 +5332,7 @@
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="8">
-        <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G101" s="7" t="n"/>
@@ -5331,7 +5354,7 @@
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="8">
-        <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G102" s="7" t="n"/>
@@ -5353,7 +5376,7 @@
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="8">
-        <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G103" s="7" t="n"/>
@@ -5375,7 +5398,7 @@
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="8">
-        <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -5397,7 +5420,7 @@
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="8">
-        <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -5419,7 +5442,7 @@
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="8">
-        <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G106" s="7" t="n"/>
@@ -5441,7 +5464,7 @@
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="8">
-        <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G107" s="7" t="n"/>
@@ -5463,7 +5486,7 @@
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="8">
-        <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G108" s="7" t="n"/>
@@ -5485,7 +5508,7 @@
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
       <c r="F109" s="8">
-        <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -5507,7 +5530,7 @@
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="8">
-        <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G110" s="7" t="n"/>
@@ -5529,7 +5552,7 @@
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
       <c r="F111" s="8">
-        <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -5551,7 +5574,7 @@
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="8">
-        <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -5573,7 +5596,7 @@
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
       <c r="F113" s="8">
-        <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -5595,7 +5618,7 @@
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
       <c r="F114" s="8">
-        <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -5617,7 +5640,7 @@
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
       <c r="F115" s="8">
-        <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -5639,7 +5662,7 @@
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
       <c r="F116" s="8">
-        <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -5661,7 +5684,7 @@
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
       <c r="F117" s="8">
-        <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -5683,7 +5706,7 @@
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
       <c r="F118" s="8">
-        <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5705,7 +5728,7 @@
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
       <c r="F119" s="8">
-        <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G119" s="7" t="n"/>
@@ -5727,7 +5750,7 @@
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="8">
-        <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -5749,7 +5772,7 @@
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
       <c r="F121" s="8">
-        <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G121" s="7" t="n"/>
@@ -5771,7 +5794,7 @@
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="8">
-        <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -5793,7 +5816,7 @@
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
       <c r="F123" s="8">
-        <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G123" s="7" t="n"/>
@@ -5815,7 +5838,7 @@
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="8">
-        <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G124" s="7" t="n"/>
@@ -5837,7 +5860,7 @@
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
       <c r="F125" s="8">
-        <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G125" s="7" t="n"/>
@@ -5859,7 +5882,7 @@
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
       <c r="F126" s="8">
-        <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G126" s="7" t="n"/>
@@ -5881,7 +5904,7 @@
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
       <c r="F127" s="8">
-        <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G127" s="7" t="n"/>
@@ -5903,7 +5926,7 @@
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="8">
-        <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G128" s="7" t="n"/>
@@ -5925,7 +5948,7 @@
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
       <c r="F129" s="8">
-        <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G129" s="7" t="n"/>
@@ -5947,7 +5970,7 @@
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="8">
-        <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G130" s="7" t="n"/>
@@ -5969,7 +5992,7 @@
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
       <c r="F131" s="8">
-        <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G131" s="7" t="n"/>
@@ -5991,7 +6014,7 @@
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="8">
-        <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G132" s="7" t="n"/>
@@ -6013,7 +6036,7 @@
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
       <c r="F133" s="8">
-        <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G133" s="7" t="n"/>
@@ -6035,7 +6058,7 @@
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="8">
-        <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G134" s="7" t="n"/>
@@ -6057,7 +6080,7 @@
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
       <c r="F135" s="8">
-        <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G135" s="7" t="n"/>
@@ -6079,7 +6102,7 @@
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="8">
-        <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G136" s="7" t="n"/>
@@ -6101,7 +6124,7 @@
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
       <c r="F137" s="8">
-        <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G137" s="7" t="n"/>
@@ -6123,7 +6146,7 @@
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="8">
-        <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G138" s="7" t="n"/>
@@ -6145,7 +6168,7 @@
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
       <c r="F139" s="8">
-        <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G139" s="7" t="n"/>
@@ -6167,7 +6190,7 @@
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="8">
-        <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G140" s="7" t="n"/>
@@ -6189,7 +6212,7 @@
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
       <c r="F141" s="8">
-        <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G141" s="7" t="n"/>
@@ -6211,7 +6234,7 @@
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="8">
-        <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G142" s="7" t="n"/>
@@ -6233,7 +6256,7 @@
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
       <c r="F143" s="8">
-        <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G143" s="7" t="n"/>
@@ -6255,7 +6278,7 @@
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="8">
-        <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G144" s="7" t="n"/>
@@ -6277,7 +6300,7 @@
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
       <c r="F145" s="8">
-        <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G145" s="7" t="n"/>
@@ -6299,7 +6322,7 @@
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
       <c r="F146" s="8">
-        <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G146" s="7" t="n"/>
@@ -6321,7 +6344,7 @@
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
       <c r="F147" s="8">
-        <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G147" s="7" t="n"/>
@@ -6343,7 +6366,7 @@
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
       <c r="F148" s="8">
-        <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G148" s="7" t="n"/>
@@ -6365,7 +6388,7 @@
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
       <c r="F149" s="8">
-        <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G149" s="7" t="n"/>
@@ -6387,7 +6410,7 @@
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="8">
-        <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G150" s="7" t="n"/>
@@ -6409,7 +6432,7 @@
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
       <c r="F151" s="8">
-        <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G151" s="7" t="n"/>
@@ -6431,7 +6454,7 @@
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="8">
-        <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G152" s="7" t="n"/>
@@ -6453,7 +6476,7 @@
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
       <c r="F153" s="8">
-        <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G153" s="7" t="n"/>
@@ -6475,7 +6498,7 @@
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
       <c r="F154" s="8">
-        <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G154" s="7" t="n"/>
@@ -6497,7 +6520,7 @@
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
       <c r="F155" s="8">
-        <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G155" s="7" t="n"/>
@@ -6519,7 +6542,7 @@
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="8">
-        <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G156" s="7" t="n"/>
@@ -6541,7 +6564,7 @@
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
       <c r="F157" s="8">
-        <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G157" s="7" t="n"/>
@@ -6563,7 +6586,7 @@
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
       <c r="F158" s="8">
-        <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G158" s="7" t="n"/>
@@ -6585,7 +6608,7 @@
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
       <c r="F159" s="8">
-        <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G159" s="7" t="n"/>
@@ -6607,7 +6630,7 @@
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
       <c r="F160" s="8">
-        <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G160" s="7" t="n"/>
@@ -6629,7 +6652,7 @@
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
       <c r="F161" s="8">
-        <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G161" s="7" t="n"/>
@@ -6651,7 +6674,7 @@
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="8">
-        <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G162" s="7" t="n"/>
@@ -6673,7 +6696,7 @@
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
       <c r="F163" s="8">
-        <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G163" s="7" t="n"/>
@@ -6695,7 +6718,7 @@
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
       <c r="F164" s="8">
-        <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G164" s="7" t="n"/>
@@ -6717,7 +6740,7 @@
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
       <c r="F165" s="8">
-        <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G165" s="7" t="n"/>
@@ -6739,7 +6762,7 @@
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="8">
-        <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G166" s="7" t="n"/>
@@ -6761,7 +6784,7 @@
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
       <c r="F167" s="8">
-        <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G167" s="7" t="n"/>
@@ -6783,7 +6806,7 @@
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
       <c r="F168" s="8">
-        <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G168" s="7" t="n"/>
@@ -6805,7 +6828,7 @@
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
       <c r="F169" s="8">
-        <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G169" s="7" t="n"/>
@@ -6827,7 +6850,7 @@
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="8">
-        <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G170" s="7" t="n"/>
@@ -6849,7 +6872,7 @@
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
       <c r="F171" s="8">
-        <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G171" s="7" t="n"/>
@@ -6871,7 +6894,7 @@
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="8">
-        <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G172" s="7" t="n"/>
@@ -6893,7 +6916,7 @@
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
       <c r="F173" s="8">
-        <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G173" s="7" t="n"/>
@@ -6915,7 +6938,7 @@
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
       <c r="F174" s="8">
-        <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G174" s="7" t="n"/>
@@ -6937,7 +6960,7 @@
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
       <c r="F175" s="8">
-        <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G175" s="7" t="n"/>
@@ -6959,7 +6982,7 @@
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="8">
-        <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G176" s="7" t="n"/>
@@ -6981,7 +7004,7 @@
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
       <c r="F177" s="8">
-        <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G177" s="7" t="n"/>
@@ -7003,7 +7026,7 @@
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="8">
-        <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G178" s="7" t="n"/>
@@ -7025,7 +7048,7 @@
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
       <c r="F179" s="8">
-        <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G179" s="7" t="n"/>
@@ -7047,7 +7070,7 @@
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="8">
-        <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G180" s="7" t="n"/>
@@ -7069,7 +7092,7 @@
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
       <c r="F181" s="8">
-        <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G181" s="7" t="n"/>
@@ -7091,7 +7114,7 @@
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="8">
-        <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G182" s="7" t="n"/>
@@ -7113,7 +7136,7 @@
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
       <c r="F183" s="8">
-        <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G183" s="7" t="n"/>
@@ -7135,7 +7158,7 @@
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="8">
-        <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G184" s="7" t="n"/>
@@ -7157,7 +7180,7 @@
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
       <c r="F185" s="8">
-        <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G185" s="7" t="n"/>
@@ -7179,7 +7202,7 @@
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="8">
-        <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G186" s="7" t="n"/>
@@ -7201,7 +7224,7 @@
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
       <c r="F187" s="8">
-        <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G187" s="7" t="n"/>
@@ -7223,7 +7246,7 @@
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="8">
-        <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G188" s="7" t="n"/>
@@ -7245,7 +7268,7 @@
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
       <c r="F189" s="8">
-        <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G189" s="7" t="n"/>
@@ -7267,7 +7290,7 @@
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="8">
-        <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G190" s="7" t="n"/>
@@ -7289,7 +7312,7 @@
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
       <c r="F191" s="8">
-        <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G191" s="7" t="n"/>
@@ -7311,7 +7334,7 @@
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="8">
-        <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G192" s="7" t="n"/>
@@ -7333,7 +7356,7 @@
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
       <c r="F193" s="8">
-        <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G193" s="7" t="n"/>
@@ -7355,7 +7378,7 @@
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="8">
-        <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G194" s="7" t="n"/>
@@ -7377,7 +7400,7 @@
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
       <c r="F195" s="8">
-        <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G195" s="7" t="n"/>
@@ -7399,7 +7422,7 @@
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="8">
-        <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G196" s="7" t="n"/>
@@ -7421,7 +7444,7 @@
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
       <c r="F197" s="8">
-        <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G197" s="7" t="n"/>
@@ -7443,7 +7466,7 @@
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="8">
-        <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G198" s="7" t="n"/>
@@ -7465,7 +7488,7 @@
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
       <c r="F199" s="8">
-        <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G199" s="7" t="n"/>
@@ -7487,7 +7510,7 @@
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="8">
-        <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G200" s="7" t="n"/>
@@ -7509,7 +7532,7 @@
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
       <c r="F201" s="8">
-        <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G201" s="7" t="n"/>
@@ -7531,7 +7554,7 @@
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
       <c r="F202" s="8">
-        <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G202" s="7" t="n"/>
@@ -7553,7 +7576,7 @@
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
       <c r="F203" s="8">
-        <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G203" s="7" t="n"/>
@@ -7575,7 +7598,7 @@
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
       <c r="F204" s="8">
-        <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13)))))</f>
+        <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
       <c r="G204" s="7" t="n"/>
@@ -7969,7 +7992,7 @@
       </c>
       <c r="AC4" s="7" t="n"/>
       <c r="AD4" s="8">
-        <f>IF(A4="","",IF(AC4&lt;&gt;"",AC4,IF(E4="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A4="","",IF(AC4&lt;&gt;"",AC4,IF(E4="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E4,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B4))="SWALE",UPPER(TRIM(AI4))="PIPE"),AND(UPPER(TRIM(B4))="TRENCH",UPPER(TRIM(AI4))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE4" s="8">
@@ -8121,7 +8144,7 @@
       </c>
       <c r="AC5" s="7" t="n"/>
       <c r="AD5" s="8">
-        <f>IF(A5="","",IF(AC5&lt;&gt;"",AC5,IF(E5="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A5="","",IF(AC5&lt;&gt;"",AC5,IF(E5="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E5,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B5))="SWALE",UPPER(TRIM(AI5))="PIPE"),AND(UPPER(TRIM(B5))="TRENCH",UPPER(TRIM(AI5))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE5" s="8">
@@ -8262,7 +8285,7 @@
       </c>
       <c r="AC6" s="7" t="n"/>
       <c r="AD6" s="8">
-        <f>IF(A6="","",IF(AC6&lt;&gt;"",AC6,IF(E6="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A6="","",IF(AC6&lt;&gt;"",AC6,IF(E6="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E6,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B6))="SWALE",UPPER(TRIM(AI6))="PIPE"),AND(UPPER(TRIM(B6))="TRENCH",UPPER(TRIM(AI6))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE6" s="8">
@@ -8408,7 +8431,7 @@
       </c>
       <c r="AC7" s="7" t="n"/>
       <c r="AD7" s="8">
-        <f>IF(A7="","",IF(AC7&lt;&gt;"",AC7,IF(E7="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A7="","",IF(AC7&lt;&gt;"",AC7,IF(E7="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E7,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B7))="SWALE",UPPER(TRIM(AI7))="PIPE"),AND(UPPER(TRIM(B7))="TRENCH",UPPER(TRIM(AI7))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE7" s="8">
@@ -8554,7 +8577,7 @@
       </c>
       <c r="AC8" s="7" t="n"/>
       <c r="AD8" s="8">
-        <f>IF(A8="","",IF(AC8&lt;&gt;"",AC8,IF(E8="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A8="","",IF(AC8&lt;&gt;"",AC8,IF(E8="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E8,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B8))="SWALE",UPPER(TRIM(AI8))="PIPE"),AND(UPPER(TRIM(B8))="TRENCH",UPPER(TRIM(AI8))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE8" s="8">
@@ -8696,7 +8719,7 @@
       </c>
       <c r="AC9" s="7" t="n"/>
       <c r="AD9" s="8">
-        <f>IF(A9="","",IF(AC9&lt;&gt;"",AC9,IF(E9="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A9="","",IF(AC9&lt;&gt;"",AC9,IF(E9="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E9,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B9))="SWALE",UPPER(TRIM(AI9))="PIPE"),AND(UPPER(TRIM(B9))="TRENCH",UPPER(TRIM(AI9))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE9" s="8">
@@ -8842,7 +8865,7 @@
       </c>
       <c r="AC10" s="7" t="n"/>
       <c r="AD10" s="8">
-        <f>IF(A10="","",IF(AC10&lt;&gt;"",AC10,IF(E10="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A10="","",IF(AC10&lt;&gt;"",AC10,IF(E10="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E10,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B10))="SWALE",UPPER(TRIM(AI10))="PIPE"),AND(UPPER(TRIM(B10))="TRENCH",UPPER(TRIM(AI10))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE10" s="8">
@@ -8984,7 +9007,7 @@
       </c>
       <c r="AC11" s="7" t="n"/>
       <c r="AD11" s="8">
-        <f>IF(A11="","",IF(AC11&lt;&gt;"",AC11,IF(E11="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A11="","",IF(AC11&lt;&gt;"",AC11,IF(E11="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E11,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B11))="SWALE",UPPER(TRIM(AI11))="PIPE"),AND(UPPER(TRIM(B11))="TRENCH",UPPER(TRIM(AI11))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE11" s="8">
@@ -9130,7 +9153,7 @@
       </c>
       <c r="AC12" s="7" t="n"/>
       <c r="AD12" s="8">
-        <f>IF(A12="","",IF(AC12&lt;&gt;"",AC12,IF(E12="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A12="","",IF(AC12&lt;&gt;"",AC12,IF(E12="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E12,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B12))="SWALE",UPPER(TRIM(AI12))="PIPE"),AND(UPPER(TRIM(B12))="TRENCH",UPPER(TRIM(AI12))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE12" s="8">
@@ -9239,7 +9262,7 @@
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="7" t="n"/>
       <c r="AD13" s="8">
-        <f>IF(A13="","",IF(AC13&lt;&gt;"",AC13,IF(E13="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A13="","",IF(AC13&lt;&gt;"",AC13,IF(E13="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E13,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B13))="SWALE",UPPER(TRIM(AI13))="PIPE"),AND(UPPER(TRIM(B13))="TRENCH",UPPER(TRIM(AI13))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE13" s="8">
@@ -9376,7 +9399,7 @@
       </c>
       <c r="AC14" s="7" t="n"/>
       <c r="AD14" s="8">
-        <f>IF(A14="","",IF(AC14&lt;&gt;"",AC14,IF(E14="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A14="","",IF(AC14&lt;&gt;"",AC14,IF(E14="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E14,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B14))="SWALE",UPPER(TRIM(AI14))="PIPE"),AND(UPPER(TRIM(B14))="TRENCH",UPPER(TRIM(AI14))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE14" s="8">
@@ -9513,7 +9536,7 @@
       </c>
       <c r="AC15" s="7" t="n"/>
       <c r="AD15" s="8">
-        <f>IF(A15="","",IF(AC15&lt;&gt;"",AC15,IF(E15="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A15="","",IF(AC15&lt;&gt;"",AC15,IF(E15="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E15,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B15))="SWALE",UPPER(TRIM(AI15))="PIPE"),AND(UPPER(TRIM(B15))="TRENCH",UPPER(TRIM(AI15))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE15" s="8">
@@ -9622,7 +9645,7 @@
       <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="7" t="n"/>
       <c r="AD16" s="8">
-        <f>IF(A16="","",IF(AC16&lt;&gt;"",AC16,IF(E16="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A16="","",IF(AC16&lt;&gt;"",AC16,IF(E16="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE16" s="8">
@@ -9731,7 +9754,7 @@
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="7" t="n"/>
       <c r="AD17" s="8">
-        <f>IF(A17="","",IF(AC17&lt;&gt;"",AC17,IF(E17="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A17="","",IF(AC17&lt;&gt;"",AC17,IF(E17="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E17,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B17))="SWALE",UPPER(TRIM(AI17))="PIPE"),AND(UPPER(TRIM(B17))="TRENCH",UPPER(TRIM(AI17))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE17" s="8">
@@ -9840,7 +9863,7 @@
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="7" t="n"/>
       <c r="AD18" s="8">
-        <f>IF(A18="","",IF(AC18&lt;&gt;"",AC18,IF(E18="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A18="","",IF(AC18&lt;&gt;"",AC18,IF(E18="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E18,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B18))="SWALE",UPPER(TRIM(AI18))="PIPE"),AND(UPPER(TRIM(B18))="TRENCH",UPPER(TRIM(AI18))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE18" s="8">
@@ -9949,7 +9972,7 @@
       <c r="AB19" s="4" t="n"/>
       <c r="AC19" s="7" t="n"/>
       <c r="AD19" s="8">
-        <f>IF(A19="","",IF(AC19&lt;&gt;"",AC19,IF(E19="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A19="","",IF(AC19&lt;&gt;"",AC19,IF(E19="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E19,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B19))="SWALE",UPPER(TRIM(AI19))="PIPE"),AND(UPPER(TRIM(B19))="TRENCH",UPPER(TRIM(AI19))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE19" s="8">
@@ -10058,7 +10081,7 @@
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="7" t="n"/>
       <c r="AD20" s="8">
-        <f>IF(A20="","",IF(AC20&lt;&gt;"",AC20,IF(E20="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A20="","",IF(AC20&lt;&gt;"",AC20,IF(E20="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E20,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B20))="SWALE",UPPER(TRIM(AI20))="PIPE"),AND(UPPER(TRIM(B20))="TRENCH",UPPER(TRIM(AI20))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE20" s="8">
@@ -10169,7 +10192,7 @@
       <c r="AB21" s="4" t="n"/>
       <c r="AC21" s="7" t="n"/>
       <c r="AD21" s="8">
-        <f>IF(A21="","",IF(AC21&lt;&gt;"",AC21,IF(E21="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A21="","",IF(AC21&lt;&gt;"",AC21,IF(E21="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E21,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B21))="SWALE",UPPER(TRIM(AI21))="PIPE"),AND(UPPER(TRIM(B21))="TRENCH",UPPER(TRIM(AI21))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE21" s="8">
@@ -10280,7 +10303,7 @@
       <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="7" t="n"/>
       <c r="AD22" s="8">
-        <f>IF(A22="","",IF(AC22&lt;&gt;"",AC22,IF(E22="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A22="","",IF(AC22&lt;&gt;"",AC22,IF(E22="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E22,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B22))="SWALE",UPPER(TRIM(AI22))="PIPE"),AND(UPPER(TRIM(B22))="TRENCH",UPPER(TRIM(AI22))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE22" s="8">
@@ -10391,7 +10414,7 @@
       <c r="AB23" s="4" t="n"/>
       <c r="AC23" s="7" t="n"/>
       <c r="AD23" s="8">
-        <f>IF(A23="","",IF(AC23&lt;&gt;"",AC23,IF(E23="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A23="","",IF(AC23&lt;&gt;"",AC23,IF(E23="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E23,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B23))="SWALE",UPPER(TRIM(AI23))="PIPE"),AND(UPPER(TRIM(B23))="TRENCH",UPPER(TRIM(AI23))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE23" s="8">
@@ -10502,7 +10525,7 @@
       <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="7" t="n"/>
       <c r="AD24" s="8">
-        <f>IF(A24="","",IF(AC24&lt;&gt;"",AC24,IF(E24="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A24="","",IF(AC24&lt;&gt;"",AC24,IF(E24="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E24,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B24))="SWALE",UPPER(TRIM(AI24))="PIPE"),AND(UPPER(TRIM(B24))="TRENCH",UPPER(TRIM(AI24))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE24" s="8">
@@ -10613,7 +10636,7 @@
       <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="7" t="n"/>
       <c r="AD25" s="8">
-        <f>IF(A25="","",IF(AC25&lt;&gt;"",AC25,IF(E25="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A25="","",IF(AC25&lt;&gt;"",AC25,IF(E25="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E25,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B25))="SWALE",UPPER(TRIM(AI25))="PIPE"),AND(UPPER(TRIM(B25))="TRENCH",UPPER(TRIM(AI25))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE25" s="8">
@@ -10724,7 +10747,7 @@
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="7" t="n"/>
       <c r="AD26" s="8">
-        <f>IF(A26="","",IF(AC26&lt;&gt;"",AC26,IF(E26="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A26="","",IF(AC26&lt;&gt;"",AC26,IF(E26="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E26,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B26))="SWALE",UPPER(TRIM(AI26))="PIPE"),AND(UPPER(TRIM(B26))="TRENCH",UPPER(TRIM(AI26))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE26" s="8">
@@ -10835,7 +10858,7 @@
       <c r="AB27" s="4" t="n"/>
       <c r="AC27" s="7" t="n"/>
       <c r="AD27" s="8">
-        <f>IF(A27="","",IF(AC27&lt;&gt;"",AC27,IF(E27="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A27="","",IF(AC27&lt;&gt;"",AC27,IF(E27="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E27,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B27))="SWALE",UPPER(TRIM(AI27))="PIPE"),AND(UPPER(TRIM(B27))="TRENCH",UPPER(TRIM(AI27))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE27" s="8">
@@ -10946,7 +10969,7 @@
       <c r="AB28" s="4" t="n"/>
       <c r="AC28" s="7" t="n"/>
       <c r="AD28" s="8">
-        <f>IF(A28="","",IF(AC28&lt;&gt;"",AC28,IF(E28="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A28="","",IF(AC28&lt;&gt;"",AC28,IF(E28="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E28,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B28))="SWALE",UPPER(TRIM(AI28))="PIPE"),AND(UPPER(TRIM(B28))="TRENCH",UPPER(TRIM(AI28))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE28" s="8">
@@ -11057,7 +11080,7 @@
       <c r="AB29" s="4" t="n"/>
       <c r="AC29" s="7" t="n"/>
       <c r="AD29" s="8">
-        <f>IF(A29="","",IF(AC29&lt;&gt;"",AC29,IF(E29="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A29="","",IF(AC29&lt;&gt;"",AC29,IF(E29="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E29,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B29))="SWALE",UPPER(TRIM(AI29))="PIPE"),AND(UPPER(TRIM(B29))="TRENCH",UPPER(TRIM(AI29))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE29" s="8">
@@ -11168,7 +11191,7 @@
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="7" t="n"/>
       <c r="AD30" s="8">
-        <f>IF(A30="","",IF(AC30&lt;&gt;"",AC30,IF(E30="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A30="","",IF(AC30&lt;&gt;"",AC30,IF(E30="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E30,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B30))="SWALE",UPPER(TRIM(AI30))="PIPE"),AND(UPPER(TRIM(B30))="TRENCH",UPPER(TRIM(AI30))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE30" s="8">
@@ -11279,7 +11302,7 @@
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="7" t="n"/>
       <c r="AD31" s="8">
-        <f>IF(A31="","",IF(AC31&lt;&gt;"",AC31,IF(E31="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A31="","",IF(AC31&lt;&gt;"",AC31,IF(E31="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E31,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B31))="SWALE",UPPER(TRIM(AI31))="PIPE"),AND(UPPER(TRIM(B31))="TRENCH",UPPER(TRIM(AI31))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE31" s="8">
@@ -11390,7 +11413,7 @@
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="7" t="n"/>
       <c r="AD32" s="8">
-        <f>IF(A32="","",IF(AC32&lt;&gt;"",AC32,IF(E32="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A32="","",IF(AC32&lt;&gt;"",AC32,IF(E32="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E32,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B32))="SWALE",UPPER(TRIM(AI32))="PIPE"),AND(UPPER(TRIM(B32))="TRENCH",UPPER(TRIM(AI32))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE32" s="8">
@@ -11501,7 +11524,7 @@
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="7" t="n"/>
       <c r="AD33" s="8">
-        <f>IF(A33="","",IF(AC33&lt;&gt;"",AC33,IF(E33="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A33="","",IF(AC33&lt;&gt;"",AC33,IF(E33="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E33,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B33))="SWALE",UPPER(TRIM(AI33))="PIPE"),AND(UPPER(TRIM(B33))="TRENCH",UPPER(TRIM(AI33))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE33" s="8">
@@ -11612,7 +11635,7 @@
       <c r="AB34" s="4" t="n"/>
       <c r="AC34" s="7" t="n"/>
       <c r="AD34" s="8">
-        <f>IF(A34="","",IF(AC34&lt;&gt;"",AC34,IF(E34="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A34="","",IF(AC34&lt;&gt;"",AC34,IF(E34="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E34,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B34))="SWALE",UPPER(TRIM(AI34))="PIPE"),AND(UPPER(TRIM(B34))="TRENCH",UPPER(TRIM(AI34))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE34" s="8">
@@ -11723,7 +11746,7 @@
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="7" t="n"/>
       <c r="AD35" s="8">
-        <f>IF(A35="","",IF(AC35&lt;&gt;"",AC35,IF(E35="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A35="","",IF(AC35&lt;&gt;"",AC35,IF(E35="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E35,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B35))="SWALE",UPPER(TRIM(AI35))="PIPE"),AND(UPPER(TRIM(B35))="TRENCH",UPPER(TRIM(AI35))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE35" s="8">
@@ -11834,7 +11857,7 @@
       <c r="AB36" s="4" t="n"/>
       <c r="AC36" s="7" t="n"/>
       <c r="AD36" s="8">
-        <f>IF(A36="","",IF(AC36&lt;&gt;"",AC36,IF(E36="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A36="","",IF(AC36&lt;&gt;"",AC36,IF(E36="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E36,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B36))="SWALE",UPPER(TRIM(AI36))="PIPE"),AND(UPPER(TRIM(B36))="TRENCH",UPPER(TRIM(AI36))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE36" s="8">
@@ -11945,7 +11968,7 @@
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="7" t="n"/>
       <c r="AD37" s="8">
-        <f>IF(A37="","",IF(AC37&lt;&gt;"",AC37,IF(E37="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A37="","",IF(AC37&lt;&gt;"",AC37,IF(E37="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E37,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B37))="SWALE",UPPER(TRIM(AI37))="PIPE"),AND(UPPER(TRIM(B37))="TRENCH",UPPER(TRIM(AI37))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE37" s="8">
@@ -12056,7 +12079,7 @@
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="7" t="n"/>
       <c r="AD38" s="8">
-        <f>IF(A38="","",IF(AC38&lt;&gt;"",AC38,IF(E38="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A38="","",IF(AC38&lt;&gt;"",AC38,IF(E38="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E38,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B38))="SWALE",UPPER(TRIM(AI38))="PIPE"),AND(UPPER(TRIM(B38))="TRENCH",UPPER(TRIM(AI38))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE38" s="8">
@@ -12167,7 +12190,7 @@
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="7" t="n"/>
       <c r="AD39" s="8">
-        <f>IF(A39="","",IF(AC39&lt;&gt;"",AC39,IF(E39="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A39="","",IF(AC39&lt;&gt;"",AC39,IF(E39="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E39,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B39))="SWALE",UPPER(TRIM(AI39))="PIPE"),AND(UPPER(TRIM(B39))="TRENCH",UPPER(TRIM(AI39))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE39" s="8">
@@ -12278,7 +12301,7 @@
       <c r="AB40" s="4" t="n"/>
       <c r="AC40" s="7" t="n"/>
       <c r="AD40" s="8">
-        <f>IF(A40="","",IF(AC40&lt;&gt;"",AC40,IF(E40="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A40="","",IF(AC40&lt;&gt;"",AC40,IF(E40="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E40,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B40))="SWALE",UPPER(TRIM(AI40))="PIPE"),AND(UPPER(TRIM(B40))="TRENCH",UPPER(TRIM(AI40))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE40" s="8">
@@ -12389,7 +12412,7 @@
       <c r="AB41" s="4" t="n"/>
       <c r="AC41" s="7" t="n"/>
       <c r="AD41" s="8">
-        <f>IF(A41="","",IF(AC41&lt;&gt;"",AC41,IF(E41="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A41="","",IF(AC41&lt;&gt;"",AC41,IF(E41="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E41,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B41))="SWALE",UPPER(TRIM(AI41))="PIPE"),AND(UPPER(TRIM(B41))="TRENCH",UPPER(TRIM(AI41))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE41" s="8">
@@ -12500,7 +12523,7 @@
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="7" t="n"/>
       <c r="AD42" s="8">
-        <f>IF(A42="","",IF(AC42&lt;&gt;"",AC42,IF(E42="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A42="","",IF(AC42&lt;&gt;"",AC42,IF(E42="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E42,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B42))="SWALE",UPPER(TRIM(AI42))="PIPE"),AND(UPPER(TRIM(B42))="TRENCH",UPPER(TRIM(AI42))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE42" s="8">
@@ -12611,7 +12634,7 @@
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="7" t="n"/>
       <c r="AD43" s="8">
-        <f>IF(A43="","",IF(AC43&lt;&gt;"",AC43,IF(E43="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A43="","",IF(AC43&lt;&gt;"",AC43,IF(E43="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E43,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B43))="SWALE",UPPER(TRIM(AI43))="PIPE"),AND(UPPER(TRIM(B43))="TRENCH",UPPER(TRIM(AI43))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE43" s="8">
@@ -12722,7 +12745,7 @@
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="7" t="n"/>
       <c r="AD44" s="8">
-        <f>IF(A44="","",IF(AC44&lt;&gt;"",AC44,IF(E44="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A44="","",IF(AC44&lt;&gt;"",AC44,IF(E44="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E44,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B44))="SWALE",UPPER(TRIM(AI44))="PIPE"),AND(UPPER(TRIM(B44))="TRENCH",UPPER(TRIM(AI44))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE44" s="8">
@@ -12833,7 +12856,7 @@
       <c r="AB45" s="4" t="n"/>
       <c r="AC45" s="7" t="n"/>
       <c r="AD45" s="8">
-        <f>IF(A45="","",IF(AC45&lt;&gt;"",AC45,IF(E45="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A45="","",IF(AC45&lt;&gt;"",AC45,IF(E45="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E45,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B45))="SWALE",UPPER(TRIM(AI45))="PIPE"),AND(UPPER(TRIM(B45))="TRENCH",UPPER(TRIM(AI45))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE45" s="8">
@@ -12944,7 +12967,7 @@
       <c r="AB46" s="4" t="n"/>
       <c r="AC46" s="7" t="n"/>
       <c r="AD46" s="8">
-        <f>IF(A46="","",IF(AC46&lt;&gt;"",AC46,IF(E46="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A46="","",IF(AC46&lt;&gt;"",AC46,IF(E46="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E46,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B46))="SWALE",UPPER(TRIM(AI46))="PIPE"),AND(UPPER(TRIM(B46))="TRENCH",UPPER(TRIM(AI46))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE46" s="8">
@@ -13055,7 +13078,7 @@
       <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="7" t="n"/>
       <c r="AD47" s="8">
-        <f>IF(A47="","",IF(AC47&lt;&gt;"",AC47,IF(E47="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A47="","",IF(AC47&lt;&gt;"",AC47,IF(E47="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E47,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B47))="SWALE",UPPER(TRIM(AI47))="PIPE"),AND(UPPER(TRIM(B47))="TRENCH",UPPER(TRIM(AI47))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE47" s="8">
@@ -13166,7 +13189,7 @@
       <c r="AB48" s="4" t="n"/>
       <c r="AC48" s="7" t="n"/>
       <c r="AD48" s="8">
-        <f>IF(A48="","",IF(AC48&lt;&gt;"",AC48,IF(E48="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A48="","",IF(AC48&lt;&gt;"",AC48,IF(E48="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E48,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B48))="SWALE",UPPER(TRIM(AI48))="PIPE"),AND(UPPER(TRIM(B48))="TRENCH",UPPER(TRIM(AI48))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE48" s="8">
@@ -13277,7 +13300,7 @@
       <c r="AB49" s="4" t="n"/>
       <c r="AC49" s="7" t="n"/>
       <c r="AD49" s="8">
-        <f>IF(A49="","",IF(AC49&lt;&gt;"",AC49,IF(E49="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A49="","",IF(AC49&lt;&gt;"",AC49,IF(E49="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E49,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B49))="SWALE",UPPER(TRIM(AI49))="PIPE"),AND(UPPER(TRIM(B49))="TRENCH",UPPER(TRIM(AI49))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE49" s="8">
@@ -13388,7 +13411,7 @@
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="7" t="n"/>
       <c r="AD50" s="8">
-        <f>IF(A50="","",IF(AC50&lt;&gt;"",AC50,IF(E50="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A50="","",IF(AC50&lt;&gt;"",AC50,IF(E50="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E50,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B50))="SWALE",UPPER(TRIM(AI50))="PIPE"),AND(UPPER(TRIM(B50))="TRENCH",UPPER(TRIM(AI50))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE50" s="8">
@@ -13499,7 +13522,7 @@
       <c r="AB51" s="4" t="n"/>
       <c r="AC51" s="7" t="n"/>
       <c r="AD51" s="8">
-        <f>IF(A51="","",IF(AC51&lt;&gt;"",AC51,IF(E51="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A51="","",IF(AC51&lt;&gt;"",AC51,IF(E51="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E51,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B51))="SWALE",UPPER(TRIM(AI51))="PIPE"),AND(UPPER(TRIM(B51))="TRENCH",UPPER(TRIM(AI51))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE51" s="8">
@@ -13610,7 +13633,7 @@
       <c r="AB52" s="4" t="n"/>
       <c r="AC52" s="7" t="n"/>
       <c r="AD52" s="8">
-        <f>IF(A52="","",IF(AC52&lt;&gt;"",AC52,IF(E52="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A52="","",IF(AC52&lt;&gt;"",AC52,IF(E52="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E52,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B52))="SWALE",UPPER(TRIM(AI52))="PIPE"),AND(UPPER(TRIM(B52))="TRENCH",UPPER(TRIM(AI52))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE52" s="8">
@@ -13721,7 +13744,7 @@
       <c r="AB53" s="4" t="n"/>
       <c r="AC53" s="7" t="n"/>
       <c r="AD53" s="8">
-        <f>IF(A53="","",IF(AC53&lt;&gt;"",AC53,IF(E53="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A53="","",IF(AC53&lt;&gt;"",AC53,IF(E53="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E53,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B53))="SWALE",UPPER(TRIM(AI53))="PIPE"),AND(UPPER(TRIM(B53))="TRENCH",UPPER(TRIM(AI53))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE53" s="8">
@@ -13832,7 +13855,7 @@
       <c r="AB54" s="4" t="n"/>
       <c r="AC54" s="7" t="n"/>
       <c r="AD54" s="8">
-        <f>IF(A54="","",IF(AC54&lt;&gt;"",AC54,IF(E54="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A54="","",IF(AC54&lt;&gt;"",AC54,IF(E54="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E54,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B54))="SWALE",UPPER(TRIM(AI54))="PIPE"),AND(UPPER(TRIM(B54))="TRENCH",UPPER(TRIM(AI54))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE54" s="8">
@@ -13943,7 +13966,7 @@
       <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="7" t="n"/>
       <c r="AD55" s="8">
-        <f>IF(A55="","",IF(AC55&lt;&gt;"",AC55,IF(E55="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A55="","",IF(AC55&lt;&gt;"",AC55,IF(E55="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E55,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B55))="SWALE",UPPER(TRIM(AI55))="PIPE"),AND(UPPER(TRIM(B55))="TRENCH",UPPER(TRIM(AI55))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE55" s="8">
@@ -14054,7 +14077,7 @@
       <c r="AB56" s="4" t="n"/>
       <c r="AC56" s="7" t="n"/>
       <c r="AD56" s="8">
-        <f>IF(A56="","",IF(AC56&lt;&gt;"",AC56,IF(E56="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A56="","",IF(AC56&lt;&gt;"",AC56,IF(E56="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E56,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B56))="SWALE",UPPER(TRIM(AI56))="PIPE"),AND(UPPER(TRIM(B56))="TRENCH",UPPER(TRIM(AI56))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE56" s="8">
@@ -14165,7 +14188,7 @@
       <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="7" t="n"/>
       <c r="AD57" s="8">
-        <f>IF(A57="","",IF(AC57&lt;&gt;"",AC57,IF(E57="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A57="","",IF(AC57&lt;&gt;"",AC57,IF(E57="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E57,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B57))="SWALE",UPPER(TRIM(AI57))="PIPE"),AND(UPPER(TRIM(B57))="TRENCH",UPPER(TRIM(AI57))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE57" s="8">
@@ -14276,7 +14299,7 @@
       <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="7" t="n"/>
       <c r="AD58" s="8">
-        <f>IF(A58="","",IF(AC58&lt;&gt;"",AC58,IF(E58="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A58="","",IF(AC58&lt;&gt;"",AC58,IF(E58="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E58,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B58))="SWALE",UPPER(TRIM(AI58))="PIPE"),AND(UPPER(TRIM(B58))="TRENCH",UPPER(TRIM(AI58))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE58" s="8">
@@ -14387,7 +14410,7 @@
       <c r="AB59" s="4" t="n"/>
       <c r="AC59" s="7" t="n"/>
       <c r="AD59" s="8">
-        <f>IF(A59="","",IF(AC59&lt;&gt;"",AC59,IF(E59="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A59="","",IF(AC59&lt;&gt;"",AC59,IF(E59="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E59,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B59))="SWALE",UPPER(TRIM(AI59))="PIPE"),AND(UPPER(TRIM(B59))="TRENCH",UPPER(TRIM(AI59))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE59" s="8">
@@ -14498,7 +14521,7 @@
       <c r="AB60" s="4" t="n"/>
       <c r="AC60" s="7" t="n"/>
       <c r="AD60" s="8">
-        <f>IF(A60="","",IF(AC60&lt;&gt;"",AC60,IF(E60="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A60="","",IF(AC60&lt;&gt;"",AC60,IF(E60="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E60,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B60))="SWALE",UPPER(TRIM(AI60))="PIPE"),AND(UPPER(TRIM(B60))="TRENCH",UPPER(TRIM(AI60))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE60" s="8">
@@ -14609,7 +14632,7 @@
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="7" t="n"/>
       <c r="AD61" s="8">
-        <f>IF(A61="","",IF(AC61&lt;&gt;"",AC61,IF(E61="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A61="","",IF(AC61&lt;&gt;"",AC61,IF(E61="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E61,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B61))="SWALE",UPPER(TRIM(AI61))="PIPE"),AND(UPPER(TRIM(B61))="TRENCH",UPPER(TRIM(AI61))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE61" s="8">
@@ -14720,7 +14743,7 @@
       <c r="AB62" s="4" t="n"/>
       <c r="AC62" s="7" t="n"/>
       <c r="AD62" s="8">
-        <f>IF(A62="","",IF(AC62&lt;&gt;"",AC62,IF(E62="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A62="","",IF(AC62&lt;&gt;"",AC62,IF(E62="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E62,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B62))="SWALE",UPPER(TRIM(AI62))="PIPE"),AND(UPPER(TRIM(B62))="TRENCH",UPPER(TRIM(AI62))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE62" s="8">
@@ -14831,7 +14854,7 @@
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="7" t="n"/>
       <c r="AD63" s="8">
-        <f>IF(A63="","",IF(AC63&lt;&gt;"",AC63,IF(E63="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A63="","",IF(AC63&lt;&gt;"",AC63,IF(E63="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E63,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B63))="SWALE",UPPER(TRIM(AI63))="PIPE"),AND(UPPER(TRIM(B63))="TRENCH",UPPER(TRIM(AI63))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE63" s="8">
@@ -14942,7 +14965,7 @@
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="7" t="n"/>
       <c r="AD64" s="8">
-        <f>IF(A64="","",IF(AC64&lt;&gt;"",AC64,IF(E64="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A64="","",IF(AC64&lt;&gt;"",AC64,IF(E64="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E64,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B64))="SWALE",UPPER(TRIM(AI64))="PIPE"),AND(UPPER(TRIM(B64))="TRENCH",UPPER(TRIM(AI64))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE64" s="8">
@@ -15053,7 +15076,7 @@
       <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="7" t="n"/>
       <c r="AD65" s="8">
-        <f>IF(A65="","",IF(AC65&lt;&gt;"",AC65,IF(E65="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A65="","",IF(AC65&lt;&gt;"",AC65,IF(E65="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E65,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B65))="SWALE",UPPER(TRIM(AI65))="PIPE"),AND(UPPER(TRIM(B65))="TRENCH",UPPER(TRIM(AI65))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE65" s="8">
@@ -15164,7 +15187,7 @@
       <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="7" t="n"/>
       <c r="AD66" s="8">
-        <f>IF(A66="","",IF(AC66&lt;&gt;"",AC66,IF(E66="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A66="","",IF(AC66&lt;&gt;"",AC66,IF(E66="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E66,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B66))="SWALE",UPPER(TRIM(AI66))="PIPE"),AND(UPPER(TRIM(B66))="TRENCH",UPPER(TRIM(AI66))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE66" s="8">
@@ -15275,7 +15298,7 @@
       <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="7" t="n"/>
       <c r="AD67" s="8">
-        <f>IF(A67="","",IF(AC67&lt;&gt;"",AC67,IF(E67="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A67="","",IF(AC67&lt;&gt;"",AC67,IF(E67="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E67,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B67))="SWALE",UPPER(TRIM(AI67))="PIPE"),AND(UPPER(TRIM(B67))="TRENCH",UPPER(TRIM(AI67))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE67" s="8">
@@ -15386,7 +15409,7 @@
       <c r="AB68" s="4" t="n"/>
       <c r="AC68" s="7" t="n"/>
       <c r="AD68" s="8">
-        <f>IF(A68="","",IF(AC68&lt;&gt;"",AC68,IF(E68="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A68="","",IF(AC68&lt;&gt;"",AC68,IF(E68="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E68,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B68))="SWALE",UPPER(TRIM(AI68))="PIPE"),AND(UPPER(TRIM(B68))="TRENCH",UPPER(TRIM(AI68))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE68" s="8">
@@ -15497,7 +15520,7 @@
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="7" t="n"/>
       <c r="AD69" s="8">
-        <f>IF(A69="","",IF(AC69&lt;&gt;"",AC69,IF(E69="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A69="","",IF(AC69&lt;&gt;"",AC69,IF(E69="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E69,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B69))="SWALE",UPPER(TRIM(AI69))="PIPE"),AND(UPPER(TRIM(B69))="TRENCH",UPPER(TRIM(AI69))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE69" s="8">
@@ -15608,7 +15631,7 @@
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="7" t="n"/>
       <c r="AD70" s="8">
-        <f>IF(A70="","",IF(AC70&lt;&gt;"",AC70,IF(E70="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A70="","",IF(AC70&lt;&gt;"",AC70,IF(E70="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E70,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B70))="SWALE",UPPER(TRIM(AI70))="PIPE"),AND(UPPER(TRIM(B70))="TRENCH",UPPER(TRIM(AI70))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE70" s="8">
@@ -15719,7 +15742,7 @@
       <c r="AB71" s="4" t="n"/>
       <c r="AC71" s="7" t="n"/>
       <c r="AD71" s="8">
-        <f>IF(A71="","",IF(AC71&lt;&gt;"",AC71,IF(E71="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A71="","",IF(AC71&lt;&gt;"",AC71,IF(E71="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E71,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B71))="SWALE",UPPER(TRIM(AI71))="PIPE"),AND(UPPER(TRIM(B71))="TRENCH",UPPER(TRIM(AI71))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE71" s="8">
@@ -15830,7 +15853,7 @@
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="7" t="n"/>
       <c r="AD72" s="8">
-        <f>IF(A72="","",IF(AC72&lt;&gt;"",AC72,IF(E72="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A72="","",IF(AC72&lt;&gt;"",AC72,IF(E72="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E72,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B72))="SWALE",UPPER(TRIM(AI72))="PIPE"),AND(UPPER(TRIM(B72))="TRENCH",UPPER(TRIM(AI72))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE72" s="8">
@@ -15941,7 +15964,7 @@
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="7" t="n"/>
       <c r="AD73" s="8">
-        <f>IF(A73="","",IF(AC73&lt;&gt;"",AC73,IF(E73="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A73="","",IF(AC73&lt;&gt;"",AC73,IF(E73="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E73,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B73))="SWALE",UPPER(TRIM(AI73))="PIPE"),AND(UPPER(TRIM(B73))="TRENCH",UPPER(TRIM(AI73))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE73" s="8">
@@ -16052,7 +16075,7 @@
       <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="7" t="n"/>
       <c r="AD74" s="8">
-        <f>IF(A74="","",IF(AC74&lt;&gt;"",AC74,IF(E74="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A74="","",IF(AC74&lt;&gt;"",AC74,IF(E74="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E74,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B74))="SWALE",UPPER(TRIM(AI74))="PIPE"),AND(UPPER(TRIM(B74))="TRENCH",UPPER(TRIM(AI74))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE74" s="8">
@@ -16163,7 +16186,7 @@
       <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="7" t="n"/>
       <c r="AD75" s="8">
-        <f>IF(A75="","",IF(AC75&lt;&gt;"",AC75,IF(E75="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A75="","",IF(AC75&lt;&gt;"",AC75,IF(E75="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E75,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B75))="SWALE",UPPER(TRIM(AI75))="PIPE"),AND(UPPER(TRIM(B75))="TRENCH",UPPER(TRIM(AI75))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE75" s="8">
@@ -16274,7 +16297,7 @@
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="7" t="n"/>
       <c r="AD76" s="8">
-        <f>IF(A76="","",IF(AC76&lt;&gt;"",AC76,IF(E76="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A76="","",IF(AC76&lt;&gt;"",AC76,IF(E76="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E76,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B76))="SWALE",UPPER(TRIM(AI76))="PIPE"),AND(UPPER(TRIM(B76))="TRENCH",UPPER(TRIM(AI76))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE76" s="8">
@@ -16385,7 +16408,7 @@
       <c r="AB77" s="4" t="n"/>
       <c r="AC77" s="7" t="n"/>
       <c r="AD77" s="8">
-        <f>IF(A77="","",IF(AC77&lt;&gt;"",AC77,IF(E77="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A77="","",IF(AC77&lt;&gt;"",AC77,IF(E77="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E77,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B77))="SWALE",UPPER(TRIM(AI77))="PIPE"),AND(UPPER(TRIM(B77))="TRENCH",UPPER(TRIM(AI77))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE77" s="8">
@@ -16496,7 +16519,7 @@
       <c r="AB78" s="4" t="n"/>
       <c r="AC78" s="7" t="n"/>
       <c r="AD78" s="8">
-        <f>IF(A78="","",IF(AC78&lt;&gt;"",AC78,IF(E78="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A78="","",IF(AC78&lt;&gt;"",AC78,IF(E78="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E78,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B78))="SWALE",UPPER(TRIM(AI78))="PIPE"),AND(UPPER(TRIM(B78))="TRENCH",UPPER(TRIM(AI78))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE78" s="8">
@@ -16607,7 +16630,7 @@
       <c r="AB79" s="4" t="n"/>
       <c r="AC79" s="7" t="n"/>
       <c r="AD79" s="8">
-        <f>IF(A79="","",IF(AC79&lt;&gt;"",AC79,IF(E79="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A79="","",IF(AC79&lt;&gt;"",AC79,IF(E79="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E79,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B79))="SWALE",UPPER(TRIM(AI79))="PIPE"),AND(UPPER(TRIM(B79))="TRENCH",UPPER(TRIM(AI79))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE79" s="8">
@@ -16718,7 +16741,7 @@
       <c r="AB80" s="4" t="n"/>
       <c r="AC80" s="7" t="n"/>
       <c r="AD80" s="8">
-        <f>IF(A80="","",IF(AC80&lt;&gt;"",AC80,IF(E80="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A80="","",IF(AC80&lt;&gt;"",AC80,IF(E80="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E80,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B80))="SWALE",UPPER(TRIM(AI80))="PIPE"),AND(UPPER(TRIM(B80))="TRENCH",UPPER(TRIM(AI80))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE80" s="8">
@@ -16829,7 +16852,7 @@
       <c r="AB81" s="4" t="n"/>
       <c r="AC81" s="7" t="n"/>
       <c r="AD81" s="8">
-        <f>IF(A81="","",IF(AC81&lt;&gt;"",AC81,IF(E81="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A81="","",IF(AC81&lt;&gt;"",AC81,IF(E81="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E81,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B81))="SWALE",UPPER(TRIM(AI81))="PIPE"),AND(UPPER(TRIM(B81))="TRENCH",UPPER(TRIM(AI81))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE81" s="8">
@@ -16940,7 +16963,7 @@
       <c r="AB82" s="4" t="n"/>
       <c r="AC82" s="7" t="n"/>
       <c r="AD82" s="8">
-        <f>IF(A82="","",IF(AC82&lt;&gt;"",AC82,IF(E82="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A82="","",IF(AC82&lt;&gt;"",AC82,IF(E82="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E82,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B82))="SWALE",UPPER(TRIM(AI82))="PIPE"),AND(UPPER(TRIM(B82))="TRENCH",UPPER(TRIM(AI82))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE82" s="8">
@@ -17051,7 +17074,7 @@
       <c r="AB83" s="4" t="n"/>
       <c r="AC83" s="7" t="n"/>
       <c r="AD83" s="8">
-        <f>IF(A83="","",IF(AC83&lt;&gt;"",AC83,IF(E83="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A83="","",IF(AC83&lt;&gt;"",AC83,IF(E83="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E83,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B83))="SWALE",UPPER(TRIM(AI83))="PIPE"),AND(UPPER(TRIM(B83))="TRENCH",UPPER(TRIM(AI83))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE83" s="8">
@@ -17162,7 +17185,7 @@
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="7" t="n"/>
       <c r="AD84" s="8">
-        <f>IF(A84="","",IF(AC84&lt;&gt;"",AC84,IF(E84="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A84="","",IF(AC84&lt;&gt;"",AC84,IF(E84="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E84,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B84))="SWALE",UPPER(TRIM(AI84))="PIPE"),AND(UPPER(TRIM(B84))="TRENCH",UPPER(TRIM(AI84))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE84" s="8">
@@ -17273,7 +17296,7 @@
       <c r="AB85" s="4" t="n"/>
       <c r="AC85" s="7" t="n"/>
       <c r="AD85" s="8">
-        <f>IF(A85="","",IF(AC85&lt;&gt;"",AC85,IF(E85="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A85="","",IF(AC85&lt;&gt;"",AC85,IF(E85="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E85,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B85))="SWALE",UPPER(TRIM(AI85))="PIPE"),AND(UPPER(TRIM(B85))="TRENCH",UPPER(TRIM(AI85))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE85" s="8">
@@ -17384,7 +17407,7 @@
       <c r="AB86" s="4" t="n"/>
       <c r="AC86" s="7" t="n"/>
       <c r="AD86" s="8">
-        <f>IF(A86="","",IF(AC86&lt;&gt;"",AC86,IF(E86="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A86="","",IF(AC86&lt;&gt;"",AC86,IF(E86="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E86,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B86))="SWALE",UPPER(TRIM(AI86))="PIPE"),AND(UPPER(TRIM(B86))="TRENCH",UPPER(TRIM(AI86))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE86" s="8">
@@ -17495,7 +17518,7 @@
       <c r="AB87" s="4" t="n"/>
       <c r="AC87" s="7" t="n"/>
       <c r="AD87" s="8">
-        <f>IF(A87="","",IF(AC87&lt;&gt;"",AC87,IF(E87="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A87="","",IF(AC87&lt;&gt;"",AC87,IF(E87="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E87,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B87))="SWALE",UPPER(TRIM(AI87))="PIPE"),AND(UPPER(TRIM(B87))="TRENCH",UPPER(TRIM(AI87))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE87" s="8">
@@ -17606,7 +17629,7 @@
       <c r="AB88" s="4" t="n"/>
       <c r="AC88" s="7" t="n"/>
       <c r="AD88" s="8">
-        <f>IF(A88="","",IF(AC88&lt;&gt;"",AC88,IF(E88="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A88="","",IF(AC88&lt;&gt;"",AC88,IF(E88="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E88,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B88))="SWALE",UPPER(TRIM(AI88))="PIPE"),AND(UPPER(TRIM(B88))="TRENCH",UPPER(TRIM(AI88))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE88" s="8">
@@ -17717,7 +17740,7 @@
       <c r="AB89" s="4" t="n"/>
       <c r="AC89" s="7" t="n"/>
       <c r="AD89" s="8">
-        <f>IF(A89="","",IF(AC89&lt;&gt;"",AC89,IF(E89="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A89="","",IF(AC89&lt;&gt;"",AC89,IF(E89="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E89,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B89))="SWALE",UPPER(TRIM(AI89))="PIPE"),AND(UPPER(TRIM(B89))="TRENCH",UPPER(TRIM(AI89))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE89" s="8">
@@ -17828,7 +17851,7 @@
       <c r="AB90" s="4" t="n"/>
       <c r="AC90" s="7" t="n"/>
       <c r="AD90" s="8">
-        <f>IF(A90="","",IF(AC90&lt;&gt;"",AC90,IF(E90="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A90="","",IF(AC90&lt;&gt;"",AC90,IF(E90="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E90,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B90))="SWALE",UPPER(TRIM(AI90))="PIPE"),AND(UPPER(TRIM(B90))="TRENCH",UPPER(TRIM(AI90))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE90" s="8">
@@ -17939,7 +17962,7 @@
       <c r="AB91" s="4" t="n"/>
       <c r="AC91" s="7" t="n"/>
       <c r="AD91" s="8">
-        <f>IF(A91="","",IF(AC91&lt;&gt;"",AC91,IF(E91="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A91="","",IF(AC91&lt;&gt;"",AC91,IF(E91="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E91,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B91))="SWALE",UPPER(TRIM(AI91))="PIPE"),AND(UPPER(TRIM(B91))="TRENCH",UPPER(TRIM(AI91))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE91" s="8">
@@ -18050,7 +18073,7 @@
       <c r="AB92" s="4" t="n"/>
       <c r="AC92" s="7" t="n"/>
       <c r="AD92" s="8">
-        <f>IF(A92="","",IF(AC92&lt;&gt;"",AC92,IF(E92="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A92="","",IF(AC92&lt;&gt;"",AC92,IF(E92="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E92,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B92))="SWALE",UPPER(TRIM(AI92))="PIPE"),AND(UPPER(TRIM(B92))="TRENCH",UPPER(TRIM(AI92))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE92" s="8">
@@ -18161,7 +18184,7 @@
       <c r="AB93" s="4" t="n"/>
       <c r="AC93" s="7" t="n"/>
       <c r="AD93" s="8">
-        <f>IF(A93="","",IF(AC93&lt;&gt;"",AC93,IF(E93="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A93="","",IF(AC93&lt;&gt;"",AC93,IF(E93="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E93,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B93))="SWALE",UPPER(TRIM(AI93))="PIPE"),AND(UPPER(TRIM(B93))="TRENCH",UPPER(TRIM(AI93))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE93" s="8">
@@ -18272,7 +18295,7 @@
       <c r="AB94" s="4" t="n"/>
       <c r="AC94" s="7" t="n"/>
       <c r="AD94" s="8">
-        <f>IF(A94="","",IF(AC94&lt;&gt;"",AC94,IF(E94="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A94="","",IF(AC94&lt;&gt;"",AC94,IF(E94="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E94,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B94))="SWALE",UPPER(TRIM(AI94))="PIPE"),AND(UPPER(TRIM(B94))="TRENCH",UPPER(TRIM(AI94))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE94" s="8">
@@ -18383,7 +18406,7 @@
       <c r="AB95" s="4" t="n"/>
       <c r="AC95" s="7" t="n"/>
       <c r="AD95" s="8">
-        <f>IF(A95="","",IF(AC95&lt;&gt;"",AC95,IF(E95="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A95="","",IF(AC95&lt;&gt;"",AC95,IF(E95="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E95,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B95))="SWALE",UPPER(TRIM(AI95))="PIPE"),AND(UPPER(TRIM(B95))="TRENCH",UPPER(TRIM(AI95))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE95" s="8">
@@ -18494,7 +18517,7 @@
       <c r="AB96" s="4" t="n"/>
       <c r="AC96" s="7" t="n"/>
       <c r="AD96" s="8">
-        <f>IF(A96="","",IF(AC96&lt;&gt;"",AC96,IF(E96="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A96="","",IF(AC96&lt;&gt;"",AC96,IF(E96="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E96,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B96))="SWALE",UPPER(TRIM(AI96))="PIPE"),AND(UPPER(TRIM(B96))="TRENCH",UPPER(TRIM(AI96))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE96" s="8">
@@ -18605,7 +18628,7 @@
       <c r="AB97" s="4" t="n"/>
       <c r="AC97" s="7" t="n"/>
       <c r="AD97" s="8">
-        <f>IF(A97="","",IF(AC97&lt;&gt;"",AC97,IF(E97="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A97="","",IF(AC97&lt;&gt;"",AC97,IF(E97="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E97,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B97))="SWALE",UPPER(TRIM(AI97))="PIPE"),AND(UPPER(TRIM(B97))="TRENCH",UPPER(TRIM(AI97))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE97" s="8">
@@ -18716,7 +18739,7 @@
       <c r="AB98" s="4" t="n"/>
       <c r="AC98" s="7" t="n"/>
       <c r="AD98" s="8">
-        <f>IF(A98="","",IF(AC98&lt;&gt;"",AC98,IF(E98="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A98="","",IF(AC98&lt;&gt;"",AC98,IF(E98="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E98,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B98))="SWALE",UPPER(TRIM(AI98))="PIPE"),AND(UPPER(TRIM(B98))="TRENCH",UPPER(TRIM(AI98))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE98" s="8">
@@ -18827,7 +18850,7 @@
       <c r="AB99" s="4" t="n"/>
       <c r="AC99" s="7" t="n"/>
       <c r="AD99" s="8">
-        <f>IF(A99="","",IF(AC99&lt;&gt;"",AC99,IF(E99="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A99="","",IF(AC99&lt;&gt;"",AC99,IF(E99="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E99,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B99))="SWALE",UPPER(TRIM(AI99))="PIPE"),AND(UPPER(TRIM(B99))="TRENCH",UPPER(TRIM(AI99))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE99" s="8">
@@ -18938,7 +18961,7 @@
       <c r="AB100" s="4" t="n"/>
       <c r="AC100" s="7" t="n"/>
       <c r="AD100" s="8">
-        <f>IF(A100="","",IF(AC100&lt;&gt;"",AC100,IF(E100="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A100="","",IF(AC100&lt;&gt;"",AC100,IF(E100="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E100,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B100))="SWALE",UPPER(TRIM(AI100))="PIPE"),AND(UPPER(TRIM(B100))="TRENCH",UPPER(TRIM(AI100))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE100" s="8">
@@ -19049,7 +19072,7 @@
       <c r="AB101" s="4" t="n"/>
       <c r="AC101" s="7" t="n"/>
       <c r="AD101" s="8">
-        <f>IF(A101="","",IF(AC101&lt;&gt;"",AC101,IF(E101="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A101="","",IF(AC101&lt;&gt;"",AC101,IF(E101="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E101,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B101))="SWALE",UPPER(TRIM(AI101))="PIPE"),AND(UPPER(TRIM(B101))="TRENCH",UPPER(TRIM(AI101))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE101" s="8">
@@ -19160,7 +19183,7 @@
       <c r="AB102" s="4" t="n"/>
       <c r="AC102" s="7" t="n"/>
       <c r="AD102" s="8">
-        <f>IF(A102="","",IF(AC102&lt;&gt;"",AC102,IF(E102="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A102="","",IF(AC102&lt;&gt;"",AC102,IF(E102="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E102,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B102))="SWALE",UPPER(TRIM(AI102))="PIPE"),AND(UPPER(TRIM(B102))="TRENCH",UPPER(TRIM(AI102))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE102" s="8">
@@ -19271,7 +19294,7 @@
       <c r="AB103" s="4" t="n"/>
       <c r="AC103" s="7" t="n"/>
       <c r="AD103" s="8">
-        <f>IF(A103="","",IF(AC103&lt;&gt;"",AC103,IF(E103="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A103="","",IF(AC103&lt;&gt;"",AC103,IF(E103="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E103,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B103))="SWALE",UPPER(TRIM(AI103))="PIPE"),AND(UPPER(TRIM(B103))="TRENCH",UPPER(TRIM(AI103))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE103" s="8">
@@ -19382,7 +19405,7 @@
       <c r="AB104" s="4" t="n"/>
       <c r="AC104" s="7" t="n"/>
       <c r="AD104" s="8">
-        <f>IF(A104="","",IF(AC104&lt;&gt;"",AC104,IF(E104="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A104="","",IF(AC104&lt;&gt;"",AC104,IF(E104="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E104,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B104))="SWALE",UPPER(TRIM(AI104))="PIPE"),AND(UPPER(TRIM(B104))="TRENCH",UPPER(TRIM(AI104))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE104" s="8">
@@ -19493,7 +19516,7 @@
       <c r="AB105" s="4" t="n"/>
       <c r="AC105" s="7" t="n"/>
       <c r="AD105" s="8">
-        <f>IF(A105="","",IF(AC105&lt;&gt;"",AC105,IF(E105="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A105="","",IF(AC105&lt;&gt;"",AC105,IF(E105="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E105,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B105))="SWALE",UPPER(TRIM(AI105))="PIPE"),AND(UPPER(TRIM(B105))="TRENCH",UPPER(TRIM(AI105))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE105" s="8">
@@ -19604,7 +19627,7 @@
       <c r="AB106" s="4" t="n"/>
       <c r="AC106" s="7" t="n"/>
       <c r="AD106" s="8">
-        <f>IF(A106="","",IF(AC106&lt;&gt;"",AC106,IF(E106="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A106="","",IF(AC106&lt;&gt;"",AC106,IF(E106="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E106,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B106))="SWALE",UPPER(TRIM(AI106))="PIPE"),AND(UPPER(TRIM(B106))="TRENCH",UPPER(TRIM(AI106))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE106" s="8">
@@ -19715,7 +19738,7 @@
       <c r="AB107" s="4" t="n"/>
       <c r="AC107" s="7" t="n"/>
       <c r="AD107" s="8">
-        <f>IF(A107="","",IF(AC107&lt;&gt;"",AC107,IF(E107="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A107="","",IF(AC107&lt;&gt;"",AC107,IF(E107="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E107,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B107))="SWALE",UPPER(TRIM(AI107))="PIPE"),AND(UPPER(TRIM(B107))="TRENCH",UPPER(TRIM(AI107))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE107" s="8">
@@ -19826,7 +19849,7 @@
       <c r="AB108" s="4" t="n"/>
       <c r="AC108" s="7" t="n"/>
       <c r="AD108" s="8">
-        <f>IF(A108="","",IF(AC108&lt;&gt;"",AC108,IF(E108="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A108="","",IF(AC108&lt;&gt;"",AC108,IF(E108="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E108,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B108))="SWALE",UPPER(TRIM(AI108))="PIPE"),AND(UPPER(TRIM(B108))="TRENCH",UPPER(TRIM(AI108))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE108" s="8">
@@ -19937,7 +19960,7 @@
       <c r="AB109" s="4" t="n"/>
       <c r="AC109" s="7" t="n"/>
       <c r="AD109" s="8">
-        <f>IF(A109="","",IF(AC109&lt;&gt;"",AC109,IF(E109="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A109="","",IF(AC109&lt;&gt;"",AC109,IF(E109="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E109,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B109))="SWALE",UPPER(TRIM(AI109))="PIPE"),AND(UPPER(TRIM(B109))="TRENCH",UPPER(TRIM(AI109))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE109" s="8">
@@ -20048,7 +20071,7 @@
       <c r="AB110" s="4" t="n"/>
       <c r="AC110" s="7" t="n"/>
       <c r="AD110" s="8">
-        <f>IF(A110="","",IF(AC110&lt;&gt;"",AC110,IF(E110="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A110="","",IF(AC110&lt;&gt;"",AC110,IF(E110="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E110,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B110))="SWALE",UPPER(TRIM(AI110))="PIPE"),AND(UPPER(TRIM(B110))="TRENCH",UPPER(TRIM(AI110))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE110" s="8">
@@ -20159,7 +20182,7 @@
       <c r="AB111" s="4" t="n"/>
       <c r="AC111" s="7" t="n"/>
       <c r="AD111" s="8">
-        <f>IF(A111="","",IF(AC111&lt;&gt;"",AC111,IF(E111="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A111="","",IF(AC111&lt;&gt;"",AC111,IF(E111="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E111,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B111))="SWALE",UPPER(TRIM(AI111))="PIPE"),AND(UPPER(TRIM(B111))="TRENCH",UPPER(TRIM(AI111))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE111" s="8">
@@ -20270,7 +20293,7 @@
       <c r="AB112" s="4" t="n"/>
       <c r="AC112" s="7" t="n"/>
       <c r="AD112" s="8">
-        <f>IF(A112="","",IF(AC112&lt;&gt;"",AC112,IF(E112="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A112="","",IF(AC112&lt;&gt;"",AC112,IF(E112="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E112,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B112))="SWALE",UPPER(TRIM(AI112))="PIPE"),AND(UPPER(TRIM(B112))="TRENCH",UPPER(TRIM(AI112))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE112" s="8">
@@ -20381,7 +20404,7 @@
       <c r="AB113" s="4" t="n"/>
       <c r="AC113" s="7" t="n"/>
       <c r="AD113" s="8">
-        <f>IF(A113="","",IF(AC113&lt;&gt;"",AC113,IF(E113="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A113="","",IF(AC113&lt;&gt;"",AC113,IF(E113="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E113,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B113))="SWALE",UPPER(TRIM(AI113))="PIPE"),AND(UPPER(TRIM(B113))="TRENCH",UPPER(TRIM(AI113))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE113" s="8">
@@ -20492,7 +20515,7 @@
       <c r="AB114" s="4" t="n"/>
       <c r="AC114" s="7" t="n"/>
       <c r="AD114" s="8">
-        <f>IF(A114="","",IF(AC114&lt;&gt;"",AC114,IF(E114="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A114="","",IF(AC114&lt;&gt;"",AC114,IF(E114="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E114,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B114))="SWALE",UPPER(TRIM(AI114))="PIPE"),AND(UPPER(TRIM(B114))="TRENCH",UPPER(TRIM(AI114))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE114" s="8">
@@ -20603,7 +20626,7 @@
       <c r="AB115" s="4" t="n"/>
       <c r="AC115" s="7" t="n"/>
       <c r="AD115" s="8">
-        <f>IF(A115="","",IF(AC115&lt;&gt;"",AC115,IF(E115="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A115="","",IF(AC115&lt;&gt;"",AC115,IF(E115="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E115,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B115))="SWALE",UPPER(TRIM(AI115))="PIPE"),AND(UPPER(TRIM(B115))="TRENCH",UPPER(TRIM(AI115))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE115" s="8">
@@ -20714,7 +20737,7 @@
       <c r="AB116" s="4" t="n"/>
       <c r="AC116" s="7" t="n"/>
       <c r="AD116" s="8">
-        <f>IF(A116="","",IF(AC116&lt;&gt;"",AC116,IF(E116="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A116="","",IF(AC116&lt;&gt;"",AC116,IF(E116="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E116,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B116))="SWALE",UPPER(TRIM(AI116))="PIPE"),AND(UPPER(TRIM(B116))="TRENCH",UPPER(TRIM(AI116))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE116" s="8">
@@ -20825,7 +20848,7 @@
       <c r="AB117" s="4" t="n"/>
       <c r="AC117" s="7" t="n"/>
       <c r="AD117" s="8">
-        <f>IF(A117="","",IF(AC117&lt;&gt;"",AC117,IF(E117="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A117="","",IF(AC117&lt;&gt;"",AC117,IF(E117="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E117,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B117))="SWALE",UPPER(TRIM(AI117))="PIPE"),AND(UPPER(TRIM(B117))="TRENCH",UPPER(TRIM(AI117))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE117" s="8">
@@ -20936,7 +20959,7 @@
       <c r="AB118" s="4" t="n"/>
       <c r="AC118" s="7" t="n"/>
       <c r="AD118" s="8">
-        <f>IF(A118="","",IF(AC118&lt;&gt;"",AC118,IF(E118="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A118="","",IF(AC118&lt;&gt;"",AC118,IF(E118="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E118,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B118))="SWALE",UPPER(TRIM(AI118))="PIPE"),AND(UPPER(TRIM(B118))="TRENCH",UPPER(TRIM(AI118))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE118" s="8">
@@ -21047,7 +21070,7 @@
       <c r="AB119" s="4" t="n"/>
       <c r="AC119" s="7" t="n"/>
       <c r="AD119" s="8">
-        <f>IF(A119="","",IF(AC119&lt;&gt;"",AC119,IF(E119="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A119="","",IF(AC119&lt;&gt;"",AC119,IF(E119="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E119,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B119))="SWALE",UPPER(TRIM(AI119))="PIPE"),AND(UPPER(TRIM(B119))="TRENCH",UPPER(TRIM(AI119))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE119" s="8">
@@ -21158,7 +21181,7 @@
       <c r="AB120" s="4" t="n"/>
       <c r="AC120" s="7" t="n"/>
       <c r="AD120" s="8">
-        <f>IF(A120="","",IF(AC120&lt;&gt;"",AC120,IF(E120="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A120="","",IF(AC120&lt;&gt;"",AC120,IF(E120="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E120,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B120))="SWALE",UPPER(TRIM(AI120))="PIPE"),AND(UPPER(TRIM(B120))="TRENCH",UPPER(TRIM(AI120))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE120" s="8">
@@ -21269,7 +21292,7 @@
       <c r="AB121" s="4" t="n"/>
       <c r="AC121" s="7" t="n"/>
       <c r="AD121" s="8">
-        <f>IF(A121="","",IF(AC121&lt;&gt;"",AC121,IF(E121="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A121="","",IF(AC121&lt;&gt;"",AC121,IF(E121="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E121,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B121))="SWALE",UPPER(TRIM(AI121))="PIPE"),AND(UPPER(TRIM(B121))="TRENCH",UPPER(TRIM(AI121))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE121" s="8">
@@ -21380,7 +21403,7 @@
       <c r="AB122" s="4" t="n"/>
       <c r="AC122" s="7" t="n"/>
       <c r="AD122" s="8">
-        <f>IF(A122="","",IF(AC122&lt;&gt;"",AC122,IF(E122="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A122="","",IF(AC122&lt;&gt;"",AC122,IF(E122="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E122,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B122))="SWALE",UPPER(TRIM(AI122))="PIPE"),AND(UPPER(TRIM(B122))="TRENCH",UPPER(TRIM(AI122))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE122" s="8">
@@ -21491,7 +21514,7 @@
       <c r="AB123" s="4" t="n"/>
       <c r="AC123" s="7" t="n"/>
       <c r="AD123" s="8">
-        <f>IF(A123="","",IF(AC123&lt;&gt;"",AC123,IF(E123="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A123="","",IF(AC123&lt;&gt;"",AC123,IF(E123="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E123,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B123))="SWALE",UPPER(TRIM(AI123))="PIPE"),AND(UPPER(TRIM(B123))="TRENCH",UPPER(TRIM(AI123))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE123" s="8">
@@ -21602,7 +21625,7 @@
       <c r="AB124" s="4" t="n"/>
       <c r="AC124" s="7" t="n"/>
       <c r="AD124" s="8">
-        <f>IF(A124="","",IF(AC124&lt;&gt;"",AC124,IF(E124="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A124="","",IF(AC124&lt;&gt;"",AC124,IF(E124="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E124,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B124))="SWALE",UPPER(TRIM(AI124))="PIPE"),AND(UPPER(TRIM(B124))="TRENCH",UPPER(TRIM(AI124))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE124" s="8">
@@ -21713,7 +21736,7 @@
       <c r="AB125" s="4" t="n"/>
       <c r="AC125" s="7" t="n"/>
       <c r="AD125" s="8">
-        <f>IF(A125="","",IF(AC125&lt;&gt;"",AC125,IF(E125="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A125="","",IF(AC125&lt;&gt;"",AC125,IF(E125="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E125,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B125))="SWALE",UPPER(TRIM(AI125))="PIPE"),AND(UPPER(TRIM(B125))="TRENCH",UPPER(TRIM(AI125))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE125" s="8">
@@ -21824,7 +21847,7 @@
       <c r="AB126" s="4" t="n"/>
       <c r="AC126" s="7" t="n"/>
       <c r="AD126" s="8">
-        <f>IF(A126="","",IF(AC126&lt;&gt;"",AC126,IF(E126="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A126="","",IF(AC126&lt;&gt;"",AC126,IF(E126="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E126,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B126))="SWALE",UPPER(TRIM(AI126))="PIPE"),AND(UPPER(TRIM(B126))="TRENCH",UPPER(TRIM(AI126))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE126" s="8">
@@ -21935,7 +21958,7 @@
       <c r="AB127" s="4" t="n"/>
       <c r="AC127" s="7" t="n"/>
       <c r="AD127" s="8">
-        <f>IF(A127="","",IF(AC127&lt;&gt;"",AC127,IF(E127="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A127="","",IF(AC127&lt;&gt;"",AC127,IF(E127="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E127,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B127))="SWALE",UPPER(TRIM(AI127))="PIPE"),AND(UPPER(TRIM(B127))="TRENCH",UPPER(TRIM(AI127))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE127" s="8">
@@ -22046,7 +22069,7 @@
       <c r="AB128" s="4" t="n"/>
       <c r="AC128" s="7" t="n"/>
       <c r="AD128" s="8">
-        <f>IF(A128="","",IF(AC128&lt;&gt;"",AC128,IF(E128="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A128="","",IF(AC128&lt;&gt;"",AC128,IF(E128="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E128,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B128))="SWALE",UPPER(TRIM(AI128))="PIPE"),AND(UPPER(TRIM(B128))="TRENCH",UPPER(TRIM(AI128))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE128" s="8">
@@ -22157,7 +22180,7 @@
       <c r="AB129" s="4" t="n"/>
       <c r="AC129" s="7" t="n"/>
       <c r="AD129" s="8">
-        <f>IF(A129="","",IF(AC129&lt;&gt;"",AC129,IF(E129="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A129="","",IF(AC129&lt;&gt;"",AC129,IF(E129="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E129,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B129))="SWALE",UPPER(TRIM(AI129))="PIPE"),AND(UPPER(TRIM(B129))="TRENCH",UPPER(TRIM(AI129))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE129" s="8">
@@ -22268,7 +22291,7 @@
       <c r="AB130" s="4" t="n"/>
       <c r="AC130" s="7" t="n"/>
       <c r="AD130" s="8">
-        <f>IF(A130="","",IF(AC130&lt;&gt;"",AC130,IF(E130="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A130="","",IF(AC130&lt;&gt;"",AC130,IF(E130="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E130,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B130))="SWALE",UPPER(TRIM(AI130))="PIPE"),AND(UPPER(TRIM(B130))="TRENCH",UPPER(TRIM(AI130))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE130" s="8">
@@ -22379,7 +22402,7 @@
       <c r="AB131" s="4" t="n"/>
       <c r="AC131" s="7" t="n"/>
       <c r="AD131" s="8">
-        <f>IF(A131="","",IF(AC131&lt;&gt;"",AC131,IF(E131="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A131="","",IF(AC131&lt;&gt;"",AC131,IF(E131="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E131,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B131))="SWALE",UPPER(TRIM(AI131))="PIPE"),AND(UPPER(TRIM(B131))="TRENCH",UPPER(TRIM(AI131))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE131" s="8">
@@ -22490,7 +22513,7 @@
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="7" t="n"/>
       <c r="AD132" s="8">
-        <f>IF(A132="","",IF(AC132&lt;&gt;"",AC132,IF(E132="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A132="","",IF(AC132&lt;&gt;"",AC132,IF(E132="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E132,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B132))="SWALE",UPPER(TRIM(AI132))="PIPE"),AND(UPPER(TRIM(B132))="TRENCH",UPPER(TRIM(AI132))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE132" s="8">
@@ -22601,7 +22624,7 @@
       <c r="AB133" s="4" t="n"/>
       <c r="AC133" s="7" t="n"/>
       <c r="AD133" s="8">
-        <f>IF(A133="","",IF(AC133&lt;&gt;"",AC133,IF(E133="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A133="","",IF(AC133&lt;&gt;"",AC133,IF(E133="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E133,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B133))="SWALE",UPPER(TRIM(AI133))="PIPE"),AND(UPPER(TRIM(B133))="TRENCH",UPPER(TRIM(AI133))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE133" s="8">
@@ -22712,7 +22735,7 @@
       <c r="AB134" s="4" t="n"/>
       <c r="AC134" s="7" t="n"/>
       <c r="AD134" s="8">
-        <f>IF(A134="","",IF(AC134&lt;&gt;"",AC134,IF(E134="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A134="","",IF(AC134&lt;&gt;"",AC134,IF(E134="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E134,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B134))="SWALE",UPPER(TRIM(AI134))="PIPE"),AND(UPPER(TRIM(B134))="TRENCH",UPPER(TRIM(AI134))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE134" s="8">
@@ -22823,7 +22846,7 @@
       <c r="AB135" s="4" t="n"/>
       <c r="AC135" s="7" t="n"/>
       <c r="AD135" s="8">
-        <f>IF(A135="","",IF(AC135&lt;&gt;"",AC135,IF(E135="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A135="","",IF(AC135&lt;&gt;"",AC135,IF(E135="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E135,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B135))="SWALE",UPPER(TRIM(AI135))="PIPE"),AND(UPPER(TRIM(B135))="TRENCH",UPPER(TRIM(AI135))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE135" s="8">
@@ -22934,7 +22957,7 @@
       <c r="AB136" s="4" t="n"/>
       <c r="AC136" s="7" t="n"/>
       <c r="AD136" s="8">
-        <f>IF(A136="","",IF(AC136&lt;&gt;"",AC136,IF(E136="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A136="","",IF(AC136&lt;&gt;"",AC136,IF(E136="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E136,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B136))="SWALE",UPPER(TRIM(AI136))="PIPE"),AND(UPPER(TRIM(B136))="TRENCH",UPPER(TRIM(AI136))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE136" s="8">
@@ -23045,7 +23068,7 @@
       <c r="AB137" s="4" t="n"/>
       <c r="AC137" s="7" t="n"/>
       <c r="AD137" s="8">
-        <f>IF(A137="","",IF(AC137&lt;&gt;"",AC137,IF(E137="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A137="","",IF(AC137&lt;&gt;"",AC137,IF(E137="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E137,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B137))="SWALE",UPPER(TRIM(AI137))="PIPE"),AND(UPPER(TRIM(B137))="TRENCH",UPPER(TRIM(AI137))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE137" s="8">
@@ -23156,7 +23179,7 @@
       <c r="AB138" s="4" t="n"/>
       <c r="AC138" s="7" t="n"/>
       <c r="AD138" s="8">
-        <f>IF(A138="","",IF(AC138&lt;&gt;"",AC138,IF(E138="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A138="","",IF(AC138&lt;&gt;"",AC138,IF(E138="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E138,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B138))="SWALE",UPPER(TRIM(AI138))="PIPE"),AND(UPPER(TRIM(B138))="TRENCH",UPPER(TRIM(AI138))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE138" s="8">
@@ -23267,7 +23290,7 @@
       <c r="AB139" s="4" t="n"/>
       <c r="AC139" s="7" t="n"/>
       <c r="AD139" s="8">
-        <f>IF(A139="","",IF(AC139&lt;&gt;"",AC139,IF(E139="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A139="","",IF(AC139&lt;&gt;"",AC139,IF(E139="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E139,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B139))="SWALE",UPPER(TRIM(AI139))="PIPE"),AND(UPPER(TRIM(B139))="TRENCH",UPPER(TRIM(AI139))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE139" s="8">
@@ -23378,7 +23401,7 @@
       <c r="AB140" s="4" t="n"/>
       <c r="AC140" s="7" t="n"/>
       <c r="AD140" s="8">
-        <f>IF(A140="","",IF(AC140&lt;&gt;"",AC140,IF(E140="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A140="","",IF(AC140&lt;&gt;"",AC140,IF(E140="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E140,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B140))="SWALE",UPPER(TRIM(AI140))="PIPE"),AND(UPPER(TRIM(B140))="TRENCH",UPPER(TRIM(AI140))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE140" s="8">
@@ -23489,7 +23512,7 @@
       <c r="AB141" s="4" t="n"/>
       <c r="AC141" s="7" t="n"/>
       <c r="AD141" s="8">
-        <f>IF(A141="","",IF(AC141&lt;&gt;"",AC141,IF(E141="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A141="","",IF(AC141&lt;&gt;"",AC141,IF(E141="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E141,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B141))="SWALE",UPPER(TRIM(AI141))="PIPE"),AND(UPPER(TRIM(B141))="TRENCH",UPPER(TRIM(AI141))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE141" s="8">
@@ -23600,7 +23623,7 @@
       <c r="AB142" s="4" t="n"/>
       <c r="AC142" s="7" t="n"/>
       <c r="AD142" s="8">
-        <f>IF(A142="","",IF(AC142&lt;&gt;"",AC142,IF(E142="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A142="","",IF(AC142&lt;&gt;"",AC142,IF(E142="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E142,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B142))="SWALE",UPPER(TRIM(AI142))="PIPE"),AND(UPPER(TRIM(B142))="TRENCH",UPPER(TRIM(AI142))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE142" s="8">
@@ -23711,7 +23734,7 @@
       <c r="AB143" s="4" t="n"/>
       <c r="AC143" s="7" t="n"/>
       <c r="AD143" s="8">
-        <f>IF(A143="","",IF(AC143&lt;&gt;"",AC143,IF(E143="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A143="","",IF(AC143&lt;&gt;"",AC143,IF(E143="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E143,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B143))="SWALE",UPPER(TRIM(AI143))="PIPE"),AND(UPPER(TRIM(B143))="TRENCH",UPPER(TRIM(AI143))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE143" s="8">
@@ -23822,7 +23845,7 @@
       <c r="AB144" s="4" t="n"/>
       <c r="AC144" s="7" t="n"/>
       <c r="AD144" s="8">
-        <f>IF(A144="","",IF(AC144&lt;&gt;"",AC144,IF(E144="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A144="","",IF(AC144&lt;&gt;"",AC144,IF(E144="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E144,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B144))="SWALE",UPPER(TRIM(AI144))="PIPE"),AND(UPPER(TRIM(B144))="TRENCH",UPPER(TRIM(AI144))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE144" s="8">
@@ -23933,7 +23956,7 @@
       <c r="AB145" s="4" t="n"/>
       <c r="AC145" s="7" t="n"/>
       <c r="AD145" s="8">
-        <f>IF(A145="","",IF(AC145&lt;&gt;"",AC145,IF(E145="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A145="","",IF(AC145&lt;&gt;"",AC145,IF(E145="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E145,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B145))="SWALE",UPPER(TRIM(AI145))="PIPE"),AND(UPPER(TRIM(B145))="TRENCH",UPPER(TRIM(AI145))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE145" s="8">
@@ -24044,7 +24067,7 @@
       <c r="AB146" s="4" t="n"/>
       <c r="AC146" s="7" t="n"/>
       <c r="AD146" s="8">
-        <f>IF(A146="","",IF(AC146&lt;&gt;"",AC146,IF(E146="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A146="","",IF(AC146&lt;&gt;"",AC146,IF(E146="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E146,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B146))="SWALE",UPPER(TRIM(AI146))="PIPE"),AND(UPPER(TRIM(B146))="TRENCH",UPPER(TRIM(AI146))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE146" s="8">
@@ -24155,7 +24178,7 @@
       <c r="AB147" s="4" t="n"/>
       <c r="AC147" s="7" t="n"/>
       <c r="AD147" s="8">
-        <f>IF(A147="","",IF(AC147&lt;&gt;"",AC147,IF(E147="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A147="","",IF(AC147&lt;&gt;"",AC147,IF(E147="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E147,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B147))="SWALE",UPPER(TRIM(AI147))="PIPE"),AND(UPPER(TRIM(B147))="TRENCH",UPPER(TRIM(AI147))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE147" s="8">
@@ -24266,7 +24289,7 @@
       <c r="AB148" s="4" t="n"/>
       <c r="AC148" s="7" t="n"/>
       <c r="AD148" s="8">
-        <f>IF(A148="","",IF(AC148&lt;&gt;"",AC148,IF(E148="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A148="","",IF(AC148&lt;&gt;"",AC148,IF(E148="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E148,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B148))="SWALE",UPPER(TRIM(AI148))="PIPE"),AND(UPPER(TRIM(B148))="TRENCH",UPPER(TRIM(AI148))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE148" s="8">
@@ -24377,7 +24400,7 @@
       <c r="AB149" s="4" t="n"/>
       <c r="AC149" s="7" t="n"/>
       <c r="AD149" s="8">
-        <f>IF(A149="","",IF(AC149&lt;&gt;"",AC149,IF(E149="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A149="","",IF(AC149&lt;&gt;"",AC149,IF(E149="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E149,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B149))="SWALE",UPPER(TRIM(AI149))="PIPE"),AND(UPPER(TRIM(B149))="TRENCH",UPPER(TRIM(AI149))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE149" s="8">
@@ -24488,7 +24511,7 @@
       <c r="AB150" s="4" t="n"/>
       <c r="AC150" s="7" t="n"/>
       <c r="AD150" s="8">
-        <f>IF(A150="","",IF(AC150&lt;&gt;"",AC150,IF(E150="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A150="","",IF(AC150&lt;&gt;"",AC150,IF(E150="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E150,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B150))="SWALE",UPPER(TRIM(AI150))="PIPE"),AND(UPPER(TRIM(B150))="TRENCH",UPPER(TRIM(AI150))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE150" s="8">
@@ -24599,7 +24622,7 @@
       <c r="AB151" s="4" t="n"/>
       <c r="AC151" s="7" t="n"/>
       <c r="AD151" s="8">
-        <f>IF(A151="","",IF(AC151&lt;&gt;"",AC151,IF(E151="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A151="","",IF(AC151&lt;&gt;"",AC151,IF(E151="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E151,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B151))="SWALE",UPPER(TRIM(AI151))="PIPE"),AND(UPPER(TRIM(B151))="TRENCH",UPPER(TRIM(AI151))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE151" s="8">
@@ -24710,7 +24733,7 @@
       <c r="AB152" s="4" t="n"/>
       <c r="AC152" s="7" t="n"/>
       <c r="AD152" s="8">
-        <f>IF(A152="","",IF(AC152&lt;&gt;"",AC152,IF(E152="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A152="","",IF(AC152&lt;&gt;"",AC152,IF(E152="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E152,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B152))="SWALE",UPPER(TRIM(AI152))="PIPE"),AND(UPPER(TRIM(B152))="TRENCH",UPPER(TRIM(AI152))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE152" s="8">
@@ -24821,7 +24844,7 @@
       <c r="AB153" s="4" t="n"/>
       <c r="AC153" s="7" t="n"/>
       <c r="AD153" s="8">
-        <f>IF(A153="","",IF(AC153&lt;&gt;"",AC153,IF(E153="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A153="","",IF(AC153&lt;&gt;"",AC153,IF(E153="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E153,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B153))="SWALE",UPPER(TRIM(AI153))="PIPE"),AND(UPPER(TRIM(B153))="TRENCH",UPPER(TRIM(AI153))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE153" s="8">
@@ -24932,7 +24955,7 @@
       <c r="AB154" s="4" t="n"/>
       <c r="AC154" s="7" t="n"/>
       <c r="AD154" s="8">
-        <f>IF(A154="","",IF(AC154&lt;&gt;"",AC154,IF(E154="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A154="","",IF(AC154&lt;&gt;"",AC154,IF(E154="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E154,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B154))="SWALE",UPPER(TRIM(AI154))="PIPE"),AND(UPPER(TRIM(B154))="TRENCH",UPPER(TRIM(AI154))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE154" s="8">
@@ -25043,7 +25066,7 @@
       <c r="AB155" s="4" t="n"/>
       <c r="AC155" s="7" t="n"/>
       <c r="AD155" s="8">
-        <f>IF(A155="","",IF(AC155&lt;&gt;"",AC155,IF(E155="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A155="","",IF(AC155&lt;&gt;"",AC155,IF(E155="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E155,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B155))="SWALE",UPPER(TRIM(AI155))="PIPE"),AND(UPPER(TRIM(B155))="TRENCH",UPPER(TRIM(AI155))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE155" s="8">
@@ -25154,7 +25177,7 @@
       <c r="AB156" s="4" t="n"/>
       <c r="AC156" s="7" t="n"/>
       <c r="AD156" s="8">
-        <f>IF(A156="","",IF(AC156&lt;&gt;"",AC156,IF(E156="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A156="","",IF(AC156&lt;&gt;"",AC156,IF(E156="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E156,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B156))="SWALE",UPPER(TRIM(AI156))="PIPE"),AND(UPPER(TRIM(B156))="TRENCH",UPPER(TRIM(AI156))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE156" s="8">
@@ -25265,7 +25288,7 @@
       <c r="AB157" s="4" t="n"/>
       <c r="AC157" s="7" t="n"/>
       <c r="AD157" s="8">
-        <f>IF(A157="","",IF(AC157&lt;&gt;"",AC157,IF(E157="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A157="","",IF(AC157&lt;&gt;"",AC157,IF(E157="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E157,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B157))="SWALE",UPPER(TRIM(AI157))="PIPE"),AND(UPPER(TRIM(B157))="TRENCH",UPPER(TRIM(AI157))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE157" s="8">
@@ -25376,7 +25399,7 @@
       <c r="AB158" s="4" t="n"/>
       <c r="AC158" s="7" t="n"/>
       <c r="AD158" s="8">
-        <f>IF(A158="","",IF(AC158&lt;&gt;"",AC158,IF(E158="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A158="","",IF(AC158&lt;&gt;"",AC158,IF(E158="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E158,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B158))="SWALE",UPPER(TRIM(AI158))="PIPE"),AND(UPPER(TRIM(B158))="TRENCH",UPPER(TRIM(AI158))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE158" s="8">
@@ -25487,7 +25510,7 @@
       <c r="AB159" s="4" t="n"/>
       <c r="AC159" s="7" t="n"/>
       <c r="AD159" s="8">
-        <f>IF(A159="","",IF(AC159&lt;&gt;"",AC159,IF(E159="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A159="","",IF(AC159&lt;&gt;"",AC159,IF(E159="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E159,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B159))="SWALE",UPPER(TRIM(AI159))="PIPE"),AND(UPPER(TRIM(B159))="TRENCH",UPPER(TRIM(AI159))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE159" s="8">
@@ -25598,7 +25621,7 @@
       <c r="AB160" s="4" t="n"/>
       <c r="AC160" s="7" t="n"/>
       <c r="AD160" s="8">
-        <f>IF(A160="","",IF(AC160&lt;&gt;"",AC160,IF(E160="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A160="","",IF(AC160&lt;&gt;"",AC160,IF(E160="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E160,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B160))="SWALE",UPPER(TRIM(AI160))="PIPE"),AND(UPPER(TRIM(B160))="TRENCH",UPPER(TRIM(AI160))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE160" s="8">
@@ -25709,7 +25732,7 @@
       <c r="AB161" s="4" t="n"/>
       <c r="AC161" s="7" t="n"/>
       <c r="AD161" s="8">
-        <f>IF(A161="","",IF(AC161&lt;&gt;"",AC161,IF(E161="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A161="","",IF(AC161&lt;&gt;"",AC161,IF(E161="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E161,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B161))="SWALE",UPPER(TRIM(AI161))="PIPE"),AND(UPPER(TRIM(B161))="TRENCH",UPPER(TRIM(AI161))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE161" s="8">
@@ -25820,7 +25843,7 @@
       <c r="AB162" s="4" t="n"/>
       <c r="AC162" s="7" t="n"/>
       <c r="AD162" s="8">
-        <f>IF(A162="","",IF(AC162&lt;&gt;"",AC162,IF(E162="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A162="","",IF(AC162&lt;&gt;"",AC162,IF(E162="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E162,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B162))="SWALE",UPPER(TRIM(AI162))="PIPE"),AND(UPPER(TRIM(B162))="TRENCH",UPPER(TRIM(AI162))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE162" s="8">
@@ -25931,7 +25954,7 @@
       <c r="AB163" s="4" t="n"/>
       <c r="AC163" s="7" t="n"/>
       <c r="AD163" s="8">
-        <f>IF(A163="","",IF(AC163&lt;&gt;"",AC163,IF(E163="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A163="","",IF(AC163&lt;&gt;"",AC163,IF(E163="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E163,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B163))="SWALE",UPPER(TRIM(AI163))="PIPE"),AND(UPPER(TRIM(B163))="TRENCH",UPPER(TRIM(AI163))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE163" s="8">
@@ -26042,7 +26065,7 @@
       <c r="AB164" s="4" t="n"/>
       <c r="AC164" s="7" t="n"/>
       <c r="AD164" s="8">
-        <f>IF(A164="","",IF(AC164&lt;&gt;"",AC164,IF(E164="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A164="","",IF(AC164&lt;&gt;"",AC164,IF(E164="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E164,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B164))="SWALE",UPPER(TRIM(AI164))="PIPE"),AND(UPPER(TRIM(B164))="TRENCH",UPPER(TRIM(AI164))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE164" s="8">
@@ -26153,7 +26176,7 @@
       <c r="AB165" s="4" t="n"/>
       <c r="AC165" s="7" t="n"/>
       <c r="AD165" s="8">
-        <f>IF(A165="","",IF(AC165&lt;&gt;"",AC165,IF(E165="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A165="","",IF(AC165&lt;&gt;"",AC165,IF(E165="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E165,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B165))="SWALE",UPPER(TRIM(AI165))="PIPE"),AND(UPPER(TRIM(B165))="TRENCH",UPPER(TRIM(AI165))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE165" s="8">
@@ -26264,7 +26287,7 @@
       <c r="AB166" s="4" t="n"/>
       <c r="AC166" s="7" t="n"/>
       <c r="AD166" s="8">
-        <f>IF(A166="","",IF(AC166&lt;&gt;"",AC166,IF(E166="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A166="","",IF(AC166&lt;&gt;"",AC166,IF(E166="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E166,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B166))="SWALE",UPPER(TRIM(AI166))="PIPE"),AND(UPPER(TRIM(B166))="TRENCH",UPPER(TRIM(AI166))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE166" s="8">
@@ -26375,7 +26398,7 @@
       <c r="AB167" s="4" t="n"/>
       <c r="AC167" s="7" t="n"/>
       <c r="AD167" s="8">
-        <f>IF(A167="","",IF(AC167&lt;&gt;"",AC167,IF(E167="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A167="","",IF(AC167&lt;&gt;"",AC167,IF(E167="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E167,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B167))="SWALE",UPPER(TRIM(AI167))="PIPE"),AND(UPPER(TRIM(B167))="TRENCH",UPPER(TRIM(AI167))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE167" s="8">
@@ -26486,7 +26509,7 @@
       <c r="AB168" s="4" t="n"/>
       <c r="AC168" s="7" t="n"/>
       <c r="AD168" s="8">
-        <f>IF(A168="","",IF(AC168&lt;&gt;"",AC168,IF(E168="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A168="","",IF(AC168&lt;&gt;"",AC168,IF(E168="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E168,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B168))="SWALE",UPPER(TRIM(AI168))="PIPE"),AND(UPPER(TRIM(B168))="TRENCH",UPPER(TRIM(AI168))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE168" s="8">
@@ -26597,7 +26620,7 @@
       <c r="AB169" s="4" t="n"/>
       <c r="AC169" s="7" t="n"/>
       <c r="AD169" s="8">
-        <f>IF(A169="","",IF(AC169&lt;&gt;"",AC169,IF(E169="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A169="","",IF(AC169&lt;&gt;"",AC169,IF(E169="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E169,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B169))="SWALE",UPPER(TRIM(AI169))="PIPE"),AND(UPPER(TRIM(B169))="TRENCH",UPPER(TRIM(AI169))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE169" s="8">
@@ -26708,7 +26731,7 @@
       <c r="AB170" s="4" t="n"/>
       <c r="AC170" s="7" t="n"/>
       <c r="AD170" s="8">
-        <f>IF(A170="","",IF(AC170&lt;&gt;"",AC170,IF(E170="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A170="","",IF(AC170&lt;&gt;"",AC170,IF(E170="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E170,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B170))="SWALE",UPPER(TRIM(AI170))="PIPE"),AND(UPPER(TRIM(B170))="TRENCH",UPPER(TRIM(AI170))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE170" s="8">
@@ -26819,7 +26842,7 @@
       <c r="AB171" s="4" t="n"/>
       <c r="AC171" s="7" t="n"/>
       <c r="AD171" s="8">
-        <f>IF(A171="","",IF(AC171&lt;&gt;"",AC171,IF(E171="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A171="","",IF(AC171&lt;&gt;"",AC171,IF(E171="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E171,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B171))="SWALE",UPPER(TRIM(AI171))="PIPE"),AND(UPPER(TRIM(B171))="TRENCH",UPPER(TRIM(AI171))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE171" s="8">
@@ -26930,7 +26953,7 @@
       <c r="AB172" s="4" t="n"/>
       <c r="AC172" s="7" t="n"/>
       <c r="AD172" s="8">
-        <f>IF(A172="","",IF(AC172&lt;&gt;"",AC172,IF(E172="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A172="","",IF(AC172&lt;&gt;"",AC172,IF(E172="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E172,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B172))="SWALE",UPPER(TRIM(AI172))="PIPE"),AND(UPPER(TRIM(B172))="TRENCH",UPPER(TRIM(AI172))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE172" s="8">
@@ -27041,7 +27064,7 @@
       <c r="AB173" s="4" t="n"/>
       <c r="AC173" s="7" t="n"/>
       <c r="AD173" s="8">
-        <f>IF(A173="","",IF(AC173&lt;&gt;"",AC173,IF(E173="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A173="","",IF(AC173&lt;&gt;"",AC173,IF(E173="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E173,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B173))="SWALE",UPPER(TRIM(AI173))="PIPE"),AND(UPPER(TRIM(B173))="TRENCH",UPPER(TRIM(AI173))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE173" s="8">
@@ -27152,7 +27175,7 @@
       <c r="AB174" s="4" t="n"/>
       <c r="AC174" s="7" t="n"/>
       <c r="AD174" s="8">
-        <f>IF(A174="","",IF(AC174&lt;&gt;"",AC174,IF(E174="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A174="","",IF(AC174&lt;&gt;"",AC174,IF(E174="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E174,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B174))="SWALE",UPPER(TRIM(AI174))="PIPE"),AND(UPPER(TRIM(B174))="TRENCH",UPPER(TRIM(AI174))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE174" s="8">
@@ -27263,7 +27286,7 @@
       <c r="AB175" s="4" t="n"/>
       <c r="AC175" s="7" t="n"/>
       <c r="AD175" s="8">
-        <f>IF(A175="","",IF(AC175&lt;&gt;"",AC175,IF(E175="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A175="","",IF(AC175&lt;&gt;"",AC175,IF(E175="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E175,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B175))="SWALE",UPPER(TRIM(AI175))="PIPE"),AND(UPPER(TRIM(B175))="TRENCH",UPPER(TRIM(AI175))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE175" s="8">
@@ -27374,7 +27397,7 @@
       <c r="AB176" s="4" t="n"/>
       <c r="AC176" s="7" t="n"/>
       <c r="AD176" s="8">
-        <f>IF(A176="","",IF(AC176&lt;&gt;"",AC176,IF(E176="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A176="","",IF(AC176&lt;&gt;"",AC176,IF(E176="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E176,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B176))="SWALE",UPPER(TRIM(AI176))="PIPE"),AND(UPPER(TRIM(B176))="TRENCH",UPPER(TRIM(AI176))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE176" s="8">
@@ -27485,7 +27508,7 @@
       <c r="AB177" s="4" t="n"/>
       <c r="AC177" s="7" t="n"/>
       <c r="AD177" s="8">
-        <f>IF(A177="","",IF(AC177&lt;&gt;"",AC177,IF(E177="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A177="","",IF(AC177&lt;&gt;"",AC177,IF(E177="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E177,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B177))="SWALE",UPPER(TRIM(AI177))="PIPE"),AND(UPPER(TRIM(B177))="TRENCH",UPPER(TRIM(AI177))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE177" s="8">
@@ -27596,7 +27619,7 @@
       <c r="AB178" s="4" t="n"/>
       <c r="AC178" s="7" t="n"/>
       <c r="AD178" s="8">
-        <f>IF(A178="","",IF(AC178&lt;&gt;"",AC178,IF(E178="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A178="","",IF(AC178&lt;&gt;"",AC178,IF(E178="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E178,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B178))="SWALE",UPPER(TRIM(AI178))="PIPE"),AND(UPPER(TRIM(B178))="TRENCH",UPPER(TRIM(AI178))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE178" s="8">
@@ -27707,7 +27730,7 @@
       <c r="AB179" s="4" t="n"/>
       <c r="AC179" s="7" t="n"/>
       <c r="AD179" s="8">
-        <f>IF(A179="","",IF(AC179&lt;&gt;"",AC179,IF(E179="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A179="","",IF(AC179&lt;&gt;"",AC179,IF(E179="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E179,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B179))="SWALE",UPPER(TRIM(AI179))="PIPE"),AND(UPPER(TRIM(B179))="TRENCH",UPPER(TRIM(AI179))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE179" s="8">
@@ -27818,7 +27841,7 @@
       <c r="AB180" s="4" t="n"/>
       <c r="AC180" s="7" t="n"/>
       <c r="AD180" s="8">
-        <f>IF(A180="","",IF(AC180&lt;&gt;"",AC180,IF(E180="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A180="","",IF(AC180&lt;&gt;"",AC180,IF(E180="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E180,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B180))="SWALE",UPPER(TRIM(AI180))="PIPE"),AND(UPPER(TRIM(B180))="TRENCH",UPPER(TRIM(AI180))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE180" s="8">
@@ -27929,7 +27952,7 @@
       <c r="AB181" s="4" t="n"/>
       <c r="AC181" s="7" t="n"/>
       <c r="AD181" s="8">
-        <f>IF(A181="","",IF(AC181&lt;&gt;"",AC181,IF(E181="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A181="","",IF(AC181&lt;&gt;"",AC181,IF(E181="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E181,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B181))="SWALE",UPPER(TRIM(AI181))="PIPE"),AND(UPPER(TRIM(B181))="TRENCH",UPPER(TRIM(AI181))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE181" s="8">
@@ -28040,7 +28063,7 @@
       <c r="AB182" s="4" t="n"/>
       <c r="AC182" s="7" t="n"/>
       <c r="AD182" s="8">
-        <f>IF(A182="","",IF(AC182&lt;&gt;"",AC182,IF(E182="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A182="","",IF(AC182&lt;&gt;"",AC182,IF(E182="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E182,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B182))="SWALE",UPPER(TRIM(AI182))="PIPE"),AND(UPPER(TRIM(B182))="TRENCH",UPPER(TRIM(AI182))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE182" s="8">
@@ -28151,7 +28174,7 @@
       <c r="AB183" s="4" t="n"/>
       <c r="AC183" s="7" t="n"/>
       <c r="AD183" s="8">
-        <f>IF(A183="","",IF(AC183&lt;&gt;"",AC183,IF(E183="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A183="","",IF(AC183&lt;&gt;"",AC183,IF(E183="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E183,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B183))="SWALE",UPPER(TRIM(AI183))="PIPE"),AND(UPPER(TRIM(B183))="TRENCH",UPPER(TRIM(AI183))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE183" s="8">
@@ -28262,7 +28285,7 @@
       <c r="AB184" s="4" t="n"/>
       <c r="AC184" s="7" t="n"/>
       <c r="AD184" s="8">
-        <f>IF(A184="","",IF(AC184&lt;&gt;"",AC184,IF(E184="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A184="","",IF(AC184&lt;&gt;"",AC184,IF(E184="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E184,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B184))="SWALE",UPPER(TRIM(AI184))="PIPE"),AND(UPPER(TRIM(B184))="TRENCH",UPPER(TRIM(AI184))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE184" s="8">
@@ -28373,7 +28396,7 @@
       <c r="AB185" s="4" t="n"/>
       <c r="AC185" s="7" t="n"/>
       <c r="AD185" s="8">
-        <f>IF(A185="","",IF(AC185&lt;&gt;"",AC185,IF(E185="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A185="","",IF(AC185&lt;&gt;"",AC185,IF(E185="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E185,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B185))="SWALE",UPPER(TRIM(AI185))="PIPE"),AND(UPPER(TRIM(B185))="TRENCH",UPPER(TRIM(AI185))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE185" s="8">
@@ -28484,7 +28507,7 @@
       <c r="AB186" s="4" t="n"/>
       <c r="AC186" s="7" t="n"/>
       <c r="AD186" s="8">
-        <f>IF(A186="","",IF(AC186&lt;&gt;"",AC186,IF(E186="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A186="","",IF(AC186&lt;&gt;"",AC186,IF(E186="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E186,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B186))="SWALE",UPPER(TRIM(AI186))="PIPE"),AND(UPPER(TRIM(B186))="TRENCH",UPPER(TRIM(AI186))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE186" s="8">
@@ -28595,7 +28618,7 @@
       <c r="AB187" s="4" t="n"/>
       <c r="AC187" s="7" t="n"/>
       <c r="AD187" s="8">
-        <f>IF(A187="","",IF(AC187&lt;&gt;"",AC187,IF(E187="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A187="","",IF(AC187&lt;&gt;"",AC187,IF(E187="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E187,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B187))="SWALE",UPPER(TRIM(AI187))="PIPE"),AND(UPPER(TRIM(B187))="TRENCH",UPPER(TRIM(AI187))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE187" s="8">
@@ -28706,7 +28729,7 @@
       <c r="AB188" s="4" t="n"/>
       <c r="AC188" s="7" t="n"/>
       <c r="AD188" s="8">
-        <f>IF(A188="","",IF(AC188&lt;&gt;"",AC188,IF(E188="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A188="","",IF(AC188&lt;&gt;"",AC188,IF(E188="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E188,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B188))="SWALE",UPPER(TRIM(AI188))="PIPE"),AND(UPPER(TRIM(B188))="TRENCH",UPPER(TRIM(AI188))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE188" s="8">
@@ -28817,7 +28840,7 @@
       <c r="AB189" s="4" t="n"/>
       <c r="AC189" s="7" t="n"/>
       <c r="AD189" s="8">
-        <f>IF(A189="","",IF(AC189&lt;&gt;"",AC189,IF(E189="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A189="","",IF(AC189&lt;&gt;"",AC189,IF(E189="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E189,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B189))="SWALE",UPPER(TRIM(AI189))="PIPE"),AND(UPPER(TRIM(B189))="TRENCH",UPPER(TRIM(AI189))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE189" s="8">
@@ -28928,7 +28951,7 @@
       <c r="AB190" s="4" t="n"/>
       <c r="AC190" s="7" t="n"/>
       <c r="AD190" s="8">
-        <f>IF(A190="","",IF(AC190&lt;&gt;"",AC190,IF(E190="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A190="","",IF(AC190&lt;&gt;"",AC190,IF(E190="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E190,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B190))="SWALE",UPPER(TRIM(AI190))="PIPE"),AND(UPPER(TRIM(B190))="TRENCH",UPPER(TRIM(AI190))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE190" s="8">
@@ -29039,7 +29062,7 @@
       <c r="AB191" s="4" t="n"/>
       <c r="AC191" s="7" t="n"/>
       <c r="AD191" s="8">
-        <f>IF(A191="","",IF(AC191&lt;&gt;"",AC191,IF(E191="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A191="","",IF(AC191&lt;&gt;"",AC191,IF(E191="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E191,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B191))="SWALE",UPPER(TRIM(AI191))="PIPE"),AND(UPPER(TRIM(B191))="TRENCH",UPPER(TRIM(AI191))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE191" s="8">
@@ -29150,7 +29173,7 @@
       <c r="AB192" s="4" t="n"/>
       <c r="AC192" s="7" t="n"/>
       <c r="AD192" s="8">
-        <f>IF(A192="","",IF(AC192&lt;&gt;"",AC192,IF(E192="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A192="","",IF(AC192&lt;&gt;"",AC192,IF(E192="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E192,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B192))="SWALE",UPPER(TRIM(AI192))="PIPE"),AND(UPPER(TRIM(B192))="TRENCH",UPPER(TRIM(AI192))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE192" s="8">
@@ -29261,7 +29284,7 @@
       <c r="AB193" s="4" t="n"/>
       <c r="AC193" s="7" t="n"/>
       <c r="AD193" s="8">
-        <f>IF(A193="","",IF(AC193&lt;&gt;"",AC193,IF(E193="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A193="","",IF(AC193&lt;&gt;"",AC193,IF(E193="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E193,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B193))="SWALE",UPPER(TRIM(AI193))="PIPE"),AND(UPPER(TRIM(B193))="TRENCH",UPPER(TRIM(AI193))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE193" s="8">
@@ -29372,7 +29395,7 @@
       <c r="AB194" s="4" t="n"/>
       <c r="AC194" s="7" t="n"/>
       <c r="AD194" s="8">
-        <f>IF(A194="","",IF(AC194&lt;&gt;"",AC194,IF(E194="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A194="","",IF(AC194&lt;&gt;"",AC194,IF(E194="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E194,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B194))="SWALE",UPPER(TRIM(AI194))="PIPE"),AND(UPPER(TRIM(B194))="TRENCH",UPPER(TRIM(AI194))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE194" s="8">
@@ -29483,7 +29506,7 @@
       <c r="AB195" s="4" t="n"/>
       <c r="AC195" s="7" t="n"/>
       <c r="AD195" s="8">
-        <f>IF(A195="","",IF(AC195&lt;&gt;"",AC195,IF(E195="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A195="","",IF(AC195&lt;&gt;"",AC195,IF(E195="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E195,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B195))="SWALE",UPPER(TRIM(AI195))="PIPE"),AND(UPPER(TRIM(B195))="TRENCH",UPPER(TRIM(AI195))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE195" s="8">
@@ -29594,7 +29617,7 @@
       <c r="AB196" s="4" t="n"/>
       <c r="AC196" s="7" t="n"/>
       <c r="AD196" s="8">
-        <f>IF(A196="","",IF(AC196&lt;&gt;"",AC196,IF(E196="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A196="","",IF(AC196&lt;&gt;"",AC196,IF(E196="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E196,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B196))="SWALE",UPPER(TRIM(AI196))="PIPE"),AND(UPPER(TRIM(B196))="TRENCH",UPPER(TRIM(AI196))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE196" s="8">
@@ -29705,7 +29728,7 @@
       <c r="AB197" s="4" t="n"/>
       <c r="AC197" s="7" t="n"/>
       <c r="AD197" s="8">
-        <f>IF(A197="","",IF(AC197&lt;&gt;"",AC197,IF(E197="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A197="","",IF(AC197&lt;&gt;"",AC197,IF(E197="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E197,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B197))="SWALE",UPPER(TRIM(AI197))="PIPE"),AND(UPPER(TRIM(B197))="TRENCH",UPPER(TRIM(AI197))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE197" s="8">
@@ -29816,7 +29839,7 @@
       <c r="AB198" s="4" t="n"/>
       <c r="AC198" s="7" t="n"/>
       <c r="AD198" s="8">
-        <f>IF(A198="","",IF(AC198&lt;&gt;"",AC198,IF(E198="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A198="","",IF(AC198&lt;&gt;"",AC198,IF(E198="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E198,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B198))="SWALE",UPPER(TRIM(AI198))="PIPE"),AND(UPPER(TRIM(B198))="TRENCH",UPPER(TRIM(AI198))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE198" s="8">
@@ -29927,7 +29950,7 @@
       <c r="AB199" s="4" t="n"/>
       <c r="AC199" s="7" t="n"/>
       <c r="AD199" s="8">
-        <f>IF(A199="","",IF(AC199&lt;&gt;"",AC199,IF(E199="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A199="","",IF(AC199&lt;&gt;"",AC199,IF(E199="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E199,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B199))="SWALE",UPPER(TRIM(AI199))="PIPE"),AND(UPPER(TRIM(B199))="TRENCH",UPPER(TRIM(AI199))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE199" s="8">
@@ -30038,7 +30061,7 @@
       <c r="AB200" s="4" t="n"/>
       <c r="AC200" s="7" t="n"/>
       <c r="AD200" s="8">
-        <f>IF(A200="","",IF(AC200&lt;&gt;"",AC200,IF(E200="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A200="","",IF(AC200&lt;&gt;"",AC200,IF(E200="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E200,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B200))="SWALE",UPPER(TRIM(AI200))="PIPE"),AND(UPPER(TRIM(B200))="TRENCH",UPPER(TRIM(AI200))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE200" s="8">
@@ -30149,7 +30172,7 @@
       <c r="AB201" s="4" t="n"/>
       <c r="AC201" s="7" t="n"/>
       <c r="AD201" s="8">
-        <f>IF(A201="","",IF(AC201&lt;&gt;"",AC201,IF(E201="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A201="","",IF(AC201&lt;&gt;"",AC201,IF(E201="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E201,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B201))="SWALE",UPPER(TRIM(AI201))="PIPE"),AND(UPPER(TRIM(B201))="TRENCH",UPPER(TRIM(AI201))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE201" s="8">
@@ -30260,7 +30283,7 @@
       <c r="AB202" s="4" t="n"/>
       <c r="AC202" s="7" t="n"/>
       <c r="AD202" s="8">
-        <f>IF(A202="","",IF(AC202&lt;&gt;"",AC202,IF(E202="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A202="","",IF(AC202&lt;&gt;"",AC202,IF(E202="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E202,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B202))="SWALE",UPPER(TRIM(AI202))="PIPE"),AND(UPPER(TRIM(B202))="TRENCH",UPPER(TRIM(AI202))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE202" s="8">
@@ -30371,7 +30394,7 @@
       <c r="AB203" s="4" t="n"/>
       <c r="AC203" s="7" t="n"/>
       <c r="AD203" s="8">
-        <f>IF(A203="","",IF(AC203&lt;&gt;"",AC203,IF(E203="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A203="","",IF(AC203&lt;&gt;"",AC203,IF(E203="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E203,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B203))="SWALE",UPPER(TRIM(AI203))="PIPE"),AND(UPPER(TRIM(B203))="TRENCH",UPPER(TRIM(AI203))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE203" s="8">
@@ -30482,7 +30505,7 @@
       <c r="AB204" s="4" t="n"/>
       <c r="AC204" s="7" t="n"/>
       <c r="AD204" s="8">
-        <f>IF(A204="","",IF(AC204&lt;&gt;"",AC204,IF(E204="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0)),""))))</f>
+        <f>IF(A204="","",IF(AC204&lt;&gt;"",AC204,IF(E204="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E204,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B204))="SWALE",UPPER(TRIM(AI204))="PIPE"),AND(UPPER(TRIM(B204))="TRENCH",UPPER(TRIM(AI204))="PIPE")),Inputs!$B$57,0),""))))</f>
         <v/>
       </c>
       <c r="AE204" s="8">

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="[&lt;1]0.000;0.00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -110,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -133,6 +136,7 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1216,7 +1220,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4) Exutoire final au bassin de retention via J-BASSIN-IN -&gt; BASSIN-RET.</t>
+          <t>4) Deux entrees au bassin: EST (J-BASSIN-IN) et OUEST (J-BASSIN-OUEST) vers BASSIN-RET.</t>
         </is>
       </c>
     </row>
@@ -1366,18 +1370,19 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>South basin corridor width x length (m)</t>
+          <t>West connector to basin inlet (m)</t>
         </is>
       </c>
       <c r="B14" s="9">
-        <f>Inputs!B34&amp;" x "&amp;Inputs!B35</f>
+        <f>Inputs!B53</f>
         <v/>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Between building and pedestrian road</t>
-        </is>
-      </c>
+          <t>Measured corner link J-OUEST-AVAL -&gt; J-BASSIN-OUEST</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>E04</t>
@@ -1399,54 +1404,51 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Basin target depth (m)</t>
+          <t>Retention basin corridor width x length (m)</t>
         </is>
       </c>
       <c r="B15" s="9">
-        <f>Inputs!B36</f>
+        <f>Inputs!B34&amp;" x "&amp;Inputs!B35</f>
         <v/>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Adjust with topo survey</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="F15" s="4">
-        <f>IFERROR(INDEX(Elements_hybrides!$B$4:$B$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="13">
-        <f>IFERROR(INDEX(Elements_hybrides!$Q$4:$Q$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="4">
-        <f>IFERROR(INDEX(Elements_hybrides!$AA$4:$AA$204,MATCH(E15,Elements_hybrides!$A$4:$A$204,0)),"")</f>
-        <v/>
+          <t>Storage geometry at node BASSIN-RET (not an E04 reach).</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>BASSIN-RET (node)</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Max cover near west utilities (m)</t>
+          <t>East inlet pipe length to basin (m)</t>
         </is>
       </c>
       <c r="B16" s="9">
-        <f>Inputs!B39</f>
+        <f>IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH("E07",Elements_hybrides!$A$4:$A$204,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Conservative limit</t>
-        </is>
-      </c>
+          <t>J-BASSIN-IN -&gt; BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="F16" s="4">
@@ -1463,9 +1465,24 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>West inlet pipe length to basin (m)</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH("E08",Elements_hybrides!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>J-BASSIN-OUEST -&gt; BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="F17" s="4">

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -833,6 +833,27 @@
       <c r="A44" t="inlineStr">
         <is>
           <t>Cela represente un raccord via regard/caniveau: fond noue plus haut que l'invert de conduite aval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tc automatise dans Zones_tributaires: Tc_used = (Tc base override L ou Default_tc_min) + temps transit element route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Temps transit = Longueur element route / (Inputs!B59 * 60).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Inputs!B59 est une vitesse adoptee (pas la vitesse calculee hydraulique) pour eviter references circulaires.</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2820,6 +2841,26 @@
       <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Coefficient ruissellement pour surfaces pavees (pave-uni/pavage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Tc_travel_velocity_mps</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Vitesse adoptee pour calcul temps de transit dans element route (evite references circulaires).</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:N204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2851,6 +2892,9 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2923,6 +2967,21 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Tc_base_override_min</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Travel_time_routed_element_min</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Tc_auto_used_min</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2948,8 +3007,9 @@
         <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>12</v>
+      <c r="G4" s="8">
+        <f>IF(A4="","",N4)</f>
+        <v/>
       </c>
       <c r="H4" s="8">
         <f>IF(A4="","",Inputs!$B$3/((IF(G4="",Inputs!$B$14,G4)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -2968,6 +3028,17 @@
         <is>
           <t>Routage provisoire vers entree EST; scinder est/ouest plus tard si detail aval disponible.</t>
         </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="9">
+        <f>IF(A4="","",IF(OR(J4="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J4,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N4" s="9">
+        <f>IF(A4="","",IF(L4="",Inputs!$B$14,L4)+M4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -2994,8 +3065,9 @@
         <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>8</v>
+      <c r="G5" s="8">
+        <f>IF(A5="","",N5)</f>
+        <v/>
       </c>
       <c r="H5" s="8">
         <f>IF(A5="","",Inputs!$B$3/((IF(G5="",Inputs!$B$14,G5)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3014,6 +3086,17 @@
         <is>
           <t>Pente vers bande est</t>
         </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="9">
+        <f>IF(A5="","",IF(OR(J5="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J5,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="9">
+        <f>IF(A5="","",IF(L5="",Inputs!$B$14,L5)+M5)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3040,8 +3123,9 @@
         <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>10</v>
+      <c r="G6" s="8">
+        <f>IF(A6="","",N6)</f>
+        <v/>
       </c>
       <c r="H6" s="8">
         <f>IF(A6="","",Inputs!$B$3/((IF(G6="",Inputs!$B$14,G6)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3060,6 +3144,17 @@
         <is>
           <t>Vers underdrain est</t>
         </is>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="9">
+        <f>IF(A6="","",IF(OR(J6="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J6,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(A6="","",IF(L6="",Inputs!$B$14,L6)+M6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3086,8 +3181,9 @@
         <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>10</v>
+      <c r="G7" s="8">
+        <f>IF(A7="","",N7)</f>
+        <v/>
       </c>
       <c r="H7" s="8">
         <f>IF(A7="","",Inputs!$B$3/((IF(G7="",Inputs!$B$14,G7)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3106,6 +3202,17 @@
         <is>
           <t>Image: zone verte amont gauche.</t>
         </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(A7="","",IF(OR(J7="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J7,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(A7="","",IF(L7="",Inputs!$B$14,L7)+M7)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -3132,8 +3239,9 @@
         <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>10</v>
+      <c r="G8" s="8">
+        <f>IF(A8="","",N8)</f>
+        <v/>
       </c>
       <c r="H8" s="8">
         <f>IF(A8="","",Inputs!$B$3/((IF(G8="",Inputs!$B$14,G8)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3152,6 +3260,17 @@
         <is>
           <t>Surface pavage (pas tresfond).</t>
         </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="9">
+        <f>IF(A8="","",IF(OR(J8="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J8,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(A8="","",IF(L8="",Inputs!$B$14,L8)+M8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3178,8 +3297,9 @@
         <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>10</v>
+      <c r="G9" s="8">
+        <f>IF(A9="","",N9)</f>
+        <v/>
       </c>
       <c r="H9" s="8">
         <f>IF(A9="","",Inputs!$B$3/((IF(G9="",Inputs!$B$14,G9)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3198,6 +3318,17 @@
         <is>
           <t>Image: bande verte milieu ouest.</t>
         </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(A9="","",IF(OR(J9="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J9,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(A9="","",IF(L9="",Inputs!$B$14,L9)+M9)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3224,8 +3355,9 @@
         <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>9</v>
+      <c r="G10" s="8">
+        <f>IF(A10="","",N10)</f>
+        <v/>
       </c>
       <c r="H10" s="8">
         <f>IF(A10="","",Inputs!$B$3/((IF(G10="",Inputs!$B$14,G10)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3244,6 +3376,17 @@
         <is>
           <t>Surface pavage principal (pave-uni), entre Z05 et Z06.</t>
         </is>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="9">
+        <f>IF(A10="","",IF(OR(J10="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J10,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(A10="","",IF(L10="",Inputs!$B$14,L10)+M10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3270,8 +3413,9 @@
         <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>10</v>
+      <c r="G11" s="8">
+        <f>IF(A11="","",N11)</f>
+        <v/>
       </c>
       <c r="H11" s="8">
         <f>IF(A11="","",Inputs!$B$3/((IF(G11="",Inputs!$B$14,G11)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3290,6 +3434,17 @@
         <is>
           <t>Image: zone verte pres J-OUEST-AVAL.</t>
         </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="9">
+        <f>IF(A11="","",IF(OR(J11="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J11,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="9">
+        <f>IF(A11="","",IF(L11="",Inputs!$B$14,L11)+M11)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3316,8 +3471,9 @@
         <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>10</v>
+      <c r="G12" s="8">
+        <f>IF(A12="","",N12)</f>
+        <v/>
       </c>
       <c r="H12" s="8">
         <f>IF(A12="","",Inputs!$B$3/((IF(G12="",Inputs!$B$14,G12)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3332,6 +3488,17 @@
         <is>
           <t>Non contributive par defaut (Inputs!B52=NO). Mettre YES pour sensibilité si requis.</t>
         </is>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="9">
+        <f>IF(A12="","",IF(OR(J12="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J12,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(A12="","",IF(L12="",Inputs!$B$14,L12)+M12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3358,8 +3525,9 @@
         <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>8</v>
+      <c r="G13" s="8">
+        <f>IF(A13="","",N13)</f>
+        <v/>
       </c>
       <c r="H13" s="8">
         <f>IF(A13="","",Inputs!$B$3/((IF(G13="",Inputs!$B$14,G13)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3378,6 +3546,17 @@
         <is>
           <t>Surface pavage locale (pas tresfond), routage vers entree EST.</t>
         </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" s="9">
+        <f>IF(A13="","",IF(OR(J13="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J13,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="9">
+        <f>IF(A13="","",IF(L13="",Inputs!$B$14,L13)+M13)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3404,8 +3583,9 @@
         <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>10</v>
+      <c r="G14" s="8">
+        <f>IF(A14="","",N14)</f>
+        <v/>
       </c>
       <c r="H14" s="8">
         <f>IF(A14="","",Inputs!$B$3/((IF(G14="",Inputs!$B$14,G14)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3424,6 +3604,17 @@
         <is>
           <t>Vers noue sud</t>
         </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" s="9">
+        <f>IF(A14="","",IF(OR(J14="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J14,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(A14="","",IF(L14="",Inputs!$B$14,L14)+M14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3450,8 +3641,9 @@
         <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>8</v>
+      <c r="G15" s="8">
+        <f>IF(A15="","",N15)</f>
+        <v/>
       </c>
       <c r="H15" s="8">
         <f>IF(A15="","",Inputs!$B$3/((IF(G15="",Inputs!$B$14,G15)+Inputs!$B$4)^Inputs!$B$5))</f>
@@ -3470,6 +3662,17 @@
         <is>
           <t>Surface pavage petite zone sud-est (pas tresfond).</t>
         </is>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" s="9">
+        <f>IF(A15="","",IF(OR(J15="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J15,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="9">
+        <f>IF(A15="","",IF(L15="",Inputs!$B$14,L15)+M15)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3482,7 +3685,10 @@
         <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G16" s="7" t="n"/>
+      <c r="G16" s="8">
+        <f>IF(A16="","",N16)</f>
+        <v/>
+      </c>
       <c r="H16" s="8">
         <f>IF(A16="","",Inputs!$B$3/((IF(G16="",Inputs!$B$14,G16)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3493,6 +3699,15 @@
       </c>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="9">
+        <f>IF(A16="","",IF(OR(J16="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J16,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="9">
+        <f>IF(A16="","",IF(L16="",Inputs!$B$14,L16)+M16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
@@ -3504,7 +3719,10 @@
         <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G17" s="7" t="n"/>
+      <c r="G17" s="8">
+        <f>IF(A17="","",N17)</f>
+        <v/>
+      </c>
       <c r="H17" s="8">
         <f>IF(A17="","",Inputs!$B$3/((IF(G17="",Inputs!$B$14,G17)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3515,6 +3733,15 @@
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="9">
+        <f>IF(A17="","",IF(OR(J17="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J17,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="9">
+        <f>IF(A17="","",IF(L17="",Inputs!$B$14,L17)+M17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n"/>
@@ -3526,7 +3753,10 @@
         <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="8">
+        <f>IF(A18="","",N18)</f>
+        <v/>
+      </c>
       <c r="H18" s="8">
         <f>IF(A18="","",Inputs!$B$3/((IF(G18="",Inputs!$B$14,G18)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3537,6 +3767,15 @@
       </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="9">
+        <f>IF(A18="","",IF(OR(J18="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J18,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="9">
+        <f>IF(A18="","",IF(L18="",Inputs!$B$14,L18)+M18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -3548,7 +3787,10 @@
         <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="8">
+        <f>IF(A19="","",N19)</f>
+        <v/>
+      </c>
       <c r="H19" s="8">
         <f>IF(A19="","",Inputs!$B$3/((IF(G19="",Inputs!$B$14,G19)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3559,6 +3801,15 @@
       </c>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="9">
+        <f>IF(A19="","",IF(OR(J19="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J19,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="9">
+        <f>IF(A19="","",IF(L19="",Inputs!$B$14,L19)+M19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -3570,7 +3821,10 @@
         <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="8">
+        <f>IF(A20="","",N20)</f>
+        <v/>
+      </c>
       <c r="H20" s="8">
         <f>IF(A20="","",Inputs!$B$3/((IF(G20="",Inputs!$B$14,G20)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3581,6 +3835,15 @@
       </c>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="9">
+        <f>IF(A20="","",IF(OR(J20="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J20,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="9">
+        <f>IF(A20="","",IF(L20="",Inputs!$B$14,L20)+M20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n"/>
@@ -3592,7 +3855,10 @@
         <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G21" s="7" t="n"/>
+      <c r="G21" s="8">
+        <f>IF(A21="","",N21)</f>
+        <v/>
+      </c>
       <c r="H21" s="8">
         <f>IF(A21="","",Inputs!$B$3/((IF(G21="",Inputs!$B$14,G21)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3603,6 +3869,15 @@
       </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="9">
+        <f>IF(A21="","",IF(OR(J21="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J21,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="9">
+        <f>IF(A21="","",IF(L21="",Inputs!$B$14,L21)+M21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n"/>
@@ -3614,7 +3889,10 @@
         <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="8">
+        <f>IF(A22="","",N22)</f>
+        <v/>
+      </c>
       <c r="H22" s="8">
         <f>IF(A22="","",Inputs!$B$3/((IF(G22="",Inputs!$B$14,G22)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3625,6 +3903,15 @@
       </c>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="9">
+        <f>IF(A22="","",IF(OR(J22="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J22,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="9">
+        <f>IF(A22="","",IF(L22="",Inputs!$B$14,L22)+M22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n"/>
@@ -3636,7 +3923,10 @@
         <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G23" s="7" t="n"/>
+      <c r="G23" s="8">
+        <f>IF(A23="","",N23)</f>
+        <v/>
+      </c>
       <c r="H23" s="8">
         <f>IF(A23="","",Inputs!$B$3/((IF(G23="",Inputs!$B$14,G23)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3647,6 +3937,15 @@
       </c>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="9">
+        <f>IF(A23="","",IF(OR(J23="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J23,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="9">
+        <f>IF(A23="","",IF(L23="",Inputs!$B$14,L23)+M23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n"/>
@@ -3658,7 +3957,10 @@
         <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G24" s="7" t="n"/>
+      <c r="G24" s="8">
+        <f>IF(A24="","",N24)</f>
+        <v/>
+      </c>
       <c r="H24" s="8">
         <f>IF(A24="","",Inputs!$B$3/((IF(G24="",Inputs!$B$14,G24)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3669,6 +3971,15 @@
       </c>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="9">
+        <f>IF(A24="","",IF(OR(J24="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J24,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="9">
+        <f>IF(A24="","",IF(L24="",Inputs!$B$14,L24)+M24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n"/>
@@ -3680,7 +3991,10 @@
         <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G25" s="7" t="n"/>
+      <c r="G25" s="8">
+        <f>IF(A25="","",N25)</f>
+        <v/>
+      </c>
       <c r="H25" s="8">
         <f>IF(A25="","",Inputs!$B$3/((IF(G25="",Inputs!$B$14,G25)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3691,6 +4005,15 @@
       </c>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="9">
+        <f>IF(A25="","",IF(OR(J25="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J25,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="9">
+        <f>IF(A25="","",IF(L25="",Inputs!$B$14,L25)+M25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
@@ -3702,7 +4025,10 @@
         <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G26" s="7" t="n"/>
+      <c r="G26" s="8">
+        <f>IF(A26="","",N26)</f>
+        <v/>
+      </c>
       <c r="H26" s="8">
         <f>IF(A26="","",Inputs!$B$3/((IF(G26="",Inputs!$B$14,G26)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3713,6 +4039,15 @@
       </c>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="9">
+        <f>IF(A26="","",IF(OR(J26="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J26,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="9">
+        <f>IF(A26="","",IF(L26="",Inputs!$B$14,L26)+M26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
@@ -3724,7 +4059,10 @@
         <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G27" s="7" t="n"/>
+      <c r="G27" s="8">
+        <f>IF(A27="","",N27)</f>
+        <v/>
+      </c>
       <c r="H27" s="8">
         <f>IF(A27="","",Inputs!$B$3/((IF(G27="",Inputs!$B$14,G27)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3735,6 +4073,15 @@
       </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="9">
+        <f>IF(A27="","",IF(OR(J27="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J27,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="9">
+        <f>IF(A27="","",IF(L27="",Inputs!$B$14,L27)+M27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
@@ -3746,7 +4093,10 @@
         <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G28" s="7" t="n"/>
+      <c r="G28" s="8">
+        <f>IF(A28="","",N28)</f>
+        <v/>
+      </c>
       <c r="H28" s="8">
         <f>IF(A28="","",Inputs!$B$3/((IF(G28="",Inputs!$B$14,G28)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3757,6 +4107,15 @@
       </c>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="9">
+        <f>IF(A28="","",IF(OR(J28="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J28,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="9">
+        <f>IF(A28="","",IF(L28="",Inputs!$B$14,L28)+M28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
@@ -3768,7 +4127,10 @@
         <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G29" s="7" t="n"/>
+      <c r="G29" s="8">
+        <f>IF(A29="","",N29)</f>
+        <v/>
+      </c>
       <c r="H29" s="8">
         <f>IF(A29="","",Inputs!$B$3/((IF(G29="",Inputs!$B$14,G29)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3779,6 +4141,15 @@
       </c>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="9">
+        <f>IF(A29="","",IF(OR(J29="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J29,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="9">
+        <f>IF(A29="","",IF(L29="",Inputs!$B$14,L29)+M29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -3790,7 +4161,10 @@
         <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G30" s="7" t="n"/>
+      <c r="G30" s="8">
+        <f>IF(A30="","",N30)</f>
+        <v/>
+      </c>
       <c r="H30" s="8">
         <f>IF(A30="","",Inputs!$B$3/((IF(G30="",Inputs!$B$14,G30)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3801,6 +4175,15 @@
       </c>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="9">
+        <f>IF(A30="","",IF(OR(J30="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J30,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N30" s="9">
+        <f>IF(A30="","",IF(L30="",Inputs!$B$14,L30)+M30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -3812,7 +4195,10 @@
         <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G31" s="7" t="n"/>
+      <c r="G31" s="8">
+        <f>IF(A31="","",N31)</f>
+        <v/>
+      </c>
       <c r="H31" s="8">
         <f>IF(A31="","",Inputs!$B$3/((IF(G31="",Inputs!$B$14,G31)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3823,6 +4209,15 @@
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="9">
+        <f>IF(A31="","",IF(OR(J31="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J31,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N31" s="9">
+        <f>IF(A31="","",IF(L31="",Inputs!$B$14,L31)+M31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -3834,7 +4229,10 @@
         <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G32" s="7" t="n"/>
+      <c r="G32" s="8">
+        <f>IF(A32="","",N32)</f>
+        <v/>
+      </c>
       <c r="H32" s="8">
         <f>IF(A32="","",Inputs!$B$3/((IF(G32="",Inputs!$B$14,G32)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3845,6 +4243,15 @@
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="9">
+        <f>IF(A32="","",IF(OR(J32="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J32,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N32" s="9">
+        <f>IF(A32="","",IF(L32="",Inputs!$B$14,L32)+M32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -3856,7 +4263,10 @@
         <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G33" s="7" t="n"/>
+      <c r="G33" s="8">
+        <f>IF(A33="","",N33)</f>
+        <v/>
+      </c>
       <c r="H33" s="8">
         <f>IF(A33="","",Inputs!$B$3/((IF(G33="",Inputs!$B$14,G33)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3867,6 +4277,15 @@
       </c>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="9">
+        <f>IF(A33="","",IF(OR(J33="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J33,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N33" s="9">
+        <f>IF(A33="","",IF(L33="",Inputs!$B$14,L33)+M33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -3878,7 +4297,10 @@
         <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G34" s="7" t="n"/>
+      <c r="G34" s="8">
+        <f>IF(A34="","",N34)</f>
+        <v/>
+      </c>
       <c r="H34" s="8">
         <f>IF(A34="","",Inputs!$B$3/((IF(G34="",Inputs!$B$14,G34)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3889,6 +4311,15 @@
       </c>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="9">
+        <f>IF(A34="","",IF(OR(J34="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J34,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N34" s="9">
+        <f>IF(A34="","",IF(L34="",Inputs!$B$14,L34)+M34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -3900,7 +4331,10 @@
         <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G35" s="7" t="n"/>
+      <c r="G35" s="8">
+        <f>IF(A35="","",N35)</f>
+        <v/>
+      </c>
       <c r="H35" s="8">
         <f>IF(A35="","",Inputs!$B$3/((IF(G35="",Inputs!$B$14,G35)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3911,6 +4345,15 @@
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="9">
+        <f>IF(A35="","",IF(OR(J35="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J35,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N35" s="9">
+        <f>IF(A35="","",IF(L35="",Inputs!$B$14,L35)+M35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -3922,7 +4365,10 @@
         <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G36" s="7" t="n"/>
+      <c r="G36" s="8">
+        <f>IF(A36="","",N36)</f>
+        <v/>
+      </c>
       <c r="H36" s="8">
         <f>IF(A36="","",Inputs!$B$3/((IF(G36="",Inputs!$B$14,G36)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3933,6 +4379,15 @@
       </c>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="9">
+        <f>IF(A36="","",IF(OR(J36="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J36,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N36" s="9">
+        <f>IF(A36="","",IF(L36="",Inputs!$B$14,L36)+M36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -3944,7 +4399,10 @@
         <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G37" s="7" t="n"/>
+      <c r="G37" s="8">
+        <f>IF(A37="","",N37)</f>
+        <v/>
+      </c>
       <c r="H37" s="8">
         <f>IF(A37="","",Inputs!$B$3/((IF(G37="",Inputs!$B$14,G37)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3955,6 +4413,15 @@
       </c>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="9">
+        <f>IF(A37="","",IF(OR(J37="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J37,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N37" s="9">
+        <f>IF(A37="","",IF(L37="",Inputs!$B$14,L37)+M37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -3966,7 +4433,10 @@
         <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G38" s="7" t="n"/>
+      <c r="G38" s="8">
+        <f>IF(A38="","",N38)</f>
+        <v/>
+      </c>
       <c r="H38" s="8">
         <f>IF(A38="","",Inputs!$B$3/((IF(G38="",Inputs!$B$14,G38)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3977,6 +4447,15 @@
       </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="9">
+        <f>IF(A38="","",IF(OR(J38="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J38,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N38" s="9">
+        <f>IF(A38="","",IF(L38="",Inputs!$B$14,L38)+M38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -3988,7 +4467,10 @@
         <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G39" s="7" t="n"/>
+      <c r="G39" s="8">
+        <f>IF(A39="","",N39)</f>
+        <v/>
+      </c>
       <c r="H39" s="8">
         <f>IF(A39="","",Inputs!$B$3/((IF(G39="",Inputs!$B$14,G39)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -3999,6 +4481,15 @@
       </c>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="9">
+        <f>IF(A39="","",IF(OR(J39="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J39,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N39" s="9">
+        <f>IF(A39="","",IF(L39="",Inputs!$B$14,L39)+M39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -4010,7 +4501,10 @@
         <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G40" s="7" t="n"/>
+      <c r="G40" s="8">
+        <f>IF(A40="","",N40)</f>
+        <v/>
+      </c>
       <c r="H40" s="8">
         <f>IF(A40="","",Inputs!$B$3/((IF(G40="",Inputs!$B$14,G40)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4021,6 +4515,15 @@
       </c>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="9">
+        <f>IF(A40="","",IF(OR(J40="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J40,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N40" s="9">
+        <f>IF(A40="","",IF(L40="",Inputs!$B$14,L40)+M40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -4032,7 +4535,10 @@
         <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G41" s="7" t="n"/>
+      <c r="G41" s="8">
+        <f>IF(A41="","",N41)</f>
+        <v/>
+      </c>
       <c r="H41" s="8">
         <f>IF(A41="","",Inputs!$B$3/((IF(G41="",Inputs!$B$14,G41)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4043,6 +4549,15 @@
       </c>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="9">
+        <f>IF(A41="","",IF(OR(J41="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J41,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N41" s="9">
+        <f>IF(A41="","",IF(L41="",Inputs!$B$14,L41)+M41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
@@ -4054,7 +4569,10 @@
         <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G42" s="7" t="n"/>
+      <c r="G42" s="8">
+        <f>IF(A42="","",N42)</f>
+        <v/>
+      </c>
       <c r="H42" s="8">
         <f>IF(A42="","",Inputs!$B$3/((IF(G42="",Inputs!$B$14,G42)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4065,6 +4583,15 @@
       </c>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="9">
+        <f>IF(A42="","",IF(OR(J42="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J42,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N42" s="9">
+        <f>IF(A42="","",IF(L42="",Inputs!$B$14,L42)+M42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
@@ -4076,7 +4603,10 @@
         <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G43" s="7" t="n"/>
+      <c r="G43" s="8">
+        <f>IF(A43="","",N43)</f>
+        <v/>
+      </c>
       <c r="H43" s="8">
         <f>IF(A43="","",Inputs!$B$3/((IF(G43="",Inputs!$B$14,G43)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4087,6 +4617,15 @@
       </c>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="9">
+        <f>IF(A43="","",IF(OR(J43="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J43,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N43" s="9">
+        <f>IF(A43="","",IF(L43="",Inputs!$B$14,L43)+M43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
@@ -4098,7 +4637,10 @@
         <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G44" s="7" t="n"/>
+      <c r="G44" s="8">
+        <f>IF(A44="","",N44)</f>
+        <v/>
+      </c>
       <c r="H44" s="8">
         <f>IF(A44="","",Inputs!$B$3/((IF(G44="",Inputs!$B$14,G44)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4109,6 +4651,15 @@
       </c>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="9">
+        <f>IF(A44="","",IF(OR(J44="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J44,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N44" s="9">
+        <f>IF(A44="","",IF(L44="",Inputs!$B$14,L44)+M44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n"/>
@@ -4120,7 +4671,10 @@
         <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G45" s="7" t="n"/>
+      <c r="G45" s="8">
+        <f>IF(A45="","",N45)</f>
+        <v/>
+      </c>
       <c r="H45" s="8">
         <f>IF(A45="","",Inputs!$B$3/((IF(G45="",Inputs!$B$14,G45)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4131,6 +4685,15 @@
       </c>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="9">
+        <f>IF(A45="","",IF(OR(J45="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J45,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N45" s="9">
+        <f>IF(A45="","",IF(L45="",Inputs!$B$14,L45)+M45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n"/>
@@ -4142,7 +4705,10 @@
         <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G46" s="7" t="n"/>
+      <c r="G46" s="8">
+        <f>IF(A46="","",N46)</f>
+        <v/>
+      </c>
       <c r="H46" s="8">
         <f>IF(A46="","",Inputs!$B$3/((IF(G46="",Inputs!$B$14,G46)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4153,6 +4719,15 @@
       </c>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="9">
+        <f>IF(A46="","",IF(OR(J46="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J46,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N46" s="9">
+        <f>IF(A46="","",IF(L46="",Inputs!$B$14,L46)+M46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n"/>
@@ -4164,7 +4739,10 @@
         <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G47" s="7" t="n"/>
+      <c r="G47" s="8">
+        <f>IF(A47="","",N47)</f>
+        <v/>
+      </c>
       <c r="H47" s="8">
         <f>IF(A47="","",Inputs!$B$3/((IF(G47="",Inputs!$B$14,G47)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4175,6 +4753,15 @@
       </c>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="9">
+        <f>IF(A47="","",IF(OR(J47="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J47,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N47" s="9">
+        <f>IF(A47="","",IF(L47="",Inputs!$B$14,L47)+M47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n"/>
@@ -4186,7 +4773,10 @@
         <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G48" s="7" t="n"/>
+      <c r="G48" s="8">
+        <f>IF(A48="","",N48)</f>
+        <v/>
+      </c>
       <c r="H48" s="8">
         <f>IF(A48="","",Inputs!$B$3/((IF(G48="",Inputs!$B$14,G48)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4197,6 +4787,15 @@
       </c>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="9">
+        <f>IF(A48="","",IF(OR(J48="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J48,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N48" s="9">
+        <f>IF(A48="","",IF(L48="",Inputs!$B$14,L48)+M48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n"/>
@@ -4208,7 +4807,10 @@
         <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G49" s="7" t="n"/>
+      <c r="G49" s="8">
+        <f>IF(A49="","",N49)</f>
+        <v/>
+      </c>
       <c r="H49" s="8">
         <f>IF(A49="","",Inputs!$B$3/((IF(G49="",Inputs!$B$14,G49)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4219,6 +4821,15 @@
       </c>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="9">
+        <f>IF(A49="","",IF(OR(J49="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J49,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N49" s="9">
+        <f>IF(A49="","",IF(L49="",Inputs!$B$14,L49)+M49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n"/>
@@ -4230,7 +4841,10 @@
         <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G50" s="7" t="n"/>
+      <c r="G50" s="8">
+        <f>IF(A50="","",N50)</f>
+        <v/>
+      </c>
       <c r="H50" s="8">
         <f>IF(A50="","",Inputs!$B$3/((IF(G50="",Inputs!$B$14,G50)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4241,6 +4855,15 @@
       </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="9">
+        <f>IF(A50="","",IF(OR(J50="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J50,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N50" s="9">
+        <f>IF(A50="","",IF(L50="",Inputs!$B$14,L50)+M50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n"/>
@@ -4252,7 +4875,10 @@
         <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G51" s="7" t="n"/>
+      <c r="G51" s="8">
+        <f>IF(A51="","",N51)</f>
+        <v/>
+      </c>
       <c r="H51" s="8">
         <f>IF(A51="","",Inputs!$B$3/((IF(G51="",Inputs!$B$14,G51)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4263,6 +4889,15 @@
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="9">
+        <f>IF(A51="","",IF(OR(J51="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J51,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N51" s="9">
+        <f>IF(A51="","",IF(L51="",Inputs!$B$14,L51)+M51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n"/>
@@ -4274,7 +4909,10 @@
         <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G52" s="7" t="n"/>
+      <c r="G52" s="8">
+        <f>IF(A52="","",N52)</f>
+        <v/>
+      </c>
       <c r="H52" s="8">
         <f>IF(A52="","",Inputs!$B$3/((IF(G52="",Inputs!$B$14,G52)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4285,6 +4923,15 @@
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="9">
+        <f>IF(A52="","",IF(OR(J52="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J52,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N52" s="9">
+        <f>IF(A52="","",IF(L52="",Inputs!$B$14,L52)+M52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n"/>
@@ -4296,7 +4943,10 @@
         <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G53" s="7" t="n"/>
+      <c r="G53" s="8">
+        <f>IF(A53="","",N53)</f>
+        <v/>
+      </c>
       <c r="H53" s="8">
         <f>IF(A53="","",Inputs!$B$3/((IF(G53="",Inputs!$B$14,G53)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4307,6 +4957,15 @@
       </c>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="9">
+        <f>IF(A53="","",IF(OR(J53="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J53,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N53" s="9">
+        <f>IF(A53="","",IF(L53="",Inputs!$B$14,L53)+M53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n"/>
@@ -4318,7 +4977,10 @@
         <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G54" s="7" t="n"/>
+      <c r="G54" s="8">
+        <f>IF(A54="","",N54)</f>
+        <v/>
+      </c>
       <c r="H54" s="8">
         <f>IF(A54="","",Inputs!$B$3/((IF(G54="",Inputs!$B$14,G54)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4329,6 +4991,15 @@
       </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="9">
+        <f>IF(A54="","",IF(OR(J54="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J54,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N54" s="9">
+        <f>IF(A54="","",IF(L54="",Inputs!$B$14,L54)+M54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n"/>
@@ -4340,7 +5011,10 @@
         <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G55" s="7" t="n"/>
+      <c r="G55" s="8">
+        <f>IF(A55="","",N55)</f>
+        <v/>
+      </c>
       <c r="H55" s="8">
         <f>IF(A55="","",Inputs!$B$3/((IF(G55="",Inputs!$B$14,G55)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4351,6 +5025,15 @@
       </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="9">
+        <f>IF(A55="","",IF(OR(J55="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J55,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N55" s="9">
+        <f>IF(A55="","",IF(L55="",Inputs!$B$14,L55)+M55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n"/>
@@ -4362,7 +5045,10 @@
         <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G56" s="7" t="n"/>
+      <c r="G56" s="8">
+        <f>IF(A56="","",N56)</f>
+        <v/>
+      </c>
       <c r="H56" s="8">
         <f>IF(A56="","",Inputs!$B$3/((IF(G56="",Inputs!$B$14,G56)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4373,6 +5059,15 @@
       </c>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="9">
+        <f>IF(A56="","",IF(OR(J56="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J56,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N56" s="9">
+        <f>IF(A56="","",IF(L56="",Inputs!$B$14,L56)+M56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n"/>
@@ -4384,7 +5079,10 @@
         <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G57" s="7" t="n"/>
+      <c r="G57" s="8">
+        <f>IF(A57="","",N57)</f>
+        <v/>
+      </c>
       <c r="H57" s="8">
         <f>IF(A57="","",Inputs!$B$3/((IF(G57="",Inputs!$B$14,G57)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4395,6 +5093,15 @@
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="9">
+        <f>IF(A57="","",IF(OR(J57="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J57,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N57" s="9">
+        <f>IF(A57="","",IF(L57="",Inputs!$B$14,L57)+M57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n"/>
@@ -4406,7 +5113,10 @@
         <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G58" s="7" t="n"/>
+      <c r="G58" s="8">
+        <f>IF(A58="","",N58)</f>
+        <v/>
+      </c>
       <c r="H58" s="8">
         <f>IF(A58="","",Inputs!$B$3/((IF(G58="",Inputs!$B$14,G58)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4417,6 +5127,15 @@
       </c>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="9">
+        <f>IF(A58="","",IF(OR(J58="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J58,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N58" s="9">
+        <f>IF(A58="","",IF(L58="",Inputs!$B$14,L58)+M58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n"/>
@@ -4428,7 +5147,10 @@
         <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G59" s="7" t="n"/>
+      <c r="G59" s="8">
+        <f>IF(A59="","",N59)</f>
+        <v/>
+      </c>
       <c r="H59" s="8">
         <f>IF(A59="","",Inputs!$B$3/((IF(G59="",Inputs!$B$14,G59)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4439,6 +5161,15 @@
       </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="9">
+        <f>IF(A59="","",IF(OR(J59="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J59,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="9">
+        <f>IF(A59="","",IF(L59="",Inputs!$B$14,L59)+M59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n"/>
@@ -4450,7 +5181,10 @@
         <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G60" s="7" t="n"/>
+      <c r="G60" s="8">
+        <f>IF(A60="","",N60)</f>
+        <v/>
+      </c>
       <c r="H60" s="8">
         <f>IF(A60="","",Inputs!$B$3/((IF(G60="",Inputs!$B$14,G60)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4461,6 +5195,15 @@
       </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="9">
+        <f>IF(A60="","",IF(OR(J60="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J60,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="9">
+        <f>IF(A60="","",IF(L60="",Inputs!$B$14,L60)+M60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n"/>
@@ -4472,7 +5215,10 @@
         <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G61" s="7" t="n"/>
+      <c r="G61" s="8">
+        <f>IF(A61="","",N61)</f>
+        <v/>
+      </c>
       <c r="H61" s="8">
         <f>IF(A61="","",Inputs!$B$3/((IF(G61="",Inputs!$B$14,G61)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4483,6 +5229,15 @@
       </c>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="9">
+        <f>IF(A61="","",IF(OR(J61="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J61,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="9">
+        <f>IF(A61="","",IF(L61="",Inputs!$B$14,L61)+M61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n"/>
@@ -4494,7 +5249,10 @@
         <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G62" s="7" t="n"/>
+      <c r="G62" s="8">
+        <f>IF(A62="","",N62)</f>
+        <v/>
+      </c>
       <c r="H62" s="8">
         <f>IF(A62="","",Inputs!$B$3/((IF(G62="",Inputs!$B$14,G62)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4505,6 +5263,15 @@
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="9">
+        <f>IF(A62="","",IF(OR(J62="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J62,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N62" s="9">
+        <f>IF(A62="","",IF(L62="",Inputs!$B$14,L62)+M62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n"/>
@@ -4516,7 +5283,10 @@
         <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G63" s="7" t="n"/>
+      <c r="G63" s="8">
+        <f>IF(A63="","",N63)</f>
+        <v/>
+      </c>
       <c r="H63" s="8">
         <f>IF(A63="","",Inputs!$B$3/((IF(G63="",Inputs!$B$14,G63)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4527,6 +5297,15 @@
       </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="9">
+        <f>IF(A63="","",IF(OR(J63="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J63,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N63" s="9">
+        <f>IF(A63="","",IF(L63="",Inputs!$B$14,L63)+M63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n"/>
@@ -4538,7 +5317,10 @@
         <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G64" s="7" t="n"/>
+      <c r="G64" s="8">
+        <f>IF(A64="","",N64)</f>
+        <v/>
+      </c>
       <c r="H64" s="8">
         <f>IF(A64="","",Inputs!$B$3/((IF(G64="",Inputs!$B$14,G64)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4549,6 +5331,15 @@
       </c>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="9">
+        <f>IF(A64="","",IF(OR(J64="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J64,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N64" s="9">
+        <f>IF(A64="","",IF(L64="",Inputs!$B$14,L64)+M64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n"/>
@@ -4560,7 +5351,10 @@
         <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G65" s="7" t="n"/>
+      <c r="G65" s="8">
+        <f>IF(A65="","",N65)</f>
+        <v/>
+      </c>
       <c r="H65" s="8">
         <f>IF(A65="","",Inputs!$B$3/((IF(G65="",Inputs!$B$14,G65)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4571,6 +5365,15 @@
       </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="9">
+        <f>IF(A65="","",IF(OR(J65="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J65,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N65" s="9">
+        <f>IF(A65="","",IF(L65="",Inputs!$B$14,L65)+M65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n"/>
@@ -4582,7 +5385,10 @@
         <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G66" s="7" t="n"/>
+      <c r="G66" s="8">
+        <f>IF(A66="","",N66)</f>
+        <v/>
+      </c>
       <c r="H66" s="8">
         <f>IF(A66="","",Inputs!$B$3/((IF(G66="",Inputs!$B$14,G66)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4593,6 +5399,15 @@
       </c>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="9">
+        <f>IF(A66="","",IF(OR(J66="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J66,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N66" s="9">
+        <f>IF(A66="","",IF(L66="",Inputs!$B$14,L66)+M66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n"/>
@@ -4604,7 +5419,10 @@
         <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G67" s="7" t="n"/>
+      <c r="G67" s="8">
+        <f>IF(A67="","",N67)</f>
+        <v/>
+      </c>
       <c r="H67" s="8">
         <f>IF(A67="","",Inputs!$B$3/((IF(G67="",Inputs!$B$14,G67)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4615,6 +5433,15 @@
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="9">
+        <f>IF(A67="","",IF(OR(J67="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J67,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N67" s="9">
+        <f>IF(A67="","",IF(L67="",Inputs!$B$14,L67)+M67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n"/>
@@ -4626,7 +5453,10 @@
         <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G68" s="7" t="n"/>
+      <c r="G68" s="8">
+        <f>IF(A68="","",N68)</f>
+        <v/>
+      </c>
       <c r="H68" s="8">
         <f>IF(A68="","",Inputs!$B$3/((IF(G68="",Inputs!$B$14,G68)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4637,6 +5467,15 @@
       </c>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="9">
+        <f>IF(A68="","",IF(OR(J68="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J68,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N68" s="9">
+        <f>IF(A68="","",IF(L68="",Inputs!$B$14,L68)+M68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n"/>
@@ -4648,7 +5487,10 @@
         <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G69" s="7" t="n"/>
+      <c r="G69" s="8">
+        <f>IF(A69="","",N69)</f>
+        <v/>
+      </c>
       <c r="H69" s="8">
         <f>IF(A69="","",Inputs!$B$3/((IF(G69="",Inputs!$B$14,G69)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4659,6 +5501,15 @@
       </c>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="9">
+        <f>IF(A69="","",IF(OR(J69="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J69,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N69" s="9">
+        <f>IF(A69="","",IF(L69="",Inputs!$B$14,L69)+M69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n"/>
@@ -4670,7 +5521,10 @@
         <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G70" s="7" t="n"/>
+      <c r="G70" s="8">
+        <f>IF(A70="","",N70)</f>
+        <v/>
+      </c>
       <c r="H70" s="8">
         <f>IF(A70="","",Inputs!$B$3/((IF(G70="",Inputs!$B$14,G70)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4681,6 +5535,15 @@
       </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="9">
+        <f>IF(A70="","",IF(OR(J70="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J70,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N70" s="9">
+        <f>IF(A70="","",IF(L70="",Inputs!$B$14,L70)+M70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n"/>
@@ -4692,7 +5555,10 @@
         <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G71" s="7" t="n"/>
+      <c r="G71" s="8">
+        <f>IF(A71="","",N71)</f>
+        <v/>
+      </c>
       <c r="H71" s="8">
         <f>IF(A71="","",Inputs!$B$3/((IF(G71="",Inputs!$B$14,G71)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4703,6 +5569,15 @@
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="9">
+        <f>IF(A71="","",IF(OR(J71="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J71,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N71" s="9">
+        <f>IF(A71="","",IF(L71="",Inputs!$B$14,L71)+M71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n"/>
@@ -4714,7 +5589,10 @@
         <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G72" s="7" t="n"/>
+      <c r="G72" s="8">
+        <f>IF(A72="","",N72)</f>
+        <v/>
+      </c>
       <c r="H72" s="8">
         <f>IF(A72="","",Inputs!$B$3/((IF(G72="",Inputs!$B$14,G72)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4725,6 +5603,15 @@
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="9">
+        <f>IF(A72="","",IF(OR(J72="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J72,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N72" s="9">
+        <f>IF(A72="","",IF(L72="",Inputs!$B$14,L72)+M72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n"/>
@@ -4736,7 +5623,10 @@
         <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G73" s="7" t="n"/>
+      <c r="G73" s="8">
+        <f>IF(A73="","",N73)</f>
+        <v/>
+      </c>
       <c r="H73" s="8">
         <f>IF(A73="","",Inputs!$B$3/((IF(G73="",Inputs!$B$14,G73)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4747,6 +5637,15 @@
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="9">
+        <f>IF(A73="","",IF(OR(J73="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J73,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N73" s="9">
+        <f>IF(A73="","",IF(L73="",Inputs!$B$14,L73)+M73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n"/>
@@ -4758,7 +5657,10 @@
         <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G74" s="7" t="n"/>
+      <c r="G74" s="8">
+        <f>IF(A74="","",N74)</f>
+        <v/>
+      </c>
       <c r="H74" s="8">
         <f>IF(A74="","",Inputs!$B$3/((IF(G74="",Inputs!$B$14,G74)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4769,6 +5671,15 @@
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="9">
+        <f>IF(A74="","",IF(OR(J74="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J74,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N74" s="9">
+        <f>IF(A74="","",IF(L74="",Inputs!$B$14,L74)+M74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
@@ -4780,7 +5691,10 @@
         <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G75" s="7" t="n"/>
+      <c r="G75" s="8">
+        <f>IF(A75="","",N75)</f>
+        <v/>
+      </c>
       <c r="H75" s="8">
         <f>IF(A75="","",Inputs!$B$3/((IF(G75="",Inputs!$B$14,G75)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4791,6 +5705,15 @@
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
+      <c r="L75" s="5" t="n"/>
+      <c r="M75" s="9">
+        <f>IF(A75="","",IF(OR(J75="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J75,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N75" s="9">
+        <f>IF(A75="","",IF(L75="",Inputs!$B$14,L75)+M75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
@@ -4802,7 +5725,10 @@
         <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G76" s="7" t="n"/>
+      <c r="G76" s="8">
+        <f>IF(A76="","",N76)</f>
+        <v/>
+      </c>
       <c r="H76" s="8">
         <f>IF(A76="","",Inputs!$B$3/((IF(G76="",Inputs!$B$14,G76)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4813,6 +5739,15 @@
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="9">
+        <f>IF(A76="","",IF(OR(J76="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J76,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N76" s="9">
+        <f>IF(A76="","",IF(L76="",Inputs!$B$14,L76)+M76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -4824,7 +5759,10 @@
         <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G77" s="7" t="n"/>
+      <c r="G77" s="8">
+        <f>IF(A77="","",N77)</f>
+        <v/>
+      </c>
       <c r="H77" s="8">
         <f>IF(A77="","",Inputs!$B$3/((IF(G77="",Inputs!$B$14,G77)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4835,6 +5773,15 @@
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="9">
+        <f>IF(A77="","",IF(OR(J77="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J77,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N77" s="9">
+        <f>IF(A77="","",IF(L77="",Inputs!$B$14,L77)+M77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n"/>
@@ -4846,7 +5793,10 @@
         <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G78" s="7" t="n"/>
+      <c r="G78" s="8">
+        <f>IF(A78="","",N78)</f>
+        <v/>
+      </c>
       <c r="H78" s="8">
         <f>IF(A78="","",Inputs!$B$3/((IF(G78="",Inputs!$B$14,G78)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4857,6 +5807,15 @@
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="9">
+        <f>IF(A78="","",IF(OR(J78="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J78,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N78" s="9">
+        <f>IF(A78="","",IF(L78="",Inputs!$B$14,L78)+M78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n"/>
@@ -4868,7 +5827,10 @@
         <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G79" s="7" t="n"/>
+      <c r="G79" s="8">
+        <f>IF(A79="","",N79)</f>
+        <v/>
+      </c>
       <c r="H79" s="8">
         <f>IF(A79="","",Inputs!$B$3/((IF(G79="",Inputs!$B$14,G79)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4879,6 +5841,15 @@
       </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="9">
+        <f>IF(A79="","",IF(OR(J79="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J79,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N79" s="9">
+        <f>IF(A79="","",IF(L79="",Inputs!$B$14,L79)+M79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n"/>
@@ -4890,7 +5861,10 @@
         <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G80" s="7" t="n"/>
+      <c r="G80" s="8">
+        <f>IF(A80="","",N80)</f>
+        <v/>
+      </c>
       <c r="H80" s="8">
         <f>IF(A80="","",Inputs!$B$3/((IF(G80="",Inputs!$B$14,G80)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4901,6 +5875,15 @@
       </c>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="9">
+        <f>IF(A80="","",IF(OR(J80="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J80,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N80" s="9">
+        <f>IF(A80="","",IF(L80="",Inputs!$B$14,L80)+M80)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n"/>
@@ -4912,7 +5895,10 @@
         <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G81" s="7" t="n"/>
+      <c r="G81" s="8">
+        <f>IF(A81="","",N81)</f>
+        <v/>
+      </c>
       <c r="H81" s="8">
         <f>IF(A81="","",Inputs!$B$3/((IF(G81="",Inputs!$B$14,G81)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4923,6 +5909,15 @@
       </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="9">
+        <f>IF(A81="","",IF(OR(J81="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J81,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N81" s="9">
+        <f>IF(A81="","",IF(L81="",Inputs!$B$14,L81)+M81)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
@@ -4934,7 +5929,10 @@
         <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G82" s="7" t="n"/>
+      <c r="G82" s="8">
+        <f>IF(A82="","",N82)</f>
+        <v/>
+      </c>
       <c r="H82" s="8">
         <f>IF(A82="","",Inputs!$B$3/((IF(G82="",Inputs!$B$14,G82)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4945,6 +5943,15 @@
       </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="9">
+        <f>IF(A82="","",IF(OR(J82="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J82,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N82" s="9">
+        <f>IF(A82="","",IF(L82="",Inputs!$B$14,L82)+M82)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
@@ -4956,7 +5963,10 @@
         <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G83" s="7" t="n"/>
+      <c r="G83" s="8">
+        <f>IF(A83="","",N83)</f>
+        <v/>
+      </c>
       <c r="H83" s="8">
         <f>IF(A83="","",Inputs!$B$3/((IF(G83="",Inputs!$B$14,G83)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4967,6 +5977,15 @@
       </c>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="9">
+        <f>IF(A83="","",IF(OR(J83="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J83,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N83" s="9">
+        <f>IF(A83="","",IF(L83="",Inputs!$B$14,L83)+M83)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
@@ -4978,7 +5997,10 @@
         <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G84" s="7" t="n"/>
+      <c r="G84" s="8">
+        <f>IF(A84="","",N84)</f>
+        <v/>
+      </c>
       <c r="H84" s="8">
         <f>IF(A84="","",Inputs!$B$3/((IF(G84="",Inputs!$B$14,G84)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -4989,6 +6011,15 @@
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="9">
+        <f>IF(A84="","",IF(OR(J84="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J84,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N84" s="9">
+        <f>IF(A84="","",IF(L84="",Inputs!$B$14,L84)+M84)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
@@ -5000,7 +6031,10 @@
         <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G85" s="7" t="n"/>
+      <c r="G85" s="8">
+        <f>IF(A85="","",N85)</f>
+        <v/>
+      </c>
       <c r="H85" s="8">
         <f>IF(A85="","",Inputs!$B$3/((IF(G85="",Inputs!$B$14,G85)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5011,6 +6045,15 @@
       </c>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="9">
+        <f>IF(A85="","",IF(OR(J85="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J85,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N85" s="9">
+        <f>IF(A85="","",IF(L85="",Inputs!$B$14,L85)+M85)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -5022,7 +6065,10 @@
         <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G86" s="7" t="n"/>
+      <c r="G86" s="8">
+        <f>IF(A86="","",N86)</f>
+        <v/>
+      </c>
       <c r="H86" s="8">
         <f>IF(A86="","",Inputs!$B$3/((IF(G86="",Inputs!$B$14,G86)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5033,6 +6079,15 @@
       </c>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="9">
+        <f>IF(A86="","",IF(OR(J86="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J86,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N86" s="9">
+        <f>IF(A86="","",IF(L86="",Inputs!$B$14,L86)+M86)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n"/>
@@ -5044,7 +6099,10 @@
         <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G87" s="7" t="n"/>
+      <c r="G87" s="8">
+        <f>IF(A87="","",N87)</f>
+        <v/>
+      </c>
       <c r="H87" s="8">
         <f>IF(A87="","",Inputs!$B$3/((IF(G87="",Inputs!$B$14,G87)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5055,6 +6113,15 @@
       </c>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="9">
+        <f>IF(A87="","",IF(OR(J87="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J87,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N87" s="9">
+        <f>IF(A87="","",IF(L87="",Inputs!$B$14,L87)+M87)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n"/>
@@ -5066,7 +6133,10 @@
         <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G88" s="7" t="n"/>
+      <c r="G88" s="8">
+        <f>IF(A88="","",N88)</f>
+        <v/>
+      </c>
       <c r="H88" s="8">
         <f>IF(A88="","",Inputs!$B$3/((IF(G88="",Inputs!$B$14,G88)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5077,6 +6147,15 @@
       </c>
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="9">
+        <f>IF(A88="","",IF(OR(J88="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J88,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N88" s="9">
+        <f>IF(A88="","",IF(L88="",Inputs!$B$14,L88)+M88)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
@@ -5088,7 +6167,10 @@
         <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G89" s="7" t="n"/>
+      <c r="G89" s="8">
+        <f>IF(A89="","",N89)</f>
+        <v/>
+      </c>
       <c r="H89" s="8">
         <f>IF(A89="","",Inputs!$B$3/((IF(G89="",Inputs!$B$14,G89)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5099,6 +6181,15 @@
       </c>
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="9">
+        <f>IF(A89="","",IF(OR(J89="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J89,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N89" s="9">
+        <f>IF(A89="","",IF(L89="",Inputs!$B$14,L89)+M89)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
@@ -5110,7 +6201,10 @@
         <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G90" s="7" t="n"/>
+      <c r="G90" s="8">
+        <f>IF(A90="","",N90)</f>
+        <v/>
+      </c>
       <c r="H90" s="8">
         <f>IF(A90="","",Inputs!$B$3/((IF(G90="",Inputs!$B$14,G90)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5121,6 +6215,15 @@
       </c>
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="9">
+        <f>IF(A90="","",IF(OR(J90="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J90,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N90" s="9">
+        <f>IF(A90="","",IF(L90="",Inputs!$B$14,L90)+M90)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
@@ -5132,7 +6235,10 @@
         <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G91" s="7" t="n"/>
+      <c r="G91" s="8">
+        <f>IF(A91="","",N91)</f>
+        <v/>
+      </c>
       <c r="H91" s="8">
         <f>IF(A91="","",Inputs!$B$3/((IF(G91="",Inputs!$B$14,G91)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5143,6 +6249,15 @@
       </c>
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="9">
+        <f>IF(A91="","",IF(OR(J91="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J91,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N91" s="9">
+        <f>IF(A91="","",IF(L91="",Inputs!$B$14,L91)+M91)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -5154,7 +6269,10 @@
         <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G92" s="7" t="n"/>
+      <c r="G92" s="8">
+        <f>IF(A92="","",N92)</f>
+        <v/>
+      </c>
       <c r="H92" s="8">
         <f>IF(A92="","",Inputs!$B$3/((IF(G92="",Inputs!$B$14,G92)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5165,6 +6283,15 @@
       </c>
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="9">
+        <f>IF(A92="","",IF(OR(J92="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J92,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N92" s="9">
+        <f>IF(A92="","",IF(L92="",Inputs!$B$14,L92)+M92)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -5176,7 +6303,10 @@
         <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G93" s="7" t="n"/>
+      <c r="G93" s="8">
+        <f>IF(A93="","",N93)</f>
+        <v/>
+      </c>
       <c r="H93" s="8">
         <f>IF(A93="","",Inputs!$B$3/((IF(G93="",Inputs!$B$14,G93)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5187,6 +6317,15 @@
       </c>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="9">
+        <f>IF(A93="","",IF(OR(J93="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J93,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N93" s="9">
+        <f>IF(A93="","",IF(L93="",Inputs!$B$14,L93)+M93)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
@@ -5198,7 +6337,10 @@
         <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G94" s="7" t="n"/>
+      <c r="G94" s="8">
+        <f>IF(A94="","",N94)</f>
+        <v/>
+      </c>
       <c r="H94" s="8">
         <f>IF(A94="","",Inputs!$B$3/((IF(G94="",Inputs!$B$14,G94)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5209,6 +6351,15 @@
       </c>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="9">
+        <f>IF(A94="","",IF(OR(J94="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J94,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N94" s="9">
+        <f>IF(A94="","",IF(L94="",Inputs!$B$14,L94)+M94)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
@@ -5220,7 +6371,10 @@
         <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G95" s="7" t="n"/>
+      <c r="G95" s="8">
+        <f>IF(A95="","",N95)</f>
+        <v/>
+      </c>
       <c r="H95" s="8">
         <f>IF(A95="","",Inputs!$B$3/((IF(G95="",Inputs!$B$14,G95)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5231,6 +6385,15 @@
       </c>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="9">
+        <f>IF(A95="","",IF(OR(J95="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J95,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N95" s="9">
+        <f>IF(A95="","",IF(L95="",Inputs!$B$14,L95)+M95)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
@@ -5242,7 +6405,10 @@
         <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G96" s="7" t="n"/>
+      <c r="G96" s="8">
+        <f>IF(A96="","",N96)</f>
+        <v/>
+      </c>
       <c r="H96" s="8">
         <f>IF(A96="","",Inputs!$B$3/((IF(G96="",Inputs!$B$14,G96)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5253,6 +6419,15 @@
       </c>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="9">
+        <f>IF(A96="","",IF(OR(J96="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J96,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N96" s="9">
+        <f>IF(A96="","",IF(L96="",Inputs!$B$14,L96)+M96)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -5264,7 +6439,10 @@
         <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G97" s="7" t="n"/>
+      <c r="G97" s="8">
+        <f>IF(A97="","",N97)</f>
+        <v/>
+      </c>
       <c r="H97" s="8">
         <f>IF(A97="","",Inputs!$B$3/((IF(G97="",Inputs!$B$14,G97)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5275,6 +6453,15 @@
       </c>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="9">
+        <f>IF(A97="","",IF(OR(J97="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J97,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N97" s="9">
+        <f>IF(A97="","",IF(L97="",Inputs!$B$14,L97)+M97)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -5286,7 +6473,10 @@
         <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G98" s="7" t="n"/>
+      <c r="G98" s="8">
+        <f>IF(A98="","",N98)</f>
+        <v/>
+      </c>
       <c r="H98" s="8">
         <f>IF(A98="","",Inputs!$B$3/((IF(G98="",Inputs!$B$14,G98)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5297,6 +6487,15 @@
       </c>
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="9">
+        <f>IF(A98="","",IF(OR(J98="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J98,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N98" s="9">
+        <f>IF(A98="","",IF(L98="",Inputs!$B$14,L98)+M98)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n"/>
@@ -5308,7 +6507,10 @@
         <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G99" s="7" t="n"/>
+      <c r="G99" s="8">
+        <f>IF(A99="","",N99)</f>
+        <v/>
+      </c>
       <c r="H99" s="8">
         <f>IF(A99="","",Inputs!$B$3/((IF(G99="",Inputs!$B$14,G99)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5319,6 +6521,15 @@
       </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
+      <c r="L99" s="5" t="n"/>
+      <c r="M99" s="9">
+        <f>IF(A99="","",IF(OR(J99="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J99,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N99" s="9">
+        <f>IF(A99="","",IF(L99="",Inputs!$B$14,L99)+M99)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
@@ -5330,7 +6541,10 @@
         <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G100" s="7" t="n"/>
+      <c r="G100" s="8">
+        <f>IF(A100="","",N100)</f>
+        <v/>
+      </c>
       <c r="H100" s="8">
         <f>IF(A100="","",Inputs!$B$3/((IF(G100="",Inputs!$B$14,G100)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5341,6 +6555,15 @@
       </c>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="9">
+        <f>IF(A100="","",IF(OR(J100="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J100,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N100" s="9">
+        <f>IF(A100="","",IF(L100="",Inputs!$B$14,L100)+M100)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
@@ -5352,7 +6575,10 @@
         <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G101" s="7" t="n"/>
+      <c r="G101" s="8">
+        <f>IF(A101="","",N101)</f>
+        <v/>
+      </c>
       <c r="H101" s="8">
         <f>IF(A101="","",Inputs!$B$3/((IF(G101="",Inputs!$B$14,G101)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5363,6 +6589,15 @@
       </c>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="9">
+        <f>IF(A101="","",IF(OR(J101="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J101,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N101" s="9">
+        <f>IF(A101="","",IF(L101="",Inputs!$B$14,L101)+M101)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
@@ -5374,7 +6609,10 @@
         <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G102" s="7" t="n"/>
+      <c r="G102" s="8">
+        <f>IF(A102="","",N102)</f>
+        <v/>
+      </c>
       <c r="H102" s="8">
         <f>IF(A102="","",Inputs!$B$3/((IF(G102="",Inputs!$B$14,G102)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5385,6 +6623,15 @@
       </c>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="9">
+        <f>IF(A102="","",IF(OR(J102="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J102,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N102" s="9">
+        <f>IF(A102="","",IF(L102="",Inputs!$B$14,L102)+M102)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -5396,7 +6643,10 @@
         <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G103" s="7" t="n"/>
+      <c r="G103" s="8">
+        <f>IF(A103="","",N103)</f>
+        <v/>
+      </c>
       <c r="H103" s="8">
         <f>IF(A103="","",Inputs!$B$3/((IF(G103="",Inputs!$B$14,G103)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5407,6 +6657,15 @@
       </c>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="9">
+        <f>IF(A103="","",IF(OR(J103="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J103,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N103" s="9">
+        <f>IF(A103="","",IF(L103="",Inputs!$B$14,L103)+M103)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -5418,7 +6677,10 @@
         <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G104" s="7" t="n"/>
+      <c r="G104" s="8">
+        <f>IF(A104="","",N104)</f>
+        <v/>
+      </c>
       <c r="H104" s="8">
         <f>IF(A104="","",Inputs!$B$3/((IF(G104="",Inputs!$B$14,G104)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5429,6 +6691,15 @@
       </c>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="9">
+        <f>IF(A104="","",IF(OR(J104="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J104,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N104" s="9">
+        <f>IF(A104="","",IF(L104="",Inputs!$B$14,L104)+M104)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
@@ -5440,7 +6711,10 @@
         <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G105" s="7" t="n"/>
+      <c r="G105" s="8">
+        <f>IF(A105="","",N105)</f>
+        <v/>
+      </c>
       <c r="H105" s="8">
         <f>IF(A105="","",Inputs!$B$3/((IF(G105="",Inputs!$B$14,G105)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5451,6 +6725,15 @@
       </c>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="9">
+        <f>IF(A105="","",IF(OR(J105="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J105,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N105" s="9">
+        <f>IF(A105="","",IF(L105="",Inputs!$B$14,L105)+M105)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
@@ -5462,7 +6745,10 @@
         <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G106" s="7" t="n"/>
+      <c r="G106" s="8">
+        <f>IF(A106="","",N106)</f>
+        <v/>
+      </c>
       <c r="H106" s="8">
         <f>IF(A106="","",Inputs!$B$3/((IF(G106="",Inputs!$B$14,G106)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5473,6 +6759,15 @@
       </c>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="9">
+        <f>IF(A106="","",IF(OR(J106="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J106,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N106" s="9">
+        <f>IF(A106="","",IF(L106="",Inputs!$B$14,L106)+M106)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
@@ -5484,7 +6779,10 @@
         <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G107" s="7" t="n"/>
+      <c r="G107" s="8">
+        <f>IF(A107="","",N107)</f>
+        <v/>
+      </c>
       <c r="H107" s="8">
         <f>IF(A107="","",Inputs!$B$3/((IF(G107="",Inputs!$B$14,G107)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5495,6 +6793,15 @@
       </c>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="9">
+        <f>IF(A107="","",IF(OR(J107="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J107,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N107" s="9">
+        <f>IF(A107="","",IF(L107="",Inputs!$B$14,L107)+M107)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
@@ -5506,7 +6813,10 @@
         <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G108" s="7" t="n"/>
+      <c r="G108" s="8">
+        <f>IF(A108="","",N108)</f>
+        <v/>
+      </c>
       <c r="H108" s="8">
         <f>IF(A108="","",Inputs!$B$3/((IF(G108="",Inputs!$B$14,G108)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5517,6 +6827,15 @@
       </c>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
+      <c r="L108" s="5" t="n"/>
+      <c r="M108" s="9">
+        <f>IF(A108="","",IF(OR(J108="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J108,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N108" s="9">
+        <f>IF(A108="","",IF(L108="",Inputs!$B$14,L108)+M108)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n"/>
@@ -5528,7 +6847,10 @@
         <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G109" s="7" t="n"/>
+      <c r="G109" s="8">
+        <f>IF(A109="","",N109)</f>
+        <v/>
+      </c>
       <c r="H109" s="8">
         <f>IF(A109="","",Inputs!$B$3/((IF(G109="",Inputs!$B$14,G109)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5539,6 +6861,15 @@
       </c>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
+      <c r="L109" s="5" t="n"/>
+      <c r="M109" s="9">
+        <f>IF(A109="","",IF(OR(J109="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J109,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N109" s="9">
+        <f>IF(A109="","",IF(L109="",Inputs!$B$14,L109)+M109)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n"/>
@@ -5550,7 +6881,10 @@
         <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G110" s="7" t="n"/>
+      <c r="G110" s="8">
+        <f>IF(A110="","",N110)</f>
+        <v/>
+      </c>
       <c r="H110" s="8">
         <f>IF(A110="","",Inputs!$B$3/((IF(G110="",Inputs!$B$14,G110)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5561,6 +6895,15 @@
       </c>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="9">
+        <f>IF(A110="","",IF(OR(J110="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J110,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N110" s="9">
+        <f>IF(A110="","",IF(L110="",Inputs!$B$14,L110)+M110)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
@@ -5572,7 +6915,10 @@
         <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G111" s="7" t="n"/>
+      <c r="G111" s="8">
+        <f>IF(A111="","",N111)</f>
+        <v/>
+      </c>
       <c r="H111" s="8">
         <f>IF(A111="","",Inputs!$B$3/((IF(G111="",Inputs!$B$14,G111)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5583,6 +6929,15 @@
       </c>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
+      <c r="L111" s="5" t="n"/>
+      <c r="M111" s="9">
+        <f>IF(A111="","",IF(OR(J111="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J111,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N111" s="9">
+        <f>IF(A111="","",IF(L111="",Inputs!$B$14,L111)+M111)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -5594,7 +6949,10 @@
         <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G112" s="7" t="n"/>
+      <c r="G112" s="8">
+        <f>IF(A112="","",N112)</f>
+        <v/>
+      </c>
       <c r="H112" s="8">
         <f>IF(A112="","",Inputs!$B$3/((IF(G112="",Inputs!$B$14,G112)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5605,6 +6963,15 @@
       </c>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="9">
+        <f>IF(A112="","",IF(OR(J112="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J112,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N112" s="9">
+        <f>IF(A112="","",IF(L112="",Inputs!$B$14,L112)+M112)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
@@ -5616,7 +6983,10 @@
         <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G113" s="7" t="n"/>
+      <c r="G113" s="8">
+        <f>IF(A113="","",N113)</f>
+        <v/>
+      </c>
       <c r="H113" s="8">
         <f>IF(A113="","",Inputs!$B$3/((IF(G113="",Inputs!$B$14,G113)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5627,6 +6997,15 @@
       </c>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="9">
+        <f>IF(A113="","",IF(OR(J113="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J113,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N113" s="9">
+        <f>IF(A113="","",IF(L113="",Inputs!$B$14,L113)+M113)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
@@ -5638,7 +7017,10 @@
         <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G114" s="7" t="n"/>
+      <c r="G114" s="8">
+        <f>IF(A114="","",N114)</f>
+        <v/>
+      </c>
       <c r="H114" s="8">
         <f>IF(A114="","",Inputs!$B$3/((IF(G114="",Inputs!$B$14,G114)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5649,6 +7031,15 @@
       </c>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="9">
+        <f>IF(A114="","",IF(OR(J114="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J114,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N114" s="9">
+        <f>IF(A114="","",IF(L114="",Inputs!$B$14,L114)+M114)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
@@ -5660,7 +7051,10 @@
         <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G115" s="7" t="n"/>
+      <c r="G115" s="8">
+        <f>IF(A115="","",N115)</f>
+        <v/>
+      </c>
       <c r="H115" s="8">
         <f>IF(A115="","",Inputs!$B$3/((IF(G115="",Inputs!$B$14,G115)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5671,6 +7065,15 @@
       </c>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="9">
+        <f>IF(A115="","",IF(OR(J115="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J115,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N115" s="9">
+        <f>IF(A115="","",IF(L115="",Inputs!$B$14,L115)+M115)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n"/>
@@ -5682,7 +7085,10 @@
         <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G116" s="7" t="n"/>
+      <c r="G116" s="8">
+        <f>IF(A116="","",N116)</f>
+        <v/>
+      </c>
       <c r="H116" s="8">
         <f>IF(A116="","",Inputs!$B$3/((IF(G116="",Inputs!$B$14,G116)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5693,6 +7099,15 @@
       </c>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
+      <c r="L116" s="5" t="n"/>
+      <c r="M116" s="9">
+        <f>IF(A116="","",IF(OR(J116="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J116,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N116" s="9">
+        <f>IF(A116="","",IF(L116="",Inputs!$B$14,L116)+M116)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n"/>
@@ -5704,7 +7119,10 @@
         <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G117" s="7" t="n"/>
+      <c r="G117" s="8">
+        <f>IF(A117="","",N117)</f>
+        <v/>
+      </c>
       <c r="H117" s="8">
         <f>IF(A117="","",Inputs!$B$3/((IF(G117="",Inputs!$B$14,G117)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5715,6 +7133,15 @@
       </c>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
+      <c r="L117" s="5" t="n"/>
+      <c r="M117" s="9">
+        <f>IF(A117="","",IF(OR(J117="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J117,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N117" s="9">
+        <f>IF(A117="","",IF(L117="",Inputs!$B$14,L117)+M117)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n"/>
@@ -5726,7 +7153,10 @@
         <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G118" s="7" t="n"/>
+      <c r="G118" s="8">
+        <f>IF(A118="","",N118)</f>
+        <v/>
+      </c>
       <c r="H118" s="8">
         <f>IF(A118="","",Inputs!$B$3/((IF(G118="",Inputs!$B$14,G118)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5737,6 +7167,15 @@
       </c>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
+      <c r="L118" s="5" t="n"/>
+      <c r="M118" s="9">
+        <f>IF(A118="","",IF(OR(J118="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J118,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N118" s="9">
+        <f>IF(A118="","",IF(L118="",Inputs!$B$14,L118)+M118)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n"/>
@@ -5748,7 +7187,10 @@
         <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G119" s="7" t="n"/>
+      <c r="G119" s="8">
+        <f>IF(A119="","",N119)</f>
+        <v/>
+      </c>
       <c r="H119" s="8">
         <f>IF(A119="","",Inputs!$B$3/((IF(G119="",Inputs!$B$14,G119)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5759,6 +7201,15 @@
       </c>
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n"/>
+      <c r="L119" s="5" t="n"/>
+      <c r="M119" s="9">
+        <f>IF(A119="","",IF(OR(J119="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J119,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N119" s="9">
+        <f>IF(A119="","",IF(L119="",Inputs!$B$14,L119)+M119)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n"/>
@@ -5770,7 +7221,10 @@
         <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G120" s="7" t="n"/>
+      <c r="G120" s="8">
+        <f>IF(A120="","",N120)</f>
+        <v/>
+      </c>
       <c r="H120" s="8">
         <f>IF(A120="","",Inputs!$B$3/((IF(G120="",Inputs!$B$14,G120)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5781,6 +7235,15 @@
       </c>
       <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="9">
+        <f>IF(A120="","",IF(OR(J120="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J120,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N120" s="9">
+        <f>IF(A120="","",IF(L120="",Inputs!$B$14,L120)+M120)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n"/>
@@ -5792,7 +7255,10 @@
         <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G121" s="7" t="n"/>
+      <c r="G121" s="8">
+        <f>IF(A121="","",N121)</f>
+        <v/>
+      </c>
       <c r="H121" s="8">
         <f>IF(A121="","",Inputs!$B$3/((IF(G121="",Inputs!$B$14,G121)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5803,6 +7269,15 @@
       </c>
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="9">
+        <f>IF(A121="","",IF(OR(J121="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J121,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N121" s="9">
+        <f>IF(A121="","",IF(L121="",Inputs!$B$14,L121)+M121)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -5814,7 +7289,10 @@
         <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G122" s="7" t="n"/>
+      <c r="G122" s="8">
+        <f>IF(A122="","",N122)</f>
+        <v/>
+      </c>
       <c r="H122" s="8">
         <f>IF(A122="","",Inputs!$B$3/((IF(G122="",Inputs!$B$14,G122)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5825,6 +7303,15 @@
       </c>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="9">
+        <f>IF(A122="","",IF(OR(J122="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J122,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N122" s="9">
+        <f>IF(A122="","",IF(L122="",Inputs!$B$14,L122)+M122)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n"/>
@@ -5836,7 +7323,10 @@
         <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G123" s="7" t="n"/>
+      <c r="G123" s="8">
+        <f>IF(A123="","",N123)</f>
+        <v/>
+      </c>
       <c r="H123" s="8">
         <f>IF(A123="","",Inputs!$B$3/((IF(G123="",Inputs!$B$14,G123)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5847,6 +7337,15 @@
       </c>
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
+      <c r="L123" s="5" t="n"/>
+      <c r="M123" s="9">
+        <f>IF(A123="","",IF(OR(J123="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J123,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N123" s="9">
+        <f>IF(A123="","",IF(L123="",Inputs!$B$14,L123)+M123)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n"/>
@@ -5858,7 +7357,10 @@
         <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G124" s="7" t="n"/>
+      <c r="G124" s="8">
+        <f>IF(A124="","",N124)</f>
+        <v/>
+      </c>
       <c r="H124" s="8">
         <f>IF(A124="","",Inputs!$B$3/((IF(G124="",Inputs!$B$14,G124)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5869,6 +7371,15 @@
       </c>
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="9">
+        <f>IF(A124="","",IF(OR(J124="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J124,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N124" s="9">
+        <f>IF(A124="","",IF(L124="",Inputs!$B$14,L124)+M124)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -5880,7 +7391,10 @@
         <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G125" s="7" t="n"/>
+      <c r="G125" s="8">
+        <f>IF(A125="","",N125)</f>
+        <v/>
+      </c>
       <c r="H125" s="8">
         <f>IF(A125="","",Inputs!$B$3/((IF(G125="",Inputs!$B$14,G125)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5891,6 +7405,15 @@
       </c>
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="9">
+        <f>IF(A125="","",IF(OR(J125="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J125,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N125" s="9">
+        <f>IF(A125="","",IF(L125="",Inputs!$B$14,L125)+M125)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -5902,7 +7425,10 @@
         <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G126" s="7" t="n"/>
+      <c r="G126" s="8">
+        <f>IF(A126="","",N126)</f>
+        <v/>
+      </c>
       <c r="H126" s="8">
         <f>IF(A126="","",Inputs!$B$3/((IF(G126="",Inputs!$B$14,G126)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5913,6 +7439,15 @@
       </c>
       <c r="J126" s="4" t="n"/>
       <c r="K126" s="4" t="n"/>
+      <c r="L126" s="5" t="n"/>
+      <c r="M126" s="9">
+        <f>IF(A126="","",IF(OR(J126="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J126,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N126" s="9">
+        <f>IF(A126="","",IF(L126="",Inputs!$B$14,L126)+M126)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n"/>
@@ -5924,7 +7459,10 @@
         <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G127" s="7" t="n"/>
+      <c r="G127" s="8">
+        <f>IF(A127="","",N127)</f>
+        <v/>
+      </c>
       <c r="H127" s="8">
         <f>IF(A127="","",Inputs!$B$3/((IF(G127="",Inputs!$B$14,G127)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5935,6 +7473,15 @@
       </c>
       <c r="J127" s="4" t="n"/>
       <c r="K127" s="4" t="n"/>
+      <c r="L127" s="5" t="n"/>
+      <c r="M127" s="9">
+        <f>IF(A127="","",IF(OR(J127="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J127,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N127" s="9">
+        <f>IF(A127="","",IF(L127="",Inputs!$B$14,L127)+M127)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n"/>
@@ -5946,7 +7493,10 @@
         <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G128" s="7" t="n"/>
+      <c r="G128" s="8">
+        <f>IF(A128="","",N128)</f>
+        <v/>
+      </c>
       <c r="H128" s="8">
         <f>IF(A128="","",Inputs!$B$3/((IF(G128="",Inputs!$B$14,G128)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5957,6 +7507,15 @@
       </c>
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="9">
+        <f>IF(A128="","",IF(OR(J128="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J128,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N128" s="9">
+        <f>IF(A128="","",IF(L128="",Inputs!$B$14,L128)+M128)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n"/>
@@ -5968,7 +7527,10 @@
         <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G129" s="7" t="n"/>
+      <c r="G129" s="8">
+        <f>IF(A129="","",N129)</f>
+        <v/>
+      </c>
       <c r="H129" s="8">
         <f>IF(A129="","",Inputs!$B$3/((IF(G129="",Inputs!$B$14,G129)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -5979,6 +7541,15 @@
       </c>
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
+      <c r="L129" s="5" t="n"/>
+      <c r="M129" s="9">
+        <f>IF(A129="","",IF(OR(J129="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J129,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N129" s="9">
+        <f>IF(A129="","",IF(L129="",Inputs!$B$14,L129)+M129)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n"/>
@@ -5990,7 +7561,10 @@
         <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G130" s="7" t="n"/>
+      <c r="G130" s="8">
+        <f>IF(A130="","",N130)</f>
+        <v/>
+      </c>
       <c r="H130" s="8">
         <f>IF(A130="","",Inputs!$B$3/((IF(G130="",Inputs!$B$14,G130)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6001,6 +7575,15 @@
       </c>
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="9">
+        <f>IF(A130="","",IF(OR(J130="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J130,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N130" s="9">
+        <f>IF(A130="","",IF(L130="",Inputs!$B$14,L130)+M130)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n"/>
@@ -6012,7 +7595,10 @@
         <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G131" s="7" t="n"/>
+      <c r="G131" s="8">
+        <f>IF(A131="","",N131)</f>
+        <v/>
+      </c>
       <c r="H131" s="8">
         <f>IF(A131="","",Inputs!$B$3/((IF(G131="",Inputs!$B$14,G131)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6023,6 +7609,15 @@
       </c>
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="9">
+        <f>IF(A131="","",IF(OR(J131="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J131,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N131" s="9">
+        <f>IF(A131="","",IF(L131="",Inputs!$B$14,L131)+M131)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n"/>
@@ -6034,7 +7629,10 @@
         <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G132" s="7" t="n"/>
+      <c r="G132" s="8">
+        <f>IF(A132="","",N132)</f>
+        <v/>
+      </c>
       <c r="H132" s="8">
         <f>IF(A132="","",Inputs!$B$3/((IF(G132="",Inputs!$B$14,G132)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6045,6 +7643,15 @@
       </c>
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="9">
+        <f>IF(A132="","",IF(OR(J132="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J132,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N132" s="9">
+        <f>IF(A132="","",IF(L132="",Inputs!$B$14,L132)+M132)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n"/>
@@ -6056,7 +7663,10 @@
         <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G133" s="7" t="n"/>
+      <c r="G133" s="8">
+        <f>IF(A133="","",N133)</f>
+        <v/>
+      </c>
       <c r="H133" s="8">
         <f>IF(A133="","",Inputs!$B$3/((IF(G133="",Inputs!$B$14,G133)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6067,6 +7677,15 @@
       </c>
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="4" t="n"/>
+      <c r="L133" s="5" t="n"/>
+      <c r="M133" s="9">
+        <f>IF(A133="","",IF(OR(J133="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J133,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N133" s="9">
+        <f>IF(A133="","",IF(L133="",Inputs!$B$14,L133)+M133)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n"/>
@@ -6078,7 +7697,10 @@
         <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G134" s="7" t="n"/>
+      <c r="G134" s="8">
+        <f>IF(A134="","",N134)</f>
+        <v/>
+      </c>
       <c r="H134" s="8">
         <f>IF(A134="","",Inputs!$B$3/((IF(G134="",Inputs!$B$14,G134)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6089,6 +7711,15 @@
       </c>
       <c r="J134" s="4" t="n"/>
       <c r="K134" s="4" t="n"/>
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="9">
+        <f>IF(A134="","",IF(OR(J134="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J134,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N134" s="9">
+        <f>IF(A134="","",IF(L134="",Inputs!$B$14,L134)+M134)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n"/>
@@ -6100,7 +7731,10 @@
         <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G135" s="7" t="n"/>
+      <c r="G135" s="8">
+        <f>IF(A135="","",N135)</f>
+        <v/>
+      </c>
       <c r="H135" s="8">
         <f>IF(A135="","",Inputs!$B$3/((IF(G135="",Inputs!$B$14,G135)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6111,6 +7745,15 @@
       </c>
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="9">
+        <f>IF(A135="","",IF(OR(J135="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J135,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N135" s="9">
+        <f>IF(A135="","",IF(L135="",Inputs!$B$14,L135)+M135)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n"/>
@@ -6122,7 +7765,10 @@
         <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G136" s="7" t="n"/>
+      <c r="G136" s="8">
+        <f>IF(A136="","",N136)</f>
+        <v/>
+      </c>
       <c r="H136" s="8">
         <f>IF(A136="","",Inputs!$B$3/((IF(G136="",Inputs!$B$14,G136)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6133,6 +7779,15 @@
       </c>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="9">
+        <f>IF(A136="","",IF(OR(J136="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J136,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N136" s="9">
+        <f>IF(A136="","",IF(L136="",Inputs!$B$14,L136)+M136)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -6144,7 +7799,10 @@
         <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G137" s="7" t="n"/>
+      <c r="G137" s="8">
+        <f>IF(A137="","",N137)</f>
+        <v/>
+      </c>
       <c r="H137" s="8">
         <f>IF(A137="","",Inputs!$B$3/((IF(G137="",Inputs!$B$14,G137)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6155,6 +7813,15 @@
       </c>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
+      <c r="L137" s="5" t="n"/>
+      <c r="M137" s="9">
+        <f>IF(A137="","",IF(OR(J137="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J137,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N137" s="9">
+        <f>IF(A137="","",IF(L137="",Inputs!$B$14,L137)+M137)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -6166,7 +7833,10 @@
         <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G138" s="7" t="n"/>
+      <c r="G138" s="8">
+        <f>IF(A138="","",N138)</f>
+        <v/>
+      </c>
       <c r="H138" s="8">
         <f>IF(A138="","",Inputs!$B$3/((IF(G138="",Inputs!$B$14,G138)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6177,6 +7847,15 @@
       </c>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
+      <c r="L138" s="5" t="n"/>
+      <c r="M138" s="9">
+        <f>IF(A138="","",IF(OR(J138="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J138,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N138" s="9">
+        <f>IF(A138="","",IF(L138="",Inputs!$B$14,L138)+M138)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n"/>
@@ -6188,7 +7867,10 @@
         <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G139" s="7" t="n"/>
+      <c r="G139" s="8">
+        <f>IF(A139="","",N139)</f>
+        <v/>
+      </c>
       <c r="H139" s="8">
         <f>IF(A139="","",Inputs!$B$3/((IF(G139="",Inputs!$B$14,G139)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6199,6 +7881,15 @@
       </c>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
+      <c r="L139" s="5" t="n"/>
+      <c r="M139" s="9">
+        <f>IF(A139="","",IF(OR(J139="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J139,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N139" s="9">
+        <f>IF(A139="","",IF(L139="",Inputs!$B$14,L139)+M139)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n"/>
@@ -6210,7 +7901,10 @@
         <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G140" s="7" t="n"/>
+      <c r="G140" s="8">
+        <f>IF(A140="","",N140)</f>
+        <v/>
+      </c>
       <c r="H140" s="8">
         <f>IF(A140="","",Inputs!$B$3/((IF(G140="",Inputs!$B$14,G140)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6221,6 +7915,15 @@
       </c>
       <c r="J140" s="4" t="n"/>
       <c r="K140" s="4" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="9">
+        <f>IF(A140="","",IF(OR(J140="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J140,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N140" s="9">
+        <f>IF(A140="","",IF(L140="",Inputs!$B$14,L140)+M140)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n"/>
@@ -6232,7 +7935,10 @@
         <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G141" s="7" t="n"/>
+      <c r="G141" s="8">
+        <f>IF(A141="","",N141)</f>
+        <v/>
+      </c>
       <c r="H141" s="8">
         <f>IF(A141="","",Inputs!$B$3/((IF(G141="",Inputs!$B$14,G141)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6243,6 +7949,15 @@
       </c>
       <c r="J141" s="4" t="n"/>
       <c r="K141" s="4" t="n"/>
+      <c r="L141" s="5" t="n"/>
+      <c r="M141" s="9">
+        <f>IF(A141="","",IF(OR(J141="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J141,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N141" s="9">
+        <f>IF(A141="","",IF(L141="",Inputs!$B$14,L141)+M141)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
@@ -6254,7 +7969,10 @@
         <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G142" s="7" t="n"/>
+      <c r="G142" s="8">
+        <f>IF(A142="","",N142)</f>
+        <v/>
+      </c>
       <c r="H142" s="8">
         <f>IF(A142="","",Inputs!$B$3/((IF(G142="",Inputs!$B$14,G142)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6265,6 +7983,15 @@
       </c>
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
+      <c r="L142" s="5" t="n"/>
+      <c r="M142" s="9">
+        <f>IF(A142="","",IF(OR(J142="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J142,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N142" s="9">
+        <f>IF(A142="","",IF(L142="",Inputs!$B$14,L142)+M142)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
@@ -6276,7 +8003,10 @@
         <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G143" s="7" t="n"/>
+      <c r="G143" s="8">
+        <f>IF(A143="","",N143)</f>
+        <v/>
+      </c>
       <c r="H143" s="8">
         <f>IF(A143="","",Inputs!$B$3/((IF(G143="",Inputs!$B$14,G143)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6287,6 +8017,15 @@
       </c>
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
+      <c r="L143" s="5" t="n"/>
+      <c r="M143" s="9">
+        <f>IF(A143="","",IF(OR(J143="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J143,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N143" s="9">
+        <f>IF(A143="","",IF(L143="",Inputs!$B$14,L143)+M143)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
@@ -6298,7 +8037,10 @@
         <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G144" s="7" t="n"/>
+      <c r="G144" s="8">
+        <f>IF(A144="","",N144)</f>
+        <v/>
+      </c>
       <c r="H144" s="8">
         <f>IF(A144="","",Inputs!$B$3/((IF(G144="",Inputs!$B$14,G144)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6309,6 +8051,15 @@
       </c>
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
+      <c r="L144" s="5" t="n"/>
+      <c r="M144" s="9">
+        <f>IF(A144="","",IF(OR(J144="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J144,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N144" s="9">
+        <f>IF(A144="","",IF(L144="",Inputs!$B$14,L144)+M144)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
@@ -6320,7 +8071,10 @@
         <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G145" s="7" t="n"/>
+      <c r="G145" s="8">
+        <f>IF(A145="","",N145)</f>
+        <v/>
+      </c>
       <c r="H145" s="8">
         <f>IF(A145="","",Inputs!$B$3/((IF(G145="",Inputs!$B$14,G145)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6331,6 +8085,15 @@
       </c>
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="9">
+        <f>IF(A145="","",IF(OR(J145="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J145,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N145" s="9">
+        <f>IF(A145="","",IF(L145="",Inputs!$B$14,L145)+M145)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -6342,7 +8105,10 @@
         <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G146" s="7" t="n"/>
+      <c r="G146" s="8">
+        <f>IF(A146="","",N146)</f>
+        <v/>
+      </c>
       <c r="H146" s="8">
         <f>IF(A146="","",Inputs!$B$3/((IF(G146="",Inputs!$B$14,G146)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6353,6 +8119,15 @@
       </c>
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
+      <c r="L146" s="5" t="n"/>
+      <c r="M146" s="9">
+        <f>IF(A146="","",IF(OR(J146="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J146,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N146" s="9">
+        <f>IF(A146="","",IF(L146="",Inputs!$B$14,L146)+M146)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -6364,7 +8139,10 @@
         <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G147" s="7" t="n"/>
+      <c r="G147" s="8">
+        <f>IF(A147="","",N147)</f>
+        <v/>
+      </c>
       <c r="H147" s="8">
         <f>IF(A147="","",Inputs!$B$3/((IF(G147="",Inputs!$B$14,G147)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6375,6 +8153,15 @@
       </c>
       <c r="J147" s="4" t="n"/>
       <c r="K147" s="4" t="n"/>
+      <c r="L147" s="5" t="n"/>
+      <c r="M147" s="9">
+        <f>IF(A147="","",IF(OR(J147="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J147,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N147" s="9">
+        <f>IF(A147="","",IF(L147="",Inputs!$B$14,L147)+M147)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n"/>
@@ -6386,7 +8173,10 @@
         <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G148" s="7" t="n"/>
+      <c r="G148" s="8">
+        <f>IF(A148="","",N148)</f>
+        <v/>
+      </c>
       <c r="H148" s="8">
         <f>IF(A148="","",Inputs!$B$3/((IF(G148="",Inputs!$B$14,G148)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6397,6 +8187,15 @@
       </c>
       <c r="J148" s="4" t="n"/>
       <c r="K148" s="4" t="n"/>
+      <c r="L148" s="5" t="n"/>
+      <c r="M148" s="9">
+        <f>IF(A148="","",IF(OR(J148="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J148,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N148" s="9">
+        <f>IF(A148="","",IF(L148="",Inputs!$B$14,L148)+M148)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n"/>
@@ -6408,7 +8207,10 @@
         <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G149" s="7" t="n"/>
+      <c r="G149" s="8">
+        <f>IF(A149="","",N149)</f>
+        <v/>
+      </c>
       <c r="H149" s="8">
         <f>IF(A149="","",Inputs!$B$3/((IF(G149="",Inputs!$B$14,G149)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6419,6 +8221,15 @@
       </c>
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
+      <c r="L149" s="5" t="n"/>
+      <c r="M149" s="9">
+        <f>IF(A149="","",IF(OR(J149="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J149,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N149" s="9">
+        <f>IF(A149="","",IF(L149="",Inputs!$B$14,L149)+M149)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n"/>
@@ -6430,7 +8241,10 @@
         <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G150" s="7" t="n"/>
+      <c r="G150" s="8">
+        <f>IF(A150="","",N150)</f>
+        <v/>
+      </c>
       <c r="H150" s="8">
         <f>IF(A150="","",Inputs!$B$3/((IF(G150="",Inputs!$B$14,G150)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6441,6 +8255,15 @@
       </c>
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
+      <c r="L150" s="5" t="n"/>
+      <c r="M150" s="9">
+        <f>IF(A150="","",IF(OR(J150="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J150,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N150" s="9">
+        <f>IF(A150="","",IF(L150="",Inputs!$B$14,L150)+M150)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
@@ -6452,7 +8275,10 @@
         <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G151" s="7" t="n"/>
+      <c r="G151" s="8">
+        <f>IF(A151="","",N151)</f>
+        <v/>
+      </c>
       <c r="H151" s="8">
         <f>IF(A151="","",Inputs!$B$3/((IF(G151="",Inputs!$B$14,G151)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6463,6 +8289,15 @@
       </c>
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
+      <c r="L151" s="5" t="n"/>
+      <c r="M151" s="9">
+        <f>IF(A151="","",IF(OR(J151="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J151,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N151" s="9">
+        <f>IF(A151="","",IF(L151="",Inputs!$B$14,L151)+M151)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -6474,7 +8309,10 @@
         <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G152" s="7" t="n"/>
+      <c r="G152" s="8">
+        <f>IF(A152="","",N152)</f>
+        <v/>
+      </c>
       <c r="H152" s="8">
         <f>IF(A152="","",Inputs!$B$3/((IF(G152="",Inputs!$B$14,G152)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6485,6 +8323,15 @@
       </c>
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="9">
+        <f>IF(A152="","",IF(OR(J152="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J152,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N152" s="9">
+        <f>IF(A152="","",IF(L152="",Inputs!$B$14,L152)+M152)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
@@ -6496,7 +8343,10 @@
         <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G153" s="7" t="n"/>
+      <c r="G153" s="8">
+        <f>IF(A153="","",N153)</f>
+        <v/>
+      </c>
       <c r="H153" s="8">
         <f>IF(A153="","",Inputs!$B$3/((IF(G153="",Inputs!$B$14,G153)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6507,6 +8357,15 @@
       </c>
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
+      <c r="L153" s="5" t="n"/>
+      <c r="M153" s="9">
+        <f>IF(A153="","",IF(OR(J153="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J153,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N153" s="9">
+        <f>IF(A153="","",IF(L153="",Inputs!$B$14,L153)+M153)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
@@ -6518,7 +8377,10 @@
         <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G154" s="7" t="n"/>
+      <c r="G154" s="8">
+        <f>IF(A154="","",N154)</f>
+        <v/>
+      </c>
       <c r="H154" s="8">
         <f>IF(A154="","",Inputs!$B$3/((IF(G154="",Inputs!$B$14,G154)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6529,6 +8391,15 @@
       </c>
       <c r="J154" s="4" t="n"/>
       <c r="K154" s="4" t="n"/>
+      <c r="L154" s="5" t="n"/>
+      <c r="M154" s="9">
+        <f>IF(A154="","",IF(OR(J154="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J154,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N154" s="9">
+        <f>IF(A154="","",IF(L154="",Inputs!$B$14,L154)+M154)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
@@ -6540,7 +8411,10 @@
         <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G155" s="7" t="n"/>
+      <c r="G155" s="8">
+        <f>IF(A155="","",N155)</f>
+        <v/>
+      </c>
       <c r="H155" s="8">
         <f>IF(A155="","",Inputs!$B$3/((IF(G155="",Inputs!$B$14,G155)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6551,6 +8425,15 @@
       </c>
       <c r="J155" s="4" t="n"/>
       <c r="K155" s="4" t="n"/>
+      <c r="L155" s="5" t="n"/>
+      <c r="M155" s="9">
+        <f>IF(A155="","",IF(OR(J155="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J155,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N155" s="9">
+        <f>IF(A155="","",IF(L155="",Inputs!$B$14,L155)+M155)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -6562,7 +8445,10 @@
         <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G156" s="7" t="n"/>
+      <c r="G156" s="8">
+        <f>IF(A156="","",N156)</f>
+        <v/>
+      </c>
       <c r="H156" s="8">
         <f>IF(A156="","",Inputs!$B$3/((IF(G156="",Inputs!$B$14,G156)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6573,6 +8459,15 @@
       </c>
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="9">
+        <f>IF(A156="","",IF(OR(J156="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J156,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N156" s="9">
+        <f>IF(A156="","",IF(L156="",Inputs!$B$14,L156)+M156)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -6584,7 +8479,10 @@
         <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G157" s="7" t="n"/>
+      <c r="G157" s="8">
+        <f>IF(A157="","",N157)</f>
+        <v/>
+      </c>
       <c r="H157" s="8">
         <f>IF(A157="","",Inputs!$B$3/((IF(G157="",Inputs!$B$14,G157)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6595,6 +8493,15 @@
       </c>
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
+      <c r="L157" s="5" t="n"/>
+      <c r="M157" s="9">
+        <f>IF(A157="","",IF(OR(J157="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J157,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N157" s="9">
+        <f>IF(A157="","",IF(L157="",Inputs!$B$14,L157)+M157)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -6606,7 +8513,10 @@
         <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G158" s="7" t="n"/>
+      <c r="G158" s="8">
+        <f>IF(A158="","",N158)</f>
+        <v/>
+      </c>
       <c r="H158" s="8">
         <f>IF(A158="","",Inputs!$B$3/((IF(G158="",Inputs!$B$14,G158)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6617,6 +8527,15 @@
       </c>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
+      <c r="L158" s="5" t="n"/>
+      <c r="M158" s="9">
+        <f>IF(A158="","",IF(OR(J158="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J158,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N158" s="9">
+        <f>IF(A158="","",IF(L158="",Inputs!$B$14,L158)+M158)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n"/>
@@ -6628,7 +8547,10 @@
         <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G159" s="7" t="n"/>
+      <c r="G159" s="8">
+        <f>IF(A159="","",N159)</f>
+        <v/>
+      </c>
       <c r="H159" s="8">
         <f>IF(A159="","",Inputs!$B$3/((IF(G159="",Inputs!$B$14,G159)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6639,6 +8561,15 @@
       </c>
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="9">
+        <f>IF(A159="","",IF(OR(J159="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J159,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N159" s="9">
+        <f>IF(A159="","",IF(L159="",Inputs!$B$14,L159)+M159)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
@@ -6650,7 +8581,10 @@
         <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G160" s="7" t="n"/>
+      <c r="G160" s="8">
+        <f>IF(A160="","",N160)</f>
+        <v/>
+      </c>
       <c r="H160" s="8">
         <f>IF(A160="","",Inputs!$B$3/((IF(G160="",Inputs!$B$14,G160)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6661,6 +8595,15 @@
       </c>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
+      <c r="L160" s="5" t="n"/>
+      <c r="M160" s="9">
+        <f>IF(A160="","",IF(OR(J160="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J160,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N160" s="9">
+        <f>IF(A160="","",IF(L160="",Inputs!$B$14,L160)+M160)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
@@ -6672,7 +8615,10 @@
         <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G161" s="7" t="n"/>
+      <c r="G161" s="8">
+        <f>IF(A161="","",N161)</f>
+        <v/>
+      </c>
       <c r="H161" s="8">
         <f>IF(A161="","",Inputs!$B$3/((IF(G161="",Inputs!$B$14,G161)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6683,6 +8629,15 @@
       </c>
       <c r="J161" s="4" t="n"/>
       <c r="K161" s="4" t="n"/>
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="9">
+        <f>IF(A161="","",IF(OR(J161="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J161,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N161" s="9">
+        <f>IF(A161="","",IF(L161="",Inputs!$B$14,L161)+M161)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -6694,7 +8649,10 @@
         <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G162" s="7" t="n"/>
+      <c r="G162" s="8">
+        <f>IF(A162="","",N162)</f>
+        <v/>
+      </c>
       <c r="H162" s="8">
         <f>IF(A162="","",Inputs!$B$3/((IF(G162="",Inputs!$B$14,G162)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6705,6 +8663,15 @@
       </c>
       <c r="J162" s="4" t="n"/>
       <c r="K162" s="4" t="n"/>
+      <c r="L162" s="5" t="n"/>
+      <c r="M162" s="9">
+        <f>IF(A162="","",IF(OR(J162="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J162,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N162" s="9">
+        <f>IF(A162="","",IF(L162="",Inputs!$B$14,L162)+M162)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -6716,7 +8683,10 @@
         <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G163" s="7" t="n"/>
+      <c r="G163" s="8">
+        <f>IF(A163="","",N163)</f>
+        <v/>
+      </c>
       <c r="H163" s="8">
         <f>IF(A163="","",Inputs!$B$3/((IF(G163="",Inputs!$B$14,G163)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6727,6 +8697,15 @@
       </c>
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
+      <c r="L163" s="5" t="n"/>
+      <c r="M163" s="9">
+        <f>IF(A163="","",IF(OR(J163="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J163,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N163" s="9">
+        <f>IF(A163="","",IF(L163="",Inputs!$B$14,L163)+M163)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -6738,7 +8717,10 @@
         <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G164" s="7" t="n"/>
+      <c r="G164" s="8">
+        <f>IF(A164="","",N164)</f>
+        <v/>
+      </c>
       <c r="H164" s="8">
         <f>IF(A164="","",Inputs!$B$3/((IF(G164="",Inputs!$B$14,G164)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6749,6 +8731,15 @@
       </c>
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
+      <c r="L164" s="5" t="n"/>
+      <c r="M164" s="9">
+        <f>IF(A164="","",IF(OR(J164="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J164,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N164" s="9">
+        <f>IF(A164="","",IF(L164="",Inputs!$B$14,L164)+M164)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -6760,7 +8751,10 @@
         <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G165" s="7" t="n"/>
+      <c r="G165" s="8">
+        <f>IF(A165="","",N165)</f>
+        <v/>
+      </c>
       <c r="H165" s="8">
         <f>IF(A165="","",Inputs!$B$3/((IF(G165="",Inputs!$B$14,G165)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6771,6 +8765,15 @@
       </c>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
+      <c r="L165" s="5" t="n"/>
+      <c r="M165" s="9">
+        <f>IF(A165="","",IF(OR(J165="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J165,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N165" s="9">
+        <f>IF(A165="","",IF(L165="",Inputs!$B$14,L165)+M165)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -6782,7 +8785,10 @@
         <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G166" s="7" t="n"/>
+      <c r="G166" s="8">
+        <f>IF(A166="","",N166)</f>
+        <v/>
+      </c>
       <c r="H166" s="8">
         <f>IF(A166="","",Inputs!$B$3/((IF(G166="",Inputs!$B$14,G166)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6793,6 +8799,15 @@
       </c>
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
+      <c r="L166" s="5" t="n"/>
+      <c r="M166" s="9">
+        <f>IF(A166="","",IF(OR(J166="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J166,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N166" s="9">
+        <f>IF(A166="","",IF(L166="",Inputs!$B$14,L166)+M166)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -6804,7 +8819,10 @@
         <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G167" s="7" t="n"/>
+      <c r="G167" s="8">
+        <f>IF(A167="","",N167)</f>
+        <v/>
+      </c>
       <c r="H167" s="8">
         <f>IF(A167="","",Inputs!$B$3/((IF(G167="",Inputs!$B$14,G167)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6815,6 +8833,15 @@
       </c>
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="9">
+        <f>IF(A167="","",IF(OR(J167="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J167,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N167" s="9">
+        <f>IF(A167="","",IF(L167="",Inputs!$B$14,L167)+M167)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
@@ -6826,7 +8853,10 @@
         <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G168" s="7" t="n"/>
+      <c r="G168" s="8">
+        <f>IF(A168="","",N168)</f>
+        <v/>
+      </c>
       <c r="H168" s="8">
         <f>IF(A168="","",Inputs!$B$3/((IF(G168="",Inputs!$B$14,G168)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6837,6 +8867,15 @@
       </c>
       <c r="J168" s="4" t="n"/>
       <c r="K168" s="4" t="n"/>
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" s="9">
+        <f>IF(A168="","",IF(OR(J168="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J168,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N168" s="9">
+        <f>IF(A168="","",IF(L168="",Inputs!$B$14,L168)+M168)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -6848,7 +8887,10 @@
         <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G169" s="7" t="n"/>
+      <c r="G169" s="8">
+        <f>IF(A169="","",N169)</f>
+        <v/>
+      </c>
       <c r="H169" s="8">
         <f>IF(A169="","",Inputs!$B$3/((IF(G169="",Inputs!$B$14,G169)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6859,6 +8901,15 @@
       </c>
       <c r="J169" s="4" t="n"/>
       <c r="K169" s="4" t="n"/>
+      <c r="L169" s="5" t="n"/>
+      <c r="M169" s="9">
+        <f>IF(A169="","",IF(OR(J169="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J169,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N169" s="9">
+        <f>IF(A169="","",IF(L169="",Inputs!$B$14,L169)+M169)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -6870,7 +8921,10 @@
         <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G170" s="7" t="n"/>
+      <c r="G170" s="8">
+        <f>IF(A170="","",N170)</f>
+        <v/>
+      </c>
       <c r="H170" s="8">
         <f>IF(A170="","",Inputs!$B$3/((IF(G170="",Inputs!$B$14,G170)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6881,6 +8935,15 @@
       </c>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
+      <c r="L170" s="5" t="n"/>
+      <c r="M170" s="9">
+        <f>IF(A170="","",IF(OR(J170="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J170,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N170" s="9">
+        <f>IF(A170="","",IF(L170="",Inputs!$B$14,L170)+M170)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -6892,7 +8955,10 @@
         <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G171" s="7" t="n"/>
+      <c r="G171" s="8">
+        <f>IF(A171="","",N171)</f>
+        <v/>
+      </c>
       <c r="H171" s="8">
         <f>IF(A171="","",Inputs!$B$3/((IF(G171="",Inputs!$B$14,G171)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6903,6 +8969,15 @@
       </c>
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" s="9">
+        <f>IF(A171="","",IF(OR(J171="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J171,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N171" s="9">
+        <f>IF(A171="","",IF(L171="",Inputs!$B$14,L171)+M171)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -6914,7 +8989,10 @@
         <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G172" s="7" t="n"/>
+      <c r="G172" s="8">
+        <f>IF(A172="","",N172)</f>
+        <v/>
+      </c>
       <c r="H172" s="8">
         <f>IF(A172="","",Inputs!$B$3/((IF(G172="",Inputs!$B$14,G172)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6925,6 +9003,15 @@
       </c>
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
+      <c r="L172" s="5" t="n"/>
+      <c r="M172" s="9">
+        <f>IF(A172="","",IF(OR(J172="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J172,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N172" s="9">
+        <f>IF(A172="","",IF(L172="",Inputs!$B$14,L172)+M172)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n"/>
@@ -6936,7 +9023,10 @@
         <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G173" s="7" t="n"/>
+      <c r="G173" s="8">
+        <f>IF(A173="","",N173)</f>
+        <v/>
+      </c>
       <c r="H173" s="8">
         <f>IF(A173="","",Inputs!$B$3/((IF(G173="",Inputs!$B$14,G173)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6947,6 +9037,15 @@
       </c>
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
+      <c r="L173" s="5" t="n"/>
+      <c r="M173" s="9">
+        <f>IF(A173="","",IF(OR(J173="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J173,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N173" s="9">
+        <f>IF(A173="","",IF(L173="",Inputs!$B$14,L173)+M173)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
@@ -6958,7 +9057,10 @@
         <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G174" s="7" t="n"/>
+      <c r="G174" s="8">
+        <f>IF(A174="","",N174)</f>
+        <v/>
+      </c>
       <c r="H174" s="8">
         <f>IF(A174="","",Inputs!$B$3/((IF(G174="",Inputs!$B$14,G174)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6969,6 +9071,15 @@
       </c>
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" s="9">
+        <f>IF(A174="","",IF(OR(J174="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J174,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N174" s="9">
+        <f>IF(A174="","",IF(L174="",Inputs!$B$14,L174)+M174)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -6980,7 +9091,10 @@
         <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G175" s="7" t="n"/>
+      <c r="G175" s="8">
+        <f>IF(A175="","",N175)</f>
+        <v/>
+      </c>
       <c r="H175" s="8">
         <f>IF(A175="","",Inputs!$B$3/((IF(G175="",Inputs!$B$14,G175)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -6991,6 +9105,15 @@
       </c>
       <c r="J175" s="4" t="n"/>
       <c r="K175" s="4" t="n"/>
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" s="9">
+        <f>IF(A175="","",IF(OR(J175="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J175,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N175" s="9">
+        <f>IF(A175="","",IF(L175="",Inputs!$B$14,L175)+M175)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -7002,7 +9125,10 @@
         <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G176" s="7" t="n"/>
+      <c r="G176" s="8">
+        <f>IF(A176="","",N176)</f>
+        <v/>
+      </c>
       <c r="H176" s="8">
         <f>IF(A176="","",Inputs!$B$3/((IF(G176="",Inputs!$B$14,G176)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7013,6 +9139,15 @@
       </c>
       <c r="J176" s="4" t="n"/>
       <c r="K176" s="4" t="n"/>
+      <c r="L176" s="5" t="n"/>
+      <c r="M176" s="9">
+        <f>IF(A176="","",IF(OR(J176="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J176,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N176" s="9">
+        <f>IF(A176="","",IF(L176="",Inputs!$B$14,L176)+M176)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -7024,7 +9159,10 @@
         <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G177" s="7" t="n"/>
+      <c r="G177" s="8">
+        <f>IF(A177="","",N177)</f>
+        <v/>
+      </c>
       <c r="H177" s="8">
         <f>IF(A177="","",Inputs!$B$3/((IF(G177="",Inputs!$B$14,G177)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7035,6 +9173,15 @@
       </c>
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="9">
+        <f>IF(A177="","",IF(OR(J177="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J177,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N177" s="9">
+        <f>IF(A177="","",IF(L177="",Inputs!$B$14,L177)+M177)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n"/>
@@ -7046,7 +9193,10 @@
         <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G178" s="7" t="n"/>
+      <c r="G178" s="8">
+        <f>IF(A178="","",N178)</f>
+        <v/>
+      </c>
       <c r="H178" s="8">
         <f>IF(A178="","",Inputs!$B$3/((IF(G178="",Inputs!$B$14,G178)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7057,6 +9207,15 @@
       </c>
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
+      <c r="L178" s="5" t="n"/>
+      <c r="M178" s="9">
+        <f>IF(A178="","",IF(OR(J178="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J178,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N178" s="9">
+        <f>IF(A178="","",IF(L178="",Inputs!$B$14,L178)+M178)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -7068,7 +9227,10 @@
         <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G179" s="7" t="n"/>
+      <c r="G179" s="8">
+        <f>IF(A179="","",N179)</f>
+        <v/>
+      </c>
       <c r="H179" s="8">
         <f>IF(A179="","",Inputs!$B$3/((IF(G179="",Inputs!$B$14,G179)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7079,6 +9241,15 @@
       </c>
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" s="9">
+        <f>IF(A179="","",IF(OR(J179="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J179,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N179" s="9">
+        <f>IF(A179="","",IF(L179="",Inputs!$B$14,L179)+M179)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n"/>
@@ -7090,7 +9261,10 @@
         <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G180" s="7" t="n"/>
+      <c r="G180" s="8">
+        <f>IF(A180="","",N180)</f>
+        <v/>
+      </c>
       <c r="H180" s="8">
         <f>IF(A180="","",Inputs!$B$3/((IF(G180="",Inputs!$B$14,G180)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7101,6 +9275,15 @@
       </c>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
+      <c r="L180" s="5" t="n"/>
+      <c r="M180" s="9">
+        <f>IF(A180="","",IF(OR(J180="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J180,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N180" s="9">
+        <f>IF(A180="","",IF(L180="",Inputs!$B$14,L180)+M180)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -7112,7 +9295,10 @@
         <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G181" s="7" t="n"/>
+      <c r="G181" s="8">
+        <f>IF(A181="","",N181)</f>
+        <v/>
+      </c>
       <c r="H181" s="8">
         <f>IF(A181="","",Inputs!$B$3/((IF(G181="",Inputs!$B$14,G181)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7123,6 +9309,15 @@
       </c>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
+      <c r="L181" s="5" t="n"/>
+      <c r="M181" s="9">
+        <f>IF(A181="","",IF(OR(J181="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J181,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N181" s="9">
+        <f>IF(A181="","",IF(L181="",Inputs!$B$14,L181)+M181)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -7134,7 +9329,10 @@
         <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G182" s="7" t="n"/>
+      <c r="G182" s="8">
+        <f>IF(A182="","",N182)</f>
+        <v/>
+      </c>
       <c r="H182" s="8">
         <f>IF(A182="","",Inputs!$B$3/((IF(G182="",Inputs!$B$14,G182)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7145,6 +9343,15 @@
       </c>
       <c r="J182" s="4" t="n"/>
       <c r="K182" s="4" t="n"/>
+      <c r="L182" s="5" t="n"/>
+      <c r="M182" s="9">
+        <f>IF(A182="","",IF(OR(J182="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J182,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N182" s="9">
+        <f>IF(A182="","",IF(L182="",Inputs!$B$14,L182)+M182)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -7156,7 +9363,10 @@
         <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G183" s="7" t="n"/>
+      <c r="G183" s="8">
+        <f>IF(A183="","",N183)</f>
+        <v/>
+      </c>
       <c r="H183" s="8">
         <f>IF(A183="","",Inputs!$B$3/((IF(G183="",Inputs!$B$14,G183)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7167,6 +9377,15 @@
       </c>
       <c r="J183" s="4" t="n"/>
       <c r="K183" s="4" t="n"/>
+      <c r="L183" s="5" t="n"/>
+      <c r="M183" s="9">
+        <f>IF(A183="","",IF(OR(J183="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J183,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N183" s="9">
+        <f>IF(A183="","",IF(L183="",Inputs!$B$14,L183)+M183)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -7178,7 +9397,10 @@
         <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G184" s="7" t="n"/>
+      <c r="G184" s="8">
+        <f>IF(A184="","",N184)</f>
+        <v/>
+      </c>
       <c r="H184" s="8">
         <f>IF(A184="","",Inputs!$B$3/((IF(G184="",Inputs!$B$14,G184)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7189,6 +9411,15 @@
       </c>
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
+      <c r="L184" s="5" t="n"/>
+      <c r="M184" s="9">
+        <f>IF(A184="","",IF(OR(J184="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J184,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N184" s="9">
+        <f>IF(A184="","",IF(L184="",Inputs!$B$14,L184)+M184)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -7200,7 +9431,10 @@
         <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G185" s="7" t="n"/>
+      <c r="G185" s="8">
+        <f>IF(A185="","",N185)</f>
+        <v/>
+      </c>
       <c r="H185" s="8">
         <f>IF(A185="","",Inputs!$B$3/((IF(G185="",Inputs!$B$14,G185)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7211,6 +9445,15 @@
       </c>
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
+      <c r="L185" s="5" t="n"/>
+      <c r="M185" s="9">
+        <f>IF(A185="","",IF(OR(J185="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J185,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N185" s="9">
+        <f>IF(A185="","",IF(L185="",Inputs!$B$14,L185)+M185)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n"/>
@@ -7222,7 +9465,10 @@
         <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G186" s="7" t="n"/>
+      <c r="G186" s="8">
+        <f>IF(A186="","",N186)</f>
+        <v/>
+      </c>
       <c r="H186" s="8">
         <f>IF(A186="","",Inputs!$B$3/((IF(G186="",Inputs!$B$14,G186)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7233,6 +9479,15 @@
       </c>
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
+      <c r="L186" s="5" t="n"/>
+      <c r="M186" s="9">
+        <f>IF(A186="","",IF(OR(J186="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J186,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N186" s="9">
+        <f>IF(A186="","",IF(L186="",Inputs!$B$14,L186)+M186)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n"/>
@@ -7244,7 +9499,10 @@
         <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G187" s="7" t="n"/>
+      <c r="G187" s="8">
+        <f>IF(A187="","",N187)</f>
+        <v/>
+      </c>
       <c r="H187" s="8">
         <f>IF(A187="","",Inputs!$B$3/((IF(G187="",Inputs!$B$14,G187)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7255,6 +9513,15 @@
       </c>
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
+      <c r="L187" s="5" t="n"/>
+      <c r="M187" s="9">
+        <f>IF(A187="","",IF(OR(J187="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J187,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N187" s="9">
+        <f>IF(A187="","",IF(L187="",Inputs!$B$14,L187)+M187)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -7266,7 +9533,10 @@
         <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G188" s="7" t="n"/>
+      <c r="G188" s="8">
+        <f>IF(A188="","",N188)</f>
+        <v/>
+      </c>
       <c r="H188" s="8">
         <f>IF(A188="","",Inputs!$B$3/((IF(G188="",Inputs!$B$14,G188)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7277,6 +9547,15 @@
       </c>
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
+      <c r="L188" s="5" t="n"/>
+      <c r="M188" s="9">
+        <f>IF(A188="","",IF(OR(J188="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J188,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N188" s="9">
+        <f>IF(A188="","",IF(L188="",Inputs!$B$14,L188)+M188)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -7288,7 +9567,10 @@
         <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G189" s="7" t="n"/>
+      <c r="G189" s="8">
+        <f>IF(A189="","",N189)</f>
+        <v/>
+      </c>
       <c r="H189" s="8">
         <f>IF(A189="","",Inputs!$B$3/((IF(G189="",Inputs!$B$14,G189)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7299,6 +9581,15 @@
       </c>
       <c r="J189" s="4" t="n"/>
       <c r="K189" s="4" t="n"/>
+      <c r="L189" s="5" t="n"/>
+      <c r="M189" s="9">
+        <f>IF(A189="","",IF(OR(J189="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J189,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N189" s="9">
+        <f>IF(A189="","",IF(L189="",Inputs!$B$14,L189)+M189)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -7310,7 +9601,10 @@
         <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G190" s="7" t="n"/>
+      <c r="G190" s="8">
+        <f>IF(A190="","",N190)</f>
+        <v/>
+      </c>
       <c r="H190" s="8">
         <f>IF(A190="","",Inputs!$B$3/((IF(G190="",Inputs!$B$14,G190)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7321,6 +9615,15 @@
       </c>
       <c r="J190" s="4" t="n"/>
       <c r="K190" s="4" t="n"/>
+      <c r="L190" s="5" t="n"/>
+      <c r="M190" s="9">
+        <f>IF(A190="","",IF(OR(J190="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J190,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N190" s="9">
+        <f>IF(A190="","",IF(L190="",Inputs!$B$14,L190)+M190)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -7332,7 +9635,10 @@
         <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G191" s="7" t="n"/>
+      <c r="G191" s="8">
+        <f>IF(A191="","",N191)</f>
+        <v/>
+      </c>
       <c r="H191" s="8">
         <f>IF(A191="","",Inputs!$B$3/((IF(G191="",Inputs!$B$14,G191)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7343,6 +9649,15 @@
       </c>
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
+      <c r="L191" s="5" t="n"/>
+      <c r="M191" s="9">
+        <f>IF(A191="","",IF(OR(J191="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J191,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N191" s="9">
+        <f>IF(A191="","",IF(L191="",Inputs!$B$14,L191)+M191)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -7354,7 +9669,10 @@
         <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G192" s="7" t="n"/>
+      <c r="G192" s="8">
+        <f>IF(A192="","",N192)</f>
+        <v/>
+      </c>
       <c r="H192" s="8">
         <f>IF(A192="","",Inputs!$B$3/((IF(G192="",Inputs!$B$14,G192)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7365,6 +9683,15 @@
       </c>
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
+      <c r="L192" s="5" t="n"/>
+      <c r="M192" s="9">
+        <f>IF(A192="","",IF(OR(J192="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J192,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N192" s="9">
+        <f>IF(A192="","",IF(L192="",Inputs!$B$14,L192)+M192)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n"/>
@@ -7376,7 +9703,10 @@
         <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G193" s="7" t="n"/>
+      <c r="G193" s="8">
+        <f>IF(A193="","",N193)</f>
+        <v/>
+      </c>
       <c r="H193" s="8">
         <f>IF(A193="","",Inputs!$B$3/((IF(G193="",Inputs!$B$14,G193)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7387,6 +9717,15 @@
       </c>
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
+      <c r="L193" s="5" t="n"/>
+      <c r="M193" s="9">
+        <f>IF(A193="","",IF(OR(J193="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J193,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N193" s="9">
+        <f>IF(A193="","",IF(L193="",Inputs!$B$14,L193)+M193)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n"/>
@@ -7398,7 +9737,10 @@
         <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G194" s="7" t="n"/>
+      <c r="G194" s="8">
+        <f>IF(A194="","",N194)</f>
+        <v/>
+      </c>
       <c r="H194" s="8">
         <f>IF(A194="","",Inputs!$B$3/((IF(G194="",Inputs!$B$14,G194)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7409,6 +9751,15 @@
       </c>
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
+      <c r="L194" s="5" t="n"/>
+      <c r="M194" s="9">
+        <f>IF(A194="","",IF(OR(J194="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J194,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N194" s="9">
+        <f>IF(A194="","",IF(L194="",Inputs!$B$14,L194)+M194)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -7420,7 +9771,10 @@
         <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G195" s="7" t="n"/>
+      <c r="G195" s="8">
+        <f>IF(A195="","",N195)</f>
+        <v/>
+      </c>
       <c r="H195" s="8">
         <f>IF(A195="","",Inputs!$B$3/((IF(G195="",Inputs!$B$14,G195)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7431,6 +9785,15 @@
       </c>
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
+      <c r="L195" s="5" t="n"/>
+      <c r="M195" s="9">
+        <f>IF(A195="","",IF(OR(J195="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J195,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N195" s="9">
+        <f>IF(A195="","",IF(L195="",Inputs!$B$14,L195)+M195)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -7442,7 +9805,10 @@
         <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G196" s="7" t="n"/>
+      <c r="G196" s="8">
+        <f>IF(A196="","",N196)</f>
+        <v/>
+      </c>
       <c r="H196" s="8">
         <f>IF(A196="","",Inputs!$B$3/((IF(G196="",Inputs!$B$14,G196)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7453,6 +9819,15 @@
       </c>
       <c r="J196" s="4" t="n"/>
       <c r="K196" s="4" t="n"/>
+      <c r="L196" s="5" t="n"/>
+      <c r="M196" s="9">
+        <f>IF(A196="","",IF(OR(J196="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J196,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N196" s="9">
+        <f>IF(A196="","",IF(L196="",Inputs!$B$14,L196)+M196)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -7464,7 +9839,10 @@
         <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G197" s="7" t="n"/>
+      <c r="G197" s="8">
+        <f>IF(A197="","",N197)</f>
+        <v/>
+      </c>
       <c r="H197" s="8">
         <f>IF(A197="","",Inputs!$B$3/((IF(G197="",Inputs!$B$14,G197)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7475,6 +9853,15 @@
       </c>
       <c r="J197" s="4" t="n"/>
       <c r="K197" s="4" t="n"/>
+      <c r="L197" s="5" t="n"/>
+      <c r="M197" s="9">
+        <f>IF(A197="","",IF(OR(J197="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J197,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N197" s="9">
+        <f>IF(A197="","",IF(L197="",Inputs!$B$14,L197)+M197)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -7486,7 +9873,10 @@
         <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G198" s="7" t="n"/>
+      <c r="G198" s="8">
+        <f>IF(A198="","",N198)</f>
+        <v/>
+      </c>
       <c r="H198" s="8">
         <f>IF(A198="","",Inputs!$B$3/((IF(G198="",Inputs!$B$14,G198)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7497,6 +9887,15 @@
       </c>
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
+      <c r="L198" s="5" t="n"/>
+      <c r="M198" s="9">
+        <f>IF(A198="","",IF(OR(J198="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J198,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N198" s="9">
+        <f>IF(A198="","",IF(L198="",Inputs!$B$14,L198)+M198)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -7508,7 +9907,10 @@
         <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G199" s="7" t="n"/>
+      <c r="G199" s="8">
+        <f>IF(A199="","",N199)</f>
+        <v/>
+      </c>
       <c r="H199" s="8">
         <f>IF(A199="","",Inputs!$B$3/((IF(G199="",Inputs!$B$14,G199)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7519,6 +9921,15 @@
       </c>
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
+      <c r="L199" s="5" t="n"/>
+      <c r="M199" s="9">
+        <f>IF(A199="","",IF(OR(J199="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J199,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N199" s="9">
+        <f>IF(A199="","",IF(L199="",Inputs!$B$14,L199)+M199)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n"/>
@@ -7530,7 +9941,10 @@
         <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G200" s="7" t="n"/>
+      <c r="G200" s="8">
+        <f>IF(A200="","",N200)</f>
+        <v/>
+      </c>
       <c r="H200" s="8">
         <f>IF(A200="","",Inputs!$B$3/((IF(G200="",Inputs!$B$14,G200)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7541,6 +9955,15 @@
       </c>
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
+      <c r="L200" s="5" t="n"/>
+      <c r="M200" s="9">
+        <f>IF(A200="","",IF(OR(J200="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J200,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N200" s="9">
+        <f>IF(A200="","",IF(L200="",Inputs!$B$14,L200)+M200)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n"/>
@@ -7552,7 +9975,10 @@
         <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G201" s="7" t="n"/>
+      <c r="G201" s="8">
+        <f>IF(A201="","",N201)</f>
+        <v/>
+      </c>
       <c r="H201" s="8">
         <f>IF(A201="","",Inputs!$B$3/((IF(G201="",Inputs!$B$14,G201)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7563,6 +9989,15 @@
       </c>
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
+      <c r="L201" s="5" t="n"/>
+      <c r="M201" s="9">
+        <f>IF(A201="","",IF(OR(J201="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J201,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N201" s="9">
+        <f>IF(A201="","",IF(L201="",Inputs!$B$14,L201)+M201)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -7574,7 +10009,10 @@
         <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G202" s="7" t="n"/>
+      <c r="G202" s="8">
+        <f>IF(A202="","",N202)</f>
+        <v/>
+      </c>
       <c r="H202" s="8">
         <f>IF(A202="","",Inputs!$B$3/((IF(G202="",Inputs!$B$14,G202)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7585,6 +10023,15 @@
       </c>
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
+      <c r="L202" s="5" t="n"/>
+      <c r="M202" s="9">
+        <f>IF(A202="","",IF(OR(J202="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J202,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N202" s="9">
+        <f>IF(A202="","",IF(L202="",Inputs!$B$14,L202)+M202)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -7596,7 +10043,10 @@
         <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G203" s="7" t="n"/>
+      <c r="G203" s="8">
+        <f>IF(A203="","",N203)</f>
+        <v/>
+      </c>
       <c r="H203" s="8">
         <f>IF(A203="","",Inputs!$B$3/((IF(G203="",Inputs!$B$14,G203)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7607,6 +10057,15 @@
       </c>
       <c r="J203" s="4" t="n"/>
       <c r="K203" s="4" t="n"/>
+      <c r="L203" s="5" t="n"/>
+      <c r="M203" s="9">
+        <f>IF(A203="","",IF(OR(J203="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J203,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N203" s="9">
+        <f>IF(A203="","",IF(L203="",Inputs!$B$14,L203)+M203)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -7618,7 +10077,10 @@
         <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G204" s="7" t="n"/>
+      <c r="G204" s="8">
+        <f>IF(A204="","",N204)</f>
+        <v/>
+      </c>
       <c r="H204" s="8">
         <f>IF(A204="","",Inputs!$B$3/((IF(G204="",Inputs!$B$14,G204)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
@@ -7629,6 +10091,15 @@
       </c>
       <c r="J204" s="4" t="n"/>
       <c r="K204" s="4" t="n"/>
+      <c r="L204" s="5" t="n"/>
+      <c r="M204" s="9">
+        <f>IF(A204="","",IF(OR(J204="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J204,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
+        <v/>
+      </c>
+      <c r="N204" s="9">
+        <f>IF(A204="","",IF(L204="",Inputs!$B$14,L204)+M204)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -854,6 +854,27 @@
       <c r="A47" t="inlineStr">
         <is>
           <t>Inputs!B59 est une vitesse adoptee (pas la vitesse calculee hydraulique) pour eviter references circulaires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Important: un ecoulement gravitaire ne peut pas remonter de la conduite vers une noue plus haute sans pompage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Condition pratique PIPE-&gt;SWALE: radier sortie conduite &gt;= fond noue aval (ou tres legerement au-dessus), sinon CHECK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Le regard/ouvrage de sortie sert a dissiper/organiser la transition, pas a "lever" l eau par gravite.</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10412,7 @@
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>21.6</v>
+        <v>9.6</v>
       </c>
       <c r="G4" s="7">
         <f>Inputs!$B$33</f>
@@ -10475,7 +10496,7 @@
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>Bande est amont (arbres) - underdrain segment 1.</t>
+          <t>Longueur corrigee selon plan: P-01 -&gt; P-02 = 9.6 m.</t>
         </is>
       </c>
       <c r="AC4" s="7" t="n"/>
@@ -10543,7 +10564,7 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>21.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G5" s="7">
         <f>Inputs!$B$33</f>
@@ -10627,7 +10648,7 @@
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>Bande est aval (arbres) - underdrain segment 2.</t>
+          <t>Longueur corrigee selon plan: P-02 -&gt; P-03 = 8.7 m.</t>
         </is>
       </c>
       <c r="AC5" s="7" t="n"/>
@@ -11202,7 +11223,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni court via caniveau/grille + conduite (DN250).</t>
+          <t>Traverse pave-uni: capture ponctuelle (caniveau/avaloir grille) + conduite courte de traversee DN250.</t>
         </is>
       </c>
       <c r="AC9" s="7" t="n"/>
@@ -11490,7 +11511,7 @@
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni principal via caniveau/grille + conduite (DN300).</t>
+          <t>Traverse pave-uni: capture ponctuelle (grille) + conduite courte de traversee DN300 vers noue aval.</t>
         </is>
       </c>
       <c r="AC11" s="7" t="n"/>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -875,6 +875,20 @@
       <c r="A50" t="inlineStr">
         <is>
           <t>Le regard/ouvrage de sortie sert a dissiper/organiser la transition, pas a "lever" l eau par gravite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Strategie ouest revisee: traverses pave-uni traitees en caniveaux de surface (E05B, E05D), pas en conduites enterrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Objectif: eviter cas pipe profond -&gt; noue aval plus haute, et garder un profil gravitaire lisible.</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11144,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>SWALE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -11155,17 +11169,23 @@
       <c r="G9" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="n">
+        <v>0.015</v>
+      </c>
       <c r="I9" s="8">
         <f>IF(A9="","",IF(H9&lt;&gt;"",H9,IF(UPPER(TRIM(B9))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B9))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="n">
-        <v>250</v>
-      </c>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
@@ -11223,7 +11243,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni: capture ponctuelle (caniveau/avaloir grille) + conduite courte de traversee DN250.</t>
+          <t>Traverse pave-uni par caniveau a grille de surface (pas de conduite enterree sur ce troncon).</t>
         </is>
       </c>
       <c r="AC9" s="7" t="n"/>
@@ -11418,7 +11438,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>SWALE</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11443,17 +11463,23 @@
       <c r="G11" s="7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="n">
+        <v>0.015</v>
+      </c>
       <c r="I11" s="8">
         <f>IF(A11="","",IF(H11&lt;&gt;"",H11,IF(UPPER(TRIM(B11))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B11))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="n">
-        <v>300</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
@@ -11511,7 +11537,7 @@
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni: capture ponctuelle (grille) + conduite courte de traversee DN300 vers noue aval.</t>
+          <t>Traverse pave-uni principal par caniveau a grille de surface (pas de conduite enterree sur ce troncon).</t>
         </is>
       </c>
       <c r="AC11" s="7" t="n"/>
@@ -40285,22 +40311,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Caniveau grille + pipe DN250</t>
+          <t>Caniveau grille de surface</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>E05B (PIPE)</t>
+          <t>E05B (CANIVEAU SURFACE)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>slope ~1.0%</t>
+          <t>section ~0.25 x 0.08 m</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Raccorder aux noeuds MH.</t>
+          <t>Aucune remontee hydraulique requise; ecoulement de surface continu.</t>
         </is>
       </c>
     </row>
@@ -40349,22 +40375,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Caniveau grille + pipe DN300</t>
+          <t>Caniveau grille de surface</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>E05D (PIPE)</t>
+          <t>E05D (CANIVEAU SURFACE)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>slope ~0.9%</t>
+          <t>section ~0.30 x 0.10 m</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Verifier degagement lateraux.</t>
+          <t>Aucune conduite profonde de traversee sur ce troncon.</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -137,6 +137,7 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -573,14 +574,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cote droite avec arbres: prioriser noue de surface peu profonde + protections racinaires; eviter conduite profonde en zone racinaire.</t>
+          <t>2) Bande sud (2.0 m): conduite/collecte vers volume de retention dans le corridor contraint.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Exutoire: bassin de retention en bas a gauche (node BASIN_RET).</t>
+          <t>3) Ouest: strategie revisee en conduites (pas de noues) vers E04 puis E08 et bassin.</t>
         </is>
       </c>
     </row>
@@ -889,6 +890,20 @@
       <c r="A52" t="inlineStr">
         <is>
           <t>Objectif: eviter cas pipe profond -&gt; noue aval plus haute, et garder un profil gravitaire lisible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Changement concept: zone grise est (tresfond) drainee vers puisards et reseau interne mecanique jusqu'a sortie sud pres bassin (E09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Resume surfaces disponibles dans Decision_Summary (A34:B37) et Resume_checks (B10:B12).</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1269,14 +1284,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3) Ouest (utilities): collecte de surface peu profonde priorisee, traverses ponctuelles controlees.</t>
+          <t>3) Ouest: drainage en conduites (DN250/DN300) vers E04 puis entree ouest bassin.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4) Deux entrees au bassin: EST (J-BASSIN-IN) et OUEST (J-BASSIN-OUEST) vers BASSIN-RET.</t>
+          <t>4) Zone grise est (tresfond): puisards + reseau interne mecanique vers sortie sud et bassin.</t>
         </is>
       </c>
     </row>
@@ -1673,6 +1688,67 @@
           <t>- Verifier protection racinaire et details constructifs (barriere racinaire + cleanouts + acces entretien).</t>
         </is>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Surface summary (readable quantities)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Impervious area total (m2)</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>Resume_checks!B10</f>
+        <v/>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ROOF + PAVAGE + TRESFOND</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Grass area total (m2)</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>Resume_checks!B11</f>
+        <v/>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>GRASS only</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Impervious fraction</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>Resume_checks!B12</f>
+        <v/>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Impervious/(Impervious+Grass)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1710,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2896,6 +2972,46 @@
       <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Vitesse adoptee pour calcul temps de transit dans element route (evite references circulaires).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Mech_internal_outlet_length_m</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Longueur approximative conduite interne mecanique (puisards est -&gt; sortie sud pres bassin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Mech_internal_outlet_diameter_mm</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Diametre indicatif conduite mecanique interne (a confirmer par equipe mecanique).</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3230,12 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Pente vers bande est</t>
+          <t>Puisards zone grise est -&gt; reseau interne mecanique -&gt; sortie sud pres bassin (pas vers bande est).</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
@@ -10852,7 +10968,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10882,16 +10998,12 @@
         <f>IF(A7="","",IF(H7&lt;&gt;"",H7,IF(UPPER(TRIM(B7))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B7))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J7" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="n">
         <v>0</v>
       </c>
@@ -10949,7 +11061,7 @@
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>Corrige: liaison ouest courte vers entree ouest bassin (4.7 m mesure).</t>
+          <t>Collecteur ouest final en conduite (4.7 m) vers entree ouest bassin.</t>
         </is>
       </c>
       <c r="AC7" s="7" t="n"/>
@@ -10998,7 +11110,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -11028,16 +11140,12 @@
         <f>IF(A8="","",IF(H8&lt;&gt;"",H8,IF(UPPER(TRIM(B8))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B8))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J8" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="7" t="n">
         <v>0</v>
       </c>
@@ -11095,7 +11203,7 @@
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
-          <t>Ouest gazon amont - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
+          <t>Ouest segment amont en conduite DN250 vers E05B.</t>
         </is>
       </c>
       <c r="AC8" s="7" t="n"/>
@@ -11144,7 +11252,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -11169,23 +11277,17 @@
       <c r="G9" s="7" t="n">
         <v>0.01</v>
       </c>
-      <c r="H9" s="7" t="n">
-        <v>0.015</v>
-      </c>
+      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="8">
         <f>IF(A9="","",IF(H9&lt;&gt;"",H9,IF(UPPER(TRIM(B9))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B9))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
@@ -11243,7 +11345,7 @@
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni par caniveau a grille de surface (pas de conduite enterree sur ce troncon).</t>
+          <t>Traverse pave-uni court en conduite DN250 (strategy ouest tout-pipe).</t>
         </is>
       </c>
       <c r="AC9" s="7" t="n"/>
@@ -11292,7 +11394,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -11322,16 +11424,12 @@
         <f>IF(A10="","",IF(H10&lt;&gt;"",H10,IF(UPPER(TRIM(B10))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B10))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J10" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
@@ -11389,7 +11487,7 @@
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>Ouest gazon milieu - longueur issue cotes plan (chaine 11.1 m repartie par aires).</t>
+          <t>Ouest segment milieu en conduite DN300 vers E05D.</t>
         </is>
       </c>
       <c r="AC10" s="7" t="n"/>
@@ -11438,7 +11536,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11463,23 +11561,17 @@
       <c r="G11" s="7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="H11" s="7" t="n">
-        <v>0.015</v>
-      </c>
+      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="8">
         <f>IF(A11="","",IF(H11&lt;&gt;"",H11,IF(UPPER(TRIM(B11))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B11))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
@@ -11537,7 +11629,7 @@
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
-          <t>Traverse pave-uni principal par caniveau a grille de surface (pas de conduite enterree sur ce troncon).</t>
+          <t>Traverse pave-uni principal en conduite DN300.</t>
         </is>
       </c>
       <c r="AC11" s="7" t="n"/>
@@ -11586,7 +11678,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SWALE</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11616,16 +11708,12 @@
         <f>IF(A12="","",IF(H12&lt;&gt;"",H12,IF(UPPER(TRIM(B12))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B12))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="J12" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
@@ -11683,7 +11771,7 @@
       </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
-          <t>Ouest gazon aval - longueur solde sur chaine totale 23.58 m.</t>
+          <t>Ouest segment aval en conduite DN300 vers E04.</t>
         </is>
       </c>
       <c r="AC12" s="7" t="n"/>
@@ -12108,23 +12196,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>J-MECH-OUT</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>BASSIN-RET</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="7">
+        <f>Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="8">
         <f>IF(A16="","",IF(H16&lt;&gt;"",H16,IF(UPPER(TRIM(B16))="PIPE",Inputs!$B$7,IF(UPPER(TRIM(B16))="SWALE",Inputs!$B$8,Inputs!$B$9))))</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
+      <c r="J16" s="7">
+        <f>Inputs!$B$61</f>
+        <v/>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="O16" s="8">
         <f>IF(A16="","",SUMIFS(Zones_tributaires!$I:$I,Zones_tributaires!$J:$J,$A16))</f>
         <v/>
@@ -12177,7 +12291,11 @@
         <f>IF(A16="","",IF(OR(U16&gt;1,AND(X16&lt;&gt;"",X16&lt;Inputs!$B$16),AND(X16&lt;&gt;"",X16&gt;Inputs!$B$17),G16&lt;Inputs!$B$18,AH16="CHECK"),"CHECK","OK"))</f>
         <v/>
       </c>
-      <c r="AB16" s="4" t="n"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>Apport puisards zone grise est via reseau interne mecanique (traversant batiment) vers bassin sud.</t>
+        </is>
+      </c>
       <c r="AC16" s="7" t="n"/>
       <c r="AD16" s="8">
         <f>IF(A16="","",IF(AC16&lt;&gt;"",AC16,IF(E16="",Inputs!$B$38,IFERROR(INDEX($AE$4:$AE$204,MATCH(E16,$A$4:$A$204,0))+IF(OR(AND(UPPER(TRIM(B16))="SWALE",UPPER(TRIM(AI16))="PIPE"),AND(UPPER(TRIM(B16))="TRENCH",UPPER(TRIM(AI16))="PIPE")),Inputs!$B$57,0),""))))</f>
@@ -33881,22 +33999,39 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>J-MECH-OUT</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
       <c r="C18" s="7" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="8">
         <f>IF(OR(C18="",D18=""),"",MAX(0,C18-D18))</f>
         <v/>
       </c>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>CIRC</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="8">
         <f>IF(A18="","",IF(UPPER(TRIM(F18))="CIRC",PI()*(G18/2)^2*E18,IF(UPPER(TRIM(F18))="RECT",G18*H18*E18,"")))</f>
         <v/>
       </c>
-      <c r="J18" s="7" t="n"/>
+      <c r="J18" s="7">
+        <f>Inputs!$B$23</f>
+        <v/>
+      </c>
       <c r="K18" s="8">
         <f>IF(A18="","",SUMIFS(Elements_hybrides!$Q:$Q,Elements_hybrides!$D:$D,$A18))</f>
         <v/>
@@ -39504,7 +39639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -39581,6 +39716,39 @@
       </c>
       <c r="B9" s="8">
         <f>IFERROR(INDEX(Noeuds_stockage!$I$4:$I$204,MATCH("BASIN_RET",Noeuds_stockage!$A$4:$A$204,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Impervious_area_total_m2 (ROOF+PAVAGE+TRESFOND)</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"ROOF")+SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"PAVAGE")+SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"TRESFOND")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Grass_area_total_m2</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"GRASS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Impervious_fraction_of_(impervious+grass)</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IF((B10+B11)=0,"",B10/(B10+B11))</f>
         <v/>
       </c>
     </row>
@@ -40279,22 +40447,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Ecoulement de surface peu profond</t>
+          <t>Conduite enterree peu profonde</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>E05A (SWALE)</t>
+          <t>E05A (PIPE)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>depth ~0.15-0.20 m</t>
+          <t>DN250, pente ~1.0%</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Eviter fouille profonde.</t>
+          <t>Strategie client: ouest privilegie en conduites.</t>
         </is>
       </c>
     </row>
@@ -40311,22 +40479,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Caniveau grille de surface</t>
+          <t>Conduite traversee pave-uni</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>E05B (CANIVEAU SURFACE)</t>
+          <t>E05B (PIPE)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>section ~0.25 x 0.08 m</t>
+          <t>DN250, pente ~1.0%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Aucune remontee hydraulique requise; ecoulement de surface continu.</t>
+          <t>Raccord vers regard intermediaire.</t>
         </is>
       </c>
     </row>
@@ -40343,22 +40511,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Noue de surface</t>
+          <t>Conduite enterree</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>E05C (SWALE)</t>
+          <t>E05C (PIPE)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>depth ~0.15-0.20 m</t>
+          <t>DN300, pente ~0.9%</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Conduire vers traverse 2.</t>
+          <t>Segment principal vers aval.</t>
         </is>
       </c>
     </row>
@@ -40375,22 +40543,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Caniveau grille de surface</t>
+          <t>Conduite traversee pave-uni</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>E05D (CANIVEAU SURFACE)</t>
+          <t>E05D (PIPE)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>section ~0.30 x 0.10 m</t>
+          <t>DN300, pente ~0.9%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Aucune conduite profonde de traversee sur ce troncon.</t>
+          <t>Traverse mineralisee en conduite.</t>
         </is>
       </c>
     </row>
@@ -40407,22 +40575,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Noue de surface</t>
+          <t>Conduite enterree</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>E05E (SWALE)</t>
+          <t>E05E (PIPE)</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>vers J-OUEST-AVAL</t>
+          <t>DN300, pente ~0.8%</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Transition vers E06.</t>
+          <t>Vers E04 puis E08 et bassin.</t>
         </is>
       </c>
     </row>

--- a/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
+++ b/engineering/drainage-design/Reseau_tresfond_hybride_retention.xlsx
@@ -26,9 +26,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[&lt;1]0.000;0.00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="[&lt;1]0.0000;0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -113,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -138,6 +139,8 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="145" customWidth="1" min="1" max="1"/>
@@ -904,6 +907,20 @@
       <c r="A54" t="inlineStr">
         <is>
           <t>Resume surfaces disponibles dans Decision_Summary (A34:B37) et Resume_checks (B10:B12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mise a jour: bande est verte scindee -&gt; 164.7 m2 vers E01/E02 + 40.8 m2 (Z13) vers puisard PEHD central/reseau mecanique (E09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Affichage decimal harmonise: format [&lt;1]0.0000;0.000 applique aux champs calcules Tc/temps/Q.</t>
         </is>
       </c>
     </row>
@@ -3154,19 +3171,19 @@
         <v>1013.8</v>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="8">
+      <c r="F4" s="20">
         <f>IF(E4&lt;&gt;"",E4,IF(UPPER(TRIM(C4))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C4))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C4))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C4))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C4))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="20">
         <f>IF(A4="","",N4)</f>
         <v/>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="20">
         <f>IF(A4="","",Inputs!$B$3/((IF(G4="",Inputs!$B$14,G4)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="20">
         <f>IF(A4="","",2.78E-7*F4*D4*H4)</f>
         <v/>
       </c>
@@ -3183,11 +3200,11 @@
       <c r="L4" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="20">
         <f>IF(A4="","",IF(OR(J4="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J4,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="20">
         <f>IF(A4="","",IF(L4="",Inputs!$B$14,L4)+M4)</f>
         <v/>
       </c>
@@ -3212,19 +3229,19 @@
         <v>351</v>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="8">
+      <c r="F5" s="20">
         <f>IF(E5&lt;&gt;"",E5,IF(UPPER(TRIM(C5))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C5))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C5))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C5))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C5))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="20">
         <f>IF(A5="","",N5)</f>
         <v/>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="20">
         <f>IF(A5="","",Inputs!$B$3/((IF(G5="",Inputs!$B$14,G5)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="20">
         <f>IF(A5="","",2.78E-7*F5*D5*H5)</f>
         <v/>
       </c>
@@ -3241,11 +3258,11 @@
       <c r="L5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="20">
         <f>IF(A5="","",IF(OR(J5="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J5,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="20">
         <f>IF(A5="","",IF(L5="",Inputs!$B$14,L5)+M5)</f>
         <v/>
       </c>
@@ -3267,22 +3284,22 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>205.5</v>
+        <v>164.7</v>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="8">
+      <c r="F6" s="20">
         <f>IF(E6&lt;&gt;"",E6,IF(UPPER(TRIM(C6))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C6))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C6))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C6))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C6))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="20">
         <f>IF(A6="","",N6)</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="20">
         <f>IF(A6="","",Inputs!$B$3/((IF(G6="",Inputs!$B$14,G6)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="20">
         <f>IF(A6="","",2.78E-7*F6*D6*H6)</f>
         <v/>
       </c>
@@ -3293,17 +3310,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Vers underdrain est</t>
+          <t>Bande est verte reduite: 205.5 - 40.8 = 164.7 m2 (partie haute deviee vers puisard PEHD central).</t>
         </is>
       </c>
       <c r="L6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="20">
         <f>IF(A6="","",IF(OR(J6="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J6,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="20">
         <f>IF(A6="","",IF(L6="",Inputs!$B$14,L6)+M6)</f>
         <v/>
       </c>
@@ -3328,19 +3345,19 @@
         <v>12.5</v>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8">
+      <c r="F7" s="20">
         <f>IF(E7&lt;&gt;"",E7,IF(UPPER(TRIM(C7))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C7))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C7))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C7))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C7))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="20">
         <f>IF(A7="","",N7)</f>
         <v/>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="20">
         <f>IF(A7="","",Inputs!$B$3/((IF(G7="",Inputs!$B$14,G7)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="20">
         <f>IF(A7="","",2.78E-7*F7*D7*H7)</f>
         <v/>
       </c>
@@ -3357,11 +3374,11 @@
       <c r="L7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="20">
         <f>IF(A7="","",IF(OR(J7="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J7,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="20">
         <f>IF(A7="","",IF(L7="",Inputs!$B$14,L7)+M7)</f>
         <v/>
       </c>
@@ -3386,19 +3403,19 @@
         <v>6.7</v>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="8">
+      <c r="F8" s="20">
         <f>IF(E8&lt;&gt;"",E8,IF(UPPER(TRIM(C8))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C8))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C8))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C8))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C8))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="20">
         <f>IF(A8="","",N8)</f>
         <v/>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="20">
         <f>IF(A8="","",Inputs!$B$3/((IF(G8="",Inputs!$B$14,G8)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="20">
         <f>IF(A8="","",2.78E-7*F8*D8*H8)</f>
         <v/>
       </c>
@@ -3415,11 +3432,11 @@
       <c r="L8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="20">
         <f>IF(A8="","",IF(OR(J8="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J8,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="20">
         <f>IF(A8="","",IF(L8="",Inputs!$B$14,L8)+M8)</f>
         <v/>
       </c>
@@ -3444,19 +3461,19 @@
         <v>27.2</v>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8">
+      <c r="F9" s="20">
         <f>IF(E9&lt;&gt;"",E9,IF(UPPER(TRIM(C9))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C9))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C9))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C9))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C9))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="20">
         <f>IF(A9="","",N9)</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="20">
         <f>IF(A9="","",Inputs!$B$3/((IF(G9="",Inputs!$B$14,G9)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="20">
         <f>IF(A9="","",2.78E-7*F9*D9*H9)</f>
         <v/>
       </c>
@@ -3473,11 +3490,11 @@
       <c r="L9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="20">
         <f>IF(A9="","",IF(OR(J9="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J9,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="20">
         <f>IF(A9="","",IF(L9="",Inputs!$B$14,L9)+M9)</f>
         <v/>
       </c>
@@ -3502,19 +3519,19 @@
         <v>37.5</v>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="8">
+      <c r="F10" s="20">
         <f>IF(E10&lt;&gt;"",E10,IF(UPPER(TRIM(C10))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C10))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C10))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C10))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C10))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="20">
         <f>IF(A10="","",N10)</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="20">
         <f>IF(A10="","",Inputs!$B$3/((IF(G10="",Inputs!$B$14,G10)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="20">
         <f>IF(A10="","",2.78E-7*F10*D10*H10)</f>
         <v/>
       </c>
@@ -3531,11 +3548,11 @@
       <c r="L10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="20">
         <f>IF(A10="","",IF(OR(J10="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J10,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="20">
         <f>IF(A10="","",IF(L10="",Inputs!$B$14,L10)+M10)</f>
         <v/>
       </c>
@@ -3560,19 +3577,19 @@
         <v>21.9</v>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8">
+      <c r="F11" s="20">
         <f>IF(E11&lt;&gt;"",E11,IF(UPPER(TRIM(C11))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C11))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C11))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C11))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C11))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="20">
         <f>IF(A11="","",N11)</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="20">
         <f>IF(A11="","",Inputs!$B$3/((IF(G11="",Inputs!$B$14,G11)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="20">
         <f>IF(A11="","",2.78E-7*F11*D11*H11)</f>
         <v/>
       </c>
@@ -3589,11 +3606,11 @@
       <c r="L11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="20">
         <f>IF(A11="","",IF(OR(J11="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J11,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="20">
         <f>IF(A11="","",IF(L11="",Inputs!$B$14,L11)+M11)</f>
         <v/>
       </c>
@@ -3618,19 +3635,19 @@
         <v>109.7</v>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="8">
+      <c r="F12" s="20">
         <f>IF(E12&lt;&gt;"",E12,IF(UPPER(TRIM(C12))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C12))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C12))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C12))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C12))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="20">
         <f>IF(A12="","",N12)</f>
         <v/>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="20">
         <f>IF(A12="","",Inputs!$B$3/((IF(G12="",Inputs!$B$14,G12)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="20">
         <f>IF(A12="","",2.78E-7*F12*D12*H12)</f>
         <v/>
       </c>
@@ -3643,11 +3660,11 @@
       <c r="L12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="20">
         <f>IF(A12="","",IF(OR(J12="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J12,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="20">
         <f>IF(A12="","",IF(L12="",Inputs!$B$14,L12)+M12)</f>
         <v/>
       </c>
@@ -3672,19 +3689,19 @@
         <v>44.3</v>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="8">
+      <c r="F13" s="20">
         <f>IF(E13&lt;&gt;"",E13,IF(UPPER(TRIM(C13))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C13))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C13))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C13))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C13))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="20">
         <f>IF(A13="","",N13)</f>
         <v/>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="20">
         <f>IF(A13="","",Inputs!$B$3/((IF(G13="",Inputs!$B$14,G13)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="20">
         <f>IF(A13="","",2.78E-7*F13*D13*H13)</f>
         <v/>
       </c>
@@ -3701,11 +3718,11 @@
       <c r="L13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="20">
         <f>IF(A13="","",IF(OR(J13="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J13,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="20">
         <f>IF(A13="","",IF(L13="",Inputs!$B$14,L13)+M13)</f>
         <v/>
       </c>
@@ -3730,19 +3747,19 @@
         <v>20.5</v>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="8">
+      <c r="F14" s="20">
         <f>IF(E14&lt;&gt;"",E14,IF(UPPER(TRIM(C14))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C14))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C14))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C14))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C14))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="20">
         <f>IF(A14="","",N14)</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="20">
         <f>IF(A14="","",Inputs!$B$3/((IF(G14="",Inputs!$B$14,G14)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="20">
         <f>IF(A14="","",2.78E-7*F14*D14*H14)</f>
         <v/>
       </c>
@@ -3759,11 +3776,11 @@
       <c r="L14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="20">
         <f>IF(A14="","",IF(OR(J14="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J14,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="20">
         <f>IF(A14="","",IF(L14="",Inputs!$B$14,L14)+M14)</f>
         <v/>
       </c>
@@ -3788,19 +3805,19 @@
         <v>5.8</v>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="8">
+      <c r="F15" s="20">
         <f>IF(E15&lt;&gt;"",E15,IF(UPPER(TRIM(C15))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C15))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C15))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C15))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C15))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="20">
         <f>IF(A15="","",N15)</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="20">
         <f>IF(A15="","",Inputs!$B$3/((IF(G15="",Inputs!$B$14,G15)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="20">
         <f>IF(A15="","",2.78E-7*F15*D15*H15)</f>
         <v/>
       </c>
@@ -3817,45 +3834,67 @@
       <c r="L15" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="20">
         <f>IF(A15="","",IF(OR(J15="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J15,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="20">
         <f>IF(A15="","",IF(L15="",Inputs!$B$14,L15)+M15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="8">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Z13</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Petit strip vert nord (vers puisard PEHD central)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>GRASS</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="20">
         <f>IF(E16&lt;&gt;"",E16,IF(UPPER(TRIM(C16))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C16))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C16))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C16))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C16))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="20">
         <f>IF(A16="","",N16)</f>
         <v/>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="20">
         <f>IF(A16="","",Inputs!$B$3/((IF(G16="",Inputs!$B$14,G16)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="20">
         <f>IF(A16="","",2.78E-7*F16*D16*H16)</f>
         <v/>
       </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Devie vers puisard PEHD central puis reseau interne mecanique vers bassin (pas via bande est).</t>
+        </is>
+      </c>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="9">
+      <c r="M16" s="20">
         <f>IF(A16="","",IF(OR(J16="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J16,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="20">
         <f>IF(A16="","",IF(L16="",Inputs!$B$14,L16)+M16)</f>
         <v/>
       </c>
@@ -3866,30 +3905,30 @@
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
-      <c r="F17" s="8">
+      <c r="F17" s="20">
         <f>IF(E17&lt;&gt;"",E17,IF(UPPER(TRIM(C17))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C17))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C17))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C17))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C17))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="20">
         <f>IF(A17="","",N17)</f>
         <v/>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="20">
         <f>IF(A17="","",Inputs!$B$3/((IF(G17="",Inputs!$B$14,G17)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="20">
         <f>IF(A17="","",2.78E-7*F17*D17*H17)</f>
         <v/>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="9">
+      <c r="M17" s="20">
         <f>IF(A17="","",IF(OR(J17="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J17,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="20">
         <f>IF(A17="","",IF(L17="",Inputs!$B$14,L17)+M17)</f>
         <v/>
       </c>
@@ -3900,30 +3939,30 @@
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="8">
+      <c r="F18" s="20">
         <f>IF(E18&lt;&gt;"",E18,IF(UPPER(TRIM(C18))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C18))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C18))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C18))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C18))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="20">
         <f>IF(A18="","",N18)</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="20">
         <f>IF(A18="","",Inputs!$B$3/((IF(G18="",Inputs!$B$14,G18)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="20">
         <f>IF(A18="","",2.78E-7*F18*D18*H18)</f>
         <v/>
       </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="9">
+      <c r="M18" s="20">
         <f>IF(A18="","",IF(OR(J18="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J18,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="20">
         <f>IF(A18="","",IF(L18="",Inputs!$B$14,L18)+M18)</f>
         <v/>
       </c>
@@ -3934,30 +3973,30 @@
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8">
+      <c r="F19" s="20">
         <f>IF(E19&lt;&gt;"",E19,IF(UPPER(TRIM(C19))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C19))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C19))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C19))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C19))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="20">
         <f>IF(A19="","",N19)</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="20">
         <f>IF(A19="","",Inputs!$B$3/((IF(G19="",Inputs!$B$14,G19)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="20">
         <f>IF(A19="","",2.78E-7*F19*D19*H19)</f>
         <v/>
       </c>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="9">
+      <c r="M19" s="20">
         <f>IF(A19="","",IF(OR(J19="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J19,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="20">
         <f>IF(A19="","",IF(L19="",Inputs!$B$14,L19)+M19)</f>
         <v/>
       </c>
@@ -3968,30 +4007,30 @@
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="8">
+      <c r="F20" s="20">
         <f>IF(E20&lt;&gt;"",E20,IF(UPPER(TRIM(C20))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C20))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C20))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C20))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C20))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="20">
         <f>IF(A20="","",N20)</f>
         <v/>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="20">
         <f>IF(A20="","",Inputs!$B$3/((IF(G20="",Inputs!$B$14,G20)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="20">
         <f>IF(A20="","",2.78E-7*F20*D20*H20)</f>
         <v/>
       </c>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="9">
+      <c r="M20" s="20">
         <f>IF(A20="","",IF(OR(J20="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J20,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="20">
         <f>IF(A20="","",IF(L20="",Inputs!$B$14,L20)+M20)</f>
         <v/>
       </c>
@@ -4002,30 +4041,30 @@
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8">
+      <c r="F21" s="20">
         <f>IF(E21&lt;&gt;"",E21,IF(UPPER(TRIM(C21))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C21))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C21))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C21))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C21))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="20">
         <f>IF(A21="","",N21)</f>
         <v/>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="20">
         <f>IF(A21="","",Inputs!$B$3/((IF(G21="",Inputs!$B$14,G21)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="20">
         <f>IF(A21="","",2.78E-7*F21*D21*H21)</f>
         <v/>
       </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="5" t="n"/>
-      <c r="M21" s="9">
+      <c r="M21" s="20">
         <f>IF(A21="","",IF(OR(J21="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J21,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="20">
         <f>IF(A21="","",IF(L21="",Inputs!$B$14,L21)+M21)</f>
         <v/>
       </c>
@@ -4036,30 +4075,30 @@
       <c r="C22" s="4" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="8">
+      <c r="F22" s="20">
         <f>IF(E22&lt;&gt;"",E22,IF(UPPER(TRIM(C22))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C22))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C22))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C22))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C22))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="20">
         <f>IF(A22="","",N22)</f>
         <v/>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="20">
         <f>IF(A22="","",Inputs!$B$3/((IF(G22="",Inputs!$B$14,G22)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="20">
         <f>IF(A22="","",2.78E-7*F22*D22*H22)</f>
         <v/>
       </c>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="5" t="n"/>
-      <c r="M22" s="9">
+      <c r="M22" s="20">
         <f>IF(A22="","",IF(OR(J22="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J22,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="20">
         <f>IF(A22="","",IF(L22="",Inputs!$B$14,L22)+M22)</f>
         <v/>
       </c>
@@ -4070,30 +4109,30 @@
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8">
+      <c r="F23" s="20">
         <f>IF(E23&lt;&gt;"",E23,IF(UPPER(TRIM(C23))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C23))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C23))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C23))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C23))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="20">
         <f>IF(A23="","",N23)</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="20">
         <f>IF(A23="","",Inputs!$B$3/((IF(G23="",Inputs!$B$14,G23)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="20">
         <f>IF(A23="","",2.78E-7*F23*D23*H23)</f>
         <v/>
       </c>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="5" t="n"/>
-      <c r="M23" s="9">
+      <c r="M23" s="20">
         <f>IF(A23="","",IF(OR(J23="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J23,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="20">
         <f>IF(A23="","",IF(L23="",Inputs!$B$14,L23)+M23)</f>
         <v/>
       </c>
@@ -4104,30 +4143,30 @@
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8">
+      <c r="F24" s="20">
         <f>IF(E24&lt;&gt;"",E24,IF(UPPER(TRIM(C24))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C24))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C24))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C24))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C24))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="20">
         <f>IF(A24="","",N24)</f>
         <v/>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="20">
         <f>IF(A24="","",Inputs!$B$3/((IF(G24="",Inputs!$B$14,G24)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="20">
         <f>IF(A24="","",2.78E-7*F24*D24*H24)</f>
         <v/>
       </c>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="5" t="n"/>
-      <c r="M24" s="9">
+      <c r="M24" s="20">
         <f>IF(A24="","",IF(OR(J24="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J24,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="20">
         <f>IF(A24="","",IF(L24="",Inputs!$B$14,L24)+M24)</f>
         <v/>
       </c>
@@ -4138,30 +4177,30 @@
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="8">
+      <c r="F25" s="20">
         <f>IF(E25&lt;&gt;"",E25,IF(UPPER(TRIM(C25))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C25))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C25))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C25))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C25))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="20">
         <f>IF(A25="","",N25)</f>
         <v/>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="20">
         <f>IF(A25="","",Inputs!$B$3/((IF(G25="",Inputs!$B$14,G25)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="20">
         <f>IF(A25="","",2.78E-7*F25*D25*H25)</f>
         <v/>
       </c>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="5" t="n"/>
-      <c r="M25" s="9">
+      <c r="M25" s="20">
         <f>IF(A25="","",IF(OR(J25="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J25,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="20">
         <f>IF(A25="","",IF(L25="",Inputs!$B$14,L25)+M25)</f>
         <v/>
       </c>
@@ -4172,30 +4211,30 @@
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8">
+      <c r="F26" s="20">
         <f>IF(E26&lt;&gt;"",E26,IF(UPPER(TRIM(C26))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C26))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C26))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C26))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C26))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="20">
         <f>IF(A26="","",N26)</f>
         <v/>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="20">
         <f>IF(A26="","",Inputs!$B$3/((IF(G26="",Inputs!$B$14,G26)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="20">
         <f>IF(A26="","",2.78E-7*F26*D26*H26)</f>
         <v/>
       </c>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="5" t="n"/>
-      <c r="M26" s="9">
+      <c r="M26" s="20">
         <f>IF(A26="","",IF(OR(J26="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J26,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="20">
         <f>IF(A26="","",IF(L26="",Inputs!$B$14,L26)+M26)</f>
         <v/>
       </c>
@@ -4206,30 +4245,30 @@
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="8">
+      <c r="F27" s="20">
         <f>IF(E27&lt;&gt;"",E27,IF(UPPER(TRIM(C27))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C27))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C27))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C27))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C27))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="20">
         <f>IF(A27="","",N27)</f>
         <v/>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="20">
         <f>IF(A27="","",Inputs!$B$3/((IF(G27="",Inputs!$B$14,G27)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="20">
         <f>IF(A27="","",2.78E-7*F27*D27*H27)</f>
         <v/>
       </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="5" t="n"/>
-      <c r="M27" s="9">
+      <c r="M27" s="20">
         <f>IF(A27="","",IF(OR(J27="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J27,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N27" s="9">
+      <c r="N27" s="20">
         <f>IF(A27="","",IF(L27="",Inputs!$B$14,L27)+M27)</f>
         <v/>
       </c>
@@ -4240,30 +4279,30 @@
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8">
+      <c r="F28" s="20">
         <f>IF(E28&lt;&gt;"",E28,IF(UPPER(TRIM(C28))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C28))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C28))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C28))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C28))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="20">
         <f>IF(A28="","",N28)</f>
         <v/>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="20">
         <f>IF(A28="","",Inputs!$B$3/((IF(G28="",Inputs!$B$14,G28)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="20">
         <f>IF(A28="","",2.78E-7*F28*D28*H28)</f>
         <v/>
       </c>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="5" t="n"/>
-      <c r="M28" s="9">
+      <c r="M28" s="20">
         <f>IF(A28="","",IF(OR(J28="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J28,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N28" s="9">
+      <c r="N28" s="20">
         <f>IF(A28="","",IF(L28="",Inputs!$B$14,L28)+M28)</f>
         <v/>
       </c>
@@ -4274,30 +4313,30 @@
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8">
+      <c r="F29" s="20">
         <f>IF(E29&lt;&gt;"",E29,IF(UPPER(TRIM(C29))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C29))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C29))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C29))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C29))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="20">
         <f>IF(A29="","",N29)</f>
         <v/>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="20">
         <f>IF(A29="","",Inputs!$B$3/((IF(G29="",Inputs!$B$14,G29)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="20">
         <f>IF(A29="","",2.78E-7*F29*D29*H29)</f>
         <v/>
       </c>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="5" t="n"/>
-      <c r="M29" s="9">
+      <c r="M29" s="20">
         <f>IF(A29="","",IF(OR(J29="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J29,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="20">
         <f>IF(A29="","",IF(L29="",Inputs!$B$14,L29)+M29)</f>
         <v/>
       </c>
@@ -4308,30 +4347,30 @@
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
-      <c r="F30" s="8">
+      <c r="F30" s="20">
         <f>IF(E30&lt;&gt;"",E30,IF(UPPER(TRIM(C30))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C30))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C30))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C30))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C30))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="20">
         <f>IF(A30="","",N30)</f>
         <v/>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="20">
         <f>IF(A30="","",Inputs!$B$3/((IF(G30="",Inputs!$B$14,G30)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="20">
         <f>IF(A30="","",2.78E-7*F30*D30*H30)</f>
         <v/>
       </c>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="5" t="n"/>
-      <c r="M30" s="9">
+      <c r="M30" s="20">
         <f>IF(A30="","",IF(OR(J30="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J30,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="20">
         <f>IF(A30="","",IF(L30="",Inputs!$B$14,L30)+M30)</f>
         <v/>
       </c>
@@ -4342,30 +4381,30 @@
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="8">
+      <c r="F31" s="20">
         <f>IF(E31&lt;&gt;"",E31,IF(UPPER(TRIM(C31))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C31))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C31))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C31))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C31))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="20">
         <f>IF(A31="","",N31)</f>
         <v/>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="20">
         <f>IF(A31="","",Inputs!$B$3/((IF(G31="",Inputs!$B$14,G31)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="20">
         <f>IF(A31="","",2.78E-7*F31*D31*H31)</f>
         <v/>
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="5" t="n"/>
-      <c r="M31" s="9">
+      <c r="M31" s="20">
         <f>IF(A31="","",IF(OR(J31="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J31,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N31" s="9">
+      <c r="N31" s="20">
         <f>IF(A31="","",IF(L31="",Inputs!$B$14,L31)+M31)</f>
         <v/>
       </c>
@@ -4376,30 +4415,30 @@
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="8">
+      <c r="F32" s="20">
         <f>IF(E32&lt;&gt;"",E32,IF(UPPER(TRIM(C32))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C32))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C32))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C32))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C32))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="20">
         <f>IF(A32="","",N32)</f>
         <v/>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="20">
         <f>IF(A32="","",Inputs!$B$3/((IF(G32="",Inputs!$B$14,G32)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="20">
         <f>IF(A32="","",2.78E-7*F32*D32*H32)</f>
         <v/>
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="5" t="n"/>
-      <c r="M32" s="9">
+      <c r="M32" s="20">
         <f>IF(A32="","",IF(OR(J32="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J32,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="20">
         <f>IF(A32="","",IF(L32="",Inputs!$B$14,L32)+M32)</f>
         <v/>
       </c>
@@ -4410,30 +4449,30 @@
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="8">
+      <c r="F33" s="20">
         <f>IF(E33&lt;&gt;"",E33,IF(UPPER(TRIM(C33))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C33))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C33))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C33))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C33))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="20">
         <f>IF(A33="","",N33)</f>
         <v/>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="20">
         <f>IF(A33="","",Inputs!$B$3/((IF(G33="",Inputs!$B$14,G33)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="20">
         <f>IF(A33="","",2.78E-7*F33*D33*H33)</f>
         <v/>
       </c>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="5" t="n"/>
-      <c r="M33" s="9">
+      <c r="M33" s="20">
         <f>IF(A33="","",IF(OR(J33="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J33,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N33" s="9">
+      <c r="N33" s="20">
         <f>IF(A33="","",IF(L33="",Inputs!$B$14,L33)+M33)</f>
         <v/>
       </c>
@@ -4444,30 +4483,30 @@
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
-      <c r="F34" s="8">
+      <c r="F34" s="20">
         <f>IF(E34&lt;&gt;"",E34,IF(UPPER(TRIM(C34))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C34))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C34))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C34))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C34))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="20">
         <f>IF(A34="","",N34)</f>
         <v/>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="20">
         <f>IF(A34="","",Inputs!$B$3/((IF(G34="",Inputs!$B$14,G34)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="20">
         <f>IF(A34="","",2.78E-7*F34*D34*H34)</f>
         <v/>
       </c>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="5" t="n"/>
-      <c r="M34" s="9">
+      <c r="M34" s="20">
         <f>IF(A34="","",IF(OR(J34="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J34,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="20">
         <f>IF(A34="","",IF(L34="",Inputs!$B$14,L34)+M34)</f>
         <v/>
       </c>
@@ -4478,30 +4517,30 @@
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="8">
+      <c r="F35" s="20">
         <f>IF(E35&lt;&gt;"",E35,IF(UPPER(TRIM(C35))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C35))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C35))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C35))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C35))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="20">
         <f>IF(A35="","",N35)</f>
         <v/>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="20">
         <f>IF(A35="","",Inputs!$B$3/((IF(G35="",Inputs!$B$14,G35)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="20">
         <f>IF(A35="","",2.78E-7*F35*D35*H35)</f>
         <v/>
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="5" t="n"/>
-      <c r="M35" s="9">
+      <c r="M35" s="20">
         <f>IF(A35="","",IF(OR(J35="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J35,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N35" s="9">
+      <c r="N35" s="20">
         <f>IF(A35="","",IF(L35="",Inputs!$B$14,L35)+M35)</f>
         <v/>
       </c>
@@ -4512,30 +4551,30 @@
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="8">
+      <c r="F36" s="20">
         <f>IF(E36&lt;&gt;"",E36,IF(UPPER(TRIM(C36))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C36))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C36))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C36))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C36))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="20">
         <f>IF(A36="","",N36)</f>
         <v/>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="20">
         <f>IF(A36="","",Inputs!$B$3/((IF(G36="",Inputs!$B$14,G36)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="20">
         <f>IF(A36="","",2.78E-7*F36*D36*H36)</f>
         <v/>
       </c>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="5" t="n"/>
-      <c r="M36" s="9">
+      <c r="M36" s="20">
         <f>IF(A36="","",IF(OR(J36="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J36,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="20">
         <f>IF(A36="","",IF(L36="",Inputs!$B$14,L36)+M36)</f>
         <v/>
       </c>
@@ -4546,30 +4585,30 @@
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="8">
+      <c r="F37" s="20">
         <f>IF(E37&lt;&gt;"",E37,IF(UPPER(TRIM(C37))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C37))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C37))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C37))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C37))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="20">
         <f>IF(A37="","",N37)</f>
         <v/>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="20">
         <f>IF(A37="","",Inputs!$B$3/((IF(G37="",Inputs!$B$14,G37)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="20">
         <f>IF(A37="","",2.78E-7*F37*D37*H37)</f>
         <v/>
       </c>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="5" t="n"/>
-      <c r="M37" s="9">
+      <c r="M37" s="20">
         <f>IF(A37="","",IF(OR(J37="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J37,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N37" s="9">
+      <c r="N37" s="20">
         <f>IF(A37="","",IF(L37="",Inputs!$B$14,L37)+M37)</f>
         <v/>
       </c>
@@ -4580,30 +4619,30 @@
       <c r="C38" s="4" t="n"/>
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="7" t="n"/>
-      <c r="F38" s="8">
+      <c r="F38" s="20">
         <f>IF(E38&lt;&gt;"",E38,IF(UPPER(TRIM(C38))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C38))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C38))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C38))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C38))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="20">
         <f>IF(A38="","",N38)</f>
         <v/>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="20">
         <f>IF(A38="","",Inputs!$B$3/((IF(G38="",Inputs!$B$14,G38)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="20">
         <f>IF(A38="","",2.78E-7*F38*D38*H38)</f>
         <v/>
       </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="5" t="n"/>
-      <c r="M38" s="9">
+      <c r="M38" s="20">
         <f>IF(A38="","",IF(OR(J38="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J38,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N38" s="9">
+      <c r="N38" s="20">
         <f>IF(A38="","",IF(L38="",Inputs!$B$14,L38)+M38)</f>
         <v/>
       </c>
@@ -4614,30 +4653,30 @@
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="7" t="n"/>
-      <c r="F39" s="8">
+      <c r="F39" s="20">
         <f>IF(E39&lt;&gt;"",E39,IF(UPPER(TRIM(C39))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C39))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C39))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C39))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C39))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="20">
         <f>IF(A39="","",N39)</f>
         <v/>
       </c>
-      <c r="H39" s="8">
+      <c r="H39" s="20">
         <f>IF(A39="","",Inputs!$B$3/((IF(G39="",Inputs!$B$14,G39)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="20">
         <f>IF(A39="","",2.78E-7*F39*D39*H39)</f>
         <v/>
       </c>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="5" t="n"/>
-      <c r="M39" s="9">
+      <c r="M39" s="20">
         <f>IF(A39="","",IF(OR(J39="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J39,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N39" s="9">
+      <c r="N39" s="20">
         <f>IF(A39="","",IF(L39="",Inputs!$B$14,L39)+M39)</f>
         <v/>
       </c>
@@ -4648,30 +4687,30 @@
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="7" t="n"/>
-      <c r="F40" s="8">
+      <c r="F40" s="20">
         <f>IF(E40&lt;&gt;"",E40,IF(UPPER(TRIM(C40))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C40))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C40))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C40))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C40))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="20">
         <f>IF(A40="","",N40)</f>
         <v/>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="20">
         <f>IF(A40="","",Inputs!$B$3/((IF(G40="",Inputs!$B$14,G40)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="20">
         <f>IF(A40="","",2.78E-7*F40*D40*H40)</f>
         <v/>
       </c>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="5" t="n"/>
-      <c r="M40" s="9">
+      <c r="M40" s="20">
         <f>IF(A40="","",IF(OR(J40="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J40,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N40" s="9">
+      <c r="N40" s="20">
         <f>IF(A40="","",IF(L40="",Inputs!$B$14,L40)+M40)</f>
         <v/>
       </c>
@@ -4682,30 +4721,30 @@
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
-      <c r="F41" s="8">
+      <c r="F41" s="20">
         <f>IF(E41&lt;&gt;"",E41,IF(UPPER(TRIM(C41))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C41))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C41))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C41))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C41))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="20">
         <f>IF(A41="","",N41)</f>
         <v/>
       </c>
-      <c r="H41" s="8">
+      <c r="H41" s="20">
         <f>IF(A41="","",Inputs!$B$3/((IF(G41="",Inputs!$B$14,G41)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I41" s="8">
+      <c r="I41" s="20">
         <f>IF(A41="","",2.78E-7*F41*D41*H41)</f>
         <v/>
       </c>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="5" t="n"/>
-      <c r="M41" s="9">
+      <c r="M41" s="20">
         <f>IF(A41="","",IF(OR(J41="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J41,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N41" s="9">
+      <c r="N41" s="20">
         <f>IF(A41="","",IF(L41="",Inputs!$B$14,L41)+M41)</f>
         <v/>
       </c>
@@ -4716,30 +4755,30 @@
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
-      <c r="F42" s="8">
+      <c r="F42" s="20">
         <f>IF(E42&lt;&gt;"",E42,IF(UPPER(TRIM(C42))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C42))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C42))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C42))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C42))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="20">
         <f>IF(A42="","",N42)</f>
         <v/>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="20">
         <f>IF(A42="","",Inputs!$B$3/((IF(G42="",Inputs!$B$14,G42)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I42" s="8">
+      <c r="I42" s="20">
         <f>IF(A42="","",2.78E-7*F42*D42*H42)</f>
         <v/>
       </c>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="5" t="n"/>
-      <c r="M42" s="9">
+      <c r="M42" s="20">
         <f>IF(A42="","",IF(OR(J42="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J42,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N42" s="9">
+      <c r="N42" s="20">
         <f>IF(A42="","",IF(L42="",Inputs!$B$14,L42)+M42)</f>
         <v/>
       </c>
@@ -4750,30 +4789,30 @@
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="8">
+      <c r="F43" s="20">
         <f>IF(E43&lt;&gt;"",E43,IF(UPPER(TRIM(C43))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C43))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C43))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C43))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C43))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="20">
         <f>IF(A43="","",N43)</f>
         <v/>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="20">
         <f>IF(A43="","",Inputs!$B$3/((IF(G43="",Inputs!$B$14,G43)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I43" s="8">
+      <c r="I43" s="20">
         <f>IF(A43="","",2.78E-7*F43*D43*H43)</f>
         <v/>
       </c>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="5" t="n"/>
-      <c r="M43" s="9">
+      <c r="M43" s="20">
         <f>IF(A43="","",IF(OR(J43="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J43,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N43" s="9">
+      <c r="N43" s="20">
         <f>IF(A43="","",IF(L43="",Inputs!$B$14,L43)+M43)</f>
         <v/>
       </c>
@@ -4784,30 +4823,30 @@
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
-      <c r="F44" s="8">
+      <c r="F44" s="20">
         <f>IF(E44&lt;&gt;"",E44,IF(UPPER(TRIM(C44))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C44))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C44))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C44))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C44))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="20">
         <f>IF(A44="","",N44)</f>
         <v/>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="20">
         <f>IF(A44="","",Inputs!$B$3/((IF(G44="",Inputs!$B$14,G44)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="20">
         <f>IF(A44="","",2.78E-7*F44*D44*H44)</f>
         <v/>
       </c>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="5" t="n"/>
-      <c r="M44" s="9">
+      <c r="M44" s="20">
         <f>IF(A44="","",IF(OR(J44="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J44,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N44" s="9">
+      <c r="N44" s="20">
         <f>IF(A44="","",IF(L44="",Inputs!$B$14,L44)+M44)</f>
         <v/>
       </c>
@@ -4818,30 +4857,30 @@
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="8">
+      <c r="F45" s="20">
         <f>IF(E45&lt;&gt;"",E45,IF(UPPER(TRIM(C45))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C45))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C45))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C45))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C45))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="20">
         <f>IF(A45="","",N45)</f>
         <v/>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="20">
         <f>IF(A45="","",Inputs!$B$3/((IF(G45="",Inputs!$B$14,G45)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="20">
         <f>IF(A45="","",2.78E-7*F45*D45*H45)</f>
         <v/>
       </c>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="5" t="n"/>
-      <c r="M45" s="9">
+      <c r="M45" s="20">
         <f>IF(A45="","",IF(OR(J45="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J45,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N45" s="9">
+      <c r="N45" s="20">
         <f>IF(A45="","",IF(L45="",Inputs!$B$14,L45)+M45)</f>
         <v/>
       </c>
@@ -4852,30 +4891,30 @@
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
-      <c r="F46" s="8">
+      <c r="F46" s="20">
         <f>IF(E46&lt;&gt;"",E46,IF(UPPER(TRIM(C46))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C46))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C46))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C46))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C46))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="20">
         <f>IF(A46="","",N46)</f>
         <v/>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="20">
         <f>IF(A46="","",Inputs!$B$3/((IF(G46="",Inputs!$B$14,G46)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="20">
         <f>IF(A46="","",2.78E-7*F46*D46*H46)</f>
         <v/>
       </c>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="5" t="n"/>
-      <c r="M46" s="9">
+      <c r="M46" s="20">
         <f>IF(A46="","",IF(OR(J46="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J46,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N46" s="9">
+      <c r="N46" s="20">
         <f>IF(A46="","",IF(L46="",Inputs!$B$14,L46)+M46)</f>
         <v/>
       </c>
@@ -4886,30 +4925,30 @@
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="7" t="n"/>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="8">
+      <c r="F47" s="20">
         <f>IF(E47&lt;&gt;"",E47,IF(UPPER(TRIM(C47))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C47))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C47))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C47))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C47))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="20">
         <f>IF(A47="","",N47)</f>
         <v/>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="20">
         <f>IF(A47="","",Inputs!$B$3/((IF(G47="",Inputs!$B$14,G47)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="20">
         <f>IF(A47="","",2.78E-7*F47*D47*H47)</f>
         <v/>
       </c>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="5" t="n"/>
-      <c r="M47" s="9">
+      <c r="M47" s="20">
         <f>IF(A47="","",IF(OR(J47="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J47,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N47" s="9">
+      <c r="N47" s="20">
         <f>IF(A47="","",IF(L47="",Inputs!$B$14,L47)+M47)</f>
         <v/>
       </c>
@@ -4920,30 +4959,30 @@
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
-      <c r="F48" s="8">
+      <c r="F48" s="20">
         <f>IF(E48&lt;&gt;"",E48,IF(UPPER(TRIM(C48))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C48))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C48))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C48))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C48))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="20">
         <f>IF(A48="","",N48)</f>
         <v/>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="20">
         <f>IF(A48="","",Inputs!$B$3/((IF(G48="",Inputs!$B$14,G48)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="20">
         <f>IF(A48="","",2.78E-7*F48*D48*H48)</f>
         <v/>
       </c>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="5" t="n"/>
-      <c r="M48" s="9">
+      <c r="M48" s="20">
         <f>IF(A48="","",IF(OR(J48="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J48,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N48" s="9">
+      <c r="N48" s="20">
         <f>IF(A48="","",IF(L48="",Inputs!$B$14,L48)+M48)</f>
         <v/>
       </c>
@@ -4954,30 +4993,30 @@
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
-      <c r="F49" s="8">
+      <c r="F49" s="20">
         <f>IF(E49&lt;&gt;"",E49,IF(UPPER(TRIM(C49))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C49))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C49))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C49))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C49))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="20">
         <f>IF(A49="","",N49)</f>
         <v/>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="20">
         <f>IF(A49="","",Inputs!$B$3/((IF(G49="",Inputs!$B$14,G49)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="20">
         <f>IF(A49="","",2.78E-7*F49*D49*H49)</f>
         <v/>
       </c>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="5" t="n"/>
-      <c r="M49" s="9">
+      <c r="M49" s="20">
         <f>IF(A49="","",IF(OR(J49="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J49,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N49" s="9">
+      <c r="N49" s="20">
         <f>IF(A49="","",IF(L49="",Inputs!$B$14,L49)+M49)</f>
         <v/>
       </c>
@@ -4988,30 +5027,30 @@
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="8">
+      <c r="F50" s="20">
         <f>IF(E50&lt;&gt;"",E50,IF(UPPER(TRIM(C50))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C50))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C50))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C50))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C50))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="20">
         <f>IF(A50="","",N50)</f>
         <v/>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="20">
         <f>IF(A50="","",Inputs!$B$3/((IF(G50="",Inputs!$B$14,G50)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I50" s="8">
+      <c r="I50" s="20">
         <f>IF(A50="","",2.78E-7*F50*D50*H50)</f>
         <v/>
       </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="5" t="n"/>
-      <c r="M50" s="9">
+      <c r="M50" s="20">
         <f>IF(A50="","",IF(OR(J50="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J50,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N50" s="9">
+      <c r="N50" s="20">
         <f>IF(A50="","",IF(L50="",Inputs!$B$14,L50)+M50)</f>
         <v/>
       </c>
@@ -5022,30 +5061,30 @@
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="8">
+      <c r="F51" s="20">
         <f>IF(E51&lt;&gt;"",E51,IF(UPPER(TRIM(C51))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C51))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C51))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C51))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C51))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="20">
         <f>IF(A51="","",N51)</f>
         <v/>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="20">
         <f>IF(A51="","",Inputs!$B$3/((IF(G51="",Inputs!$B$14,G51)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="20">
         <f>IF(A51="","",2.78E-7*F51*D51*H51)</f>
         <v/>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="5" t="n"/>
-      <c r="M51" s="9">
+      <c r="M51" s="20">
         <f>IF(A51="","",IF(OR(J51="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J51,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N51" s="9">
+      <c r="N51" s="20">
         <f>IF(A51="","",IF(L51="",Inputs!$B$14,L51)+M51)</f>
         <v/>
       </c>
@@ -5056,30 +5095,30 @@
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="8">
+      <c r="F52" s="20">
         <f>IF(E52&lt;&gt;"",E52,IF(UPPER(TRIM(C52))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C52))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C52))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C52))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C52))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="20">
         <f>IF(A52="","",N52)</f>
         <v/>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="20">
         <f>IF(A52="","",Inputs!$B$3/((IF(G52="",Inputs!$B$14,G52)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="20">
         <f>IF(A52="","",2.78E-7*F52*D52*H52)</f>
         <v/>
       </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="5" t="n"/>
-      <c r="M52" s="9">
+      <c r="M52" s="20">
         <f>IF(A52="","",IF(OR(J52="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J52,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N52" s="9">
+      <c r="N52" s="20">
         <f>IF(A52="","",IF(L52="",Inputs!$B$14,L52)+M52)</f>
         <v/>
       </c>
@@ -5090,30 +5129,30 @@
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="7" t="n"/>
       <c r="E53" s="7" t="n"/>
-      <c r="F53" s="8">
+      <c r="F53" s="20">
         <f>IF(E53&lt;&gt;"",E53,IF(UPPER(TRIM(C53))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C53))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C53))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C53))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C53))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="20">
         <f>IF(A53="","",N53)</f>
         <v/>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="20">
         <f>IF(A53="","",Inputs!$B$3/((IF(G53="",Inputs!$B$14,G53)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="20">
         <f>IF(A53="","",2.78E-7*F53*D53*H53)</f>
         <v/>
       </c>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="5" t="n"/>
-      <c r="M53" s="9">
+      <c r="M53" s="20">
         <f>IF(A53="","",IF(OR(J53="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J53,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N53" s="9">
+      <c r="N53" s="20">
         <f>IF(A53="","",IF(L53="",Inputs!$B$14,L53)+M53)</f>
         <v/>
       </c>
@@ -5124,30 +5163,30 @@
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="7" t="n"/>
       <c r="E54" s="7" t="n"/>
-      <c r="F54" s="8">
+      <c r="F54" s="20">
         <f>IF(E54&lt;&gt;"",E54,IF(UPPER(TRIM(C54))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C54))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C54))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C54))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C54))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="20">
         <f>IF(A54="","",N54)</f>
         <v/>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="20">
         <f>IF(A54="","",Inputs!$B$3/((IF(G54="",Inputs!$B$14,G54)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="20">
         <f>IF(A54="","",2.78E-7*F54*D54*H54)</f>
         <v/>
       </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="5" t="n"/>
-      <c r="M54" s="9">
+      <c r="M54" s="20">
         <f>IF(A54="","",IF(OR(J54="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J54,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N54" s="9">
+      <c r="N54" s="20">
         <f>IF(A54="","",IF(L54="",Inputs!$B$14,L54)+M54)</f>
         <v/>
       </c>
@@ -5158,30 +5197,30 @@
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="8">
+      <c r="F55" s="20">
         <f>IF(E55&lt;&gt;"",E55,IF(UPPER(TRIM(C55))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C55))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C55))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C55))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C55))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="20">
         <f>IF(A55="","",N55)</f>
         <v/>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="20">
         <f>IF(A55="","",Inputs!$B$3/((IF(G55="",Inputs!$B$14,G55)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="20">
         <f>IF(A55="","",2.78E-7*F55*D55*H55)</f>
         <v/>
       </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="5" t="n"/>
-      <c r="M55" s="9">
+      <c r="M55" s="20">
         <f>IF(A55="","",IF(OR(J55="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J55,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N55" s="9">
+      <c r="N55" s="20">
         <f>IF(A55="","",IF(L55="",Inputs!$B$14,L55)+M55)</f>
         <v/>
       </c>
@@ -5192,30 +5231,30 @@
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="8">
+      <c r="F56" s="20">
         <f>IF(E56&lt;&gt;"",E56,IF(UPPER(TRIM(C56))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C56))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C56))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C56))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C56))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="20">
         <f>IF(A56="","",N56)</f>
         <v/>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="20">
         <f>IF(A56="","",Inputs!$B$3/((IF(G56="",Inputs!$B$14,G56)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="20">
         <f>IF(A56="","",2.78E-7*F56*D56*H56)</f>
         <v/>
       </c>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="5" t="n"/>
-      <c r="M56" s="9">
+      <c r="M56" s="20">
         <f>IF(A56="","",IF(OR(J56="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J56,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N56" s="9">
+      <c r="N56" s="20">
         <f>IF(A56="","",IF(L56="",Inputs!$B$14,L56)+M56)</f>
         <v/>
       </c>
@@ -5226,30 +5265,30 @@
       <c r="C57" s="4" t="n"/>
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="8">
+      <c r="F57" s="20">
         <f>IF(E57&lt;&gt;"",E57,IF(UPPER(TRIM(C57))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C57))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C57))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C57))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C57))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="20">
         <f>IF(A57="","",N57)</f>
         <v/>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="20">
         <f>IF(A57="","",Inputs!$B$3/((IF(G57="",Inputs!$B$14,G57)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="20">
         <f>IF(A57="","",2.78E-7*F57*D57*H57)</f>
         <v/>
       </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="5" t="n"/>
-      <c r="M57" s="9">
+      <c r="M57" s="20">
         <f>IF(A57="","",IF(OR(J57="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J57,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N57" s="9">
+      <c r="N57" s="20">
         <f>IF(A57="","",IF(L57="",Inputs!$B$14,L57)+M57)</f>
         <v/>
       </c>
@@ -5260,30 +5299,30 @@
       <c r="C58" s="4" t="n"/>
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="8">
+      <c r="F58" s="20">
         <f>IF(E58&lt;&gt;"",E58,IF(UPPER(TRIM(C58))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C58))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C58))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C58))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C58))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="20">
         <f>IF(A58="","",N58)</f>
         <v/>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="20">
         <f>IF(A58="","",Inputs!$B$3/((IF(G58="",Inputs!$B$14,G58)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="20">
         <f>IF(A58="","",2.78E-7*F58*D58*H58)</f>
         <v/>
       </c>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="5" t="n"/>
-      <c r="M58" s="9">
+      <c r="M58" s="20">
         <f>IF(A58="","",IF(OR(J58="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J58,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N58" s="9">
+      <c r="N58" s="20">
         <f>IF(A58="","",IF(L58="",Inputs!$B$14,L58)+M58)</f>
         <v/>
       </c>
@@ -5294,30 +5333,30 @@
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="8">
+      <c r="F59" s="20">
         <f>IF(E59&lt;&gt;"",E59,IF(UPPER(TRIM(C59))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C59))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C59))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C59))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C59))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="20">
         <f>IF(A59="","",N59)</f>
         <v/>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="20">
         <f>IF(A59="","",Inputs!$B$3/((IF(G59="",Inputs!$B$14,G59)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="20">
         <f>IF(A59="","",2.78E-7*F59*D59*H59)</f>
         <v/>
       </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="5" t="n"/>
-      <c r="M59" s="9">
+      <c r="M59" s="20">
         <f>IF(A59="","",IF(OR(J59="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J59,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N59" s="9">
+      <c r="N59" s="20">
         <f>IF(A59="","",IF(L59="",Inputs!$B$14,L59)+M59)</f>
         <v/>
       </c>
@@ -5328,30 +5367,30 @@
       <c r="C60" s="4" t="n"/>
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="7" t="n"/>
-      <c r="F60" s="8">
+      <c r="F60" s="20">
         <f>IF(E60&lt;&gt;"",E60,IF(UPPER(TRIM(C60))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C60))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C60))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C60))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C60))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="20">
         <f>IF(A60="","",N60)</f>
         <v/>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="20">
         <f>IF(A60="","",Inputs!$B$3/((IF(G60="",Inputs!$B$14,G60)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I60" s="8">
+      <c r="I60" s="20">
         <f>IF(A60="","",2.78E-7*F60*D60*H60)</f>
         <v/>
       </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="5" t="n"/>
-      <c r="M60" s="9">
+      <c r="M60" s="20">
         <f>IF(A60="","",IF(OR(J60="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J60,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N60" s="9">
+      <c r="N60" s="20">
         <f>IF(A60="","",IF(L60="",Inputs!$B$14,L60)+M60)</f>
         <v/>
       </c>
@@ -5362,30 +5401,30 @@
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
-      <c r="F61" s="8">
+      <c r="F61" s="20">
         <f>IF(E61&lt;&gt;"",E61,IF(UPPER(TRIM(C61))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C61))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C61))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C61))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C61))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="20">
         <f>IF(A61="","",N61)</f>
         <v/>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="20">
         <f>IF(A61="","",Inputs!$B$3/((IF(G61="",Inputs!$B$14,G61)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I61" s="8">
+      <c r="I61" s="20">
         <f>IF(A61="","",2.78E-7*F61*D61*H61)</f>
         <v/>
       </c>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="5" t="n"/>
-      <c r="M61" s="9">
+      <c r="M61" s="20">
         <f>IF(A61="","",IF(OR(J61="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J61,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N61" s="9">
+      <c r="N61" s="20">
         <f>IF(A61="","",IF(L61="",Inputs!$B$14,L61)+M61)</f>
         <v/>
       </c>
@@ -5396,30 +5435,30 @@
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="8">
+      <c r="F62" s="20">
         <f>IF(E62&lt;&gt;"",E62,IF(UPPER(TRIM(C62))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C62))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C62))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C62))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C62))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="20">
         <f>IF(A62="","",N62)</f>
         <v/>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="20">
         <f>IF(A62="","",Inputs!$B$3/((IF(G62="",Inputs!$B$14,G62)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="20">
         <f>IF(A62="","",2.78E-7*F62*D62*H62)</f>
         <v/>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="5" t="n"/>
-      <c r="M62" s="9">
+      <c r="M62" s="20">
         <f>IF(A62="","",IF(OR(J62="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J62,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N62" s="9">
+      <c r="N62" s="20">
         <f>IF(A62="","",IF(L62="",Inputs!$B$14,L62)+M62)</f>
         <v/>
       </c>
@@ -5430,30 +5469,30 @@
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="7" t="n"/>
-      <c r="F63" s="8">
+      <c r="F63" s="20">
         <f>IF(E63&lt;&gt;"",E63,IF(UPPER(TRIM(C63))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C63))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C63))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C63))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C63))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="20">
         <f>IF(A63="","",N63)</f>
         <v/>
       </c>
-      <c r="H63" s="8">
+      <c r="H63" s="20">
         <f>IF(A63="","",Inputs!$B$3/((IF(G63="",Inputs!$B$14,G63)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I63" s="8">
+      <c r="I63" s="20">
         <f>IF(A63="","",2.78E-7*F63*D63*H63)</f>
         <v/>
       </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="5" t="n"/>
-      <c r="M63" s="9">
+      <c r="M63" s="20">
         <f>IF(A63="","",IF(OR(J63="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J63,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N63" s="9">
+      <c r="N63" s="20">
         <f>IF(A63="","",IF(L63="",Inputs!$B$14,L63)+M63)</f>
         <v/>
       </c>
@@ -5464,30 +5503,30 @@
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="8">
+      <c r="F64" s="20">
         <f>IF(E64&lt;&gt;"",E64,IF(UPPER(TRIM(C64))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C64))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C64))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C64))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C64))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="20">
         <f>IF(A64="","",N64)</f>
         <v/>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="20">
         <f>IF(A64="","",Inputs!$B$3/((IF(G64="",Inputs!$B$14,G64)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I64" s="8">
+      <c r="I64" s="20">
         <f>IF(A64="","",2.78E-7*F64*D64*H64)</f>
         <v/>
       </c>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="5" t="n"/>
-      <c r="M64" s="9">
+      <c r="M64" s="20">
         <f>IF(A64="","",IF(OR(J64="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J64,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N64" s="9">
+      <c r="N64" s="20">
         <f>IF(A64="","",IF(L64="",Inputs!$B$14,L64)+M64)</f>
         <v/>
       </c>
@@ -5498,30 +5537,30 @@
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="7" t="n"/>
-      <c r="F65" s="8">
+      <c r="F65" s="20">
         <f>IF(E65&lt;&gt;"",E65,IF(UPPER(TRIM(C65))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C65))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C65))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C65))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C65))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="20">
         <f>IF(A65="","",N65)</f>
         <v/>
       </c>
-      <c r="H65" s="8">
+      <c r="H65" s="20">
         <f>IF(A65="","",Inputs!$B$3/((IF(G65="",Inputs!$B$14,G65)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I65" s="8">
+      <c r="I65" s="20">
         <f>IF(A65="","",2.78E-7*F65*D65*H65)</f>
         <v/>
       </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="5" t="n"/>
-      <c r="M65" s="9">
+      <c r="M65" s="20">
         <f>IF(A65="","",IF(OR(J65="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J65,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N65" s="9">
+      <c r="N65" s="20">
         <f>IF(A65="","",IF(L65="",Inputs!$B$14,L65)+M65)</f>
         <v/>
       </c>
@@ -5532,30 +5571,30 @@
       <c r="C66" s="4" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="8">
+      <c r="F66" s="20">
         <f>IF(E66&lt;&gt;"",E66,IF(UPPER(TRIM(C66))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C66))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C66))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C66))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C66))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="20">
         <f>IF(A66="","",N66)</f>
         <v/>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="20">
         <f>IF(A66="","",Inputs!$B$3/((IF(G66="",Inputs!$B$14,G66)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I66" s="8">
+      <c r="I66" s="20">
         <f>IF(A66="","",2.78E-7*F66*D66*H66)</f>
         <v/>
       </c>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="5" t="n"/>
-      <c r="M66" s="9">
+      <c r="M66" s="20">
         <f>IF(A66="","",IF(OR(J66="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J66,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N66" s="9">
+      <c r="N66" s="20">
         <f>IF(A66="","",IF(L66="",Inputs!$B$14,L66)+M66)</f>
         <v/>
       </c>
@@ -5566,30 +5605,30 @@
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="7" t="n"/>
-      <c r="F67" s="8">
+      <c r="F67" s="20">
         <f>IF(E67&lt;&gt;"",E67,IF(UPPER(TRIM(C67))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C67))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C67))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C67))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C67))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="20">
         <f>IF(A67="","",N67)</f>
         <v/>
       </c>
-      <c r="H67" s="8">
+      <c r="H67" s="20">
         <f>IF(A67="","",Inputs!$B$3/((IF(G67="",Inputs!$B$14,G67)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I67" s="8">
+      <c r="I67" s="20">
         <f>IF(A67="","",2.78E-7*F67*D67*H67)</f>
         <v/>
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="5" t="n"/>
-      <c r="M67" s="9">
+      <c r="M67" s="20">
         <f>IF(A67="","",IF(OR(J67="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J67,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N67" s="9">
+      <c r="N67" s="20">
         <f>IF(A67="","",IF(L67="",Inputs!$B$14,L67)+M67)</f>
         <v/>
       </c>
@@ -5600,30 +5639,30 @@
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="8">
+      <c r="F68" s="20">
         <f>IF(E68&lt;&gt;"",E68,IF(UPPER(TRIM(C68))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C68))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C68))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C68))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C68))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="20">
         <f>IF(A68="","",N68)</f>
         <v/>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="20">
         <f>IF(A68="","",Inputs!$B$3/((IF(G68="",Inputs!$B$14,G68)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I68" s="8">
+      <c r="I68" s="20">
         <f>IF(A68="","",2.78E-7*F68*D68*H68)</f>
         <v/>
       </c>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="5" t="n"/>
-      <c r="M68" s="9">
+      <c r="M68" s="20">
         <f>IF(A68="","",IF(OR(J68="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J68,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N68" s="9">
+      <c r="N68" s="20">
         <f>IF(A68="","",IF(L68="",Inputs!$B$14,L68)+M68)</f>
         <v/>
       </c>
@@ -5634,30 +5673,30 @@
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
-      <c r="F69" s="8">
+      <c r="F69" s="20">
         <f>IF(E69&lt;&gt;"",E69,IF(UPPER(TRIM(C69))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C69))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C69))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C69))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C69))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="20">
         <f>IF(A69="","",N69)</f>
         <v/>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="20">
         <f>IF(A69="","",Inputs!$B$3/((IF(G69="",Inputs!$B$14,G69)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I69" s="8">
+      <c r="I69" s="20">
         <f>IF(A69="","",2.78E-7*F69*D69*H69)</f>
         <v/>
       </c>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="5" t="n"/>
-      <c r="M69" s="9">
+      <c r="M69" s="20">
         <f>IF(A69="","",IF(OR(J69="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J69,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N69" s="9">
+      <c r="N69" s="20">
         <f>IF(A69="","",IF(L69="",Inputs!$B$14,L69)+M69)</f>
         <v/>
       </c>
@@ -5668,30 +5707,30 @@
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="8">
+      <c r="F70" s="20">
         <f>IF(E70&lt;&gt;"",E70,IF(UPPER(TRIM(C70))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C70))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C70))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C70))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C70))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="20">
         <f>IF(A70="","",N70)</f>
         <v/>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="20">
         <f>IF(A70="","",Inputs!$B$3/((IF(G70="",Inputs!$B$14,G70)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="20">
         <f>IF(A70="","",2.78E-7*F70*D70*H70)</f>
         <v/>
       </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="5" t="n"/>
-      <c r="M70" s="9">
+      <c r="M70" s="20">
         <f>IF(A70="","",IF(OR(J70="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J70,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N70" s="9">
+      <c r="N70" s="20">
         <f>IF(A70="","",IF(L70="",Inputs!$B$14,L70)+M70)</f>
         <v/>
       </c>
@@ -5702,30 +5741,30 @@
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
-      <c r="F71" s="8">
+      <c r="F71" s="20">
         <f>IF(E71&lt;&gt;"",E71,IF(UPPER(TRIM(C71))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C71))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C71))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C71))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C71))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="20">
         <f>IF(A71="","",N71)</f>
         <v/>
       </c>
-      <c r="H71" s="8">
+      <c r="H71" s="20">
         <f>IF(A71="","",Inputs!$B$3/((IF(G71="",Inputs!$B$14,G71)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I71" s="8">
+      <c r="I71" s="20">
         <f>IF(A71="","",2.78E-7*F71*D71*H71)</f>
         <v/>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="5" t="n"/>
-      <c r="M71" s="9">
+      <c r="M71" s="20">
         <f>IF(A71="","",IF(OR(J71="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J71,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N71" s="9">
+      <c r="N71" s="20">
         <f>IF(A71="","",IF(L71="",Inputs!$B$14,L71)+M71)</f>
         <v/>
       </c>
@@ -5736,30 +5775,30 @@
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="7" t="n"/>
-      <c r="F72" s="8">
+      <c r="F72" s="20">
         <f>IF(E72&lt;&gt;"",E72,IF(UPPER(TRIM(C72))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C72))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C72))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C72))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C72))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="20">
         <f>IF(A72="","",N72)</f>
         <v/>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="20">
         <f>IF(A72="","",Inputs!$B$3/((IF(G72="",Inputs!$B$14,G72)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="20">
         <f>IF(A72="","",2.78E-7*F72*D72*H72)</f>
         <v/>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="5" t="n"/>
-      <c r="M72" s="9">
+      <c r="M72" s="20">
         <f>IF(A72="","",IF(OR(J72="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J72,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N72" s="9">
+      <c r="N72" s="20">
         <f>IF(A72="","",IF(L72="",Inputs!$B$14,L72)+M72)</f>
         <v/>
       </c>
@@ -5770,30 +5809,30 @@
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="7" t="n"/>
-      <c r="F73" s="8">
+      <c r="F73" s="20">
         <f>IF(E73&lt;&gt;"",E73,IF(UPPER(TRIM(C73))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C73))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C73))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C73))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C73))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="20">
         <f>IF(A73="","",N73)</f>
         <v/>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="20">
         <f>IF(A73="","",Inputs!$B$3/((IF(G73="",Inputs!$B$14,G73)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="20">
         <f>IF(A73="","",2.78E-7*F73*D73*H73)</f>
         <v/>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="5" t="n"/>
-      <c r="M73" s="9">
+      <c r="M73" s="20">
         <f>IF(A73="","",IF(OR(J73="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J73,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N73" s="9">
+      <c r="N73" s="20">
         <f>IF(A73="","",IF(L73="",Inputs!$B$14,L73)+M73)</f>
         <v/>
       </c>
@@ -5804,30 +5843,30 @@
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="7" t="n"/>
-      <c r="F74" s="8">
+      <c r="F74" s="20">
         <f>IF(E74&lt;&gt;"",E74,IF(UPPER(TRIM(C74))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C74))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C74))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C74))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C74))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="20">
         <f>IF(A74="","",N74)</f>
         <v/>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="20">
         <f>IF(A74="","",Inputs!$B$3/((IF(G74="",Inputs!$B$14,G74)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="20">
         <f>IF(A74="","",2.78E-7*F74*D74*H74)</f>
         <v/>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="5" t="n"/>
-      <c r="M74" s="9">
+      <c r="M74" s="20">
         <f>IF(A74="","",IF(OR(J74="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J74,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N74" s="9">
+      <c r="N74" s="20">
         <f>IF(A74="","",IF(L74="",Inputs!$B$14,L74)+M74)</f>
         <v/>
       </c>
@@ -5838,30 +5877,30 @@
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="7" t="n"/>
-      <c r="F75" s="8">
+      <c r="F75" s="20">
         <f>IF(E75&lt;&gt;"",E75,IF(UPPER(TRIM(C75))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C75))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C75))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C75))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C75))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="20">
         <f>IF(A75="","",N75)</f>
         <v/>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="20">
         <f>IF(A75="","",Inputs!$B$3/((IF(G75="",Inputs!$B$14,G75)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="20">
         <f>IF(A75="","",2.78E-7*F75*D75*H75)</f>
         <v/>
       </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="5" t="n"/>
-      <c r="M75" s="9">
+      <c r="M75" s="20">
         <f>IF(A75="","",IF(OR(J75="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J75,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N75" s="9">
+      <c r="N75" s="20">
         <f>IF(A75="","",IF(L75="",Inputs!$B$14,L75)+M75)</f>
         <v/>
       </c>
@@ -5872,30 +5911,30 @@
       <c r="C76" s="4" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="8">
+      <c r="F76" s="20">
         <f>IF(E76&lt;&gt;"",E76,IF(UPPER(TRIM(C76))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C76))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C76))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C76))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C76))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="20">
         <f>IF(A76="","",N76)</f>
         <v/>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="20">
         <f>IF(A76="","",Inputs!$B$3/((IF(G76="",Inputs!$B$14,G76)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I76" s="8">
+      <c r="I76" s="20">
         <f>IF(A76="","",2.78E-7*F76*D76*H76)</f>
         <v/>
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="5" t="n"/>
-      <c r="M76" s="9">
+      <c r="M76" s="20">
         <f>IF(A76="","",IF(OR(J76="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J76,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N76" s="9">
+      <c r="N76" s="20">
         <f>IF(A76="","",IF(L76="",Inputs!$B$14,L76)+M76)</f>
         <v/>
       </c>
@@ -5906,30 +5945,30 @@
       <c r="C77" s="4" t="n"/>
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="8">
+      <c r="F77" s="20">
         <f>IF(E77&lt;&gt;"",E77,IF(UPPER(TRIM(C77))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C77))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C77))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C77))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C77))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="20">
         <f>IF(A77="","",N77)</f>
         <v/>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="20">
         <f>IF(A77="","",Inputs!$B$3/((IF(G77="",Inputs!$B$14,G77)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I77" s="8">
+      <c r="I77" s="20">
         <f>IF(A77="","",2.78E-7*F77*D77*H77)</f>
         <v/>
       </c>
       <c r="J77" s="4" t="n"/>
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="5" t="n"/>
-      <c r="M77" s="9">
+      <c r="M77" s="20">
         <f>IF(A77="","",IF(OR(J77="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J77,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N77" s="9">
+      <c r="N77" s="20">
         <f>IF(A77="","",IF(L77="",Inputs!$B$14,L77)+M77)</f>
         <v/>
       </c>
@@ -5940,30 +5979,30 @@
       <c r="C78" s="4" t="n"/>
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="7" t="n"/>
-      <c r="F78" s="8">
+      <c r="F78" s="20">
         <f>IF(E78&lt;&gt;"",E78,IF(UPPER(TRIM(C78))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C78))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C78))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C78))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C78))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="20">
         <f>IF(A78="","",N78)</f>
         <v/>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="20">
         <f>IF(A78="","",Inputs!$B$3/((IF(G78="",Inputs!$B$14,G78)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I78" s="8">
+      <c r="I78" s="20">
         <f>IF(A78="","",2.78E-7*F78*D78*H78)</f>
         <v/>
       </c>
       <c r="J78" s="4" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="5" t="n"/>
-      <c r="M78" s="9">
+      <c r="M78" s="20">
         <f>IF(A78="","",IF(OR(J78="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J78,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N78" s="9">
+      <c r="N78" s="20">
         <f>IF(A78="","",IF(L78="",Inputs!$B$14,L78)+M78)</f>
         <v/>
       </c>
@@ -5974,30 +6013,30 @@
       <c r="C79" s="4" t="n"/>
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="8">
+      <c r="F79" s="20">
         <f>IF(E79&lt;&gt;"",E79,IF(UPPER(TRIM(C79))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C79))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C79))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C79))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C79))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="20">
         <f>IF(A79="","",N79)</f>
         <v/>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="20">
         <f>IF(A79="","",Inputs!$B$3/((IF(G79="",Inputs!$B$14,G79)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="20">
         <f>IF(A79="","",2.78E-7*F79*D79*H79)</f>
         <v/>
       </c>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="5" t="n"/>
-      <c r="M79" s="9">
+      <c r="M79" s="20">
         <f>IF(A79="","",IF(OR(J79="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J79,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N79" s="9">
+      <c r="N79" s="20">
         <f>IF(A79="","",IF(L79="",Inputs!$B$14,L79)+M79)</f>
         <v/>
       </c>
@@ -6008,30 +6047,30 @@
       <c r="C80" s="4" t="n"/>
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="8">
+      <c r="F80" s="20">
         <f>IF(E80&lt;&gt;"",E80,IF(UPPER(TRIM(C80))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C80))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C80))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C80))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C80))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="20">
         <f>IF(A80="","",N80)</f>
         <v/>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="20">
         <f>IF(A80="","",Inputs!$B$3/((IF(G80="",Inputs!$B$14,G80)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="20">
         <f>IF(A80="","",2.78E-7*F80*D80*H80)</f>
         <v/>
       </c>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="5" t="n"/>
-      <c r="M80" s="9">
+      <c r="M80" s="20">
         <f>IF(A80="","",IF(OR(J80="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J80,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N80" s="9">
+      <c r="N80" s="20">
         <f>IF(A80="","",IF(L80="",Inputs!$B$14,L80)+M80)</f>
         <v/>
       </c>
@@ -6042,30 +6081,30 @@
       <c r="C81" s="4" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="8">
+      <c r="F81" s="20">
         <f>IF(E81&lt;&gt;"",E81,IF(UPPER(TRIM(C81))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C81))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C81))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C81))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C81))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="20">
         <f>IF(A81="","",N81)</f>
         <v/>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="20">
         <f>IF(A81="","",Inputs!$B$3/((IF(G81="",Inputs!$B$14,G81)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I81" s="8">
+      <c r="I81" s="20">
         <f>IF(A81="","",2.78E-7*F81*D81*H81)</f>
         <v/>
       </c>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="5" t="n"/>
-      <c r="M81" s="9">
+      <c r="M81" s="20">
         <f>IF(A81="","",IF(OR(J81="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J81,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N81" s="9">
+      <c r="N81" s="20">
         <f>IF(A81="","",IF(L81="",Inputs!$B$14,L81)+M81)</f>
         <v/>
       </c>
@@ -6076,30 +6115,30 @@
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="7" t="n"/>
-      <c r="F82" s="8">
+      <c r="F82" s="20">
         <f>IF(E82&lt;&gt;"",E82,IF(UPPER(TRIM(C82))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C82))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C82))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C82))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C82))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="20">
         <f>IF(A82="","",N82)</f>
         <v/>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="20">
         <f>IF(A82="","",Inputs!$B$3/((IF(G82="",Inputs!$B$14,G82)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I82" s="8">
+      <c r="I82" s="20">
         <f>IF(A82="","",2.78E-7*F82*D82*H82)</f>
         <v/>
       </c>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="5" t="n"/>
-      <c r="M82" s="9">
+      <c r="M82" s="20">
         <f>IF(A82="","",IF(OR(J82="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J82,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N82" s="9">
+      <c r="N82" s="20">
         <f>IF(A82="","",IF(L82="",Inputs!$B$14,L82)+M82)</f>
         <v/>
       </c>
@@ -6110,30 +6149,30 @@
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="7" t="n"/>
-      <c r="F83" s="8">
+      <c r="F83" s="20">
         <f>IF(E83&lt;&gt;"",E83,IF(UPPER(TRIM(C83))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C83))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C83))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C83))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C83))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="20">
         <f>IF(A83="","",N83)</f>
         <v/>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="20">
         <f>IF(A83="","",Inputs!$B$3/((IF(G83="",Inputs!$B$14,G83)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I83" s="8">
+      <c r="I83" s="20">
         <f>IF(A83="","",2.78E-7*F83*D83*H83)</f>
         <v/>
       </c>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="5" t="n"/>
-      <c r="M83" s="9">
+      <c r="M83" s="20">
         <f>IF(A83="","",IF(OR(J83="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J83,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N83" s="9">
+      <c r="N83" s="20">
         <f>IF(A83="","",IF(L83="",Inputs!$B$14,L83)+M83)</f>
         <v/>
       </c>
@@ -6144,30 +6183,30 @@
       <c r="C84" s="4" t="n"/>
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="7" t="n"/>
-      <c r="F84" s="8">
+      <c r="F84" s="20">
         <f>IF(E84&lt;&gt;"",E84,IF(UPPER(TRIM(C84))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C84))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C84))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C84))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C84))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="20">
         <f>IF(A84="","",N84)</f>
         <v/>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="20">
         <f>IF(A84="","",Inputs!$B$3/((IF(G84="",Inputs!$B$14,G84)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I84" s="8">
+      <c r="I84" s="20">
         <f>IF(A84="","",2.78E-7*F84*D84*H84)</f>
         <v/>
       </c>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="5" t="n"/>
-      <c r="M84" s="9">
+      <c r="M84" s="20">
         <f>IF(A84="","",IF(OR(J84="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J84,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N84" s="9">
+      <c r="N84" s="20">
         <f>IF(A84="","",IF(L84="",Inputs!$B$14,L84)+M84)</f>
         <v/>
       </c>
@@ -6178,30 +6217,30 @@
       <c r="C85" s="4" t="n"/>
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="8">
+      <c r="F85" s="20">
         <f>IF(E85&lt;&gt;"",E85,IF(UPPER(TRIM(C85))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C85))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C85))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C85))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C85))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G85" s="8">
+      <c r="G85" s="20">
         <f>IF(A85="","",N85)</f>
         <v/>
       </c>
-      <c r="H85" s="8">
+      <c r="H85" s="20">
         <f>IF(A85="","",Inputs!$B$3/((IF(G85="",Inputs!$B$14,G85)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="20">
         <f>IF(A85="","",2.78E-7*F85*D85*H85)</f>
         <v/>
       </c>
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="5" t="n"/>
-      <c r="M85" s="9">
+      <c r="M85" s="20">
         <f>IF(A85="","",IF(OR(J85="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J85,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N85" s="9">
+      <c r="N85" s="20">
         <f>IF(A85="","",IF(L85="",Inputs!$B$14,L85)+M85)</f>
         <v/>
       </c>
@@ -6212,30 +6251,30 @@
       <c r="C86" s="4" t="n"/>
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
-      <c r="F86" s="8">
+      <c r="F86" s="20">
         <f>IF(E86&lt;&gt;"",E86,IF(UPPER(TRIM(C86))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C86))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C86))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C86))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C86))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="20">
         <f>IF(A86="","",N86)</f>
         <v/>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="20">
         <f>IF(A86="","",Inputs!$B$3/((IF(G86="",Inputs!$B$14,G86)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I86" s="8">
+      <c r="I86" s="20">
         <f>IF(A86="","",2.78E-7*F86*D86*H86)</f>
         <v/>
       </c>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="5" t="n"/>
-      <c r="M86" s="9">
+      <c r="M86" s="20">
         <f>IF(A86="","",IF(OR(J86="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J86,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N86" s="9">
+      <c r="N86" s="20">
         <f>IF(A86="","",IF(L86="",Inputs!$B$14,L86)+M86)</f>
         <v/>
       </c>
@@ -6246,30 +6285,30 @@
       <c r="C87" s="4" t="n"/>
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="7" t="n"/>
-      <c r="F87" s="8">
+      <c r="F87" s="20">
         <f>IF(E87&lt;&gt;"",E87,IF(UPPER(TRIM(C87))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C87))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C87))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C87))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C87))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G87" s="8">
+      <c r="G87" s="20">
         <f>IF(A87="","",N87)</f>
         <v/>
       </c>
-      <c r="H87" s="8">
+      <c r="H87" s="20">
         <f>IF(A87="","",Inputs!$B$3/((IF(G87="",Inputs!$B$14,G87)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I87" s="8">
+      <c r="I87" s="20">
         <f>IF(A87="","",2.78E-7*F87*D87*H87)</f>
         <v/>
       </c>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="5" t="n"/>
-      <c r="M87" s="9">
+      <c r="M87" s="20">
         <f>IF(A87="","",IF(OR(J87="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J87,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N87" s="9">
+      <c r="N87" s="20">
         <f>IF(A87="","",IF(L87="",Inputs!$B$14,L87)+M87)</f>
         <v/>
       </c>
@@ -6280,30 +6319,30 @@
       <c r="C88" s="4" t="n"/>
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="8">
+      <c r="F88" s="20">
         <f>IF(E88&lt;&gt;"",E88,IF(UPPER(TRIM(C88))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C88))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C88))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C88))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C88))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G88" s="8">
+      <c r="G88" s="20">
         <f>IF(A88="","",N88)</f>
         <v/>
       </c>
-      <c r="H88" s="8">
+      <c r="H88" s="20">
         <f>IF(A88="","",Inputs!$B$3/((IF(G88="",Inputs!$B$14,G88)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I88" s="8">
+      <c r="I88" s="20">
         <f>IF(A88="","",2.78E-7*F88*D88*H88)</f>
         <v/>
       </c>
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="5" t="n"/>
-      <c r="M88" s="9">
+      <c r="M88" s="20">
         <f>IF(A88="","",IF(OR(J88="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J88,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N88" s="9">
+      <c r="N88" s="20">
         <f>IF(A88="","",IF(L88="",Inputs!$B$14,L88)+M88)</f>
         <v/>
       </c>
@@ -6314,30 +6353,30 @@
       <c r="C89" s="4" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="8">
+      <c r="F89" s="20">
         <f>IF(E89&lt;&gt;"",E89,IF(UPPER(TRIM(C89))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C89))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C89))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C89))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C89))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G89" s="8">
+      <c r="G89" s="20">
         <f>IF(A89="","",N89)</f>
         <v/>
       </c>
-      <c r="H89" s="8">
+      <c r="H89" s="20">
         <f>IF(A89="","",Inputs!$B$3/((IF(G89="",Inputs!$B$14,G89)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I89" s="8">
+      <c r="I89" s="20">
         <f>IF(A89="","",2.78E-7*F89*D89*H89)</f>
         <v/>
       </c>
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="5" t="n"/>
-      <c r="M89" s="9">
+      <c r="M89" s="20">
         <f>IF(A89="","",IF(OR(J89="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J89,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N89" s="9">
+      <c r="N89" s="20">
         <f>IF(A89="","",IF(L89="",Inputs!$B$14,L89)+M89)</f>
         <v/>
       </c>
@@ -6348,30 +6387,30 @@
       <c r="C90" s="4" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="8">
+      <c r="F90" s="20">
         <f>IF(E90&lt;&gt;"",E90,IF(UPPER(TRIM(C90))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C90))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C90))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C90))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C90))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G90" s="8">
+      <c r="G90" s="20">
         <f>IF(A90="","",N90)</f>
         <v/>
       </c>
-      <c r="H90" s="8">
+      <c r="H90" s="20">
         <f>IF(A90="","",Inputs!$B$3/((IF(G90="",Inputs!$B$14,G90)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I90" s="8">
+      <c r="I90" s="20">
         <f>IF(A90="","",2.78E-7*F90*D90*H90)</f>
         <v/>
       </c>
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="5" t="n"/>
-      <c r="M90" s="9">
+      <c r="M90" s="20">
         <f>IF(A90="","",IF(OR(J90="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J90,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N90" s="9">
+      <c r="N90" s="20">
         <f>IF(A90="","",IF(L90="",Inputs!$B$14,L90)+M90)</f>
         <v/>
       </c>
@@ -6382,30 +6421,30 @@
       <c r="C91" s="4" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="8">
+      <c r="F91" s="20">
         <f>IF(E91&lt;&gt;"",E91,IF(UPPER(TRIM(C91))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C91))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C91))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C91))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C91))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G91" s="8">
+      <c r="G91" s="20">
         <f>IF(A91="","",N91)</f>
         <v/>
       </c>
-      <c r="H91" s="8">
+      <c r="H91" s="20">
         <f>IF(A91="","",Inputs!$B$3/((IF(G91="",Inputs!$B$14,G91)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I91" s="8">
+      <c r="I91" s="20">
         <f>IF(A91="","",2.78E-7*F91*D91*H91)</f>
         <v/>
       </c>
       <c r="J91" s="4" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="5" t="n"/>
-      <c r="M91" s="9">
+      <c r="M91" s="20">
         <f>IF(A91="","",IF(OR(J91="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J91,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N91" s="9">
+      <c r="N91" s="20">
         <f>IF(A91="","",IF(L91="",Inputs!$B$14,L91)+M91)</f>
         <v/>
       </c>
@@ -6416,30 +6455,30 @@
       <c r="C92" s="4" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="8">
+      <c r="F92" s="20">
         <f>IF(E92&lt;&gt;"",E92,IF(UPPER(TRIM(C92))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C92))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C92))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C92))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C92))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="20">
         <f>IF(A92="","",N92)</f>
         <v/>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="20">
         <f>IF(A92="","",Inputs!$B$3/((IF(G92="",Inputs!$B$14,G92)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="20">
         <f>IF(A92="","",2.78E-7*F92*D92*H92)</f>
         <v/>
       </c>
       <c r="J92" s="4" t="n"/>
       <c r="K92" s="4" t="n"/>
       <c r="L92" s="5" t="n"/>
-      <c r="M92" s="9">
+      <c r="M92" s="20">
         <f>IF(A92="","",IF(OR(J92="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J92,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N92" s="9">
+      <c r="N92" s="20">
         <f>IF(A92="","",IF(L92="",Inputs!$B$14,L92)+M92)</f>
         <v/>
       </c>
@@ -6450,30 +6489,30 @@
       <c r="C93" s="4" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="8">
+      <c r="F93" s="20">
         <f>IF(E93&lt;&gt;"",E93,IF(UPPER(TRIM(C93))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C93))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C93))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C93))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C93))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="20">
         <f>IF(A93="","",N93)</f>
         <v/>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="20">
         <f>IF(A93="","",Inputs!$B$3/((IF(G93="",Inputs!$B$14,G93)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I93" s="8">
+      <c r="I93" s="20">
         <f>IF(A93="","",2.78E-7*F93*D93*H93)</f>
         <v/>
       </c>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="5" t="n"/>
-      <c r="M93" s="9">
+      <c r="M93" s="20">
         <f>IF(A93="","",IF(OR(J93="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J93,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N93" s="9">
+      <c r="N93" s="20">
         <f>IF(A93="","",IF(L93="",Inputs!$B$14,L93)+M93)</f>
         <v/>
       </c>
@@ -6484,30 +6523,30 @@
       <c r="C94" s="4" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="8">
+      <c r="F94" s="20">
         <f>IF(E94&lt;&gt;"",E94,IF(UPPER(TRIM(C94))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C94))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C94))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C94))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C94))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="20">
         <f>IF(A94="","",N94)</f>
         <v/>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="20">
         <f>IF(A94="","",Inputs!$B$3/((IF(G94="",Inputs!$B$14,G94)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I94" s="8">
+      <c r="I94" s="20">
         <f>IF(A94="","",2.78E-7*F94*D94*H94)</f>
         <v/>
       </c>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="5" t="n"/>
-      <c r="M94" s="9">
+      <c r="M94" s="20">
         <f>IF(A94="","",IF(OR(J94="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J94,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N94" s="9">
+      <c r="N94" s="20">
         <f>IF(A94="","",IF(L94="",Inputs!$B$14,L94)+M94)</f>
         <v/>
       </c>
@@ -6518,30 +6557,30 @@
       <c r="C95" s="4" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="8">
+      <c r="F95" s="20">
         <f>IF(E95&lt;&gt;"",E95,IF(UPPER(TRIM(C95))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C95))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C95))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C95))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C95))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="20">
         <f>IF(A95="","",N95)</f>
         <v/>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="20">
         <f>IF(A95="","",Inputs!$B$3/((IF(G95="",Inputs!$B$14,G95)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I95" s="8">
+      <c r="I95" s="20">
         <f>IF(A95="","",2.78E-7*F95*D95*H95)</f>
         <v/>
       </c>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="5" t="n"/>
-      <c r="M95" s="9">
+      <c r="M95" s="20">
         <f>IF(A95="","",IF(OR(J95="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J95,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N95" s="9">
+      <c r="N95" s="20">
         <f>IF(A95="","",IF(L95="",Inputs!$B$14,L95)+M95)</f>
         <v/>
       </c>
@@ -6552,30 +6591,30 @@
       <c r="C96" s="4" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="8">
+      <c r="F96" s="20">
         <f>IF(E96&lt;&gt;"",E96,IF(UPPER(TRIM(C96))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C96))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C96))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C96))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C96))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="20">
         <f>IF(A96="","",N96)</f>
         <v/>
       </c>
-      <c r="H96" s="8">
+      <c r="H96" s="20">
         <f>IF(A96="","",Inputs!$B$3/((IF(G96="",Inputs!$B$14,G96)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I96" s="8">
+      <c r="I96" s="20">
         <f>IF(A96="","",2.78E-7*F96*D96*H96)</f>
         <v/>
       </c>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="5" t="n"/>
-      <c r="M96" s="9">
+      <c r="M96" s="20">
         <f>IF(A96="","",IF(OR(J96="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J96,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N96" s="9">
+      <c r="N96" s="20">
         <f>IF(A96="","",IF(L96="",Inputs!$B$14,L96)+M96)</f>
         <v/>
       </c>
@@ -6586,30 +6625,30 @@
       <c r="C97" s="4" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="8">
+      <c r="F97" s="20">
         <f>IF(E97&lt;&gt;"",E97,IF(UPPER(TRIM(C97))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C97))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C97))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C97))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C97))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G97" s="8">
+      <c r="G97" s="20">
         <f>IF(A97="","",N97)</f>
         <v/>
       </c>
-      <c r="H97" s="8">
+      <c r="H97" s="20">
         <f>IF(A97="","",Inputs!$B$3/((IF(G97="",Inputs!$B$14,G97)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I97" s="8">
+      <c r="I97" s="20">
         <f>IF(A97="","",2.78E-7*F97*D97*H97)</f>
         <v/>
       </c>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="5" t="n"/>
-      <c r="M97" s="9">
+      <c r="M97" s="20">
         <f>IF(A97="","",IF(OR(J97="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J97,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N97" s="9">
+      <c r="N97" s="20">
         <f>IF(A97="","",IF(L97="",Inputs!$B$14,L97)+M97)</f>
         <v/>
       </c>
@@ -6620,30 +6659,30 @@
       <c r="C98" s="4" t="n"/>
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="8">
+      <c r="F98" s="20">
         <f>IF(E98&lt;&gt;"",E98,IF(UPPER(TRIM(C98))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C98))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C98))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C98))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C98))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="20">
         <f>IF(A98="","",N98)</f>
         <v/>
       </c>
-      <c r="H98" s="8">
+      <c r="H98" s="20">
         <f>IF(A98="","",Inputs!$B$3/((IF(G98="",Inputs!$B$14,G98)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I98" s="8">
+      <c r="I98" s="20">
         <f>IF(A98="","",2.78E-7*F98*D98*H98)</f>
         <v/>
       </c>
       <c r="J98" s="4" t="n"/>
       <c r="K98" s="4" t="n"/>
       <c r="L98" s="5" t="n"/>
-      <c r="M98" s="9">
+      <c r="M98" s="20">
         <f>IF(A98="","",IF(OR(J98="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J98,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N98" s="9">
+      <c r="N98" s="20">
         <f>IF(A98="","",IF(L98="",Inputs!$B$14,L98)+M98)</f>
         <v/>
       </c>
@@ -6654,30 +6693,30 @@
       <c r="C99" s="4" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="8">
+      <c r="F99" s="20">
         <f>IF(E99&lt;&gt;"",E99,IF(UPPER(TRIM(C99))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C99))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C99))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C99))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C99))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G99" s="8">
+      <c r="G99" s="20">
         <f>IF(A99="","",N99)</f>
         <v/>
       </c>
-      <c r="H99" s="8">
+      <c r="H99" s="20">
         <f>IF(A99="","",Inputs!$B$3/((IF(G99="",Inputs!$B$14,G99)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I99" s="8">
+      <c r="I99" s="20">
         <f>IF(A99="","",2.78E-7*F99*D99*H99)</f>
         <v/>
       </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
       <c r="L99" s="5" t="n"/>
-      <c r="M99" s="9">
+      <c r="M99" s="20">
         <f>IF(A99="","",IF(OR(J99="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J99,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N99" s="9">
+      <c r="N99" s="20">
         <f>IF(A99="","",IF(L99="",Inputs!$B$14,L99)+M99)</f>
         <v/>
       </c>
@@ -6688,30 +6727,30 @@
       <c r="C100" s="4" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
-      <c r="F100" s="8">
+      <c r="F100" s="20">
         <f>IF(E100&lt;&gt;"",E100,IF(UPPER(TRIM(C100))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C100))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C100))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C100))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C100))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G100" s="8">
+      <c r="G100" s="20">
         <f>IF(A100="","",N100)</f>
         <v/>
       </c>
-      <c r="H100" s="8">
+      <c r="H100" s="20">
         <f>IF(A100="","",Inputs!$B$3/((IF(G100="",Inputs!$B$14,G100)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I100" s="8">
+      <c r="I100" s="20">
         <f>IF(A100="","",2.78E-7*F100*D100*H100)</f>
         <v/>
       </c>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="5" t="n"/>
-      <c r="M100" s="9">
+      <c r="M100" s="20">
         <f>IF(A100="","",IF(OR(J100="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J100,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N100" s="9">
+      <c r="N100" s="20">
         <f>IF(A100="","",IF(L100="",Inputs!$B$14,L100)+M100)</f>
         <v/>
       </c>
@@ -6722,30 +6761,30 @@
       <c r="C101" s="4" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="8">
+      <c r="F101" s="20">
         <f>IF(E101&lt;&gt;"",E101,IF(UPPER(TRIM(C101))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C101))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C101))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C101))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C101))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="20">
         <f>IF(A101="","",N101)</f>
         <v/>
       </c>
-      <c r="H101" s="8">
+      <c r="H101" s="20">
         <f>IF(A101="","",Inputs!$B$3/((IF(G101="",Inputs!$B$14,G101)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I101" s="8">
+      <c r="I101" s="20">
         <f>IF(A101="","",2.78E-7*F101*D101*H101)</f>
         <v/>
       </c>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="5" t="n"/>
-      <c r="M101" s="9">
+      <c r="M101" s="20">
         <f>IF(A101="","",IF(OR(J101="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J101,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N101" s="9">
+      <c r="N101" s="20">
         <f>IF(A101="","",IF(L101="",Inputs!$B$14,L101)+M101)</f>
         <v/>
       </c>
@@ -6756,30 +6795,30 @@
       <c r="C102" s="4" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
-      <c r="F102" s="8">
+      <c r="F102" s="20">
         <f>IF(E102&lt;&gt;"",E102,IF(UPPER(TRIM(C102))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C102))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C102))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C102))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C102))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G102" s="8">
+      <c r="G102" s="20">
         <f>IF(A102="","",N102)</f>
         <v/>
       </c>
-      <c r="H102" s="8">
+      <c r="H102" s="20">
         <f>IF(A102="","",Inputs!$B$3/((IF(G102="",Inputs!$B$14,G102)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I102" s="8">
+      <c r="I102" s="20">
         <f>IF(A102="","",2.78E-7*F102*D102*H102)</f>
         <v/>
       </c>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="5" t="n"/>
-      <c r="M102" s="9">
+      <c r="M102" s="20">
         <f>IF(A102="","",IF(OR(J102="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J102,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N102" s="9">
+      <c r="N102" s="20">
         <f>IF(A102="","",IF(L102="",Inputs!$B$14,L102)+M102)</f>
         <v/>
       </c>
@@ -6790,30 +6829,30 @@
       <c r="C103" s="4" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="8">
+      <c r="F103" s="20">
         <f>IF(E103&lt;&gt;"",E103,IF(UPPER(TRIM(C103))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C103))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C103))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C103))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C103))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G103" s="8">
+      <c r="G103" s="20">
         <f>IF(A103="","",N103)</f>
         <v/>
       </c>
-      <c r="H103" s="8">
+      <c r="H103" s="20">
         <f>IF(A103="","",Inputs!$B$3/((IF(G103="",Inputs!$B$14,G103)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I103" s="8">
+      <c r="I103" s="20">
         <f>IF(A103="","",2.78E-7*F103*D103*H103)</f>
         <v/>
       </c>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="5" t="n"/>
-      <c r="M103" s="9">
+      <c r="M103" s="20">
         <f>IF(A103="","",IF(OR(J103="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J103,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N103" s="9">
+      <c r="N103" s="20">
         <f>IF(A103="","",IF(L103="",Inputs!$B$14,L103)+M103)</f>
         <v/>
       </c>
@@ -6824,30 +6863,30 @@
       <c r="C104" s="4" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8">
+      <c r="F104" s="20">
         <f>IF(E104&lt;&gt;"",E104,IF(UPPER(TRIM(C104))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C104))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C104))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C104))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C104))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="20">
         <f>IF(A104="","",N104)</f>
         <v/>
       </c>
-      <c r="H104" s="8">
+      <c r="H104" s="20">
         <f>IF(A104="","",Inputs!$B$3/((IF(G104="",Inputs!$B$14,G104)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I104" s="8">
+      <c r="I104" s="20">
         <f>IF(A104="","",2.78E-7*F104*D104*H104)</f>
         <v/>
       </c>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="5" t="n"/>
-      <c r="M104" s="9">
+      <c r="M104" s="20">
         <f>IF(A104="","",IF(OR(J104="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J104,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N104" s="9">
+      <c r="N104" s="20">
         <f>IF(A104="","",IF(L104="",Inputs!$B$14,L104)+M104)</f>
         <v/>
       </c>
@@ -6858,30 +6897,30 @@
       <c r="C105" s="4" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="8">
+      <c r="F105" s="20">
         <f>IF(E105&lt;&gt;"",E105,IF(UPPER(TRIM(C105))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C105))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C105))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C105))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C105))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G105" s="8">
+      <c r="G105" s="20">
         <f>IF(A105="","",N105)</f>
         <v/>
       </c>
-      <c r="H105" s="8">
+      <c r="H105" s="20">
         <f>IF(A105="","",Inputs!$B$3/((IF(G105="",Inputs!$B$14,G105)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I105" s="8">
+      <c r="I105" s="20">
         <f>IF(A105="","",2.78E-7*F105*D105*H105)</f>
         <v/>
       </c>
       <c r="J105" s="4" t="n"/>
       <c r="K105" s="4" t="n"/>
       <c r="L105" s="5" t="n"/>
-      <c r="M105" s="9">
+      <c r="M105" s="20">
         <f>IF(A105="","",IF(OR(J105="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J105,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N105" s="9">
+      <c r="N105" s="20">
         <f>IF(A105="","",IF(L105="",Inputs!$B$14,L105)+M105)</f>
         <v/>
       </c>
@@ -6892,30 +6931,30 @@
       <c r="C106" s="4" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
-      <c r="F106" s="8">
+      <c r="F106" s="20">
         <f>IF(E106&lt;&gt;"",E106,IF(UPPER(TRIM(C106))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C106))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C106))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C106))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C106))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G106" s="8">
+      <c r="G106" s="20">
         <f>IF(A106="","",N106)</f>
         <v/>
       </c>
-      <c r="H106" s="8">
+      <c r="H106" s="20">
         <f>IF(A106="","",Inputs!$B$3/((IF(G106="",Inputs!$B$14,G106)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I106" s="8">
+      <c r="I106" s="20">
         <f>IF(A106="","",2.78E-7*F106*D106*H106)</f>
         <v/>
       </c>
       <c r="J106" s="4" t="n"/>
       <c r="K106" s="4" t="n"/>
       <c r="L106" s="5" t="n"/>
-      <c r="M106" s="9">
+      <c r="M106" s="20">
         <f>IF(A106="","",IF(OR(J106="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J106,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N106" s="9">
+      <c r="N106" s="20">
         <f>IF(A106="","",IF(L106="",Inputs!$B$14,L106)+M106)</f>
         <v/>
       </c>
@@ -6926,30 +6965,30 @@
       <c r="C107" s="4" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="8">
+      <c r="F107" s="20">
         <f>IF(E107&lt;&gt;"",E107,IF(UPPER(TRIM(C107))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C107))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C107))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C107))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C107))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="20">
         <f>IF(A107="","",N107)</f>
         <v/>
       </c>
-      <c r="H107" s="8">
+      <c r="H107" s="20">
         <f>IF(A107="","",Inputs!$B$3/((IF(G107="",Inputs!$B$14,G107)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I107" s="8">
+      <c r="I107" s="20">
         <f>IF(A107="","",2.78E-7*F107*D107*H107)</f>
         <v/>
       </c>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="5" t="n"/>
-      <c r="M107" s="9">
+      <c r="M107" s="20">
         <f>IF(A107="","",IF(OR(J107="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J107,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N107" s="9">
+      <c r="N107" s="20">
         <f>IF(A107="","",IF(L107="",Inputs!$B$14,L107)+M107)</f>
         <v/>
       </c>
@@ -6960,30 +6999,30 @@
       <c r="C108" s="4" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="8">
+      <c r="F108" s="20">
         <f>IF(E108&lt;&gt;"",E108,IF(UPPER(TRIM(C108))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C108))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C108))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C108))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C108))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="20">
         <f>IF(A108="","",N108)</f>
         <v/>
       </c>
-      <c r="H108" s="8">
+      <c r="H108" s="20">
         <f>IF(A108="","",Inputs!$B$3/((IF(G108="",Inputs!$B$14,G108)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I108" s="8">
+      <c r="I108" s="20">
         <f>IF(A108="","",2.78E-7*F108*D108*H108)</f>
         <v/>
       </c>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="5" t="n"/>
-      <c r="M108" s="9">
+      <c r="M108" s="20">
         <f>IF(A108="","",IF(OR(J108="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J108,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N108" s="9">
+      <c r="N108" s="20">
         <f>IF(A108="","",IF(L108="",Inputs!$B$14,L108)+M108)</f>
         <v/>
       </c>
@@ -6994,30 +7033,30 @@
       <c r="C109" s="4" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
-      <c r="F109" s="8">
+      <c r="F109" s="20">
         <f>IF(E109&lt;&gt;"",E109,IF(UPPER(TRIM(C109))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C109))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C109))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C109))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C109))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="20">
         <f>IF(A109="","",N109)</f>
         <v/>
       </c>
-      <c r="H109" s="8">
+      <c r="H109" s="20">
         <f>IF(A109="","",Inputs!$B$3/((IF(G109="",Inputs!$B$14,G109)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I109" s="8">
+      <c r="I109" s="20">
         <f>IF(A109="","",2.78E-7*F109*D109*H109)</f>
         <v/>
       </c>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="5" t="n"/>
-      <c r="M109" s="9">
+      <c r="M109" s="20">
         <f>IF(A109="","",IF(OR(J109="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J109,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N109" s="9">
+      <c r="N109" s="20">
         <f>IF(A109="","",IF(L109="",Inputs!$B$14,L109)+M109)</f>
         <v/>
       </c>
@@ -7028,30 +7067,30 @@
       <c r="C110" s="4" t="n"/>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
-      <c r="F110" s="8">
+      <c r="F110" s="20">
         <f>IF(E110&lt;&gt;"",E110,IF(UPPER(TRIM(C110))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C110))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C110))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C110))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C110))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="20">
         <f>IF(A110="","",N110)</f>
         <v/>
       </c>
-      <c r="H110" s="8">
+      <c r="H110" s="20">
         <f>IF(A110="","",Inputs!$B$3/((IF(G110="",Inputs!$B$14,G110)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I110" s="8">
+      <c r="I110" s="20">
         <f>IF(A110="","",2.78E-7*F110*D110*H110)</f>
         <v/>
       </c>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="5" t="n"/>
-      <c r="M110" s="9">
+      <c r="M110" s="20">
         <f>IF(A110="","",IF(OR(J110="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J110,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N110" s="9">
+      <c r="N110" s="20">
         <f>IF(A110="","",IF(L110="",Inputs!$B$14,L110)+M110)</f>
         <v/>
       </c>
@@ -7062,30 +7101,30 @@
       <c r="C111" s="4" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8">
+      <c r="F111" s="20">
         <f>IF(E111&lt;&gt;"",E111,IF(UPPER(TRIM(C111))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C111))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C111))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C111))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C111))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="20">
         <f>IF(A111="","",N111)</f>
         <v/>
       </c>
-      <c r="H111" s="8">
+      <c r="H111" s="20">
         <f>IF(A111="","",Inputs!$B$3/((IF(G111="",Inputs!$B$14,G111)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I111" s="8">
+      <c r="I111" s="20">
         <f>IF(A111="","",2.78E-7*F111*D111*H111)</f>
         <v/>
       </c>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="5" t="n"/>
-      <c r="M111" s="9">
+      <c r="M111" s="20">
         <f>IF(A111="","",IF(OR(J111="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J111,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N111" s="9">
+      <c r="N111" s="20">
         <f>IF(A111="","",IF(L111="",Inputs!$B$14,L111)+M111)</f>
         <v/>
       </c>
@@ -7096,30 +7135,30 @@
       <c r="C112" s="4" t="n"/>
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8">
+      <c r="F112" s="20">
         <f>IF(E112&lt;&gt;"",E112,IF(UPPER(TRIM(C112))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C112))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C112))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C112))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C112))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="20">
         <f>IF(A112="","",N112)</f>
         <v/>
       </c>
-      <c r="H112" s="8">
+      <c r="H112" s="20">
         <f>IF(A112="","",Inputs!$B$3/((IF(G112="",Inputs!$B$14,G112)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I112" s="8">
+      <c r="I112" s="20">
         <f>IF(A112="","",2.78E-7*F112*D112*H112)</f>
         <v/>
       </c>
       <c r="J112" s="4" t="n"/>
       <c r="K112" s="4" t="n"/>
       <c r="L112" s="5" t="n"/>
-      <c r="M112" s="9">
+      <c r="M112" s="20">
         <f>IF(A112="","",IF(OR(J112="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J112,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N112" s="9">
+      <c r="N112" s="20">
         <f>IF(A112="","",IF(L112="",Inputs!$B$14,L112)+M112)</f>
         <v/>
       </c>
@@ -7130,30 +7169,30 @@
       <c r="C113" s="4" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
-      <c r="F113" s="8">
+      <c r="F113" s="20">
         <f>IF(E113&lt;&gt;"",E113,IF(UPPER(TRIM(C113))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C113))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C113))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C113))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C113))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G113" s="8">
+      <c r="G113" s="20">
         <f>IF(A113="","",N113)</f>
         <v/>
       </c>
-      <c r="H113" s="8">
+      <c r="H113" s="20">
         <f>IF(A113="","",Inputs!$B$3/((IF(G113="",Inputs!$B$14,G113)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I113" s="8">
+      <c r="I113" s="20">
         <f>IF(A113="","",2.78E-7*F113*D113*H113)</f>
         <v/>
       </c>
       <c r="J113" s="4" t="n"/>
       <c r="K113" s="4" t="n"/>
       <c r="L113" s="5" t="n"/>
-      <c r="M113" s="9">
+      <c r="M113" s="20">
         <f>IF(A113="","",IF(OR(J113="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J113,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N113" s="9">
+      <c r="N113" s="20">
         <f>IF(A113="","",IF(L113="",Inputs!$B$14,L113)+M113)</f>
         <v/>
       </c>
@@ -7164,30 +7203,30 @@
       <c r="C114" s="4" t="n"/>
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
-      <c r="F114" s="8">
+      <c r="F114" s="20">
         <f>IF(E114&lt;&gt;"",E114,IF(UPPER(TRIM(C114))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C114))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C114))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C114))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C114))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G114" s="8">
+      <c r="G114" s="20">
         <f>IF(A114="","",N114)</f>
         <v/>
       </c>
-      <c r="H114" s="8">
+      <c r="H114" s="20">
         <f>IF(A114="","",Inputs!$B$3/((IF(G114="",Inputs!$B$14,G114)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I114" s="8">
+      <c r="I114" s="20">
         <f>IF(A114="","",2.78E-7*F114*D114*H114)</f>
         <v/>
       </c>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="5" t="n"/>
-      <c r="M114" s="9">
+      <c r="M114" s="20">
         <f>IF(A114="","",IF(OR(J114="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J114,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N114" s="9">
+      <c r="N114" s="20">
         <f>IF(A114="","",IF(L114="",Inputs!$B$14,L114)+M114)</f>
         <v/>
       </c>
@@ -7198,30 +7237,30 @@
       <c r="C115" s="4" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="8">
+      <c r="F115" s="20">
         <f>IF(E115&lt;&gt;"",E115,IF(UPPER(TRIM(C115))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C115))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C115))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C115))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C115))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G115" s="8">
+      <c r="G115" s="20">
         <f>IF(A115="","",N115)</f>
         <v/>
       </c>
-      <c r="H115" s="8">
+      <c r="H115" s="20">
         <f>IF(A115="","",Inputs!$B$3/((IF(G115="",Inputs!$B$14,G115)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I115" s="8">
+      <c r="I115" s="20">
         <f>IF(A115="","",2.78E-7*F115*D115*H115)</f>
         <v/>
       </c>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="5" t="n"/>
-      <c r="M115" s="9">
+      <c r="M115" s="20">
         <f>IF(A115="","",IF(OR(J115="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J115,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N115" s="9">
+      <c r="N115" s="20">
         <f>IF(A115="","",IF(L115="",Inputs!$B$14,L115)+M115)</f>
         <v/>
       </c>
@@ -7232,30 +7271,30 @@
       <c r="C116" s="4" t="n"/>
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
-      <c r="F116" s="8">
+      <c r="F116" s="20">
         <f>IF(E116&lt;&gt;"",E116,IF(UPPER(TRIM(C116))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C116))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C116))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C116))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C116))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G116" s="8">
+      <c r="G116" s="20">
         <f>IF(A116="","",N116)</f>
         <v/>
       </c>
-      <c r="H116" s="8">
+      <c r="H116" s="20">
         <f>IF(A116="","",Inputs!$B$3/((IF(G116="",Inputs!$B$14,G116)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I116" s="8">
+      <c r="I116" s="20">
         <f>IF(A116="","",2.78E-7*F116*D116*H116)</f>
         <v/>
       </c>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="5" t="n"/>
-      <c r="M116" s="9">
+      <c r="M116" s="20">
         <f>IF(A116="","",IF(OR(J116="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J116,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N116" s="9">
+      <c r="N116" s="20">
         <f>IF(A116="","",IF(L116="",Inputs!$B$14,L116)+M116)</f>
         <v/>
       </c>
@@ -7266,30 +7305,30 @@
       <c r="C117" s="4" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
-      <c r="F117" s="8">
+      <c r="F117" s="20">
         <f>IF(E117&lt;&gt;"",E117,IF(UPPER(TRIM(C117))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C117))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C117))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C117))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C117))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G117" s="8">
+      <c r="G117" s="20">
         <f>IF(A117="","",N117)</f>
         <v/>
       </c>
-      <c r="H117" s="8">
+      <c r="H117" s="20">
         <f>IF(A117="","",Inputs!$B$3/((IF(G117="",Inputs!$B$14,G117)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I117" s="8">
+      <c r="I117" s="20">
         <f>IF(A117="","",2.78E-7*F117*D117*H117)</f>
         <v/>
       </c>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="5" t="n"/>
-      <c r="M117" s="9">
+      <c r="M117" s="20">
         <f>IF(A117="","",IF(OR(J117="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J117,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N117" s="9">
+      <c r="N117" s="20">
         <f>IF(A117="","",IF(L117="",Inputs!$B$14,L117)+M117)</f>
         <v/>
       </c>
@@ -7300,30 +7339,30 @@
       <c r="C118" s="4" t="n"/>
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
-      <c r="F118" s="8">
+      <c r="F118" s="20">
         <f>IF(E118&lt;&gt;"",E118,IF(UPPER(TRIM(C118))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C118))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C118))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C118))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C118))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G118" s="8">
+      <c r="G118" s="20">
         <f>IF(A118="","",N118)</f>
         <v/>
       </c>
-      <c r="H118" s="8">
+      <c r="H118" s="20">
         <f>IF(A118="","",Inputs!$B$3/((IF(G118="",Inputs!$B$14,G118)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I118" s="8">
+      <c r="I118" s="20">
         <f>IF(A118="","",2.78E-7*F118*D118*H118)</f>
         <v/>
       </c>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="5" t="n"/>
-      <c r="M118" s="9">
+      <c r="M118" s="20">
         <f>IF(A118="","",IF(OR(J118="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J118,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N118" s="9">
+      <c r="N118" s="20">
         <f>IF(A118="","",IF(L118="",Inputs!$B$14,L118)+M118)</f>
         <v/>
       </c>
@@ -7334,30 +7373,30 @@
       <c r="C119" s="4" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
-      <c r="F119" s="8">
+      <c r="F119" s="20">
         <f>IF(E119&lt;&gt;"",E119,IF(UPPER(TRIM(C119))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C119))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C119))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C119))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C119))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G119" s="8">
+      <c r="G119" s="20">
         <f>IF(A119="","",N119)</f>
         <v/>
       </c>
-      <c r="H119" s="8">
+      <c r="H119" s="20">
         <f>IF(A119="","",Inputs!$B$3/((IF(G119="",Inputs!$B$14,G119)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I119" s="8">
+      <c r="I119" s="20">
         <f>IF(A119="","",2.78E-7*F119*D119*H119)</f>
         <v/>
       </c>
       <c r="J119" s="4" t="n"/>
       <c r="K119" s="4" t="n"/>
       <c r="L119" s="5" t="n"/>
-      <c r="M119" s="9">
+      <c r="M119" s="20">
         <f>IF(A119="","",IF(OR(J119="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J119,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N119" s="9">
+      <c r="N119" s="20">
         <f>IF(A119="","",IF(L119="",Inputs!$B$14,L119)+M119)</f>
         <v/>
       </c>
@@ -7368,30 +7407,30 @@
       <c r="C120" s="4" t="n"/>
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
-      <c r="F120" s="8">
+      <c r="F120" s="20">
         <f>IF(E120&lt;&gt;"",E120,IF(UPPER(TRIM(C120))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C120))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C120))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C120))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C120))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G120" s="8">
+      <c r="G120" s="20">
         <f>IF(A120="","",N120)</f>
         <v/>
       </c>
-      <c r="H120" s="8">
+      <c r="H120" s="20">
         <f>IF(A120="","",Inputs!$B$3/((IF(G120="",Inputs!$B$14,G120)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I120" s="8">
+      <c r="I120" s="20">
         <f>IF(A120="","",2.78E-7*F120*D120*H120)</f>
         <v/>
       </c>
       <c r="J120" s="4" t="n"/>
       <c r="K120" s="4" t="n"/>
       <c r="L120" s="5" t="n"/>
-      <c r="M120" s="9">
+      <c r="M120" s="20">
         <f>IF(A120="","",IF(OR(J120="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J120,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N120" s="9">
+      <c r="N120" s="20">
         <f>IF(A120="","",IF(L120="",Inputs!$B$14,L120)+M120)</f>
         <v/>
       </c>
@@ -7402,30 +7441,30 @@
       <c r="C121" s="4" t="n"/>
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
-      <c r="F121" s="8">
+      <c r="F121" s="20">
         <f>IF(E121&lt;&gt;"",E121,IF(UPPER(TRIM(C121))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C121))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C121))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C121))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C121))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G121" s="8">
+      <c r="G121" s="20">
         <f>IF(A121="","",N121)</f>
         <v/>
       </c>
-      <c r="H121" s="8">
+      <c r="H121" s="20">
         <f>IF(A121="","",Inputs!$B$3/((IF(G121="",Inputs!$B$14,G121)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I121" s="8">
+      <c r="I121" s="20">
         <f>IF(A121="","",2.78E-7*F121*D121*H121)</f>
         <v/>
       </c>
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="5" t="n"/>
-      <c r="M121" s="9">
+      <c r="M121" s="20">
         <f>IF(A121="","",IF(OR(J121="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J121,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N121" s="9">
+      <c r="N121" s="20">
         <f>IF(A121="","",IF(L121="",Inputs!$B$14,L121)+M121)</f>
         <v/>
       </c>
@@ -7436,30 +7475,30 @@
       <c r="C122" s="4" t="n"/>
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
-      <c r="F122" s="8">
+      <c r="F122" s="20">
         <f>IF(E122&lt;&gt;"",E122,IF(UPPER(TRIM(C122))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C122))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C122))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C122))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C122))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G122" s="8">
+      <c r="G122" s="20">
         <f>IF(A122="","",N122)</f>
         <v/>
       </c>
-      <c r="H122" s="8">
+      <c r="H122" s="20">
         <f>IF(A122="","",Inputs!$B$3/((IF(G122="",Inputs!$B$14,G122)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I122" s="8">
+      <c r="I122" s="20">
         <f>IF(A122="","",2.78E-7*F122*D122*H122)</f>
         <v/>
       </c>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="5" t="n"/>
-      <c r="M122" s="9">
+      <c r="M122" s="20">
         <f>IF(A122="","",IF(OR(J122="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J122,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N122" s="9">
+      <c r="N122" s="20">
         <f>IF(A122="","",IF(L122="",Inputs!$B$14,L122)+M122)</f>
         <v/>
       </c>
@@ -7470,30 +7509,30 @@
       <c r="C123" s="4" t="n"/>
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
-      <c r="F123" s="8">
+      <c r="F123" s="20">
         <f>IF(E123&lt;&gt;"",E123,IF(UPPER(TRIM(C123))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C123))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C123))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C123))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C123))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="20">
         <f>IF(A123="","",N123)</f>
         <v/>
       </c>
-      <c r="H123" s="8">
+      <c r="H123" s="20">
         <f>IF(A123="","",Inputs!$B$3/((IF(G123="",Inputs!$B$14,G123)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I123" s="8">
+      <c r="I123" s="20">
         <f>IF(A123="","",2.78E-7*F123*D123*H123)</f>
         <v/>
       </c>
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="5" t="n"/>
-      <c r="M123" s="9">
+      <c r="M123" s="20">
         <f>IF(A123="","",IF(OR(J123="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J123,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N123" s="9">
+      <c r="N123" s="20">
         <f>IF(A123="","",IF(L123="",Inputs!$B$14,L123)+M123)</f>
         <v/>
       </c>
@@ -7504,30 +7543,30 @@
       <c r="C124" s="4" t="n"/>
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
-      <c r="F124" s="8">
+      <c r="F124" s="20">
         <f>IF(E124&lt;&gt;"",E124,IF(UPPER(TRIM(C124))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C124))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C124))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C124))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C124))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G124" s="8">
+      <c r="G124" s="20">
         <f>IF(A124="","",N124)</f>
         <v/>
       </c>
-      <c r="H124" s="8">
+      <c r="H124" s="20">
         <f>IF(A124="","",Inputs!$B$3/((IF(G124="",Inputs!$B$14,G124)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I124" s="8">
+      <c r="I124" s="20">
         <f>IF(A124="","",2.78E-7*F124*D124*H124)</f>
         <v/>
       </c>
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="5" t="n"/>
-      <c r="M124" s="9">
+      <c r="M124" s="20">
         <f>IF(A124="","",IF(OR(J124="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J124,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N124" s="9">
+      <c r="N124" s="20">
         <f>IF(A124="","",IF(L124="",Inputs!$B$14,L124)+M124)</f>
         <v/>
       </c>
@@ -7538,30 +7577,30 @@
       <c r="C125" s="4" t="n"/>
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
-      <c r="F125" s="8">
+      <c r="F125" s="20">
         <f>IF(E125&lt;&gt;"",E125,IF(UPPER(TRIM(C125))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C125))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C125))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C125))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C125))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G125" s="8">
+      <c r="G125" s="20">
         <f>IF(A125="","",N125)</f>
         <v/>
       </c>
-      <c r="H125" s="8">
+      <c r="H125" s="20">
         <f>IF(A125="","",Inputs!$B$3/((IF(G125="",Inputs!$B$14,G125)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I125" s="8">
+      <c r="I125" s="20">
         <f>IF(A125="","",2.78E-7*F125*D125*H125)</f>
         <v/>
       </c>
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="5" t="n"/>
-      <c r="M125" s="9">
+      <c r="M125" s="20">
         <f>IF(A125="","",IF(OR(J125="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J125,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N125" s="9">
+      <c r="N125" s="20">
         <f>IF(A125="","",IF(L125="",Inputs!$B$14,L125)+M125)</f>
         <v/>
       </c>
@@ -7572,30 +7611,30 @@
       <c r="C126" s="4" t="n"/>
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
-      <c r="F126" s="8">
+      <c r="F126" s="20">
         <f>IF(E126&lt;&gt;"",E126,IF(UPPER(TRIM(C126))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C126))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C126))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C126))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C126))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G126" s="8">
+      <c r="G126" s="20">
         <f>IF(A126="","",N126)</f>
         <v/>
       </c>
-      <c r="H126" s="8">
+      <c r="H126" s="20">
         <f>IF(A126="","",Inputs!$B$3/((IF(G126="",Inputs!$B$14,G126)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I126" s="8">
+      <c r="I126" s="20">
         <f>IF(A126="","",2.78E-7*F126*D126*H126)</f>
         <v/>
       </c>
       <c r="J126" s="4" t="n"/>
       <c r="K126" s="4" t="n"/>
       <c r="L126" s="5" t="n"/>
-      <c r="M126" s="9">
+      <c r="M126" s="20">
         <f>IF(A126="","",IF(OR(J126="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J126,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N126" s="9">
+      <c r="N126" s="20">
         <f>IF(A126="","",IF(L126="",Inputs!$B$14,L126)+M126)</f>
         <v/>
       </c>
@@ -7606,30 +7645,30 @@
       <c r="C127" s="4" t="n"/>
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
-      <c r="F127" s="8">
+      <c r="F127" s="20">
         <f>IF(E127&lt;&gt;"",E127,IF(UPPER(TRIM(C127))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C127))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C127))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C127))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C127))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G127" s="8">
+      <c r="G127" s="20">
         <f>IF(A127="","",N127)</f>
         <v/>
       </c>
-      <c r="H127" s="8">
+      <c r="H127" s="20">
         <f>IF(A127="","",Inputs!$B$3/((IF(G127="",Inputs!$B$14,G127)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I127" s="8">
+      <c r="I127" s="20">
         <f>IF(A127="","",2.78E-7*F127*D127*H127)</f>
         <v/>
       </c>
       <c r="J127" s="4" t="n"/>
       <c r="K127" s="4" t="n"/>
       <c r="L127" s="5" t="n"/>
-      <c r="M127" s="9">
+      <c r="M127" s="20">
         <f>IF(A127="","",IF(OR(J127="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J127,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N127" s="9">
+      <c r="N127" s="20">
         <f>IF(A127="","",IF(L127="",Inputs!$B$14,L127)+M127)</f>
         <v/>
       </c>
@@ -7640,30 +7679,30 @@
       <c r="C128" s="4" t="n"/>
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
-      <c r="F128" s="8">
+      <c r="F128" s="20">
         <f>IF(E128&lt;&gt;"",E128,IF(UPPER(TRIM(C128))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C128))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C128))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C128))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C128))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G128" s="8">
+      <c r="G128" s="20">
         <f>IF(A128="","",N128)</f>
         <v/>
       </c>
-      <c r="H128" s="8">
+      <c r="H128" s="20">
         <f>IF(A128="","",Inputs!$B$3/((IF(G128="",Inputs!$B$14,G128)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I128" s="8">
+      <c r="I128" s="20">
         <f>IF(A128="","",2.78E-7*F128*D128*H128)</f>
         <v/>
       </c>
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="5" t="n"/>
-      <c r="M128" s="9">
+      <c r="M128" s="20">
         <f>IF(A128="","",IF(OR(J128="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J128,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N128" s="9">
+      <c r="N128" s="20">
         <f>IF(A128="","",IF(L128="",Inputs!$B$14,L128)+M128)</f>
         <v/>
       </c>
@@ -7674,30 +7713,30 @@
       <c r="C129" s="4" t="n"/>
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
-      <c r="F129" s="8">
+      <c r="F129" s="20">
         <f>IF(E129&lt;&gt;"",E129,IF(UPPER(TRIM(C129))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C129))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C129))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C129))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C129))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G129" s="8">
+      <c r="G129" s="20">
         <f>IF(A129="","",N129)</f>
         <v/>
       </c>
-      <c r="H129" s="8">
+      <c r="H129" s="20">
         <f>IF(A129="","",Inputs!$B$3/((IF(G129="",Inputs!$B$14,G129)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I129" s="8">
+      <c r="I129" s="20">
         <f>IF(A129="","",2.78E-7*F129*D129*H129)</f>
         <v/>
       </c>
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="5" t="n"/>
-      <c r="M129" s="9">
+      <c r="M129" s="20">
         <f>IF(A129="","",IF(OR(J129="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J129,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N129" s="9">
+      <c r="N129" s="20">
         <f>IF(A129="","",IF(L129="",Inputs!$B$14,L129)+M129)</f>
         <v/>
       </c>
@@ -7708,30 +7747,30 @@
       <c r="C130" s="4" t="n"/>
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
-      <c r="F130" s="8">
+      <c r="F130" s="20">
         <f>IF(E130&lt;&gt;"",E130,IF(UPPER(TRIM(C130))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C130))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C130))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C130))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C130))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G130" s="8">
+      <c r="G130" s="20">
         <f>IF(A130="","",N130)</f>
         <v/>
       </c>
-      <c r="H130" s="8">
+      <c r="H130" s="20">
         <f>IF(A130="","",Inputs!$B$3/((IF(G130="",Inputs!$B$14,G130)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I130" s="8">
+      <c r="I130" s="20">
         <f>IF(A130="","",2.78E-7*F130*D130*H130)</f>
         <v/>
       </c>
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="5" t="n"/>
-      <c r="M130" s="9">
+      <c r="M130" s="20">
         <f>IF(A130="","",IF(OR(J130="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J130,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N130" s="9">
+      <c r="N130" s="20">
         <f>IF(A130="","",IF(L130="",Inputs!$B$14,L130)+M130)</f>
         <v/>
       </c>
@@ -7742,30 +7781,30 @@
       <c r="C131" s="4" t="n"/>
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
-      <c r="F131" s="8">
+      <c r="F131" s="20">
         <f>IF(E131&lt;&gt;"",E131,IF(UPPER(TRIM(C131))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C131))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C131))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C131))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C131))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G131" s="8">
+      <c r="G131" s="20">
         <f>IF(A131="","",N131)</f>
         <v/>
       </c>
-      <c r="H131" s="8">
+      <c r="H131" s="20">
         <f>IF(A131="","",Inputs!$B$3/((IF(G131="",Inputs!$B$14,G131)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I131" s="8">
+      <c r="I131" s="20">
         <f>IF(A131="","",2.78E-7*F131*D131*H131)</f>
         <v/>
       </c>
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="5" t="n"/>
-      <c r="M131" s="9">
+      <c r="M131" s="20">
         <f>IF(A131="","",IF(OR(J131="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J131,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N131" s="9">
+      <c r="N131" s="20">
         <f>IF(A131="","",IF(L131="",Inputs!$B$14,L131)+M131)</f>
         <v/>
       </c>
@@ -7776,30 +7815,30 @@
       <c r="C132" s="4" t="n"/>
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
-      <c r="F132" s="8">
+      <c r="F132" s="20">
         <f>IF(E132&lt;&gt;"",E132,IF(UPPER(TRIM(C132))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C132))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C132))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C132))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C132))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G132" s="8">
+      <c r="G132" s="20">
         <f>IF(A132="","",N132)</f>
         <v/>
       </c>
-      <c r="H132" s="8">
+      <c r="H132" s="20">
         <f>IF(A132="","",Inputs!$B$3/((IF(G132="",Inputs!$B$14,G132)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I132" s="8">
+      <c r="I132" s="20">
         <f>IF(A132="","",2.78E-7*F132*D132*H132)</f>
         <v/>
       </c>
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="5" t="n"/>
-      <c r="M132" s="9">
+      <c r="M132" s="20">
         <f>IF(A132="","",IF(OR(J132="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J132,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N132" s="9">
+      <c r="N132" s="20">
         <f>IF(A132="","",IF(L132="",Inputs!$B$14,L132)+M132)</f>
         <v/>
       </c>
@@ -7810,30 +7849,30 @@
       <c r="C133" s="4" t="n"/>
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
-      <c r="F133" s="8">
+      <c r="F133" s="20">
         <f>IF(E133&lt;&gt;"",E133,IF(UPPER(TRIM(C133))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C133))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C133))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C133))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C133))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G133" s="8">
+      <c r="G133" s="20">
         <f>IF(A133="","",N133)</f>
         <v/>
       </c>
-      <c r="H133" s="8">
+      <c r="H133" s="20">
         <f>IF(A133="","",Inputs!$B$3/((IF(G133="",Inputs!$B$14,G133)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I133" s="8">
+      <c r="I133" s="20">
         <f>IF(A133="","",2.78E-7*F133*D133*H133)</f>
         <v/>
       </c>
       <c r="J133" s="4" t="n"/>
       <c r="K133" s="4" t="n"/>
       <c r="L133" s="5" t="n"/>
-      <c r="M133" s="9">
+      <c r="M133" s="20">
         <f>IF(A133="","",IF(OR(J133="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J133,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N133" s="9">
+      <c r="N133" s="20">
         <f>IF(A133="","",IF(L133="",Inputs!$B$14,L133)+M133)</f>
         <v/>
       </c>
@@ -7844,30 +7883,30 @@
       <c r="C134" s="4" t="n"/>
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
-      <c r="F134" s="8">
+      <c r="F134" s="20">
         <f>IF(E134&lt;&gt;"",E134,IF(UPPER(TRIM(C134))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C134))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C134))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C134))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C134))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G134" s="8">
+      <c r="G134" s="20">
         <f>IF(A134="","",N134)</f>
         <v/>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="20">
         <f>IF(A134="","",Inputs!$B$3/((IF(G134="",Inputs!$B$14,G134)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I134" s="8">
+      <c r="I134" s="20">
         <f>IF(A134="","",2.78E-7*F134*D134*H134)</f>
         <v/>
       </c>
       <c r="J134" s="4" t="n"/>
       <c r="K134" s="4" t="n"/>
       <c r="L134" s="5" t="n"/>
-      <c r="M134" s="9">
+      <c r="M134" s="20">
         <f>IF(A134="","",IF(OR(J134="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J134,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N134" s="9">
+      <c r="N134" s="20">
         <f>IF(A134="","",IF(L134="",Inputs!$B$14,L134)+M134)</f>
         <v/>
       </c>
@@ -7878,30 +7917,30 @@
       <c r="C135" s="4" t="n"/>
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
-      <c r="F135" s="8">
+      <c r="F135" s="20">
         <f>IF(E135&lt;&gt;"",E135,IF(UPPER(TRIM(C135))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C135))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C135))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C135))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C135))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G135" s="8">
+      <c r="G135" s="20">
         <f>IF(A135="","",N135)</f>
         <v/>
       </c>
-      <c r="H135" s="8">
+      <c r="H135" s="20">
         <f>IF(A135="","",Inputs!$B$3/((IF(G135="",Inputs!$B$14,G135)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I135" s="8">
+      <c r="I135" s="20">
         <f>IF(A135="","",2.78E-7*F135*D135*H135)</f>
         <v/>
       </c>
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="5" t="n"/>
-      <c r="M135" s="9">
+      <c r="M135" s="20">
         <f>IF(A135="","",IF(OR(J135="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J135,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N135" s="9">
+      <c r="N135" s="20">
         <f>IF(A135="","",IF(L135="",Inputs!$B$14,L135)+M135)</f>
         <v/>
       </c>
@@ -7912,30 +7951,30 @@
       <c r="C136" s="4" t="n"/>
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
-      <c r="F136" s="8">
+      <c r="F136" s="20">
         <f>IF(E136&lt;&gt;"",E136,IF(UPPER(TRIM(C136))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C136))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C136))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C136))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C136))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G136" s="8">
+      <c r="G136" s="20">
         <f>IF(A136="","",N136)</f>
         <v/>
       </c>
-      <c r="H136" s="8">
+      <c r="H136" s="20">
         <f>IF(A136="","",Inputs!$B$3/((IF(G136="",Inputs!$B$14,G136)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I136" s="8">
+      <c r="I136" s="20">
         <f>IF(A136="","",2.78E-7*F136*D136*H136)</f>
         <v/>
       </c>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="5" t="n"/>
-      <c r="M136" s="9">
+      <c r="M136" s="20">
         <f>IF(A136="","",IF(OR(J136="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J136,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N136" s="9">
+      <c r="N136" s="20">
         <f>IF(A136="","",IF(L136="",Inputs!$B$14,L136)+M136)</f>
         <v/>
       </c>
@@ -7946,30 +7985,30 @@
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
-      <c r="F137" s="8">
+      <c r="F137" s="20">
         <f>IF(E137&lt;&gt;"",E137,IF(UPPER(TRIM(C137))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C137))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C137))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C137))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C137))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G137" s="8">
+      <c r="G137" s="20">
         <f>IF(A137="","",N137)</f>
         <v/>
       </c>
-      <c r="H137" s="8">
+      <c r="H137" s="20">
         <f>IF(A137="","",Inputs!$B$3/((IF(G137="",Inputs!$B$14,G137)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I137" s="8">
+      <c r="I137" s="20">
         <f>IF(A137="","",2.78E-7*F137*D137*H137)</f>
         <v/>
       </c>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="5" t="n"/>
-      <c r="M137" s="9">
+      <c r="M137" s="20">
         <f>IF(A137="","",IF(OR(J137="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J137,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N137" s="9">
+      <c r="N137" s="20">
         <f>IF(A137="","",IF(L137="",Inputs!$B$14,L137)+M137)</f>
         <v/>
       </c>
@@ -7980,30 +8019,30 @@
       <c r="C138" s="4" t="n"/>
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
-      <c r="F138" s="8">
+      <c r="F138" s="20">
         <f>IF(E138&lt;&gt;"",E138,IF(UPPER(TRIM(C138))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C138))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C138))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C138))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C138))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G138" s="8">
+      <c r="G138" s="20">
         <f>IF(A138="","",N138)</f>
         <v/>
       </c>
-      <c r="H138" s="8">
+      <c r="H138" s="20">
         <f>IF(A138="","",Inputs!$B$3/((IF(G138="",Inputs!$B$14,G138)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I138" s="8">
+      <c r="I138" s="20">
         <f>IF(A138="","",2.78E-7*F138*D138*H138)</f>
         <v/>
       </c>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="5" t="n"/>
-      <c r="M138" s="9">
+      <c r="M138" s="20">
         <f>IF(A138="","",IF(OR(J138="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J138,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N138" s="9">
+      <c r="N138" s="20">
         <f>IF(A138="","",IF(L138="",Inputs!$B$14,L138)+M138)</f>
         <v/>
       </c>
@@ -8014,30 +8053,30 @@
       <c r="C139" s="4" t="n"/>
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
-      <c r="F139" s="8">
+      <c r="F139" s="20">
         <f>IF(E139&lt;&gt;"",E139,IF(UPPER(TRIM(C139))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C139))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C139))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C139))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C139))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G139" s="8">
+      <c r="G139" s="20">
         <f>IF(A139="","",N139)</f>
         <v/>
       </c>
-      <c r="H139" s="8">
+      <c r="H139" s="20">
         <f>IF(A139="","",Inputs!$B$3/((IF(G139="",Inputs!$B$14,G139)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I139" s="8">
+      <c r="I139" s="20">
         <f>IF(A139="","",2.78E-7*F139*D139*H139)</f>
         <v/>
       </c>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="5" t="n"/>
-      <c r="M139" s="9">
+      <c r="M139" s="20">
         <f>IF(A139="","",IF(OR(J139="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J139,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N139" s="9">
+      <c r="N139" s="20">
         <f>IF(A139="","",IF(L139="",Inputs!$B$14,L139)+M139)</f>
         <v/>
       </c>
@@ -8048,30 +8087,30 @@
       <c r="C140" s="4" t="n"/>
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
-      <c r="F140" s="8">
+      <c r="F140" s="20">
         <f>IF(E140&lt;&gt;"",E140,IF(UPPER(TRIM(C140))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C140))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C140))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C140))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C140))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G140" s="8">
+      <c r="G140" s="20">
         <f>IF(A140="","",N140)</f>
         <v/>
       </c>
-      <c r="H140" s="8">
+      <c r="H140" s="20">
         <f>IF(A140="","",Inputs!$B$3/((IF(G140="",Inputs!$B$14,G140)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I140" s="8">
+      <c r="I140" s="20">
         <f>IF(A140="","",2.78E-7*F140*D140*H140)</f>
         <v/>
       </c>
       <c r="J140" s="4" t="n"/>
       <c r="K140" s="4" t="n"/>
       <c r="L140" s="5" t="n"/>
-      <c r="M140" s="9">
+      <c r="M140" s="20">
         <f>IF(A140="","",IF(OR(J140="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J140,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N140" s="9">
+      <c r="N140" s="20">
         <f>IF(A140="","",IF(L140="",Inputs!$B$14,L140)+M140)</f>
         <v/>
       </c>
@@ -8082,30 +8121,30 @@
       <c r="C141" s="4" t="n"/>
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
-      <c r="F141" s="8">
+      <c r="F141" s="20">
         <f>IF(E141&lt;&gt;"",E141,IF(UPPER(TRIM(C141))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C141))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C141))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C141))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C141))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G141" s="8">
+      <c r="G141" s="20">
         <f>IF(A141="","",N141)</f>
         <v/>
       </c>
-      <c r="H141" s="8">
+      <c r="H141" s="20">
         <f>IF(A141="","",Inputs!$B$3/((IF(G141="",Inputs!$B$14,G141)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I141" s="8">
+      <c r="I141" s="20">
         <f>IF(A141="","",2.78E-7*F141*D141*H141)</f>
         <v/>
       </c>
       <c r="J141" s="4" t="n"/>
       <c r="K141" s="4" t="n"/>
       <c r="L141" s="5" t="n"/>
-      <c r="M141" s="9">
+      <c r="M141" s="20">
         <f>IF(A141="","",IF(OR(J141="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J141,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N141" s="9">
+      <c r="N141" s="20">
         <f>IF(A141="","",IF(L141="",Inputs!$B$14,L141)+M141)</f>
         <v/>
       </c>
@@ -8116,30 +8155,30 @@
       <c r="C142" s="4" t="n"/>
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
-      <c r="F142" s="8">
+      <c r="F142" s="20">
         <f>IF(E142&lt;&gt;"",E142,IF(UPPER(TRIM(C142))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C142))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C142))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C142))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C142))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G142" s="8">
+      <c r="G142" s="20">
         <f>IF(A142="","",N142)</f>
         <v/>
       </c>
-      <c r="H142" s="8">
+      <c r="H142" s="20">
         <f>IF(A142="","",Inputs!$B$3/((IF(G142="",Inputs!$B$14,G142)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I142" s="8">
+      <c r="I142" s="20">
         <f>IF(A142="","",2.78E-7*F142*D142*H142)</f>
         <v/>
       </c>
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="5" t="n"/>
-      <c r="M142" s="9">
+      <c r="M142" s="20">
         <f>IF(A142="","",IF(OR(J142="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J142,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N142" s="9">
+      <c r="N142" s="20">
         <f>IF(A142="","",IF(L142="",Inputs!$B$14,L142)+M142)</f>
         <v/>
       </c>
@@ -8150,30 +8189,30 @@
       <c r="C143" s="4" t="n"/>
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
-      <c r="F143" s="8">
+      <c r="F143" s="20">
         <f>IF(E143&lt;&gt;"",E143,IF(UPPER(TRIM(C143))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C143))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C143))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C143))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C143))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G143" s="8">
+      <c r="G143" s="20">
         <f>IF(A143="","",N143)</f>
         <v/>
       </c>
-      <c r="H143" s="8">
+      <c r="H143" s="20">
         <f>IF(A143="","",Inputs!$B$3/((IF(G143="",Inputs!$B$14,G143)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I143" s="8">
+      <c r="I143" s="20">
         <f>IF(A143="","",2.78E-7*F143*D143*H143)</f>
         <v/>
       </c>
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="5" t="n"/>
-      <c r="M143" s="9">
+      <c r="M143" s="20">
         <f>IF(A143="","",IF(OR(J143="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J143,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N143" s="9">
+      <c r="N143" s="20">
         <f>IF(A143="","",IF(L143="",Inputs!$B$14,L143)+M143)</f>
         <v/>
       </c>
@@ -8184,30 +8223,30 @@
       <c r="C144" s="4" t="n"/>
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
-      <c r="F144" s="8">
+      <c r="F144" s="20">
         <f>IF(E144&lt;&gt;"",E144,IF(UPPER(TRIM(C144))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C144))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C144))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C144))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C144))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G144" s="8">
+      <c r="G144" s="20">
         <f>IF(A144="","",N144)</f>
         <v/>
       </c>
-      <c r="H144" s="8">
+      <c r="H144" s="20">
         <f>IF(A144="","",Inputs!$B$3/((IF(G144="",Inputs!$B$14,G144)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I144" s="8">
+      <c r="I144" s="20">
         <f>IF(A144="","",2.78E-7*F144*D144*H144)</f>
         <v/>
       </c>
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="5" t="n"/>
-      <c r="M144" s="9">
+      <c r="M144" s="20">
         <f>IF(A144="","",IF(OR(J144="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J144,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N144" s="9">
+      <c r="N144" s="20">
         <f>IF(A144="","",IF(L144="",Inputs!$B$14,L144)+M144)</f>
         <v/>
       </c>
@@ -8218,30 +8257,30 @@
       <c r="C145" s="4" t="n"/>
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
-      <c r="F145" s="8">
+      <c r="F145" s="20">
         <f>IF(E145&lt;&gt;"",E145,IF(UPPER(TRIM(C145))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C145))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C145))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C145))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C145))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G145" s="8">
+      <c r="G145" s="20">
         <f>IF(A145="","",N145)</f>
         <v/>
       </c>
-      <c r="H145" s="8">
+      <c r="H145" s="20">
         <f>IF(A145="","",Inputs!$B$3/((IF(G145="",Inputs!$B$14,G145)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I145" s="8">
+      <c r="I145" s="20">
         <f>IF(A145="","",2.78E-7*F145*D145*H145)</f>
         <v/>
       </c>
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="5" t="n"/>
-      <c r="M145" s="9">
+      <c r="M145" s="20">
         <f>IF(A145="","",IF(OR(J145="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J145,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N145" s="9">
+      <c r="N145" s="20">
         <f>IF(A145="","",IF(L145="",Inputs!$B$14,L145)+M145)</f>
         <v/>
       </c>
@@ -8252,30 +8291,30 @@
       <c r="C146" s="4" t="n"/>
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
-      <c r="F146" s="8">
+      <c r="F146" s="20">
         <f>IF(E146&lt;&gt;"",E146,IF(UPPER(TRIM(C146))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C146))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C146))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C146))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C146))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G146" s="8">
+      <c r="G146" s="20">
         <f>IF(A146="","",N146)</f>
         <v/>
       </c>
-      <c r="H146" s="8">
+      <c r="H146" s="20">
         <f>IF(A146="","",Inputs!$B$3/((IF(G146="",Inputs!$B$14,G146)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I146" s="8">
+      <c r="I146" s="20">
         <f>IF(A146="","",2.78E-7*F146*D146*H146)</f>
         <v/>
       </c>
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="5" t="n"/>
-      <c r="M146" s="9">
+      <c r="M146" s="20">
         <f>IF(A146="","",IF(OR(J146="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J146,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N146" s="9">
+      <c r="N146" s="20">
         <f>IF(A146="","",IF(L146="",Inputs!$B$14,L146)+M146)</f>
         <v/>
       </c>
@@ -8286,30 +8325,30 @@
       <c r="C147" s="4" t="n"/>
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
-      <c r="F147" s="8">
+      <c r="F147" s="20">
         <f>IF(E147&lt;&gt;"",E147,IF(UPPER(TRIM(C147))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C147))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C147))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C147))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C147))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G147" s="8">
+      <c r="G147" s="20">
         <f>IF(A147="","",N147)</f>
         <v/>
       </c>
-      <c r="H147" s="8">
+      <c r="H147" s="20">
         <f>IF(A147="","",Inputs!$B$3/((IF(G147="",Inputs!$B$14,G147)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I147" s="8">
+      <c r="I147" s="20">
         <f>IF(A147="","",2.78E-7*F147*D147*H147)</f>
         <v/>
       </c>
       <c r="J147" s="4" t="n"/>
       <c r="K147" s="4" t="n"/>
       <c r="L147" s="5" t="n"/>
-      <c r="M147" s="9">
+      <c r="M147" s="20">
         <f>IF(A147="","",IF(OR(J147="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J147,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N147" s="9">
+      <c r="N147" s="20">
         <f>IF(A147="","",IF(L147="",Inputs!$B$14,L147)+M147)</f>
         <v/>
       </c>
@@ -8320,30 +8359,30 @@
       <c r="C148" s="4" t="n"/>
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
-      <c r="F148" s="8">
+      <c r="F148" s="20">
         <f>IF(E148&lt;&gt;"",E148,IF(UPPER(TRIM(C148))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C148))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C148))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C148))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C148))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G148" s="8">
+      <c r="G148" s="20">
         <f>IF(A148="","",N148)</f>
         <v/>
       </c>
-      <c r="H148" s="8">
+      <c r="H148" s="20">
         <f>IF(A148="","",Inputs!$B$3/((IF(G148="",Inputs!$B$14,G148)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I148" s="8">
+      <c r="I148" s="20">
         <f>IF(A148="","",2.78E-7*F148*D148*H148)</f>
         <v/>
       </c>
       <c r="J148" s="4" t="n"/>
       <c r="K148" s="4" t="n"/>
       <c r="L148" s="5" t="n"/>
-      <c r="M148" s="9">
+      <c r="M148" s="20">
         <f>IF(A148="","",IF(OR(J148="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J148,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N148" s="9">
+      <c r="N148" s="20">
         <f>IF(A148="","",IF(L148="",Inputs!$B$14,L148)+M148)</f>
         <v/>
       </c>
@@ -8354,30 +8393,30 @@
       <c r="C149" s="4" t="n"/>
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
-      <c r="F149" s="8">
+      <c r="F149" s="20">
         <f>IF(E149&lt;&gt;"",E149,IF(UPPER(TRIM(C149))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C149))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C149))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C149))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C149))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G149" s="8">
+      <c r="G149" s="20">
         <f>IF(A149="","",N149)</f>
         <v/>
       </c>
-      <c r="H149" s="8">
+      <c r="H149" s="20">
         <f>IF(A149="","",Inputs!$B$3/((IF(G149="",Inputs!$B$14,G149)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I149" s="8">
+      <c r="I149" s="20">
         <f>IF(A149="","",2.78E-7*F149*D149*H149)</f>
         <v/>
       </c>
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="5" t="n"/>
-      <c r="M149" s="9">
+      <c r="M149" s="20">
         <f>IF(A149="","",IF(OR(J149="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J149,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N149" s="9">
+      <c r="N149" s="20">
         <f>IF(A149="","",IF(L149="",Inputs!$B$14,L149)+M149)</f>
         <v/>
       </c>
@@ -8388,30 +8427,30 @@
       <c r="C150" s="4" t="n"/>
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
-      <c r="F150" s="8">
+      <c r="F150" s="20">
         <f>IF(E150&lt;&gt;"",E150,IF(UPPER(TRIM(C150))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C150))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C150))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C150))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C150))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G150" s="8">
+      <c r="G150" s="20">
         <f>IF(A150="","",N150)</f>
         <v/>
       </c>
-      <c r="H150" s="8">
+      <c r="H150" s="20">
         <f>IF(A150="","",Inputs!$B$3/((IF(G150="",Inputs!$B$14,G150)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I150" s="8">
+      <c r="I150" s="20">
         <f>IF(A150="","",2.78E-7*F150*D150*H150)</f>
         <v/>
       </c>
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="5" t="n"/>
-      <c r="M150" s="9">
+      <c r="M150" s="20">
         <f>IF(A150="","",IF(OR(J150="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J150,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N150" s="9">
+      <c r="N150" s="20">
         <f>IF(A150="","",IF(L150="",Inputs!$B$14,L150)+M150)</f>
         <v/>
       </c>
@@ -8422,30 +8461,30 @@
       <c r="C151" s="4" t="n"/>
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
-      <c r="F151" s="8">
+      <c r="F151" s="20">
         <f>IF(E151&lt;&gt;"",E151,IF(UPPER(TRIM(C151))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C151))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C151))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C151))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C151))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G151" s="8">
+      <c r="G151" s="20">
         <f>IF(A151="","",N151)</f>
         <v/>
       </c>
-      <c r="H151" s="8">
+      <c r="H151" s="20">
         <f>IF(A151="","",Inputs!$B$3/((IF(G151="",Inputs!$B$14,G151)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I151" s="8">
+      <c r="I151" s="20">
         <f>IF(A151="","",2.78E-7*F151*D151*H151)</f>
         <v/>
       </c>
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="5" t="n"/>
-      <c r="M151" s="9">
+      <c r="M151" s="20">
         <f>IF(A151="","",IF(OR(J151="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J151,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N151" s="9">
+      <c r="N151" s="20">
         <f>IF(A151="","",IF(L151="",Inputs!$B$14,L151)+M151)</f>
         <v/>
       </c>
@@ -8456,30 +8495,30 @@
       <c r="C152" s="4" t="n"/>
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
-      <c r="F152" s="8">
+      <c r="F152" s="20">
         <f>IF(E152&lt;&gt;"",E152,IF(UPPER(TRIM(C152))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C152))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C152))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C152))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C152))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G152" s="8">
+      <c r="G152" s="20">
         <f>IF(A152="","",N152)</f>
         <v/>
       </c>
-      <c r="H152" s="8">
+      <c r="H152" s="20">
         <f>IF(A152="","",Inputs!$B$3/((IF(G152="",Inputs!$B$14,G152)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I152" s="8">
+      <c r="I152" s="20">
         <f>IF(A152="","",2.78E-7*F152*D152*H152)</f>
         <v/>
       </c>
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="5" t="n"/>
-      <c r="M152" s="9">
+      <c r="M152" s="20">
         <f>IF(A152="","",IF(OR(J152="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J152,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N152" s="9">
+      <c r="N152" s="20">
         <f>IF(A152="","",IF(L152="",Inputs!$B$14,L152)+M152)</f>
         <v/>
       </c>
@@ -8490,30 +8529,30 @@
       <c r="C153" s="4" t="n"/>
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
-      <c r="F153" s="8">
+      <c r="F153" s="20">
         <f>IF(E153&lt;&gt;"",E153,IF(UPPER(TRIM(C153))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C153))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C153))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C153))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C153))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G153" s="8">
+      <c r="G153" s="20">
         <f>IF(A153="","",N153)</f>
         <v/>
       </c>
-      <c r="H153" s="8">
+      <c r="H153" s="20">
         <f>IF(A153="","",Inputs!$B$3/((IF(G153="",Inputs!$B$14,G153)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I153" s="8">
+      <c r="I153" s="20">
         <f>IF(A153="","",2.78E-7*F153*D153*H153)</f>
         <v/>
       </c>
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="5" t="n"/>
-      <c r="M153" s="9">
+      <c r="M153" s="20">
         <f>IF(A153="","",IF(OR(J153="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J153,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N153" s="9">
+      <c r="N153" s="20">
         <f>IF(A153="","",IF(L153="",Inputs!$B$14,L153)+M153)</f>
         <v/>
       </c>
@@ -8524,30 +8563,30 @@
       <c r="C154" s="4" t="n"/>
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
-      <c r="F154" s="8">
+      <c r="F154" s="20">
         <f>IF(E154&lt;&gt;"",E154,IF(UPPER(TRIM(C154))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C154))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C154))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C154))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C154))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G154" s="8">
+      <c r="G154" s="20">
         <f>IF(A154="","",N154)</f>
         <v/>
       </c>
-      <c r="H154" s="8">
+      <c r="H154" s="20">
         <f>IF(A154="","",Inputs!$B$3/((IF(G154="",Inputs!$B$14,G154)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I154" s="8">
+      <c r="I154" s="20">
         <f>IF(A154="","",2.78E-7*F154*D154*H154)</f>
         <v/>
       </c>
       <c r="J154" s="4" t="n"/>
       <c r="K154" s="4" t="n"/>
       <c r="L154" s="5" t="n"/>
-      <c r="M154" s="9">
+      <c r="M154" s="20">
         <f>IF(A154="","",IF(OR(J154="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J154,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N154" s="9">
+      <c r="N154" s="20">
         <f>IF(A154="","",IF(L154="",Inputs!$B$14,L154)+M154)</f>
         <v/>
       </c>
@@ -8558,30 +8597,30 @@
       <c r="C155" s="4" t="n"/>
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
-      <c r="F155" s="8">
+      <c r="F155" s="20">
         <f>IF(E155&lt;&gt;"",E155,IF(UPPER(TRIM(C155))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C155))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C155))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C155))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C155))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G155" s="8">
+      <c r="G155" s="20">
         <f>IF(A155="","",N155)</f>
         <v/>
       </c>
-      <c r="H155" s="8">
+      <c r="H155" s="20">
         <f>IF(A155="","",Inputs!$B$3/((IF(G155="",Inputs!$B$14,G155)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I155" s="8">
+      <c r="I155" s="20">
         <f>IF(A155="","",2.78E-7*F155*D155*H155)</f>
         <v/>
       </c>
       <c r="J155" s="4" t="n"/>
       <c r="K155" s="4" t="n"/>
       <c r="L155" s="5" t="n"/>
-      <c r="M155" s="9">
+      <c r="M155" s="20">
         <f>IF(A155="","",IF(OR(J155="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J155,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N155" s="9">
+      <c r="N155" s="20">
         <f>IF(A155="","",IF(L155="",Inputs!$B$14,L155)+M155)</f>
         <v/>
       </c>
@@ -8592,30 +8631,30 @@
       <c r="C156" s="4" t="n"/>
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
-      <c r="F156" s="8">
+      <c r="F156" s="20">
         <f>IF(E156&lt;&gt;"",E156,IF(UPPER(TRIM(C156))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C156))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C156))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C156))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C156))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G156" s="8">
+      <c r="G156" s="20">
         <f>IF(A156="","",N156)</f>
         <v/>
       </c>
-      <c r="H156" s="8">
+      <c r="H156" s="20">
         <f>IF(A156="","",Inputs!$B$3/((IF(G156="",Inputs!$B$14,G156)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I156" s="8">
+      <c r="I156" s="20">
         <f>IF(A156="","",2.78E-7*F156*D156*H156)</f>
         <v/>
       </c>
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="5" t="n"/>
-      <c r="M156" s="9">
+      <c r="M156" s="20">
         <f>IF(A156="","",IF(OR(J156="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J156,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N156" s="9">
+      <c r="N156" s="20">
         <f>IF(A156="","",IF(L156="",Inputs!$B$14,L156)+M156)</f>
         <v/>
       </c>
@@ -8626,30 +8665,30 @@
       <c r="C157" s="4" t="n"/>
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
-      <c r="F157" s="8">
+      <c r="F157" s="20">
         <f>IF(E157&lt;&gt;"",E157,IF(UPPER(TRIM(C157))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C157))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C157))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C157))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C157))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G157" s="8">
+      <c r="G157" s="20">
         <f>IF(A157="","",N157)</f>
         <v/>
       </c>
-      <c r="H157" s="8">
+      <c r="H157" s="20">
         <f>IF(A157="","",Inputs!$B$3/((IF(G157="",Inputs!$B$14,G157)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I157" s="8">
+      <c r="I157" s="20">
         <f>IF(A157="","",2.78E-7*F157*D157*H157)</f>
         <v/>
       </c>
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="5" t="n"/>
-      <c r="M157" s="9">
+      <c r="M157" s="20">
         <f>IF(A157="","",IF(OR(J157="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J157,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N157" s="9">
+      <c r="N157" s="20">
         <f>IF(A157="","",IF(L157="",Inputs!$B$14,L157)+M157)</f>
         <v/>
       </c>
@@ -8660,30 +8699,30 @@
       <c r="C158" s="4" t="n"/>
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
-      <c r="F158" s="8">
+      <c r="F158" s="20">
         <f>IF(E158&lt;&gt;"",E158,IF(UPPER(TRIM(C158))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C158))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C158))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C158))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C158))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G158" s="8">
+      <c r="G158" s="20">
         <f>IF(A158="","",N158)</f>
         <v/>
       </c>
-      <c r="H158" s="8">
+      <c r="H158" s="20">
         <f>IF(A158="","",Inputs!$B$3/((IF(G158="",Inputs!$B$14,G158)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I158" s="8">
+      <c r="I158" s="20">
         <f>IF(A158="","",2.78E-7*F158*D158*H158)</f>
         <v/>
       </c>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="5" t="n"/>
-      <c r="M158" s="9">
+      <c r="M158" s="20">
         <f>IF(A158="","",IF(OR(J158="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J158,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N158" s="9">
+      <c r="N158" s="20">
         <f>IF(A158="","",IF(L158="",Inputs!$B$14,L158)+M158)</f>
         <v/>
       </c>
@@ -8694,30 +8733,30 @@
       <c r="C159" s="4" t="n"/>
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
-      <c r="F159" s="8">
+      <c r="F159" s="20">
         <f>IF(E159&lt;&gt;"",E159,IF(UPPER(TRIM(C159))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C159))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C159))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C159))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C159))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G159" s="8">
+      <c r="G159" s="20">
         <f>IF(A159="","",N159)</f>
         <v/>
       </c>
-      <c r="H159" s="8">
+      <c r="H159" s="20">
         <f>IF(A159="","",Inputs!$B$3/((IF(G159="",Inputs!$B$14,G159)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I159" s="8">
+      <c r="I159" s="20">
         <f>IF(A159="","",2.78E-7*F159*D159*H159)</f>
         <v/>
       </c>
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="5" t="n"/>
-      <c r="M159" s="9">
+      <c r="M159" s="20">
         <f>IF(A159="","",IF(OR(J159="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J159,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N159" s="9">
+      <c r="N159" s="20">
         <f>IF(A159="","",IF(L159="",Inputs!$B$14,L159)+M159)</f>
         <v/>
       </c>
@@ -8728,30 +8767,30 @@
       <c r="C160" s="4" t="n"/>
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
-      <c r="F160" s="8">
+      <c r="F160" s="20">
         <f>IF(E160&lt;&gt;"",E160,IF(UPPER(TRIM(C160))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C160))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C160))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C160))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C160))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G160" s="8">
+      <c r="G160" s="20">
         <f>IF(A160="","",N160)</f>
         <v/>
       </c>
-      <c r="H160" s="8">
+      <c r="H160" s="20">
         <f>IF(A160="","",Inputs!$B$3/((IF(G160="",Inputs!$B$14,G160)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I160" s="8">
+      <c r="I160" s="20">
         <f>IF(A160="","",2.78E-7*F160*D160*H160)</f>
         <v/>
       </c>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="5" t="n"/>
-      <c r="M160" s="9">
+      <c r="M160" s="20">
         <f>IF(A160="","",IF(OR(J160="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J160,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N160" s="9">
+      <c r="N160" s="20">
         <f>IF(A160="","",IF(L160="",Inputs!$B$14,L160)+M160)</f>
         <v/>
       </c>
@@ -8762,30 +8801,30 @@
       <c r="C161" s="4" t="n"/>
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
-      <c r="F161" s="8">
+      <c r="F161" s="20">
         <f>IF(E161&lt;&gt;"",E161,IF(UPPER(TRIM(C161))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C161))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C161))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C161))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C161))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G161" s="8">
+      <c r="G161" s="20">
         <f>IF(A161="","",N161)</f>
         <v/>
       </c>
-      <c r="H161" s="8">
+      <c r="H161" s="20">
         <f>IF(A161="","",Inputs!$B$3/((IF(G161="",Inputs!$B$14,G161)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I161" s="8">
+      <c r="I161" s="20">
         <f>IF(A161="","",2.78E-7*F161*D161*H161)</f>
         <v/>
       </c>
       <c r="J161" s="4" t="n"/>
       <c r="K161" s="4" t="n"/>
       <c r="L161" s="5" t="n"/>
-      <c r="M161" s="9">
+      <c r="M161" s="20">
         <f>IF(A161="","",IF(OR(J161="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J161,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N161" s="9">
+      <c r="N161" s="20">
         <f>IF(A161="","",IF(L161="",Inputs!$B$14,L161)+M161)</f>
         <v/>
       </c>
@@ -8796,30 +8835,30 @@
       <c r="C162" s="4" t="n"/>
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
-      <c r="F162" s="8">
+      <c r="F162" s="20">
         <f>IF(E162&lt;&gt;"",E162,IF(UPPER(TRIM(C162))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C162))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C162))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C162))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C162))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G162" s="8">
+      <c r="G162" s="20">
         <f>IF(A162="","",N162)</f>
         <v/>
       </c>
-      <c r="H162" s="8">
+      <c r="H162" s="20">
         <f>IF(A162="","",Inputs!$B$3/((IF(G162="",Inputs!$B$14,G162)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I162" s="8">
+      <c r="I162" s="20">
         <f>IF(A162="","",2.78E-7*F162*D162*H162)</f>
         <v/>
       </c>
       <c r="J162" s="4" t="n"/>
       <c r="K162" s="4" t="n"/>
       <c r="L162" s="5" t="n"/>
-      <c r="M162" s="9">
+      <c r="M162" s="20">
         <f>IF(A162="","",IF(OR(J162="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J162,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N162" s="9">
+      <c r="N162" s="20">
         <f>IF(A162="","",IF(L162="",Inputs!$B$14,L162)+M162)</f>
         <v/>
       </c>
@@ -8830,30 +8869,30 @@
       <c r="C163" s="4" t="n"/>
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
-      <c r="F163" s="8">
+      <c r="F163" s="20">
         <f>IF(E163&lt;&gt;"",E163,IF(UPPER(TRIM(C163))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C163))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C163))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C163))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C163))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G163" s="8">
+      <c r="G163" s="20">
         <f>IF(A163="","",N163)</f>
         <v/>
       </c>
-      <c r="H163" s="8">
+      <c r="H163" s="20">
         <f>IF(A163="","",Inputs!$B$3/((IF(G163="",Inputs!$B$14,G163)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I163" s="8">
+      <c r="I163" s="20">
         <f>IF(A163="","",2.78E-7*F163*D163*H163)</f>
         <v/>
       </c>
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="5" t="n"/>
-      <c r="M163" s="9">
+      <c r="M163" s="20">
         <f>IF(A163="","",IF(OR(J163="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J163,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N163" s="9">
+      <c r="N163" s="20">
         <f>IF(A163="","",IF(L163="",Inputs!$B$14,L163)+M163)</f>
         <v/>
       </c>
@@ -8864,30 +8903,30 @@
       <c r="C164" s="4" t="n"/>
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
-      <c r="F164" s="8">
+      <c r="F164" s="20">
         <f>IF(E164&lt;&gt;"",E164,IF(UPPER(TRIM(C164))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C164))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C164))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C164))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C164))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G164" s="8">
+      <c r="G164" s="20">
         <f>IF(A164="","",N164)</f>
         <v/>
       </c>
-      <c r="H164" s="8">
+      <c r="H164" s="20">
         <f>IF(A164="","",Inputs!$B$3/((IF(G164="",Inputs!$B$14,G164)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I164" s="8">
+      <c r="I164" s="20">
         <f>IF(A164="","",2.78E-7*F164*D164*H164)</f>
         <v/>
       </c>
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="5" t="n"/>
-      <c r="M164" s="9">
+      <c r="M164" s="20">
         <f>IF(A164="","",IF(OR(J164="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J164,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N164" s="9">
+      <c r="N164" s="20">
         <f>IF(A164="","",IF(L164="",Inputs!$B$14,L164)+M164)</f>
         <v/>
       </c>
@@ -8898,30 +8937,30 @@
       <c r="C165" s="4" t="n"/>
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
-      <c r="F165" s="8">
+      <c r="F165" s="20">
         <f>IF(E165&lt;&gt;"",E165,IF(UPPER(TRIM(C165))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C165))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C165))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C165))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C165))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G165" s="8">
+      <c r="G165" s="20">
         <f>IF(A165="","",N165)</f>
         <v/>
       </c>
-      <c r="H165" s="8">
+      <c r="H165" s="20">
         <f>IF(A165="","",Inputs!$B$3/((IF(G165="",Inputs!$B$14,G165)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I165" s="8">
+      <c r="I165" s="20">
         <f>IF(A165="","",2.78E-7*F165*D165*H165)</f>
         <v/>
       </c>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="5" t="n"/>
-      <c r="M165" s="9">
+      <c r="M165" s="20">
         <f>IF(A165="","",IF(OR(J165="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J165,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N165" s="9">
+      <c r="N165" s="20">
         <f>IF(A165="","",IF(L165="",Inputs!$B$14,L165)+M165)</f>
         <v/>
       </c>
@@ -8932,30 +8971,30 @@
       <c r="C166" s="4" t="n"/>
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
-      <c r="F166" s="8">
+      <c r="F166" s="20">
         <f>IF(E166&lt;&gt;"",E166,IF(UPPER(TRIM(C166))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C166))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C166))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C166))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C166))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G166" s="8">
+      <c r="G166" s="20">
         <f>IF(A166="","",N166)</f>
         <v/>
       </c>
-      <c r="H166" s="8">
+      <c r="H166" s="20">
         <f>IF(A166="","",Inputs!$B$3/((IF(G166="",Inputs!$B$14,G166)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I166" s="8">
+      <c r="I166" s="20">
         <f>IF(A166="","",2.78E-7*F166*D166*H166)</f>
         <v/>
       </c>
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="5" t="n"/>
-      <c r="M166" s="9">
+      <c r="M166" s="20">
         <f>IF(A166="","",IF(OR(J166="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J166,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N166" s="9">
+      <c r="N166" s="20">
         <f>IF(A166="","",IF(L166="",Inputs!$B$14,L166)+M166)</f>
         <v/>
       </c>
@@ -8966,30 +9005,30 @@
       <c r="C167" s="4" t="n"/>
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
-      <c r="F167" s="8">
+      <c r="F167" s="20">
         <f>IF(E167&lt;&gt;"",E167,IF(UPPER(TRIM(C167))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C167))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C167))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C167))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C167))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G167" s="8">
+      <c r="G167" s="20">
         <f>IF(A167="","",N167)</f>
         <v/>
       </c>
-      <c r="H167" s="8">
+      <c r="H167" s="20">
         <f>IF(A167="","",Inputs!$B$3/((IF(G167="",Inputs!$B$14,G167)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I167" s="8">
+      <c r="I167" s="20">
         <f>IF(A167="","",2.78E-7*F167*D167*H167)</f>
         <v/>
       </c>
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="5" t="n"/>
-      <c r="M167" s="9">
+      <c r="M167" s="20">
         <f>IF(A167="","",IF(OR(J167="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J167,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N167" s="9">
+      <c r="N167" s="20">
         <f>IF(A167="","",IF(L167="",Inputs!$B$14,L167)+M167)</f>
         <v/>
       </c>
@@ -9000,30 +9039,30 @@
       <c r="C168" s="4" t="n"/>
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
-      <c r="F168" s="8">
+      <c r="F168" s="20">
         <f>IF(E168&lt;&gt;"",E168,IF(UPPER(TRIM(C168))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C168))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C168))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C168))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C168))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G168" s="8">
+      <c r="G168" s="20">
         <f>IF(A168="","",N168)</f>
         <v/>
       </c>
-      <c r="H168" s="8">
+      <c r="H168" s="20">
         <f>IF(A168="","",Inputs!$B$3/((IF(G168="",Inputs!$B$14,G168)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I168" s="8">
+      <c r="I168" s="20">
         <f>IF(A168="","",2.78E-7*F168*D168*H168)</f>
         <v/>
       </c>
       <c r="J168" s="4" t="n"/>
       <c r="K168" s="4" t="n"/>
       <c r="L168" s="5" t="n"/>
-      <c r="M168" s="9">
+      <c r="M168" s="20">
         <f>IF(A168="","",IF(OR(J168="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J168,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N168" s="9">
+      <c r="N168" s="20">
         <f>IF(A168="","",IF(L168="",Inputs!$B$14,L168)+M168)</f>
         <v/>
       </c>
@@ -9034,30 +9073,30 @@
       <c r="C169" s="4" t="n"/>
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
-      <c r="F169" s="8">
+      <c r="F169" s="20">
         <f>IF(E169&lt;&gt;"",E169,IF(UPPER(TRIM(C169))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C169))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C169))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C169))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C169))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G169" s="8">
+      <c r="G169" s="20">
         <f>IF(A169="","",N169)</f>
         <v/>
       </c>
-      <c r="H169" s="8">
+      <c r="H169" s="20">
         <f>IF(A169="","",Inputs!$B$3/((IF(G169="",Inputs!$B$14,G169)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I169" s="8">
+      <c r="I169" s="20">
         <f>IF(A169="","",2.78E-7*F169*D169*H169)</f>
         <v/>
       </c>
       <c r="J169" s="4" t="n"/>
       <c r="K169" s="4" t="n"/>
       <c r="L169" s="5" t="n"/>
-      <c r="M169" s="9">
+      <c r="M169" s="20">
         <f>IF(A169="","",IF(OR(J169="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J169,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N169" s="9">
+      <c r="N169" s="20">
         <f>IF(A169="","",IF(L169="",Inputs!$B$14,L169)+M169)</f>
         <v/>
       </c>
@@ -9068,30 +9107,30 @@
       <c r="C170" s="4" t="n"/>
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
-      <c r="F170" s="8">
+      <c r="F170" s="20">
         <f>IF(E170&lt;&gt;"",E170,IF(UPPER(TRIM(C170))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C170))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C170))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C170))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C170))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G170" s="8">
+      <c r="G170" s="20">
         <f>IF(A170="","",N170)</f>
         <v/>
       </c>
-      <c r="H170" s="8">
+      <c r="H170" s="20">
         <f>IF(A170="","",Inputs!$B$3/((IF(G170="",Inputs!$B$14,G170)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I170" s="8">
+      <c r="I170" s="20">
         <f>IF(A170="","",2.78E-7*F170*D170*H170)</f>
         <v/>
       </c>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="5" t="n"/>
-      <c r="M170" s="9">
+      <c r="M170" s="20">
         <f>IF(A170="","",IF(OR(J170="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J170,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N170" s="9">
+      <c r="N170" s="20">
         <f>IF(A170="","",IF(L170="",Inputs!$B$14,L170)+M170)</f>
         <v/>
       </c>
@@ -9102,30 +9141,30 @@
       <c r="C171" s="4" t="n"/>
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
-      <c r="F171" s="8">
+      <c r="F171" s="20">
         <f>IF(E171&lt;&gt;"",E171,IF(UPPER(TRIM(C171))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C171))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C171))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C171))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C171))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G171" s="8">
+      <c r="G171" s="20">
         <f>IF(A171="","",N171)</f>
         <v/>
       </c>
-      <c r="H171" s="8">
+      <c r="H171" s="20">
         <f>IF(A171="","",Inputs!$B$3/((IF(G171="",Inputs!$B$14,G171)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I171" s="8">
+      <c r="I171" s="20">
         <f>IF(A171="","",2.78E-7*F171*D171*H171)</f>
         <v/>
       </c>
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="5" t="n"/>
-      <c r="M171" s="9">
+      <c r="M171" s="20">
         <f>IF(A171="","",IF(OR(J171="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J171,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N171" s="9">
+      <c r="N171" s="20">
         <f>IF(A171="","",IF(L171="",Inputs!$B$14,L171)+M171)</f>
         <v/>
       </c>
@@ -9136,30 +9175,30 @@
       <c r="C172" s="4" t="n"/>
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
-      <c r="F172" s="8">
+      <c r="F172" s="20">
         <f>IF(E172&lt;&gt;"",E172,IF(UPPER(TRIM(C172))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C172))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C172))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C172))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C172))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G172" s="8">
+      <c r="G172" s="20">
         <f>IF(A172="","",N172)</f>
         <v/>
       </c>
-      <c r="H172" s="8">
+      <c r="H172" s="20">
         <f>IF(A172="","",Inputs!$B$3/((IF(G172="",Inputs!$B$14,G172)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I172" s="8">
+      <c r="I172" s="20">
         <f>IF(A172="","",2.78E-7*F172*D172*H172)</f>
         <v/>
       </c>
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="5" t="n"/>
-      <c r="M172" s="9">
+      <c r="M172" s="20">
         <f>IF(A172="","",IF(OR(J172="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J172,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N172" s="9">
+      <c r="N172" s="20">
         <f>IF(A172="","",IF(L172="",Inputs!$B$14,L172)+M172)</f>
         <v/>
       </c>
@@ -9170,30 +9209,30 @@
       <c r="C173" s="4" t="n"/>
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
-      <c r="F173" s="8">
+      <c r="F173" s="20">
         <f>IF(E173&lt;&gt;"",E173,IF(UPPER(TRIM(C173))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C173))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C173))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C173))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C173))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G173" s="8">
+      <c r="G173" s="20">
         <f>IF(A173="","",N173)</f>
         <v/>
       </c>
-      <c r="H173" s="8">
+      <c r="H173" s="20">
         <f>IF(A173="","",Inputs!$B$3/((IF(G173="",Inputs!$B$14,G173)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I173" s="8">
+      <c r="I173" s="20">
         <f>IF(A173="","",2.78E-7*F173*D173*H173)</f>
         <v/>
       </c>
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="5" t="n"/>
-      <c r="M173" s="9">
+      <c r="M173" s="20">
         <f>IF(A173="","",IF(OR(J173="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J173,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N173" s="9">
+      <c r="N173" s="20">
         <f>IF(A173="","",IF(L173="",Inputs!$B$14,L173)+M173)</f>
         <v/>
       </c>
@@ -9204,30 +9243,30 @@
       <c r="C174" s="4" t="n"/>
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
-      <c r="F174" s="8">
+      <c r="F174" s="20">
         <f>IF(E174&lt;&gt;"",E174,IF(UPPER(TRIM(C174))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C174))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C174))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C174))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C174))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G174" s="8">
+      <c r="G174" s="20">
         <f>IF(A174="","",N174)</f>
         <v/>
       </c>
-      <c r="H174" s="8">
+      <c r="H174" s="20">
         <f>IF(A174="","",Inputs!$B$3/((IF(G174="",Inputs!$B$14,G174)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I174" s="8">
+      <c r="I174" s="20">
         <f>IF(A174="","",2.78E-7*F174*D174*H174)</f>
         <v/>
       </c>
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="5" t="n"/>
-      <c r="M174" s="9">
+      <c r="M174" s="20">
         <f>IF(A174="","",IF(OR(J174="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J174,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N174" s="9">
+      <c r="N174" s="20">
         <f>IF(A174="","",IF(L174="",Inputs!$B$14,L174)+M174)</f>
         <v/>
       </c>
@@ -9238,30 +9277,30 @@
       <c r="C175" s="4" t="n"/>
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
-      <c r="F175" s="8">
+      <c r="F175" s="20">
         <f>IF(E175&lt;&gt;"",E175,IF(UPPER(TRIM(C175))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C175))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C175))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C175))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C175))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G175" s="8">
+      <c r="G175" s="20">
         <f>IF(A175="","",N175)</f>
         <v/>
       </c>
-      <c r="H175" s="8">
+      <c r="H175" s="20">
         <f>IF(A175="","",Inputs!$B$3/((IF(G175="",Inputs!$B$14,G175)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I175" s="8">
+      <c r="I175" s="20">
         <f>IF(A175="","",2.78E-7*F175*D175*H175)</f>
         <v/>
       </c>
       <c r="J175" s="4" t="n"/>
       <c r="K175" s="4" t="n"/>
       <c r="L175" s="5" t="n"/>
-      <c r="M175" s="9">
+      <c r="M175" s="20">
         <f>IF(A175="","",IF(OR(J175="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J175,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N175" s="9">
+      <c r="N175" s="20">
         <f>IF(A175="","",IF(L175="",Inputs!$B$14,L175)+M175)</f>
         <v/>
       </c>
@@ -9272,30 +9311,30 @@
       <c r="C176" s="4" t="n"/>
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
-      <c r="F176" s="8">
+      <c r="F176" s="20">
         <f>IF(E176&lt;&gt;"",E176,IF(UPPER(TRIM(C176))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C176))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C176))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C176))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C176))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G176" s="8">
+      <c r="G176" s="20">
         <f>IF(A176="","",N176)</f>
         <v/>
       </c>
-      <c r="H176" s="8">
+      <c r="H176" s="20">
         <f>IF(A176="","",Inputs!$B$3/((IF(G176="",Inputs!$B$14,G176)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I176" s="8">
+      <c r="I176" s="20">
         <f>IF(A176="","",2.78E-7*F176*D176*H176)</f>
         <v/>
       </c>
       <c r="J176" s="4" t="n"/>
       <c r="K176" s="4" t="n"/>
       <c r="L176" s="5" t="n"/>
-      <c r="M176" s="9">
+      <c r="M176" s="20">
         <f>IF(A176="","",IF(OR(J176="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J176,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N176" s="9">
+      <c r="N176" s="20">
         <f>IF(A176="","",IF(L176="",Inputs!$B$14,L176)+M176)</f>
         <v/>
       </c>
@@ -9306,30 +9345,30 @@
       <c r="C177" s="4" t="n"/>
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
-      <c r="F177" s="8">
+      <c r="F177" s="20">
         <f>IF(E177&lt;&gt;"",E177,IF(UPPER(TRIM(C177))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C177))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C177))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C177))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C177))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G177" s="8">
+      <c r="G177" s="20">
         <f>IF(A177="","",N177)</f>
         <v/>
       </c>
-      <c r="H177" s="8">
+      <c r="H177" s="20">
         <f>IF(A177="","",Inputs!$B$3/((IF(G177="",Inputs!$B$14,G177)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I177" s="8">
+      <c r="I177" s="20">
         <f>IF(A177="","",2.78E-7*F177*D177*H177)</f>
         <v/>
       </c>
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="5" t="n"/>
-      <c r="M177" s="9">
+      <c r="M177" s="20">
         <f>IF(A177="","",IF(OR(J177="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J177,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N177" s="9">
+      <c r="N177" s="20">
         <f>IF(A177="","",IF(L177="",Inputs!$B$14,L177)+M177)</f>
         <v/>
       </c>
@@ -9340,30 +9379,30 @@
       <c r="C178" s="4" t="n"/>
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
-      <c r="F178" s="8">
+      <c r="F178" s="20">
         <f>IF(E178&lt;&gt;"",E178,IF(UPPER(TRIM(C178))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C178))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C178))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C178))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C178))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G178" s="8">
+      <c r="G178" s="20">
         <f>IF(A178="","",N178)</f>
         <v/>
       </c>
-      <c r="H178" s="8">
+      <c r="H178" s="20">
         <f>IF(A178="","",Inputs!$B$3/((IF(G178="",Inputs!$B$14,G178)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I178" s="8">
+      <c r="I178" s="20">
         <f>IF(A178="","",2.78E-7*F178*D178*H178)</f>
         <v/>
       </c>
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="5" t="n"/>
-      <c r="M178" s="9">
+      <c r="M178" s="20">
         <f>IF(A178="","",IF(OR(J178="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J178,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N178" s="9">
+      <c r="N178" s="20">
         <f>IF(A178="","",IF(L178="",Inputs!$B$14,L178)+M178)</f>
         <v/>
       </c>
@@ -9374,30 +9413,30 @@
       <c r="C179" s="4" t="n"/>
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
-      <c r="F179" s="8">
+      <c r="F179" s="20">
         <f>IF(E179&lt;&gt;"",E179,IF(UPPER(TRIM(C179))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C179))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C179))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C179))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C179))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G179" s="8">
+      <c r="G179" s="20">
         <f>IF(A179="","",N179)</f>
         <v/>
       </c>
-      <c r="H179" s="8">
+      <c r="H179" s="20">
         <f>IF(A179="","",Inputs!$B$3/((IF(G179="",Inputs!$B$14,G179)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I179" s="8">
+      <c r="I179" s="20">
         <f>IF(A179="","",2.78E-7*F179*D179*H179)</f>
         <v/>
       </c>
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="5" t="n"/>
-      <c r="M179" s="9">
+      <c r="M179" s="20">
         <f>IF(A179="","",IF(OR(J179="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J179,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N179" s="9">
+      <c r="N179" s="20">
         <f>IF(A179="","",IF(L179="",Inputs!$B$14,L179)+M179)</f>
         <v/>
       </c>
@@ -9408,30 +9447,30 @@
       <c r="C180" s="4" t="n"/>
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
-      <c r="F180" s="8">
+      <c r="F180" s="20">
         <f>IF(E180&lt;&gt;"",E180,IF(UPPER(TRIM(C180))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C180))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C180))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C180))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C180))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G180" s="8">
+      <c r="G180" s="20">
         <f>IF(A180="","",N180)</f>
         <v/>
       </c>
-      <c r="H180" s="8">
+      <c r="H180" s="20">
         <f>IF(A180="","",Inputs!$B$3/((IF(G180="",Inputs!$B$14,G180)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I180" s="8">
+      <c r="I180" s="20">
         <f>IF(A180="","",2.78E-7*F180*D180*H180)</f>
         <v/>
       </c>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="5" t="n"/>
-      <c r="M180" s="9">
+      <c r="M180" s="20">
         <f>IF(A180="","",IF(OR(J180="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J180,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N180" s="9">
+      <c r="N180" s="20">
         <f>IF(A180="","",IF(L180="",Inputs!$B$14,L180)+M180)</f>
         <v/>
       </c>
@@ -9442,30 +9481,30 @@
       <c r="C181" s="4" t="n"/>
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
-      <c r="F181" s="8">
+      <c r="F181" s="20">
         <f>IF(E181&lt;&gt;"",E181,IF(UPPER(TRIM(C181))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C181))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C181))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C181))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C181))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G181" s="8">
+      <c r="G181" s="20">
         <f>IF(A181="","",N181)</f>
         <v/>
       </c>
-      <c r="H181" s="8">
+      <c r="H181" s="20">
         <f>IF(A181="","",Inputs!$B$3/((IF(G181="",Inputs!$B$14,G181)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I181" s="8">
+      <c r="I181" s="20">
         <f>IF(A181="","",2.78E-7*F181*D181*H181)</f>
         <v/>
       </c>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="5" t="n"/>
-      <c r="M181" s="9">
+      <c r="M181" s="20">
         <f>IF(A181="","",IF(OR(J181="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J181,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N181" s="9">
+      <c r="N181" s="20">
         <f>IF(A181="","",IF(L181="",Inputs!$B$14,L181)+M181)</f>
         <v/>
       </c>
@@ -9476,30 +9515,30 @@
       <c r="C182" s="4" t="n"/>
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
-      <c r="F182" s="8">
+      <c r="F182" s="20">
         <f>IF(E182&lt;&gt;"",E182,IF(UPPER(TRIM(C182))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C182))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C182))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C182))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C182))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G182" s="8">
+      <c r="G182" s="20">
         <f>IF(A182="","",N182)</f>
         <v/>
       </c>
-      <c r="H182" s="8">
+      <c r="H182" s="20">
         <f>IF(A182="","",Inputs!$B$3/((IF(G182="",Inputs!$B$14,G182)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I182" s="8">
+      <c r="I182" s="20">
         <f>IF(A182="","",2.78E-7*F182*D182*H182)</f>
         <v/>
       </c>
       <c r="J182" s="4" t="n"/>
       <c r="K182" s="4" t="n"/>
       <c r="L182" s="5" t="n"/>
-      <c r="M182" s="9">
+      <c r="M182" s="20">
         <f>IF(A182="","",IF(OR(J182="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J182,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N182" s="9">
+      <c r="N182" s="20">
         <f>IF(A182="","",IF(L182="",Inputs!$B$14,L182)+M182)</f>
         <v/>
       </c>
@@ -9510,30 +9549,30 @@
       <c r="C183" s="4" t="n"/>
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
-      <c r="F183" s="8">
+      <c r="F183" s="20">
         <f>IF(E183&lt;&gt;"",E183,IF(UPPER(TRIM(C183))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C183))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C183))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C183))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C183))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G183" s="8">
+      <c r="G183" s="20">
         <f>IF(A183="","",N183)</f>
         <v/>
       </c>
-      <c r="H183" s="8">
+      <c r="H183" s="20">
         <f>IF(A183="","",Inputs!$B$3/((IF(G183="",Inputs!$B$14,G183)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I183" s="8">
+      <c r="I183" s="20">
         <f>IF(A183="","",2.78E-7*F183*D183*H183)</f>
         <v/>
       </c>
       <c r="J183" s="4" t="n"/>
       <c r="K183" s="4" t="n"/>
       <c r="L183" s="5" t="n"/>
-      <c r="M183" s="9">
+      <c r="M183" s="20">
         <f>IF(A183="","",IF(OR(J183="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J183,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N183" s="9">
+      <c r="N183" s="20">
         <f>IF(A183="","",IF(L183="",Inputs!$B$14,L183)+M183)</f>
         <v/>
       </c>
@@ -9544,30 +9583,30 @@
       <c r="C184" s="4" t="n"/>
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
-      <c r="F184" s="8">
+      <c r="F184" s="20">
         <f>IF(E184&lt;&gt;"",E184,IF(UPPER(TRIM(C184))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C184))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C184))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C184))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C184))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G184" s="8">
+      <c r="G184" s="20">
         <f>IF(A184="","",N184)</f>
         <v/>
       </c>
-      <c r="H184" s="8">
+      <c r="H184" s="20">
         <f>IF(A184="","",Inputs!$B$3/((IF(G184="",Inputs!$B$14,G184)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I184" s="8">
+      <c r="I184" s="20">
         <f>IF(A184="","",2.78E-7*F184*D184*H184)</f>
         <v/>
       </c>
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="5" t="n"/>
-      <c r="M184" s="9">
+      <c r="M184" s="20">
         <f>IF(A184="","",IF(OR(J184="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J184,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N184" s="9">
+      <c r="N184" s="20">
         <f>IF(A184="","",IF(L184="",Inputs!$B$14,L184)+M184)</f>
         <v/>
       </c>
@@ -9578,30 +9617,30 @@
       <c r="C185" s="4" t="n"/>
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
-      <c r="F185" s="8">
+      <c r="F185" s="20">
         <f>IF(E185&lt;&gt;"",E185,IF(UPPER(TRIM(C185))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C185))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C185))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C185))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C185))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G185" s="8">
+      <c r="G185" s="20">
         <f>IF(A185="","",N185)</f>
         <v/>
       </c>
-      <c r="H185" s="8">
+      <c r="H185" s="20">
         <f>IF(A185="","",Inputs!$B$3/((IF(G185="",Inputs!$B$14,G185)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I185" s="8">
+      <c r="I185" s="20">
         <f>IF(A185="","",2.78E-7*F185*D185*H185)</f>
         <v/>
       </c>
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="5" t="n"/>
-      <c r="M185" s="9">
+      <c r="M185" s="20">
         <f>IF(A185="","",IF(OR(J185="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J185,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N185" s="9">
+      <c r="N185" s="20">
         <f>IF(A185="","",IF(L185="",Inputs!$B$14,L185)+M185)</f>
         <v/>
       </c>
@@ -9612,30 +9651,30 @@
       <c r="C186" s="4" t="n"/>
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
-      <c r="F186" s="8">
+      <c r="F186" s="20">
         <f>IF(E186&lt;&gt;"",E186,IF(UPPER(TRIM(C186))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C186))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C186))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C186))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C186))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G186" s="8">
+      <c r="G186" s="20">
         <f>IF(A186="","",N186)</f>
         <v/>
       </c>
-      <c r="H186" s="8">
+      <c r="H186" s="20">
         <f>IF(A186="","",Inputs!$B$3/((IF(G186="",Inputs!$B$14,G186)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I186" s="8">
+      <c r="I186" s="20">
         <f>IF(A186="","",2.78E-7*F186*D186*H186)</f>
         <v/>
       </c>
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="5" t="n"/>
-      <c r="M186" s="9">
+      <c r="M186" s="20">
         <f>IF(A186="","",IF(OR(J186="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J186,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N186" s="9">
+      <c r="N186" s="20">
         <f>IF(A186="","",IF(L186="",Inputs!$B$14,L186)+M186)</f>
         <v/>
       </c>
@@ -9646,30 +9685,30 @@
       <c r="C187" s="4" t="n"/>
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
-      <c r="F187" s="8">
+      <c r="F187" s="20">
         <f>IF(E187&lt;&gt;"",E187,IF(UPPER(TRIM(C187))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C187))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C187))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C187))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C187))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G187" s="8">
+      <c r="G187" s="20">
         <f>IF(A187="","",N187)</f>
         <v/>
       </c>
-      <c r="H187" s="8">
+      <c r="H187" s="20">
         <f>IF(A187="","",Inputs!$B$3/((IF(G187="",Inputs!$B$14,G187)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I187" s="8">
+      <c r="I187" s="20">
         <f>IF(A187="","",2.78E-7*F187*D187*H187)</f>
         <v/>
       </c>
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="5" t="n"/>
-      <c r="M187" s="9">
+      <c r="M187" s="20">
         <f>IF(A187="","",IF(OR(J187="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J187,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N187" s="9">
+      <c r="N187" s="20">
         <f>IF(A187="","",IF(L187="",Inputs!$B$14,L187)+M187)</f>
         <v/>
       </c>
@@ -9680,30 +9719,30 @@
       <c r="C188" s="4" t="n"/>
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
-      <c r="F188" s="8">
+      <c r="F188" s="20">
         <f>IF(E188&lt;&gt;"",E188,IF(UPPER(TRIM(C188))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C188))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C188))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C188))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C188))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G188" s="8">
+      <c r="G188" s="20">
         <f>IF(A188="","",N188)</f>
         <v/>
       </c>
-      <c r="H188" s="8">
+      <c r="H188" s="20">
         <f>IF(A188="","",Inputs!$B$3/((IF(G188="",Inputs!$B$14,G188)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I188" s="8">
+      <c r="I188" s="20">
         <f>IF(A188="","",2.78E-7*F188*D188*H188)</f>
         <v/>
       </c>
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="5" t="n"/>
-      <c r="M188" s="9">
+      <c r="M188" s="20">
         <f>IF(A188="","",IF(OR(J188="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J188,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N188" s="9">
+      <c r="N188" s="20">
         <f>IF(A188="","",IF(L188="",Inputs!$B$14,L188)+M188)</f>
         <v/>
       </c>
@@ -9714,30 +9753,30 @@
       <c r="C189" s="4" t="n"/>
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
-      <c r="F189" s="8">
+      <c r="F189" s="20">
         <f>IF(E189&lt;&gt;"",E189,IF(UPPER(TRIM(C189))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C189))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C189))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C189))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C189))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G189" s="8">
+      <c r="G189" s="20">
         <f>IF(A189="","",N189)</f>
         <v/>
       </c>
-      <c r="H189" s="8">
+      <c r="H189" s="20">
         <f>IF(A189="","",Inputs!$B$3/((IF(G189="",Inputs!$B$14,G189)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I189" s="8">
+      <c r="I189" s="20">
         <f>IF(A189="","",2.78E-7*F189*D189*H189)</f>
         <v/>
       </c>
       <c r="J189" s="4" t="n"/>
       <c r="K189" s="4" t="n"/>
       <c r="L189" s="5" t="n"/>
-      <c r="M189" s="9">
+      <c r="M189" s="20">
         <f>IF(A189="","",IF(OR(J189="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J189,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N189" s="9">
+      <c r="N189" s="20">
         <f>IF(A189="","",IF(L189="",Inputs!$B$14,L189)+M189)</f>
         <v/>
       </c>
@@ -9748,30 +9787,30 @@
       <c r="C190" s="4" t="n"/>
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
-      <c r="F190" s="8">
+      <c r="F190" s="20">
         <f>IF(E190&lt;&gt;"",E190,IF(UPPER(TRIM(C190))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C190))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C190))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C190))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C190))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G190" s="8">
+      <c r="G190" s="20">
         <f>IF(A190="","",N190)</f>
         <v/>
       </c>
-      <c r="H190" s="8">
+      <c r="H190" s="20">
         <f>IF(A190="","",Inputs!$B$3/((IF(G190="",Inputs!$B$14,G190)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I190" s="8">
+      <c r="I190" s="20">
         <f>IF(A190="","",2.78E-7*F190*D190*H190)</f>
         <v/>
       </c>
       <c r="J190" s="4" t="n"/>
       <c r="K190" s="4" t="n"/>
       <c r="L190" s="5" t="n"/>
-      <c r="M190" s="9">
+      <c r="M190" s="20">
         <f>IF(A190="","",IF(OR(J190="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J190,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N190" s="9">
+      <c r="N190" s="20">
         <f>IF(A190="","",IF(L190="",Inputs!$B$14,L190)+M190)</f>
         <v/>
       </c>
@@ -9782,30 +9821,30 @@
       <c r="C191" s="4" t="n"/>
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
-      <c r="F191" s="8">
+      <c r="F191" s="20">
         <f>IF(E191&lt;&gt;"",E191,IF(UPPER(TRIM(C191))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C191))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C191))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C191))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C191))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G191" s="8">
+      <c r="G191" s="20">
         <f>IF(A191="","",N191)</f>
         <v/>
       </c>
-      <c r="H191" s="8">
+      <c r="H191" s="20">
         <f>IF(A191="","",Inputs!$B$3/((IF(G191="",Inputs!$B$14,G191)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I191" s="8">
+      <c r="I191" s="20">
         <f>IF(A191="","",2.78E-7*F191*D191*H191)</f>
         <v/>
       </c>
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="5" t="n"/>
-      <c r="M191" s="9">
+      <c r="M191" s="20">
         <f>IF(A191="","",IF(OR(J191="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J191,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N191" s="9">
+      <c r="N191" s="20">
         <f>IF(A191="","",IF(L191="",Inputs!$B$14,L191)+M191)</f>
         <v/>
       </c>
@@ -9816,30 +9855,30 @@
       <c r="C192" s="4" t="n"/>
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
-      <c r="F192" s="8">
+      <c r="F192" s="20">
         <f>IF(E192&lt;&gt;"",E192,IF(UPPER(TRIM(C192))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C192))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C192))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C192))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C192))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G192" s="8">
+      <c r="G192" s="20">
         <f>IF(A192="","",N192)</f>
         <v/>
       </c>
-      <c r="H192" s="8">
+      <c r="H192" s="20">
         <f>IF(A192="","",Inputs!$B$3/((IF(G192="",Inputs!$B$14,G192)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I192" s="8">
+      <c r="I192" s="20">
         <f>IF(A192="","",2.78E-7*F192*D192*H192)</f>
         <v/>
       </c>
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="5" t="n"/>
-      <c r="M192" s="9">
+      <c r="M192" s="20">
         <f>IF(A192="","",IF(OR(J192="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J192,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N192" s="9">
+      <c r="N192" s="20">
         <f>IF(A192="","",IF(L192="",Inputs!$B$14,L192)+M192)</f>
         <v/>
       </c>
@@ -9850,30 +9889,30 @@
       <c r="C193" s="4" t="n"/>
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
-      <c r="F193" s="8">
+      <c r="F193" s="20">
         <f>IF(E193&lt;&gt;"",E193,IF(UPPER(TRIM(C193))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C193))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C193))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C193))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C193))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G193" s="8">
+      <c r="G193" s="20">
         <f>IF(A193="","",N193)</f>
         <v/>
       </c>
-      <c r="H193" s="8">
+      <c r="H193" s="20">
         <f>IF(A193="","",Inputs!$B$3/((IF(G193="",Inputs!$B$14,G193)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I193" s="8">
+      <c r="I193" s="20">
         <f>IF(A193="","",2.78E-7*F193*D193*H193)</f>
         <v/>
       </c>
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="5" t="n"/>
-      <c r="M193" s="9">
+      <c r="M193" s="20">
         <f>IF(A193="","",IF(OR(J193="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J193,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N193" s="9">
+      <c r="N193" s="20">
         <f>IF(A193="","",IF(L193="",Inputs!$B$14,L193)+M193)</f>
         <v/>
       </c>
@@ -9884,30 +9923,30 @@
       <c r="C194" s="4" t="n"/>
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
-      <c r="F194" s="8">
+      <c r="F194" s="20">
         <f>IF(E194&lt;&gt;"",E194,IF(UPPER(TRIM(C194))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C194))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C194))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C194))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C194))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G194" s="8">
+      <c r="G194" s="20">
         <f>IF(A194="","",N194)</f>
         <v/>
       </c>
-      <c r="H194" s="8">
+      <c r="H194" s="20">
         <f>IF(A194="","",Inputs!$B$3/((IF(G194="",Inputs!$B$14,G194)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I194" s="8">
+      <c r="I194" s="20">
         <f>IF(A194="","",2.78E-7*F194*D194*H194)</f>
         <v/>
       </c>
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="5" t="n"/>
-      <c r="M194" s="9">
+      <c r="M194" s="20">
         <f>IF(A194="","",IF(OR(J194="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J194,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N194" s="9">
+      <c r="N194" s="20">
         <f>IF(A194="","",IF(L194="",Inputs!$B$14,L194)+M194)</f>
         <v/>
       </c>
@@ -9918,30 +9957,30 @@
       <c r="C195" s="4" t="n"/>
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
-      <c r="F195" s="8">
+      <c r="F195" s="20">
         <f>IF(E195&lt;&gt;"",E195,IF(UPPER(TRIM(C195))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C195))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C195))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C195))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C195))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G195" s="8">
+      <c r="G195" s="20">
         <f>IF(A195="","",N195)</f>
         <v/>
       </c>
-      <c r="H195" s="8">
+      <c r="H195" s="20">
         <f>IF(A195="","",Inputs!$B$3/((IF(G195="",Inputs!$B$14,G195)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I195" s="8">
+      <c r="I195" s="20">
         <f>IF(A195="","",2.78E-7*F195*D195*H195)</f>
         <v/>
       </c>
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="5" t="n"/>
-      <c r="M195" s="9">
+      <c r="M195" s="20">
         <f>IF(A195="","",IF(OR(J195="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J195,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N195" s="9">
+      <c r="N195" s="20">
         <f>IF(A195="","",IF(L195="",Inputs!$B$14,L195)+M195)</f>
         <v/>
       </c>
@@ -9952,30 +9991,30 @@
       <c r="C196" s="4" t="n"/>
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
-      <c r="F196" s="8">
+      <c r="F196" s="20">
         <f>IF(E196&lt;&gt;"",E196,IF(UPPER(TRIM(C196))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C196))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C196))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C196))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C196))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G196" s="8">
+      <c r="G196" s="20">
         <f>IF(A196="","",N196)</f>
         <v/>
       </c>
-      <c r="H196" s="8">
+      <c r="H196" s="20">
         <f>IF(A196="","",Inputs!$B$3/((IF(G196="",Inputs!$B$14,G196)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I196" s="8">
+      <c r="I196" s="20">
         <f>IF(A196="","",2.78E-7*F196*D196*H196)</f>
         <v/>
       </c>
       <c r="J196" s="4" t="n"/>
       <c r="K196" s="4" t="n"/>
       <c r="L196" s="5" t="n"/>
-      <c r="M196" s="9">
+      <c r="M196" s="20">
         <f>IF(A196="","",IF(OR(J196="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J196,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N196" s="9">
+      <c r="N196" s="20">
         <f>IF(A196="","",IF(L196="",Inputs!$B$14,L196)+M196)</f>
         <v/>
       </c>
@@ -9986,30 +10025,30 @@
       <c r="C197" s="4" t="n"/>
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
-      <c r="F197" s="8">
+      <c r="F197" s="20">
         <f>IF(E197&lt;&gt;"",E197,IF(UPPER(TRIM(C197))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C197))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C197))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C197))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C197))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G197" s="8">
+      <c r="G197" s="20">
         <f>IF(A197="","",N197)</f>
         <v/>
       </c>
-      <c r="H197" s="8">
+      <c r="H197" s="20">
         <f>IF(A197="","",Inputs!$B$3/((IF(G197="",Inputs!$B$14,G197)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I197" s="8">
+      <c r="I197" s="20">
         <f>IF(A197="","",2.78E-7*F197*D197*H197)</f>
         <v/>
       </c>
       <c r="J197" s="4" t="n"/>
       <c r="K197" s="4" t="n"/>
       <c r="L197" s="5" t="n"/>
-      <c r="M197" s="9">
+      <c r="M197" s="20">
         <f>IF(A197="","",IF(OR(J197="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J197,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N197" s="9">
+      <c r="N197" s="20">
         <f>IF(A197="","",IF(L197="",Inputs!$B$14,L197)+M197)</f>
         <v/>
       </c>
@@ -10020,30 +10059,30 @@
       <c r="C198" s="4" t="n"/>
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
-      <c r="F198" s="8">
+      <c r="F198" s="20">
         <f>IF(E198&lt;&gt;"",E198,IF(UPPER(TRIM(C198))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C198))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C198))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C198))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C198))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G198" s="8">
+      <c r="G198" s="20">
         <f>IF(A198="","",N198)</f>
         <v/>
       </c>
-      <c r="H198" s="8">
+      <c r="H198" s="20">
         <f>IF(A198="","",Inputs!$B$3/((IF(G198="",Inputs!$B$14,G198)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I198" s="8">
+      <c r="I198" s="20">
         <f>IF(A198="","",2.78E-7*F198*D198*H198)</f>
         <v/>
       </c>
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="5" t="n"/>
-      <c r="M198" s="9">
+      <c r="M198" s="20">
         <f>IF(A198="","",IF(OR(J198="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J198,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N198" s="9">
+      <c r="N198" s="20">
         <f>IF(A198="","",IF(L198="",Inputs!$B$14,L198)+M198)</f>
         <v/>
       </c>
@@ -10054,30 +10093,30 @@
       <c r="C199" s="4" t="n"/>
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
-      <c r="F199" s="8">
+      <c r="F199" s="20">
         <f>IF(E199&lt;&gt;"",E199,IF(UPPER(TRIM(C199))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C199))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C199))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C199))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C199))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G199" s="8">
+      <c r="G199" s="20">
         <f>IF(A199="","",N199)</f>
         <v/>
       </c>
-      <c r="H199" s="8">
+      <c r="H199" s="20">
         <f>IF(A199="","",Inputs!$B$3/((IF(G199="",Inputs!$B$14,G199)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I199" s="8">
+      <c r="I199" s="20">
         <f>IF(A199="","",2.78E-7*F199*D199*H199)</f>
         <v/>
       </c>
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="5" t="n"/>
-      <c r="M199" s="9">
+      <c r="M199" s="20">
         <f>IF(A199="","",IF(OR(J199="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J199,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N199" s="9">
+      <c r="N199" s="20">
         <f>IF(A199="","",IF(L199="",Inputs!$B$14,L199)+M199)</f>
         <v/>
       </c>
@@ -10088,30 +10127,30 @@
       <c r="C200" s="4" t="n"/>
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
-      <c r="F200" s="8">
+      <c r="F200" s="20">
         <f>IF(E200&lt;&gt;"",E200,IF(UPPER(TRIM(C200))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C200))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C200))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C200))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C200))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G200" s="8">
+      <c r="G200" s="20">
         <f>IF(A200="","",N200)</f>
         <v/>
       </c>
-      <c r="H200" s="8">
+      <c r="H200" s="20">
         <f>IF(A200="","",Inputs!$B$3/((IF(G200="",Inputs!$B$14,G200)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I200" s="8">
+      <c r="I200" s="20">
         <f>IF(A200="","",2.78E-7*F200*D200*H200)</f>
         <v/>
       </c>
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="5" t="n"/>
-      <c r="M200" s="9">
+      <c r="M200" s="20">
         <f>IF(A200="","",IF(OR(J200="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J200,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N200" s="9">
+      <c r="N200" s="20">
         <f>IF(A200="","",IF(L200="",Inputs!$B$14,L200)+M200)</f>
         <v/>
       </c>
@@ -10122,30 +10161,30 @@
       <c r="C201" s="4" t="n"/>
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
-      <c r="F201" s="8">
+      <c r="F201" s="20">
         <f>IF(E201&lt;&gt;"",E201,IF(UPPER(TRIM(C201))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C201))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C201))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C201))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C201))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G201" s="8">
+      <c r="G201" s="20">
         <f>IF(A201="","",N201)</f>
         <v/>
       </c>
-      <c r="H201" s="8">
+      <c r="H201" s="20">
         <f>IF(A201="","",Inputs!$B$3/((IF(G201="",Inputs!$B$14,G201)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I201" s="8">
+      <c r="I201" s="20">
         <f>IF(A201="","",2.78E-7*F201*D201*H201)</f>
         <v/>
       </c>
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="5" t="n"/>
-      <c r="M201" s="9">
+      <c r="M201" s="20">
         <f>IF(A201="","",IF(OR(J201="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J201,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N201" s="9">
+      <c r="N201" s="20">
         <f>IF(A201="","",IF(L201="",Inputs!$B$14,L201)+M201)</f>
         <v/>
       </c>
@@ -10156,30 +10195,30 @@
       <c r="C202" s="4" t="n"/>
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
-      <c r="F202" s="8">
+      <c r="F202" s="20">
         <f>IF(E202&lt;&gt;"",E202,IF(UPPER(TRIM(C202))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C202))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C202))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C202))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C202))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G202" s="8">
+      <c r="G202" s="20">
         <f>IF(A202="","",N202)</f>
         <v/>
       </c>
-      <c r="H202" s="8">
+      <c r="H202" s="20">
         <f>IF(A202="","",Inputs!$B$3/((IF(G202="",Inputs!$B$14,G202)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I202" s="8">
+      <c r="I202" s="20">
         <f>IF(A202="","",2.78E-7*F202*D202*H202)</f>
         <v/>
       </c>
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="5" t="n"/>
-      <c r="M202" s="9">
+      <c r="M202" s="20">
         <f>IF(A202="","",IF(OR(J202="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J202,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N202" s="9">
+      <c r="N202" s="20">
         <f>IF(A202="","",IF(L202="",Inputs!$B$14,L202)+M202)</f>
         <v/>
       </c>
@@ -10190,30 +10229,30 @@
       <c r="C203" s="4" t="n"/>
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
-      <c r="F203" s="8">
+      <c r="F203" s="20">
         <f>IF(E203&lt;&gt;"",E203,IF(UPPER(TRIM(C203))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C203))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C203))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C203))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C203))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G203" s="8">
+      <c r="G203" s="20">
         <f>IF(A203="","",N203)</f>
         <v/>
       </c>
-      <c r="H203" s="8">
+      <c r="H203" s="20">
         <f>IF(A203="","",Inputs!$B$3/((IF(G203="",Inputs!$B$14,G203)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I203" s="8">
+      <c r="I203" s="20">
         <f>IF(A203="","",2.78E-7*F203*D203*H203)</f>
         <v/>
       </c>
       <c r="J203" s="4" t="n"/>
       <c r="K203" s="4" t="n"/>
       <c r="L203" s="5" t="n"/>
-      <c r="M203" s="9">
+      <c r="M203" s="20">
         <f>IF(A203="","",IF(OR(J203="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J203,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N203" s="9">
+      <c r="N203" s="20">
         <f>IF(A203="","",IF(L203="",Inputs!$B$14,L203)+M203)</f>
         <v/>
       </c>
@@ -10224,30 +10263,30 @@
       <c r="C204" s="4" t="n"/>
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
-      <c r="F204" s="8">
+      <c r="F204" s="20">
         <f>IF(E204&lt;&gt;"",E204,IF(UPPER(TRIM(C204))="BASIN",IF(UPPER(TRIM(Inputs!$B$52))="YES",Inputs!$B$12,0),IF(UPPER(TRIM(C204))="ROOF",Inputs!$B$10,IF(UPPER(TRIM(C204))="PAVAGE",Inputs!$B$58,IF(UPPER(TRIM(C204))="TRESFOND",Inputs!$B$11,IF(UPPER(TRIM(C204))="GRASS",Inputs!$B$12,Inputs!$B$13))))))</f>
         <v/>
       </c>
-      <c r="G204" s="8">
+      <c r="G204" s="20">
         <f>IF(A204="","",N204)</f>
         <v/>
       </c>
-      <c r="H204" s="8">
+      <c r="H204" s="20">
         <f>IF(A204="","",Inputs!$B$3/((IF(G204="",Inputs!$B$14,G204)+Inputs!$B$4)^Inputs!$B$5))</f>
         <v/>
       </c>
-      <c r="I204" s="8">
+      <c r="I204" s="20">
         <f>IF(A204="","",2.78E-7*F204*D204*H204)</f>
         <v/>
       </c>
       <c r="J204" s="4" t="n"/>
       <c r="K204" s="4" t="n"/>
       <c r="L204" s="5" t="n"/>
-      <c r="M204" s="9">
+      <c r="M204" s="20">
         <f>IF(A204="","",IF(OR(J204="",Inputs!$B$59=""),0,IFERROR(INDEX(Elements_hybrides!$F$4:$F$204,MATCH(J204,Elements_hybrides!$A$4:$A$204,0))/(Inputs!$B$59*60),0)))</f>
         <v/>
       </c>
-      <c r="N204" s="9">
+      <c r="N204" s="20">
         <f>IF(A204="","",IF(L204="",Inputs!$B$14,L204)+M204)</f>
         <v/>
       </c>
@@ -39692,7 +39731,7 @@
           <t>Total_zone_Q_peak_m3s</t>
         </is>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="20">
         <f>SUM(Zones_tributaires!$I$4:$I$204)</f>
         <v/>
       </c>
@@ -39703,7 +39742,7 @@
           <t>Total_storage_elements_m3</t>
         </is>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="20">
         <f>SUM(Elements_hybrides!$Z$4:$Z$204)</f>
         <v/>
       </c>
@@ -39714,7 +39753,7 @@
           <t>Retention_node_storage_m3</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="20">
         <f>IFERROR(INDEX(Noeuds_stockage!$I$4:$I$204,MATCH("BASIN_RET",Noeuds_stockage!$A$4:$A$204,0)),"")</f>
         <v/>
       </c>
@@ -39725,7 +39764,7 @@
           <t>Impervious_area_total_m2 (ROOF+PAVAGE+TRESFOND)</t>
         </is>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="21">
         <f>SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"ROOF")+SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"PAVAGE")+SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"TRESFOND")</f>
         <v/>
       </c>
@@ -39736,7 +39775,7 @@
           <t>Grass_area_total_m2</t>
         </is>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="21">
         <f>SUMIFS(Zones_tributaires!$D$4:$D$204,Zones_tributaires!$C$4:$C$204,"GRASS")</f>
         <v/>
       </c>
@@ -39747,7 +39786,7 @@
           <t>Impervious_fraction_of_(impervious+grass)</t>
         </is>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="21">
         <f>IF((B10+B11)=0,"",B10/(B10+B11))</f>
         <v/>
       </c>
